--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B7CEACA-F814-435D-8509-26BA62519F68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4214B6A4-FF41-46D4-B106-B611A9940C9B}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3196" uniqueCount="1101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3207" uniqueCount="1105">
   <si>
     <t>Id</t>
   </si>
@@ -3339,6 +3339,18 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/7ced95dd-e67a-4204-bf7b-e44ce5fa9968_Starbucks%20Valle%20Dora.jpeg</t>
+  </si>
+  <si>
+    <t>Validacion Horario Festivo Sep 26</t>
+  </si>
+  <si>
+    <t>09:00 p. m.</t>
+  </si>
+  <si>
+    <t>10:00 a. m.</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17893447697313410038252777551976_Enrique%20Cesar%20Flores.jpg</t>
   </si>
 </sst>
 </file>
@@ -3477,8 +3489,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB713" totalsRowShown="0">
-  <autoFilter ref="A1:AB713" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB715" totalsRowShown="0">
+  <autoFilter ref="A1:AB715" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="25">
       <extLst>
@@ -3680,7 +3692,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="716" latestEventMarker="1040">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="718" latestEventMarker="1042">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4012,7 +4024,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB713"/>
+  <dimension ref="A1:AB715"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="28" width="20" bestFit="1" customWidth="1"/>
@@ -34698,6 +34710,104 @@
       <c r="AA713" s="1"/>
       <c r="AB713" s="1"/>
     </row>
+    <row r="714" spans="1:28">
+      <c r="A714" s="3">
+        <v>717</v>
+      </c>
+      <c r="B714" s="2">
+        <v>46278.758564814802</v>
+      </c>
+      <c r="C714" s="2">
+        <v>46278.759131944404</v>
+      </c>
+      <c r="D714" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E714" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F714" s="3">
+        <v>38371</v>
+      </c>
+      <c r="G714" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H714" s="1"/>
+      <c r="I714" s="1"/>
+      <c r="J714" s="1"/>
+      <c r="K714" s="1"/>
+      <c r="L714" s="1"/>
+      <c r="M714" s="1"/>
+      <c r="N714" s="1"/>
+      <c r="O714" s="1"/>
+      <c r="P714" s="1"/>
+      <c r="Q714" s="1"/>
+      <c r="R714" s="1"/>
+      <c r="S714" s="1"/>
+      <c r="T714" s="1"/>
+      <c r="U714" s="1"/>
+      <c r="V714" s="4"/>
+      <c r="W714" s="4"/>
+      <c r="X714" s="1"/>
+      <c r="Y714" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="Z714" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="AA714" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="AB714" s="1" t="s">
+        <v>1104</v>
+      </c>
+    </row>
+    <row r="715" spans="1:28">
+      <c r="A715" s="3">
+        <v>718</v>
+      </c>
+      <c r="B715" s="2">
+        <v>46278.759143518502</v>
+      </c>
+      <c r="C715" s="2">
+        <v>46278.759375000001</v>
+      </c>
+      <c r="D715" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="E715" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="F715" s="3">
+        <v>38119</v>
+      </c>
+      <c r="G715" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="H715" s="1"/>
+      <c r="I715" s="1"/>
+      <c r="J715" s="1"/>
+      <c r="K715" s="1"/>
+      <c r="L715" s="1"/>
+      <c r="M715" s="1"/>
+      <c r="N715" s="1"/>
+      <c r="O715" s="1"/>
+      <c r="P715" s="1"/>
+      <c r="Q715" s="1"/>
+      <c r="R715" s="1"/>
+      <c r="S715" s="1"/>
+      <c r="T715" s="1"/>
+      <c r="U715" s="1"/>
+      <c r="V715" s="4"/>
+      <c r="W715" s="4"/>
+      <c r="X715" s="1"/>
+      <c r="Y715" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="Z715" s="1"/>
+      <c r="AA715" s="1"/>
+      <c r="AB715" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ref0f487e050b4029"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R96bb80a497c84e93"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -35974,121 +35974,17 @@
       <x:c r="AD713"/>
       <x:c r="AE713"/>
     </x:row>
-    <x:row r="714">
-      <x:c r="A714" t="n">
-        <x:v>717</x:v>
-      </x:c>
-      <x:c r="B714" t="n">
-        <x:v>46278.7585648148</x:v>
-      </x:c>
-      <x:c r="C714" t="n">
-        <x:v>46278.7591319444</x:v>
-      </x:c>
-      <x:c r="D714" t="str">
-        <x:v>enrique.cesar@starbucks.com.mx</x:v>
-      </x:c>
-      <x:c r="E714" t="str">
-        <x:v>Enrique Cesar Flores</x:v>
-      </x:c>
-      <x:c r="F714"/>
-      <x:c r="G714" t="n">
-        <x:v>38371</x:v>
-      </x:c>
-      <x:c r="H714" t="str">
-        <x:v>Validacion Horario Festivo Sep 26</x:v>
-      </x:c>
-      <x:c r="I714"/>
-      <x:c r="J714"/>
-      <x:c r="K714"/>
-      <x:c r="L714"/>
-      <x:c r="M714"/>
-      <x:c r="N714"/>
-      <x:c r="O714"/>
-      <x:c r="P714"/>
-      <x:c r="Q714"/>
-      <x:c r="R714"/>
-      <x:c r="S714"/>
-      <x:c r="T714"/>
-      <x:c r="U714"/>
-      <x:c r="V714"/>
-      <x:c r="W714"/>
-      <x:c r="X714"/>
-      <x:c r="Y714"/>
-      <x:c r="Z714"/>
-      <x:c r="AA714"/>
-      <x:c r="AB714" t="str">
-        <x:v>Si</x:v>
-      </x:c>
-      <x:c r="AC714" t="str">
-        <x:v>09:00 p. m.</x:v>
-      </x:c>
-      <x:c r="AD714" t="str">
-        <x:v>10:00 a. m.</x:v>
-      </x:c>
-      <x:c r="AE714" t="str">
-        <x:v>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17893447697313410038252777551976_Enrique%20Cesar%20Flores.jpg</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="715">
-      <x:c r="A715" t="n">
-        <x:v>718</x:v>
-      </x:c>
-      <x:c r="B715" t="n">
-        <x:v>46278.7591435185</x:v>
-      </x:c>
-      <x:c r="C715" t="n">
-        <x:v>46278.759375</x:v>
-      </x:c>
-      <x:c r="D715" t="str">
-        <x:v>enrique.cesar@starbucks.com.mx</x:v>
-      </x:c>
-      <x:c r="E715" t="str">
-        <x:v>Enrique Cesar Flores</x:v>
-      </x:c>
-      <x:c r="F715"/>
-      <x:c r="G715" t="n">
-        <x:v>38119</x:v>
-      </x:c>
-      <x:c r="H715" t="str">
-        <x:v>Validacion Horario Festivo Sep 26</x:v>
-      </x:c>
-      <x:c r="I715"/>
-      <x:c r="J715"/>
-      <x:c r="K715"/>
-      <x:c r="L715"/>
-      <x:c r="M715"/>
-      <x:c r="N715"/>
-      <x:c r="O715"/>
-      <x:c r="P715"/>
-      <x:c r="Q715"/>
-      <x:c r="R715"/>
-      <x:c r="S715"/>
-      <x:c r="T715"/>
-      <x:c r="U715"/>
-      <x:c r="V715"/>
-      <x:c r="W715"/>
-      <x:c r="X715"/>
-      <x:c r="Y715"/>
-      <x:c r="Z715"/>
-      <x:c r="AA715"/>
-      <x:c r="AB715" t="str">
-        <x:v>No</x:v>
-      </x:c>
-      <x:c r="AC715"/>
-      <x:c r="AD715"/>
-      <x:c r="AE715"/>
-    </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="Rb40b8577fc534f1a"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="Ra7c44d0c4f0f4ec6"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="R567fe3f7aacc4c67"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="R177bc0b7a07a4aa8"/>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="Rae9b890de05843d7"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="Rfbc2eae78df04482"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="M50" r:id="R5c4232d6cd964c93"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I82" r:id="Rfef8f2ac3bd148c6"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S132" r:id="R238cd5305bd8464d"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="S136" r:id="R433e019da6734fc6"/>
   </x:hyperlinks>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re1c8da1e573b4a3b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf720171e92cc4f11"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A24F9B0A-5E4C-428B-865D-662988D2A7FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="60" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{90DA6279-CD7E-4E93-884B-E89C18D56283}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A53449FD-0545-4032-A92F-279C003034CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C54CF5B2-CE1B-4548-9E36-7B116ECD1B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26034,7 +26034,7 @@
         <v>211</v>
       </c>
       <c r="F514">
-        <v>388445</v>
+        <v>38845</v>
       </c>
       <c r="G514" s="1" t="s">
         <v>102</v>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C54CF5B2-CE1B-4548-9E36-7B116ECD1B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5623EFD9-7B04-4A1C-BD22-D626D232AEC6}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3141" uniqueCount="1098">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="1105">
   <si>
     <t>Id</t>
   </si>
@@ -3330,6 +3330,27 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Galerias%20P.jpg</t>
+  </si>
+  <si>
+    <t>09:00 p. m.</t>
+  </si>
+  <si>
+    <t>09:00 a. m.</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/WhatsApp%20Image%202026-09-14%20at%2012.19.02%20PM_Starbucks%20Cosmopol.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894098786624170437606810729851_Ramon%20Espinosa%20Macia.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894103186815180756369685527455_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/88602217-3b47-41c4-8327-3737ba7d5f5d_Starbucks%20Echegaray.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/17894104465239153539716206541114_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
   </si>
 </sst>
 </file>
@@ -3374,12 +3395,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -3478,8 +3500,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB698" totalsRowShown="0">
-  <autoFilter ref="A1:AB698" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB706" totalsRowShown="0">
+  <autoFilter ref="A1:AB706" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="25">
       <extLst>
@@ -3681,7 +3703,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="719" latestEventMarker="1043">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="727" latestEventMarker="1051">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4013,7 +4035,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB698"/>
+  <dimension ref="A1:AB706"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -34979,6 +35001,392 @@
         <v>1097</v>
       </c>
     </row>
+    <row r="699" spans="1:28">
+      <c r="A699" s="5">
+        <v>720</v>
+      </c>
+      <c r="B699" s="2">
+        <v>46279.513425925899</v>
+      </c>
+      <c r="C699" s="2">
+        <v>46279.513749999998</v>
+      </c>
+      <c r="D699" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E699" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F699" s="5">
+        <v>38197</v>
+      </c>
+      <c r="G699" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H699" s="1"/>
+      <c r="I699" s="1"/>
+      <c r="J699" s="1"/>
+      <c r="K699" s="1"/>
+      <c r="L699" s="1"/>
+      <c r="M699" s="1"/>
+      <c r="N699" s="1"/>
+      <c r="O699" s="1"/>
+      <c r="P699" s="1"/>
+      <c r="Q699" s="1"/>
+      <c r="R699" s="1"/>
+      <c r="S699" s="1"/>
+      <c r="T699" s="1"/>
+      <c r="U699" s="1"/>
+      <c r="V699" s="3"/>
+      <c r="W699" s="3"/>
+      <c r="X699" s="1"/>
+      <c r="Y699" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z699" s="1"/>
+      <c r="AA699" s="1"/>
+      <c r="AB699" s="1"/>
+    </row>
+    <row r="700" spans="1:28">
+      <c r="A700" s="5">
+        <v>721</v>
+      </c>
+      <c r="B700" s="2">
+        <v>46279.508773148104</v>
+      </c>
+      <c r="C700" s="2">
+        <v>46279.514016203699</v>
+      </c>
+      <c r="D700" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="E700" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="F700" s="5">
+        <v>38604</v>
+      </c>
+      <c r="G700" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H700" s="1"/>
+      <c r="I700" s="1"/>
+      <c r="J700" s="1"/>
+      <c r="K700" s="1"/>
+      <c r="L700" s="1"/>
+      <c r="M700" s="1"/>
+      <c r="N700" s="1"/>
+      <c r="O700" s="1"/>
+      <c r="P700" s="1"/>
+      <c r="Q700" s="1"/>
+      <c r="R700" s="1"/>
+      <c r="S700" s="1"/>
+      <c r="T700" s="1"/>
+      <c r="U700" s="1"/>
+      <c r="V700" s="3"/>
+      <c r="W700" s="3"/>
+      <c r="X700" s="1"/>
+      <c r="Y700" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z700" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA700" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB700" s="1" t="s">
+        <v>1100</v>
+      </c>
+    </row>
+    <row r="701" spans="1:28">
+      <c r="A701" s="5">
+        <v>722</v>
+      </c>
+      <c r="B701" s="2">
+        <v>46279.510960648098</v>
+      </c>
+      <c r="C701" s="2">
+        <v>46279.515497685199</v>
+      </c>
+      <c r="D701" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E701" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F701" s="5">
+        <v>38456</v>
+      </c>
+      <c r="G701" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H701" s="1"/>
+      <c r="I701" s="1"/>
+      <c r="J701" s="1"/>
+      <c r="K701" s="1"/>
+      <c r="L701" s="1"/>
+      <c r="M701" s="1"/>
+      <c r="N701" s="1"/>
+      <c r="O701" s="1"/>
+      <c r="P701" s="1"/>
+      <c r="Q701" s="1"/>
+      <c r="R701" s="1"/>
+      <c r="S701" s="1"/>
+      <c r="T701" s="1"/>
+      <c r="U701" s="1"/>
+      <c r="V701" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="W701" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="X701" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="Y701" s="1"/>
+      <c r="Z701" s="1"/>
+      <c r="AA701" s="1"/>
+      <c r="AB701" s="1"/>
+    </row>
+    <row r="702" spans="1:28">
+      <c r="A702" s="5">
+        <v>723</v>
+      </c>
+      <c r="B702" s="2">
+        <v>46279.517129629603</v>
+      </c>
+      <c r="C702" s="2">
+        <v>46279.518240740697</v>
+      </c>
+      <c r="D702" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E702" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F702" s="5">
+        <v>38475</v>
+      </c>
+      <c r="G702" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H702" s="1"/>
+      <c r="I702" s="1"/>
+      <c r="J702" s="1"/>
+      <c r="K702" s="1"/>
+      <c r="L702" s="1"/>
+      <c r="M702" s="1"/>
+      <c r="N702" s="1"/>
+      <c r="O702" s="1"/>
+      <c r="P702" s="1"/>
+      <c r="Q702" s="1"/>
+      <c r="R702" s="1"/>
+      <c r="S702" s="1"/>
+      <c r="T702" s="1"/>
+      <c r="U702" s="1"/>
+      <c r="V702" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="W702" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="X702" s="1" t="s">
+        <v>1102</v>
+      </c>
+      <c r="Y702" s="1"/>
+      <c r="Z702" s="1"/>
+      <c r="AA702" s="1"/>
+      <c r="AB702" s="1"/>
+    </row>
+    <row r="703" spans="1:28">
+      <c r="A703" s="5">
+        <v>724</v>
+      </c>
+      <c r="B703" s="2">
+        <v>46279.513796296298</v>
+      </c>
+      <c r="C703" s="2">
+        <v>46279.518773148098</v>
+      </c>
+      <c r="D703" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="E703" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="F703" s="5">
+        <v>38197</v>
+      </c>
+      <c r="G703" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H703" s="1"/>
+      <c r="I703" s="1"/>
+      <c r="J703" s="1"/>
+      <c r="K703" s="1"/>
+      <c r="L703" s="1"/>
+      <c r="M703" s="1"/>
+      <c r="N703" s="1"/>
+      <c r="O703" s="1"/>
+      <c r="P703" s="1"/>
+      <c r="Q703" s="1"/>
+      <c r="R703" s="1"/>
+      <c r="S703" s="1"/>
+      <c r="T703" s="1"/>
+      <c r="U703" s="1"/>
+      <c r="V703" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="W703" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="X703" s="1" t="s">
+        <v>1103</v>
+      </c>
+      <c r="Y703" s="1"/>
+      <c r="Z703" s="1"/>
+      <c r="AA703" s="1"/>
+      <c r="AB703" s="1"/>
+    </row>
+    <row r="704" spans="1:28">
+      <c r="A704" s="5">
+        <v>725</v>
+      </c>
+      <c r="B704" s="2">
+        <v>46279.518472222197</v>
+      </c>
+      <c r="C704" s="2">
+        <v>46279.519375000003</v>
+      </c>
+      <c r="D704" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E704" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F704" s="5">
+        <v>38475</v>
+      </c>
+      <c r="G704" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H704" s="1"/>
+      <c r="I704" s="1"/>
+      <c r="J704" s="1"/>
+      <c r="K704" s="1"/>
+      <c r="L704" s="1"/>
+      <c r="M704" s="1"/>
+      <c r="N704" s="1"/>
+      <c r="O704" s="1"/>
+      <c r="P704" s="1"/>
+      <c r="Q704" s="1"/>
+      <c r="R704" s="1"/>
+      <c r="S704" s="1"/>
+      <c r="T704" s="1"/>
+      <c r="U704" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="V704" s="3"/>
+      <c r="W704" s="3"/>
+      <c r="X704" s="1"/>
+      <c r="Y704" s="1"/>
+      <c r="Z704" s="1"/>
+      <c r="AA704" s="1"/>
+      <c r="AB704" s="1"/>
+    </row>
+    <row r="705" spans="1:28">
+      <c r="A705" s="5">
+        <v>726</v>
+      </c>
+      <c r="B705" s="2">
+        <v>46279.520046296297</v>
+      </c>
+      <c r="C705" s="2">
+        <v>46279.520289351902</v>
+      </c>
+      <c r="D705" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E705" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F705" s="5">
+        <v>38475</v>
+      </c>
+      <c r="G705" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H705" s="1"/>
+      <c r="I705" s="1"/>
+      <c r="J705" s="1"/>
+      <c r="K705" s="1"/>
+      <c r="L705" s="1"/>
+      <c r="M705" s="1"/>
+      <c r="N705" s="1"/>
+      <c r="O705" s="1"/>
+      <c r="P705" s="1"/>
+      <c r="Q705" s="1"/>
+      <c r="R705" s="1"/>
+      <c r="S705" s="1"/>
+      <c r="T705" s="1"/>
+      <c r="U705" s="1"/>
+      <c r="V705" s="3"/>
+      <c r="W705" s="3"/>
+      <c r="X705" s="1"/>
+      <c r="Y705" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z705" s="1"/>
+      <c r="AA705" s="1"/>
+      <c r="AB705" s="1"/>
+    </row>
+    <row r="706" spans="1:28">
+      <c r="A706" s="5">
+        <v>727</v>
+      </c>
+      <c r="B706" s="2">
+        <v>46279.525763888902</v>
+      </c>
+      <c r="C706" s="2">
+        <v>46279.526030092602</v>
+      </c>
+      <c r="D706" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E706" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="F706" s="5">
+        <v>38117</v>
+      </c>
+      <c r="G706" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H706" s="1"/>
+      <c r="I706" s="1"/>
+      <c r="J706" s="1"/>
+      <c r="K706" s="1"/>
+      <c r="L706" s="1"/>
+      <c r="M706" s="1"/>
+      <c r="N706" s="1"/>
+      <c r="O706" s="1"/>
+      <c r="P706" s="1"/>
+      <c r="Q706" s="1"/>
+      <c r="R706" s="1"/>
+      <c r="S706" s="1"/>
+      <c r="T706" s="1"/>
+      <c r="U706" s="1"/>
+      <c r="V706" s="3"/>
+      <c r="W706" s="3"/>
+      <c r="X706" s="1"/>
+      <c r="Y706" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z706" s="1"/>
+      <c r="AA706" s="1"/>
+      <c r="AB706" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S71" r:id="rId1" xr:uid="{DBEDA7D9-6C97-43FD-AB0F-DEBA1D8AA177}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="76" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5623EFD9-7B04-4A1C-BD22-D626D232AEC6}"/>
+  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8A731A9-30C7-44C7-B005-E709145E1B68}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3182" uniqueCount="1105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3305" uniqueCount="1139">
   <si>
     <t>Id</t>
   </si>
@@ -3351,6 +3351,108 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/17894104465239153539716206541114_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+  </si>
+  <si>
+    <t>07:00 a. m.</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Maria%20Teresa%20Espinoz.jpg</t>
+  </si>
+  <si>
+    <t>07:30 a. m.</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Metepec%20Pl.jpg</t>
+  </si>
+  <si>
+    <t>10:00 a. m.</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_20260914_160250239_HDR_Francisco%20Manuel%20Gon.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/IMG_2952_Starbucks%20Tlalnepant.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_2968_Starbucks%20Tlalnepant.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894240908491121633773774908313_Starbucks%20Portal%20San.jpg</t>
+  </si>
+  <si>
+    <t>karina.hernandez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Karina Anahi Hernandez Landin</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/6bc2dc23-d39f-45c7-a5e9-1b96d7c69a1f_Karina%20Anahi%20Hernand.jpeg</t>
+  </si>
+  <si>
+    <t>raul.alvarez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Raúl Eduardo Álvarez Vázquez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Ra%C3%BAl%20Eduardo%20%C3%81lvarez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Axomiatla.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG-20260914-WA0186_Starbucks%20Torre%20Virr.jpg</t>
+  </si>
+  <si>
+    <t>09:30 p. m.</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894247690178233286585894695438_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG-20260914-WA0041_Starbucks%20Parque%20Dur.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894250934056603675822650146808_Fernando%20Axel%20Velasc.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Jes%C3%BAs%20Alberto%20Alquic.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG20260914163435_Starbucks%20Centro%20M%C3%A9d.jpg</t>
+  </si>
+  <si>
+    <t>perla.franco@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Perla Franco Brito</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_20260914_165513_Perla%20Franco%20Brito.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38798@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Corporativo Televisa Santa Fe</t>
+  </si>
+  <si>
+    <t>Sin Modificacion Cierre</t>
+  </si>
+  <si>
+    <t>Sin Modificacion Apertura</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/WhatsApp%20Image%202026-09-14%20at%204.56.21%20PM_Starbucks%20Corporativ.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43147@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Juarez 70 Core</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_4851_Starbucks%20Juarez%2070.jpeg</t>
   </si>
 </sst>
 </file>
@@ -3500,8 +3602,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB706" totalsRowShown="0">
-  <autoFilter ref="A1:AB706" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB724" totalsRowShown="0">
+  <autoFilter ref="A1:AB724" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="25">
       <extLst>
@@ -3703,7 +3805,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="727" latestEventMarker="1051">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="745" latestEventMarker="1069">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4035,7 +4137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB706"/>
+  <dimension ref="A1:AB724"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -35002,7 +35104,7 @@
       </c>
     </row>
     <row r="699" spans="1:28">
-      <c r="A699" s="5">
+      <c r="A699">
         <v>720</v>
       </c>
       <c r="B699" s="2">
@@ -35017,7 +35119,7 @@
       <c r="E699" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F699" s="5">
+      <c r="F699">
         <v>38197</v>
       </c>
       <c r="G699" s="1" t="s">
@@ -35048,7 +35150,7 @@
       <c r="AB699" s="1"/>
     </row>
     <row r="700" spans="1:28">
-      <c r="A700" s="5">
+      <c r="A700">
         <v>721</v>
       </c>
       <c r="B700" s="2">
@@ -35063,7 +35165,7 @@
       <c r="E700" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="F700" s="5">
+      <c r="F700">
         <v>38604</v>
       </c>
       <c r="G700" s="1" t="s">
@@ -35100,7 +35202,7 @@
       </c>
     </row>
     <row r="701" spans="1:28">
-      <c r="A701" s="5">
+      <c r="A701">
         <v>722</v>
       </c>
       <c r="B701" s="2">
@@ -35115,7 +35217,7 @@
       <c r="E701" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F701" s="5">
+      <c r="F701">
         <v>38456</v>
       </c>
       <c r="G701" s="1" t="s">
@@ -35150,7 +35252,7 @@
       <c r="AB701" s="1"/>
     </row>
     <row r="702" spans="1:28">
-      <c r="A702" s="5">
+      <c r="A702">
         <v>723</v>
       </c>
       <c r="B702" s="2">
@@ -35165,7 +35267,7 @@
       <c r="E702" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F702" s="5">
+      <c r="F702">
         <v>38475</v>
       </c>
       <c r="G702" s="1" t="s">
@@ -35200,7 +35302,7 @@
       <c r="AB702" s="1"/>
     </row>
     <row r="703" spans="1:28">
-      <c r="A703" s="5">
+      <c r="A703">
         <v>724</v>
       </c>
       <c r="B703" s="2">
@@ -35215,7 +35317,7 @@
       <c r="E703" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="F703" s="5">
+      <c r="F703">
         <v>38197</v>
       </c>
       <c r="G703" s="1" t="s">
@@ -35250,7 +35352,7 @@
       <c r="AB703" s="1"/>
     </row>
     <row r="704" spans="1:28">
-      <c r="A704" s="5">
+      <c r="A704">
         <v>725</v>
       </c>
       <c r="B704" s="2">
@@ -35265,7 +35367,7 @@
       <c r="E704" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F704" s="5">
+      <c r="F704">
         <v>38475</v>
       </c>
       <c r="G704" s="1" t="s">
@@ -35296,7 +35398,7 @@
       <c r="AB704" s="1"/>
     </row>
     <row r="705" spans="1:28">
-      <c r="A705" s="5">
+      <c r="A705">
         <v>726</v>
       </c>
       <c r="B705" s="2">
@@ -35311,7 +35413,7 @@
       <c r="E705" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="F705" s="5">
+      <c r="F705">
         <v>38475</v>
       </c>
       <c r="G705" s="1" t="s">
@@ -35342,7 +35444,7 @@
       <c r="AB705" s="1"/>
     </row>
     <row r="706" spans="1:28">
-      <c r="A706" s="5">
+      <c r="A706">
         <v>727</v>
       </c>
       <c r="B706" s="2">
@@ -35357,7 +35459,7 @@
       <c r="E706" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="F706" s="5">
+      <c r="F706">
         <v>38117</v>
       </c>
       <c r="G706" s="1" t="s">
@@ -35387,6 +35489,936 @@
       <c r="AA706" s="1"/>
       <c r="AB706" s="1"/>
     </row>
+    <row r="707" spans="1:28">
+      <c r="A707" s="5">
+        <v>728</v>
+      </c>
+      <c r="B707" s="2">
+        <v>46279.665763888901</v>
+      </c>
+      <c r="C707" s="2">
+        <v>46279.666747685202</v>
+      </c>
+      <c r="D707" s="1" t="s">
+        <v>971</v>
+      </c>
+      <c r="E707" s="1" t="s">
+        <v>972</v>
+      </c>
+      <c r="F707" s="5">
+        <v>38717</v>
+      </c>
+      <c r="G707" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H707" s="1"/>
+      <c r="I707" s="1"/>
+      <c r="J707" s="1"/>
+      <c r="K707" s="1"/>
+      <c r="L707" s="1"/>
+      <c r="M707" s="1"/>
+      <c r="N707" s="1"/>
+      <c r="O707" s="1"/>
+      <c r="P707" s="1"/>
+      <c r="Q707" s="1"/>
+      <c r="R707" s="1"/>
+      <c r="S707" s="1"/>
+      <c r="T707" s="1"/>
+      <c r="U707" s="1"/>
+      <c r="V707" s="3"/>
+      <c r="W707" s="3"/>
+      <c r="X707" s="1"/>
+      <c r="Y707" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z707" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA707" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB707" s="1" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="708" spans="1:28">
+      <c r="A708" s="5">
+        <v>729</v>
+      </c>
+      <c r="B708" s="2">
+        <v>46279.664953703701</v>
+      </c>
+      <c r="C708" s="2">
+        <v>46279.668668981503</v>
+      </c>
+      <c r="D708" s="1" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E708" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F708" s="5">
+        <v>38441</v>
+      </c>
+      <c r="G708" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H708" s="1"/>
+      <c r="I708" s="1"/>
+      <c r="J708" s="1"/>
+      <c r="K708" s="1"/>
+      <c r="L708" s="1"/>
+      <c r="M708" s="1"/>
+      <c r="N708" s="1"/>
+      <c r="O708" s="1"/>
+      <c r="P708" s="1"/>
+      <c r="Q708" s="1"/>
+      <c r="R708" s="1"/>
+      <c r="S708" s="1"/>
+      <c r="T708" s="1"/>
+      <c r="U708" s="1"/>
+      <c r="V708" s="3"/>
+      <c r="W708" s="3"/>
+      <c r="X708" s="1"/>
+      <c r="Y708" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z708" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA708" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AB708" s="1" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="709" spans="1:28">
+      <c r="A709" s="5">
+        <v>730</v>
+      </c>
+      <c r="B709" s="2">
+        <v>46279.670439814799</v>
+      </c>
+      <c r="C709" s="2">
+        <v>46279.671006944402</v>
+      </c>
+      <c r="D709" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="E709" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="F709" s="5">
+        <v>43068</v>
+      </c>
+      <c r="G709" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H709" s="1"/>
+      <c r="I709" s="1"/>
+      <c r="J709" s="1"/>
+      <c r="K709" s="1"/>
+      <c r="L709" s="1"/>
+      <c r="M709" s="1"/>
+      <c r="N709" s="1"/>
+      <c r="O709" s="1"/>
+      <c r="P709" s="1"/>
+      <c r="Q709" s="1"/>
+      <c r="R709" s="1"/>
+      <c r="S709" s="1"/>
+      <c r="T709" s="1"/>
+      <c r="U709" s="1"/>
+      <c r="V709" s="3"/>
+      <c r="W709" s="3"/>
+      <c r="X709" s="1"/>
+      <c r="Y709" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z709" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA709" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AB709" s="1" t="s">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="710" spans="1:28">
+      <c r="A710" s="5">
+        <v>731</v>
+      </c>
+      <c r="B710" s="2">
+        <v>46279.673553240696</v>
+      </c>
+      <c r="C710" s="2">
+        <v>46279.6739930556</v>
+      </c>
+      <c r="D710" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E710" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F710" s="5">
+        <v>38606</v>
+      </c>
+      <c r="G710" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H710" s="1"/>
+      <c r="I710" s="1"/>
+      <c r="J710" s="1"/>
+      <c r="K710" s="1"/>
+      <c r="L710" s="1"/>
+      <c r="M710" s="1"/>
+      <c r="N710" s="1"/>
+      <c r="O710" s="1"/>
+      <c r="P710" s="1"/>
+      <c r="Q710" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="R710" s="1" t="s">
+        <v>1111</v>
+      </c>
+      <c r="S710" s="1"/>
+      <c r="T710" s="1"/>
+      <c r="U710" s="1"/>
+      <c r="V710" s="3"/>
+      <c r="W710" s="3"/>
+      <c r="X710" s="1"/>
+      <c r="Y710" s="1"/>
+      <c r="Z710" s="1"/>
+      <c r="AA710" s="1"/>
+      <c r="AB710" s="1"/>
+    </row>
+    <row r="711" spans="1:28">
+      <c r="A711" s="5">
+        <v>732</v>
+      </c>
+      <c r="B711" s="2">
+        <v>46279.674143518503</v>
+      </c>
+      <c r="C711" s="2">
+        <v>46279.676215277803</v>
+      </c>
+      <c r="D711" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E711" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F711" s="5">
+        <v>38606</v>
+      </c>
+      <c r="G711" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H711" s="1"/>
+      <c r="I711" s="1"/>
+      <c r="J711" s="1"/>
+      <c r="K711" s="1"/>
+      <c r="L711" s="1"/>
+      <c r="M711" s="1"/>
+      <c r="N711" s="1"/>
+      <c r="O711" s="1"/>
+      <c r="P711" s="1"/>
+      <c r="Q711" s="1"/>
+      <c r="R711" s="1"/>
+      <c r="S711" s="1"/>
+      <c r="T711" s="1"/>
+      <c r="U711" s="1"/>
+      <c r="V711" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="W711" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="X711" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="Y711" s="1"/>
+      <c r="Z711" s="1"/>
+      <c r="AA711" s="1"/>
+      <c r="AB711" s="1"/>
+    </row>
+    <row r="712" spans="1:28">
+      <c r="A712" s="5">
+        <v>733</v>
+      </c>
+      <c r="B712" s="2">
+        <v>46279.676215277803</v>
+      </c>
+      <c r="C712" s="2">
+        <v>46279.677141203698</v>
+      </c>
+      <c r="D712" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="E712" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F712" s="5">
+        <v>38720</v>
+      </c>
+      <c r="G712" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H712" s="1"/>
+      <c r="I712" s="1"/>
+      <c r="J712" s="1"/>
+      <c r="K712" s="1"/>
+      <c r="L712" s="1"/>
+      <c r="M712" s="1"/>
+      <c r="N712" s="1"/>
+      <c r="O712" s="1"/>
+      <c r="P712" s="1"/>
+      <c r="Q712" s="1"/>
+      <c r="R712" s="1"/>
+      <c r="S712" s="1"/>
+      <c r="T712" s="1"/>
+      <c r="U712" s="1"/>
+      <c r="V712" s="3"/>
+      <c r="W712" s="3"/>
+      <c r="X712" s="1"/>
+      <c r="Y712" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z712" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA712" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB712" s="1" t="s">
+        <v>1113</v>
+      </c>
+    </row>
+    <row r="713" spans="1:28">
+      <c r="A713" s="5">
+        <v>734</v>
+      </c>
+      <c r="B713" s="2">
+        <v>46279.677013888897</v>
+      </c>
+      <c r="C713" s="2">
+        <v>46279.677696759303</v>
+      </c>
+      <c r="D713" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="E713" s="1" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F713" s="5">
+        <v>38668</v>
+      </c>
+      <c r="G713" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H713" s="1"/>
+      <c r="I713" s="1"/>
+      <c r="J713" s="1"/>
+      <c r="K713" s="1"/>
+      <c r="L713" s="1"/>
+      <c r="M713" s="1"/>
+      <c r="N713" s="1"/>
+      <c r="O713" s="1"/>
+      <c r="P713" s="1"/>
+      <c r="Q713" s="1"/>
+      <c r="R713" s="1"/>
+      <c r="S713" s="1"/>
+      <c r="T713" s="1"/>
+      <c r="U713" s="1"/>
+      <c r="V713" s="3"/>
+      <c r="W713" s="3"/>
+      <c r="X713" s="1"/>
+      <c r="Y713" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z713" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA713" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB713" s="1" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="714" spans="1:28">
+      <c r="A714" s="5">
+        <v>735</v>
+      </c>
+      <c r="B714" s="2">
+        <v>46279.668680555602</v>
+      </c>
+      <c r="C714" s="2">
+        <v>46279.677743055603</v>
+      </c>
+      <c r="D714" s="1" t="s">
+        <v>1117</v>
+      </c>
+      <c r="E714" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="F714" s="5">
+        <v>38438</v>
+      </c>
+      <c r="G714" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H714" s="1"/>
+      <c r="I714" s="1"/>
+      <c r="J714" s="1"/>
+      <c r="K714" s="1"/>
+      <c r="L714" s="1"/>
+      <c r="M714" s="1"/>
+      <c r="N714" s="1"/>
+      <c r="O714" s="1"/>
+      <c r="P714" s="1"/>
+      <c r="Q714" s="1"/>
+      <c r="R714" s="1"/>
+      <c r="S714" s="1"/>
+      <c r="T714" s="1"/>
+      <c r="U714" s="1"/>
+      <c r="V714" s="3"/>
+      <c r="W714" s="3"/>
+      <c r="X714" s="1"/>
+      <c r="Y714" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z714" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA714" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB714" s="1" t="s">
+        <v>1119</v>
+      </c>
+    </row>
+    <row r="715" spans="1:28">
+      <c r="A715" s="5">
+        <v>736</v>
+      </c>
+      <c r="B715" s="2">
+        <v>46279.674212963</v>
+      </c>
+      <c r="C715" s="2">
+        <v>46279.681516203702</v>
+      </c>
+      <c r="D715" s="1" t="s">
+        <v>968</v>
+      </c>
+      <c r="E715" s="1" t="s">
+        <v>969</v>
+      </c>
+      <c r="F715" s="5">
+        <v>38617</v>
+      </c>
+      <c r="G715" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H715" s="1"/>
+      <c r="I715" s="1"/>
+      <c r="J715" s="1"/>
+      <c r="K715" s="1"/>
+      <c r="L715" s="1"/>
+      <c r="M715" s="1"/>
+      <c r="N715" s="1"/>
+      <c r="O715" s="1"/>
+      <c r="P715" s="1"/>
+      <c r="Q715" s="1"/>
+      <c r="R715" s="1"/>
+      <c r="S715" s="1"/>
+      <c r="T715" s="1"/>
+      <c r="U715" s="1"/>
+      <c r="V715" s="3"/>
+      <c r="W715" s="3"/>
+      <c r="X715" s="1"/>
+      <c r="Y715" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z715" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA715" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB715" s="1" t="s">
+        <v>1120</v>
+      </c>
+    </row>
+    <row r="716" spans="1:28">
+      <c r="A716" s="5">
+        <v>737</v>
+      </c>
+      <c r="B716" s="2">
+        <v>46279.671793981499</v>
+      </c>
+      <c r="C716" s="2">
+        <v>46279.683981481503</v>
+      </c>
+      <c r="D716" s="1" t="s">
+        <v>849</v>
+      </c>
+      <c r="E716" s="1" t="s">
+        <v>850</v>
+      </c>
+      <c r="F716" s="5">
+        <v>38644</v>
+      </c>
+      <c r="G716" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H716" s="1"/>
+      <c r="I716" s="1"/>
+      <c r="J716" s="1"/>
+      <c r="K716" s="1"/>
+      <c r="L716" s="1"/>
+      <c r="M716" s="1"/>
+      <c r="N716" s="1"/>
+      <c r="O716" s="1"/>
+      <c r="P716" s="1"/>
+      <c r="Q716" s="1"/>
+      <c r="R716" s="1"/>
+      <c r="S716" s="1"/>
+      <c r="T716" s="1"/>
+      <c r="U716" s="1"/>
+      <c r="V716" s="3"/>
+      <c r="W716" s="3"/>
+      <c r="X716" s="1"/>
+      <c r="Y716" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z716" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA716" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB716" s="1" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="717" spans="1:28">
+      <c r="A717" s="5">
+        <v>738</v>
+      </c>
+      <c r="B717" s="2">
+        <v>46279.682488425897</v>
+      </c>
+      <c r="C717" s="2">
+        <v>46279.686030092598</v>
+      </c>
+      <c r="D717" s="1" t="s">
+        <v>801</v>
+      </c>
+      <c r="E717" s="1" t="s">
+        <v>802</v>
+      </c>
+      <c r="F717" s="5">
+        <v>38366</v>
+      </c>
+      <c r="G717" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H717" s="1"/>
+      <c r="I717" s="1"/>
+      <c r="J717" s="1"/>
+      <c r="K717" s="1"/>
+      <c r="L717" s="1"/>
+      <c r="M717" s="1"/>
+      <c r="N717" s="1"/>
+      <c r="O717" s="1"/>
+      <c r="P717" s="1"/>
+      <c r="Q717" s="1"/>
+      <c r="R717" s="1"/>
+      <c r="S717" s="1"/>
+      <c r="T717" s="1"/>
+      <c r="U717" s="1"/>
+      <c r="V717" s="3"/>
+      <c r="W717" s="3"/>
+      <c r="X717" s="1"/>
+      <c r="Y717" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z717" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AA717" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB717" s="1" t="s">
+        <v>1123</v>
+      </c>
+    </row>
+    <row r="718" spans="1:28">
+      <c r="A718" s="5">
+        <v>739</v>
+      </c>
+      <c r="B718" s="2">
+        <v>46279.687615740702</v>
+      </c>
+      <c r="C718" s="2">
+        <v>46279.688229166699</v>
+      </c>
+      <c r="D718" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="E718" s="1" t="s">
+        <v>984</v>
+      </c>
+      <c r="F718" s="5">
+        <v>38386</v>
+      </c>
+      <c r="G718" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H718" s="1"/>
+      <c r="I718" s="1"/>
+      <c r="J718" s="1"/>
+      <c r="K718" s="1"/>
+      <c r="L718" s="1"/>
+      <c r="M718" s="1"/>
+      <c r="N718" s="1"/>
+      <c r="O718" s="1"/>
+      <c r="P718" s="1"/>
+      <c r="Q718" s="1"/>
+      <c r="R718" s="1"/>
+      <c r="S718" s="1"/>
+      <c r="T718" s="1"/>
+      <c r="U718" s="1"/>
+      <c r="V718" s="3"/>
+      <c r="W718" s="3"/>
+      <c r="X718" s="1"/>
+      <c r="Y718" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z718" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA718" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB718" s="1" t="s">
+        <v>1124</v>
+      </c>
+    </row>
+    <row r="719" spans="1:28">
+      <c r="A719" s="5">
+        <v>740</v>
+      </c>
+      <c r="B719" s="2">
+        <v>46279.688194444403</v>
+      </c>
+      <c r="C719" s="2">
+        <v>46279.688819444404</v>
+      </c>
+      <c r="D719" s="1" t="s">
+        <v>822</v>
+      </c>
+      <c r="E719" s="1" t="s">
+        <v>823</v>
+      </c>
+      <c r="F719" s="5">
+        <v>38121</v>
+      </c>
+      <c r="G719" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H719" s="1"/>
+      <c r="I719" s="1"/>
+      <c r="J719" s="1"/>
+      <c r="K719" s="1"/>
+      <c r="L719" s="1"/>
+      <c r="M719" s="1"/>
+      <c r="N719" s="1"/>
+      <c r="O719" s="1"/>
+      <c r="P719" s="1"/>
+      <c r="Q719" s="1"/>
+      <c r="R719" s="1"/>
+      <c r="S719" s="1"/>
+      <c r="T719" s="1"/>
+      <c r="U719" s="1"/>
+      <c r="V719" s="3"/>
+      <c r="W719" s="3"/>
+      <c r="X719" s="1"/>
+      <c r="Y719" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z719" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA719" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB719" s="1" t="s">
+        <v>1125</v>
+      </c>
+    </row>
+    <row r="720" spans="1:28">
+      <c r="A720" s="5">
+        <v>741</v>
+      </c>
+      <c r="B720" s="2">
+        <v>46279.668356481503</v>
+      </c>
+      <c r="C720" s="2">
+        <v>46279.690347222197</v>
+      </c>
+      <c r="D720" s="1" t="s">
+        <v>942</v>
+      </c>
+      <c r="E720" s="1" t="s">
+        <v>943</v>
+      </c>
+      <c r="F720" s="5">
+        <v>38532</v>
+      </c>
+      <c r="G720" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H720" s="1"/>
+      <c r="I720" s="1"/>
+      <c r="J720" s="1"/>
+      <c r="K720" s="1"/>
+      <c r="L720" s="1"/>
+      <c r="M720" s="1"/>
+      <c r="N720" s="1"/>
+      <c r="O720" s="1"/>
+      <c r="P720" s="1"/>
+      <c r="Q720" s="1"/>
+      <c r="R720" s="1"/>
+      <c r="S720" s="1"/>
+      <c r="T720" s="1"/>
+      <c r="U720" s="1"/>
+      <c r="V720" s="3"/>
+      <c r="W720" s="3"/>
+      <c r="X720" s="1"/>
+      <c r="Y720" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z720" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA720" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB720" s="1" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="721" spans="1:28">
+      <c r="A721" s="5">
+        <v>742</v>
+      </c>
+      <c r="B721" s="2">
+        <v>46279.6946412037</v>
+      </c>
+      <c r="C721" s="2">
+        <v>46279.696458333303</v>
+      </c>
+      <c r="D721" s="1" t="s">
+        <v>980</v>
+      </c>
+      <c r="E721" s="1" t="s">
+        <v>981</v>
+      </c>
+      <c r="F721" s="5">
+        <v>38400</v>
+      </c>
+      <c r="G721" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H721" s="1"/>
+      <c r="I721" s="1"/>
+      <c r="J721" s="1"/>
+      <c r="K721" s="1"/>
+      <c r="L721" s="1"/>
+      <c r="M721" s="1"/>
+      <c r="N721" s="1"/>
+      <c r="O721" s="1"/>
+      <c r="P721" s="1"/>
+      <c r="Q721" s="1"/>
+      <c r="R721" s="1"/>
+      <c r="S721" s="1"/>
+      <c r="T721" s="1"/>
+      <c r="U721" s="1"/>
+      <c r="V721" s="3"/>
+      <c r="W721" s="3"/>
+      <c r="X721" s="1"/>
+      <c r="Y721" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z721" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA721" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB721" s="1" t="s">
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="722" spans="1:28">
+      <c r="A722" s="5">
+        <v>743</v>
+      </c>
+      <c r="B722" s="2">
+        <v>46279.7051967593</v>
+      </c>
+      <c r="C722" s="2">
+        <v>46279.705462963</v>
+      </c>
+      <c r="D722" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="E722" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="F722" s="5">
+        <v>38512</v>
+      </c>
+      <c r="G722" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H722" s="1"/>
+      <c r="I722" s="1"/>
+      <c r="J722" s="1"/>
+      <c r="K722" s="1"/>
+      <c r="L722" s="1"/>
+      <c r="M722" s="1"/>
+      <c r="N722" s="1"/>
+      <c r="O722" s="1"/>
+      <c r="P722" s="1"/>
+      <c r="Q722" s="1"/>
+      <c r="R722" s="1"/>
+      <c r="S722" s="1"/>
+      <c r="T722" s="1"/>
+      <c r="U722" s="1"/>
+      <c r="V722" s="3"/>
+      <c r="W722" s="3"/>
+      <c r="X722" s="1"/>
+      <c r="Y722" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z722" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA722" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB722" s="1" t="s">
+        <v>1130</v>
+      </c>
+    </row>
+    <row r="723" spans="1:28">
+      <c r="A723" s="5">
+        <v>744</v>
+      </c>
+      <c r="B723" s="2">
+        <v>46279.706840277802</v>
+      </c>
+      <c r="C723" s="2">
+        <v>46279.707534722198</v>
+      </c>
+      <c r="D723" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="E723" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F723" s="5">
+        <v>38798</v>
+      </c>
+      <c r="G723" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H723" s="1"/>
+      <c r="I723" s="1"/>
+      <c r="J723" s="1"/>
+      <c r="K723" s="1"/>
+      <c r="L723" s="1"/>
+      <c r="M723" s="1"/>
+      <c r="N723" s="1"/>
+      <c r="O723" s="1"/>
+      <c r="P723" s="1"/>
+      <c r="Q723" s="1"/>
+      <c r="R723" s="1"/>
+      <c r="S723" s="1"/>
+      <c r="T723" s="1"/>
+      <c r="U723" s="1"/>
+      <c r="V723" s="3"/>
+      <c r="W723" s="3"/>
+      <c r="X723" s="1"/>
+      <c r="Y723" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z723" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AA723" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AB723" s="1" t="s">
+        <v>1135</v>
+      </c>
+    </row>
+    <row r="724" spans="1:28">
+      <c r="A724" s="5">
+        <v>745</v>
+      </c>
+      <c r="B724" s="2">
+        <v>46279.706979166702</v>
+      </c>
+      <c r="C724" s="2">
+        <v>46279.707696759302</v>
+      </c>
+      <c r="D724" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="E724" s="1" t="s">
+        <v>1137</v>
+      </c>
+      <c r="F724" s="5">
+        <v>43147</v>
+      </c>
+      <c r="G724" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H724" s="1"/>
+      <c r="I724" s="1"/>
+      <c r="J724" s="1"/>
+      <c r="K724" s="1"/>
+      <c r="L724" s="1"/>
+      <c r="M724" s="1"/>
+      <c r="N724" s="1"/>
+      <c r="O724" s="1"/>
+      <c r="P724" s="1"/>
+      <c r="Q724" s="1"/>
+      <c r="R724" s="1"/>
+      <c r="S724" s="1"/>
+      <c r="T724" s="1"/>
+      <c r="U724" s="1"/>
+      <c r="V724" s="3"/>
+      <c r="W724" s="3"/>
+      <c r="X724" s="1"/>
+      <c r="Y724" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z724" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA724" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB724" s="1" t="s">
+        <v>1138</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S71" r:id="rId1" xr:uid="{DBEDA7D9-6C97-43FD-AB0F-DEBA1D8AA177}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="79" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D8A731A9-30C7-44C7-B005-E709145E1B68}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1287D537-8DDC-406F-B918-54C1CB362B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3497,13 +3497,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -35490,7 +35489,7 @@
       <c r="AB706" s="1"/>
     </row>
     <row r="707" spans="1:28">
-      <c r="A707" s="5">
+      <c r="A707">
         <v>728</v>
       </c>
       <c r="B707" s="2">
@@ -35505,7 +35504,7 @@
       <c r="E707" s="1" t="s">
         <v>972</v>
       </c>
-      <c r="F707" s="5">
+      <c r="F707">
         <v>38717</v>
       </c>
       <c r="G707" s="1" t="s">
@@ -35542,7 +35541,7 @@
       </c>
     </row>
     <row r="708" spans="1:28">
-      <c r="A708" s="5">
+      <c r="A708">
         <v>729</v>
       </c>
       <c r="B708" s="2">
@@ -35557,7 +35556,7 @@
       <c r="E708" s="1" t="s">
         <v>1009</v>
       </c>
-      <c r="F708" s="5">
+      <c r="F708">
         <v>38441</v>
       </c>
       <c r="G708" s="1" t="s">
@@ -35594,7 +35593,7 @@
       </c>
     </row>
     <row r="709" spans="1:28">
-      <c r="A709" s="5">
+      <c r="A709">
         <v>730</v>
       </c>
       <c r="B709" s="2">
@@ -35609,7 +35608,7 @@
       <c r="E709" s="1" t="s">
         <v>793</v>
       </c>
-      <c r="F709" s="5">
+      <c r="F709">
         <v>43068</v>
       </c>
       <c r="G709" s="1" t="s">
@@ -35646,7 +35645,7 @@
       </c>
     </row>
     <row r="710" spans="1:28">
-      <c r="A710" s="5">
+      <c r="A710">
         <v>731</v>
       </c>
       <c r="B710" s="2">
@@ -35661,7 +35660,7 @@
       <c r="E710" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F710" s="5">
+      <c r="F710">
         <v>38606</v>
       </c>
       <c r="G710" s="1" t="s">
@@ -35694,7 +35693,7 @@
       <c r="AB710" s="1"/>
     </row>
     <row r="711" spans="1:28">
-      <c r="A711" s="5">
+      <c r="A711">
         <v>732</v>
       </c>
       <c r="B711" s="2">
@@ -35709,7 +35708,7 @@
       <c r="E711" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="F711" s="5">
+      <c r="F711">
         <v>38606</v>
       </c>
       <c r="G711" s="1" t="s">
@@ -35744,7 +35743,7 @@
       <c r="AB711" s="1"/>
     </row>
     <row r="712" spans="1:28">
-      <c r="A712" s="5">
+      <c r="A712">
         <v>733</v>
       </c>
       <c r="B712" s="2">
@@ -35759,7 +35758,7 @@
       <c r="E712" s="1" t="s">
         <v>781</v>
       </c>
-      <c r="F712" s="5">
+      <c r="F712">
         <v>38720</v>
       </c>
       <c r="G712" s="1" t="s">
@@ -35796,7 +35795,7 @@
       </c>
     </row>
     <row r="713" spans="1:28">
-      <c r="A713" s="5">
+      <c r="A713">
         <v>734</v>
       </c>
       <c r="B713" s="2">
@@ -35811,7 +35810,7 @@
       <c r="E713" s="1" t="s">
         <v>1115</v>
       </c>
-      <c r="F713" s="5">
+      <c r="F713">
         <v>38668</v>
       </c>
       <c r="G713" s="1" t="s">
@@ -35848,7 +35847,7 @@
       </c>
     </row>
     <row r="714" spans="1:28">
-      <c r="A714" s="5">
+      <c r="A714">
         <v>735</v>
       </c>
       <c r="B714" s="2">
@@ -35863,7 +35862,7 @@
       <c r="E714" s="1" t="s">
         <v>1118</v>
       </c>
-      <c r="F714" s="5">
+      <c r="F714">
         <v>38438</v>
       </c>
       <c r="G714" s="1" t="s">
@@ -35900,7 +35899,7 @@
       </c>
     </row>
     <row r="715" spans="1:28">
-      <c r="A715" s="5">
+      <c r="A715">
         <v>736</v>
       </c>
       <c r="B715" s="2">
@@ -35915,7 +35914,7 @@
       <c r="E715" s="1" t="s">
         <v>969</v>
       </c>
-      <c r="F715" s="5">
+      <c r="F715">
         <v>38617</v>
       </c>
       <c r="G715" s="1" t="s">
@@ -35952,7 +35951,7 @@
       </c>
     </row>
     <row r="716" spans="1:28">
-      <c r="A716" s="5">
+      <c r="A716">
         <v>737</v>
       </c>
       <c r="B716" s="2">
@@ -35967,7 +35966,7 @@
       <c r="E716" s="1" t="s">
         <v>850</v>
       </c>
-      <c r="F716" s="5">
+      <c r="F716">
         <v>38644</v>
       </c>
       <c r="G716" s="1" t="s">
@@ -36004,7 +36003,7 @@
       </c>
     </row>
     <row r="717" spans="1:28">
-      <c r="A717" s="5">
+      <c r="A717">
         <v>738</v>
       </c>
       <c r="B717" s="2">
@@ -36019,7 +36018,7 @@
       <c r="E717" s="1" t="s">
         <v>802</v>
       </c>
-      <c r="F717" s="5">
+      <c r="F717">
         <v>38366</v>
       </c>
       <c r="G717" s="1" t="s">
@@ -36056,7 +36055,7 @@
       </c>
     </row>
     <row r="718" spans="1:28">
-      <c r="A718" s="5">
+      <c r="A718">
         <v>739</v>
       </c>
       <c r="B718" s="2">
@@ -36071,7 +36070,7 @@
       <c r="E718" s="1" t="s">
         <v>984</v>
       </c>
-      <c r="F718" s="5">
+      <c r="F718">
         <v>38386</v>
       </c>
       <c r="G718" s="1" t="s">
@@ -36108,7 +36107,7 @@
       </c>
     </row>
     <row r="719" spans="1:28">
-      <c r="A719" s="5">
+      <c r="A719">
         <v>740</v>
       </c>
       <c r="B719" s="2">
@@ -36123,7 +36122,7 @@
       <c r="E719" s="1" t="s">
         <v>823</v>
       </c>
-      <c r="F719" s="5">
+      <c r="F719">
         <v>38121</v>
       </c>
       <c r="G719" s="1" t="s">
@@ -36160,7 +36159,7 @@
       </c>
     </row>
     <row r="720" spans="1:28">
-      <c r="A720" s="5">
+      <c r="A720">
         <v>741</v>
       </c>
       <c r="B720" s="2">
@@ -36175,7 +36174,7 @@
       <c r="E720" s="1" t="s">
         <v>943</v>
       </c>
-      <c r="F720" s="5">
+      <c r="F720">
         <v>38532</v>
       </c>
       <c r="G720" s="1" t="s">
@@ -36212,7 +36211,7 @@
       </c>
     </row>
     <row r="721" spans="1:28">
-      <c r="A721" s="5">
+      <c r="A721">
         <v>742</v>
       </c>
       <c r="B721" s="2">
@@ -36227,7 +36226,7 @@
       <c r="E721" s="1" t="s">
         <v>981</v>
       </c>
-      <c r="F721" s="5">
+      <c r="F721">
         <v>38400</v>
       </c>
       <c r="G721" s="1" t="s">
@@ -36264,7 +36263,7 @@
       </c>
     </row>
     <row r="722" spans="1:28">
-      <c r="A722" s="5">
+      <c r="A722">
         <v>743</v>
       </c>
       <c r="B722" s="2">
@@ -36279,7 +36278,7 @@
       <c r="E722" s="1" t="s">
         <v>1129</v>
       </c>
-      <c r="F722" s="5">
+      <c r="F722">
         <v>38512</v>
       </c>
       <c r="G722" s="1" t="s">
@@ -36316,7 +36315,7 @@
       </c>
     </row>
     <row r="723" spans="1:28">
-      <c r="A723" s="5">
+      <c r="A723">
         <v>744</v>
       </c>
       <c r="B723" s="2">
@@ -36331,7 +36330,7 @@
       <c r="E723" s="1" t="s">
         <v>1132</v>
       </c>
-      <c r="F723" s="5">
+      <c r="F723">
         <v>38798</v>
       </c>
       <c r="G723" s="1" t="s">
@@ -36368,7 +36367,7 @@
       </c>
     </row>
     <row r="724" spans="1:28">
-      <c r="A724" s="5">
+      <c r="A724">
         <v>745</v>
       </c>
       <c r="B724" s="2">
@@ -36383,7 +36382,7 @@
       <c r="E724" s="1" t="s">
         <v>1137</v>
       </c>
-      <c r="F724" s="5">
+      <c r="F724">
         <v>43147</v>
       </c>
       <c r="G724" s="1" t="s">

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1287D537-8DDC-406F-B918-54C1CB362B46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0F74058-D8AA-4C4F-AEE7-F87B25A5D3AA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3305" uniqueCount="1139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3667" uniqueCount="1200">
   <si>
     <t>Id</t>
   </si>
@@ -3453,6 +3453,189 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_4851_Starbucks%20Juarez%2070.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17894272771425575916565575925970_Ramon%20Espinosa%20Macia.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/file_000000007c6481f5ad0226fc8a655e79_Starbucks%20Bosque%20Rea.png</t>
+  </si>
+  <si>
+    <t>nancy.arroyo@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Nancy Arroyo Vázquez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/20260914_171502_Nancy%20Arroyo%20V%C3%A1zquez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Plaza%20Cent.jpg</t>
+  </si>
+  <si>
+    <t>brenda.nateras@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Brenda Nateras Reyes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894272488533167192953013727319_Brenda%20Nateras%20Reyes.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/16cd661a-01e3-456b-9d73-74f3799e9252_Starbucks%20CC%20Samara.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_5170_Starbucks%20Plaza%20Exhi.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894286959175884525572335782779_Ramon%20Espinosa%20Macia.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894285369371548324662037879201_Starbucks%20Outlet%20Ler.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894294362313993647424495617005_Starbucks%20Apto%20Toluc.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_2056_Starbucks%20Montes%20Ura.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_7796_Carlos%20Rodriguez%20Mor.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Paseo%20Toll.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Punta%20Zero.jpg</t>
+  </si>
+  <si>
+    <t>jose.lopez-resendiz@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Jose Antonio Lopez Resendiz</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/803c292b-575f-4452-a5ef-03666c00d4a8_Jose%20Antonio%20Lopez%20R.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Felix%20Cuev.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/3874621e-d942-4631-9612-47854aac1254_Starbucks%20Tecnologic.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/1789432235331375473490729147892_Starbucks%20Corporativ.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Galerias%20P.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Galerias%20P%201.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_8180_Starbucks%20Monte%20Pelv.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/60E8DD4C-182C-44DD-B56D-8047C5B4966F_Starbucks%20Galerias%20P.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_4782_Starbucks%20Galerias%20P.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_4725_Eduardo%20Hernandez%20Pe.jpeg</t>
+  </si>
+  <si>
+    <t>08:30 a. m.</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Townsquare.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/1789433834489773385900930918506_Starbucks%20Portal%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20CC%20Coalcal.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_0299_Starbucks%20Plaza%20Lila.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/21d535a4-6aa9-4964-8d4d-febb4f3b8362_Starbucks%20CC%20Coalcal.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_9499_Luis%20Javier%20Perez%20Mo.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38466@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Paseo Interlomas 1</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894360562226144244955470698883_Starbucks%20Paseo%20Inte.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Plaza%20Mayo.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_4782_Starbucks%20Paseo%20Inte.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/dd878677-b3b3-4f6e-a676-f774a596f85a_Starbucks%20Magnocentr.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894384717133978208447511783030_Starbucks%20M%C3%A9xico-Tol.jpg</t>
+  </si>
+  <si>
+    <t>erika.martinez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Erika Janette Martinez Jimenez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/tempImagejUgyCw_Erika%20Janette%20Martin.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/9c8a74e7-5595-43b6-abb0-5f18c7ea963f_Starbucks%20Metropoli.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/f7817d4d-cfcf-4f63-a07c-cc7bcfe0ef3f_Starbucks%20Carr%20Toluc.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG-20260914-WA0173_Starbucks%20TORRE%20ZENT.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Parque%20la.jpg</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17894440988043570746312247014305_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/16E0A561-50F1-438C-86F0-F70E0E2910FB_Starbucks%20El%20Rosario.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894779357146050088576105559553_Starbucks%20TEC%20SANTA.jpg</t>
+  </si>
+  <si>
+    <t>10:00 p. m.</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Superama%20S.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_20260915_084807860_HDR_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894841953833155598802420551585_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_7462_Jorge%20Humberto%20Rojas.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
   </si>
 </sst>
 </file>
@@ -3497,12 +3680,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -3601,8 +3785,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB724" totalsRowShown="0">
-  <autoFilter ref="A1:AB724" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB782" totalsRowShown="0">
+  <autoFilter ref="A1:AB782" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="25">
       <extLst>
@@ -3804,7 +3988,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="745" latestEventMarker="1069">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="803" latestEventMarker="1127">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4136,7 +4320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB724"/>
+  <dimension ref="A1:AB782"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -36418,6 +36602,2934 @@
         <v>1138</v>
       </c>
     </row>
+    <row r="725" spans="1:28">
+      <c r="A725" s="5">
+        <v>746</v>
+      </c>
+      <c r="B725" s="2">
+        <v>46279.712500000001</v>
+      </c>
+      <c r="C725" s="2">
+        <v>46279.714756944399</v>
+      </c>
+      <c r="D725" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E725" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F725" s="5">
+        <v>38456</v>
+      </c>
+      <c r="G725" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H725" s="1"/>
+      <c r="I725" s="1"/>
+      <c r="J725" s="1"/>
+      <c r="K725" s="1"/>
+      <c r="L725" s="1"/>
+      <c r="M725" s="1"/>
+      <c r="N725" s="1"/>
+      <c r="O725" s="1" t="s">
+        <v>1139</v>
+      </c>
+      <c r="P725" s="1"/>
+      <c r="Q725" s="1"/>
+      <c r="R725" s="1"/>
+      <c r="S725" s="1"/>
+      <c r="T725" s="1"/>
+      <c r="U725" s="1"/>
+      <c r="V725" s="3"/>
+      <c r="W725" s="3"/>
+      <c r="X725" s="1"/>
+      <c r="Y725" s="1"/>
+      <c r="Z725" s="1"/>
+      <c r="AA725" s="1"/>
+      <c r="AB725" s="1"/>
+    </row>
+    <row r="726" spans="1:28">
+      <c r="A726" s="5">
+        <v>747</v>
+      </c>
+      <c r="B726" s="2">
+        <v>46279.715706018498</v>
+      </c>
+      <c r="C726" s="2">
+        <v>46279.716585648101</v>
+      </c>
+      <c r="D726" s="1" t="s">
+        <v>825</v>
+      </c>
+      <c r="E726" s="1" t="s">
+        <v>826</v>
+      </c>
+      <c r="F726" s="5">
+        <v>38918</v>
+      </c>
+      <c r="G726" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H726" s="1"/>
+      <c r="I726" s="1"/>
+      <c r="J726" s="1"/>
+      <c r="K726" s="1"/>
+      <c r="L726" s="1"/>
+      <c r="M726" s="1"/>
+      <c r="N726" s="1"/>
+      <c r="O726" s="1"/>
+      <c r="P726" s="1"/>
+      <c r="Q726" s="1"/>
+      <c r="R726" s="1"/>
+      <c r="S726" s="1"/>
+      <c r="T726" s="1"/>
+      <c r="U726" s="1"/>
+      <c r="V726" s="3"/>
+      <c r="W726" s="3"/>
+      <c r="X726" s="1"/>
+      <c r="Y726" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z726" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA726" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB726" s="1" t="s">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="727" spans="1:28">
+      <c r="A727" s="5">
+        <v>748</v>
+      </c>
+      <c r="B727" s="2">
+        <v>46279.719687500001</v>
+      </c>
+      <c r="C727" s="2">
+        <v>46279.720439814802</v>
+      </c>
+      <c r="D727" s="1" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E727" s="1" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F727" s="5">
+        <v>38461</v>
+      </c>
+      <c r="G727" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H727" s="1"/>
+      <c r="I727" s="1"/>
+      <c r="J727" s="1"/>
+      <c r="K727" s="1"/>
+      <c r="L727" s="1"/>
+      <c r="M727" s="1"/>
+      <c r="N727" s="1"/>
+      <c r="O727" s="1"/>
+      <c r="P727" s="1"/>
+      <c r="Q727" s="1"/>
+      <c r="R727" s="1"/>
+      <c r="S727" s="1"/>
+      <c r="T727" s="1"/>
+      <c r="U727" s="1"/>
+      <c r="V727" s="3"/>
+      <c r="W727" s="3"/>
+      <c r="X727" s="1"/>
+      <c r="Y727" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z727" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA727" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB727" s="1" t="s">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="728" spans="1:28">
+      <c r="A728" s="5">
+        <v>749</v>
+      </c>
+      <c r="B728" s="2">
+        <v>46279.697615740697</v>
+      </c>
+      <c r="C728" s="2">
+        <v>46279.720659722203</v>
+      </c>
+      <c r="D728" s="1" t="s">
+        <v>999</v>
+      </c>
+      <c r="E728" s="1" t="s">
+        <v>1000</v>
+      </c>
+      <c r="F728" s="5">
+        <v>38810</v>
+      </c>
+      <c r="G728" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H728" s="1"/>
+      <c r="I728" s="1"/>
+      <c r="J728" s="1"/>
+      <c r="K728" s="1"/>
+      <c r="L728" s="1"/>
+      <c r="M728" s="1"/>
+      <c r="N728" s="1"/>
+      <c r="O728" s="1"/>
+      <c r="P728" s="1"/>
+      <c r="Q728" s="1"/>
+      <c r="R728" s="1"/>
+      <c r="S728" s="1"/>
+      <c r="T728" s="1"/>
+      <c r="U728" s="1"/>
+      <c r="V728" s="3"/>
+      <c r="W728" s="3"/>
+      <c r="X728" s="1"/>
+      <c r="Y728" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z728" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA728" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB728" s="1" t="s">
+        <v>1144</v>
+      </c>
+    </row>
+    <row r="729" spans="1:28">
+      <c r="A729" s="5">
+        <v>750</v>
+      </c>
+      <c r="B729" s="2">
+        <v>46279.712314814802</v>
+      </c>
+      <c r="C729" s="2">
+        <v>46279.727719907401</v>
+      </c>
+      <c r="D729" s="1" t="s">
+        <v>1145</v>
+      </c>
+      <c r="E729" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="F729" s="5">
+        <v>38390</v>
+      </c>
+      <c r="G729" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H729" s="1"/>
+      <c r="I729" s="1"/>
+      <c r="J729" s="1"/>
+      <c r="K729" s="1"/>
+      <c r="L729" s="1"/>
+      <c r="M729" s="1"/>
+      <c r="N729" s="1"/>
+      <c r="O729" s="1"/>
+      <c r="P729" s="1"/>
+      <c r="Q729" s="1"/>
+      <c r="R729" s="1"/>
+      <c r="S729" s="1"/>
+      <c r="T729" s="1"/>
+      <c r="U729" s="1"/>
+      <c r="V729" s="3"/>
+      <c r="W729" s="3"/>
+      <c r="X729" s="1"/>
+      <c r="Y729" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z729" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA729" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AB729" s="1" t="s">
+        <v>1147</v>
+      </c>
+    </row>
+    <row r="730" spans="1:28">
+      <c r="A730" s="5">
+        <v>751</v>
+      </c>
+      <c r="B730" s="2">
+        <v>46279.727708333303</v>
+      </c>
+      <c r="C730" s="2">
+        <v>46279.728564814803</v>
+      </c>
+      <c r="D730" s="1" t="s">
+        <v>831</v>
+      </c>
+      <c r="E730" s="1" t="s">
+        <v>832</v>
+      </c>
+      <c r="F730" s="5">
+        <v>38445</v>
+      </c>
+      <c r="G730" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H730" s="1"/>
+      <c r="I730" s="1"/>
+      <c r="J730" s="1"/>
+      <c r="K730" s="1"/>
+      <c r="L730" s="1"/>
+      <c r="M730" s="1"/>
+      <c r="N730" s="1"/>
+      <c r="O730" s="1"/>
+      <c r="P730" s="1"/>
+      <c r="Q730" s="1"/>
+      <c r="R730" s="1"/>
+      <c r="S730" s="1"/>
+      <c r="T730" s="1"/>
+      <c r="U730" s="1"/>
+      <c r="V730" s="3"/>
+      <c r="W730" s="3"/>
+      <c r="X730" s="1"/>
+      <c r="Y730" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z730" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA730" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB730" s="1" t="s">
+        <v>1148</v>
+      </c>
+    </row>
+    <row r="731" spans="1:28">
+      <c r="A731" s="5">
+        <v>752</v>
+      </c>
+      <c r="B731" s="2">
+        <v>46279.728275463</v>
+      </c>
+      <c r="C731" s="2">
+        <v>46279.728692129604</v>
+      </c>
+      <c r="D731" s="1" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E731" s="1" t="s">
+        <v>1079</v>
+      </c>
+      <c r="F731" s="5">
+        <v>38692</v>
+      </c>
+      <c r="G731" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H731" s="1"/>
+      <c r="I731" s="1"/>
+      <c r="J731" s="1"/>
+      <c r="K731" s="1"/>
+      <c r="L731" s="1"/>
+      <c r="M731" s="1"/>
+      <c r="N731" s="1"/>
+      <c r="O731" s="1"/>
+      <c r="P731" s="1"/>
+      <c r="Q731" s="1"/>
+      <c r="R731" s="1"/>
+      <c r="S731" s="1"/>
+      <c r="T731" s="1"/>
+      <c r="U731" s="1"/>
+      <c r="V731" s="3"/>
+      <c r="W731" s="3"/>
+      <c r="X731" s="1"/>
+      <c r="Y731" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z731" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA731" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB731" s="1" t="s">
+        <v>1149</v>
+      </c>
+    </row>
+    <row r="732" spans="1:28">
+      <c r="A732" s="5">
+        <v>753</v>
+      </c>
+      <c r="B732" s="2">
+        <v>46279.726504629602</v>
+      </c>
+      <c r="C732" s="2">
+        <v>46279.730798611097</v>
+      </c>
+      <c r="D732" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E732" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F732" s="5">
+        <v>38456</v>
+      </c>
+      <c r="G732" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H732" s="1"/>
+      <c r="I732" s="1"/>
+      <c r="J732" s="1"/>
+      <c r="K732" s="1"/>
+      <c r="L732" s="1"/>
+      <c r="M732" s="1"/>
+      <c r="N732" s="1"/>
+      <c r="O732" s="1"/>
+      <c r="P732" s="1"/>
+      <c r="Q732" s="1"/>
+      <c r="R732" s="1"/>
+      <c r="S732" s="1"/>
+      <c r="T732" s="1"/>
+      <c r="U732" s="1"/>
+      <c r="V732" s="3"/>
+      <c r="W732" s="3"/>
+      <c r="X732" s="1"/>
+      <c r="Y732" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z732" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA732" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB732" s="1" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="733" spans="1:28">
+      <c r="A733" s="5">
+        <v>754</v>
+      </c>
+      <c r="B733" s="2">
+        <v>46279.727476851898</v>
+      </c>
+      <c r="C733" s="2">
+        <v>46279.733460648102</v>
+      </c>
+      <c r="D733" s="1" t="s">
+        <v>958</v>
+      </c>
+      <c r="E733" s="1" t="s">
+        <v>959</v>
+      </c>
+      <c r="F733" s="5">
+        <v>38829</v>
+      </c>
+      <c r="G733" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H733" s="1"/>
+      <c r="I733" s="1"/>
+      <c r="J733" s="1"/>
+      <c r="K733" s="1"/>
+      <c r="L733" s="1"/>
+      <c r="M733" s="1"/>
+      <c r="N733" s="1"/>
+      <c r="O733" s="1"/>
+      <c r="P733" s="1"/>
+      <c r="Q733" s="1"/>
+      <c r="R733" s="1"/>
+      <c r="S733" s="1"/>
+      <c r="T733" s="1"/>
+      <c r="U733" s="1"/>
+      <c r="V733" s="3"/>
+      <c r="W733" s="3"/>
+      <c r="X733" s="1"/>
+      <c r="Y733" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z733" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA733" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB733" s="1" t="s">
+        <v>1151</v>
+      </c>
+    </row>
+    <row r="734" spans="1:28">
+      <c r="A734" s="5">
+        <v>755</v>
+      </c>
+      <c r="B734" s="2">
+        <v>46279.716226851902</v>
+      </c>
+      <c r="C734" s="2">
+        <v>46279.739421296297</v>
+      </c>
+      <c r="D734" s="1" t="s">
+        <v>912</v>
+      </c>
+      <c r="E734" s="1" t="s">
+        <v>913</v>
+      </c>
+      <c r="F734" s="5">
+        <v>43162</v>
+      </c>
+      <c r="G734" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H734" s="1"/>
+      <c r="I734" s="1"/>
+      <c r="J734" s="1"/>
+      <c r="K734" s="1"/>
+      <c r="L734" s="1"/>
+      <c r="M734" s="1"/>
+      <c r="N734" s="1"/>
+      <c r="O734" s="1"/>
+      <c r="P734" s="1"/>
+      <c r="Q734" s="1"/>
+      <c r="R734" s="1"/>
+      <c r="S734" s="1"/>
+      <c r="T734" s="1"/>
+      <c r="U734" s="1"/>
+      <c r="V734" s="3"/>
+      <c r="W734" s="3"/>
+      <c r="X734" s="1"/>
+      <c r="Y734" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z734" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA734" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AB734" s="1" t="s">
+        <v>1152</v>
+      </c>
+    </row>
+    <row r="735" spans="1:28">
+      <c r="A735" s="5">
+        <v>756</v>
+      </c>
+      <c r="B735" s="2">
+        <v>46279.717523148203</v>
+      </c>
+      <c r="C735" s="2">
+        <v>46279.742395833302</v>
+      </c>
+      <c r="D735" s="1" t="s">
+        <v>987</v>
+      </c>
+      <c r="E735" s="1" t="s">
+        <v>988</v>
+      </c>
+      <c r="F735" s="5">
+        <v>43142</v>
+      </c>
+      <c r="G735" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H735" s="1"/>
+      <c r="I735" s="1"/>
+      <c r="J735" s="1"/>
+      <c r="K735" s="1"/>
+      <c r="L735" s="1"/>
+      <c r="M735" s="1"/>
+      <c r="N735" s="1"/>
+      <c r="O735" s="1"/>
+      <c r="P735" s="1"/>
+      <c r="Q735" s="1"/>
+      <c r="R735" s="1"/>
+      <c r="S735" s="1"/>
+      <c r="T735" s="1"/>
+      <c r="U735" s="1"/>
+      <c r="V735" s="3"/>
+      <c r="W735" s="3"/>
+      <c r="X735" s="1"/>
+      <c r="Y735" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z735" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AA735" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AB735" s="1" t="s">
+        <v>1153</v>
+      </c>
+    </row>
+    <row r="736" spans="1:28">
+      <c r="A736" s="5">
+        <v>757</v>
+      </c>
+      <c r="B736" s="2">
+        <v>46279.742719907401</v>
+      </c>
+      <c r="C736" s="2">
+        <v>46279.743842592601</v>
+      </c>
+      <c r="D736" s="1" t="s">
+        <v>955</v>
+      </c>
+      <c r="E736" s="1" t="s">
+        <v>956</v>
+      </c>
+      <c r="F736" s="5">
+        <v>38727</v>
+      </c>
+      <c r="G736" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H736" s="1"/>
+      <c r="I736" s="1"/>
+      <c r="J736" s="1"/>
+      <c r="K736" s="1"/>
+      <c r="L736" s="1"/>
+      <c r="M736" s="1"/>
+      <c r="N736" s="1"/>
+      <c r="O736" s="1"/>
+      <c r="P736" s="1"/>
+      <c r="Q736" s="1"/>
+      <c r="R736" s="1"/>
+      <c r="S736" s="1"/>
+      <c r="T736" s="1"/>
+      <c r="U736" s="1"/>
+      <c r="V736" s="3"/>
+      <c r="W736" s="3"/>
+      <c r="X736" s="1"/>
+      <c r="Y736" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z736" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA736" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB736" s="1" t="s">
+        <v>1154</v>
+      </c>
+    </row>
+    <row r="737" spans="1:28">
+      <c r="A737" s="5">
+        <v>758</v>
+      </c>
+      <c r="B737" s="2">
+        <v>46279.747476851902</v>
+      </c>
+      <c r="C737" s="2">
+        <v>46279.748726851903</v>
+      </c>
+      <c r="D737" s="1" t="s">
+        <v>1075</v>
+      </c>
+      <c r="E737" s="1" t="s">
+        <v>1076</v>
+      </c>
+      <c r="F737" s="5">
+        <v>38896</v>
+      </c>
+      <c r="G737" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H737" s="1"/>
+      <c r="I737" s="1"/>
+      <c r="J737" s="1"/>
+      <c r="K737" s="1"/>
+      <c r="L737" s="1"/>
+      <c r="M737" s="1"/>
+      <c r="N737" s="1"/>
+      <c r="O737" s="1"/>
+      <c r="P737" s="1"/>
+      <c r="Q737" s="1"/>
+      <c r="R737" s="1"/>
+      <c r="S737" s="1"/>
+      <c r="T737" s="1"/>
+      <c r="U737" s="1"/>
+      <c r="V737" s="3"/>
+      <c r="W737" s="3"/>
+      <c r="X737" s="1"/>
+      <c r="Y737" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z737" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA737" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB737" s="1" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="738" spans="1:28">
+      <c r="A738" s="5">
+        <v>759</v>
+      </c>
+      <c r="B738" s="2">
+        <v>46279.749039351896</v>
+      </c>
+      <c r="C738" s="2">
+        <v>46279.749386574098</v>
+      </c>
+      <c r="D738" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="E738" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F738" s="5">
+        <v>38590</v>
+      </c>
+      <c r="G738" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H738" s="1"/>
+      <c r="I738" s="1"/>
+      <c r="J738" s="1"/>
+      <c r="K738" s="1"/>
+      <c r="L738" s="1"/>
+      <c r="M738" s="1"/>
+      <c r="N738" s="1"/>
+      <c r="O738" s="1"/>
+      <c r="P738" s="1"/>
+      <c r="Q738" s="1"/>
+      <c r="R738" s="1"/>
+      <c r="S738" s="1"/>
+      <c r="T738" s="1"/>
+      <c r="U738" s="1"/>
+      <c r="V738" s="3"/>
+      <c r="W738" s="3"/>
+      <c r="X738" s="1"/>
+      <c r="Y738" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z738" s="1"/>
+      <c r="AA738" s="1"/>
+      <c r="AB738" s="1"/>
+    </row>
+    <row r="739" spans="1:28">
+      <c r="A739" s="5">
+        <v>760</v>
+      </c>
+      <c r="B739" s="2">
+        <v>46279.751689814802</v>
+      </c>
+      <c r="C739" s="2">
+        <v>46279.752592592602</v>
+      </c>
+      <c r="D739" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E739" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F739" s="5">
+        <v>38987</v>
+      </c>
+      <c r="G739" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H739" s="1"/>
+      <c r="I739" s="1"/>
+      <c r="J739" s="1"/>
+      <c r="K739" s="1"/>
+      <c r="L739" s="1"/>
+      <c r="M739" s="1"/>
+      <c r="N739" s="1"/>
+      <c r="O739" s="1"/>
+      <c r="P739" s="1"/>
+      <c r="Q739" s="1"/>
+      <c r="R739" s="1"/>
+      <c r="S739" s="1"/>
+      <c r="T739" s="1"/>
+      <c r="U739" s="1"/>
+      <c r="V739" s="3"/>
+      <c r="W739" s="3"/>
+      <c r="X739" s="1"/>
+      <c r="Y739" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z739" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA739" s="1" t="s">
+        <v>1107</v>
+      </c>
+      <c r="AB739" s="1" t="s">
+        <v>1156</v>
+      </c>
+    </row>
+    <row r="740" spans="1:28">
+      <c r="A740" s="5">
+        <v>761</v>
+      </c>
+      <c r="B740" s="2">
+        <v>46279.754814814798</v>
+      </c>
+      <c r="C740" s="2">
+        <v>46279.754976851902</v>
+      </c>
+      <c r="D740" s="1" t="s">
+        <v>813</v>
+      </c>
+      <c r="E740" s="1" t="s">
+        <v>814</v>
+      </c>
+      <c r="F740" s="5">
+        <v>38709</v>
+      </c>
+      <c r="G740" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H740" s="1"/>
+      <c r="I740" s="1"/>
+      <c r="J740" s="1"/>
+      <c r="K740" s="1"/>
+      <c r="L740" s="1"/>
+      <c r="M740" s="1"/>
+      <c r="N740" s="1"/>
+      <c r="O740" s="1"/>
+      <c r="P740" s="1"/>
+      <c r="Q740" s="1"/>
+      <c r="R740" s="1"/>
+      <c r="S740" s="1"/>
+      <c r="T740" s="1"/>
+      <c r="U740" s="1"/>
+      <c r="V740" s="3"/>
+      <c r="W740" s="3"/>
+      <c r="X740" s="1"/>
+      <c r="Y740" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z740" s="1"/>
+      <c r="AA740" s="1"/>
+      <c r="AB740" s="1"/>
+    </row>
+    <row r="741" spans="1:28">
+      <c r="A741" s="5">
+        <v>762</v>
+      </c>
+      <c r="B741" s="2">
+        <v>46279.763437499998</v>
+      </c>
+      <c r="C741" s="2">
+        <v>46279.765092592599</v>
+      </c>
+      <c r="D741" s="1" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E741" s="1" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F741" s="5">
+        <v>38138</v>
+      </c>
+      <c r="G741" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H741" s="1"/>
+      <c r="I741" s="1"/>
+      <c r="J741" s="1"/>
+      <c r="K741" s="1"/>
+      <c r="L741" s="1"/>
+      <c r="M741" s="1"/>
+      <c r="N741" s="1"/>
+      <c r="O741" s="1"/>
+      <c r="P741" s="1"/>
+      <c r="Q741" s="1"/>
+      <c r="R741" s="1"/>
+      <c r="S741" s="1"/>
+      <c r="T741" s="1"/>
+      <c r="U741" s="1"/>
+      <c r="V741" s="3"/>
+      <c r="W741" s="3"/>
+      <c r="X741" s="1"/>
+      <c r="Y741" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z741" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA741" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB741" s="1" t="s">
+        <v>1159</v>
+      </c>
+    </row>
+    <row r="742" spans="1:28">
+      <c r="A742" s="5">
+        <v>763</v>
+      </c>
+      <c r="B742" s="2">
+        <v>46279.760914351798</v>
+      </c>
+      <c r="C742" s="2">
+        <v>46279.765740740702</v>
+      </c>
+      <c r="D742" s="1" t="s">
+        <v>1005</v>
+      </c>
+      <c r="E742" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F742" s="5">
+        <v>38372</v>
+      </c>
+      <c r="G742" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H742" s="1"/>
+      <c r="I742" s="1"/>
+      <c r="J742" s="1"/>
+      <c r="K742" s="1"/>
+      <c r="L742" s="1"/>
+      <c r="M742" s="1"/>
+      <c r="N742" s="1"/>
+      <c r="O742" s="1"/>
+      <c r="P742" s="1"/>
+      <c r="Q742" s="1"/>
+      <c r="R742" s="1"/>
+      <c r="S742" s="1"/>
+      <c r="T742" s="1"/>
+      <c r="U742" s="1"/>
+      <c r="V742" s="3"/>
+      <c r="W742" s="3"/>
+      <c r="X742" s="1"/>
+      <c r="Y742" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z742" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA742" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB742" s="1" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="743" spans="1:28">
+      <c r="A743" s="5">
+        <v>764</v>
+      </c>
+      <c r="B743" s="2">
+        <v>46279.767893518503</v>
+      </c>
+      <c r="C743" s="2">
+        <v>46279.772002314799</v>
+      </c>
+      <c r="D743" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="E743" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F743" s="5">
+        <v>38319</v>
+      </c>
+      <c r="G743" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H743" s="1"/>
+      <c r="I743" s="1"/>
+      <c r="J743" s="1"/>
+      <c r="K743" s="1"/>
+      <c r="L743" s="1"/>
+      <c r="M743" s="1"/>
+      <c r="N743" s="1"/>
+      <c r="O743" s="1"/>
+      <c r="P743" s="1"/>
+      <c r="Q743" s="1"/>
+      <c r="R743" s="1"/>
+      <c r="S743" s="1"/>
+      <c r="T743" s="1"/>
+      <c r="U743" s="1"/>
+      <c r="V743" s="3"/>
+      <c r="W743" s="3"/>
+      <c r="X743" s="1"/>
+      <c r="Y743" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z743" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA743" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB743" s="1" t="s">
+        <v>1161</v>
+      </c>
+    </row>
+    <row r="744" spans="1:28">
+      <c r="A744" s="5">
+        <v>765</v>
+      </c>
+      <c r="B744" s="2">
+        <v>46279.769849536999</v>
+      </c>
+      <c r="C744" s="2">
+        <v>46279.773321759298</v>
+      </c>
+      <c r="D744" s="1" t="s">
+        <v>945</v>
+      </c>
+      <c r="E744" s="1" t="s">
+        <v>946</v>
+      </c>
+      <c r="F744" s="5">
+        <v>38755</v>
+      </c>
+      <c r="G744" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H744" s="1"/>
+      <c r="I744" s="1"/>
+      <c r="J744" s="1"/>
+      <c r="K744" s="1"/>
+      <c r="L744" s="1"/>
+      <c r="M744" s="1"/>
+      <c r="N744" s="1"/>
+      <c r="O744" s="1"/>
+      <c r="P744" s="1"/>
+      <c r="Q744" s="1"/>
+      <c r="R744" s="1"/>
+      <c r="S744" s="1"/>
+      <c r="T744" s="1"/>
+      <c r="U744" s="1"/>
+      <c r="V744" s="3"/>
+      <c r="W744" s="3"/>
+      <c r="X744" s="1"/>
+      <c r="Y744" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z744" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA744" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AB744" s="1" t="s">
+        <v>1162</v>
+      </c>
+    </row>
+    <row r="745" spans="1:28">
+      <c r="A745" s="5">
+        <v>766</v>
+      </c>
+      <c r="B745" s="2">
+        <v>46279.7735300926</v>
+      </c>
+      <c r="C745" s="2">
+        <v>46279.774421296301</v>
+      </c>
+      <c r="D745" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E745" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F745" s="5">
+        <v>38894</v>
+      </c>
+      <c r="G745" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H745" s="1"/>
+      <c r="I745" s="1"/>
+      <c r="J745" s="1"/>
+      <c r="K745" s="1"/>
+      <c r="L745" s="1"/>
+      <c r="M745" s="1"/>
+      <c r="N745" s="1"/>
+      <c r="O745" s="1"/>
+      <c r="P745" s="1"/>
+      <c r="Q745" s="1"/>
+      <c r="R745" s="1"/>
+      <c r="S745" s="1"/>
+      <c r="T745" s="1"/>
+      <c r="U745" s="1"/>
+      <c r="V745" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="W745" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="X745" s="1" t="s">
+        <v>1163</v>
+      </c>
+      <c r="Y745" s="1"/>
+      <c r="Z745" s="1"/>
+      <c r="AA745" s="1"/>
+      <c r="AB745" s="1"/>
+    </row>
+    <row r="746" spans="1:28">
+      <c r="A746" s="5">
+        <v>767</v>
+      </c>
+      <c r="B746" s="2">
+        <v>46279.774675925903</v>
+      </c>
+      <c r="C746" s="2">
+        <v>46279.775312500002</v>
+      </c>
+      <c r="D746" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E746" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F746" s="5">
+        <v>38894</v>
+      </c>
+      <c r="G746" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H746" s="1"/>
+      <c r="I746" s="1"/>
+      <c r="J746" s="1"/>
+      <c r="K746" s="1"/>
+      <c r="L746" s="1"/>
+      <c r="M746" s="1"/>
+      <c r="N746" s="1"/>
+      <c r="O746" s="1"/>
+      <c r="P746" s="1"/>
+      <c r="Q746" s="1"/>
+      <c r="R746" s="1"/>
+      <c r="S746" s="1"/>
+      <c r="T746" s="1"/>
+      <c r="U746" s="1"/>
+      <c r="V746" s="3"/>
+      <c r="W746" s="3"/>
+      <c r="X746" s="1"/>
+      <c r="Y746" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z746" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA746" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB746" s="1" t="s">
+        <v>1164</v>
+      </c>
+    </row>
+    <row r="747" spans="1:28">
+      <c r="A747" s="5">
+        <v>768</v>
+      </c>
+      <c r="B747" s="2">
+        <v>46279.763217592597</v>
+      </c>
+      <c r="C747" s="2">
+        <v>46279.776018518503</v>
+      </c>
+      <c r="D747" s="1" t="s">
+        <v>858</v>
+      </c>
+      <c r="E747" s="1" t="s">
+        <v>859</v>
+      </c>
+      <c r="F747" s="5">
+        <v>38538</v>
+      </c>
+      <c r="G747" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H747" s="1"/>
+      <c r="I747" s="1"/>
+      <c r="J747" s="1"/>
+      <c r="K747" s="1"/>
+      <c r="L747" s="1"/>
+      <c r="M747" s="1"/>
+      <c r="N747" s="1"/>
+      <c r="O747" s="1"/>
+      <c r="P747" s="1"/>
+      <c r="Q747" s="1"/>
+      <c r="R747" s="1"/>
+      <c r="S747" s="1"/>
+      <c r="T747" s="1"/>
+      <c r="U747" s="1"/>
+      <c r="V747" s="3"/>
+      <c r="W747" s="3"/>
+      <c r="X747" s="1"/>
+      <c r="Y747" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z747" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA747" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB747" s="1" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="748" spans="1:28">
+      <c r="A748" s="5">
+        <v>769</v>
+      </c>
+      <c r="B748" s="2">
+        <v>46279.775879629597</v>
+      </c>
+      <c r="C748" s="2">
+        <v>46279.777986111098</v>
+      </c>
+      <c r="D748" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E748" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F748" s="5">
+        <v>38894</v>
+      </c>
+      <c r="G748" s="1" t="s">
+        <v>244</v>
+      </c>
+      <c r="H748" s="1"/>
+      <c r="I748" s="1"/>
+      <c r="J748" s="1"/>
+      <c r="K748" s="1"/>
+      <c r="L748" s="1"/>
+      <c r="M748" s="1"/>
+      <c r="N748" s="1"/>
+      <c r="O748" s="1"/>
+      <c r="P748" s="1"/>
+      <c r="Q748" s="1"/>
+      <c r="R748" s="1"/>
+      <c r="S748" s="1"/>
+      <c r="T748" s="1" t="s">
+        <v>1166</v>
+      </c>
+      <c r="U748" s="1"/>
+      <c r="V748" s="3"/>
+      <c r="W748" s="3"/>
+      <c r="X748" s="1"/>
+      <c r="Y748" s="1"/>
+      <c r="Z748" s="1"/>
+      <c r="AA748" s="1"/>
+      <c r="AB748" s="1"/>
+    </row>
+    <row r="749" spans="1:28">
+      <c r="A749" s="5">
+        <v>770</v>
+      </c>
+      <c r="B749" s="2">
+        <v>46279.778136574103</v>
+      </c>
+      <c r="C749" s="2">
+        <v>46279.780219907399</v>
+      </c>
+      <c r="D749" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="E749" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="F749" s="5">
+        <v>38894</v>
+      </c>
+      <c r="G749" s="1" t="s">
+        <v>246</v>
+      </c>
+      <c r="H749" s="1"/>
+      <c r="I749" s="1"/>
+      <c r="J749" s="1"/>
+      <c r="K749" s="1"/>
+      <c r="L749" s="1"/>
+      <c r="M749" s="1"/>
+      <c r="N749" s="1"/>
+      <c r="O749" s="1"/>
+      <c r="P749" s="1"/>
+      <c r="Q749" s="1"/>
+      <c r="R749" s="1"/>
+      <c r="S749" s="1"/>
+      <c r="T749" s="1"/>
+      <c r="U749" s="1" t="s">
+        <v>1167</v>
+      </c>
+      <c r="V749" s="3"/>
+      <c r="W749" s="3"/>
+      <c r="X749" s="1"/>
+      <c r="Y749" s="1"/>
+      <c r="Z749" s="1"/>
+      <c r="AA749" s="1"/>
+      <c r="AB749" s="1"/>
+    </row>
+    <row r="750" spans="1:28">
+      <c r="A750" s="5">
+        <v>771</v>
+      </c>
+      <c r="B750" s="2">
+        <v>46279.784675925897</v>
+      </c>
+      <c r="C750" s="2">
+        <v>46279.784884259301</v>
+      </c>
+      <c r="D750" s="1" t="s">
+        <v>894</v>
+      </c>
+      <c r="E750" s="1" t="s">
+        <v>895</v>
+      </c>
+      <c r="F750" s="5">
+        <v>43041</v>
+      </c>
+      <c r="G750" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H750" s="1"/>
+      <c r="I750" s="1"/>
+      <c r="J750" s="1"/>
+      <c r="K750" s="1"/>
+      <c r="L750" s="1"/>
+      <c r="M750" s="1"/>
+      <c r="N750" s="1"/>
+      <c r="O750" s="1"/>
+      <c r="P750" s="1"/>
+      <c r="Q750" s="1"/>
+      <c r="R750" s="1"/>
+      <c r="S750" s="1"/>
+      <c r="T750" s="1"/>
+      <c r="U750" s="1"/>
+      <c r="V750" s="3"/>
+      <c r="W750" s="3"/>
+      <c r="X750" s="1"/>
+      <c r="Y750" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z750" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA750" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB750" s="1" t="s">
+        <v>1168</v>
+      </c>
+    </row>
+    <row r="751" spans="1:28">
+      <c r="A751" s="5">
+        <v>772</v>
+      </c>
+      <c r="B751" s="2">
+        <v>46279.786018518498</v>
+      </c>
+      <c r="C751" s="2">
+        <v>46279.789178240702</v>
+      </c>
+      <c r="D751" s="1" t="s">
+        <v>1064</v>
+      </c>
+      <c r="E751" s="1" t="s">
+        <v>1065</v>
+      </c>
+      <c r="F751" s="5">
+        <v>38841</v>
+      </c>
+      <c r="G751" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H751" s="1"/>
+      <c r="I751" s="1"/>
+      <c r="J751" s="1"/>
+      <c r="K751" s="1"/>
+      <c r="L751" s="1"/>
+      <c r="M751" s="1"/>
+      <c r="N751" s="1"/>
+      <c r="O751" s="1"/>
+      <c r="P751" s="1"/>
+      <c r="Q751" s="1"/>
+      <c r="R751" s="1"/>
+      <c r="S751" s="1"/>
+      <c r="T751" s="1"/>
+      <c r="U751" s="1"/>
+      <c r="V751" s="3"/>
+      <c r="W751" s="3"/>
+      <c r="X751" s="1"/>
+      <c r="Y751" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z751" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA751" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AB751" s="1" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="752" spans="1:28">
+      <c r="A752" s="5">
+        <v>773</v>
+      </c>
+      <c r="B752" s="2">
+        <v>46279.788865740702</v>
+      </c>
+      <c r="C752" s="2">
+        <v>46279.789895833303</v>
+      </c>
+      <c r="D752" s="1" t="s">
+        <v>891</v>
+      </c>
+      <c r="E752" s="1" t="s">
+        <v>892</v>
+      </c>
+      <c r="F752" s="5">
+        <v>38722</v>
+      </c>
+      <c r="G752" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H752" s="1"/>
+      <c r="I752" s="1"/>
+      <c r="J752" s="1"/>
+      <c r="K752" s="1"/>
+      <c r="L752" s="1"/>
+      <c r="M752" s="1"/>
+      <c r="N752" s="1"/>
+      <c r="O752" s="1"/>
+      <c r="P752" s="1"/>
+      <c r="Q752" s="1"/>
+      <c r="R752" s="1"/>
+      <c r="S752" s="1"/>
+      <c r="T752" s="1"/>
+      <c r="U752" s="1"/>
+      <c r="V752" s="3"/>
+      <c r="W752" s="3"/>
+      <c r="X752" s="1"/>
+      <c r="Y752" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z752" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA752" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB752" s="1" t="s">
+        <v>1171</v>
+      </c>
+    </row>
+    <row r="753" spans="1:28">
+      <c r="A753" s="5">
+        <v>774</v>
+      </c>
+      <c r="B753" s="2">
+        <v>46279.78875</v>
+      </c>
+      <c r="C753" s="2">
+        <v>46279.794236111098</v>
+      </c>
+      <c r="D753" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E753" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F753" s="5">
+        <v>38401</v>
+      </c>
+      <c r="G753" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H753" s="1"/>
+      <c r="I753" s="1"/>
+      <c r="J753" s="1"/>
+      <c r="K753" s="1"/>
+      <c r="L753" s="1"/>
+      <c r="M753" s="1"/>
+      <c r="N753" s="1"/>
+      <c r="O753" s="1"/>
+      <c r="P753" s="1"/>
+      <c r="Q753" s="1"/>
+      <c r="R753" s="1"/>
+      <c r="S753" s="1"/>
+      <c r="T753" s="1"/>
+      <c r="U753" s="1"/>
+      <c r="V753" s="3"/>
+      <c r="W753" s="3"/>
+      <c r="X753" s="1"/>
+      <c r="Y753" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z753" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="AA753" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AB753" s="1" t="s">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="754" spans="1:28">
+      <c r="A754" s="5">
+        <v>775</v>
+      </c>
+      <c r="B754" s="2">
+        <v>46279.800104166701</v>
+      </c>
+      <c r="C754" s="2">
+        <v>46279.800648148099</v>
+      </c>
+      <c r="D754" s="1" t="s">
+        <v>921</v>
+      </c>
+      <c r="E754" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="F754" s="5">
+        <v>38158</v>
+      </c>
+      <c r="G754" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H754" s="1"/>
+      <c r="I754" s="1"/>
+      <c r="J754" s="1"/>
+      <c r="K754" s="1"/>
+      <c r="L754" s="1"/>
+      <c r="M754" s="1"/>
+      <c r="N754" s="1"/>
+      <c r="O754" s="1"/>
+      <c r="P754" s="1"/>
+      <c r="Q754" s="1"/>
+      <c r="R754" s="1"/>
+      <c r="S754" s="1"/>
+      <c r="T754" s="1"/>
+      <c r="U754" s="1"/>
+      <c r="V754" s="3"/>
+      <c r="W754" s="3"/>
+      <c r="X754" s="1"/>
+      <c r="Y754" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z754" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA754" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB754" s="1" t="s">
+        <v>1173</v>
+      </c>
+    </row>
+    <row r="755" spans="1:28">
+      <c r="A755" s="5">
+        <v>776</v>
+      </c>
+      <c r="B755" s="2">
+        <v>46279.807094907403</v>
+      </c>
+      <c r="C755" s="2">
+        <v>46279.808981481503</v>
+      </c>
+      <c r="D755" s="1" t="s">
+        <v>189</v>
+      </c>
+      <c r="E755" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F755" s="5">
+        <v>38401</v>
+      </c>
+      <c r="G755" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H755" s="1"/>
+      <c r="I755" s="1"/>
+      <c r="J755" s="1"/>
+      <c r="K755" s="1"/>
+      <c r="L755" s="1"/>
+      <c r="M755" s="1"/>
+      <c r="N755" s="1"/>
+      <c r="O755" s="1"/>
+      <c r="P755" s="1"/>
+      <c r="Q755" s="1"/>
+      <c r="R755" s="1"/>
+      <c r="S755" s="1"/>
+      <c r="T755" s="1"/>
+      <c r="U755" s="1"/>
+      <c r="V755" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="W755" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="X755" s="1" t="s">
+        <v>1174</v>
+      </c>
+      <c r="Y755" s="1"/>
+      <c r="Z755" s="1"/>
+      <c r="AA755" s="1"/>
+      <c r="AB755" s="1"/>
+    </row>
+    <row r="756" spans="1:28">
+      <c r="A756" s="5">
+        <v>777</v>
+      </c>
+      <c r="B756" s="2">
+        <v>46279.809675925899</v>
+      </c>
+      <c r="C756" s="2">
+        <v>46279.810601851903</v>
+      </c>
+      <c r="D756" s="1" t="s">
+        <v>949</v>
+      </c>
+      <c r="E756" s="1" t="s">
+        <v>950</v>
+      </c>
+      <c r="F756" s="5">
+        <v>38929</v>
+      </c>
+      <c r="G756" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H756" s="1"/>
+      <c r="I756" s="1"/>
+      <c r="J756" s="1"/>
+      <c r="K756" s="1"/>
+      <c r="L756" s="1"/>
+      <c r="M756" s="1"/>
+      <c r="N756" s="1"/>
+      <c r="O756" s="1"/>
+      <c r="P756" s="1"/>
+      <c r="Q756" s="1"/>
+      <c r="R756" s="1"/>
+      <c r="S756" s="1"/>
+      <c r="T756" s="1"/>
+      <c r="U756" s="1"/>
+      <c r="V756" s="3"/>
+      <c r="W756" s="3"/>
+      <c r="X756" s="1"/>
+      <c r="Y756" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z756" s="1"/>
+      <c r="AA756" s="1"/>
+      <c r="AB756" s="1"/>
+    </row>
+    <row r="757" spans="1:28">
+      <c r="A757" s="5">
+        <v>778</v>
+      </c>
+      <c r="B757" s="2">
+        <v>46279.794861111099</v>
+      </c>
+      <c r="C757" s="2">
+        <v>46279.811967592599</v>
+      </c>
+      <c r="D757" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="E757" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="F757" s="5">
+        <v>43193</v>
+      </c>
+      <c r="G757" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H757" s="1"/>
+      <c r="I757" s="1"/>
+      <c r="J757" s="1"/>
+      <c r="K757" s="1"/>
+      <c r="L757" s="1"/>
+      <c r="M757" s="1"/>
+      <c r="N757" s="1"/>
+      <c r="O757" s="1"/>
+      <c r="P757" s="1"/>
+      <c r="Q757" s="1"/>
+      <c r="R757" s="1"/>
+      <c r="S757" s="1"/>
+      <c r="T757" s="1"/>
+      <c r="U757" s="1"/>
+      <c r="V757" s="3"/>
+      <c r="W757" s="3"/>
+      <c r="X757" s="1"/>
+      <c r="Y757" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z757" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA757" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB757" s="1" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="758" spans="1:28">
+      <c r="A758" s="5">
+        <v>779</v>
+      </c>
+      <c r="B758" s="2">
+        <v>46279.813935185201</v>
+      </c>
+      <c r="C758" s="2">
+        <v>46279.815821759301</v>
+      </c>
+      <c r="D758" s="1" t="s">
+        <v>1176</v>
+      </c>
+      <c r="E758" s="1" t="s">
+        <v>1177</v>
+      </c>
+      <c r="F758" s="5">
+        <v>38466</v>
+      </c>
+      <c r="G758" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H758" s="1"/>
+      <c r="I758" s="1"/>
+      <c r="J758" s="1"/>
+      <c r="K758" s="1"/>
+      <c r="L758" s="1"/>
+      <c r="M758" s="1"/>
+      <c r="N758" s="1"/>
+      <c r="O758" s="1"/>
+      <c r="P758" s="1"/>
+      <c r="Q758" s="1"/>
+      <c r="R758" s="1"/>
+      <c r="S758" s="1"/>
+      <c r="T758" s="1"/>
+      <c r="U758" s="1"/>
+      <c r="V758" s="3"/>
+      <c r="W758" s="3"/>
+      <c r="X758" s="1"/>
+      <c r="Y758" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z758" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA758" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB758" s="1" t="s">
+        <v>1178</v>
+      </c>
+    </row>
+    <row r="759" spans="1:28">
+      <c r="A759" s="5">
+        <v>780</v>
+      </c>
+      <c r="B759" s="2">
+        <v>46279.8123611111</v>
+      </c>
+      <c r="C759" s="2">
+        <v>46279.820949074099</v>
+      </c>
+      <c r="D759" s="1" t="s">
+        <v>795</v>
+      </c>
+      <c r="E759" s="1" t="s">
+        <v>796</v>
+      </c>
+      <c r="F759" s="5">
+        <v>38141</v>
+      </c>
+      <c r="G759" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H759" s="1"/>
+      <c r="I759" s="1"/>
+      <c r="J759" s="1"/>
+      <c r="K759" s="1"/>
+      <c r="L759" s="1"/>
+      <c r="M759" s="1"/>
+      <c r="N759" s="1"/>
+      <c r="O759" s="1"/>
+      <c r="P759" s="1"/>
+      <c r="Q759" s="1"/>
+      <c r="R759" s="1"/>
+      <c r="S759" s="1"/>
+      <c r="T759" s="1"/>
+      <c r="U759" s="1"/>
+      <c r="V759" s="3"/>
+      <c r="W759" s="3"/>
+      <c r="X759" s="1"/>
+      <c r="Y759" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z759" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA759" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB759" s="1" t="s">
+        <v>1179</v>
+      </c>
+    </row>
+    <row r="760" spans="1:28">
+      <c r="A760" s="5">
+        <v>781</v>
+      </c>
+      <c r="B760" s="2">
+        <v>46279.824814814798</v>
+      </c>
+      <c r="C760" s="2">
+        <v>46279.827685185199</v>
+      </c>
+      <c r="D760" s="1" t="s">
+        <v>843</v>
+      </c>
+      <c r="E760" s="1" t="s">
+        <v>844</v>
+      </c>
+      <c r="F760" s="5">
+        <v>38799</v>
+      </c>
+      <c r="G760" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H760" s="1"/>
+      <c r="I760" s="1"/>
+      <c r="J760" s="1"/>
+      <c r="K760" s="1"/>
+      <c r="L760" s="1"/>
+      <c r="M760" s="1"/>
+      <c r="N760" s="1"/>
+      <c r="O760" s="1"/>
+      <c r="P760" s="1"/>
+      <c r="Q760" s="1"/>
+      <c r="R760" s="1"/>
+      <c r="S760" s="1"/>
+      <c r="T760" s="1"/>
+      <c r="U760" s="1"/>
+      <c r="V760" s="3"/>
+      <c r="W760" s="3"/>
+      <c r="X760" s="1"/>
+      <c r="Y760" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z760" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA760" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB760" s="1" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="761" spans="1:28">
+      <c r="A761" s="5">
+        <v>782</v>
+      </c>
+      <c r="B761" s="2">
+        <v>46279.8344097222</v>
+      </c>
+      <c r="C761" s="2">
+        <v>46279.835821759298</v>
+      </c>
+      <c r="D761" s="1" t="s">
+        <v>852</v>
+      </c>
+      <c r="E761" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="F761" s="5">
+        <v>38185</v>
+      </c>
+      <c r="G761" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H761" s="1"/>
+      <c r="I761" s="1"/>
+      <c r="J761" s="1"/>
+      <c r="K761" s="1"/>
+      <c r="L761" s="1"/>
+      <c r="M761" s="1"/>
+      <c r="N761" s="1"/>
+      <c r="O761" s="1"/>
+      <c r="P761" s="1"/>
+      <c r="Q761" s="1"/>
+      <c r="R761" s="1"/>
+      <c r="S761" s="1"/>
+      <c r="T761" s="1"/>
+      <c r="U761" s="1"/>
+      <c r="V761" s="3"/>
+      <c r="W761" s="3"/>
+      <c r="X761" s="1"/>
+      <c r="Y761" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z761" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA761" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB761" s="1" t="s">
+        <v>1181</v>
+      </c>
+    </row>
+    <row r="762" spans="1:28">
+      <c r="A762" s="5">
+        <v>783</v>
+      </c>
+      <c r="B762" s="2">
+        <v>46279.842905092599</v>
+      </c>
+      <c r="C762" s="2">
+        <v>46279.8436111111</v>
+      </c>
+      <c r="D762" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E762" s="1" t="s">
+        <v>1044</v>
+      </c>
+      <c r="F762" s="5">
+        <v>38607</v>
+      </c>
+      <c r="G762" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H762" s="1"/>
+      <c r="I762" s="1"/>
+      <c r="J762" s="1"/>
+      <c r="K762" s="1"/>
+      <c r="L762" s="1"/>
+      <c r="M762" s="1"/>
+      <c r="N762" s="1"/>
+      <c r="O762" s="1"/>
+      <c r="P762" s="1"/>
+      <c r="Q762" s="1"/>
+      <c r="R762" s="1"/>
+      <c r="S762" s="1"/>
+      <c r="T762" s="1"/>
+      <c r="U762" s="1"/>
+      <c r="V762" s="3"/>
+      <c r="W762" s="3"/>
+      <c r="X762" s="1"/>
+      <c r="Y762" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z762" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA762" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB762" s="1" t="s">
+        <v>1182</v>
+      </c>
+    </row>
+    <row r="763" spans="1:28">
+      <c r="A763" s="5">
+        <v>784</v>
+      </c>
+      <c r="B763" s="2">
+        <v>46279.848495370403</v>
+      </c>
+      <c r="C763" s="2">
+        <v>46279.8488194444</v>
+      </c>
+      <c r="D763" s="1" t="s">
+        <v>834</v>
+      </c>
+      <c r="E763" s="1" t="s">
+        <v>835</v>
+      </c>
+      <c r="F763" s="5">
+        <v>38179</v>
+      </c>
+      <c r="G763" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H763" s="1"/>
+      <c r="I763" s="1"/>
+      <c r="J763" s="1"/>
+      <c r="K763" s="1"/>
+      <c r="L763" s="1"/>
+      <c r="M763" s="1"/>
+      <c r="N763" s="1"/>
+      <c r="O763" s="1"/>
+      <c r="P763" s="1"/>
+      <c r="Q763" s="1"/>
+      <c r="R763" s="1"/>
+      <c r="S763" s="1"/>
+      <c r="T763" s="1"/>
+      <c r="U763" s="1"/>
+      <c r="V763" s="3"/>
+      <c r="W763" s="3"/>
+      <c r="X763" s="1"/>
+      <c r="Y763" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z763" s="1"/>
+      <c r="AA763" s="1"/>
+      <c r="AB763" s="1"/>
+    </row>
+    <row r="764" spans="1:28">
+      <c r="A764" s="5">
+        <v>785</v>
+      </c>
+      <c r="B764" s="2">
+        <v>46279.701493055603</v>
+      </c>
+      <c r="C764" s="2">
+        <v>46279.857662037</v>
+      </c>
+      <c r="D764" s="1" t="s">
+        <v>1183</v>
+      </c>
+      <c r="E764" s="1" t="s">
+        <v>1184</v>
+      </c>
+      <c r="F764" s="5">
+        <v>38847</v>
+      </c>
+      <c r="G764" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H764" s="1"/>
+      <c r="I764" s="1"/>
+      <c r="J764" s="1"/>
+      <c r="K764" s="1"/>
+      <c r="L764" s="1"/>
+      <c r="M764" s="1"/>
+      <c r="N764" s="1"/>
+      <c r="O764" s="1"/>
+      <c r="P764" s="1"/>
+      <c r="Q764" s="1"/>
+      <c r="R764" s="1"/>
+      <c r="S764" s="1"/>
+      <c r="T764" s="1"/>
+      <c r="U764" s="1"/>
+      <c r="V764" s="3"/>
+      <c r="W764" s="3"/>
+      <c r="X764" s="1"/>
+      <c r="Y764" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z764" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA764" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB764" s="1" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="765" spans="1:28">
+      <c r="A765" s="5">
+        <v>786</v>
+      </c>
+      <c r="B765" s="2">
+        <v>46279.872407407398</v>
+      </c>
+      <c r="C765" s="2">
+        <v>46279.872777777797</v>
+      </c>
+      <c r="D765" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E765" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F765" s="5">
+        <v>38193</v>
+      </c>
+      <c r="G765" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H765" s="1"/>
+      <c r="I765" s="1"/>
+      <c r="J765" s="1"/>
+      <c r="K765" s="1"/>
+      <c r="L765" s="1"/>
+      <c r="M765" s="1"/>
+      <c r="N765" s="1"/>
+      <c r="O765" s="1"/>
+      <c r="P765" s="1"/>
+      <c r="Q765" s="1"/>
+      <c r="R765" s="1"/>
+      <c r="S765" s="1"/>
+      <c r="T765" s="1"/>
+      <c r="U765" s="1"/>
+      <c r="V765" s="3"/>
+      <c r="W765" s="3"/>
+      <c r="X765" s="1"/>
+      <c r="Y765" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z765" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA765" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB765" s="1" t="s">
+        <v>1186</v>
+      </c>
+    </row>
+    <row r="766" spans="1:28">
+      <c r="A766" s="5">
+        <v>787</v>
+      </c>
+      <c r="B766" s="2">
+        <v>46279.892118055599</v>
+      </c>
+      <c r="C766" s="2">
+        <v>46279.893807870401</v>
+      </c>
+      <c r="D766" s="1" t="s">
+        <v>816</v>
+      </c>
+      <c r="E766" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="F766" s="5">
+        <v>38547</v>
+      </c>
+      <c r="G766" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H766" s="1"/>
+      <c r="I766" s="1"/>
+      <c r="J766" s="1"/>
+      <c r="K766" s="1"/>
+      <c r="L766" s="1"/>
+      <c r="M766" s="1"/>
+      <c r="N766" s="1"/>
+      <c r="O766" s="1"/>
+      <c r="P766" s="1"/>
+      <c r="Q766" s="1"/>
+      <c r="R766" s="1"/>
+      <c r="S766" s="1"/>
+      <c r="T766" s="1"/>
+      <c r="U766" s="1"/>
+      <c r="V766" s="3"/>
+      <c r="W766" s="3"/>
+      <c r="X766" s="1"/>
+      <c r="Y766" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z766" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA766" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB766" s="1" t="s">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="767" spans="1:28">
+      <c r="A767" s="5">
+        <v>788</v>
+      </c>
+      <c r="B767" s="2">
+        <v>46279.896990740701</v>
+      </c>
+      <c r="C767" s="2">
+        <v>46279.897337962997</v>
+      </c>
+      <c r="D767" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E767" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F767" s="5">
+        <v>38751</v>
+      </c>
+      <c r="G767" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H767" s="1"/>
+      <c r="I767" s="1"/>
+      <c r="J767" s="1"/>
+      <c r="K767" s="1"/>
+      <c r="L767" s="1"/>
+      <c r="M767" s="1"/>
+      <c r="N767" s="1"/>
+      <c r="O767" s="1"/>
+      <c r="P767" s="1"/>
+      <c r="Q767" s="1"/>
+      <c r="R767" s="1"/>
+      <c r="S767" s="1"/>
+      <c r="T767" s="1"/>
+      <c r="U767" s="1"/>
+      <c r="V767" s="3"/>
+      <c r="W767" s="3"/>
+      <c r="X767" s="1"/>
+      <c r="Y767" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z767" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA767" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB767" s="1" t="s">
+        <v>1188</v>
+      </c>
+    </row>
+    <row r="768" spans="1:28">
+      <c r="A768" s="5">
+        <v>789</v>
+      </c>
+      <c r="B768" s="2">
+        <v>46279.898020833301</v>
+      </c>
+      <c r="C768" s="2">
+        <v>46279.899050925902</v>
+      </c>
+      <c r="D768" s="1" t="s">
+        <v>924</v>
+      </c>
+      <c r="E768" s="1" t="s">
+        <v>925</v>
+      </c>
+      <c r="F768" s="5">
+        <v>38777</v>
+      </c>
+      <c r="G768" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H768" s="1"/>
+      <c r="I768" s="1"/>
+      <c r="J768" s="1"/>
+      <c r="K768" s="1"/>
+      <c r="L768" s="1"/>
+      <c r="M768" s="1"/>
+      <c r="N768" s="1"/>
+      <c r="O768" s="1"/>
+      <c r="P768" s="1"/>
+      <c r="Q768" s="1"/>
+      <c r="R768" s="1"/>
+      <c r="S768" s="1"/>
+      <c r="T768" s="1"/>
+      <c r="U768" s="1"/>
+      <c r="V768" s="3"/>
+      <c r="W768" s="3"/>
+      <c r="X768" s="1"/>
+      <c r="Y768" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z768" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AA768" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB768" s="1" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="769" spans="1:28">
+      <c r="A769" s="5">
+        <v>790</v>
+      </c>
+      <c r="B769" s="2">
+        <v>46279.908148148097</v>
+      </c>
+      <c r="C769" s="2">
+        <v>46279.909108796302</v>
+      </c>
+      <c r="D769" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E769" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F769" s="5">
+        <v>38561</v>
+      </c>
+      <c r="G769" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H769" s="1"/>
+      <c r="I769" s="1"/>
+      <c r="J769" s="1"/>
+      <c r="K769" s="1"/>
+      <c r="L769" s="1"/>
+      <c r="M769" s="1"/>
+      <c r="N769" s="1"/>
+      <c r="O769" s="1"/>
+      <c r="P769" s="1"/>
+      <c r="Q769" s="1"/>
+      <c r="R769" s="1"/>
+      <c r="S769" s="1"/>
+      <c r="T769" s="1"/>
+      <c r="U769" s="1"/>
+      <c r="V769" s="3" t="s">
+        <v>1190</v>
+      </c>
+      <c r="W769" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="X769" s="1" t="s">
+        <v>1191</v>
+      </c>
+      <c r="Y769" s="1"/>
+      <c r="Z769" s="1"/>
+      <c r="AA769" s="1"/>
+      <c r="AB769" s="1"/>
+    </row>
+    <row r="770" spans="1:28">
+      <c r="A770" s="5">
+        <v>791</v>
+      </c>
+      <c r="B770" s="2">
+        <v>46279.909270833297</v>
+      </c>
+      <c r="C770" s="2">
+        <v>46279.909467592603</v>
+      </c>
+      <c r="D770" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E770" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F770" s="5">
+        <v>38561</v>
+      </c>
+      <c r="G770" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H770" s="1"/>
+      <c r="I770" s="1"/>
+      <c r="J770" s="1"/>
+      <c r="K770" s="1"/>
+      <c r="L770" s="1"/>
+      <c r="M770" s="1"/>
+      <c r="N770" s="1"/>
+      <c r="O770" s="1"/>
+      <c r="P770" s="1"/>
+      <c r="Q770" s="1"/>
+      <c r="R770" s="1"/>
+      <c r="S770" s="1"/>
+      <c r="T770" s="1"/>
+      <c r="U770" s="1"/>
+      <c r="V770" s="3"/>
+      <c r="W770" s="3"/>
+      <c r="X770" s="1"/>
+      <c r="Y770" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z770" s="1"/>
+      <c r="AA770" s="1"/>
+      <c r="AB770" s="1"/>
+    </row>
+    <row r="771" spans="1:28">
+      <c r="A771" s="5">
+        <v>792</v>
+      </c>
+      <c r="B771" s="2">
+        <v>46279.936354166697</v>
+      </c>
+      <c r="C771" s="2">
+        <v>46279.936620370398</v>
+      </c>
+      <c r="D771" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E771" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F771" s="5">
+        <v>38656</v>
+      </c>
+      <c r="G771" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H771" s="1"/>
+      <c r="I771" s="1"/>
+      <c r="J771" s="1"/>
+      <c r="K771" s="1"/>
+      <c r="L771" s="1"/>
+      <c r="M771" s="1"/>
+      <c r="N771" s="1"/>
+      <c r="O771" s="1"/>
+      <c r="P771" s="1"/>
+      <c r="Q771" s="1"/>
+      <c r="R771" s="1"/>
+      <c r="S771" s="1"/>
+      <c r="T771" s="1"/>
+      <c r="U771" s="1"/>
+      <c r="V771" s="3"/>
+      <c r="W771" s="3"/>
+      <c r="X771" s="1"/>
+      <c r="Y771" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z771" s="1"/>
+      <c r="AA771" s="1"/>
+      <c r="AB771" s="1"/>
+    </row>
+    <row r="772" spans="1:28">
+      <c r="A772" s="5">
+        <v>793</v>
+      </c>
+      <c r="B772" s="2">
+        <v>46280.108182870397</v>
+      </c>
+      <c r="C772" s="2">
+        <v>46280.108483796299</v>
+      </c>
+      <c r="D772" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E772" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F772" s="5">
+        <v>38458</v>
+      </c>
+      <c r="G772" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H772" s="1"/>
+      <c r="I772" s="1"/>
+      <c r="J772" s="1"/>
+      <c r="K772" s="1"/>
+      <c r="L772" s="1"/>
+      <c r="M772" s="1"/>
+      <c r="N772" s="1"/>
+      <c r="O772" s="1"/>
+      <c r="P772" s="1"/>
+      <c r="Q772" s="1"/>
+      <c r="R772" s="1"/>
+      <c r="S772" s="1"/>
+      <c r="T772" s="1"/>
+      <c r="U772" s="1"/>
+      <c r="V772" s="3"/>
+      <c r="W772" s="3"/>
+      <c r="X772" s="1"/>
+      <c r="Y772" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z772" s="1"/>
+      <c r="AA772" s="1"/>
+      <c r="AB772" s="1"/>
+    </row>
+    <row r="773" spans="1:28">
+      <c r="A773" s="5">
+        <v>794</v>
+      </c>
+      <c r="B773" s="2">
+        <v>46280.108773148197</v>
+      </c>
+      <c r="C773" s="2">
+        <v>46280.111597222203</v>
+      </c>
+      <c r="D773" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="E773" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F773" s="5">
+        <v>38458</v>
+      </c>
+      <c r="G773" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H773" s="1"/>
+      <c r="I773" s="1"/>
+      <c r="J773" s="1"/>
+      <c r="K773" s="1"/>
+      <c r="L773" s="1"/>
+      <c r="M773" s="1"/>
+      <c r="N773" s="1"/>
+      <c r="O773" s="1"/>
+      <c r="P773" s="1"/>
+      <c r="Q773" s="1"/>
+      <c r="R773" s="1"/>
+      <c r="S773" s="1"/>
+      <c r="T773" s="1"/>
+      <c r="U773" s="1"/>
+      <c r="V773" s="3" t="s">
+        <v>758</v>
+      </c>
+      <c r="W773" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="X773" s="1" t="s">
+        <v>1192</v>
+      </c>
+      <c r="Y773" s="1"/>
+      <c r="Z773" s="1"/>
+      <c r="AA773" s="1"/>
+      <c r="AB773" s="1"/>
+    </row>
+    <row r="774" spans="1:28">
+      <c r="A774" s="5">
+        <v>795</v>
+      </c>
+      <c r="B774" s="2">
+        <v>46280.261284722197</v>
+      </c>
+      <c r="C774" s="2">
+        <v>46280.261550925898</v>
+      </c>
+      <c r="D774" s="1" t="s">
+        <v>1067</v>
+      </c>
+      <c r="E774" s="1" t="s">
+        <v>1068</v>
+      </c>
+      <c r="F774" s="5">
+        <v>38633</v>
+      </c>
+      <c r="G774" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H774" s="1"/>
+      <c r="I774" s="1"/>
+      <c r="J774" s="1"/>
+      <c r="K774" s="1"/>
+      <c r="L774" s="1"/>
+      <c r="M774" s="1"/>
+      <c r="N774" s="1"/>
+      <c r="O774" s="1"/>
+      <c r="P774" s="1"/>
+      <c r="Q774" s="1"/>
+      <c r="R774" s="1"/>
+      <c r="S774" s="1"/>
+      <c r="T774" s="1"/>
+      <c r="U774" s="1"/>
+      <c r="V774" s="3"/>
+      <c r="W774" s="3"/>
+      <c r="X774" s="1"/>
+      <c r="Y774" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z774" s="1"/>
+      <c r="AA774" s="1"/>
+      <c r="AB774" s="1"/>
+    </row>
+    <row r="775" spans="1:28">
+      <c r="A775" s="5">
+        <v>796</v>
+      </c>
+      <c r="B775" s="2">
+        <v>46280.299780092602</v>
+      </c>
+      <c r="C775" s="2">
+        <v>46280.300335648099</v>
+      </c>
+      <c r="D775" s="1" t="s">
+        <v>918</v>
+      </c>
+      <c r="E775" s="1" t="s">
+        <v>919</v>
+      </c>
+      <c r="F775" s="5">
+        <v>38780</v>
+      </c>
+      <c r="G775" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H775" s="1"/>
+      <c r="I775" s="1"/>
+      <c r="J775" s="1"/>
+      <c r="K775" s="1"/>
+      <c r="L775" s="1"/>
+      <c r="M775" s="1"/>
+      <c r="N775" s="1"/>
+      <c r="O775" s="1"/>
+      <c r="P775" s="1"/>
+      <c r="Q775" s="1"/>
+      <c r="R775" s="1"/>
+      <c r="S775" s="1"/>
+      <c r="T775" s="1"/>
+      <c r="U775" s="1"/>
+      <c r="V775" s="3"/>
+      <c r="W775" s="3"/>
+      <c r="X775" s="1"/>
+      <c r="Y775" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z775" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA775" s="1" t="s">
+        <v>1134</v>
+      </c>
+      <c r="AB775" s="1" t="s">
+        <v>1193</v>
+      </c>
+    </row>
+    <row r="776" spans="1:28">
+      <c r="A776" s="5">
+        <v>797</v>
+      </c>
+      <c r="B776" s="2">
+        <v>46280.341168981497</v>
+      </c>
+      <c r="C776" s="2">
+        <v>46280.341805555603</v>
+      </c>
+      <c r="D776" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="E776" s="1" t="s">
+        <v>940</v>
+      </c>
+      <c r="F776" s="5">
+        <v>38166</v>
+      </c>
+      <c r="G776" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H776" s="1"/>
+      <c r="I776" s="1"/>
+      <c r="J776" s="1"/>
+      <c r="K776" s="1"/>
+      <c r="L776" s="1"/>
+      <c r="M776" s="1"/>
+      <c r="N776" s="1"/>
+      <c r="O776" s="1"/>
+      <c r="P776" s="1"/>
+      <c r="Q776" s="1"/>
+      <c r="R776" s="1"/>
+      <c r="S776" s="1"/>
+      <c r="T776" s="1"/>
+      <c r="U776" s="1"/>
+      <c r="V776" s="3"/>
+      <c r="W776" s="3"/>
+      <c r="X776" s="1"/>
+      <c r="Y776" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z776" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AA776" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB776" s="1" t="s">
+        <v>1195</v>
+      </c>
+    </row>
+    <row r="777" spans="1:28">
+      <c r="A777" s="5">
+        <v>798</v>
+      </c>
+      <c r="B777" s="2">
+        <v>46280.363865740699</v>
+      </c>
+      <c r="C777" s="2">
+        <v>46280.364259259302</v>
+      </c>
+      <c r="D777" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="E777" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F777" s="5">
+        <v>38747</v>
+      </c>
+      <c r="G777" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H777" s="1"/>
+      <c r="I777" s="1"/>
+      <c r="J777" s="1"/>
+      <c r="K777" s="1"/>
+      <c r="L777" s="1"/>
+      <c r="M777" s="1"/>
+      <c r="N777" s="1"/>
+      <c r="O777" s="1"/>
+      <c r="P777" s="1"/>
+      <c r="Q777" s="1"/>
+      <c r="R777" s="1"/>
+      <c r="S777" s="1"/>
+      <c r="T777" s="1"/>
+      <c r="U777" s="1"/>
+      <c r="V777" s="3"/>
+      <c r="W777" s="3"/>
+      <c r="X777" s="1"/>
+      <c r="Y777" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z777" s="1"/>
+      <c r="AA777" s="1"/>
+      <c r="AB777" s="1"/>
+    </row>
+    <row r="778" spans="1:28">
+      <c r="A778" s="5">
+        <v>799</v>
+      </c>
+      <c r="B778" s="2">
+        <v>46280.365138888897</v>
+      </c>
+      <c r="C778" s="2">
+        <v>46280.367476851898</v>
+      </c>
+      <c r="D778" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E778" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F778" s="5">
+        <v>38862</v>
+      </c>
+      <c r="G778" s="1" t="s">
+        <v>757</v>
+      </c>
+      <c r="H778" s="1"/>
+      <c r="I778" s="1"/>
+      <c r="J778" s="1"/>
+      <c r="K778" s="1"/>
+      <c r="L778" s="1"/>
+      <c r="M778" s="1"/>
+      <c r="N778" s="1"/>
+      <c r="O778" s="1"/>
+      <c r="P778" s="1"/>
+      <c r="Q778" s="1"/>
+      <c r="R778" s="1"/>
+      <c r="S778" s="1"/>
+      <c r="T778" s="1"/>
+      <c r="U778" s="1"/>
+      <c r="V778" s="3" t="s">
+        <v>766</v>
+      </c>
+      <c r="W778" s="3" t="s">
+        <v>759</v>
+      </c>
+      <c r="X778" s="1" t="s">
+        <v>1196</v>
+      </c>
+      <c r="Y778" s="1"/>
+      <c r="Z778" s="1"/>
+      <c r="AA778" s="1"/>
+      <c r="AB778" s="1"/>
+    </row>
+    <row r="779" spans="1:28">
+      <c r="A779" s="5">
+        <v>800</v>
+      </c>
+      <c r="B779" s="2">
+        <v>46280.367604166699</v>
+      </c>
+      <c r="C779" s="2">
+        <v>46280.372962963003</v>
+      </c>
+      <c r="D779" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E779" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F779" s="5">
+        <v>38862</v>
+      </c>
+      <c r="G779" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H779" s="1"/>
+      <c r="I779" s="1"/>
+      <c r="J779" s="1"/>
+      <c r="K779" s="1"/>
+      <c r="L779" s="1"/>
+      <c r="M779" s="1"/>
+      <c r="N779" s="1"/>
+      <c r="O779" s="1"/>
+      <c r="P779" s="1"/>
+      <c r="Q779" s="1"/>
+      <c r="R779" s="1"/>
+      <c r="S779" s="1"/>
+      <c r="T779" s="1"/>
+      <c r="U779" s="1"/>
+      <c r="V779" s="3"/>
+      <c r="W779" s="3"/>
+      <c r="X779" s="1"/>
+      <c r="Y779" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z779" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA779" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB779" s="1" t="s">
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="780" spans="1:28">
+      <c r="A780" s="5">
+        <v>801</v>
+      </c>
+      <c r="B780" s="2">
+        <v>46280.378472222197</v>
+      </c>
+      <c r="C780" s="2">
+        <v>46280.379050925898</v>
+      </c>
+      <c r="D780" s="1" t="s">
+        <v>961</v>
+      </c>
+      <c r="E780" s="1" t="s">
+        <v>962</v>
+      </c>
+      <c r="F780" s="5">
+        <v>38233</v>
+      </c>
+      <c r="G780" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H780" s="1"/>
+      <c r="I780" s="1"/>
+      <c r="J780" s="1"/>
+      <c r="K780" s="1"/>
+      <c r="L780" s="1"/>
+      <c r="M780" s="1"/>
+      <c r="N780" s="1"/>
+      <c r="O780" s="1"/>
+      <c r="P780" s="1"/>
+      <c r="Q780" s="1"/>
+      <c r="R780" s="1"/>
+      <c r="S780" s="1"/>
+      <c r="T780" s="1"/>
+      <c r="U780" s="1"/>
+      <c r="V780" s="3"/>
+      <c r="W780" s="3"/>
+      <c r="X780" s="1"/>
+      <c r="Y780" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z780" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA780" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB780" s="1" t="s">
+        <v>1198</v>
+      </c>
+    </row>
+    <row r="781" spans="1:28">
+      <c r="A781" s="5">
+        <v>802</v>
+      </c>
+      <c r="B781" s="2">
+        <v>46280.390775462998</v>
+      </c>
+      <c r="C781" s="2">
+        <v>46280.391458333303</v>
+      </c>
+      <c r="D781" s="1" t="s">
+        <v>819</v>
+      </c>
+      <c r="E781" s="1" t="s">
+        <v>820</v>
+      </c>
+      <c r="F781" s="5">
+        <v>38553</v>
+      </c>
+      <c r="G781" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H781" s="1"/>
+      <c r="I781" s="1"/>
+      <c r="J781" s="1"/>
+      <c r="K781" s="1"/>
+      <c r="L781" s="1"/>
+      <c r="M781" s="1"/>
+      <c r="N781" s="1"/>
+      <c r="O781" s="1"/>
+      <c r="P781" s="1"/>
+      <c r="Q781" s="1"/>
+      <c r="R781" s="1"/>
+      <c r="S781" s="1"/>
+      <c r="T781" s="1"/>
+      <c r="U781" s="1"/>
+      <c r="V781" s="3"/>
+      <c r="W781" s="3"/>
+      <c r="X781" s="1"/>
+      <c r="Y781" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z781" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA781" s="1" t="s">
+        <v>1109</v>
+      </c>
+      <c r="AB781" s="1" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="782" spans="1:28">
+      <c r="A782" s="5">
+        <v>803</v>
+      </c>
+      <c r="B782" s="2">
+        <v>46280.394467592603</v>
+      </c>
+      <c r="C782" s="2">
+        <v>46280.394965277803</v>
+      </c>
+      <c r="D782" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="E782" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F782" s="5">
+        <v>38704</v>
+      </c>
+      <c r="G782" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H782" s="1"/>
+      <c r="I782" s="1"/>
+      <c r="J782" s="1"/>
+      <c r="K782" s="1"/>
+      <c r="L782" s="1"/>
+      <c r="M782" s="1"/>
+      <c r="N782" s="1"/>
+      <c r="O782" s="1"/>
+      <c r="P782" s="1"/>
+      <c r="Q782" s="1"/>
+      <c r="R782" s="1"/>
+      <c r="S782" s="1"/>
+      <c r="T782" s="1"/>
+      <c r="U782" s="1"/>
+      <c r="V782" s="3"/>
+      <c r="W782" s="3"/>
+      <c r="X782" s="1"/>
+      <c r="Y782" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z782" s="1"/>
+      <c r="AA782" s="1"/>
+      <c r="AB782" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S71" r:id="rId1" xr:uid="{DBEDA7D9-6C97-43FD-AB0F-DEBA1D8AA177}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="86" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E0F74058-D8AA-4C4F-AEE7-F87B25A5D3AA}"/>
+  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83E7EC78-E40B-4AEC-AC63-351CF2C00481}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3667" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3702" uniqueCount="1207">
   <si>
     <t>Id</t>
   </si>
@@ -3636,13 +3636,34 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Monica%20Lizeth%20Carre%C3%B1.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Maria%20Fernanda%20Migue.jpg</t>
+  </si>
+  <si>
+    <t>ricardo.acosta@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Ricardo Acosta Soto</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/WhatsApp%20Image%202026-09-15%20at%209.56.51%20AM_Ricardo%20Acosta%20Soto.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Santa%20Fe.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/93d1f20f-5ce0-49c2-aba7-d86c26bd06c0_Moises%20Garcia%20Santos.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/1789489491477902937509053623929_Starbucks%20Central%20In.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3772,7 +3793,9 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="Invisible" pivot="0" table="0" count="0" xr9:uid="{6D0D4D43-C215-4EA0-8CBB-E997EF6A057F}"/>
+  </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -3784,9 +3807,13 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB782" totalsRowShown="0">
-  <autoFilter ref="A1:AB782" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB787" totalsRowShown="0">
+  <autoFilter ref="A1:AB787" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="25">
       <extLst>
@@ -3988,7 +4015,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="803" latestEventMarker="1127">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="808" latestEventMarker="1132">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4320,15 +4347,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB782"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AB787"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.42578125" customWidth="1"/>
+    <col min="5" max="5" width="32.453125" customWidth="1"/>
     <col min="6" max="28" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4414,7 +4441,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>13</v>
       </c>
@@ -4440,7 +4467,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:28">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>14</v>
       </c>
@@ -4466,7 +4493,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:28">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>15</v>
       </c>
@@ -4492,7 +4519,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:28">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>16</v>
       </c>
@@ -4518,7 +4545,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:28">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>17</v>
       </c>
@@ -4544,7 +4571,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:28">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>18</v>
       </c>
@@ -4570,7 +4597,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:28">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>19</v>
       </c>
@@ -4596,7 +4623,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:28">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>20</v>
       </c>
@@ -4622,7 +4649,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:28">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>21</v>
       </c>
@@ -4648,7 +4675,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:28">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>22</v>
       </c>
@@ -4674,7 +4701,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:28">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>23</v>
       </c>
@@ -4700,7 +4727,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:28">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>24</v>
       </c>
@@ -4726,7 +4753,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:28">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>25</v>
       </c>
@@ -4752,7 +4779,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:28">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>26</v>
       </c>
@@ -4778,7 +4805,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:28">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>27</v>
       </c>
@@ -4807,7 +4834,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>28</v>
       </c>
@@ -4833,7 +4860,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>29</v>
       </c>
@@ -4859,7 +4886,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:19">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>30</v>
       </c>
@@ -4885,7 +4912,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:19">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>31</v>
       </c>
@@ -4911,7 +4938,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>32</v>
       </c>
@@ -4937,7 +4964,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:19">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>33</v>
       </c>
@@ -4963,7 +4990,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>34</v>
       </c>
@@ -4989,7 +5016,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>35</v>
       </c>
@@ -5015,7 +5042,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>36</v>
       </c>
@@ -5041,7 +5068,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>37</v>
       </c>
@@ -5067,7 +5094,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>38</v>
       </c>
@@ -5093,7 +5120,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>39</v>
       </c>
@@ -5119,7 +5146,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>40</v>
       </c>
@@ -5145,7 +5172,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>41</v>
       </c>
@@ -5168,7 +5195,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>42</v>
       </c>
@@ -5194,7 +5221,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>43</v>
       </c>
@@ -5220,7 +5247,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>44</v>
       </c>
@@ -5246,7 +5273,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>45</v>
       </c>
@@ -5272,7 +5299,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>46</v>
       </c>
@@ -5298,7 +5325,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>47</v>
       </c>
@@ -5324,7 +5351,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>48</v>
       </c>
@@ -5350,7 +5377,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>49</v>
       </c>
@@ -5376,7 +5403,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>50</v>
       </c>
@@ -5402,7 +5429,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>51</v>
       </c>
@@ -5428,7 +5455,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>52</v>
       </c>
@@ -5454,7 +5481,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>53</v>
       </c>
@@ -5480,7 +5507,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>54</v>
       </c>
@@ -5506,7 +5533,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>55</v>
       </c>
@@ -5532,7 +5559,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:19">
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>56</v>
       </c>
@@ -5558,7 +5585,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:19">
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>57</v>
       </c>
@@ -5584,7 +5611,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>58</v>
       </c>
@@ -5610,7 +5637,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:19">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>59</v>
       </c>
@@ -5636,7 +5663,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:19">
+    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>60</v>
       </c>
@@ -5662,7 +5689,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="50" spans="1:19">
+    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>61</v>
       </c>
@@ -5688,7 +5715,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:19">
+    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>62</v>
       </c>
@@ -5714,7 +5741,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:19">
+    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>63</v>
       </c>
@@ -5740,7 +5767,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="53" spans="1:19">
+    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>64</v>
       </c>
@@ -5766,7 +5793,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" spans="1:19">
+    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>65</v>
       </c>
@@ -5792,7 +5819,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="55" spans="1:19">
+    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>66</v>
       </c>
@@ -5818,7 +5845,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:19">
+    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>67</v>
       </c>
@@ -5844,7 +5871,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="57" spans="1:19">
+    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>68</v>
       </c>
@@ -5870,7 +5897,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="58" spans="1:19">
+    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>69</v>
       </c>
@@ -5896,7 +5923,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:19">
+    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>70</v>
       </c>
@@ -5922,7 +5949,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="60" spans="1:19">
+    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>71</v>
       </c>
@@ -5948,7 +5975,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="1:19">
+    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>72</v>
       </c>
@@ -5974,7 +6001,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="62" spans="1:19">
+    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>73</v>
       </c>
@@ -6000,7 +6027,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="63" spans="1:19">
+    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>74</v>
       </c>
@@ -6026,7 +6053,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="64" spans="1:19">
+    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>75</v>
       </c>
@@ -6052,7 +6079,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="65" spans="1:19">
+    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>76</v>
       </c>
@@ -6078,7 +6105,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="66" spans="1:19">
+    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>77</v>
       </c>
@@ -6104,7 +6131,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="67" spans="1:19">
+    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>78</v>
       </c>
@@ -6130,7 +6157,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="68" spans="1:19">
+    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>79</v>
       </c>
@@ -6156,7 +6183,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="69" spans="1:19">
+    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>80</v>
       </c>
@@ -6182,7 +6209,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="70" spans="1:19">
+    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>81</v>
       </c>
@@ -6208,7 +6235,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="71" spans="1:19">
+    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>82</v>
       </c>
@@ -6234,7 +6261,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="1:19">
+    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>83</v>
       </c>
@@ -6260,7 +6287,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="73" spans="1:19">
+    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>84</v>
       </c>
@@ -6286,7 +6313,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="74" spans="1:19">
+    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>85</v>
       </c>
@@ -6312,7 +6339,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="75" spans="1:19">
+    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>86</v>
       </c>
@@ -6338,7 +6365,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" spans="1:19">
+    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>87</v>
       </c>
@@ -6364,7 +6391,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="77" spans="1:19">
+    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>88</v>
       </c>
@@ -6390,7 +6417,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="78" spans="1:19">
+    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>89</v>
       </c>
@@ -6416,7 +6443,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:19">
+    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>90</v>
       </c>
@@ -6442,7 +6469,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="80" spans="1:19">
+    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>91</v>
       </c>
@@ -6468,7 +6495,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="1:28">
+    <row r="81" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>92</v>
       </c>
@@ -6497,7 +6524,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="82" spans="1:28">
+    <row r="82" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>93</v>
       </c>
@@ -6523,7 +6550,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="83" spans="1:28">
+    <row r="83" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>94</v>
       </c>
@@ -6549,7 +6576,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="84" spans="1:28">
+    <row r="84" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>95</v>
       </c>
@@ -6575,7 +6602,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="85" spans="1:28">
+    <row r="85" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>96</v>
       </c>
@@ -6601,7 +6628,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="86" spans="1:28">
+    <row r="86" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>97</v>
       </c>
@@ -6624,7 +6651,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:28">
+    <row r="87" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>98</v>
       </c>
@@ -6650,7 +6677,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="88" spans="1:28">
+    <row r="88" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>99</v>
       </c>
@@ -6673,7 +6700,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="89" spans="1:28">
+    <row r="89" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>100</v>
       </c>
@@ -6699,7 +6726,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="90" spans="1:28">
+    <row r="90" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>101</v>
       </c>
@@ -6725,7 +6752,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="91" spans="1:28">
+    <row r="91" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>102</v>
       </c>
@@ -6754,7 +6781,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="92" spans="1:28">
+    <row r="92" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>103</v>
       </c>
@@ -6780,7 +6807,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="93" spans="1:28">
+    <row r="93" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>104</v>
       </c>
@@ -6806,7 +6833,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="94" spans="1:28">
+    <row r="94" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>105</v>
       </c>
@@ -6854,7 +6881,7 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
     </row>
-    <row r="95" spans="1:28">
+    <row r="95" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>106</v>
       </c>
@@ -6900,7 +6927,7 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
     </row>
-    <row r="96" spans="1:28">
+    <row r="96" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>107</v>
       </c>
@@ -6946,7 +6973,7 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97" spans="1:28">
+    <row r="97" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>108</v>
       </c>
@@ -6992,7 +7019,7 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
     </row>
-    <row r="98" spans="1:28">
+    <row r="98" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A98">
         <v>109</v>
       </c>
@@ -7038,7 +7065,7 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
     </row>
-    <row r="99" spans="1:28">
+    <row r="99" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A99">
         <v>110</v>
       </c>
@@ -7084,7 +7111,7 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
     </row>
-    <row r="100" spans="1:28">
+    <row r="100" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A100">
         <v>111</v>
       </c>
@@ -7130,7 +7157,7 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
     </row>
-    <row r="101" spans="1:28">
+    <row r="101" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A101">
         <v>112</v>
       </c>
@@ -7176,7 +7203,7 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
     </row>
-    <row r="102" spans="1:28">
+    <row r="102" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A102">
         <v>113</v>
       </c>
@@ -7222,7 +7249,7 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
     </row>
-    <row r="103" spans="1:28">
+    <row r="103" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A103">
         <v>114</v>
       </c>
@@ -7268,7 +7295,7 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
     </row>
-    <row r="104" spans="1:28">
+    <row r="104" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A104">
         <v>115</v>
       </c>
@@ -7314,7 +7341,7 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
     </row>
-    <row r="105" spans="1:28">
+    <row r="105" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A105">
         <v>116</v>
       </c>
@@ -7360,7 +7387,7 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
     </row>
-    <row r="106" spans="1:28">
+    <row r="106" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A106">
         <v>117</v>
       </c>
@@ -7406,7 +7433,7 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
     </row>
-    <row r="107" spans="1:28">
+    <row r="107" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A107">
         <v>118</v>
       </c>
@@ -7450,7 +7477,7 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
     </row>
-    <row r="108" spans="1:28">
+    <row r="108" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A108">
         <v>119</v>
       </c>
@@ -7496,7 +7523,7 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
     </row>
-    <row r="109" spans="1:28">
+    <row r="109" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A109">
         <v>120</v>
       </c>
@@ -7542,7 +7569,7 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
     </row>
-    <row r="110" spans="1:28">
+    <row r="110" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A110">
         <v>121</v>
       </c>
@@ -7588,7 +7615,7 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
     </row>
-    <row r="111" spans="1:28">
+    <row r="111" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A111">
         <v>122</v>
       </c>
@@ -7634,7 +7661,7 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
     </row>
-    <row r="112" spans="1:28">
+    <row r="112" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A112">
         <v>123</v>
       </c>
@@ -7680,7 +7707,7 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
     </row>
-    <row r="113" spans="1:28">
+    <row r="113" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A113">
         <v>124</v>
       </c>
@@ -7726,7 +7753,7 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
     </row>
-    <row r="114" spans="1:28">
+    <row r="114" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A114">
         <v>125</v>
       </c>
@@ -7772,7 +7799,7 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
     </row>
-    <row r="115" spans="1:28">
+    <row r="115" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A115">
         <v>126</v>
       </c>
@@ -7818,7 +7845,7 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
     </row>
-    <row r="116" spans="1:28">
+    <row r="116" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A116">
         <v>127</v>
       </c>
@@ -7864,7 +7891,7 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
     </row>
-    <row r="117" spans="1:28">
+    <row r="117" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A117">
         <v>128</v>
       </c>
@@ -7912,7 +7939,7 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
     </row>
-    <row r="118" spans="1:28">
+    <row r="118" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A118">
         <v>129</v>
       </c>
@@ -7958,7 +7985,7 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
     </row>
-    <row r="119" spans="1:28">
+    <row r="119" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A119">
         <v>130</v>
       </c>
@@ -8006,7 +8033,7 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
     </row>
-    <row r="120" spans="1:28">
+    <row r="120" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A120">
         <v>131</v>
       </c>
@@ -8052,7 +8079,7 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
     </row>
-    <row r="121" spans="1:28">
+    <row r="121" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A121">
         <v>132</v>
       </c>
@@ -8098,7 +8125,7 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
     </row>
-    <row r="122" spans="1:28">
+    <row r="122" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A122">
         <v>133</v>
       </c>
@@ -8144,7 +8171,7 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
     </row>
-    <row r="123" spans="1:28">
+    <row r="123" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A123">
         <v>134</v>
       </c>
@@ -8190,7 +8217,7 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
     </row>
-    <row r="124" spans="1:28">
+    <row r="124" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A124">
         <v>135</v>
       </c>
@@ -8236,7 +8263,7 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
     </row>
-    <row r="125" spans="1:28">
+    <row r="125" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A125">
         <v>136</v>
       </c>
@@ -8282,7 +8309,7 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
     </row>
-    <row r="126" spans="1:28">
+    <row r="126" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A126">
         <v>137</v>
       </c>
@@ -8328,7 +8355,7 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
     </row>
-    <row r="127" spans="1:28">
+    <row r="127" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A127">
         <v>138</v>
       </c>
@@ -8374,7 +8401,7 @@
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
     </row>
-    <row r="128" spans="1:28">
+    <row r="128" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A128">
         <v>139</v>
       </c>
@@ -8420,7 +8447,7 @@
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
     </row>
-    <row r="129" spans="1:28">
+    <row r="129" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A129">
         <v>140</v>
       </c>
@@ -8466,7 +8493,7 @@
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
     </row>
-    <row r="130" spans="1:28">
+    <row r="130" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A130">
         <v>141</v>
       </c>
@@ -8512,7 +8539,7 @@
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
     </row>
-    <row r="131" spans="1:28">
+    <row r="131" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A131">
         <v>142</v>
       </c>
@@ -8558,7 +8585,7 @@
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
     </row>
-    <row r="132" spans="1:28">
+    <row r="132" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A132">
         <v>143</v>
       </c>
@@ -8604,7 +8631,7 @@
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
     </row>
-    <row r="133" spans="1:28">
+    <row r="133" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A133">
         <v>144</v>
       </c>
@@ -8650,7 +8677,7 @@
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
     </row>
-    <row r="134" spans="1:28">
+    <row r="134" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A134">
         <v>145</v>
       </c>
@@ -8696,7 +8723,7 @@
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
     </row>
-    <row r="135" spans="1:28">
+    <row r="135" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A135">
         <v>146</v>
       </c>
@@ -8742,7 +8769,7 @@
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
     </row>
-    <row r="136" spans="1:28">
+    <row r="136" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A136">
         <v>147</v>
       </c>
@@ -8788,7 +8815,7 @@
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
     </row>
-    <row r="137" spans="1:28">
+    <row r="137" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A137">
         <v>148</v>
       </c>
@@ -8836,7 +8863,7 @@
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
     </row>
-    <row r="138" spans="1:28">
+    <row r="138" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A138">
         <v>149</v>
       </c>
@@ -8882,7 +8909,7 @@
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
     </row>
-    <row r="139" spans="1:28">
+    <row r="139" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A139">
         <v>150</v>
       </c>
@@ -8928,7 +8955,7 @@
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
     </row>
-    <row r="140" spans="1:28">
+    <row r="140" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A140">
         <v>151</v>
       </c>
@@ -8974,7 +9001,7 @@
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
     </row>
-    <row r="141" spans="1:28">
+    <row r="141" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A141">
         <v>152</v>
       </c>
@@ -9020,7 +9047,7 @@
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
     </row>
-    <row r="142" spans="1:28">
+    <row r="142" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A142">
         <v>153</v>
       </c>
@@ -9066,7 +9093,7 @@
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
     </row>
-    <row r="143" spans="1:28">
+    <row r="143" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A143">
         <v>154</v>
       </c>
@@ -9112,7 +9139,7 @@
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
     </row>
-    <row r="144" spans="1:28">
+    <row r="144" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A144">
         <v>155</v>
       </c>
@@ -9158,7 +9185,7 @@
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
     </row>
-    <row r="145" spans="1:28">
+    <row r="145" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A145">
         <v>156</v>
       </c>
@@ -9206,7 +9233,7 @@
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
     </row>
-    <row r="146" spans="1:28">
+    <row r="146" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A146">
         <v>157</v>
       </c>
@@ -9252,7 +9279,7 @@
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
     </row>
-    <row r="147" spans="1:28">
+    <row r="147" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A147">
         <v>158</v>
       </c>
@@ -9298,7 +9325,7 @@
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
     </row>
-    <row r="148" spans="1:28">
+    <row r="148" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A148">
         <v>159</v>
       </c>
@@ -9346,7 +9373,7 @@
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
     </row>
-    <row r="149" spans="1:28">
+    <row r="149" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A149">
         <v>160</v>
       </c>
@@ -9394,7 +9421,7 @@
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
     </row>
-    <row r="150" spans="1:28">
+    <row r="150" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A150">
         <v>161</v>
       </c>
@@ -9440,7 +9467,7 @@
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
     </row>
-    <row r="151" spans="1:28">
+    <row r="151" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A151">
         <v>162</v>
       </c>
@@ -9488,7 +9515,7 @@
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
     </row>
-    <row r="152" spans="1:28">
+    <row r="152" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A152">
         <v>163</v>
       </c>
@@ -9536,7 +9563,7 @@
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
     </row>
-    <row r="153" spans="1:28">
+    <row r="153" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A153">
         <v>164</v>
       </c>
@@ -9582,7 +9609,7 @@
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
     </row>
-    <row r="154" spans="1:28">
+    <row r="154" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A154">
         <v>165</v>
       </c>
@@ -9630,7 +9657,7 @@
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
     </row>
-    <row r="155" spans="1:28">
+    <row r="155" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A155">
         <v>166</v>
       </c>
@@ -9678,7 +9705,7 @@
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
     </row>
-    <row r="156" spans="1:28">
+    <row r="156" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A156">
         <v>167</v>
       </c>
@@ -9726,7 +9753,7 @@
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
     </row>
-    <row r="157" spans="1:28">
+    <row r="157" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A157">
         <v>168</v>
       </c>
@@ -9774,7 +9801,7 @@
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
     </row>
-    <row r="158" spans="1:28">
+    <row r="158" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A158">
         <v>169</v>
       </c>
@@ -9822,7 +9849,7 @@
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
     </row>
-    <row r="159" spans="1:28">
+    <row r="159" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A159">
         <v>170</v>
       </c>
@@ -9870,7 +9897,7 @@
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
     </row>
-    <row r="160" spans="1:28">
+    <row r="160" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A160">
         <v>171</v>
       </c>
@@ -9918,7 +9945,7 @@
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
     </row>
-    <row r="161" spans="1:28">
+    <row r="161" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A161">
         <v>172</v>
       </c>
@@ -9966,7 +9993,7 @@
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
     </row>
-    <row r="162" spans="1:28">
+    <row r="162" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A162">
         <v>173</v>
       </c>
@@ -10014,7 +10041,7 @@
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
     </row>
-    <row r="163" spans="1:28">
+    <row r="163" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A163">
         <v>174</v>
       </c>
@@ -10062,7 +10089,7 @@
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
     </row>
-    <row r="164" spans="1:28">
+    <row r="164" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A164">
         <v>175</v>
       </c>
@@ -10110,7 +10137,7 @@
       <c r="AA164" s="1"/>
       <c r="AB164" s="1"/>
     </row>
-    <row r="165" spans="1:28">
+    <row r="165" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A165">
         <v>176</v>
       </c>
@@ -10158,7 +10185,7 @@
       <c r="AA165" s="1"/>
       <c r="AB165" s="1"/>
     </row>
-    <row r="166" spans="1:28">
+    <row r="166" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A166">
         <v>177</v>
       </c>
@@ -10206,7 +10233,7 @@
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
     </row>
-    <row r="167" spans="1:28">
+    <row r="167" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A167">
         <v>178</v>
       </c>
@@ -10254,7 +10281,7 @@
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
     </row>
-    <row r="168" spans="1:28">
+    <row r="168" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A168">
         <v>179</v>
       </c>
@@ -10302,7 +10329,7 @@
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
     </row>
-    <row r="169" spans="1:28">
+    <row r="169" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A169">
         <v>180</v>
       </c>
@@ -10350,7 +10377,7 @@
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
     </row>
-    <row r="170" spans="1:28">
+    <row r="170" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A170">
         <v>181</v>
       </c>
@@ -10398,7 +10425,7 @@
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
     </row>
-    <row r="171" spans="1:28">
+    <row r="171" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A171">
         <v>182</v>
       </c>
@@ -10446,7 +10473,7 @@
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
     </row>
-    <row r="172" spans="1:28">
+    <row r="172" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A172">
         <v>183</v>
       </c>
@@ -10494,7 +10521,7 @@
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
     </row>
-    <row r="173" spans="1:28">
+    <row r="173" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A173">
         <v>184</v>
       </c>
@@ -10540,7 +10567,7 @@
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
     </row>
-    <row r="174" spans="1:28">
+    <row r="174" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A174">
         <v>185</v>
       </c>
@@ -10588,7 +10615,7 @@
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
     </row>
-    <row r="175" spans="1:28">
+    <row r="175" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A175">
         <v>186</v>
       </c>
@@ -10636,7 +10663,7 @@
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
     </row>
-    <row r="176" spans="1:28">
+    <row r="176" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A176">
         <v>187</v>
       </c>
@@ -10684,7 +10711,7 @@
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
     </row>
-    <row r="177" spans="1:28">
+    <row r="177" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A177">
         <v>188</v>
       </c>
@@ -10732,7 +10759,7 @@
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
     </row>
-    <row r="178" spans="1:28">
+    <row r="178" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A178">
         <v>189</v>
       </c>
@@ -10780,7 +10807,7 @@
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
     </row>
-    <row r="179" spans="1:28">
+    <row r="179" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A179">
         <v>190</v>
       </c>
@@ -10828,7 +10855,7 @@
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
     </row>
-    <row r="180" spans="1:28">
+    <row r="180" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A180">
         <v>191</v>
       </c>
@@ -10876,7 +10903,7 @@
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
     </row>
-    <row r="181" spans="1:28">
+    <row r="181" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A181">
         <v>192</v>
       </c>
@@ -10924,7 +10951,7 @@
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
     </row>
-    <row r="182" spans="1:28">
+    <row r="182" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A182">
         <v>193</v>
       </c>
@@ -10972,7 +10999,7 @@
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
     </row>
-    <row r="183" spans="1:28">
+    <row r="183" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A183">
         <v>194</v>
       </c>
@@ -11020,7 +11047,7 @@
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
     </row>
-    <row r="184" spans="1:28">
+    <row r="184" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A184">
         <v>195</v>
       </c>
@@ -11068,7 +11095,7 @@
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
     </row>
-    <row r="185" spans="1:28">
+    <row r="185" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A185">
         <v>196</v>
       </c>
@@ -11116,7 +11143,7 @@
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
     </row>
-    <row r="186" spans="1:28">
+    <row r="186" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A186">
         <v>197</v>
       </c>
@@ -11164,7 +11191,7 @@
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
     </row>
-    <row r="187" spans="1:28">
+    <row r="187" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A187">
         <v>198</v>
       </c>
@@ -11212,7 +11239,7 @@
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
     </row>
-    <row r="188" spans="1:28">
+    <row r="188" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A188">
         <v>199</v>
       </c>
@@ -11260,7 +11287,7 @@
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
     </row>
-    <row r="189" spans="1:28">
+    <row r="189" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A189">
         <v>200</v>
       </c>
@@ -11308,7 +11335,7 @@
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
     </row>
-    <row r="190" spans="1:28">
+    <row r="190" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A190">
         <v>201</v>
       </c>
@@ -11356,7 +11383,7 @@
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
     </row>
-    <row r="191" spans="1:28">
+    <row r="191" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A191">
         <v>202</v>
       </c>
@@ -11404,7 +11431,7 @@
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
     </row>
-    <row r="192" spans="1:28">
+    <row r="192" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A192">
         <v>203</v>
       </c>
@@ -11452,7 +11479,7 @@
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
     </row>
-    <row r="193" spans="1:28">
+    <row r="193" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A193">
         <v>204</v>
       </c>
@@ -11500,7 +11527,7 @@
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
     </row>
-    <row r="194" spans="1:28">
+    <row r="194" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A194">
         <v>205</v>
       </c>
@@ -11548,7 +11575,7 @@
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
     </row>
-    <row r="195" spans="1:28">
+    <row r="195" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A195">
         <v>206</v>
       </c>
@@ -11596,7 +11623,7 @@
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
     </row>
-    <row r="196" spans="1:28">
+    <row r="196" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A196">
         <v>207</v>
       </c>
@@ -11642,7 +11669,7 @@
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
     </row>
-    <row r="197" spans="1:28">
+    <row r="197" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A197">
         <v>208</v>
       </c>
@@ -11690,7 +11717,7 @@
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
     </row>
-    <row r="198" spans="1:28">
+    <row r="198" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A198">
         <v>209</v>
       </c>
@@ -11736,7 +11763,7 @@
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
     </row>
-    <row r="199" spans="1:28">
+    <row r="199" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A199">
         <v>210</v>
       </c>
@@ -11784,7 +11811,7 @@
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
     </row>
-    <row r="200" spans="1:28">
+    <row r="200" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A200">
         <v>211</v>
       </c>
@@ -11832,7 +11859,7 @@
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
     </row>
-    <row r="201" spans="1:28">
+    <row r="201" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A201">
         <v>212</v>
       </c>
@@ -11880,7 +11907,7 @@
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
     </row>
-    <row r="202" spans="1:28">
+    <row r="202" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A202">
         <v>213</v>
       </c>
@@ -11926,7 +11953,7 @@
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
     </row>
-    <row r="203" spans="1:28">
+    <row r="203" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A203">
         <v>214</v>
       </c>
@@ -11972,7 +11999,7 @@
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
     </row>
-    <row r="204" spans="1:28">
+    <row r="204" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A204">
         <v>215</v>
       </c>
@@ -12020,7 +12047,7 @@
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
     </row>
-    <row r="205" spans="1:28">
+    <row r="205" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A205">
         <v>216</v>
       </c>
@@ -12068,7 +12095,7 @@
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
     </row>
-    <row r="206" spans="1:28">
+    <row r="206" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A206">
         <v>217</v>
       </c>
@@ -12116,7 +12143,7 @@
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
     </row>
-    <row r="207" spans="1:28">
+    <row r="207" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A207">
         <v>218</v>
       </c>
@@ -12164,7 +12191,7 @@
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
     </row>
-    <row r="208" spans="1:28">
+    <row r="208" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A208">
         <v>219</v>
       </c>
@@ -12210,7 +12237,7 @@
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
     </row>
-    <row r="209" spans="1:28">
+    <row r="209" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A209">
         <v>220</v>
       </c>
@@ -12256,7 +12283,7 @@
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
     </row>
-    <row r="210" spans="1:28">
+    <row r="210" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A210">
         <v>221</v>
       </c>
@@ -12304,7 +12331,7 @@
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
     </row>
-    <row r="211" spans="1:28">
+    <row r="211" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A211">
         <v>222</v>
       </c>
@@ -12352,7 +12379,7 @@
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
     </row>
-    <row r="212" spans="1:28">
+    <row r="212" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A212">
         <v>223</v>
       </c>
@@ -12398,7 +12425,7 @@
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
     </row>
-    <row r="213" spans="1:28">
+    <row r="213" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A213">
         <v>224</v>
       </c>
@@ -12446,7 +12473,7 @@
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
     </row>
-    <row r="214" spans="1:28">
+    <row r="214" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A214">
         <v>225</v>
       </c>
@@ -12494,7 +12521,7 @@
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
     </row>
-    <row r="215" spans="1:28">
+    <row r="215" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A215">
         <v>226</v>
       </c>
@@ -12540,7 +12567,7 @@
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
     </row>
-    <row r="216" spans="1:28">
+    <row r="216" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A216">
         <v>227</v>
       </c>
@@ -12586,7 +12613,7 @@
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
     </row>
-    <row r="217" spans="1:28">
+    <row r="217" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A217">
         <v>228</v>
       </c>
@@ -12632,7 +12659,7 @@
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
     </row>
-    <row r="218" spans="1:28">
+    <row r="218" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A218">
         <v>229</v>
       </c>
@@ -12680,7 +12707,7 @@
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
     </row>
-    <row r="219" spans="1:28">
+    <row r="219" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A219">
         <v>230</v>
       </c>
@@ -12726,7 +12753,7 @@
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
     </row>
-    <row r="220" spans="1:28">
+    <row r="220" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A220">
         <v>231</v>
       </c>
@@ -12774,7 +12801,7 @@
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
     </row>
-    <row r="221" spans="1:28">
+    <row r="221" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A221">
         <v>232</v>
       </c>
@@ -12822,7 +12849,7 @@
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
     </row>
-    <row r="222" spans="1:28">
+    <row r="222" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A222">
         <v>233</v>
       </c>
@@ -12870,7 +12897,7 @@
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
     </row>
-    <row r="223" spans="1:28">
+    <row r="223" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A223">
         <v>234</v>
       </c>
@@ -12916,7 +12943,7 @@
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
     </row>
-    <row r="224" spans="1:28">
+    <row r="224" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A224">
         <v>235</v>
       </c>
@@ -12964,7 +12991,7 @@
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
     </row>
-    <row r="225" spans="1:28">
+    <row r="225" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A225">
         <v>236</v>
       </c>
@@ -13010,7 +13037,7 @@
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
     </row>
-    <row r="226" spans="1:28">
+    <row r="226" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A226">
         <v>237</v>
       </c>
@@ -13056,7 +13083,7 @@
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
     </row>
-    <row r="227" spans="1:28">
+    <row r="227" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A227">
         <v>238</v>
       </c>
@@ -13102,7 +13129,7 @@
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
     </row>
-    <row r="228" spans="1:28">
+    <row r="228" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A228">
         <v>239</v>
       </c>
@@ -13148,7 +13175,7 @@
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
     </row>
-    <row r="229" spans="1:28">
+    <row r="229" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A229">
         <v>240</v>
       </c>
@@ -13196,7 +13223,7 @@
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
     </row>
-    <row r="230" spans="1:28">
+    <row r="230" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A230">
         <v>241</v>
       </c>
@@ -13242,7 +13269,7 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
     </row>
-    <row r="231" spans="1:28">
+    <row r="231" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A231">
         <v>242</v>
       </c>
@@ -13288,7 +13315,7 @@
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
     </row>
-    <row r="232" spans="1:28">
+    <row r="232" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A232">
         <v>243</v>
       </c>
@@ -13334,7 +13361,7 @@
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
     </row>
-    <row r="233" spans="1:28">
+    <row r="233" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A233">
         <v>244</v>
       </c>
@@ -13380,7 +13407,7 @@
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
     </row>
-    <row r="234" spans="1:28">
+    <row r="234" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A234">
         <v>245</v>
       </c>
@@ -13426,7 +13453,7 @@
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
     </row>
-    <row r="235" spans="1:28">
+    <row r="235" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A235">
         <v>246</v>
       </c>
@@ -13472,7 +13499,7 @@
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
     </row>
-    <row r="236" spans="1:28">
+    <row r="236" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A236">
         <v>247</v>
       </c>
@@ -13518,7 +13545,7 @@
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
     </row>
-    <row r="237" spans="1:28">
+    <row r="237" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A237">
         <v>248</v>
       </c>
@@ -13564,7 +13591,7 @@
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
     </row>
-    <row r="238" spans="1:28">
+    <row r="238" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A238">
         <v>249</v>
       </c>
@@ -13610,7 +13637,7 @@
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
     </row>
-    <row r="239" spans="1:28">
+    <row r="239" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A239">
         <v>250</v>
       </c>
@@ -13656,7 +13683,7 @@
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
     </row>
-    <row r="240" spans="1:28">
+    <row r="240" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A240">
         <v>251</v>
       </c>
@@ -13702,7 +13729,7 @@
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
     </row>
-    <row r="241" spans="1:28">
+    <row r="241" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A241">
         <v>252</v>
       </c>
@@ -13750,7 +13777,7 @@
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
     </row>
-    <row r="242" spans="1:28">
+    <row r="242" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A242">
         <v>253</v>
       </c>
@@ -13796,7 +13823,7 @@
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
     </row>
-    <row r="243" spans="1:28">
+    <row r="243" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A243">
         <v>254</v>
       </c>
@@ -13844,7 +13871,7 @@
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
     </row>
-    <row r="244" spans="1:28">
+    <row r="244" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A244">
         <v>255</v>
       </c>
@@ -13892,7 +13919,7 @@
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
     </row>
-    <row r="245" spans="1:28">
+    <row r="245" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A245">
         <v>256</v>
       </c>
@@ -13940,7 +13967,7 @@
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
     </row>
-    <row r="246" spans="1:28">
+    <row r="246" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A246">
         <v>257</v>
       </c>
@@ -13986,7 +14013,7 @@
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
     </row>
-    <row r="247" spans="1:28">
+    <row r="247" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A247">
         <v>258</v>
       </c>
@@ -14032,7 +14059,7 @@
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
     </row>
-    <row r="248" spans="1:28">
+    <row r="248" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A248">
         <v>259</v>
       </c>
@@ -14078,7 +14105,7 @@
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
     </row>
-    <row r="249" spans="1:28">
+    <row r="249" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A249">
         <v>260</v>
       </c>
@@ -14124,7 +14151,7 @@
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
     </row>
-    <row r="250" spans="1:28">
+    <row r="250" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A250">
         <v>261</v>
       </c>
@@ -14170,7 +14197,7 @@
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
     </row>
-    <row r="251" spans="1:28">
+    <row r="251" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A251">
         <v>262</v>
       </c>
@@ -14216,7 +14243,7 @@
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
     </row>
-    <row r="252" spans="1:28">
+    <row r="252" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A252">
         <v>263</v>
       </c>
@@ -14264,7 +14291,7 @@
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
     </row>
-    <row r="253" spans="1:28">
+    <row r="253" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A253">
         <v>264</v>
       </c>
@@ -14310,7 +14337,7 @@
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
     </row>
-    <row r="254" spans="1:28">
+    <row r="254" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A254">
         <v>265</v>
       </c>
@@ -14356,7 +14383,7 @@
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
     </row>
-    <row r="255" spans="1:28">
+    <row r="255" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A255">
         <v>266</v>
       </c>
@@ -14402,7 +14429,7 @@
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
     </row>
-    <row r="256" spans="1:28">
+    <row r="256" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A256">
         <v>267</v>
       </c>
@@ -14448,7 +14475,7 @@
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
     </row>
-    <row r="257" spans="1:28">
+    <row r="257" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A257">
         <v>268</v>
       </c>
@@ -14494,7 +14521,7 @@
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
     </row>
-    <row r="258" spans="1:28">
+    <row r="258" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A258">
         <v>269</v>
       </c>
@@ -14542,7 +14569,7 @@
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
     </row>
-    <row r="259" spans="1:28">
+    <row r="259" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A259">
         <v>270</v>
       </c>
@@ -14588,7 +14615,7 @@
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
     </row>
-    <row r="260" spans="1:28">
+    <row r="260" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A260">
         <v>271</v>
       </c>
@@ -14634,7 +14661,7 @@
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
     </row>
-    <row r="261" spans="1:28">
+    <row r="261" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A261">
         <v>272</v>
       </c>
@@ -14680,7 +14707,7 @@
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
     </row>
-    <row r="262" spans="1:28">
+    <row r="262" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A262">
         <v>273</v>
       </c>
@@ -14726,7 +14753,7 @@
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
     </row>
-    <row r="263" spans="1:28">
+    <row r="263" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A263">
         <v>274</v>
       </c>
@@ -14772,7 +14799,7 @@
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
     </row>
-    <row r="264" spans="1:28">
+    <row r="264" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A264">
         <v>275</v>
       </c>
@@ -14818,7 +14845,7 @@
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
     </row>
-    <row r="265" spans="1:28">
+    <row r="265" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A265">
         <v>276</v>
       </c>
@@ -14866,7 +14893,7 @@
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
     </row>
-    <row r="266" spans="1:28">
+    <row r="266" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A266">
         <v>277</v>
       </c>
@@ -14912,7 +14939,7 @@
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
     </row>
-    <row r="267" spans="1:28">
+    <row r="267" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A267">
         <v>278</v>
       </c>
@@ -14958,7 +14985,7 @@
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
     </row>
-    <row r="268" spans="1:28">
+    <row r="268" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A268">
         <v>279</v>
       </c>
@@ -15006,7 +15033,7 @@
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
     </row>
-    <row r="269" spans="1:28">
+    <row r="269" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A269">
         <v>280</v>
       </c>
@@ -15052,7 +15079,7 @@
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
     </row>
-    <row r="270" spans="1:28">
+    <row r="270" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A270">
         <v>281</v>
       </c>
@@ -15100,7 +15127,7 @@
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
     </row>
-    <row r="271" spans="1:28">
+    <row r="271" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A271">
         <v>282</v>
       </c>
@@ -15146,7 +15173,7 @@
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
     </row>
-    <row r="272" spans="1:28">
+    <row r="272" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A272">
         <v>283</v>
       </c>
@@ -15194,7 +15221,7 @@
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
     </row>
-    <row r="273" spans="1:28">
+    <row r="273" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A273">
         <v>284</v>
       </c>
@@ -15240,7 +15267,7 @@
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
     </row>
-    <row r="274" spans="1:28">
+    <row r="274" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A274">
         <v>285</v>
       </c>
@@ -15288,7 +15315,7 @@
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
     </row>
-    <row r="275" spans="1:28">
+    <row r="275" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A275">
         <v>286</v>
       </c>
@@ -15334,7 +15361,7 @@
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
     </row>
-    <row r="276" spans="1:28">
+    <row r="276" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A276">
         <v>287</v>
       </c>
@@ -15380,7 +15407,7 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
     </row>
-    <row r="277" spans="1:28">
+    <row r="277" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A277">
         <v>288</v>
       </c>
@@ -15426,7 +15453,7 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
     </row>
-    <row r="278" spans="1:28">
+    <row r="278" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A278">
         <v>289</v>
       </c>
@@ -15474,7 +15501,7 @@
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
     </row>
-    <row r="279" spans="1:28">
+    <row r="279" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A279">
         <v>290</v>
       </c>
@@ -15522,7 +15549,7 @@
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
     </row>
-    <row r="280" spans="1:28">
+    <row r="280" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A280">
         <v>291</v>
       </c>
@@ -15568,7 +15595,7 @@
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
     </row>
-    <row r="281" spans="1:28">
+    <row r="281" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A281">
         <v>292</v>
       </c>
@@ -15614,7 +15641,7 @@
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
     </row>
-    <row r="282" spans="1:28">
+    <row r="282" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A282">
         <v>293</v>
       </c>
@@ -15660,7 +15687,7 @@
       <c r="AA282" s="1"/>
       <c r="AB282" s="1"/>
     </row>
-    <row r="283" spans="1:28">
+    <row r="283" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A283">
         <v>294</v>
       </c>
@@ -15708,7 +15735,7 @@
       <c r="AA283" s="1"/>
       <c r="AB283" s="1"/>
     </row>
-    <row r="284" spans="1:28">
+    <row r="284" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A284">
         <v>295</v>
       </c>
@@ -15754,7 +15781,7 @@
       <c r="AA284" s="1"/>
       <c r="AB284" s="1"/>
     </row>
-    <row r="285" spans="1:28">
+    <row r="285" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A285">
         <v>296</v>
       </c>
@@ -15802,7 +15829,7 @@
       <c r="AA285" s="1"/>
       <c r="AB285" s="1"/>
     </row>
-    <row r="286" spans="1:28">
+    <row r="286" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A286">
         <v>297</v>
       </c>
@@ -15848,7 +15875,7 @@
       <c r="AA286" s="1"/>
       <c r="AB286" s="1"/>
     </row>
-    <row r="287" spans="1:28">
+    <row r="287" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A287">
         <v>298</v>
       </c>
@@ -15894,7 +15921,7 @@
       <c r="AA287" s="1"/>
       <c r="AB287" s="1"/>
     </row>
-    <row r="288" spans="1:28">
+    <row r="288" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A288">
         <v>299</v>
       </c>
@@ -15940,7 +15967,7 @@
       <c r="AA288" s="1"/>
       <c r="AB288" s="1"/>
     </row>
-    <row r="289" spans="1:28">
+    <row r="289" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A289">
         <v>300</v>
       </c>
@@ -15986,7 +16013,7 @@
       <c r="AA289" s="1"/>
       <c r="AB289" s="1"/>
     </row>
-    <row r="290" spans="1:28">
+    <row r="290" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A290">
         <v>301</v>
       </c>
@@ -16032,7 +16059,7 @@
       <c r="AA290" s="1"/>
       <c r="AB290" s="1"/>
     </row>
-    <row r="291" spans="1:28">
+    <row r="291" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A291">
         <v>302</v>
       </c>
@@ -16078,7 +16105,7 @@
       <c r="AA291" s="1"/>
       <c r="AB291" s="1"/>
     </row>
-    <row r="292" spans="1:28">
+    <row r="292" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A292">
         <v>303</v>
       </c>
@@ -16126,7 +16153,7 @@
       <c r="AA292" s="1"/>
       <c r="AB292" s="1"/>
     </row>
-    <row r="293" spans="1:28">
+    <row r="293" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A293">
         <v>304</v>
       </c>
@@ -16172,7 +16199,7 @@
       <c r="AA293" s="1"/>
       <c r="AB293" s="1"/>
     </row>
-    <row r="294" spans="1:28">
+    <row r="294" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A294">
         <v>305</v>
       </c>
@@ -16220,7 +16247,7 @@
       <c r="AA294" s="1"/>
       <c r="AB294" s="1"/>
     </row>
-    <row r="295" spans="1:28">
+    <row r="295" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A295">
         <v>306</v>
       </c>
@@ -16268,7 +16295,7 @@
       <c r="AA295" s="1"/>
       <c r="AB295" s="1"/>
     </row>
-    <row r="296" spans="1:28">
+    <row r="296" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A296">
         <v>307</v>
       </c>
@@ -16314,7 +16341,7 @@
       <c r="AA296" s="1"/>
       <c r="AB296" s="1"/>
     </row>
-    <row r="297" spans="1:28">
+    <row r="297" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A297">
         <v>308</v>
       </c>
@@ -16360,7 +16387,7 @@
       <c r="AA297" s="1"/>
       <c r="AB297" s="1"/>
     </row>
-    <row r="298" spans="1:28">
+    <row r="298" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A298">
         <v>309</v>
       </c>
@@ -16406,7 +16433,7 @@
       <c r="AA298" s="1"/>
       <c r="AB298" s="1"/>
     </row>
-    <row r="299" spans="1:28">
+    <row r="299" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A299">
         <v>310</v>
       </c>
@@ -16452,7 +16479,7 @@
       <c r="AA299" s="1"/>
       <c r="AB299" s="1"/>
     </row>
-    <row r="300" spans="1:28">
+    <row r="300" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A300">
         <v>311</v>
       </c>
@@ -16498,7 +16525,7 @@
       <c r="AA300" s="1"/>
       <c r="AB300" s="1"/>
     </row>
-    <row r="301" spans="1:28">
+    <row r="301" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A301">
         <v>312</v>
       </c>
@@ -16544,7 +16571,7 @@
       <c r="AA301" s="1"/>
       <c r="AB301" s="1"/>
     </row>
-    <row r="302" spans="1:28">
+    <row r="302" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A302">
         <v>313</v>
       </c>
@@ -16592,7 +16619,7 @@
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
     </row>
-    <row r="303" spans="1:28">
+    <row r="303" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A303">
         <v>314</v>
       </c>
@@ -16638,7 +16665,7 @@
       <c r="AA303" s="1"/>
       <c r="AB303" s="1"/>
     </row>
-    <row r="304" spans="1:28">
+    <row r="304" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A304">
         <v>315</v>
       </c>
@@ -16684,7 +16711,7 @@
       <c r="AA304" s="1"/>
       <c r="AB304" s="1"/>
     </row>
-    <row r="305" spans="1:28">
+    <row r="305" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A305">
         <v>316</v>
       </c>
@@ -16730,7 +16757,7 @@
       <c r="AA305" s="1"/>
       <c r="AB305" s="1"/>
     </row>
-    <row r="306" spans="1:28">
+    <row r="306" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A306">
         <v>317</v>
       </c>
@@ -16778,7 +16805,7 @@
       <c r="AA306" s="1"/>
       <c r="AB306" s="1"/>
     </row>
-    <row r="307" spans="1:28">
+    <row r="307" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A307">
         <v>318</v>
       </c>
@@ -16824,7 +16851,7 @@
       <c r="AA307" s="1"/>
       <c r="AB307" s="1"/>
     </row>
-    <row r="308" spans="1:28">
+    <row r="308" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A308">
         <v>319</v>
       </c>
@@ -16870,7 +16897,7 @@
       <c r="AA308" s="1"/>
       <c r="AB308" s="1"/>
     </row>
-    <row r="309" spans="1:28">
+    <row r="309" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A309">
         <v>320</v>
       </c>
@@ -16916,7 +16943,7 @@
       <c r="AA309" s="1"/>
       <c r="AB309" s="1"/>
     </row>
-    <row r="310" spans="1:28">
+    <row r="310" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A310">
         <v>321</v>
       </c>
@@ -16964,7 +16991,7 @@
       <c r="AA310" s="1"/>
       <c r="AB310" s="1"/>
     </row>
-    <row r="311" spans="1:28">
+    <row r="311" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A311">
         <v>322</v>
       </c>
@@ -17012,7 +17039,7 @@
       <c r="AA311" s="1"/>
       <c r="AB311" s="1"/>
     </row>
-    <row r="312" spans="1:28">
+    <row r="312" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A312">
         <v>323</v>
       </c>
@@ -17058,7 +17085,7 @@
       <c r="AA312" s="1"/>
       <c r="AB312" s="1"/>
     </row>
-    <row r="313" spans="1:28">
+    <row r="313" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A313">
         <v>324</v>
       </c>
@@ -17104,7 +17131,7 @@
       <c r="AA313" s="1"/>
       <c r="AB313" s="1"/>
     </row>
-    <row r="314" spans="1:28">
+    <row r="314" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A314">
         <v>325</v>
       </c>
@@ -17150,7 +17177,7 @@
       <c r="AA314" s="1"/>
       <c r="AB314" s="1"/>
     </row>
-    <row r="315" spans="1:28">
+    <row r="315" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A315">
         <v>326</v>
       </c>
@@ -17196,7 +17223,7 @@
       <c r="AA315" s="1"/>
       <c r="AB315" s="1"/>
     </row>
-    <row r="316" spans="1:28">
+    <row r="316" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A316">
         <v>327</v>
       </c>
@@ -17242,7 +17269,7 @@
       <c r="AA316" s="1"/>
       <c r="AB316" s="1"/>
     </row>
-    <row r="317" spans="1:28">
+    <row r="317" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A317">
         <v>328</v>
       </c>
@@ -17288,7 +17315,7 @@
       <c r="AA317" s="1"/>
       <c r="AB317" s="1"/>
     </row>
-    <row r="318" spans="1:28">
+    <row r="318" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A318">
         <v>329</v>
       </c>
@@ -17334,7 +17361,7 @@
       <c r="AA318" s="1"/>
       <c r="AB318" s="1"/>
     </row>
-    <row r="319" spans="1:28">
+    <row r="319" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A319">
         <v>330</v>
       </c>
@@ -17380,7 +17407,7 @@
       <c r="AA319" s="1"/>
       <c r="AB319" s="1"/>
     </row>
-    <row r="320" spans="1:28">
+    <row r="320" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A320">
         <v>331</v>
       </c>
@@ -17428,7 +17455,7 @@
       <c r="AA320" s="1"/>
       <c r="AB320" s="1"/>
     </row>
-    <row r="321" spans="1:28">
+    <row r="321" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A321">
         <v>332</v>
       </c>
@@ -17474,7 +17501,7 @@
       <c r="AA321" s="1"/>
       <c r="AB321" s="1"/>
     </row>
-    <row r="322" spans="1:28">
+    <row r="322" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A322">
         <v>333</v>
       </c>
@@ -17520,7 +17547,7 @@
       <c r="AA322" s="1"/>
       <c r="AB322" s="1"/>
     </row>
-    <row r="323" spans="1:28">
+    <row r="323" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A323">
         <v>334</v>
       </c>
@@ -17566,7 +17593,7 @@
       <c r="AA323" s="1"/>
       <c r="AB323" s="1"/>
     </row>
-    <row r="324" spans="1:28">
+    <row r="324" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A324">
         <v>335</v>
       </c>
@@ -17612,7 +17639,7 @@
       <c r="AA324" s="1"/>
       <c r="AB324" s="1"/>
     </row>
-    <row r="325" spans="1:28">
+    <row r="325" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A325">
         <v>336</v>
       </c>
@@ -17658,7 +17685,7 @@
       <c r="AA325" s="1"/>
       <c r="AB325" s="1"/>
     </row>
-    <row r="326" spans="1:28">
+    <row r="326" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A326">
         <v>337</v>
       </c>
@@ -17704,7 +17731,7 @@
       <c r="AA326" s="1"/>
       <c r="AB326" s="1"/>
     </row>
-    <row r="327" spans="1:28">
+    <row r="327" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A327">
         <v>338</v>
       </c>
@@ -17750,7 +17777,7 @@
       <c r="AA327" s="1"/>
       <c r="AB327" s="1"/>
     </row>
-    <row r="328" spans="1:28">
+    <row r="328" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A328">
         <v>339</v>
       </c>
@@ -17796,7 +17823,7 @@
       <c r="AA328" s="1"/>
       <c r="AB328" s="1"/>
     </row>
-    <row r="329" spans="1:28">
+    <row r="329" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A329">
         <v>340</v>
       </c>
@@ -17842,7 +17869,7 @@
       <c r="AA329" s="1"/>
       <c r="AB329" s="1"/>
     </row>
-    <row r="330" spans="1:28">
+    <row r="330" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A330">
         <v>341</v>
       </c>
@@ -17890,7 +17917,7 @@
       <c r="AA330" s="1"/>
       <c r="AB330" s="1"/>
     </row>
-    <row r="331" spans="1:28">
+    <row r="331" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A331">
         <v>342</v>
       </c>
@@ -17936,7 +17963,7 @@
       <c r="AA331" s="1"/>
       <c r="AB331" s="1"/>
     </row>
-    <row r="332" spans="1:28">
+    <row r="332" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A332">
         <v>343</v>
       </c>
@@ -17984,7 +18011,7 @@
       <c r="AA332" s="1"/>
       <c r="AB332" s="1"/>
     </row>
-    <row r="333" spans="1:28">
+    <row r="333" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A333">
         <v>344</v>
       </c>
@@ -18030,7 +18057,7 @@
       <c r="AA333" s="1"/>
       <c r="AB333" s="1"/>
     </row>
-    <row r="334" spans="1:28">
+    <row r="334" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A334">
         <v>345</v>
       </c>
@@ -18076,7 +18103,7 @@
       <c r="AA334" s="1"/>
       <c r="AB334" s="1"/>
     </row>
-    <row r="335" spans="1:28">
+    <row r="335" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A335">
         <v>354</v>
       </c>
@@ -18122,7 +18149,7 @@
       <c r="AA335" s="1"/>
       <c r="AB335" s="1"/>
     </row>
-    <row r="336" spans="1:28">
+    <row r="336" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A336">
         <v>355</v>
       </c>
@@ -18170,7 +18197,7 @@
       <c r="AA336" s="1"/>
       <c r="AB336" s="1"/>
     </row>
-    <row r="337" spans="1:28">
+    <row r="337" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A337">
         <v>356</v>
       </c>
@@ -18216,7 +18243,7 @@
       <c r="AA337" s="1"/>
       <c r="AB337" s="1"/>
     </row>
-    <row r="338" spans="1:28">
+    <row r="338" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A338">
         <v>357</v>
       </c>
@@ -18262,7 +18289,7 @@
       <c r="AA338" s="1"/>
       <c r="AB338" s="1"/>
     </row>
-    <row r="339" spans="1:28">
+    <row r="339" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A339">
         <v>358</v>
       </c>
@@ -18308,7 +18335,7 @@
       <c r="AA339" s="1"/>
       <c r="AB339" s="1"/>
     </row>
-    <row r="340" spans="1:28">
+    <row r="340" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A340">
         <v>359</v>
       </c>
@@ -18354,7 +18381,7 @@
       <c r="AA340" s="1"/>
       <c r="AB340" s="1"/>
     </row>
-    <row r="341" spans="1:28">
+    <row r="341" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A341">
         <v>360</v>
       </c>
@@ -18400,7 +18427,7 @@
       <c r="AA341" s="1"/>
       <c r="AB341" s="1"/>
     </row>
-    <row r="342" spans="1:28">
+    <row r="342" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A342">
         <v>361</v>
       </c>
@@ -18446,7 +18473,7 @@
       <c r="AA342" s="1"/>
       <c r="AB342" s="1"/>
     </row>
-    <row r="343" spans="1:28">
+    <row r="343" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A343">
         <v>362</v>
       </c>
@@ -18492,7 +18519,7 @@
       <c r="AA343" s="1"/>
       <c r="AB343" s="1"/>
     </row>
-    <row r="344" spans="1:28">
+    <row r="344" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A344">
         <v>363</v>
       </c>
@@ -18538,7 +18565,7 @@
       <c r="AA344" s="1"/>
       <c r="AB344" s="1"/>
     </row>
-    <row r="345" spans="1:28">
+    <row r="345" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A345">
         <v>364</v>
       </c>
@@ -18584,7 +18611,7 @@
       <c r="AA345" s="1"/>
       <c r="AB345" s="1"/>
     </row>
-    <row r="346" spans="1:28">
+    <row r="346" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A346">
         <v>365</v>
       </c>
@@ -18630,7 +18657,7 @@
       <c r="AA346" s="1"/>
       <c r="AB346" s="1"/>
     </row>
-    <row r="347" spans="1:28">
+    <row r="347" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A347">
         <v>366</v>
       </c>
@@ -18676,7 +18703,7 @@
       <c r="AA347" s="1"/>
       <c r="AB347" s="1"/>
     </row>
-    <row r="348" spans="1:28">
+    <row r="348" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A348">
         <v>367</v>
       </c>
@@ -18722,7 +18749,7 @@
       <c r="AA348" s="1"/>
       <c r="AB348" s="1"/>
     </row>
-    <row r="349" spans="1:28">
+    <row r="349" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A349">
         <v>368</v>
       </c>
@@ -18768,7 +18795,7 @@
       <c r="AA349" s="1"/>
       <c r="AB349" s="1"/>
     </row>
-    <row r="350" spans="1:28">
+    <row r="350" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A350">
         <v>369</v>
       </c>
@@ -18814,7 +18841,7 @@
       <c r="AA350" s="1"/>
       <c r="AB350" s="1"/>
     </row>
-    <row r="351" spans="1:28">
+    <row r="351" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A351">
         <v>370</v>
       </c>
@@ -18860,7 +18887,7 @@
       <c r="AA351" s="1"/>
       <c r="AB351" s="1"/>
     </row>
-    <row r="352" spans="1:28">
+    <row r="352" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A352">
         <v>371</v>
       </c>
@@ -18906,7 +18933,7 @@
       <c r="AA352" s="1"/>
       <c r="AB352" s="1"/>
     </row>
-    <row r="353" spans="1:28">
+    <row r="353" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A353">
         <v>372</v>
       </c>
@@ -18952,7 +18979,7 @@
       <c r="AA353" s="1"/>
       <c r="AB353" s="1"/>
     </row>
-    <row r="354" spans="1:28">
+    <row r="354" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A354">
         <v>373</v>
       </c>
@@ -18998,7 +19025,7 @@
       <c r="AA354" s="1"/>
       <c r="AB354" s="1"/>
     </row>
-    <row r="355" spans="1:28">
+    <row r="355" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A355">
         <v>374</v>
       </c>
@@ -19044,7 +19071,7 @@
       <c r="AA355" s="1"/>
       <c r="AB355" s="1"/>
     </row>
-    <row r="356" spans="1:28">
+    <row r="356" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A356">
         <v>375</v>
       </c>
@@ -19090,7 +19117,7 @@
       <c r="AA356" s="1"/>
       <c r="AB356" s="1"/>
     </row>
-    <row r="357" spans="1:28">
+    <row r="357" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A357">
         <v>376</v>
       </c>
@@ -19136,7 +19163,7 @@
       <c r="AA357" s="1"/>
       <c r="AB357" s="1"/>
     </row>
-    <row r="358" spans="1:28">
+    <row r="358" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A358">
         <v>377</v>
       </c>
@@ -19182,7 +19209,7 @@
       <c r="AA358" s="1"/>
       <c r="AB358" s="1"/>
     </row>
-    <row r="359" spans="1:28">
+    <row r="359" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A359">
         <v>378</v>
       </c>
@@ -19228,7 +19255,7 @@
       <c r="AA359" s="1"/>
       <c r="AB359" s="1"/>
     </row>
-    <row r="360" spans="1:28">
+    <row r="360" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A360">
         <v>379</v>
       </c>
@@ -19274,7 +19301,7 @@
       <c r="AA360" s="1"/>
       <c r="AB360" s="1"/>
     </row>
-    <row r="361" spans="1:28">
+    <row r="361" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A361">
         <v>380</v>
       </c>
@@ -19320,7 +19347,7 @@
       <c r="AA361" s="1"/>
       <c r="AB361" s="1"/>
     </row>
-    <row r="362" spans="1:28">
+    <row r="362" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A362">
         <v>381</v>
       </c>
@@ -19366,7 +19393,7 @@
       <c r="AA362" s="1"/>
       <c r="AB362" s="1"/>
     </row>
-    <row r="363" spans="1:28">
+    <row r="363" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A363">
         <v>382</v>
       </c>
@@ -19412,7 +19439,7 @@
       <c r="AA363" s="1"/>
       <c r="AB363" s="1"/>
     </row>
-    <row r="364" spans="1:28">
+    <row r="364" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A364">
         <v>383</v>
       </c>
@@ -19458,7 +19485,7 @@
       <c r="AA364" s="1"/>
       <c r="AB364" s="1"/>
     </row>
-    <row r="365" spans="1:28">
+    <row r="365" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A365">
         <v>384</v>
       </c>
@@ -19504,7 +19531,7 @@
       <c r="AA365" s="1"/>
       <c r="AB365" s="1"/>
     </row>
-    <row r="366" spans="1:28">
+    <row r="366" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A366">
         <v>385</v>
       </c>
@@ -19550,7 +19577,7 @@
       <c r="AA366" s="1"/>
       <c r="AB366" s="1"/>
     </row>
-    <row r="367" spans="1:28">
+    <row r="367" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A367">
         <v>386</v>
       </c>
@@ -19596,7 +19623,7 @@
       <c r="AA367" s="1"/>
       <c r="AB367" s="1"/>
     </row>
-    <row r="368" spans="1:28">
+    <row r="368" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A368">
         <v>387</v>
       </c>
@@ -19642,7 +19669,7 @@
       <c r="AA368" s="1"/>
       <c r="AB368" s="1"/>
     </row>
-    <row r="369" spans="1:28">
+    <row r="369" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A369">
         <v>388</v>
       </c>
@@ -19688,7 +19715,7 @@
       <c r="AA369" s="1"/>
       <c r="AB369" s="1"/>
     </row>
-    <row r="370" spans="1:28">
+    <row r="370" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A370">
         <v>389</v>
       </c>
@@ -19734,7 +19761,7 @@
       <c r="AA370" s="1"/>
       <c r="AB370" s="1"/>
     </row>
-    <row r="371" spans="1:28">
+    <row r="371" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A371">
         <v>390</v>
       </c>
@@ -19780,7 +19807,7 @@
       <c r="AA371" s="1"/>
       <c r="AB371" s="1"/>
     </row>
-    <row r="372" spans="1:28">
+    <row r="372" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A372">
         <v>391</v>
       </c>
@@ -19826,7 +19853,7 @@
       <c r="AA372" s="1"/>
       <c r="AB372" s="1"/>
     </row>
-    <row r="373" spans="1:28">
+    <row r="373" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A373">
         <v>392</v>
       </c>
@@ -19872,7 +19899,7 @@
       <c r="AA373" s="1"/>
       <c r="AB373" s="1"/>
     </row>
-    <row r="374" spans="1:28">
+    <row r="374" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A374">
         <v>393</v>
       </c>
@@ -19918,7 +19945,7 @@
       <c r="AA374" s="1"/>
       <c r="AB374" s="1"/>
     </row>
-    <row r="375" spans="1:28">
+    <row r="375" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A375">
         <v>394</v>
       </c>
@@ -19964,7 +19991,7 @@
       <c r="AA375" s="1"/>
       <c r="AB375" s="1"/>
     </row>
-    <row r="376" spans="1:28">
+    <row r="376" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A376">
         <v>395</v>
       </c>
@@ -20010,7 +20037,7 @@
       <c r="AA376" s="1"/>
       <c r="AB376" s="1"/>
     </row>
-    <row r="377" spans="1:28">
+    <row r="377" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A377">
         <v>396</v>
       </c>
@@ -20056,7 +20083,7 @@
       <c r="AA377" s="1"/>
       <c r="AB377" s="1"/>
     </row>
-    <row r="378" spans="1:28">
+    <row r="378" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A378">
         <v>397</v>
       </c>
@@ -20102,7 +20129,7 @@
       <c r="AA378" s="1"/>
       <c r="AB378" s="1"/>
     </row>
-    <row r="379" spans="1:28">
+    <row r="379" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A379">
         <v>398</v>
       </c>
@@ -20148,7 +20175,7 @@
       <c r="AA379" s="1"/>
       <c r="AB379" s="1"/>
     </row>
-    <row r="380" spans="1:28">
+    <row r="380" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A380">
         <v>399</v>
       </c>
@@ -20194,7 +20221,7 @@
       <c r="AA380" s="1"/>
       <c r="AB380" s="1"/>
     </row>
-    <row r="381" spans="1:28">
+    <row r="381" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A381">
         <v>400</v>
       </c>
@@ -20240,7 +20267,7 @@
       <c r="AA381" s="1"/>
       <c r="AB381" s="1"/>
     </row>
-    <row r="382" spans="1:28">
+    <row r="382" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A382">
         <v>401</v>
       </c>
@@ -20286,7 +20313,7 @@
       <c r="AA382" s="1"/>
       <c r="AB382" s="1"/>
     </row>
-    <row r="383" spans="1:28">
+    <row r="383" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A383">
         <v>402</v>
       </c>
@@ -20332,7 +20359,7 @@
       <c r="AA383" s="1"/>
       <c r="AB383" s="1"/>
     </row>
-    <row r="384" spans="1:28">
+    <row r="384" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A384">
         <v>403</v>
       </c>
@@ -20378,7 +20405,7 @@
       <c r="AA384" s="1"/>
       <c r="AB384" s="1"/>
     </row>
-    <row r="385" spans="1:28">
+    <row r="385" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A385">
         <v>404</v>
       </c>
@@ -20424,7 +20451,7 @@
       <c r="AA385" s="1"/>
       <c r="AB385" s="1"/>
     </row>
-    <row r="386" spans="1:28">
+    <row r="386" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A386">
         <v>405</v>
       </c>
@@ -20470,7 +20497,7 @@
       <c r="AA386" s="1"/>
       <c r="AB386" s="1"/>
     </row>
-    <row r="387" spans="1:28">
+    <row r="387" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A387">
         <v>406</v>
       </c>
@@ -20516,7 +20543,7 @@
       <c r="AA387" s="1"/>
       <c r="AB387" s="1"/>
     </row>
-    <row r="388" spans="1:28">
+    <row r="388" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A388">
         <v>407</v>
       </c>
@@ -20562,7 +20589,7 @@
       <c r="AA388" s="1"/>
       <c r="AB388" s="1"/>
     </row>
-    <row r="389" spans="1:28">
+    <row r="389" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A389">
         <v>408</v>
       </c>
@@ -20608,7 +20635,7 @@
       <c r="AA389" s="1"/>
       <c r="AB389" s="1"/>
     </row>
-    <row r="390" spans="1:28">
+    <row r="390" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A390">
         <v>409</v>
       </c>
@@ -20654,7 +20681,7 @@
       <c r="AA390" s="1"/>
       <c r="AB390" s="1"/>
     </row>
-    <row r="391" spans="1:28">
+    <row r="391" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A391">
         <v>410</v>
       </c>
@@ -20700,7 +20727,7 @@
       <c r="AA391" s="1"/>
       <c r="AB391" s="1"/>
     </row>
-    <row r="392" spans="1:28">
+    <row r="392" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A392">
         <v>411</v>
       </c>
@@ -20746,7 +20773,7 @@
       <c r="AA392" s="1"/>
       <c r="AB392" s="1"/>
     </row>
-    <row r="393" spans="1:28">
+    <row r="393" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A393">
         <v>412</v>
       </c>
@@ -20794,7 +20821,7 @@
       <c r="AA393" s="1"/>
       <c r="AB393" s="1"/>
     </row>
-    <row r="394" spans="1:28">
+    <row r="394" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A394">
         <v>413</v>
       </c>
@@ -20840,7 +20867,7 @@
       <c r="AA394" s="1"/>
       <c r="AB394" s="1"/>
     </row>
-    <row r="395" spans="1:28">
+    <row r="395" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A395">
         <v>414</v>
       </c>
@@ -20886,7 +20913,7 @@
       <c r="AA395" s="1"/>
       <c r="AB395" s="1"/>
     </row>
-    <row r="396" spans="1:28">
+    <row r="396" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A396">
         <v>415</v>
       </c>
@@ -20932,7 +20959,7 @@
       <c r="AA396" s="1"/>
       <c r="AB396" s="1"/>
     </row>
-    <row r="397" spans="1:28">
+    <row r="397" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A397">
         <v>416</v>
       </c>
@@ -20978,7 +21005,7 @@
       <c r="AA397" s="1"/>
       <c r="AB397" s="1"/>
     </row>
-    <row r="398" spans="1:28">
+    <row r="398" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A398">
         <v>417</v>
       </c>
@@ -21024,7 +21051,7 @@
       <c r="AA398" s="1"/>
       <c r="AB398" s="1"/>
     </row>
-    <row r="399" spans="1:28">
+    <row r="399" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A399">
         <v>418</v>
       </c>
@@ -21070,7 +21097,7 @@
       <c r="AA399" s="1"/>
       <c r="AB399" s="1"/>
     </row>
-    <row r="400" spans="1:28">
+    <row r="400" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A400">
         <v>419</v>
       </c>
@@ -21116,7 +21143,7 @@
       <c r="AA400" s="1"/>
       <c r="AB400" s="1"/>
     </row>
-    <row r="401" spans="1:28">
+    <row r="401" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A401">
         <v>420</v>
       </c>
@@ -21162,7 +21189,7 @@
       <c r="AA401" s="1"/>
       <c r="AB401" s="1"/>
     </row>
-    <row r="402" spans="1:28">
+    <row r="402" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A402">
         <v>421</v>
       </c>
@@ -21208,7 +21235,7 @@
       <c r="AA402" s="1"/>
       <c r="AB402" s="1"/>
     </row>
-    <row r="403" spans="1:28">
+    <row r="403" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A403">
         <v>422</v>
       </c>
@@ -21254,7 +21281,7 @@
       <c r="AA403" s="1"/>
       <c r="AB403" s="1"/>
     </row>
-    <row r="404" spans="1:28">
+    <row r="404" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A404">
         <v>423</v>
       </c>
@@ -21300,7 +21327,7 @@
       <c r="AA404" s="1"/>
       <c r="AB404" s="1"/>
     </row>
-    <row r="405" spans="1:28">
+    <row r="405" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A405">
         <v>424</v>
       </c>
@@ -21346,7 +21373,7 @@
       <c r="AA405" s="1"/>
       <c r="AB405" s="1"/>
     </row>
-    <row r="406" spans="1:28">
+    <row r="406" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A406">
         <v>425</v>
       </c>
@@ -21392,7 +21419,7 @@
       <c r="AA406" s="1"/>
       <c r="AB406" s="1"/>
     </row>
-    <row r="407" spans="1:28">
+    <row r="407" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A407">
         <v>426</v>
       </c>
@@ -21438,7 +21465,7 @@
       <c r="AA407" s="1"/>
       <c r="AB407" s="1"/>
     </row>
-    <row r="408" spans="1:28">
+    <row r="408" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A408">
         <v>427</v>
       </c>
@@ -21484,7 +21511,7 @@
       <c r="AA408" s="1"/>
       <c r="AB408" s="1"/>
     </row>
-    <row r="409" spans="1:28">
+    <row r="409" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A409">
         <v>428</v>
       </c>
@@ -21530,7 +21557,7 @@
       <c r="AA409" s="1"/>
       <c r="AB409" s="1"/>
     </row>
-    <row r="410" spans="1:28">
+    <row r="410" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A410">
         <v>429</v>
       </c>
@@ -21576,7 +21603,7 @@
       <c r="AA410" s="1"/>
       <c r="AB410" s="1"/>
     </row>
-    <row r="411" spans="1:28">
+    <row r="411" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A411">
         <v>430</v>
       </c>
@@ -21622,7 +21649,7 @@
       <c r="AA411" s="1"/>
       <c r="AB411" s="1"/>
     </row>
-    <row r="412" spans="1:28">
+    <row r="412" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A412">
         <v>431</v>
       </c>
@@ -21668,7 +21695,7 @@
       <c r="AA412" s="1"/>
       <c r="AB412" s="1"/>
     </row>
-    <row r="413" spans="1:28">
+    <row r="413" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A413">
         <v>432</v>
       </c>
@@ -21716,7 +21743,7 @@
       <c r="AA413" s="1"/>
       <c r="AB413" s="1"/>
     </row>
-    <row r="414" spans="1:28">
+    <row r="414" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A414">
         <v>433</v>
       </c>
@@ -21762,7 +21789,7 @@
       <c r="AA414" s="1"/>
       <c r="AB414" s="1"/>
     </row>
-    <row r="415" spans="1:28">
+    <row r="415" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A415">
         <v>434</v>
       </c>
@@ -21808,7 +21835,7 @@
       <c r="AA415" s="1"/>
       <c r="AB415" s="1"/>
     </row>
-    <row r="416" spans="1:28">
+    <row r="416" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A416">
         <v>435</v>
       </c>
@@ -21856,7 +21883,7 @@
       <c r="AA416" s="1"/>
       <c r="AB416" s="1"/>
     </row>
-    <row r="417" spans="1:28">
+    <row r="417" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A417">
         <v>436</v>
       </c>
@@ -21902,7 +21929,7 @@
       <c r="AA417" s="1"/>
       <c r="AB417" s="1"/>
     </row>
-    <row r="418" spans="1:28">
+    <row r="418" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A418">
         <v>437</v>
       </c>
@@ -21948,7 +21975,7 @@
       <c r="AA418" s="1"/>
       <c r="AB418" s="1"/>
     </row>
-    <row r="419" spans="1:28">
+    <row r="419" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A419">
         <v>438</v>
       </c>
@@ -21994,7 +22021,7 @@
       <c r="AA419" s="1"/>
       <c r="AB419" s="1"/>
     </row>
-    <row r="420" spans="1:28">
+    <row r="420" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A420">
         <v>439</v>
       </c>
@@ -22040,7 +22067,7 @@
       <c r="AA420" s="1"/>
       <c r="AB420" s="1"/>
     </row>
-    <row r="421" spans="1:28">
+    <row r="421" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A421">
         <v>440</v>
       </c>
@@ -22086,7 +22113,7 @@
       <c r="AA421" s="1"/>
       <c r="AB421" s="1"/>
     </row>
-    <row r="422" spans="1:28">
+    <row r="422" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A422">
         <v>441</v>
       </c>
@@ -22132,7 +22159,7 @@
       <c r="AA422" s="1"/>
       <c r="AB422" s="1"/>
     </row>
-    <row r="423" spans="1:28">
+    <row r="423" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A423">
         <v>442</v>
       </c>
@@ -22180,7 +22207,7 @@
       <c r="AA423" s="1"/>
       <c r="AB423" s="1"/>
     </row>
-    <row r="424" spans="1:28">
+    <row r="424" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A424">
         <v>443</v>
       </c>
@@ -22226,7 +22253,7 @@
       <c r="AA424" s="1"/>
       <c r="AB424" s="1"/>
     </row>
-    <row r="425" spans="1:28">
+    <row r="425" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A425">
         <v>444</v>
       </c>
@@ -22272,7 +22299,7 @@
       <c r="AA425" s="1"/>
       <c r="AB425" s="1"/>
     </row>
-    <row r="426" spans="1:28">
+    <row r="426" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A426">
         <v>445</v>
       </c>
@@ -22318,7 +22345,7 @@
       <c r="AA426" s="1"/>
       <c r="AB426" s="1"/>
     </row>
-    <row r="427" spans="1:28">
+    <row r="427" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A427">
         <v>446</v>
       </c>
@@ -22364,7 +22391,7 @@
       <c r="AA427" s="1"/>
       <c r="AB427" s="1"/>
     </row>
-    <row r="428" spans="1:28">
+    <row r="428" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A428">
         <v>447</v>
       </c>
@@ -22410,7 +22437,7 @@
       <c r="AA428" s="1"/>
       <c r="AB428" s="1"/>
     </row>
-    <row r="429" spans="1:28">
+    <row r="429" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A429">
         <v>448</v>
       </c>
@@ -22456,7 +22483,7 @@
       <c r="AA429" s="1"/>
       <c r="AB429" s="1"/>
     </row>
-    <row r="430" spans="1:28">
+    <row r="430" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A430">
         <v>449</v>
       </c>
@@ -22502,7 +22529,7 @@
       <c r="AA430" s="1"/>
       <c r="AB430" s="1"/>
     </row>
-    <row r="431" spans="1:28">
+    <row r="431" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A431">
         <v>450</v>
       </c>
@@ -22548,7 +22575,7 @@
       <c r="AA431" s="1"/>
       <c r="AB431" s="1"/>
     </row>
-    <row r="432" spans="1:28">
+    <row r="432" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A432">
         <v>451</v>
       </c>
@@ -22594,7 +22621,7 @@
       <c r="AA432" s="1"/>
       <c r="AB432" s="1"/>
     </row>
-    <row r="433" spans="1:28">
+    <row r="433" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A433">
         <v>452</v>
       </c>
@@ -22640,7 +22667,7 @@
       <c r="AA433" s="1"/>
       <c r="AB433" s="1"/>
     </row>
-    <row r="434" spans="1:28">
+    <row r="434" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A434">
         <v>453</v>
       </c>
@@ -22686,7 +22713,7 @@
       <c r="AA434" s="1"/>
       <c r="AB434" s="1"/>
     </row>
-    <row r="435" spans="1:28">
+    <row r="435" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A435">
         <v>454</v>
       </c>
@@ -22732,7 +22759,7 @@
       <c r="AA435" s="1"/>
       <c r="AB435" s="1"/>
     </row>
-    <row r="436" spans="1:28">
+    <row r="436" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A436">
         <v>455</v>
       </c>
@@ -22778,7 +22805,7 @@
       <c r="AA436" s="1"/>
       <c r="AB436" s="1"/>
     </row>
-    <row r="437" spans="1:28">
+    <row r="437" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A437">
         <v>456</v>
       </c>
@@ -22824,7 +22851,7 @@
       <c r="AA437" s="1"/>
       <c r="AB437" s="1"/>
     </row>
-    <row r="438" spans="1:28">
+    <row r="438" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A438">
         <v>457</v>
       </c>
@@ -22870,7 +22897,7 @@
       <c r="AA438" s="1"/>
       <c r="AB438" s="1"/>
     </row>
-    <row r="439" spans="1:28">
+    <row r="439" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A439">
         <v>458</v>
       </c>
@@ -22916,7 +22943,7 @@
       <c r="AA439" s="1"/>
       <c r="AB439" s="1"/>
     </row>
-    <row r="440" spans="1:28">
+    <row r="440" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A440">
         <v>459</v>
       </c>
@@ -22962,7 +22989,7 @@
       <c r="AA440" s="1"/>
       <c r="AB440" s="1"/>
     </row>
-    <row r="441" spans="1:28">
+    <row r="441" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A441">
         <v>460</v>
       </c>
@@ -23008,7 +23035,7 @@
       <c r="AA441" s="1"/>
       <c r="AB441" s="1"/>
     </row>
-    <row r="442" spans="1:28">
+    <row r="442" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A442">
         <v>461</v>
       </c>
@@ -23054,7 +23081,7 @@
       <c r="AA442" s="1"/>
       <c r="AB442" s="1"/>
     </row>
-    <row r="443" spans="1:28">
+    <row r="443" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A443">
         <v>462</v>
       </c>
@@ -23100,7 +23127,7 @@
       <c r="AA443" s="1"/>
       <c r="AB443" s="1"/>
     </row>
-    <row r="444" spans="1:28">
+    <row r="444" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A444">
         <v>463</v>
       </c>
@@ -23146,7 +23173,7 @@
       <c r="AA444" s="1"/>
       <c r="AB444" s="1"/>
     </row>
-    <row r="445" spans="1:28">
+    <row r="445" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A445">
         <v>464</v>
       </c>
@@ -23192,7 +23219,7 @@
       <c r="AA445" s="1"/>
       <c r="AB445" s="1"/>
     </row>
-    <row r="446" spans="1:28">
+    <row r="446" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A446">
         <v>465</v>
       </c>
@@ -23238,7 +23265,7 @@
       <c r="AA446" s="1"/>
       <c r="AB446" s="1"/>
     </row>
-    <row r="447" spans="1:28">
+    <row r="447" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A447">
         <v>466</v>
       </c>
@@ -23284,7 +23311,7 @@
       <c r="AA447" s="1"/>
       <c r="AB447" s="1"/>
     </row>
-    <row r="448" spans="1:28">
+    <row r="448" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A448">
         <v>467</v>
       </c>
@@ -23330,7 +23357,7 @@
       <c r="AA448" s="1"/>
       <c r="AB448" s="1"/>
     </row>
-    <row r="449" spans="1:28">
+    <row r="449" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A449">
         <v>468</v>
       </c>
@@ -23376,7 +23403,7 @@
       <c r="AA449" s="1"/>
       <c r="AB449" s="1"/>
     </row>
-    <row r="450" spans="1:28">
+    <row r="450" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A450">
         <v>469</v>
       </c>
@@ -23422,7 +23449,7 @@
       <c r="AA450" s="1"/>
       <c r="AB450" s="1"/>
     </row>
-    <row r="451" spans="1:28">
+    <row r="451" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A451">
         <v>470</v>
       </c>
@@ -23468,7 +23495,7 @@
       <c r="AA451" s="1"/>
       <c r="AB451" s="1"/>
     </row>
-    <row r="452" spans="1:28">
+    <row r="452" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A452">
         <v>471</v>
       </c>
@@ -23514,7 +23541,7 @@
       <c r="AA452" s="1"/>
       <c r="AB452" s="1"/>
     </row>
-    <row r="453" spans="1:28">
+    <row r="453" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A453">
         <v>472</v>
       </c>
@@ -23560,7 +23587,7 @@
       <c r="AA453" s="1"/>
       <c r="AB453" s="1"/>
     </row>
-    <row r="454" spans="1:28">
+    <row r="454" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A454">
         <v>473</v>
       </c>
@@ -23606,7 +23633,7 @@
       <c r="AA454" s="1"/>
       <c r="AB454" s="1"/>
     </row>
-    <row r="455" spans="1:28">
+    <row r="455" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A455">
         <v>474</v>
       </c>
@@ -23652,7 +23679,7 @@
       <c r="AA455" s="1"/>
       <c r="AB455" s="1"/>
     </row>
-    <row r="456" spans="1:28">
+    <row r="456" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A456">
         <v>475</v>
       </c>
@@ -23698,7 +23725,7 @@
       <c r="AA456" s="1"/>
       <c r="AB456" s="1"/>
     </row>
-    <row r="457" spans="1:28">
+    <row r="457" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A457">
         <v>476</v>
       </c>
@@ -23744,7 +23771,7 @@
       <c r="AA457" s="1"/>
       <c r="AB457" s="1"/>
     </row>
-    <row r="458" spans="1:28">
+    <row r="458" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A458">
         <v>477</v>
       </c>
@@ -23790,7 +23817,7 @@
       <c r="AA458" s="1"/>
       <c r="AB458" s="1"/>
     </row>
-    <row r="459" spans="1:28">
+    <row r="459" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A459">
         <v>478</v>
       </c>
@@ -23836,7 +23863,7 @@
       <c r="AA459" s="1"/>
       <c r="AB459" s="1"/>
     </row>
-    <row r="460" spans="1:28">
+    <row r="460" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A460">
         <v>479</v>
       </c>
@@ -23882,7 +23909,7 @@
       <c r="AA460" s="1"/>
       <c r="AB460" s="1"/>
     </row>
-    <row r="461" spans="1:28">
+    <row r="461" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A461">
         <v>480</v>
       </c>
@@ -23928,7 +23955,7 @@
       <c r="AA461" s="1"/>
       <c r="AB461" s="1"/>
     </row>
-    <row r="462" spans="1:28">
+    <row r="462" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A462">
         <v>481</v>
       </c>
@@ -23974,7 +24001,7 @@
       <c r="AA462" s="1"/>
       <c r="AB462" s="1"/>
     </row>
-    <row r="463" spans="1:28">
+    <row r="463" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A463">
         <v>482</v>
       </c>
@@ -24020,7 +24047,7 @@
       <c r="AA463" s="1"/>
       <c r="AB463" s="1"/>
     </row>
-    <row r="464" spans="1:28">
+    <row r="464" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A464">
         <v>483</v>
       </c>
@@ -24066,7 +24093,7 @@
       <c r="AA464" s="1"/>
       <c r="AB464" s="1"/>
     </row>
-    <row r="465" spans="1:28">
+    <row r="465" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A465">
         <v>484</v>
       </c>
@@ -24112,7 +24139,7 @@
       <c r="AA465" s="1"/>
       <c r="AB465" s="1"/>
     </row>
-    <row r="466" spans="1:28">
+    <row r="466" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A466">
         <v>485</v>
       </c>
@@ -24158,7 +24185,7 @@
       <c r="AA466" s="1"/>
       <c r="AB466" s="1"/>
     </row>
-    <row r="467" spans="1:28">
+    <row r="467" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A467">
         <v>486</v>
       </c>
@@ -24204,7 +24231,7 @@
       <c r="AA467" s="1"/>
       <c r="AB467" s="1"/>
     </row>
-    <row r="468" spans="1:28">
+    <row r="468" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A468">
         <v>487</v>
       </c>
@@ -24250,7 +24277,7 @@
       <c r="AA468" s="1"/>
       <c r="AB468" s="1"/>
     </row>
-    <row r="469" spans="1:28">
+    <row r="469" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A469">
         <v>488</v>
       </c>
@@ -24296,7 +24323,7 @@
       <c r="AA469" s="1"/>
       <c r="AB469" s="1"/>
     </row>
-    <row r="470" spans="1:28">
+    <row r="470" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A470">
         <v>489</v>
       </c>
@@ -24342,7 +24369,7 @@
       <c r="AA470" s="1"/>
       <c r="AB470" s="1"/>
     </row>
-    <row r="471" spans="1:28">
+    <row r="471" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A471">
         <v>490</v>
       </c>
@@ -24388,7 +24415,7 @@
       <c r="AA471" s="1"/>
       <c r="AB471" s="1"/>
     </row>
-    <row r="472" spans="1:28">
+    <row r="472" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A472">
         <v>491</v>
       </c>
@@ -24434,7 +24461,7 @@
       <c r="AA472" s="1"/>
       <c r="AB472" s="1"/>
     </row>
-    <row r="473" spans="1:28">
+    <row r="473" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A473">
         <v>492</v>
       </c>
@@ -24480,7 +24507,7 @@
       <c r="AA473" s="1"/>
       <c r="AB473" s="1"/>
     </row>
-    <row r="474" spans="1:28">
+    <row r="474" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A474">
         <v>493</v>
       </c>
@@ -24526,7 +24553,7 @@
       <c r="AA474" s="1"/>
       <c r="AB474" s="1"/>
     </row>
-    <row r="475" spans="1:28">
+    <row r="475" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A475">
         <v>494</v>
       </c>
@@ -24572,7 +24599,7 @@
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
     </row>
-    <row r="476" spans="1:28">
+    <row r="476" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A476">
         <v>495</v>
       </c>
@@ -24618,7 +24645,7 @@
       <c r="AA476" s="1"/>
       <c r="AB476" s="1"/>
     </row>
-    <row r="477" spans="1:28">
+    <row r="477" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A477">
         <v>496</v>
       </c>
@@ -24664,7 +24691,7 @@
       <c r="AA477" s="1"/>
       <c r="AB477" s="1"/>
     </row>
-    <row r="478" spans="1:28">
+    <row r="478" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A478">
         <v>497</v>
       </c>
@@ -24710,7 +24737,7 @@
       <c r="AA478" s="1"/>
       <c r="AB478" s="1"/>
     </row>
-    <row r="479" spans="1:28">
+    <row r="479" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A479">
         <v>498</v>
       </c>
@@ -24756,7 +24783,7 @@
       <c r="AA479" s="1"/>
       <c r="AB479" s="1"/>
     </row>
-    <row r="480" spans="1:28">
+    <row r="480" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A480">
         <v>499</v>
       </c>
@@ -24802,7 +24829,7 @@
       <c r="AA480" s="1"/>
       <c r="AB480" s="1"/>
     </row>
-    <row r="481" spans="1:28">
+    <row r="481" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A481">
         <v>500</v>
       </c>
@@ -24848,7 +24875,7 @@
       <c r="AA481" s="1"/>
       <c r="AB481" s="1"/>
     </row>
-    <row r="482" spans="1:28">
+    <row r="482" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A482">
         <v>501</v>
       </c>
@@ -24894,7 +24921,7 @@
       <c r="AA482" s="1"/>
       <c r="AB482" s="1"/>
     </row>
-    <row r="483" spans="1:28">
+    <row r="483" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A483">
         <v>502</v>
       </c>
@@ -24940,7 +24967,7 @@
       <c r="AA483" s="1"/>
       <c r="AB483" s="1"/>
     </row>
-    <row r="484" spans="1:28">
+    <row r="484" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A484">
         <v>503</v>
       </c>
@@ -24986,7 +25013,7 @@
       <c r="AA484" s="1"/>
       <c r="AB484" s="1"/>
     </row>
-    <row r="485" spans="1:28">
+    <row r="485" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A485">
         <v>504</v>
       </c>
@@ -25032,7 +25059,7 @@
       <c r="AA485" s="1"/>
       <c r="AB485" s="1"/>
     </row>
-    <row r="486" spans="1:28">
+    <row r="486" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A486">
         <v>505</v>
       </c>
@@ -25078,7 +25105,7 @@
       <c r="AA486" s="1"/>
       <c r="AB486" s="1"/>
     </row>
-    <row r="487" spans="1:28">
+    <row r="487" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A487">
         <v>506</v>
       </c>
@@ -25124,7 +25151,7 @@
       <c r="AA487" s="1"/>
       <c r="AB487" s="1"/>
     </row>
-    <row r="488" spans="1:28">
+    <row r="488" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A488">
         <v>507</v>
       </c>
@@ -25170,7 +25197,7 @@
       <c r="AA488" s="1"/>
       <c r="AB488" s="1"/>
     </row>
-    <row r="489" spans="1:28">
+    <row r="489" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A489">
         <v>508</v>
       </c>
@@ -25216,7 +25243,7 @@
       <c r="AA489" s="1"/>
       <c r="AB489" s="1"/>
     </row>
-    <row r="490" spans="1:28">
+    <row r="490" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A490">
         <v>509</v>
       </c>
@@ -25262,7 +25289,7 @@
       <c r="AA490" s="1"/>
       <c r="AB490" s="1"/>
     </row>
-    <row r="491" spans="1:28">
+    <row r="491" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A491">
         <v>510</v>
       </c>
@@ -25308,7 +25335,7 @@
       <c r="AA491" s="1"/>
       <c r="AB491" s="1"/>
     </row>
-    <row r="492" spans="1:28">
+    <row r="492" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A492">
         <v>511</v>
       </c>
@@ -25354,7 +25381,7 @@
       <c r="AA492" s="1"/>
       <c r="AB492" s="1"/>
     </row>
-    <row r="493" spans="1:28">
+    <row r="493" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A493">
         <v>512</v>
       </c>
@@ -25400,7 +25427,7 @@
       <c r="AA493" s="1"/>
       <c r="AB493" s="1"/>
     </row>
-    <row r="494" spans="1:28">
+    <row r="494" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A494">
         <v>513</v>
       </c>
@@ -25446,7 +25473,7 @@
       <c r="AA494" s="1"/>
       <c r="AB494" s="1"/>
     </row>
-    <row r="495" spans="1:28">
+    <row r="495" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A495">
         <v>514</v>
       </c>
@@ -25494,7 +25521,7 @@
       <c r="AA495" s="1"/>
       <c r="AB495" s="1"/>
     </row>
-    <row r="496" spans="1:28">
+    <row r="496" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A496">
         <v>515</v>
       </c>
@@ -25540,7 +25567,7 @@
       <c r="AA496" s="1"/>
       <c r="AB496" s="1"/>
     </row>
-    <row r="497" spans="1:28">
+    <row r="497" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A497">
         <v>516</v>
       </c>
@@ -25586,7 +25613,7 @@
       <c r="AA497" s="1"/>
       <c r="AB497" s="1"/>
     </row>
-    <row r="498" spans="1:28">
+    <row r="498" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A498">
         <v>517</v>
       </c>
@@ -25632,7 +25659,7 @@
       <c r="AA498" s="1"/>
       <c r="AB498" s="1"/>
     </row>
-    <row r="499" spans="1:28">
+    <row r="499" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A499">
         <v>518</v>
       </c>
@@ -25678,7 +25705,7 @@
       <c r="AA499" s="1"/>
       <c r="AB499" s="1"/>
     </row>
-    <row r="500" spans="1:28">
+    <row r="500" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A500">
         <v>519</v>
       </c>
@@ -25724,7 +25751,7 @@
       <c r="AA500" s="1"/>
       <c r="AB500" s="1"/>
     </row>
-    <row r="501" spans="1:28">
+    <row r="501" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A501">
         <v>520</v>
       </c>
@@ -25770,7 +25797,7 @@
       <c r="AA501" s="1"/>
       <c r="AB501" s="1"/>
     </row>
-    <row r="502" spans="1:28">
+    <row r="502" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A502">
         <v>521</v>
       </c>
@@ -25816,7 +25843,7 @@
       <c r="AA502" s="1"/>
       <c r="AB502" s="1"/>
     </row>
-    <row r="503" spans="1:28">
+    <row r="503" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A503">
         <v>522</v>
       </c>
@@ -25862,7 +25889,7 @@
       <c r="AA503" s="1"/>
       <c r="AB503" s="1"/>
     </row>
-    <row r="504" spans="1:28">
+    <row r="504" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A504">
         <v>523</v>
       </c>
@@ -25908,7 +25935,7 @@
       <c r="AA504" s="1"/>
       <c r="AB504" s="1"/>
     </row>
-    <row r="505" spans="1:28">
+    <row r="505" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A505">
         <v>524</v>
       </c>
@@ -25954,7 +25981,7 @@
       <c r="AA505" s="1"/>
       <c r="AB505" s="1"/>
     </row>
-    <row r="506" spans="1:28">
+    <row r="506" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A506">
         <v>525</v>
       </c>
@@ -26000,7 +26027,7 @@
       <c r="AA506" s="1"/>
       <c r="AB506" s="1"/>
     </row>
-    <row r="507" spans="1:28">
+    <row r="507" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A507">
         <v>526</v>
       </c>
@@ -26048,7 +26075,7 @@
       <c r="AA507" s="1"/>
       <c r="AB507" s="1"/>
     </row>
-    <row r="508" spans="1:28">
+    <row r="508" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A508">
         <v>527</v>
       </c>
@@ -26094,7 +26121,7 @@
       <c r="AA508" s="1"/>
       <c r="AB508" s="1"/>
     </row>
-    <row r="509" spans="1:28">
+    <row r="509" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A509">
         <v>528</v>
       </c>
@@ -26140,7 +26167,7 @@
       <c r="AA509" s="1"/>
       <c r="AB509" s="1"/>
     </row>
-    <row r="510" spans="1:28">
+    <row r="510" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A510">
         <v>529</v>
       </c>
@@ -26186,7 +26213,7 @@
       <c r="AA510" s="1"/>
       <c r="AB510" s="1"/>
     </row>
-    <row r="511" spans="1:28">
+    <row r="511" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A511">
         <v>530</v>
       </c>
@@ -26232,7 +26259,7 @@
       <c r="AA511" s="1"/>
       <c r="AB511" s="1"/>
     </row>
-    <row r="512" spans="1:28">
+    <row r="512" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A512">
         <v>531</v>
       </c>
@@ -26278,7 +26305,7 @@
       <c r="AA512" s="1"/>
       <c r="AB512" s="1"/>
     </row>
-    <row r="513" spans="1:28">
+    <row r="513" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A513">
         <v>532</v>
       </c>
@@ -26324,7 +26351,7 @@
       <c r="AA513" s="1"/>
       <c r="AB513" s="1"/>
     </row>
-    <row r="514" spans="1:28">
+    <row r="514" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A514">
         <v>533</v>
       </c>
@@ -26370,7 +26397,7 @@
       <c r="AA514" s="1"/>
       <c r="AB514" s="1"/>
     </row>
-    <row r="515" spans="1:28">
+    <row r="515" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A515">
         <v>534</v>
       </c>
@@ -26416,7 +26443,7 @@
       <c r="AA515" s="1"/>
       <c r="AB515" s="1"/>
     </row>
-    <row r="516" spans="1:28">
+    <row r="516" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A516">
         <v>535</v>
       </c>
@@ -26462,7 +26489,7 @@
       <c r="AA516" s="1"/>
       <c r="AB516" s="1"/>
     </row>
-    <row r="517" spans="1:28">
+    <row r="517" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A517">
         <v>536</v>
       </c>
@@ -26508,7 +26535,7 @@
       <c r="AA517" s="1"/>
       <c r="AB517" s="1"/>
     </row>
-    <row r="518" spans="1:28">
+    <row r="518" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A518">
         <v>537</v>
       </c>
@@ -26554,7 +26581,7 @@
       <c r="AA518" s="1"/>
       <c r="AB518" s="1"/>
     </row>
-    <row r="519" spans="1:28">
+    <row r="519" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A519">
         <v>538</v>
       </c>
@@ -26600,7 +26627,7 @@
       <c r="AA519" s="1"/>
       <c r="AB519" s="1"/>
     </row>
-    <row r="520" spans="1:28">
+    <row r="520" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A520">
         <v>539</v>
       </c>
@@ -26646,7 +26673,7 @@
       <c r="AA520" s="1"/>
       <c r="AB520" s="1"/>
     </row>
-    <row r="521" spans="1:28">
+    <row r="521" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A521">
         <v>540</v>
       </c>
@@ -26692,7 +26719,7 @@
       <c r="AA521" s="1"/>
       <c r="AB521" s="1"/>
     </row>
-    <row r="522" spans="1:28">
+    <row r="522" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A522">
         <v>541</v>
       </c>
@@ -26738,7 +26765,7 @@
       <c r="AA522" s="1"/>
       <c r="AB522" s="1"/>
     </row>
-    <row r="523" spans="1:28">
+    <row r="523" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A523">
         <v>542</v>
       </c>
@@ -26784,7 +26811,7 @@
       <c r="AA523" s="1"/>
       <c r="AB523" s="1"/>
     </row>
-    <row r="524" spans="1:28">
+    <row r="524" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A524">
         <v>543</v>
       </c>
@@ -26830,7 +26857,7 @@
       <c r="AA524" s="1"/>
       <c r="AB524" s="1"/>
     </row>
-    <row r="525" spans="1:28">
+    <row r="525" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A525">
         <v>544</v>
       </c>
@@ -26876,7 +26903,7 @@
       <c r="AA525" s="1"/>
       <c r="AB525" s="1"/>
     </row>
-    <row r="526" spans="1:28">
+    <row r="526" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A526">
         <v>545</v>
       </c>
@@ -26924,7 +26951,7 @@
       <c r="AA526" s="1"/>
       <c r="AB526" s="1"/>
     </row>
-    <row r="527" spans="1:28">
+    <row r="527" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A527">
         <v>546</v>
       </c>
@@ -26970,7 +26997,7 @@
       <c r="AA527" s="1"/>
       <c r="AB527" s="1"/>
     </row>
-    <row r="528" spans="1:28">
+    <row r="528" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A528">
         <v>547</v>
       </c>
@@ -27016,7 +27043,7 @@
       <c r="AA528" s="1"/>
       <c r="AB528" s="1"/>
     </row>
-    <row r="529" spans="1:28">
+    <row r="529" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A529">
         <v>548</v>
       </c>
@@ -27062,7 +27089,7 @@
       <c r="AA529" s="1"/>
       <c r="AB529" s="1"/>
     </row>
-    <row r="530" spans="1:28">
+    <row r="530" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A530">
         <v>549</v>
       </c>
@@ -27108,7 +27135,7 @@
       <c r="AA530" s="1"/>
       <c r="AB530" s="1"/>
     </row>
-    <row r="531" spans="1:28">
+    <row r="531" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A531">
         <v>550</v>
       </c>
@@ -27154,7 +27181,7 @@
       <c r="AA531" s="1"/>
       <c r="AB531" s="1"/>
     </row>
-    <row r="532" spans="1:28">
+    <row r="532" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A532">
         <v>551</v>
       </c>
@@ -27202,7 +27229,7 @@
       <c r="AA532" s="1"/>
       <c r="AB532" s="1"/>
     </row>
-    <row r="533" spans="1:28">
+    <row r="533" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A533">
         <v>552</v>
       </c>
@@ -27248,7 +27275,7 @@
       <c r="AA533" s="1"/>
       <c r="AB533" s="1"/>
     </row>
-    <row r="534" spans="1:28">
+    <row r="534" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A534">
         <v>553</v>
       </c>
@@ -27294,7 +27321,7 @@
       <c r="AA534" s="1"/>
       <c r="AB534" s="1"/>
     </row>
-    <row r="535" spans="1:28">
+    <row r="535" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A535">
         <v>554</v>
       </c>
@@ -27340,7 +27367,7 @@
       <c r="AA535" s="1"/>
       <c r="AB535" s="1"/>
     </row>
-    <row r="536" spans="1:28">
+    <row r="536" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A536">
         <v>555</v>
       </c>
@@ -27386,7 +27413,7 @@
       <c r="AA536" s="1"/>
       <c r="AB536" s="1"/>
     </row>
-    <row r="537" spans="1:28">
+    <row r="537" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A537">
         <v>556</v>
       </c>
@@ -27434,7 +27461,7 @@
       <c r="AA537" s="1"/>
       <c r="AB537" s="1"/>
     </row>
-    <row r="538" spans="1:28">
+    <row r="538" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A538">
         <v>557</v>
       </c>
@@ -27480,7 +27507,7 @@
       <c r="AA538" s="1"/>
       <c r="AB538" s="1"/>
     </row>
-    <row r="539" spans="1:28">
+    <row r="539" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A539">
         <v>558</v>
       </c>
@@ -27526,7 +27553,7 @@
       <c r="AA539" s="1"/>
       <c r="AB539" s="1"/>
     </row>
-    <row r="540" spans="1:28">
+    <row r="540" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A540">
         <v>559</v>
       </c>
@@ -27572,7 +27599,7 @@
       <c r="AA540" s="1"/>
       <c r="AB540" s="1"/>
     </row>
-    <row r="541" spans="1:28">
+    <row r="541" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A541">
         <v>560</v>
       </c>
@@ -27618,7 +27645,7 @@
       <c r="AA541" s="1"/>
       <c r="AB541" s="1"/>
     </row>
-    <row r="542" spans="1:28">
+    <row r="542" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A542">
         <v>561</v>
       </c>
@@ -27664,7 +27691,7 @@
       <c r="AA542" s="1"/>
       <c r="AB542" s="1"/>
     </row>
-    <row r="543" spans="1:28">
+    <row r="543" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A543">
         <v>562</v>
       </c>
@@ -27710,7 +27737,7 @@
       <c r="AA543" s="1"/>
       <c r="AB543" s="1"/>
     </row>
-    <row r="544" spans="1:28">
+    <row r="544" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A544">
         <v>563</v>
       </c>
@@ -27756,7 +27783,7 @@
       <c r="AA544" s="1"/>
       <c r="AB544" s="1"/>
     </row>
-    <row r="545" spans="1:28">
+    <row r="545" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A545">
         <v>564</v>
       </c>
@@ -27802,7 +27829,7 @@
       <c r="AA545" s="1"/>
       <c r="AB545" s="1"/>
     </row>
-    <row r="546" spans="1:28">
+    <row r="546" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A546">
         <v>565</v>
       </c>
@@ -27848,7 +27875,7 @@
       <c r="AA546" s="1"/>
       <c r="AB546" s="1"/>
     </row>
-    <row r="547" spans="1:28">
+    <row r="547" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A547">
         <v>566</v>
       </c>
@@ -27894,7 +27921,7 @@
       <c r="AA547" s="1"/>
       <c r="AB547" s="1"/>
     </row>
-    <row r="548" spans="1:28">
+    <row r="548" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A548">
         <v>567</v>
       </c>
@@ -27940,7 +27967,7 @@
       <c r="AA548" s="1"/>
       <c r="AB548" s="1"/>
     </row>
-    <row r="549" spans="1:28">
+    <row r="549" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A549">
         <v>568</v>
       </c>
@@ -27986,7 +28013,7 @@
       <c r="AA549" s="1"/>
       <c r="AB549" s="1"/>
     </row>
-    <row r="550" spans="1:28">
+    <row r="550" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A550">
         <v>569</v>
       </c>
@@ -28032,7 +28059,7 @@
       <c r="AA550" s="1"/>
       <c r="AB550" s="1"/>
     </row>
-    <row r="551" spans="1:28">
+    <row r="551" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A551">
         <v>570</v>
       </c>
@@ -28078,7 +28105,7 @@
       <c r="AA551" s="1"/>
       <c r="AB551" s="1"/>
     </row>
-    <row r="552" spans="1:28">
+    <row r="552" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A552">
         <v>571</v>
       </c>
@@ -28124,7 +28151,7 @@
       <c r="AA552" s="1"/>
       <c r="AB552" s="1"/>
     </row>
-    <row r="553" spans="1:28">
+    <row r="553" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A553">
         <v>572</v>
       </c>
@@ -28170,7 +28197,7 @@
       <c r="AA553" s="1"/>
       <c r="AB553" s="1"/>
     </row>
-    <row r="554" spans="1:28">
+    <row r="554" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A554">
         <v>573</v>
       </c>
@@ -28216,7 +28243,7 @@
       <c r="AA554" s="1"/>
       <c r="AB554" s="1"/>
     </row>
-    <row r="555" spans="1:28">
+    <row r="555" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A555">
         <v>574</v>
       </c>
@@ -28262,7 +28289,7 @@
       <c r="AA555" s="1"/>
       <c r="AB555" s="1"/>
     </row>
-    <row r="556" spans="1:28">
+    <row r="556" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A556">
         <v>575</v>
       </c>
@@ -28308,7 +28335,7 @@
       <c r="AA556" s="1"/>
       <c r="AB556" s="1"/>
     </row>
-    <row r="557" spans="1:28">
+    <row r="557" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A557">
         <v>576</v>
       </c>
@@ -28354,7 +28381,7 @@
       <c r="AA557" s="1"/>
       <c r="AB557" s="1"/>
     </row>
-    <row r="558" spans="1:28">
+    <row r="558" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A558">
         <v>577</v>
       </c>
@@ -28400,7 +28427,7 @@
       <c r="AA558" s="1"/>
       <c r="AB558" s="1"/>
     </row>
-    <row r="559" spans="1:28">
+    <row r="559" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A559">
         <v>578</v>
       </c>
@@ -28448,7 +28475,7 @@
       <c r="AA559" s="1"/>
       <c r="AB559" s="1"/>
     </row>
-    <row r="560" spans="1:28">
+    <row r="560" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A560">
         <v>579</v>
       </c>
@@ -28494,7 +28521,7 @@
       <c r="AA560" s="1"/>
       <c r="AB560" s="1"/>
     </row>
-    <row r="561" spans="1:28">
+    <row r="561" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A561">
         <v>580</v>
       </c>
@@ -28540,7 +28567,7 @@
       <c r="AA561" s="1"/>
       <c r="AB561" s="1"/>
     </row>
-    <row r="562" spans="1:28">
+    <row r="562" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A562">
         <v>581</v>
       </c>
@@ -28586,7 +28613,7 @@
       <c r="AA562" s="1"/>
       <c r="AB562" s="1"/>
     </row>
-    <row r="563" spans="1:28">
+    <row r="563" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A563">
         <v>582</v>
       </c>
@@ -28632,7 +28659,7 @@
       <c r="AA563" s="1"/>
       <c r="AB563" s="1"/>
     </row>
-    <row r="564" spans="1:28">
+    <row r="564" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A564">
         <v>583</v>
       </c>
@@ -28678,7 +28705,7 @@
       <c r="AA564" s="1"/>
       <c r="AB564" s="1"/>
     </row>
-    <row r="565" spans="1:28">
+    <row r="565" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A565">
         <v>584</v>
       </c>
@@ -28728,7 +28755,7 @@
       <c r="AA565" s="1"/>
       <c r="AB565" s="1"/>
     </row>
-    <row r="566" spans="1:28">
+    <row r="566" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A566">
         <v>585</v>
       </c>
@@ -28778,7 +28805,7 @@
       <c r="AA566" s="1"/>
       <c r="AB566" s="1"/>
     </row>
-    <row r="567" spans="1:28">
+    <row r="567" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A567">
         <v>586</v>
       </c>
@@ -28824,7 +28851,7 @@
       <c r="AA567" s="1"/>
       <c r="AB567" s="1"/>
     </row>
-    <row r="568" spans="1:28">
+    <row r="568" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A568">
         <v>587</v>
       </c>
@@ -28870,7 +28897,7 @@
       <c r="AA568" s="1"/>
       <c r="AB568" s="1"/>
     </row>
-    <row r="569" spans="1:28">
+    <row r="569" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A569">
         <v>588</v>
       </c>
@@ -28920,7 +28947,7 @@
       <c r="AA569" s="1"/>
       <c r="AB569" s="1"/>
     </row>
-    <row r="570" spans="1:28">
+    <row r="570" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A570">
         <v>589</v>
       </c>
@@ -28970,7 +28997,7 @@
       <c r="AA570" s="1"/>
       <c r="AB570" s="1"/>
     </row>
-    <row r="571" spans="1:28">
+    <row r="571" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A571">
         <v>590</v>
       </c>
@@ -29020,7 +29047,7 @@
       <c r="AA571" s="1"/>
       <c r="AB571" s="1"/>
     </row>
-    <row r="572" spans="1:28">
+    <row r="572" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A572">
         <v>591</v>
       </c>
@@ -29070,7 +29097,7 @@
       <c r="AA572" s="1"/>
       <c r="AB572" s="1"/>
     </row>
-    <row r="573" spans="1:28">
+    <row r="573" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A573">
         <v>592</v>
       </c>
@@ -29116,7 +29143,7 @@
       <c r="AA573" s="1"/>
       <c r="AB573" s="1"/>
     </row>
-    <row r="574" spans="1:28">
+    <row r="574" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A574">
         <v>593</v>
       </c>
@@ -29162,7 +29189,7 @@
       <c r="AA574" s="1"/>
       <c r="AB574" s="1"/>
     </row>
-    <row r="575" spans="1:28">
+    <row r="575" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A575">
         <v>594</v>
       </c>
@@ -29212,7 +29239,7 @@
       <c r="AA575" s="1"/>
       <c r="AB575" s="1"/>
     </row>
-    <row r="576" spans="1:28">
+    <row r="576" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A576">
         <v>595</v>
       </c>
@@ -29258,7 +29285,7 @@
       <c r="AA576" s="1"/>
       <c r="AB576" s="1"/>
     </row>
-    <row r="577" spans="1:28">
+    <row r="577" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A577">
         <v>596</v>
       </c>
@@ -29308,7 +29335,7 @@
       <c r="AA577" s="1"/>
       <c r="AB577" s="1"/>
     </row>
-    <row r="578" spans="1:28">
+    <row r="578" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A578">
         <v>597</v>
       </c>
@@ -29354,7 +29381,7 @@
       <c r="AA578" s="1"/>
       <c r="AB578" s="1"/>
     </row>
-    <row r="579" spans="1:28">
+    <row r="579" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A579">
         <v>598</v>
       </c>
@@ -29400,7 +29427,7 @@
       <c r="AA579" s="1"/>
       <c r="AB579" s="1"/>
     </row>
-    <row r="580" spans="1:28">
+    <row r="580" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A580">
         <v>599</v>
       </c>
@@ -29450,7 +29477,7 @@
       <c r="AA580" s="1"/>
       <c r="AB580" s="1"/>
     </row>
-    <row r="581" spans="1:28">
+    <row r="581" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A581">
         <v>600</v>
       </c>
@@ -29500,7 +29527,7 @@
       <c r="AA581" s="1"/>
       <c r="AB581" s="1"/>
     </row>
-    <row r="582" spans="1:28">
+    <row r="582" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A582">
         <v>601</v>
       </c>
@@ -29550,7 +29577,7 @@
       <c r="AA582" s="1"/>
       <c r="AB582" s="1"/>
     </row>
-    <row r="583" spans="1:28">
+    <row r="583" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A583">
         <v>602</v>
       </c>
@@ -29600,7 +29627,7 @@
       <c r="AA583" s="1"/>
       <c r="AB583" s="1"/>
     </row>
-    <row r="584" spans="1:28">
+    <row r="584" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A584">
         <v>603</v>
       </c>
@@ -29650,7 +29677,7 @@
       <c r="AA584" s="1"/>
       <c r="AB584" s="1"/>
     </row>
-    <row r="585" spans="1:28">
+    <row r="585" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A585">
         <v>604</v>
       </c>
@@ -29700,7 +29727,7 @@
       <c r="AA585" s="1"/>
       <c r="AB585" s="1"/>
     </row>
-    <row r="586" spans="1:28">
+    <row r="586" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A586">
         <v>605</v>
       </c>
@@ -29750,7 +29777,7 @@
       <c r="AA586" s="1"/>
       <c r="AB586" s="1"/>
     </row>
-    <row r="587" spans="1:28">
+    <row r="587" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A587">
         <v>606</v>
       </c>
@@ -29800,7 +29827,7 @@
       <c r="AA587" s="1"/>
       <c r="AB587" s="1"/>
     </row>
-    <row r="588" spans="1:28">
+    <row r="588" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A588">
         <v>607</v>
       </c>
@@ -29850,7 +29877,7 @@
       <c r="AA588" s="1"/>
       <c r="AB588" s="1"/>
     </row>
-    <row r="589" spans="1:28">
+    <row r="589" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A589">
         <v>608</v>
       </c>
@@ -29900,7 +29927,7 @@
       <c r="AA589" s="1"/>
       <c r="AB589" s="1"/>
     </row>
-    <row r="590" spans="1:28">
+    <row r="590" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A590">
         <v>609</v>
       </c>
@@ -29950,7 +29977,7 @@
       <c r="AA590" s="1"/>
       <c r="AB590" s="1"/>
     </row>
-    <row r="591" spans="1:28">
+    <row r="591" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A591">
         <v>610</v>
       </c>
@@ -30000,7 +30027,7 @@
       <c r="AA591" s="1"/>
       <c r="AB591" s="1"/>
     </row>
-    <row r="592" spans="1:28">
+    <row r="592" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A592">
         <v>611</v>
       </c>
@@ -30050,7 +30077,7 @@
       <c r="AA592" s="1"/>
       <c r="AB592" s="1"/>
     </row>
-    <row r="593" spans="1:28">
+    <row r="593" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A593">
         <v>612</v>
       </c>
@@ -30100,7 +30127,7 @@
       <c r="AA593" s="1"/>
       <c r="AB593" s="1"/>
     </row>
-    <row r="594" spans="1:28">
+    <row r="594" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A594">
         <v>613</v>
       </c>
@@ -30150,7 +30177,7 @@
       <c r="AA594" s="1"/>
       <c r="AB594" s="1"/>
     </row>
-    <row r="595" spans="1:28">
+    <row r="595" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A595">
         <v>614</v>
       </c>
@@ -30200,7 +30227,7 @@
       <c r="AA595" s="1"/>
       <c r="AB595" s="1"/>
     </row>
-    <row r="596" spans="1:28">
+    <row r="596" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A596">
         <v>615</v>
       </c>
@@ -30250,7 +30277,7 @@
       <c r="AA596" s="1"/>
       <c r="AB596" s="1"/>
     </row>
-    <row r="597" spans="1:28">
+    <row r="597" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A597">
         <v>616</v>
       </c>
@@ -30300,7 +30327,7 @@
       <c r="AA597" s="1"/>
       <c r="AB597" s="1"/>
     </row>
-    <row r="598" spans="1:28">
+    <row r="598" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A598">
         <v>617</v>
       </c>
@@ -30350,7 +30377,7 @@
       <c r="AA598" s="1"/>
       <c r="AB598" s="1"/>
     </row>
-    <row r="599" spans="1:28">
+    <row r="599" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A599">
         <v>618</v>
       </c>
@@ -30400,7 +30427,7 @@
       <c r="AA599" s="1"/>
       <c r="AB599" s="1"/>
     </row>
-    <row r="600" spans="1:28">
+    <row r="600" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A600">
         <v>619</v>
       </c>
@@ -30450,7 +30477,7 @@
       <c r="AA600" s="1"/>
       <c r="AB600" s="1"/>
     </row>
-    <row r="601" spans="1:28">
+    <row r="601" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A601">
         <v>620</v>
       </c>
@@ -30500,7 +30527,7 @@
       <c r="AA601" s="1"/>
       <c r="AB601" s="1"/>
     </row>
-    <row r="602" spans="1:28">
+    <row r="602" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A602">
         <v>621</v>
       </c>
@@ -30550,7 +30577,7 @@
       <c r="AA602" s="1"/>
       <c r="AB602" s="1"/>
     </row>
-    <row r="603" spans="1:28">
+    <row r="603" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A603">
         <v>622</v>
       </c>
@@ -30600,7 +30627,7 @@
       <c r="AA603" s="1"/>
       <c r="AB603" s="1"/>
     </row>
-    <row r="604" spans="1:28">
+    <row r="604" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A604">
         <v>623</v>
       </c>
@@ -30648,7 +30675,7 @@
       <c r="AA604" s="1"/>
       <c r="AB604" s="1"/>
     </row>
-    <row r="605" spans="1:28">
+    <row r="605" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A605">
         <v>624</v>
       </c>
@@ -30698,7 +30725,7 @@
       <c r="AA605" s="1"/>
       <c r="AB605" s="1"/>
     </row>
-    <row r="606" spans="1:28">
+    <row r="606" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A606">
         <v>625</v>
       </c>
@@ -30748,7 +30775,7 @@
       <c r="AA606" s="1"/>
       <c r="AB606" s="1"/>
     </row>
-    <row r="607" spans="1:28">
+    <row r="607" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A607">
         <v>626</v>
       </c>
@@ -30798,7 +30825,7 @@
       <c r="AA607" s="1"/>
       <c r="AB607" s="1"/>
     </row>
-    <row r="608" spans="1:28">
+    <row r="608" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A608">
         <v>627</v>
       </c>
@@ -30848,7 +30875,7 @@
       <c r="AA608" s="1"/>
       <c r="AB608" s="1"/>
     </row>
-    <row r="609" spans="1:28">
+    <row r="609" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A609">
         <v>628</v>
       </c>
@@ -30898,7 +30925,7 @@
       <c r="AA609" s="1"/>
       <c r="AB609" s="1"/>
     </row>
-    <row r="610" spans="1:28">
+    <row r="610" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A610">
         <v>629</v>
       </c>
@@ -30948,7 +30975,7 @@
       <c r="AA610" s="1"/>
       <c r="AB610" s="1"/>
     </row>
-    <row r="611" spans="1:28">
+    <row r="611" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A611">
         <v>630</v>
       </c>
@@ -30994,7 +31021,7 @@
       <c r="AA611" s="1"/>
       <c r="AB611" s="1"/>
     </row>
-    <row r="612" spans="1:28">
+    <row r="612" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A612">
         <v>631</v>
       </c>
@@ -31044,7 +31071,7 @@
       <c r="AA612" s="1"/>
       <c r="AB612" s="1"/>
     </row>
-    <row r="613" spans="1:28">
+    <row r="613" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A613">
         <v>632</v>
       </c>
@@ -31092,7 +31119,7 @@
       <c r="AA613" s="1"/>
       <c r="AB613" s="1"/>
     </row>
-    <row r="614" spans="1:28">
+    <row r="614" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A614">
         <v>633</v>
       </c>
@@ -31138,7 +31165,7 @@
       <c r="AA614" s="1"/>
       <c r="AB614" s="1"/>
     </row>
-    <row r="615" spans="1:28">
+    <row r="615" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A615">
         <v>634</v>
       </c>
@@ -31188,7 +31215,7 @@
       <c r="AA615" s="1"/>
       <c r="AB615" s="1"/>
     </row>
-    <row r="616" spans="1:28">
+    <row r="616" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A616">
         <v>635</v>
       </c>
@@ -31238,7 +31265,7 @@
       <c r="AA616" s="1"/>
       <c r="AB616" s="1"/>
     </row>
-    <row r="617" spans="1:28">
+    <row r="617" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A617">
         <v>636</v>
       </c>
@@ -31288,7 +31315,7 @@
       <c r="AA617" s="1"/>
       <c r="AB617" s="1"/>
     </row>
-    <row r="618" spans="1:28">
+    <row r="618" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A618">
         <v>637</v>
       </c>
@@ -31338,7 +31365,7 @@
       <c r="AA618" s="1"/>
       <c r="AB618" s="1"/>
     </row>
-    <row r="619" spans="1:28">
+    <row r="619" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A619">
         <v>638</v>
       </c>
@@ -31388,7 +31415,7 @@
       <c r="AA619" s="1"/>
       <c r="AB619" s="1"/>
     </row>
-    <row r="620" spans="1:28">
+    <row r="620" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A620">
         <v>639</v>
       </c>
@@ -31438,7 +31465,7 @@
       <c r="AA620" s="1"/>
       <c r="AB620" s="1"/>
     </row>
-    <row r="621" spans="1:28">
+    <row r="621" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A621">
         <v>640</v>
       </c>
@@ -31488,7 +31515,7 @@
       <c r="AA621" s="1"/>
       <c r="AB621" s="1"/>
     </row>
-    <row r="622" spans="1:28">
+    <row r="622" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A622">
         <v>641</v>
       </c>
@@ -31538,7 +31565,7 @@
       <c r="AA622" s="1"/>
       <c r="AB622" s="1"/>
     </row>
-    <row r="623" spans="1:28">
+    <row r="623" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A623">
         <v>642</v>
       </c>
@@ -31588,7 +31615,7 @@
       <c r="AA623" s="1"/>
       <c r="AB623" s="1"/>
     </row>
-    <row r="624" spans="1:28">
+    <row r="624" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A624">
         <v>643</v>
       </c>
@@ -31634,7 +31661,7 @@
       <c r="AA624" s="1"/>
       <c r="AB624" s="1"/>
     </row>
-    <row r="625" spans="1:28">
+    <row r="625" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A625">
         <v>644</v>
       </c>
@@ -31684,7 +31711,7 @@
       <c r="AA625" s="1"/>
       <c r="AB625" s="1"/>
     </row>
-    <row r="626" spans="1:28">
+    <row r="626" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A626">
         <v>645</v>
       </c>
@@ -31734,7 +31761,7 @@
       <c r="AA626" s="1"/>
       <c r="AB626" s="1"/>
     </row>
-    <row r="627" spans="1:28">
+    <row r="627" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A627">
         <v>646</v>
       </c>
@@ -31784,7 +31811,7 @@
       <c r="AA627" s="1"/>
       <c r="AB627" s="1"/>
     </row>
-    <row r="628" spans="1:28">
+    <row r="628" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A628">
         <v>647</v>
       </c>
@@ -31834,7 +31861,7 @@
       <c r="AA628" s="1"/>
       <c r="AB628" s="1"/>
     </row>
-    <row r="629" spans="1:28">
+    <row r="629" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A629">
         <v>648</v>
       </c>
@@ -31884,7 +31911,7 @@
       <c r="AA629" s="1"/>
       <c r="AB629" s="1"/>
     </row>
-    <row r="630" spans="1:28">
+    <row r="630" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A630">
         <v>649</v>
       </c>
@@ -31934,7 +31961,7 @@
       <c r="AA630" s="1"/>
       <c r="AB630" s="1"/>
     </row>
-    <row r="631" spans="1:28">
+    <row r="631" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A631">
         <v>650</v>
       </c>
@@ -31984,7 +32011,7 @@
       <c r="AA631" s="1"/>
       <c r="AB631" s="1"/>
     </row>
-    <row r="632" spans="1:28">
+    <row r="632" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A632">
         <v>651</v>
       </c>
@@ -32030,7 +32057,7 @@
       <c r="AA632" s="1"/>
       <c r="AB632" s="1"/>
     </row>
-    <row r="633" spans="1:28">
+    <row r="633" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A633">
         <v>652</v>
       </c>
@@ -32080,7 +32107,7 @@
       <c r="AA633" s="1"/>
       <c r="AB633" s="1"/>
     </row>
-    <row r="634" spans="1:28">
+    <row r="634" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A634">
         <v>653</v>
       </c>
@@ -32130,7 +32157,7 @@
       <c r="AA634" s="1"/>
       <c r="AB634" s="1"/>
     </row>
-    <row r="635" spans="1:28">
+    <row r="635" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A635">
         <v>654</v>
       </c>
@@ -32180,7 +32207,7 @@
       <c r="AA635" s="1"/>
       <c r="AB635" s="1"/>
     </row>
-    <row r="636" spans="1:28">
+    <row r="636" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A636">
         <v>655</v>
       </c>
@@ -32230,7 +32257,7 @@
       <c r="AA636" s="1"/>
       <c r="AB636" s="1"/>
     </row>
-    <row r="637" spans="1:28">
+    <row r="637" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A637">
         <v>656</v>
       </c>
@@ -32280,7 +32307,7 @@
       <c r="AA637" s="1"/>
       <c r="AB637" s="1"/>
     </row>
-    <row r="638" spans="1:28">
+    <row r="638" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A638">
         <v>657</v>
       </c>
@@ -32330,7 +32357,7 @@
       <c r="AA638" s="1"/>
       <c r="AB638" s="1"/>
     </row>
-    <row r="639" spans="1:28">
+    <row r="639" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A639">
         <v>658</v>
       </c>
@@ -32380,7 +32407,7 @@
       <c r="AA639" s="1"/>
       <c r="AB639" s="1"/>
     </row>
-    <row r="640" spans="1:28">
+    <row r="640" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A640">
         <v>659</v>
       </c>
@@ -32430,7 +32457,7 @@
       <c r="AA640" s="1"/>
       <c r="AB640" s="1"/>
     </row>
-    <row r="641" spans="1:28">
+    <row r="641" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A641">
         <v>660</v>
       </c>
@@ -32476,7 +32503,7 @@
       <c r="AA641" s="1"/>
       <c r="AB641" s="1"/>
     </row>
-    <row r="642" spans="1:28">
+    <row r="642" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A642">
         <v>661</v>
       </c>
@@ -32522,7 +32549,7 @@
       <c r="AA642" s="1"/>
       <c r="AB642" s="1"/>
     </row>
-    <row r="643" spans="1:28">
+    <row r="643" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A643">
         <v>662</v>
       </c>
@@ -32572,7 +32599,7 @@
       <c r="AA643" s="1"/>
       <c r="AB643" s="1"/>
     </row>
-    <row r="644" spans="1:28">
+    <row r="644" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A644">
         <v>663</v>
       </c>
@@ -32622,7 +32649,7 @@
       <c r="AA644" s="1"/>
       <c r="AB644" s="1"/>
     </row>
-    <row r="645" spans="1:28">
+    <row r="645" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A645">
         <v>664</v>
       </c>
@@ -32672,7 +32699,7 @@
       <c r="AA645" s="1"/>
       <c r="AB645" s="1"/>
     </row>
-    <row r="646" spans="1:28">
+    <row r="646" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A646">
         <v>665</v>
       </c>
@@ -32722,7 +32749,7 @@
       <c r="AA646" s="1"/>
       <c r="AB646" s="1"/>
     </row>
-    <row r="647" spans="1:28">
+    <row r="647" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A647">
         <v>666</v>
       </c>
@@ -32772,7 +32799,7 @@
       <c r="AA647" s="1"/>
       <c r="AB647" s="1"/>
     </row>
-    <row r="648" spans="1:28">
+    <row r="648" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A648">
         <v>667</v>
       </c>
@@ -32822,7 +32849,7 @@
       <c r="AA648" s="1"/>
       <c r="AB648" s="1"/>
     </row>
-    <row r="649" spans="1:28">
+    <row r="649" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A649">
         <v>668</v>
       </c>
@@ -32872,7 +32899,7 @@
       <c r="AA649" s="1"/>
       <c r="AB649" s="1"/>
     </row>
-    <row r="650" spans="1:28">
+    <row r="650" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A650">
         <v>669</v>
       </c>
@@ -32922,7 +32949,7 @@
       <c r="AA650" s="1"/>
       <c r="AB650" s="1"/>
     </row>
-    <row r="651" spans="1:28">
+    <row r="651" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A651">
         <v>670</v>
       </c>
@@ -32968,7 +32995,7 @@
       <c r="AA651" s="1"/>
       <c r="AB651" s="1"/>
     </row>
-    <row r="652" spans="1:28">
+    <row r="652" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A652">
         <v>671</v>
       </c>
@@ -33018,7 +33045,7 @@
       <c r="AA652" s="1"/>
       <c r="AB652" s="1"/>
     </row>
-    <row r="653" spans="1:28">
+    <row r="653" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A653">
         <v>672</v>
       </c>
@@ -33068,7 +33095,7 @@
       <c r="AA653" s="1"/>
       <c r="AB653" s="1"/>
     </row>
-    <row r="654" spans="1:28">
+    <row r="654" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A654">
         <v>673</v>
       </c>
@@ -33118,7 +33145,7 @@
       <c r="AA654" s="1"/>
       <c r="AB654" s="1"/>
     </row>
-    <row r="655" spans="1:28">
+    <row r="655" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A655">
         <v>674</v>
       </c>
@@ -33168,7 +33195,7 @@
       <c r="AA655" s="1"/>
       <c r="AB655" s="1"/>
     </row>
-    <row r="656" spans="1:28">
+    <row r="656" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A656">
         <v>675</v>
       </c>
@@ -33218,7 +33245,7 @@
       <c r="AA656" s="1"/>
       <c r="AB656" s="1"/>
     </row>
-    <row r="657" spans="1:28">
+    <row r="657" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A657">
         <v>676</v>
       </c>
@@ -33268,7 +33295,7 @@
       <c r="AA657" s="1"/>
       <c r="AB657" s="1"/>
     </row>
-    <row r="658" spans="1:28">
+    <row r="658" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A658">
         <v>677</v>
       </c>
@@ -33318,7 +33345,7 @@
       <c r="AA658" s="1"/>
       <c r="AB658" s="1"/>
     </row>
-    <row r="659" spans="1:28">
+    <row r="659" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A659">
         <v>678</v>
       </c>
@@ -33368,7 +33395,7 @@
       <c r="AA659" s="1"/>
       <c r="AB659" s="1"/>
     </row>
-    <row r="660" spans="1:28">
+    <row r="660" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A660">
         <v>679</v>
       </c>
@@ -33418,7 +33445,7 @@
       <c r="AA660" s="1"/>
       <c r="AB660" s="1"/>
     </row>
-    <row r="661" spans="1:28">
+    <row r="661" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A661">
         <v>680</v>
       </c>
@@ -33468,7 +33495,7 @@
       <c r="AA661" s="1"/>
       <c r="AB661" s="1"/>
     </row>
-    <row r="662" spans="1:28">
+    <row r="662" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A662">
         <v>681</v>
       </c>
@@ -33518,7 +33545,7 @@
       <c r="AA662" s="1"/>
       <c r="AB662" s="1"/>
     </row>
-    <row r="663" spans="1:28">
+    <row r="663" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A663">
         <v>682</v>
       </c>
@@ -33568,7 +33595,7 @@
       <c r="AA663" s="1"/>
       <c r="AB663" s="1"/>
     </row>
-    <row r="664" spans="1:28">
+    <row r="664" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A664">
         <v>683</v>
       </c>
@@ -33618,7 +33645,7 @@
       <c r="AA664" s="1"/>
       <c r="AB664" s="1"/>
     </row>
-    <row r="665" spans="1:28">
+    <row r="665" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A665">
         <v>684</v>
       </c>
@@ -33668,7 +33695,7 @@
       <c r="AA665" s="1"/>
       <c r="AB665" s="1"/>
     </row>
-    <row r="666" spans="1:28">
+    <row r="666" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A666">
         <v>685</v>
       </c>
@@ -33718,7 +33745,7 @@
       <c r="AA666" s="1"/>
       <c r="AB666" s="1"/>
     </row>
-    <row r="667" spans="1:28">
+    <row r="667" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A667">
         <v>686</v>
       </c>
@@ -33768,7 +33795,7 @@
       <c r="AA667" s="1"/>
       <c r="AB667" s="1"/>
     </row>
-    <row r="668" spans="1:28">
+    <row r="668" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A668">
         <v>687</v>
       </c>
@@ -33818,7 +33845,7 @@
       <c r="AA668" s="1"/>
       <c r="AB668" s="1"/>
     </row>
-    <row r="669" spans="1:28">
+    <row r="669" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A669">
         <v>688</v>
       </c>
@@ -33868,7 +33895,7 @@
       <c r="AA669" s="1"/>
       <c r="AB669" s="1"/>
     </row>
-    <row r="670" spans="1:28">
+    <row r="670" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A670">
         <v>689</v>
       </c>
@@ -33918,7 +33945,7 @@
       <c r="AA670" s="1"/>
       <c r="AB670" s="1"/>
     </row>
-    <row r="671" spans="1:28">
+    <row r="671" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A671">
         <v>690</v>
       </c>
@@ -33968,7 +33995,7 @@
       <c r="AA671" s="1"/>
       <c r="AB671" s="1"/>
     </row>
-    <row r="672" spans="1:28">
+    <row r="672" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A672">
         <v>691</v>
       </c>
@@ -34018,7 +34045,7 @@
       <c r="AA672" s="1"/>
       <c r="AB672" s="1"/>
     </row>
-    <row r="673" spans="1:28">
+    <row r="673" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A673">
         <v>692</v>
       </c>
@@ -34068,7 +34095,7 @@
       <c r="AA673" s="1"/>
       <c r="AB673" s="1"/>
     </row>
-    <row r="674" spans="1:28">
+    <row r="674" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A674">
         <v>693</v>
       </c>
@@ -34118,7 +34145,7 @@
       <c r="AA674" s="1"/>
       <c r="AB674" s="1"/>
     </row>
-    <row r="675" spans="1:28">
+    <row r="675" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A675">
         <v>694</v>
       </c>
@@ -34168,7 +34195,7 @@
       <c r="AA675" s="1"/>
       <c r="AB675" s="1"/>
     </row>
-    <row r="676" spans="1:28">
+    <row r="676" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A676">
         <v>695</v>
       </c>
@@ -34218,7 +34245,7 @@
       <c r="AA676" s="1"/>
       <c r="AB676" s="1"/>
     </row>
-    <row r="677" spans="1:28">
+    <row r="677" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A677">
         <v>696</v>
       </c>
@@ -34268,7 +34295,7 @@
       <c r="AA677" s="1"/>
       <c r="AB677" s="1"/>
     </row>
-    <row r="678" spans="1:28">
+    <row r="678" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A678">
         <v>697</v>
       </c>
@@ -34318,7 +34345,7 @@
       <c r="AA678" s="1"/>
       <c r="AB678" s="1"/>
     </row>
-    <row r="679" spans="1:28">
+    <row r="679" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A679">
         <v>698</v>
       </c>
@@ -34368,7 +34395,7 @@
       <c r="AA679" s="1"/>
       <c r="AB679" s="1"/>
     </row>
-    <row r="680" spans="1:28">
+    <row r="680" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A680">
         <v>699</v>
       </c>
@@ -34414,7 +34441,7 @@
       <c r="AA680" s="1"/>
       <c r="AB680" s="1"/>
     </row>
-    <row r="681" spans="1:28">
+    <row r="681" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A681">
         <v>700</v>
       </c>
@@ -34464,7 +34491,7 @@
       <c r="AA681" s="1"/>
       <c r="AB681" s="1"/>
     </row>
-    <row r="682" spans="1:28">
+    <row r="682" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A682">
         <v>701</v>
       </c>
@@ -34510,7 +34537,7 @@
       <c r="AA682" s="1"/>
       <c r="AB682" s="1"/>
     </row>
-    <row r="683" spans="1:28">
+    <row r="683" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A683">
         <v>702</v>
       </c>
@@ -34556,7 +34583,7 @@
       <c r="AA683" s="1"/>
       <c r="AB683" s="1"/>
     </row>
-    <row r="684" spans="1:28">
+    <row r="684" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A684">
         <v>703</v>
       </c>
@@ -34606,7 +34633,7 @@
       <c r="AA684" s="1"/>
       <c r="AB684" s="1"/>
     </row>
-    <row r="685" spans="1:28">
+    <row r="685" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A685">
         <v>704</v>
       </c>
@@ -34656,7 +34683,7 @@
       <c r="AA685" s="1"/>
       <c r="AB685" s="1"/>
     </row>
-    <row r="686" spans="1:28">
+    <row r="686" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A686">
         <v>705</v>
       </c>
@@ -34706,7 +34733,7 @@
       <c r="AA686" s="1"/>
       <c r="AB686" s="1"/>
     </row>
-    <row r="687" spans="1:28">
+    <row r="687" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A687">
         <v>706</v>
       </c>
@@ -34756,7 +34783,7 @@
       <c r="AA687" s="1"/>
       <c r="AB687" s="1"/>
     </row>
-    <row r="688" spans="1:28">
+    <row r="688" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A688">
         <v>707</v>
       </c>
@@ -34806,7 +34833,7 @@
       <c r="AA688" s="1"/>
       <c r="AB688" s="1"/>
     </row>
-    <row r="689" spans="1:28">
+    <row r="689" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A689">
         <v>708</v>
       </c>
@@ -34852,7 +34879,7 @@
       <c r="AA689" s="1"/>
       <c r="AB689" s="1"/>
     </row>
-    <row r="690" spans="1:28">
+    <row r="690" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A690">
         <v>709</v>
       </c>
@@ -34898,7 +34925,7 @@
       <c r="AA690" s="1"/>
       <c r="AB690" s="1"/>
     </row>
-    <row r="691" spans="1:28">
+    <row r="691" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A691">
         <v>710</v>
       </c>
@@ -34944,7 +34971,7 @@
       <c r="AA691" s="1"/>
       <c r="AB691" s="1"/>
     </row>
-    <row r="692" spans="1:28">
+    <row r="692" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A692">
         <v>711</v>
       </c>
@@ -34994,7 +35021,7 @@
       <c r="AA692" s="1"/>
       <c r="AB692" s="1"/>
     </row>
-    <row r="693" spans="1:28">
+    <row r="693" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A693">
         <v>712</v>
       </c>
@@ -35044,7 +35071,7 @@
       <c r="AA693" s="1"/>
       <c r="AB693" s="1"/>
     </row>
-    <row r="694" spans="1:28">
+    <row r="694" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A694">
         <v>713</v>
       </c>
@@ -35090,7 +35117,7 @@
       <c r="AA694" s="1"/>
       <c r="AB694" s="1"/>
     </row>
-    <row r="695" spans="1:28">
+    <row r="695" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A695">
         <v>714</v>
       </c>
@@ -35136,7 +35163,7 @@
       <c r="AA695" s="1"/>
       <c r="AB695" s="1"/>
     </row>
-    <row r="696" spans="1:28">
+    <row r="696" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A696">
         <v>715</v>
       </c>
@@ -35186,7 +35213,7 @@
       <c r="AA696" s="1"/>
       <c r="AB696" s="1"/>
     </row>
-    <row r="697" spans="1:28">
+    <row r="697" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A697">
         <v>716</v>
       </c>
@@ -35234,7 +35261,7 @@
       <c r="AA697" s="1"/>
       <c r="AB697" s="1"/>
     </row>
-    <row r="698" spans="1:28">
+    <row r="698" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A698">
         <v>719</v>
       </c>
@@ -35286,7 +35313,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="699" spans="1:28">
+    <row r="699" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A699">
         <v>720</v>
       </c>
@@ -35332,7 +35359,7 @@
       <c r="AA699" s="1"/>
       <c r="AB699" s="1"/>
     </row>
-    <row r="700" spans="1:28">
+    <row r="700" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A700">
         <v>721</v>
       </c>
@@ -35384,7 +35411,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="701" spans="1:28">
+    <row r="701" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A701">
         <v>722</v>
       </c>
@@ -35434,7 +35461,7 @@
       <c r="AA701" s="1"/>
       <c r="AB701" s="1"/>
     </row>
-    <row r="702" spans="1:28">
+    <row r="702" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A702">
         <v>723</v>
       </c>
@@ -35484,7 +35511,7 @@
       <c r="AA702" s="1"/>
       <c r="AB702" s="1"/>
     </row>
-    <row r="703" spans="1:28">
+    <row r="703" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A703">
         <v>724</v>
       </c>
@@ -35534,7 +35561,7 @@
       <c r="AA703" s="1"/>
       <c r="AB703" s="1"/>
     </row>
-    <row r="704" spans="1:28">
+    <row r="704" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A704">
         <v>725</v>
       </c>
@@ -35580,7 +35607,7 @@
       <c r="AA704" s="1"/>
       <c r="AB704" s="1"/>
     </row>
-    <row r="705" spans="1:28">
+    <row r="705" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A705">
         <v>726</v>
       </c>
@@ -35626,7 +35653,7 @@
       <c r="AA705" s="1"/>
       <c r="AB705" s="1"/>
     </row>
-    <row r="706" spans="1:28">
+    <row r="706" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A706">
         <v>727</v>
       </c>
@@ -35672,7 +35699,7 @@
       <c r="AA706" s="1"/>
       <c r="AB706" s="1"/>
     </row>
-    <row r="707" spans="1:28">
+    <row r="707" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A707">
         <v>728</v>
       </c>
@@ -35724,7 +35751,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="708" spans="1:28">
+    <row r="708" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A708">
         <v>729</v>
       </c>
@@ -35776,7 +35803,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="709" spans="1:28">
+    <row r="709" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A709">
         <v>730</v>
       </c>
@@ -35828,7 +35855,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="710" spans="1:28">
+    <row r="710" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A710">
         <v>731</v>
       </c>
@@ -35876,7 +35903,7 @@
       <c r="AA710" s="1"/>
       <c r="AB710" s="1"/>
     </row>
-    <row r="711" spans="1:28">
+    <row r="711" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A711">
         <v>732</v>
       </c>
@@ -35926,7 +35953,7 @@
       <c r="AA711" s="1"/>
       <c r="AB711" s="1"/>
     </row>
-    <row r="712" spans="1:28">
+    <row r="712" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A712">
         <v>733</v>
       </c>
@@ -35978,7 +36005,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="713" spans="1:28">
+    <row r="713" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A713">
         <v>734</v>
       </c>
@@ -36030,7 +36057,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="714" spans="1:28">
+    <row r="714" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A714">
         <v>735</v>
       </c>
@@ -36082,7 +36109,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="715" spans="1:28">
+    <row r="715" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A715">
         <v>736</v>
       </c>
@@ -36134,7 +36161,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="716" spans="1:28">
+    <row r="716" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A716">
         <v>737</v>
       </c>
@@ -36186,7 +36213,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="717" spans="1:28">
+    <row r="717" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A717">
         <v>738</v>
       </c>
@@ -36238,7 +36265,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="718" spans="1:28">
+    <row r="718" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A718">
         <v>739</v>
       </c>
@@ -36290,7 +36317,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="719" spans="1:28">
+    <row r="719" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A719">
         <v>740</v>
       </c>
@@ -36342,7 +36369,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="720" spans="1:28">
+    <row r="720" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A720">
         <v>741</v>
       </c>
@@ -36394,7 +36421,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="721" spans="1:28">
+    <row r="721" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A721">
         <v>742</v>
       </c>
@@ -36446,7 +36473,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="722" spans="1:28">
+    <row r="722" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A722">
         <v>743</v>
       </c>
@@ -36498,7 +36525,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="723" spans="1:28">
+    <row r="723" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A723">
         <v>744</v>
       </c>
@@ -36550,7 +36577,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="724" spans="1:28">
+    <row r="724" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A724">
         <v>745</v>
       </c>
@@ -36602,8 +36629,8 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="725" spans="1:28">
-      <c r="A725" s="5">
+    <row r="725" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A725">
         <v>746</v>
       </c>
       <c r="B725" s="2">
@@ -36618,7 +36645,7 @@
       <c r="E725" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F725" s="5">
+      <c r="F725">
         <v>38456</v>
       </c>
       <c r="G725" s="1" t="s">
@@ -36648,8 +36675,8 @@
       <c r="AA725" s="1"/>
       <c r="AB725" s="1"/>
     </row>
-    <row r="726" spans="1:28">
-      <c r="A726" s="5">
+    <row r="726" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A726">
         <v>747</v>
       </c>
       <c r="B726" s="2">
@@ -36664,7 +36691,7 @@
       <c r="E726" s="1" t="s">
         <v>826</v>
       </c>
-      <c r="F726" s="5">
+      <c r="F726">
         <v>38918</v>
       </c>
       <c r="G726" s="1" t="s">
@@ -36700,8 +36727,8 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="727" spans="1:28">
-      <c r="A727" s="5">
+    <row r="727" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A727">
         <v>748</v>
       </c>
       <c r="B727" s="2">
@@ -36716,7 +36743,7 @@
       <c r="E727" s="1" t="s">
         <v>1142</v>
       </c>
-      <c r="F727" s="5">
+      <c r="F727">
         <v>38461</v>
       </c>
       <c r="G727" s="1" t="s">
@@ -36752,8 +36779,8 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="728" spans="1:28">
-      <c r="A728" s="5">
+    <row r="728" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A728">
         <v>749</v>
       </c>
       <c r="B728" s="2">
@@ -36768,7 +36795,7 @@
       <c r="E728" s="1" t="s">
         <v>1000</v>
       </c>
-      <c r="F728" s="5">
+      <c r="F728">
         <v>38810</v>
       </c>
       <c r="G728" s="1" t="s">
@@ -36804,8 +36831,8 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="729" spans="1:28">
-      <c r="A729" s="5">
+    <row r="729" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A729">
         <v>750</v>
       </c>
       <c r="B729" s="2">
@@ -36820,7 +36847,7 @@
       <c r="E729" s="1" t="s">
         <v>1146</v>
       </c>
-      <c r="F729" s="5">
+      <c r="F729">
         <v>38390</v>
       </c>
       <c r="G729" s="1" t="s">
@@ -36856,8 +36883,8 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="730" spans="1:28">
-      <c r="A730" s="5">
+    <row r="730" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A730">
         <v>751</v>
       </c>
       <c r="B730" s="2">
@@ -36872,7 +36899,7 @@
       <c r="E730" s="1" t="s">
         <v>832</v>
       </c>
-      <c r="F730" s="5">
+      <c r="F730">
         <v>38445</v>
       </c>
       <c r="G730" s="1" t="s">
@@ -36908,8 +36935,8 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="731" spans="1:28">
-      <c r="A731" s="5">
+    <row r="731" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A731">
         <v>752</v>
       </c>
       <c r="B731" s="2">
@@ -36924,7 +36951,7 @@
       <c r="E731" s="1" t="s">
         <v>1079</v>
       </c>
-      <c r="F731" s="5">
+      <c r="F731">
         <v>38692</v>
       </c>
       <c r="G731" s="1" t="s">
@@ -36960,8 +36987,8 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="732" spans="1:28">
-      <c r="A732" s="5">
+    <row r="732" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A732">
         <v>753</v>
       </c>
       <c r="B732" s="2">
@@ -36976,7 +37003,7 @@
       <c r="E732" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F732" s="5">
+      <c r="F732">
         <v>38456</v>
       </c>
       <c r="G732" s="1" t="s">
@@ -37012,8 +37039,8 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="733" spans="1:28">
-      <c r="A733" s="5">
+    <row r="733" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A733">
         <v>754</v>
       </c>
       <c r="B733" s="2">
@@ -37028,7 +37055,7 @@
       <c r="E733" s="1" t="s">
         <v>959</v>
       </c>
-      <c r="F733" s="5">
+      <c r="F733">
         <v>38829</v>
       </c>
       <c r="G733" s="1" t="s">
@@ -37064,8 +37091,8 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="734" spans="1:28">
-      <c r="A734" s="5">
+    <row r="734" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A734">
         <v>755</v>
       </c>
       <c r="B734" s="2">
@@ -37080,7 +37107,7 @@
       <c r="E734" s="1" t="s">
         <v>913</v>
       </c>
-      <c r="F734" s="5">
+      <c r="F734">
         <v>43162</v>
       </c>
       <c r="G734" s="1" t="s">
@@ -37116,8 +37143,8 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="735" spans="1:28">
-      <c r="A735" s="5">
+    <row r="735" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A735">
         <v>756</v>
       </c>
       <c r="B735" s="2">
@@ -37132,7 +37159,7 @@
       <c r="E735" s="1" t="s">
         <v>988</v>
       </c>
-      <c r="F735" s="5">
+      <c r="F735">
         <v>43142</v>
       </c>
       <c r="G735" s="1" t="s">
@@ -37168,8 +37195,8 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="736" spans="1:28">
-      <c r="A736" s="5">
+    <row r="736" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A736">
         <v>757</v>
       </c>
       <c r="B736" s="2">
@@ -37184,7 +37211,7 @@
       <c r="E736" s="1" t="s">
         <v>956</v>
       </c>
-      <c r="F736" s="5">
+      <c r="F736">
         <v>38727</v>
       </c>
       <c r="G736" s="1" t="s">
@@ -37220,8 +37247,8 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="737" spans="1:28">
-      <c r="A737" s="5">
+    <row r="737" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A737">
         <v>758</v>
       </c>
       <c r="B737" s="2">
@@ -37236,7 +37263,7 @@
       <c r="E737" s="1" t="s">
         <v>1076</v>
       </c>
-      <c r="F737" s="5">
+      <c r="F737">
         <v>38896</v>
       </c>
       <c r="G737" s="1" t="s">
@@ -37272,8 +37299,8 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="738" spans="1:28">
-      <c r="A738" s="5">
+    <row r="738" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A738">
         <v>759</v>
       </c>
       <c r="B738" s="2">
@@ -37288,7 +37315,7 @@
       <c r="E738" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="F738" s="5">
+      <c r="F738">
         <v>38590</v>
       </c>
       <c r="G738" s="1" t="s">
@@ -37318,8 +37345,8 @@
       <c r="AA738" s="1"/>
       <c r="AB738" s="1"/>
     </row>
-    <row r="739" spans="1:28">
-      <c r="A739" s="5">
+    <row r="739" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A739">
         <v>760</v>
       </c>
       <c r="B739" s="2">
@@ -37334,7 +37361,7 @@
       <c r="E739" s="1" t="s">
         <v>1032</v>
       </c>
-      <c r="F739" s="5">
+      <c r="F739">
         <v>38987</v>
       </c>
       <c r="G739" s="1" t="s">
@@ -37370,8 +37397,8 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="740" spans="1:28">
-      <c r="A740" s="5">
+    <row r="740" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A740">
         <v>761</v>
       </c>
       <c r="B740" s="2">
@@ -37386,7 +37413,7 @@
       <c r="E740" s="1" t="s">
         <v>814</v>
       </c>
-      <c r="F740" s="5">
+      <c r="F740">
         <v>38709</v>
       </c>
       <c r="G740" s="1" t="s">
@@ -37416,8 +37443,8 @@
       <c r="AA740" s="1"/>
       <c r="AB740" s="1"/>
     </row>
-    <row r="741" spans="1:28">
-      <c r="A741" s="5">
+    <row r="741" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A741">
         <v>762</v>
       </c>
       <c r="B741" s="2">
@@ -37432,7 +37459,7 @@
       <c r="E741" s="1" t="s">
         <v>1158</v>
       </c>
-      <c r="F741" s="5">
+      <c r="F741">
         <v>38138</v>
       </c>
       <c r="G741" s="1" t="s">
@@ -37468,8 +37495,8 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="742" spans="1:28">
-      <c r="A742" s="5">
+    <row r="742" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A742">
         <v>763</v>
       </c>
       <c r="B742" s="2">
@@ -37484,7 +37511,7 @@
       <c r="E742" s="1" t="s">
         <v>1006</v>
       </c>
-      <c r="F742" s="5">
+      <c r="F742">
         <v>38372</v>
       </c>
       <c r="G742" s="1" t="s">
@@ -37520,8 +37547,8 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="743" spans="1:28">
-      <c r="A743" s="5">
+    <row r="743" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A743">
         <v>764</v>
       </c>
       <c r="B743" s="2">
@@ -37536,7 +37563,7 @@
       <c r="E743" s="1" t="s">
         <v>1035</v>
       </c>
-      <c r="F743" s="5">
+      <c r="F743">
         <v>38319</v>
       </c>
       <c r="G743" s="1" t="s">
@@ -37572,8 +37599,8 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="744" spans="1:28">
-      <c r="A744" s="5">
+    <row r="744" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A744">
         <v>765</v>
       </c>
       <c r="B744" s="2">
@@ -37588,7 +37615,7 @@
       <c r="E744" s="1" t="s">
         <v>946</v>
       </c>
-      <c r="F744" s="5">
+      <c r="F744">
         <v>38755</v>
       </c>
       <c r="G744" s="1" t="s">
@@ -37624,8 +37651,8 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="745" spans="1:28">
-      <c r="A745" s="5">
+    <row r="745" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A745">
         <v>766</v>
       </c>
       <c r="B745" s="2">
@@ -37640,7 +37667,7 @@
       <c r="E745" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F745" s="5">
+      <c r="F745">
         <v>38894</v>
       </c>
       <c r="G745" s="1" t="s">
@@ -37674,8 +37701,8 @@
       <c r="AA745" s="1"/>
       <c r="AB745" s="1"/>
     </row>
-    <row r="746" spans="1:28">
-      <c r="A746" s="5">
+    <row r="746" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A746">
         <v>767</v>
       </c>
       <c r="B746" s="2">
@@ -37690,7 +37717,7 @@
       <c r="E746" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F746" s="5">
+      <c r="F746">
         <v>38894</v>
       </c>
       <c r="G746" s="1" t="s">
@@ -37726,8 +37753,8 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="747" spans="1:28">
-      <c r="A747" s="5">
+    <row r="747" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A747">
         <v>768</v>
       </c>
       <c r="B747" s="2">
@@ -37742,7 +37769,7 @@
       <c r="E747" s="1" t="s">
         <v>859</v>
       </c>
-      <c r="F747" s="5">
+      <c r="F747">
         <v>38538</v>
       </c>
       <c r="G747" s="1" t="s">
@@ -37778,8 +37805,8 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="748" spans="1:28">
-      <c r="A748" s="5">
+    <row r="748" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A748">
         <v>769</v>
       </c>
       <c r="B748" s="2">
@@ -37794,7 +37821,7 @@
       <c r="E748" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F748" s="5">
+      <c r="F748">
         <v>38894</v>
       </c>
       <c r="G748" s="1" t="s">
@@ -37824,8 +37851,8 @@
       <c r="AA748" s="1"/>
       <c r="AB748" s="1"/>
     </row>
-    <row r="749" spans="1:28">
-      <c r="A749" s="5">
+    <row r="749" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A749">
         <v>770</v>
       </c>
       <c r="B749" s="2">
@@ -37840,7 +37867,7 @@
       <c r="E749" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F749" s="5">
+      <c r="F749">
         <v>38894</v>
       </c>
       <c r="G749" s="1" t="s">
@@ -37870,8 +37897,8 @@
       <c r="AA749" s="1"/>
       <c r="AB749" s="1"/>
     </row>
-    <row r="750" spans="1:28">
-      <c r="A750" s="5">
+    <row r="750" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A750">
         <v>771</v>
       </c>
       <c r="B750" s="2">
@@ -37886,7 +37913,7 @@
       <c r="E750" s="1" t="s">
         <v>895</v>
       </c>
-      <c r="F750" s="5">
+      <c r="F750">
         <v>43041</v>
       </c>
       <c r="G750" s="1" t="s">
@@ -37922,8 +37949,8 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="751" spans="1:28">
-      <c r="A751" s="5">
+    <row r="751" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A751">
         <v>772</v>
       </c>
       <c r="B751" s="2">
@@ -37938,7 +37965,7 @@
       <c r="E751" s="1" t="s">
         <v>1065</v>
       </c>
-      <c r="F751" s="5">
+      <c r="F751">
         <v>38841</v>
       </c>
       <c r="G751" s="1" t="s">
@@ -37974,8 +38001,8 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="752" spans="1:28">
-      <c r="A752" s="5">
+    <row r="752" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A752">
         <v>773</v>
       </c>
       <c r="B752" s="2">
@@ -37990,7 +38017,7 @@
       <c r="E752" s="1" t="s">
         <v>892</v>
       </c>
-      <c r="F752" s="5">
+      <c r="F752">
         <v>38722</v>
       </c>
       <c r="G752" s="1" t="s">
@@ -38026,8 +38053,8 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="753" spans="1:28">
-      <c r="A753" s="5">
+    <row r="753" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A753">
         <v>774</v>
       </c>
       <c r="B753" s="2">
@@ -38042,7 +38069,7 @@
       <c r="E753" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F753" s="5">
+      <c r="F753">
         <v>38401</v>
       </c>
       <c r="G753" s="1" t="s">
@@ -38078,8 +38105,8 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="754" spans="1:28">
-      <c r="A754" s="5">
+    <row r="754" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A754">
         <v>775</v>
       </c>
       <c r="B754" s="2">
@@ -38094,7 +38121,7 @@
       <c r="E754" s="1" t="s">
         <v>922</v>
       </c>
-      <c r="F754" s="5">
+      <c r="F754">
         <v>38158</v>
       </c>
       <c r="G754" s="1" t="s">
@@ -38130,8 +38157,8 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="755" spans="1:28">
-      <c r="A755" s="5">
+    <row r="755" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A755">
         <v>776</v>
       </c>
       <c r="B755" s="2">
@@ -38146,7 +38173,7 @@
       <c r="E755" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="F755" s="5">
+      <c r="F755">
         <v>38401</v>
       </c>
       <c r="G755" s="1" t="s">
@@ -38180,8 +38207,8 @@
       <c r="AA755" s="1"/>
       <c r="AB755" s="1"/>
     </row>
-    <row r="756" spans="1:28">
-      <c r="A756" s="5">
+    <row r="756" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A756">
         <v>777</v>
       </c>
       <c r="B756" s="2">
@@ -38196,7 +38223,7 @@
       <c r="E756" s="1" t="s">
         <v>950</v>
       </c>
-      <c r="F756" s="5">
+      <c r="F756">
         <v>38929</v>
       </c>
       <c r="G756" s="1" t="s">
@@ -38226,8 +38253,8 @@
       <c r="AA756" s="1"/>
       <c r="AB756" s="1"/>
     </row>
-    <row r="757" spans="1:28">
-      <c r="A757" s="5">
+    <row r="757" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A757">
         <v>778</v>
       </c>
       <c r="B757" s="2">
@@ -38242,7 +38269,7 @@
       <c r="E757" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="F757" s="5">
+      <c r="F757">
         <v>43193</v>
       </c>
       <c r="G757" s="1" t="s">
@@ -38278,8 +38305,8 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="758" spans="1:28">
-      <c r="A758" s="5">
+    <row r="758" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A758">
         <v>779</v>
       </c>
       <c r="B758" s="2">
@@ -38294,7 +38321,7 @@
       <c r="E758" s="1" t="s">
         <v>1177</v>
       </c>
-      <c r="F758" s="5">
+      <c r="F758">
         <v>38466</v>
       </c>
       <c r="G758" s="1" t="s">
@@ -38330,8 +38357,8 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="759" spans="1:28">
-      <c r="A759" s="5">
+    <row r="759" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A759">
         <v>780</v>
       </c>
       <c r="B759" s="2">
@@ -38346,7 +38373,7 @@
       <c r="E759" s="1" t="s">
         <v>796</v>
       </c>
-      <c r="F759" s="5">
+      <c r="F759">
         <v>38141</v>
       </c>
       <c r="G759" s="1" t="s">
@@ -38382,8 +38409,8 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="760" spans="1:28">
-      <c r="A760" s="5">
+    <row r="760" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A760">
         <v>781</v>
       </c>
       <c r="B760" s="2">
@@ -38398,7 +38425,7 @@
       <c r="E760" s="1" t="s">
         <v>844</v>
       </c>
-      <c r="F760" s="5">
+      <c r="F760">
         <v>38799</v>
       </c>
       <c r="G760" s="1" t="s">
@@ -38434,8 +38461,8 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="761" spans="1:28">
-      <c r="A761" s="5">
+    <row r="761" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A761">
         <v>782</v>
       </c>
       <c r="B761" s="2">
@@ -38450,7 +38477,7 @@
       <c r="E761" s="1" t="s">
         <v>853</v>
       </c>
-      <c r="F761" s="5">
+      <c r="F761">
         <v>38185</v>
       </c>
       <c r="G761" s="1" t="s">
@@ -38486,8 +38513,8 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="762" spans="1:28">
-      <c r="A762" s="5">
+    <row r="762" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A762">
         <v>783</v>
       </c>
       <c r="B762" s="2">
@@ -38502,7 +38529,7 @@
       <c r="E762" s="1" t="s">
         <v>1044</v>
       </c>
-      <c r="F762" s="5">
+      <c r="F762">
         <v>38607</v>
       </c>
       <c r="G762" s="1" t="s">
@@ -38538,8 +38565,8 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="763" spans="1:28">
-      <c r="A763" s="5">
+    <row r="763" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A763">
         <v>784</v>
       </c>
       <c r="B763" s="2">
@@ -38554,7 +38581,7 @@
       <c r="E763" s="1" t="s">
         <v>835</v>
       </c>
-      <c r="F763" s="5">
+      <c r="F763">
         <v>38179</v>
       </c>
       <c r="G763" s="1" t="s">
@@ -38584,8 +38611,8 @@
       <c r="AA763" s="1"/>
       <c r="AB763" s="1"/>
     </row>
-    <row r="764" spans="1:28">
-      <c r="A764" s="5">
+    <row r="764" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A764">
         <v>785</v>
       </c>
       <c r="B764" s="2">
@@ -38600,7 +38627,7 @@
       <c r="E764" s="1" t="s">
         <v>1184</v>
       </c>
-      <c r="F764" s="5">
+      <c r="F764">
         <v>38847</v>
       </c>
       <c r="G764" s="1" t="s">
@@ -38636,8 +38663,8 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="765" spans="1:28">
-      <c r="A765" s="5">
+    <row r="765" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A765">
         <v>786</v>
       </c>
       <c r="B765" s="2">
@@ -38652,7 +38679,7 @@
       <c r="E765" s="1" t="s">
         <v>1029</v>
       </c>
-      <c r="F765" s="5">
+      <c r="F765">
         <v>38193</v>
       </c>
       <c r="G765" s="1" t="s">
@@ -38688,8 +38715,8 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="766" spans="1:28">
-      <c r="A766" s="5">
+    <row r="766" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A766">
         <v>787</v>
       </c>
       <c r="B766" s="2">
@@ -38704,7 +38731,7 @@
       <c r="E766" s="1" t="s">
         <v>817</v>
       </c>
-      <c r="F766" s="5">
+      <c r="F766">
         <v>38547</v>
       </c>
       <c r="G766" s="1" t="s">
@@ -38740,8 +38767,8 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="767" spans="1:28">
-      <c r="A767" s="5">
+    <row r="767" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A767">
         <v>788</v>
       </c>
       <c r="B767" s="2">
@@ -38756,7 +38783,7 @@
       <c r="E767" s="1" t="s">
         <v>1023</v>
       </c>
-      <c r="F767" s="5">
+      <c r="F767">
         <v>38751</v>
       </c>
       <c r="G767" s="1" t="s">
@@ -38792,8 +38819,8 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="768" spans="1:28">
-      <c r="A768" s="5">
+    <row r="768" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A768">
         <v>789</v>
       </c>
       <c r="B768" s="2">
@@ -38808,7 +38835,7 @@
       <c r="E768" s="1" t="s">
         <v>925</v>
       </c>
-      <c r="F768" s="5">
+      <c r="F768">
         <v>38777</v>
       </c>
       <c r="G768" s="1" t="s">
@@ -38844,8 +38871,8 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="769" spans="1:28">
-      <c r="A769" s="5">
+    <row r="769" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A769">
         <v>790</v>
       </c>
       <c r="B769" s="2">
@@ -38860,7 +38887,7 @@
       <c r="E769" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F769" s="5">
+      <c r="F769">
         <v>38561</v>
       </c>
       <c r="G769" s="1" t="s">
@@ -38894,8 +38921,8 @@
       <c r="AA769" s="1"/>
       <c r="AB769" s="1"/>
     </row>
-    <row r="770" spans="1:28">
-      <c r="A770" s="5">
+    <row r="770" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A770">
         <v>791</v>
       </c>
       <c r="B770" s="2">
@@ -38910,7 +38937,7 @@
       <c r="E770" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="F770" s="5">
+      <c r="F770">
         <v>38561</v>
       </c>
       <c r="G770" s="1" t="s">
@@ -38940,8 +38967,8 @@
       <c r="AA770" s="1"/>
       <c r="AB770" s="1"/>
     </row>
-    <row r="771" spans="1:28">
-      <c r="A771" s="5">
+    <row r="771" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A771">
         <v>792</v>
       </c>
       <c r="B771" s="2">
@@ -38956,7 +38983,7 @@
       <c r="E771" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="F771" s="5">
+      <c r="F771">
         <v>38656</v>
       </c>
       <c r="G771" s="1" t="s">
@@ -38986,8 +39013,8 @@
       <c r="AA771" s="1"/>
       <c r="AB771" s="1"/>
     </row>
-    <row r="772" spans="1:28">
-      <c r="A772" s="5">
+    <row r="772" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A772">
         <v>793</v>
       </c>
       <c r="B772" s="2">
@@ -39002,7 +39029,7 @@
       <c r="E772" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F772" s="5">
+      <c r="F772">
         <v>38458</v>
       </c>
       <c r="G772" s="1" t="s">
@@ -39032,8 +39059,8 @@
       <c r="AA772" s="1"/>
       <c r="AB772" s="1"/>
     </row>
-    <row r="773" spans="1:28">
-      <c r="A773" s="5">
+    <row r="773" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A773">
         <v>794</v>
       </c>
       <c r="B773" s="2">
@@ -39048,7 +39075,7 @@
       <c r="E773" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="F773" s="5">
+      <c r="F773">
         <v>38458</v>
       </c>
       <c r="G773" s="1" t="s">
@@ -39082,8 +39109,8 @@
       <c r="AA773" s="1"/>
       <c r="AB773" s="1"/>
     </row>
-    <row r="774" spans="1:28">
-      <c r="A774" s="5">
+    <row r="774" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A774">
         <v>795</v>
       </c>
       <c r="B774" s="2">
@@ -39098,7 +39125,7 @@
       <c r="E774" s="1" t="s">
         <v>1068</v>
       </c>
-      <c r="F774" s="5">
+      <c r="F774">
         <v>38633</v>
       </c>
       <c r="G774" s="1" t="s">
@@ -39128,8 +39155,8 @@
       <c r="AA774" s="1"/>
       <c r="AB774" s="1"/>
     </row>
-    <row r="775" spans="1:28">
-      <c r="A775" s="5">
+    <row r="775" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A775">
         <v>796</v>
       </c>
       <c r="B775" s="2">
@@ -39144,7 +39171,7 @@
       <c r="E775" s="1" t="s">
         <v>919</v>
       </c>
-      <c r="F775" s="5">
+      <c r="F775">
         <v>38780</v>
       </c>
       <c r="G775" s="1" t="s">
@@ -39180,8 +39207,8 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="776" spans="1:28">
-      <c r="A776" s="5">
+    <row r="776" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A776">
         <v>797</v>
       </c>
       <c r="B776" s="2">
@@ -39196,7 +39223,7 @@
       <c r="E776" s="1" t="s">
         <v>940</v>
       </c>
-      <c r="F776" s="5">
+      <c r="F776">
         <v>38166</v>
       </c>
       <c r="G776" s="1" t="s">
@@ -39232,8 +39259,8 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="777" spans="1:28">
-      <c r="A777" s="5">
+    <row r="777" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A777">
         <v>798</v>
       </c>
       <c r="B777" s="2">
@@ -39248,7 +39275,7 @@
       <c r="E777" s="1" t="s">
         <v>1026</v>
       </c>
-      <c r="F777" s="5">
+      <c r="F777">
         <v>38747</v>
       </c>
       <c r="G777" s="1" t="s">
@@ -39278,8 +39305,8 @@
       <c r="AA777" s="1"/>
       <c r="AB777" s="1"/>
     </row>
-    <row r="778" spans="1:28">
-      <c r="A778" s="5">
+    <row r="778" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A778">
         <v>799</v>
       </c>
       <c r="B778" s="2">
@@ -39294,7 +39321,7 @@
       <c r="E778" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F778" s="5">
+      <c r="F778">
         <v>38862</v>
       </c>
       <c r="G778" s="1" t="s">
@@ -39328,8 +39355,8 @@
       <c r="AA778" s="1"/>
       <c r="AB778" s="1"/>
     </row>
-    <row r="779" spans="1:28">
-      <c r="A779" s="5">
+    <row r="779" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A779">
         <v>800</v>
       </c>
       <c r="B779" s="2">
@@ -39344,7 +39371,7 @@
       <c r="E779" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F779" s="5">
+      <c r="F779">
         <v>38862</v>
       </c>
       <c r="G779" s="1" t="s">
@@ -39380,8 +39407,8 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="780" spans="1:28">
-      <c r="A780" s="5">
+    <row r="780" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A780">
         <v>801</v>
       </c>
       <c r="B780" s="2">
@@ -39396,7 +39423,7 @@
       <c r="E780" s="1" t="s">
         <v>962</v>
       </c>
-      <c r="F780" s="5">
+      <c r="F780">
         <v>38233</v>
       </c>
       <c r="G780" s="1" t="s">
@@ -39432,8 +39459,8 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="781" spans="1:28">
-      <c r="A781" s="5">
+    <row r="781" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A781">
         <v>802</v>
       </c>
       <c r="B781" s="2">
@@ -39448,7 +39475,7 @@
       <c r="E781" s="1" t="s">
         <v>820</v>
       </c>
-      <c r="F781" s="5">
+      <c r="F781">
         <v>38553</v>
       </c>
       <c r="G781" s="1" t="s">
@@ -39484,8 +39511,8 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="782" spans="1:28">
-      <c r="A782" s="5">
+    <row r="782" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A782">
         <v>803</v>
       </c>
       <c r="B782" s="2">
@@ -39500,7 +39527,7 @@
       <c r="E782" s="1" t="s">
         <v>1041</v>
       </c>
-      <c r="F782" s="5">
+      <c r="F782">
         <v>38704</v>
       </c>
       <c r="G782" s="1" t="s">
@@ -39530,6 +39557,266 @@
       <c r="AA782" s="1"/>
       <c r="AB782" s="1"/>
     </row>
+    <row r="783" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A783" s="5">
+        <v>804</v>
+      </c>
+      <c r="B783" s="2">
+        <v>46280.285740740699</v>
+      </c>
+      <c r="C783" s="2">
+        <v>46280.406458333302</v>
+      </c>
+      <c r="D783" s="1" t="s">
+        <v>906</v>
+      </c>
+      <c r="E783" s="1" t="s">
+        <v>907</v>
+      </c>
+      <c r="F783" s="5">
+        <v>38499</v>
+      </c>
+      <c r="G783" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H783" s="1"/>
+      <c r="I783" s="1"/>
+      <c r="J783" s="1"/>
+      <c r="K783" s="1"/>
+      <c r="L783" s="1"/>
+      <c r="M783" s="1"/>
+      <c r="N783" s="1"/>
+      <c r="O783" s="1"/>
+      <c r="P783" s="1"/>
+      <c r="Q783" s="1"/>
+      <c r="R783" s="1"/>
+      <c r="S783" s="1"/>
+      <c r="T783" s="1"/>
+      <c r="U783" s="1"/>
+      <c r="V783" s="3"/>
+      <c r="W783" s="3"/>
+      <c r="X783" s="1"/>
+      <c r="Y783" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z783" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AA783" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB783" s="1" t="s">
+        <v>1200</v>
+      </c>
+    </row>
+    <row r="784" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A784" s="5">
+        <v>805</v>
+      </c>
+      <c r="B784" s="2">
+        <v>46280.413506944402</v>
+      </c>
+      <c r="C784" s="2">
+        <v>46280.4148726852</v>
+      </c>
+      <c r="D784" s="1" t="s">
+        <v>1201</v>
+      </c>
+      <c r="E784" s="1" t="s">
+        <v>1202</v>
+      </c>
+      <c r="F784" s="5">
+        <v>38292</v>
+      </c>
+      <c r="G784" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H784" s="1"/>
+      <c r="I784" s="1"/>
+      <c r="J784" s="1"/>
+      <c r="K784" s="1"/>
+      <c r="L784" s="1"/>
+      <c r="M784" s="1"/>
+      <c r="N784" s="1"/>
+      <c r="O784" s="1"/>
+      <c r="P784" s="1"/>
+      <c r="Q784" s="1"/>
+      <c r="R784" s="1"/>
+      <c r="S784" s="1"/>
+      <c r="T784" s="1"/>
+      <c r="U784" s="1"/>
+      <c r="V784" s="3"/>
+      <c r="W784" s="3"/>
+      <c r="X784" s="1"/>
+      <c r="Y784" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z784" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA784" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB784" s="1" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="785" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A785" s="5">
+        <v>806</v>
+      </c>
+      <c r="B785" s="2">
+        <v>46280.372106481504</v>
+      </c>
+      <c r="C785" s="2">
+        <v>46280.417743055601</v>
+      </c>
+      <c r="D785" s="1" t="s">
+        <v>804</v>
+      </c>
+      <c r="E785" s="1" t="s">
+        <v>805</v>
+      </c>
+      <c r="F785" s="5">
+        <v>38122</v>
+      </c>
+      <c r="G785" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H785" s="1"/>
+      <c r="I785" s="1"/>
+      <c r="J785" s="1"/>
+      <c r="K785" s="1"/>
+      <c r="L785" s="1"/>
+      <c r="M785" s="1"/>
+      <c r="N785" s="1"/>
+      <c r="O785" s="1"/>
+      <c r="P785" s="1"/>
+      <c r="Q785" s="1"/>
+      <c r="R785" s="1"/>
+      <c r="S785" s="1"/>
+      <c r="T785" s="1"/>
+      <c r="U785" s="1"/>
+      <c r="V785" s="3"/>
+      <c r="W785" s="3"/>
+      <c r="X785" s="1"/>
+      <c r="Y785" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z785" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA785" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB785" s="1" t="s">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="786" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A786" s="5">
+        <v>807</v>
+      </c>
+      <c r="B786" s="2">
+        <v>46280.428194444401</v>
+      </c>
+      <c r="C786" s="2">
+        <v>46280.428645833301</v>
+      </c>
+      <c r="D786" s="1" t="s">
+        <v>897</v>
+      </c>
+      <c r="E786" s="1" t="s">
+        <v>898</v>
+      </c>
+      <c r="F786" s="5">
+        <v>38452</v>
+      </c>
+      <c r="G786" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H786" s="1"/>
+      <c r="I786" s="1"/>
+      <c r="J786" s="1"/>
+      <c r="K786" s="1"/>
+      <c r="L786" s="1"/>
+      <c r="M786" s="1"/>
+      <c r="N786" s="1"/>
+      <c r="O786" s="1"/>
+      <c r="P786" s="1"/>
+      <c r="Q786" s="1"/>
+      <c r="R786" s="1"/>
+      <c r="S786" s="1"/>
+      <c r="T786" s="1"/>
+      <c r="U786" s="1"/>
+      <c r="V786" s="3"/>
+      <c r="W786" s="3"/>
+      <c r="X786" s="1"/>
+      <c r="Y786" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z786" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA786" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB786" s="1" t="s">
+        <v>1205</v>
+      </c>
+    </row>
+    <row r="787" spans="1:28" x14ac:dyDescent="0.35">
+      <c r="A787" s="5">
+        <v>808</v>
+      </c>
+      <c r="B787" s="2">
+        <v>46280.433495370402</v>
+      </c>
+      <c r="C787" s="2">
+        <v>46280.434155092596</v>
+      </c>
+      <c r="D787" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="E787" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="F787" s="5">
+        <v>38815</v>
+      </c>
+      <c r="G787" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H787" s="1"/>
+      <c r="I787" s="1"/>
+      <c r="J787" s="1"/>
+      <c r="K787" s="1"/>
+      <c r="L787" s="1"/>
+      <c r="M787" s="1"/>
+      <c r="N787" s="1"/>
+      <c r="O787" s="1"/>
+      <c r="P787" s="1"/>
+      <c r="Q787" s="1"/>
+      <c r="R787" s="1"/>
+      <c r="S787" s="1"/>
+      <c r="T787" s="1"/>
+      <c r="U787" s="1"/>
+      <c r="V787" s="3"/>
+      <c r="W787" s="3"/>
+      <c r="X787" s="1"/>
+      <c r="Y787" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z787" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA787" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="AB787" s="1" t="s">
+        <v>1206</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S71" r:id="rId1" xr:uid="{DBEDA7D9-6C97-43FD-AB0F-DEBA1D8AA177}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30502"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Sistema de Evidencia OPS/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="91" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83E7EC78-E40B-4AEC-AC63-351CF2C00481}"/>
+  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{158ACDF3-985F-456E-8B85-55C22790543E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3702" uniqueCount="1207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3706" uniqueCount="1208">
   <si>
     <t>Id</t>
   </si>
@@ -3657,13 +3657,16 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/1789489491477902937509053623929_Starbucks%20Central%20In.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_8190_Starbucks%20Jinetes.jpeg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3807,13 +3810,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB787" totalsRowShown="0">
-  <autoFilter ref="A1:AB787" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB788" totalsRowShown="0">
+  <autoFilter ref="A1:AB788" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="25">
       <extLst>
@@ -4015,7 +4014,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="808" latestEventMarker="1132">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="809" latestEventMarker="1133">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4347,15 +4346,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB787"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AB788"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.453125" customWidth="1"/>
+    <col min="5" max="5" width="32.42578125" customWidth="1"/>
     <col min="6" max="28" width="20" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:28">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -4441,7 +4440,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28">
       <c r="A2">
         <v>13</v>
       </c>
@@ -4467,7 +4466,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28">
       <c r="A3">
         <v>14</v>
       </c>
@@ -4493,7 +4492,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:28">
       <c r="A4">
         <v>15</v>
       </c>
@@ -4519,7 +4518,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:28">
       <c r="A5">
         <v>16</v>
       </c>
@@ -4545,7 +4544,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:28">
       <c r="A6">
         <v>17</v>
       </c>
@@ -4571,7 +4570,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:28">
       <c r="A7">
         <v>18</v>
       </c>
@@ -4597,7 +4596,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:28">
       <c r="A8">
         <v>19</v>
       </c>
@@ -4623,7 +4622,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:28">
       <c r="A9">
         <v>20</v>
       </c>
@@ -4649,7 +4648,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:28">
       <c r="A10">
         <v>21</v>
       </c>
@@ -4675,7 +4674,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:28">
       <c r="A11">
         <v>22</v>
       </c>
@@ -4701,7 +4700,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:28">
       <c r="A12">
         <v>23</v>
       </c>
@@ -4727,7 +4726,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:28">
       <c r="A13">
         <v>24</v>
       </c>
@@ -4753,7 +4752,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:28">
       <c r="A14">
         <v>25</v>
       </c>
@@ -4779,7 +4778,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:28">
       <c r="A15">
         <v>26</v>
       </c>
@@ -4805,7 +4804,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:28">
       <c r="A16">
         <v>27</v>
       </c>
@@ -4834,7 +4833,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:19">
       <c r="A17">
         <v>28</v>
       </c>
@@ -4860,7 +4859,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:19">
       <c r="A18">
         <v>29</v>
       </c>
@@ -4886,7 +4885,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19">
       <c r="A19">
         <v>30</v>
       </c>
@@ -4912,7 +4911,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:19">
       <c r="A20">
         <v>31</v>
       </c>
@@ -4938,7 +4937,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19">
       <c r="A21">
         <v>32</v>
       </c>
@@ -4964,7 +4963,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:19">
       <c r="A22">
         <v>33</v>
       </c>
@@ -4990,7 +4989,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:19">
       <c r="A23">
         <v>34</v>
       </c>
@@ -5016,7 +5015,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19">
       <c r="A24">
         <v>35</v>
       </c>
@@ -5042,7 +5041,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:19">
       <c r="A25">
         <v>36</v>
       </c>
@@ -5068,7 +5067,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19">
       <c r="A26">
         <v>37</v>
       </c>
@@ -5094,7 +5093,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:19">
       <c r="A27">
         <v>38</v>
       </c>
@@ -5120,7 +5119,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:19">
       <c r="A28">
         <v>39</v>
       </c>
@@ -5146,7 +5145,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:19">
       <c r="A29">
         <v>40</v>
       </c>
@@ -5172,7 +5171,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:19">
       <c r="A30">
         <v>41</v>
       </c>
@@ -5195,7 +5194,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:19">
       <c r="A31">
         <v>42</v>
       </c>
@@ -5221,7 +5220,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:19">
       <c r="A32">
         <v>43</v>
       </c>
@@ -5247,7 +5246,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:19">
       <c r="A33">
         <v>44</v>
       </c>
@@ -5273,7 +5272,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="34" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>45</v>
       </c>
@@ -5299,7 +5298,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>46</v>
       </c>
@@ -5325,7 +5324,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>47</v>
       </c>
@@ -5351,7 +5350,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>48</v>
       </c>
@@ -5377,7 +5376,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>49</v>
       </c>
@@ -5403,7 +5402,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>50</v>
       </c>
@@ -5429,7 +5428,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>51</v>
       </c>
@@ -5455,7 +5454,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>52</v>
       </c>
@@ -5481,7 +5480,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>53</v>
       </c>
@@ -5507,7 +5506,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>54</v>
       </c>
@@ -5533,7 +5532,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:19">
       <c r="A44">
         <v>55</v>
       </c>
@@ -5559,7 +5558,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:19">
       <c r="A45">
         <v>56</v>
       </c>
@@ -5585,7 +5584,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:19">
       <c r="A46">
         <v>57</v>
       </c>
@@ -5611,7 +5610,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:19">
       <c r="A47">
         <v>58</v>
       </c>
@@ -5637,7 +5636,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:19">
       <c r="A48">
         <v>59</v>
       </c>
@@ -5663,7 +5662,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="49" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>60</v>
       </c>
@@ -5689,7 +5688,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="50" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>61</v>
       </c>
@@ -5715,7 +5714,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="51" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>62</v>
       </c>
@@ -5741,7 +5740,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="52" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>63</v>
       </c>
@@ -5767,7 +5766,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="53" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>64</v>
       </c>
@@ -5793,7 +5792,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="54" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>65</v>
       </c>
@@ -5819,7 +5818,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="55" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>66</v>
       </c>
@@ -5845,7 +5844,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="56" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>67</v>
       </c>
@@ -5871,7 +5870,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="57" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>68</v>
       </c>
@@ -5897,7 +5896,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="58" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>69</v>
       </c>
@@ -5923,7 +5922,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:19">
       <c r="A59">
         <v>70</v>
       </c>
@@ -5949,7 +5948,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="60" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:19">
       <c r="A60">
         <v>71</v>
       </c>
@@ -5975,7 +5974,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:19">
       <c r="A61">
         <v>72</v>
       </c>
@@ -6001,7 +6000,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="62" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:19">
       <c r="A62">
         <v>73</v>
       </c>
@@ -6027,7 +6026,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="63" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:19">
       <c r="A63">
         <v>74</v>
       </c>
@@ -6053,7 +6052,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="64" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>75</v>
       </c>
@@ -6079,7 +6078,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="65" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>76</v>
       </c>
@@ -6105,7 +6104,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="66" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>77</v>
       </c>
@@ -6131,7 +6130,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="67" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>78</v>
       </c>
@@ -6157,7 +6156,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="68" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>79</v>
       </c>
@@ -6183,7 +6182,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="69" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>80</v>
       </c>
@@ -6209,7 +6208,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="70" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>81</v>
       </c>
@@ -6235,7 +6234,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="71" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>82</v>
       </c>
@@ -6261,7 +6260,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="72" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>83</v>
       </c>
@@ -6287,7 +6286,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="73" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>84</v>
       </c>
@@ -6313,7 +6312,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="74" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:19">
       <c r="A74">
         <v>85</v>
       </c>
@@ -6339,7 +6338,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="75" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:19">
       <c r="A75">
         <v>86</v>
       </c>
@@ -6365,7 +6364,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="76" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:19">
       <c r="A76">
         <v>87</v>
       </c>
@@ -6391,7 +6390,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="77" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:19">
       <c r="A77">
         <v>88</v>
       </c>
@@ -6417,7 +6416,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="78" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:19">
       <c r="A78">
         <v>89</v>
       </c>
@@ -6443,7 +6442,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="79" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>90</v>
       </c>
@@ -6469,7 +6468,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="80" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>91</v>
       </c>
@@ -6495,7 +6494,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="81" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:28">
       <c r="A81">
         <v>92</v>
       </c>
@@ -6524,7 +6523,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="82" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:28">
       <c r="A82">
         <v>93</v>
       </c>
@@ -6550,7 +6549,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="83" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:28">
       <c r="A83">
         <v>94</v>
       </c>
@@ -6576,7 +6575,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="84" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:28">
       <c r="A84">
         <v>95</v>
       </c>
@@ -6602,7 +6601,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="85" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:28">
       <c r="A85">
         <v>96</v>
       </c>
@@ -6628,7 +6627,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="86" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:28">
       <c r="A86">
         <v>97</v>
       </c>
@@ -6651,7 +6650,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="87" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:28">
       <c r="A87">
         <v>98</v>
       </c>
@@ -6677,7 +6676,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="88" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:28">
       <c r="A88">
         <v>99</v>
       </c>
@@ -6700,7 +6699,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="89" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:28">
       <c r="A89">
         <v>100</v>
       </c>
@@ -6726,7 +6725,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="90" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:28">
       <c r="A90">
         <v>101</v>
       </c>
@@ -6752,7 +6751,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="91" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:28">
       <c r="A91">
         <v>102</v>
       </c>
@@ -6781,7 +6780,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="92" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:28">
       <c r="A92">
         <v>103</v>
       </c>
@@ -6807,7 +6806,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="93" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:28">
       <c r="A93">
         <v>104</v>
       </c>
@@ -6833,7 +6832,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="94" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:28">
       <c r="A94">
         <v>105</v>
       </c>
@@ -6881,7 +6880,7 @@
       <c r="AA94" s="1"/>
       <c r="AB94" s="1"/>
     </row>
-    <row r="95" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:28">
       <c r="A95">
         <v>106</v>
       </c>
@@ -6927,7 +6926,7 @@
       <c r="AA95" s="1"/>
       <c r="AB95" s="1"/>
     </row>
-    <row r="96" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:28">
       <c r="A96">
         <v>107</v>
       </c>
@@ -6973,7 +6972,7 @@
       <c r="AA96" s="1"/>
       <c r="AB96" s="1"/>
     </row>
-    <row r="97" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:28">
       <c r="A97">
         <v>108</v>
       </c>
@@ -7019,7 +7018,7 @@
       <c r="AA97" s="1"/>
       <c r="AB97" s="1"/>
     </row>
-    <row r="98" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:28">
       <c r="A98">
         <v>109</v>
       </c>
@@ -7065,7 +7064,7 @@
       <c r="AA98" s="1"/>
       <c r="AB98" s="1"/>
     </row>
-    <row r="99" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:28">
       <c r="A99">
         <v>110</v>
       </c>
@@ -7111,7 +7110,7 @@
       <c r="AA99" s="1"/>
       <c r="AB99" s="1"/>
     </row>
-    <row r="100" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:28">
       <c r="A100">
         <v>111</v>
       </c>
@@ -7157,7 +7156,7 @@
       <c r="AA100" s="1"/>
       <c r="AB100" s="1"/>
     </row>
-    <row r="101" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:28">
       <c r="A101">
         <v>112</v>
       </c>
@@ -7203,7 +7202,7 @@
       <c r="AA101" s="1"/>
       <c r="AB101" s="1"/>
     </row>
-    <row r="102" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:28">
       <c r="A102">
         <v>113</v>
       </c>
@@ -7249,7 +7248,7 @@
       <c r="AA102" s="1"/>
       <c r="AB102" s="1"/>
     </row>
-    <row r="103" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:28">
       <c r="A103">
         <v>114</v>
       </c>
@@ -7295,7 +7294,7 @@
       <c r="AA103" s="1"/>
       <c r="AB103" s="1"/>
     </row>
-    <row r="104" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:28">
       <c r="A104">
         <v>115</v>
       </c>
@@ -7341,7 +7340,7 @@
       <c r="AA104" s="1"/>
       <c r="AB104" s="1"/>
     </row>
-    <row r="105" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:28">
       <c r="A105">
         <v>116</v>
       </c>
@@ -7387,7 +7386,7 @@
       <c r="AA105" s="1"/>
       <c r="AB105" s="1"/>
     </row>
-    <row r="106" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:28">
       <c r="A106">
         <v>117</v>
       </c>
@@ -7433,7 +7432,7 @@
       <c r="AA106" s="1"/>
       <c r="AB106" s="1"/>
     </row>
-    <row r="107" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:28">
       <c r="A107">
         <v>118</v>
       </c>
@@ -7477,7 +7476,7 @@
       <c r="AA107" s="1"/>
       <c r="AB107" s="1"/>
     </row>
-    <row r="108" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:28">
       <c r="A108">
         <v>119</v>
       </c>
@@ -7523,7 +7522,7 @@
       <c r="AA108" s="1"/>
       <c r="AB108" s="1"/>
     </row>
-    <row r="109" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:28">
       <c r="A109">
         <v>120</v>
       </c>
@@ -7569,7 +7568,7 @@
       <c r="AA109" s="1"/>
       <c r="AB109" s="1"/>
     </row>
-    <row r="110" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:28">
       <c r="A110">
         <v>121</v>
       </c>
@@ -7615,7 +7614,7 @@
       <c r="AA110" s="1"/>
       <c r="AB110" s="1"/>
     </row>
-    <row r="111" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:28">
       <c r="A111">
         <v>122</v>
       </c>
@@ -7661,7 +7660,7 @@
       <c r="AA111" s="1"/>
       <c r="AB111" s="1"/>
     </row>
-    <row r="112" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:28">
       <c r="A112">
         <v>123</v>
       </c>
@@ -7707,7 +7706,7 @@
       <c r="AA112" s="1"/>
       <c r="AB112" s="1"/>
     </row>
-    <row r="113" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:28">
       <c r="A113">
         <v>124</v>
       </c>
@@ -7753,7 +7752,7 @@
       <c r="AA113" s="1"/>
       <c r="AB113" s="1"/>
     </row>
-    <row r="114" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:28">
       <c r="A114">
         <v>125</v>
       </c>
@@ -7799,7 +7798,7 @@
       <c r="AA114" s="1"/>
       <c r="AB114" s="1"/>
     </row>
-    <row r="115" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:28">
       <c r="A115">
         <v>126</v>
       </c>
@@ -7845,7 +7844,7 @@
       <c r="AA115" s="1"/>
       <c r="AB115" s="1"/>
     </row>
-    <row r="116" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:28">
       <c r="A116">
         <v>127</v>
       </c>
@@ -7891,7 +7890,7 @@
       <c r="AA116" s="1"/>
       <c r="AB116" s="1"/>
     </row>
-    <row r="117" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:28">
       <c r="A117">
         <v>128</v>
       </c>
@@ -7939,7 +7938,7 @@
       <c r="AA117" s="1"/>
       <c r="AB117" s="1"/>
     </row>
-    <row r="118" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:28">
       <c r="A118">
         <v>129</v>
       </c>
@@ -7985,7 +7984,7 @@
       <c r="AA118" s="1"/>
       <c r="AB118" s="1"/>
     </row>
-    <row r="119" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:28">
       <c r="A119">
         <v>130</v>
       </c>
@@ -8033,7 +8032,7 @@
       <c r="AA119" s="1"/>
       <c r="AB119" s="1"/>
     </row>
-    <row r="120" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:28">
       <c r="A120">
         <v>131</v>
       </c>
@@ -8079,7 +8078,7 @@
       <c r="AA120" s="1"/>
       <c r="AB120" s="1"/>
     </row>
-    <row r="121" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:28">
       <c r="A121">
         <v>132</v>
       </c>
@@ -8125,7 +8124,7 @@
       <c r="AA121" s="1"/>
       <c r="AB121" s="1"/>
     </row>
-    <row r="122" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:28">
       <c r="A122">
         <v>133</v>
       </c>
@@ -8171,7 +8170,7 @@
       <c r="AA122" s="1"/>
       <c r="AB122" s="1"/>
     </row>
-    <row r="123" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:28">
       <c r="A123">
         <v>134</v>
       </c>
@@ -8217,7 +8216,7 @@
       <c r="AA123" s="1"/>
       <c r="AB123" s="1"/>
     </row>
-    <row r="124" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:28">
       <c r="A124">
         <v>135</v>
       </c>
@@ -8263,7 +8262,7 @@
       <c r="AA124" s="1"/>
       <c r="AB124" s="1"/>
     </row>
-    <row r="125" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:28">
       <c r="A125">
         <v>136</v>
       </c>
@@ -8309,7 +8308,7 @@
       <c r="AA125" s="1"/>
       <c r="AB125" s="1"/>
     </row>
-    <row r="126" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:28">
       <c r="A126">
         <v>137</v>
       </c>
@@ -8355,7 +8354,7 @@
       <c r="AA126" s="1"/>
       <c r="AB126" s="1"/>
     </row>
-    <row r="127" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:28">
       <c r="A127">
         <v>138</v>
       </c>
@@ -8401,7 +8400,7 @@
       <c r="AA127" s="1"/>
       <c r="AB127" s="1"/>
     </row>
-    <row r="128" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:28">
       <c r="A128">
         <v>139</v>
       </c>
@@ -8447,7 +8446,7 @@
       <c r="AA128" s="1"/>
       <c r="AB128" s="1"/>
     </row>
-    <row r="129" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:28">
       <c r="A129">
         <v>140</v>
       </c>
@@ -8493,7 +8492,7 @@
       <c r="AA129" s="1"/>
       <c r="AB129" s="1"/>
     </row>
-    <row r="130" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:28">
       <c r="A130">
         <v>141</v>
       </c>
@@ -8539,7 +8538,7 @@
       <c r="AA130" s="1"/>
       <c r="AB130" s="1"/>
     </row>
-    <row r="131" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:28">
       <c r="A131">
         <v>142</v>
       </c>
@@ -8585,7 +8584,7 @@
       <c r="AA131" s="1"/>
       <c r="AB131" s="1"/>
     </row>
-    <row r="132" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:28">
       <c r="A132">
         <v>143</v>
       </c>
@@ -8631,7 +8630,7 @@
       <c r="AA132" s="1"/>
       <c r="AB132" s="1"/>
     </row>
-    <row r="133" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:28">
       <c r="A133">
         <v>144</v>
       </c>
@@ -8677,7 +8676,7 @@
       <c r="AA133" s="1"/>
       <c r="AB133" s="1"/>
     </row>
-    <row r="134" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:28">
       <c r="A134">
         <v>145</v>
       </c>
@@ -8723,7 +8722,7 @@
       <c r="AA134" s="1"/>
       <c r="AB134" s="1"/>
     </row>
-    <row r="135" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:28">
       <c r="A135">
         <v>146</v>
       </c>
@@ -8769,7 +8768,7 @@
       <c r="AA135" s="1"/>
       <c r="AB135" s="1"/>
     </row>
-    <row r="136" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:28">
       <c r="A136">
         <v>147</v>
       </c>
@@ -8815,7 +8814,7 @@
       <c r="AA136" s="1"/>
       <c r="AB136" s="1"/>
     </row>
-    <row r="137" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:28">
       <c r="A137">
         <v>148</v>
       </c>
@@ -8863,7 +8862,7 @@
       <c r="AA137" s="1"/>
       <c r="AB137" s="1"/>
     </row>
-    <row r="138" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:28">
       <c r="A138">
         <v>149</v>
       </c>
@@ -8909,7 +8908,7 @@
       <c r="AA138" s="1"/>
       <c r="AB138" s="1"/>
     </row>
-    <row r="139" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:28">
       <c r="A139">
         <v>150</v>
       </c>
@@ -8955,7 +8954,7 @@
       <c r="AA139" s="1"/>
       <c r="AB139" s="1"/>
     </row>
-    <row r="140" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:28">
       <c r="A140">
         <v>151</v>
       </c>
@@ -9001,7 +9000,7 @@
       <c r="AA140" s="1"/>
       <c r="AB140" s="1"/>
     </row>
-    <row r="141" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:28">
       <c r="A141">
         <v>152</v>
       </c>
@@ -9047,7 +9046,7 @@
       <c r="AA141" s="1"/>
       <c r="AB141" s="1"/>
     </row>
-    <row r="142" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:28">
       <c r="A142">
         <v>153</v>
       </c>
@@ -9093,7 +9092,7 @@
       <c r="AA142" s="1"/>
       <c r="AB142" s="1"/>
     </row>
-    <row r="143" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:28">
       <c r="A143">
         <v>154</v>
       </c>
@@ -9139,7 +9138,7 @@
       <c r="AA143" s="1"/>
       <c r="AB143" s="1"/>
     </row>
-    <row r="144" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:28">
       <c r="A144">
         <v>155</v>
       </c>
@@ -9185,7 +9184,7 @@
       <c r="AA144" s="1"/>
       <c r="AB144" s="1"/>
     </row>
-    <row r="145" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:28">
       <c r="A145">
         <v>156</v>
       </c>
@@ -9233,7 +9232,7 @@
       <c r="AA145" s="1"/>
       <c r="AB145" s="1"/>
     </row>
-    <row r="146" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:28">
       <c r="A146">
         <v>157</v>
       </c>
@@ -9279,7 +9278,7 @@
       <c r="AA146" s="1"/>
       <c r="AB146" s="1"/>
     </row>
-    <row r="147" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:28">
       <c r="A147">
         <v>158</v>
       </c>
@@ -9325,7 +9324,7 @@
       <c r="AA147" s="1"/>
       <c r="AB147" s="1"/>
     </row>
-    <row r="148" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:28">
       <c r="A148">
         <v>159</v>
       </c>
@@ -9373,7 +9372,7 @@
       <c r="AA148" s="1"/>
       <c r="AB148" s="1"/>
     </row>
-    <row r="149" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:28">
       <c r="A149">
         <v>160</v>
       </c>
@@ -9421,7 +9420,7 @@
       <c r="AA149" s="1"/>
       <c r="AB149" s="1"/>
     </row>
-    <row r="150" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:28">
       <c r="A150">
         <v>161</v>
       </c>
@@ -9467,7 +9466,7 @@
       <c r="AA150" s="1"/>
       <c r="AB150" s="1"/>
     </row>
-    <row r="151" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:28">
       <c r="A151">
         <v>162</v>
       </c>
@@ -9515,7 +9514,7 @@
       <c r="AA151" s="1"/>
       <c r="AB151" s="1"/>
     </row>
-    <row r="152" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:28">
       <c r="A152">
         <v>163</v>
       </c>
@@ -9563,7 +9562,7 @@
       <c r="AA152" s="1"/>
       <c r="AB152" s="1"/>
     </row>
-    <row r="153" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:28">
       <c r="A153">
         <v>164</v>
       </c>
@@ -9609,7 +9608,7 @@
       <c r="AA153" s="1"/>
       <c r="AB153" s="1"/>
     </row>
-    <row r="154" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:28">
       <c r="A154">
         <v>165</v>
       </c>
@@ -9657,7 +9656,7 @@
       <c r="AA154" s="1"/>
       <c r="AB154" s="1"/>
     </row>
-    <row r="155" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:28">
       <c r="A155">
         <v>166</v>
       </c>
@@ -9705,7 +9704,7 @@
       <c r="AA155" s="1"/>
       <c r="AB155" s="1"/>
     </row>
-    <row r="156" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:28">
       <c r="A156">
         <v>167</v>
       </c>
@@ -9753,7 +9752,7 @@
       <c r="AA156" s="1"/>
       <c r="AB156" s="1"/>
     </row>
-    <row r="157" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:28">
       <c r="A157">
         <v>168</v>
       </c>
@@ -9801,7 +9800,7 @@
       <c r="AA157" s="1"/>
       <c r="AB157" s="1"/>
     </row>
-    <row r="158" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:28">
       <c r="A158">
         <v>169</v>
       </c>
@@ -9849,7 +9848,7 @@
       <c r="AA158" s="1"/>
       <c r="AB158" s="1"/>
     </row>
-    <row r="159" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:28">
       <c r="A159">
         <v>170</v>
       </c>
@@ -9897,7 +9896,7 @@
       <c r="AA159" s="1"/>
       <c r="AB159" s="1"/>
     </row>
-    <row r="160" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:28">
       <c r="A160">
         <v>171</v>
       </c>
@@ -9945,7 +9944,7 @@
       <c r="AA160" s="1"/>
       <c r="AB160" s="1"/>
     </row>
-    <row r="161" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:28">
       <c r="A161">
         <v>172</v>
       </c>
@@ -9993,7 +9992,7 @@
       <c r="AA161" s="1"/>
       <c r="AB161" s="1"/>
     </row>
-    <row r="162" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:28">
       <c r="A162">
         <v>173</v>
       </c>
@@ -10041,7 +10040,7 @@
       <c r="AA162" s="1"/>
       <c r="AB162" s="1"/>
     </row>
-    <row r="163" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:28">
       <c r="A163">
         <v>174</v>
       </c>
@@ -10089,7 +10088,7 @@
       <c r="AA163" s="1"/>
       <c r="AB163" s="1"/>
     </row>
-    <row r="164" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:28">
       <c r="A164">
         <v>175</v>
       </c>
@@ -10137,7 +10136,7 @@
       <c r="AA164" s="1"/>
       <c r="AB164" s="1"/>
     </row>
-    <row r="165" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:28">
       <c r="A165">
         <v>176</v>
       </c>
@@ -10185,7 +10184,7 @@
       <c r="AA165" s="1"/>
       <c r="AB165" s="1"/>
     </row>
-    <row r="166" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:28">
       <c r="A166">
         <v>177</v>
       </c>
@@ -10233,7 +10232,7 @@
       <c r="AA166" s="1"/>
       <c r="AB166" s="1"/>
     </row>
-    <row r="167" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:28">
       <c r="A167">
         <v>178</v>
       </c>
@@ -10281,7 +10280,7 @@
       <c r="AA167" s="1"/>
       <c r="AB167" s="1"/>
     </row>
-    <row r="168" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:28">
       <c r="A168">
         <v>179</v>
       </c>
@@ -10329,7 +10328,7 @@
       <c r="AA168" s="1"/>
       <c r="AB168" s="1"/>
     </row>
-    <row r="169" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:28">
       <c r="A169">
         <v>180</v>
       </c>
@@ -10377,7 +10376,7 @@
       <c r="AA169" s="1"/>
       <c r="AB169" s="1"/>
     </row>
-    <row r="170" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:28">
       <c r="A170">
         <v>181</v>
       </c>
@@ -10425,7 +10424,7 @@
       <c r="AA170" s="1"/>
       <c r="AB170" s="1"/>
     </row>
-    <row r="171" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:28">
       <c r="A171">
         <v>182</v>
       </c>
@@ -10473,7 +10472,7 @@
       <c r="AA171" s="1"/>
       <c r="AB171" s="1"/>
     </row>
-    <row r="172" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:28">
       <c r="A172">
         <v>183</v>
       </c>
@@ -10521,7 +10520,7 @@
       <c r="AA172" s="1"/>
       <c r="AB172" s="1"/>
     </row>
-    <row r="173" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:28">
       <c r="A173">
         <v>184</v>
       </c>
@@ -10567,7 +10566,7 @@
       <c r="AA173" s="1"/>
       <c r="AB173" s="1"/>
     </row>
-    <row r="174" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:28">
       <c r="A174">
         <v>185</v>
       </c>
@@ -10615,7 +10614,7 @@
       <c r="AA174" s="1"/>
       <c r="AB174" s="1"/>
     </row>
-    <row r="175" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:28">
       <c r="A175">
         <v>186</v>
       </c>
@@ -10663,7 +10662,7 @@
       <c r="AA175" s="1"/>
       <c r="AB175" s="1"/>
     </row>
-    <row r="176" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:28">
       <c r="A176">
         <v>187</v>
       </c>
@@ -10711,7 +10710,7 @@
       <c r="AA176" s="1"/>
       <c r="AB176" s="1"/>
     </row>
-    <row r="177" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:28">
       <c r="A177">
         <v>188</v>
       </c>
@@ -10759,7 +10758,7 @@
       <c r="AA177" s="1"/>
       <c r="AB177" s="1"/>
     </row>
-    <row r="178" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:28">
       <c r="A178">
         <v>189</v>
       </c>
@@ -10807,7 +10806,7 @@
       <c r="AA178" s="1"/>
       <c r="AB178" s="1"/>
     </row>
-    <row r="179" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:28">
       <c r="A179">
         <v>190</v>
       </c>
@@ -10855,7 +10854,7 @@
       <c r="AA179" s="1"/>
       <c r="AB179" s="1"/>
     </row>
-    <row r="180" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:28">
       <c r="A180">
         <v>191</v>
       </c>
@@ -10903,7 +10902,7 @@
       <c r="AA180" s="1"/>
       <c r="AB180" s="1"/>
     </row>
-    <row r="181" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:28">
       <c r="A181">
         <v>192</v>
       </c>
@@ -10951,7 +10950,7 @@
       <c r="AA181" s="1"/>
       <c r="AB181" s="1"/>
     </row>
-    <row r="182" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:28">
       <c r="A182">
         <v>193</v>
       </c>
@@ -10999,7 +10998,7 @@
       <c r="AA182" s="1"/>
       <c r="AB182" s="1"/>
     </row>
-    <row r="183" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:28">
       <c r="A183">
         <v>194</v>
       </c>
@@ -11047,7 +11046,7 @@
       <c r="AA183" s="1"/>
       <c r="AB183" s="1"/>
     </row>
-    <row r="184" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:28">
       <c r="A184">
         <v>195</v>
       </c>
@@ -11095,7 +11094,7 @@
       <c r="AA184" s="1"/>
       <c r="AB184" s="1"/>
     </row>
-    <row r="185" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:28">
       <c r="A185">
         <v>196</v>
       </c>
@@ -11143,7 +11142,7 @@
       <c r="AA185" s="1"/>
       <c r="AB185" s="1"/>
     </row>
-    <row r="186" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:28">
       <c r="A186">
         <v>197</v>
       </c>
@@ -11191,7 +11190,7 @@
       <c r="AA186" s="1"/>
       <c r="AB186" s="1"/>
     </row>
-    <row r="187" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:28">
       <c r="A187">
         <v>198</v>
       </c>
@@ -11239,7 +11238,7 @@
       <c r="AA187" s="1"/>
       <c r="AB187" s="1"/>
     </row>
-    <row r="188" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:28">
       <c r="A188">
         <v>199</v>
       </c>
@@ -11287,7 +11286,7 @@
       <c r="AA188" s="1"/>
       <c r="AB188" s="1"/>
     </row>
-    <row r="189" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:28">
       <c r="A189">
         <v>200</v>
       </c>
@@ -11335,7 +11334,7 @@
       <c r="AA189" s="1"/>
       <c r="AB189" s="1"/>
     </row>
-    <row r="190" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:28">
       <c r="A190">
         <v>201</v>
       </c>
@@ -11383,7 +11382,7 @@
       <c r="AA190" s="1"/>
       <c r="AB190" s="1"/>
     </row>
-    <row r="191" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:28">
       <c r="A191">
         <v>202</v>
       </c>
@@ -11431,7 +11430,7 @@
       <c r="AA191" s="1"/>
       <c r="AB191" s="1"/>
     </row>
-    <row r="192" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:28">
       <c r="A192">
         <v>203</v>
       </c>
@@ -11479,7 +11478,7 @@
       <c r="AA192" s="1"/>
       <c r="AB192" s="1"/>
     </row>
-    <row r="193" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:28">
       <c r="A193">
         <v>204</v>
       </c>
@@ -11527,7 +11526,7 @@
       <c r="AA193" s="1"/>
       <c r="AB193" s="1"/>
     </row>
-    <row r="194" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:28">
       <c r="A194">
         <v>205</v>
       </c>
@@ -11575,7 +11574,7 @@
       <c r="AA194" s="1"/>
       <c r="AB194" s="1"/>
     </row>
-    <row r="195" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:28">
       <c r="A195">
         <v>206</v>
       </c>
@@ -11623,7 +11622,7 @@
       <c r="AA195" s="1"/>
       <c r="AB195" s="1"/>
     </row>
-    <row r="196" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:28">
       <c r="A196">
         <v>207</v>
       </c>
@@ -11669,7 +11668,7 @@
       <c r="AA196" s="1"/>
       <c r="AB196" s="1"/>
     </row>
-    <row r="197" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:28">
       <c r="A197">
         <v>208</v>
       </c>
@@ -11717,7 +11716,7 @@
       <c r="AA197" s="1"/>
       <c r="AB197" s="1"/>
     </row>
-    <row r="198" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:28">
       <c r="A198">
         <v>209</v>
       </c>
@@ -11763,7 +11762,7 @@
       <c r="AA198" s="1"/>
       <c r="AB198" s="1"/>
     </row>
-    <row r="199" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:28">
       <c r="A199">
         <v>210</v>
       </c>
@@ -11811,7 +11810,7 @@
       <c r="AA199" s="1"/>
       <c r="AB199" s="1"/>
     </row>
-    <row r="200" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:28">
       <c r="A200">
         <v>211</v>
       </c>
@@ -11859,7 +11858,7 @@
       <c r="AA200" s="1"/>
       <c r="AB200" s="1"/>
     </row>
-    <row r="201" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:28">
       <c r="A201">
         <v>212</v>
       </c>
@@ -11907,7 +11906,7 @@
       <c r="AA201" s="1"/>
       <c r="AB201" s="1"/>
     </row>
-    <row r="202" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:28">
       <c r="A202">
         <v>213</v>
       </c>
@@ -11953,7 +11952,7 @@
       <c r="AA202" s="1"/>
       <c r="AB202" s="1"/>
     </row>
-    <row r="203" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:28">
       <c r="A203">
         <v>214</v>
       </c>
@@ -11999,7 +11998,7 @@
       <c r="AA203" s="1"/>
       <c r="AB203" s="1"/>
     </row>
-    <row r="204" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:28">
       <c r="A204">
         <v>215</v>
       </c>
@@ -12047,7 +12046,7 @@
       <c r="AA204" s="1"/>
       <c r="AB204" s="1"/>
     </row>
-    <row r="205" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:28">
       <c r="A205">
         <v>216</v>
       </c>
@@ -12095,7 +12094,7 @@
       <c r="AA205" s="1"/>
       <c r="AB205" s="1"/>
     </row>
-    <row r="206" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:28">
       <c r="A206">
         <v>217</v>
       </c>
@@ -12143,7 +12142,7 @@
       <c r="AA206" s="1"/>
       <c r="AB206" s="1"/>
     </row>
-    <row r="207" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:28">
       <c r="A207">
         <v>218</v>
       </c>
@@ -12191,7 +12190,7 @@
       <c r="AA207" s="1"/>
       <c r="AB207" s="1"/>
     </row>
-    <row r="208" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:28">
       <c r="A208">
         <v>219</v>
       </c>
@@ -12237,7 +12236,7 @@
       <c r="AA208" s="1"/>
       <c r="AB208" s="1"/>
     </row>
-    <row r="209" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:28">
       <c r="A209">
         <v>220</v>
       </c>
@@ -12283,7 +12282,7 @@
       <c r="AA209" s="1"/>
       <c r="AB209" s="1"/>
     </row>
-    <row r="210" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:28">
       <c r="A210">
         <v>221</v>
       </c>
@@ -12331,7 +12330,7 @@
       <c r="AA210" s="1"/>
       <c r="AB210" s="1"/>
     </row>
-    <row r="211" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:28">
       <c r="A211">
         <v>222</v>
       </c>
@@ -12379,7 +12378,7 @@
       <c r="AA211" s="1"/>
       <c r="AB211" s="1"/>
     </row>
-    <row r="212" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:28">
       <c r="A212">
         <v>223</v>
       </c>
@@ -12425,7 +12424,7 @@
       <c r="AA212" s="1"/>
       <c r="AB212" s="1"/>
     </row>
-    <row r="213" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:28">
       <c r="A213">
         <v>224</v>
       </c>
@@ -12473,7 +12472,7 @@
       <c r="AA213" s="1"/>
       <c r="AB213" s="1"/>
     </row>
-    <row r="214" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:28">
       <c r="A214">
         <v>225</v>
       </c>
@@ -12521,7 +12520,7 @@
       <c r="AA214" s="1"/>
       <c r="AB214" s="1"/>
     </row>
-    <row r="215" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:28">
       <c r="A215">
         <v>226</v>
       </c>
@@ -12567,7 +12566,7 @@
       <c r="AA215" s="1"/>
       <c r="AB215" s="1"/>
     </row>
-    <row r="216" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:28">
       <c r="A216">
         <v>227</v>
       </c>
@@ -12613,7 +12612,7 @@
       <c r="AA216" s="1"/>
       <c r="AB216" s="1"/>
     </row>
-    <row r="217" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:28">
       <c r="A217">
         <v>228</v>
       </c>
@@ -12659,7 +12658,7 @@
       <c r="AA217" s="1"/>
       <c r="AB217" s="1"/>
     </row>
-    <row r="218" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:28">
       <c r="A218">
         <v>229</v>
       </c>
@@ -12707,7 +12706,7 @@
       <c r="AA218" s="1"/>
       <c r="AB218" s="1"/>
     </row>
-    <row r="219" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:28">
       <c r="A219">
         <v>230</v>
       </c>
@@ -12753,7 +12752,7 @@
       <c r="AA219" s="1"/>
       <c r="AB219" s="1"/>
     </row>
-    <row r="220" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:28">
       <c r="A220">
         <v>231</v>
       </c>
@@ -12801,7 +12800,7 @@
       <c r="AA220" s="1"/>
       <c r="AB220" s="1"/>
     </row>
-    <row r="221" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:28">
       <c r="A221">
         <v>232</v>
       </c>
@@ -12849,7 +12848,7 @@
       <c r="AA221" s="1"/>
       <c r="AB221" s="1"/>
     </row>
-    <row r="222" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:28">
       <c r="A222">
         <v>233</v>
       </c>
@@ -12897,7 +12896,7 @@
       <c r="AA222" s="1"/>
       <c r="AB222" s="1"/>
     </row>
-    <row r="223" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:28">
       <c r="A223">
         <v>234</v>
       </c>
@@ -12943,7 +12942,7 @@
       <c r="AA223" s="1"/>
       <c r="AB223" s="1"/>
     </row>
-    <row r="224" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:28">
       <c r="A224">
         <v>235</v>
       </c>
@@ -12991,7 +12990,7 @@
       <c r="AA224" s="1"/>
       <c r="AB224" s="1"/>
     </row>
-    <row r="225" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:28">
       <c r="A225">
         <v>236</v>
       </c>
@@ -13037,7 +13036,7 @@
       <c r="AA225" s="1"/>
       <c r="AB225" s="1"/>
     </row>
-    <row r="226" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:28">
       <c r="A226">
         <v>237</v>
       </c>
@@ -13083,7 +13082,7 @@
       <c r="AA226" s="1"/>
       <c r="AB226" s="1"/>
     </row>
-    <row r="227" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:28">
       <c r="A227">
         <v>238</v>
       </c>
@@ -13129,7 +13128,7 @@
       <c r="AA227" s="1"/>
       <c r="AB227" s="1"/>
     </row>
-    <row r="228" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:28">
       <c r="A228">
         <v>239</v>
       </c>
@@ -13175,7 +13174,7 @@
       <c r="AA228" s="1"/>
       <c r="AB228" s="1"/>
     </row>
-    <row r="229" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:28">
       <c r="A229">
         <v>240</v>
       </c>
@@ -13223,7 +13222,7 @@
       <c r="AA229" s="1"/>
       <c r="AB229" s="1"/>
     </row>
-    <row r="230" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:28">
       <c r="A230">
         <v>241</v>
       </c>
@@ -13269,7 +13268,7 @@
       <c r="AA230" s="1"/>
       <c r="AB230" s="1"/>
     </row>
-    <row r="231" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:28">
       <c r="A231">
         <v>242</v>
       </c>
@@ -13315,7 +13314,7 @@
       <c r="AA231" s="1"/>
       <c r="AB231" s="1"/>
     </row>
-    <row r="232" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:28">
       <c r="A232">
         <v>243</v>
       </c>
@@ -13361,7 +13360,7 @@
       <c r="AA232" s="1"/>
       <c r="AB232" s="1"/>
     </row>
-    <row r="233" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:28">
       <c r="A233">
         <v>244</v>
       </c>
@@ -13407,7 +13406,7 @@
       <c r="AA233" s="1"/>
       <c r="AB233" s="1"/>
     </row>
-    <row r="234" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:28">
       <c r="A234">
         <v>245</v>
       </c>
@@ -13453,7 +13452,7 @@
       <c r="AA234" s="1"/>
       <c r="AB234" s="1"/>
     </row>
-    <row r="235" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:28">
       <c r="A235">
         <v>246</v>
       </c>
@@ -13499,7 +13498,7 @@
       <c r="AA235" s="1"/>
       <c r="AB235" s="1"/>
     </row>
-    <row r="236" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:28">
       <c r="A236">
         <v>247</v>
       </c>
@@ -13545,7 +13544,7 @@
       <c r="AA236" s="1"/>
       <c r="AB236" s="1"/>
     </row>
-    <row r="237" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:28">
       <c r="A237">
         <v>248</v>
       </c>
@@ -13591,7 +13590,7 @@
       <c r="AA237" s="1"/>
       <c r="AB237" s="1"/>
     </row>
-    <row r="238" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:28">
       <c r="A238">
         <v>249</v>
       </c>
@@ -13637,7 +13636,7 @@
       <c r="AA238" s="1"/>
       <c r="AB238" s="1"/>
     </row>
-    <row r="239" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:28">
       <c r="A239">
         <v>250</v>
       </c>
@@ -13683,7 +13682,7 @@
       <c r="AA239" s="1"/>
       <c r="AB239" s="1"/>
     </row>
-    <row r="240" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:28">
       <c r="A240">
         <v>251</v>
       </c>
@@ -13729,7 +13728,7 @@
       <c r="AA240" s="1"/>
       <c r="AB240" s="1"/>
     </row>
-    <row r="241" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:28">
       <c r="A241">
         <v>252</v>
       </c>
@@ -13777,7 +13776,7 @@
       <c r="AA241" s="1"/>
       <c r="AB241" s="1"/>
     </row>
-    <row r="242" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:28">
       <c r="A242">
         <v>253</v>
       </c>
@@ -13823,7 +13822,7 @@
       <c r="AA242" s="1"/>
       <c r="AB242" s="1"/>
     </row>
-    <row r="243" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:28">
       <c r="A243">
         <v>254</v>
       </c>
@@ -13871,7 +13870,7 @@
       <c r="AA243" s="1"/>
       <c r="AB243" s="1"/>
     </row>
-    <row r="244" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:28">
       <c r="A244">
         <v>255</v>
       </c>
@@ -13919,7 +13918,7 @@
       <c r="AA244" s="1"/>
       <c r="AB244" s="1"/>
     </row>
-    <row r="245" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:28">
       <c r="A245">
         <v>256</v>
       </c>
@@ -13967,7 +13966,7 @@
       <c r="AA245" s="1"/>
       <c r="AB245" s="1"/>
     </row>
-    <row r="246" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:28">
       <c r="A246">
         <v>257</v>
       </c>
@@ -14013,7 +14012,7 @@
       <c r="AA246" s="1"/>
       <c r="AB246" s="1"/>
     </row>
-    <row r="247" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:28">
       <c r="A247">
         <v>258</v>
       </c>
@@ -14059,7 +14058,7 @@
       <c r="AA247" s="1"/>
       <c r="AB247" s="1"/>
     </row>
-    <row r="248" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:28">
       <c r="A248">
         <v>259</v>
       </c>
@@ -14105,7 +14104,7 @@
       <c r="AA248" s="1"/>
       <c r="AB248" s="1"/>
     </row>
-    <row r="249" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:28">
       <c r="A249">
         <v>260</v>
       </c>
@@ -14151,7 +14150,7 @@
       <c r="AA249" s="1"/>
       <c r="AB249" s="1"/>
     </row>
-    <row r="250" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:28">
       <c r="A250">
         <v>261</v>
       </c>
@@ -14197,7 +14196,7 @@
       <c r="AA250" s="1"/>
       <c r="AB250" s="1"/>
     </row>
-    <row r="251" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:28">
       <c r="A251">
         <v>262</v>
       </c>
@@ -14243,7 +14242,7 @@
       <c r="AA251" s="1"/>
       <c r="AB251" s="1"/>
     </row>
-    <row r="252" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:28">
       <c r="A252">
         <v>263</v>
       </c>
@@ -14291,7 +14290,7 @@
       <c r="AA252" s="1"/>
       <c r="AB252" s="1"/>
     </row>
-    <row r="253" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:28">
       <c r="A253">
         <v>264</v>
       </c>
@@ -14337,7 +14336,7 @@
       <c r="AA253" s="1"/>
       <c r="AB253" s="1"/>
     </row>
-    <row r="254" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:28">
       <c r="A254">
         <v>265</v>
       </c>
@@ -14383,7 +14382,7 @@
       <c r="AA254" s="1"/>
       <c r="AB254" s="1"/>
     </row>
-    <row r="255" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:28">
       <c r="A255">
         <v>266</v>
       </c>
@@ -14429,7 +14428,7 @@
       <c r="AA255" s="1"/>
       <c r="AB255" s="1"/>
     </row>
-    <row r="256" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:28">
       <c r="A256">
         <v>267</v>
       </c>
@@ -14475,7 +14474,7 @@
       <c r="AA256" s="1"/>
       <c r="AB256" s="1"/>
     </row>
-    <row r="257" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:28">
       <c r="A257">
         <v>268</v>
       </c>
@@ -14521,7 +14520,7 @@
       <c r="AA257" s="1"/>
       <c r="AB257" s="1"/>
     </row>
-    <row r="258" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:28">
       <c r="A258">
         <v>269</v>
       </c>
@@ -14569,7 +14568,7 @@
       <c r="AA258" s="1"/>
       <c r="AB258" s="1"/>
     </row>
-    <row r="259" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:28">
       <c r="A259">
         <v>270</v>
       </c>
@@ -14615,7 +14614,7 @@
       <c r="AA259" s="1"/>
       <c r="AB259" s="1"/>
     </row>
-    <row r="260" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:28">
       <c r="A260">
         <v>271</v>
       </c>
@@ -14661,7 +14660,7 @@
       <c r="AA260" s="1"/>
       <c r="AB260" s="1"/>
     </row>
-    <row r="261" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:28">
       <c r="A261">
         <v>272</v>
       </c>
@@ -14707,7 +14706,7 @@
       <c r="AA261" s="1"/>
       <c r="AB261" s="1"/>
     </row>
-    <row r="262" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:28">
       <c r="A262">
         <v>273</v>
       </c>
@@ -14753,7 +14752,7 @@
       <c r="AA262" s="1"/>
       <c r="AB262" s="1"/>
     </row>
-    <row r="263" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:28">
       <c r="A263">
         <v>274</v>
       </c>
@@ -14799,7 +14798,7 @@
       <c r="AA263" s="1"/>
       <c r="AB263" s="1"/>
     </row>
-    <row r="264" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:28">
       <c r="A264">
         <v>275</v>
       </c>
@@ -14845,7 +14844,7 @@
       <c r="AA264" s="1"/>
       <c r="AB264" s="1"/>
     </row>
-    <row r="265" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:28">
       <c r="A265">
         <v>276</v>
       </c>
@@ -14893,7 +14892,7 @@
       <c r="AA265" s="1"/>
       <c r="AB265" s="1"/>
     </row>
-    <row r="266" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:28">
       <c r="A266">
         <v>277</v>
       </c>
@@ -14939,7 +14938,7 @@
       <c r="AA266" s="1"/>
       <c r="AB266" s="1"/>
     </row>
-    <row r="267" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:28">
       <c r="A267">
         <v>278</v>
       </c>
@@ -14985,7 +14984,7 @@
       <c r="AA267" s="1"/>
       <c r="AB267" s="1"/>
     </row>
-    <row r="268" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:28">
       <c r="A268">
         <v>279</v>
       </c>
@@ -15033,7 +15032,7 @@
       <c r="AA268" s="1"/>
       <c r="AB268" s="1"/>
     </row>
-    <row r="269" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:28">
       <c r="A269">
         <v>280</v>
       </c>
@@ -15079,7 +15078,7 @@
       <c r="AA269" s="1"/>
       <c r="AB269" s="1"/>
     </row>
-    <row r="270" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:28">
       <c r="A270">
         <v>281</v>
       </c>
@@ -15127,7 +15126,7 @@
       <c r="AA270" s="1"/>
       <c r="AB270" s="1"/>
     </row>
-    <row r="271" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:28">
       <c r="A271">
         <v>282</v>
       </c>
@@ -15173,7 +15172,7 @@
       <c r="AA271" s="1"/>
       <c r="AB271" s="1"/>
     </row>
-    <row r="272" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:28">
       <c r="A272">
         <v>283</v>
       </c>
@@ -15221,7 +15220,7 @@
       <c r="AA272" s="1"/>
       <c r="AB272" s="1"/>
     </row>
-    <row r="273" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:28">
       <c r="A273">
         <v>284</v>
       </c>
@@ -15267,7 +15266,7 @@
       <c r="AA273" s="1"/>
       <c r="AB273" s="1"/>
     </row>
-    <row r="274" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:28">
       <c r="A274">
         <v>285</v>
       </c>
@@ -15315,7 +15314,7 @@
       <c r="AA274" s="1"/>
       <c r="AB274" s="1"/>
     </row>
-    <row r="275" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:28">
       <c r="A275">
         <v>286</v>
       </c>
@@ -15361,7 +15360,7 @@
       <c r="AA275" s="1"/>
       <c r="AB275" s="1"/>
     </row>
-    <row r="276" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:28">
       <c r="A276">
         <v>287</v>
       </c>
@@ -15407,7 +15406,7 @@
       <c r="AA276" s="1"/>
       <c r="AB276" s="1"/>
     </row>
-    <row r="277" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:28">
       <c r="A277">
         <v>288</v>
       </c>
@@ -15453,7 +15452,7 @@
       <c r="AA277" s="1"/>
       <c r="AB277" s="1"/>
     </row>
-    <row r="278" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:28">
       <c r="A278">
         <v>289</v>
       </c>
@@ -15501,7 +15500,7 @@
       <c r="AA278" s="1"/>
       <c r="AB278" s="1"/>
     </row>
-    <row r="279" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:28">
       <c r="A279">
         <v>290</v>
       </c>
@@ -15549,7 +15548,7 @@
       <c r="AA279" s="1"/>
       <c r="AB279" s="1"/>
     </row>
-    <row r="280" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:28">
       <c r="A280">
         <v>291</v>
       </c>
@@ -15595,7 +15594,7 @@
       <c r="AA280" s="1"/>
       <c r="AB280" s="1"/>
     </row>
-    <row r="281" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:28">
       <c r="A281">
         <v>292</v>
       </c>
@@ -15641,7 +15640,7 @@
       <c r="AA281" s="1"/>
       <c r="AB281" s="1"/>
     </row>
-    <row r="282" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:28">
       <c r="A282">
         <v>293</v>
       </c>
@@ -15687,7 +15686,7 @@
       <c r="AA282" s="1"/>
       <c r="AB282" s="1"/>
     </row>
-    <row r="283" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:28">
       <c r="A283">
         <v>294</v>
       </c>
@@ -15735,7 +15734,7 @@
       <c r="AA283" s="1"/>
       <c r="AB283" s="1"/>
     </row>
-    <row r="284" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:28">
       <c r="A284">
         <v>295</v>
       </c>
@@ -15781,7 +15780,7 @@
       <c r="AA284" s="1"/>
       <c r="AB284" s="1"/>
     </row>
-    <row r="285" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:28">
       <c r="A285">
         <v>296</v>
       </c>
@@ -15829,7 +15828,7 @@
       <c r="AA285" s="1"/>
       <c r="AB285" s="1"/>
     </row>
-    <row r="286" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:28">
       <c r="A286">
         <v>297</v>
       </c>
@@ -15875,7 +15874,7 @@
       <c r="AA286" s="1"/>
       <c r="AB286" s="1"/>
     </row>
-    <row r="287" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:28">
       <c r="A287">
         <v>298</v>
       </c>
@@ -15921,7 +15920,7 @@
       <c r="AA287" s="1"/>
       <c r="AB287" s="1"/>
     </row>
-    <row r="288" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:28">
       <c r="A288">
         <v>299</v>
       </c>
@@ -15967,7 +15966,7 @@
       <c r="AA288" s="1"/>
       <c r="AB288" s="1"/>
     </row>
-    <row r="289" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:28">
       <c r="A289">
         <v>300</v>
       </c>
@@ -16013,7 +16012,7 @@
       <c r="AA289" s="1"/>
       <c r="AB289" s="1"/>
     </row>
-    <row r="290" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:28">
       <c r="A290">
         <v>301</v>
       </c>
@@ -16059,7 +16058,7 @@
       <c r="AA290" s="1"/>
       <c r="AB290" s="1"/>
     </row>
-    <row r="291" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:28">
       <c r="A291">
         <v>302</v>
       </c>
@@ -16105,7 +16104,7 @@
       <c r="AA291" s="1"/>
       <c r="AB291" s="1"/>
     </row>
-    <row r="292" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:28">
       <c r="A292">
         <v>303</v>
       </c>
@@ -16153,7 +16152,7 @@
       <c r="AA292" s="1"/>
       <c r="AB292" s="1"/>
     </row>
-    <row r="293" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:28">
       <c r="A293">
         <v>304</v>
       </c>
@@ -16199,7 +16198,7 @@
       <c r="AA293" s="1"/>
       <c r="AB293" s="1"/>
     </row>
-    <row r="294" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:28">
       <c r="A294">
         <v>305</v>
       </c>
@@ -16247,7 +16246,7 @@
       <c r="AA294" s="1"/>
       <c r="AB294" s="1"/>
     </row>
-    <row r="295" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:28">
       <c r="A295">
         <v>306</v>
       </c>
@@ -16295,7 +16294,7 @@
       <c r="AA295" s="1"/>
       <c r="AB295" s="1"/>
     </row>
-    <row r="296" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:28">
       <c r="A296">
         <v>307</v>
       </c>
@@ -16341,7 +16340,7 @@
       <c r="AA296" s="1"/>
       <c r="AB296" s="1"/>
     </row>
-    <row r="297" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:28">
       <c r="A297">
         <v>308</v>
       </c>
@@ -16387,7 +16386,7 @@
       <c r="AA297" s="1"/>
       <c r="AB297" s="1"/>
     </row>
-    <row r="298" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:28">
       <c r="A298">
         <v>309</v>
       </c>
@@ -16433,7 +16432,7 @@
       <c r="AA298" s="1"/>
       <c r="AB298" s="1"/>
     </row>
-    <row r="299" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:28">
       <c r="A299">
         <v>310</v>
       </c>
@@ -16479,7 +16478,7 @@
       <c r="AA299" s="1"/>
       <c r="AB299" s="1"/>
     </row>
-    <row r="300" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:28">
       <c r="A300">
         <v>311</v>
       </c>
@@ -16525,7 +16524,7 @@
       <c r="AA300" s="1"/>
       <c r="AB300" s="1"/>
     </row>
-    <row r="301" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:28">
       <c r="A301">
         <v>312</v>
       </c>
@@ -16571,7 +16570,7 @@
       <c r="AA301" s="1"/>
       <c r="AB301" s="1"/>
     </row>
-    <row r="302" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:28">
       <c r="A302">
         <v>313</v>
       </c>
@@ -16619,7 +16618,7 @@
       <c r="AA302" s="1"/>
       <c r="AB302" s="1"/>
     </row>
-    <row r="303" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:28">
       <c r="A303">
         <v>314</v>
       </c>
@@ -16665,7 +16664,7 @@
       <c r="AA303" s="1"/>
       <c r="AB303" s="1"/>
     </row>
-    <row r="304" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:28">
       <c r="A304">
         <v>315</v>
       </c>
@@ -16711,7 +16710,7 @@
       <c r="AA304" s="1"/>
       <c r="AB304" s="1"/>
     </row>
-    <row r="305" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:28">
       <c r="A305">
         <v>316</v>
       </c>
@@ -16757,7 +16756,7 @@
       <c r="AA305" s="1"/>
       <c r="AB305" s="1"/>
     </row>
-    <row r="306" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:28">
       <c r="A306">
         <v>317</v>
       </c>
@@ -16805,7 +16804,7 @@
       <c r="AA306" s="1"/>
       <c r="AB306" s="1"/>
     </row>
-    <row r="307" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:28">
       <c r="A307">
         <v>318</v>
       </c>
@@ -16851,7 +16850,7 @@
       <c r="AA307" s="1"/>
       <c r="AB307" s="1"/>
     </row>
-    <row r="308" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:28">
       <c r="A308">
         <v>319</v>
       </c>
@@ -16897,7 +16896,7 @@
       <c r="AA308" s="1"/>
       <c r="AB308" s="1"/>
     </row>
-    <row r="309" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:28">
       <c r="A309">
         <v>320</v>
       </c>
@@ -16943,7 +16942,7 @@
       <c r="AA309" s="1"/>
       <c r="AB309" s="1"/>
     </row>
-    <row r="310" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:28">
       <c r="A310">
         <v>321</v>
       </c>
@@ -16991,7 +16990,7 @@
       <c r="AA310" s="1"/>
       <c r="AB310" s="1"/>
     </row>
-    <row r="311" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:28">
       <c r="A311">
         <v>322</v>
       </c>
@@ -17039,7 +17038,7 @@
       <c r="AA311" s="1"/>
       <c r="AB311" s="1"/>
     </row>
-    <row r="312" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:28">
       <c r="A312">
         <v>323</v>
       </c>
@@ -17085,7 +17084,7 @@
       <c r="AA312" s="1"/>
       <c r="AB312" s="1"/>
     </row>
-    <row r="313" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:28">
       <c r="A313">
         <v>324</v>
       </c>
@@ -17131,7 +17130,7 @@
       <c r="AA313" s="1"/>
       <c r="AB313" s="1"/>
     </row>
-    <row r="314" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:28">
       <c r="A314">
         <v>325</v>
       </c>
@@ -17177,7 +17176,7 @@
       <c r="AA314" s="1"/>
       <c r="AB314" s="1"/>
     </row>
-    <row r="315" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:28">
       <c r="A315">
         <v>326</v>
       </c>
@@ -17223,7 +17222,7 @@
       <c r="AA315" s="1"/>
       <c r="AB315" s="1"/>
     </row>
-    <row r="316" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:28">
       <c r="A316">
         <v>327</v>
       </c>
@@ -17269,7 +17268,7 @@
       <c r="AA316" s="1"/>
       <c r="AB316" s="1"/>
     </row>
-    <row r="317" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:28">
       <c r="A317">
         <v>328</v>
       </c>
@@ -17315,7 +17314,7 @@
       <c r="AA317" s="1"/>
       <c r="AB317" s="1"/>
     </row>
-    <row r="318" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:28">
       <c r="A318">
         <v>329</v>
       </c>
@@ -17361,7 +17360,7 @@
       <c r="AA318" s="1"/>
       <c r="AB318" s="1"/>
     </row>
-    <row r="319" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:28">
       <c r="A319">
         <v>330</v>
       </c>
@@ -17407,7 +17406,7 @@
       <c r="AA319" s="1"/>
       <c r="AB319" s="1"/>
     </row>
-    <row r="320" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:28">
       <c r="A320">
         <v>331</v>
       </c>
@@ -17455,7 +17454,7 @@
       <c r="AA320" s="1"/>
       <c r="AB320" s="1"/>
     </row>
-    <row r="321" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:28">
       <c r="A321">
         <v>332</v>
       </c>
@@ -17501,7 +17500,7 @@
       <c r="AA321" s="1"/>
       <c r="AB321" s="1"/>
     </row>
-    <row r="322" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:28">
       <c r="A322">
         <v>333</v>
       </c>
@@ -17547,7 +17546,7 @@
       <c r="AA322" s="1"/>
       <c r="AB322" s="1"/>
     </row>
-    <row r="323" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:28">
       <c r="A323">
         <v>334</v>
       </c>
@@ -17593,7 +17592,7 @@
       <c r="AA323" s="1"/>
       <c r="AB323" s="1"/>
     </row>
-    <row r="324" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:28">
       <c r="A324">
         <v>335</v>
       </c>
@@ -17639,7 +17638,7 @@
       <c r="AA324" s="1"/>
       <c r="AB324" s="1"/>
     </row>
-    <row r="325" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:28">
       <c r="A325">
         <v>336</v>
       </c>
@@ -17685,7 +17684,7 @@
       <c r="AA325" s="1"/>
       <c r="AB325" s="1"/>
     </row>
-    <row r="326" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:28">
       <c r="A326">
         <v>337</v>
       </c>
@@ -17731,7 +17730,7 @@
       <c r="AA326" s="1"/>
       <c r="AB326" s="1"/>
     </row>
-    <row r="327" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:28">
       <c r="A327">
         <v>338</v>
       </c>
@@ -17777,7 +17776,7 @@
       <c r="AA327" s="1"/>
       <c r="AB327" s="1"/>
     </row>
-    <row r="328" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:28">
       <c r="A328">
         <v>339</v>
       </c>
@@ -17823,7 +17822,7 @@
       <c r="AA328" s="1"/>
       <c r="AB328" s="1"/>
     </row>
-    <row r="329" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:28">
       <c r="A329">
         <v>340</v>
       </c>
@@ -17869,7 +17868,7 @@
       <c r="AA329" s="1"/>
       <c r="AB329" s="1"/>
     </row>
-    <row r="330" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:28">
       <c r="A330">
         <v>341</v>
       </c>
@@ -17917,7 +17916,7 @@
       <c r="AA330" s="1"/>
       <c r="AB330" s="1"/>
     </row>
-    <row r="331" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:28">
       <c r="A331">
         <v>342</v>
       </c>
@@ -17963,7 +17962,7 @@
       <c r="AA331" s="1"/>
       <c r="AB331" s="1"/>
     </row>
-    <row r="332" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:28">
       <c r="A332">
         <v>343</v>
       </c>
@@ -18011,7 +18010,7 @@
       <c r="AA332" s="1"/>
       <c r="AB332" s="1"/>
     </row>
-    <row r="333" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:28">
       <c r="A333">
         <v>344</v>
       </c>
@@ -18057,7 +18056,7 @@
       <c r="AA333" s="1"/>
       <c r="AB333" s="1"/>
     </row>
-    <row r="334" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:28">
       <c r="A334">
         <v>345</v>
       </c>
@@ -18103,7 +18102,7 @@
       <c r="AA334" s="1"/>
       <c r="AB334" s="1"/>
     </row>
-    <row r="335" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:28">
       <c r="A335">
         <v>354</v>
       </c>
@@ -18149,7 +18148,7 @@
       <c r="AA335" s="1"/>
       <c r="AB335" s="1"/>
     </row>
-    <row r="336" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:28">
       <c r="A336">
         <v>355</v>
       </c>
@@ -18197,7 +18196,7 @@
       <c r="AA336" s="1"/>
       <c r="AB336" s="1"/>
     </row>
-    <row r="337" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:28">
       <c r="A337">
         <v>356</v>
       </c>
@@ -18243,7 +18242,7 @@
       <c r="AA337" s="1"/>
       <c r="AB337" s="1"/>
     </row>
-    <row r="338" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:28">
       <c r="A338">
         <v>357</v>
       </c>
@@ -18289,7 +18288,7 @@
       <c r="AA338" s="1"/>
       <c r="AB338" s="1"/>
     </row>
-    <row r="339" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:28">
       <c r="A339">
         <v>358</v>
       </c>
@@ -18335,7 +18334,7 @@
       <c r="AA339" s="1"/>
       <c r="AB339" s="1"/>
     </row>
-    <row r="340" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:28">
       <c r="A340">
         <v>359</v>
       </c>
@@ -18381,7 +18380,7 @@
       <c r="AA340" s="1"/>
       <c r="AB340" s="1"/>
     </row>
-    <row r="341" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:28">
       <c r="A341">
         <v>360</v>
       </c>
@@ -18427,7 +18426,7 @@
       <c r="AA341" s="1"/>
       <c r="AB341" s="1"/>
     </row>
-    <row r="342" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:28">
       <c r="A342">
         <v>361</v>
       </c>
@@ -18473,7 +18472,7 @@
       <c r="AA342" s="1"/>
       <c r="AB342" s="1"/>
     </row>
-    <row r="343" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:28">
       <c r="A343">
         <v>362</v>
       </c>
@@ -18519,7 +18518,7 @@
       <c r="AA343" s="1"/>
       <c r="AB343" s="1"/>
     </row>
-    <row r="344" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:28">
       <c r="A344">
         <v>363</v>
       </c>
@@ -18565,7 +18564,7 @@
       <c r="AA344" s="1"/>
       <c r="AB344" s="1"/>
     </row>
-    <row r="345" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:28">
       <c r="A345">
         <v>364</v>
       </c>
@@ -18611,7 +18610,7 @@
       <c r="AA345" s="1"/>
       <c r="AB345" s="1"/>
     </row>
-    <row r="346" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:28">
       <c r="A346">
         <v>365</v>
       </c>
@@ -18657,7 +18656,7 @@
       <c r="AA346" s="1"/>
       <c r="AB346" s="1"/>
     </row>
-    <row r="347" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:28">
       <c r="A347">
         <v>366</v>
       </c>
@@ -18703,7 +18702,7 @@
       <c r="AA347" s="1"/>
       <c r="AB347" s="1"/>
     </row>
-    <row r="348" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:28">
       <c r="A348">
         <v>367</v>
       </c>
@@ -18749,7 +18748,7 @@
       <c r="AA348" s="1"/>
       <c r="AB348" s="1"/>
     </row>
-    <row r="349" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:28">
       <c r="A349">
         <v>368</v>
       </c>
@@ -18795,7 +18794,7 @@
       <c r="AA349" s="1"/>
       <c r="AB349" s="1"/>
     </row>
-    <row r="350" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:28">
       <c r="A350">
         <v>369</v>
       </c>
@@ -18841,7 +18840,7 @@
       <c r="AA350" s="1"/>
       <c r="AB350" s="1"/>
     </row>
-    <row r="351" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:28">
       <c r="A351">
         <v>370</v>
       </c>
@@ -18887,7 +18886,7 @@
       <c r="AA351" s="1"/>
       <c r="AB351" s="1"/>
     </row>
-    <row r="352" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:28">
       <c r="A352">
         <v>371</v>
       </c>
@@ -18933,7 +18932,7 @@
       <c r="AA352" s="1"/>
       <c r="AB352" s="1"/>
     </row>
-    <row r="353" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:28">
       <c r="A353">
         <v>372</v>
       </c>
@@ -18979,7 +18978,7 @@
       <c r="AA353" s="1"/>
       <c r="AB353" s="1"/>
     </row>
-    <row r="354" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:28">
       <c r="A354">
         <v>373</v>
       </c>
@@ -19025,7 +19024,7 @@
       <c r="AA354" s="1"/>
       <c r="AB354" s="1"/>
     </row>
-    <row r="355" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:28">
       <c r="A355">
         <v>374</v>
       </c>
@@ -19071,7 +19070,7 @@
       <c r="AA355" s="1"/>
       <c r="AB355" s="1"/>
     </row>
-    <row r="356" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:28">
       <c r="A356">
         <v>375</v>
       </c>
@@ -19117,7 +19116,7 @@
       <c r="AA356" s="1"/>
       <c r="AB356" s="1"/>
     </row>
-    <row r="357" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:28">
       <c r="A357">
         <v>376</v>
       </c>
@@ -19163,7 +19162,7 @@
       <c r="AA357" s="1"/>
       <c r="AB357" s="1"/>
     </row>
-    <row r="358" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:28">
       <c r="A358">
         <v>377</v>
       </c>
@@ -19209,7 +19208,7 @@
       <c r="AA358" s="1"/>
       <c r="AB358" s="1"/>
     </row>
-    <row r="359" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:28">
       <c r="A359">
         <v>378</v>
       </c>
@@ -19255,7 +19254,7 @@
       <c r="AA359" s="1"/>
       <c r="AB359" s="1"/>
     </row>
-    <row r="360" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:28">
       <c r="A360">
         <v>379</v>
       </c>
@@ -19301,7 +19300,7 @@
       <c r="AA360" s="1"/>
       <c r="AB360" s="1"/>
     </row>
-    <row r="361" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:28">
       <c r="A361">
         <v>380</v>
       </c>
@@ -19347,7 +19346,7 @@
       <c r="AA361" s="1"/>
       <c r="AB361" s="1"/>
     </row>
-    <row r="362" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:28">
       <c r="A362">
         <v>381</v>
       </c>
@@ -19393,7 +19392,7 @@
       <c r="AA362" s="1"/>
       <c r="AB362" s="1"/>
     </row>
-    <row r="363" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:28">
       <c r="A363">
         <v>382</v>
       </c>
@@ -19439,7 +19438,7 @@
       <c r="AA363" s="1"/>
       <c r="AB363" s="1"/>
     </row>
-    <row r="364" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:28">
       <c r="A364">
         <v>383</v>
       </c>
@@ -19485,7 +19484,7 @@
       <c r="AA364" s="1"/>
       <c r="AB364" s="1"/>
     </row>
-    <row r="365" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:28">
       <c r="A365">
         <v>384</v>
       </c>
@@ -19531,7 +19530,7 @@
       <c r="AA365" s="1"/>
       <c r="AB365" s="1"/>
     </row>
-    <row r="366" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:28">
       <c r="A366">
         <v>385</v>
       </c>
@@ -19577,7 +19576,7 @@
       <c r="AA366" s="1"/>
       <c r="AB366" s="1"/>
     </row>
-    <row r="367" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:28">
       <c r="A367">
         <v>386</v>
       </c>
@@ -19623,7 +19622,7 @@
       <c r="AA367" s="1"/>
       <c r="AB367" s="1"/>
     </row>
-    <row r="368" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:28">
       <c r="A368">
         <v>387</v>
       </c>
@@ -19669,7 +19668,7 @@
       <c r="AA368" s="1"/>
       <c r="AB368" s="1"/>
     </row>
-    <row r="369" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:28">
       <c r="A369">
         <v>388</v>
       </c>
@@ -19715,7 +19714,7 @@
       <c r="AA369" s="1"/>
       <c r="AB369" s="1"/>
     </row>
-    <row r="370" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:28">
       <c r="A370">
         <v>389</v>
       </c>
@@ -19761,7 +19760,7 @@
       <c r="AA370" s="1"/>
       <c r="AB370" s="1"/>
     </row>
-    <row r="371" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:28">
       <c r="A371">
         <v>390</v>
       </c>
@@ -19807,7 +19806,7 @@
       <c r="AA371" s="1"/>
       <c r="AB371" s="1"/>
     </row>
-    <row r="372" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:28">
       <c r="A372">
         <v>391</v>
       </c>
@@ -19853,7 +19852,7 @@
       <c r="AA372" s="1"/>
       <c r="AB372" s="1"/>
     </row>
-    <row r="373" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:28">
       <c r="A373">
         <v>392</v>
       </c>
@@ -19899,7 +19898,7 @@
       <c r="AA373" s="1"/>
       <c r="AB373" s="1"/>
     </row>
-    <row r="374" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:28">
       <c r="A374">
         <v>393</v>
       </c>
@@ -19945,7 +19944,7 @@
       <c r="AA374" s="1"/>
       <c r="AB374" s="1"/>
     </row>
-    <row r="375" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:28">
       <c r="A375">
         <v>394</v>
       </c>
@@ -19991,7 +19990,7 @@
       <c r="AA375" s="1"/>
       <c r="AB375" s="1"/>
     </row>
-    <row r="376" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:28">
       <c r="A376">
         <v>395</v>
       </c>
@@ -20037,7 +20036,7 @@
       <c r="AA376" s="1"/>
       <c r="AB376" s="1"/>
     </row>
-    <row r="377" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:28">
       <c r="A377">
         <v>396</v>
       </c>
@@ -20083,7 +20082,7 @@
       <c r="AA377" s="1"/>
       <c r="AB377" s="1"/>
     </row>
-    <row r="378" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:28">
       <c r="A378">
         <v>397</v>
       </c>
@@ -20129,7 +20128,7 @@
       <c r="AA378" s="1"/>
       <c r="AB378" s="1"/>
     </row>
-    <row r="379" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:28">
       <c r="A379">
         <v>398</v>
       </c>
@@ -20175,7 +20174,7 @@
       <c r="AA379" s="1"/>
       <c r="AB379" s="1"/>
     </row>
-    <row r="380" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:28">
       <c r="A380">
         <v>399</v>
       </c>
@@ -20221,7 +20220,7 @@
       <c r="AA380" s="1"/>
       <c r="AB380" s="1"/>
     </row>
-    <row r="381" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:28">
       <c r="A381">
         <v>400</v>
       </c>
@@ -20267,7 +20266,7 @@
       <c r="AA381" s="1"/>
       <c r="AB381" s="1"/>
     </row>
-    <row r="382" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:28">
       <c r="A382">
         <v>401</v>
       </c>
@@ -20313,7 +20312,7 @@
       <c r="AA382" s="1"/>
       <c r="AB382" s="1"/>
     </row>
-    <row r="383" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:28">
       <c r="A383">
         <v>402</v>
       </c>
@@ -20359,7 +20358,7 @@
       <c r="AA383" s="1"/>
       <c r="AB383" s="1"/>
     </row>
-    <row r="384" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:28">
       <c r="A384">
         <v>403</v>
       </c>
@@ -20405,7 +20404,7 @@
       <c r="AA384" s="1"/>
       <c r="AB384" s="1"/>
     </row>
-    <row r="385" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:28">
       <c r="A385">
         <v>404</v>
       </c>
@@ -20451,7 +20450,7 @@
       <c r="AA385" s="1"/>
       <c r="AB385" s="1"/>
     </row>
-    <row r="386" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:28">
       <c r="A386">
         <v>405</v>
       </c>
@@ -20497,7 +20496,7 @@
       <c r="AA386" s="1"/>
       <c r="AB386" s="1"/>
     </row>
-    <row r="387" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:28">
       <c r="A387">
         <v>406</v>
       </c>
@@ -20543,7 +20542,7 @@
       <c r="AA387" s="1"/>
       <c r="AB387" s="1"/>
     </row>
-    <row r="388" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:28">
       <c r="A388">
         <v>407</v>
       </c>
@@ -20589,7 +20588,7 @@
       <c r="AA388" s="1"/>
       <c r="AB388" s="1"/>
     </row>
-    <row r="389" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:28">
       <c r="A389">
         <v>408</v>
       </c>
@@ -20635,7 +20634,7 @@
       <c r="AA389" s="1"/>
       <c r="AB389" s="1"/>
     </row>
-    <row r="390" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:28">
       <c r="A390">
         <v>409</v>
       </c>
@@ -20681,7 +20680,7 @@
       <c r="AA390" s="1"/>
       <c r="AB390" s="1"/>
     </row>
-    <row r="391" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:28">
       <c r="A391">
         <v>410</v>
       </c>
@@ -20727,7 +20726,7 @@
       <c r="AA391" s="1"/>
       <c r="AB391" s="1"/>
     </row>
-    <row r="392" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:28">
       <c r="A392">
         <v>411</v>
       </c>
@@ -20773,7 +20772,7 @@
       <c r="AA392" s="1"/>
       <c r="AB392" s="1"/>
     </row>
-    <row r="393" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:28">
       <c r="A393">
         <v>412</v>
       </c>
@@ -20821,7 +20820,7 @@
       <c r="AA393" s="1"/>
       <c r="AB393" s="1"/>
     </row>
-    <row r="394" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:28">
       <c r="A394">
         <v>413</v>
       </c>
@@ -20867,7 +20866,7 @@
       <c r="AA394" s="1"/>
       <c r="AB394" s="1"/>
     </row>
-    <row r="395" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:28">
       <c r="A395">
         <v>414</v>
       </c>
@@ -20913,7 +20912,7 @@
       <c r="AA395" s="1"/>
       <c r="AB395" s="1"/>
     </row>
-    <row r="396" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:28">
       <c r="A396">
         <v>415</v>
       </c>
@@ -20959,7 +20958,7 @@
       <c r="AA396" s="1"/>
       <c r="AB396" s="1"/>
     </row>
-    <row r="397" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:28">
       <c r="A397">
         <v>416</v>
       </c>
@@ -21005,7 +21004,7 @@
       <c r="AA397" s="1"/>
       <c r="AB397" s="1"/>
     </row>
-    <row r="398" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:28">
       <c r="A398">
         <v>417</v>
       </c>
@@ -21051,7 +21050,7 @@
       <c r="AA398" s="1"/>
       <c r="AB398" s="1"/>
     </row>
-    <row r="399" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:28">
       <c r="A399">
         <v>418</v>
       </c>
@@ -21097,7 +21096,7 @@
       <c r="AA399" s="1"/>
       <c r="AB399" s="1"/>
     </row>
-    <row r="400" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:28">
       <c r="A400">
         <v>419</v>
       </c>
@@ -21143,7 +21142,7 @@
       <c r="AA400" s="1"/>
       <c r="AB400" s="1"/>
     </row>
-    <row r="401" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:28">
       <c r="A401">
         <v>420</v>
       </c>
@@ -21189,7 +21188,7 @@
       <c r="AA401" s="1"/>
       <c r="AB401" s="1"/>
     </row>
-    <row r="402" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:28">
       <c r="A402">
         <v>421</v>
       </c>
@@ -21235,7 +21234,7 @@
       <c r="AA402" s="1"/>
       <c r="AB402" s="1"/>
     </row>
-    <row r="403" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:28">
       <c r="A403">
         <v>422</v>
       </c>
@@ -21281,7 +21280,7 @@
       <c r="AA403" s="1"/>
       <c r="AB403" s="1"/>
     </row>
-    <row r="404" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:28">
       <c r="A404">
         <v>423</v>
       </c>
@@ -21327,7 +21326,7 @@
       <c r="AA404" s="1"/>
       <c r="AB404" s="1"/>
     </row>
-    <row r="405" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:28">
       <c r="A405">
         <v>424</v>
       </c>
@@ -21373,7 +21372,7 @@
       <c r="AA405" s="1"/>
       <c r="AB405" s="1"/>
     </row>
-    <row r="406" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:28">
       <c r="A406">
         <v>425</v>
       </c>
@@ -21419,7 +21418,7 @@
       <c r="AA406" s="1"/>
       <c r="AB406" s="1"/>
     </row>
-    <row r="407" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:28">
       <c r="A407">
         <v>426</v>
       </c>
@@ -21465,7 +21464,7 @@
       <c r="AA407" s="1"/>
       <c r="AB407" s="1"/>
     </row>
-    <row r="408" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:28">
       <c r="A408">
         <v>427</v>
       </c>
@@ -21511,7 +21510,7 @@
       <c r="AA408" s="1"/>
       <c r="AB408" s="1"/>
     </row>
-    <row r="409" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:28">
       <c r="A409">
         <v>428</v>
       </c>
@@ -21557,7 +21556,7 @@
       <c r="AA409" s="1"/>
       <c r="AB409" s="1"/>
     </row>
-    <row r="410" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:28">
       <c r="A410">
         <v>429</v>
       </c>
@@ -21603,7 +21602,7 @@
       <c r="AA410" s="1"/>
       <c r="AB410" s="1"/>
     </row>
-    <row r="411" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:28">
       <c r="A411">
         <v>430</v>
       </c>
@@ -21649,7 +21648,7 @@
       <c r="AA411" s="1"/>
       <c r="AB411" s="1"/>
     </row>
-    <row r="412" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:28">
       <c r="A412">
         <v>431</v>
       </c>
@@ -21695,7 +21694,7 @@
       <c r="AA412" s="1"/>
       <c r="AB412" s="1"/>
     </row>
-    <row r="413" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:28">
       <c r="A413">
         <v>432</v>
       </c>
@@ -21743,7 +21742,7 @@
       <c r="AA413" s="1"/>
       <c r="AB413" s="1"/>
     </row>
-    <row r="414" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:28">
       <c r="A414">
         <v>433</v>
       </c>
@@ -21789,7 +21788,7 @@
       <c r="AA414" s="1"/>
       <c r="AB414" s="1"/>
     </row>
-    <row r="415" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:28">
       <c r="A415">
         <v>434</v>
       </c>
@@ -21835,7 +21834,7 @@
       <c r="AA415" s="1"/>
       <c r="AB415" s="1"/>
     </row>
-    <row r="416" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:28">
       <c r="A416">
         <v>435</v>
       </c>
@@ -21883,7 +21882,7 @@
       <c r="AA416" s="1"/>
       <c r="AB416" s="1"/>
     </row>
-    <row r="417" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:28">
       <c r="A417">
         <v>436</v>
       </c>
@@ -21929,7 +21928,7 @@
       <c r="AA417" s="1"/>
       <c r="AB417" s="1"/>
     </row>
-    <row r="418" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:28">
       <c r="A418">
         <v>437</v>
       </c>
@@ -21975,7 +21974,7 @@
       <c r="AA418" s="1"/>
       <c r="AB418" s="1"/>
     </row>
-    <row r="419" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:28">
       <c r="A419">
         <v>438</v>
       </c>
@@ -22021,7 +22020,7 @@
       <c r="AA419" s="1"/>
       <c r="AB419" s="1"/>
     </row>
-    <row r="420" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:28">
       <c r="A420">
         <v>439</v>
       </c>
@@ -22067,7 +22066,7 @@
       <c r="AA420" s="1"/>
       <c r="AB420" s="1"/>
     </row>
-    <row r="421" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:28">
       <c r="A421">
         <v>440</v>
       </c>
@@ -22113,7 +22112,7 @@
       <c r="AA421" s="1"/>
       <c r="AB421" s="1"/>
     </row>
-    <row r="422" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:28">
       <c r="A422">
         <v>441</v>
       </c>
@@ -22159,7 +22158,7 @@
       <c r="AA422" s="1"/>
       <c r="AB422" s="1"/>
     </row>
-    <row r="423" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:28">
       <c r="A423">
         <v>442</v>
       </c>
@@ -22207,7 +22206,7 @@
       <c r="AA423" s="1"/>
       <c r="AB423" s="1"/>
     </row>
-    <row r="424" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:28">
       <c r="A424">
         <v>443</v>
       </c>
@@ -22253,7 +22252,7 @@
       <c r="AA424" s="1"/>
       <c r="AB424" s="1"/>
     </row>
-    <row r="425" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:28">
       <c r="A425">
         <v>444</v>
       </c>
@@ -22299,7 +22298,7 @@
       <c r="AA425" s="1"/>
       <c r="AB425" s="1"/>
     </row>
-    <row r="426" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:28">
       <c r="A426">
         <v>445</v>
       </c>
@@ -22345,7 +22344,7 @@
       <c r="AA426" s="1"/>
       <c r="AB426" s="1"/>
     </row>
-    <row r="427" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:28">
       <c r="A427">
         <v>446</v>
       </c>
@@ -22391,7 +22390,7 @@
       <c r="AA427" s="1"/>
       <c r="AB427" s="1"/>
     </row>
-    <row r="428" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:28">
       <c r="A428">
         <v>447</v>
       </c>
@@ -22437,7 +22436,7 @@
       <c r="AA428" s="1"/>
       <c r="AB428" s="1"/>
     </row>
-    <row r="429" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:28">
       <c r="A429">
         <v>448</v>
       </c>
@@ -22483,7 +22482,7 @@
       <c r="AA429" s="1"/>
       <c r="AB429" s="1"/>
     </row>
-    <row r="430" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:28">
       <c r="A430">
         <v>449</v>
       </c>
@@ -22529,7 +22528,7 @@
       <c r="AA430" s="1"/>
       <c r="AB430" s="1"/>
     </row>
-    <row r="431" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:28">
       <c r="A431">
         <v>450</v>
       </c>
@@ -22575,7 +22574,7 @@
       <c r="AA431" s="1"/>
       <c r="AB431" s="1"/>
     </row>
-    <row r="432" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:28">
       <c r="A432">
         <v>451</v>
       </c>
@@ -22621,7 +22620,7 @@
       <c r="AA432" s="1"/>
       <c r="AB432" s="1"/>
     </row>
-    <row r="433" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:28">
       <c r="A433">
         <v>452</v>
       </c>
@@ -22667,7 +22666,7 @@
       <c r="AA433" s="1"/>
       <c r="AB433" s="1"/>
     </row>
-    <row r="434" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:28">
       <c r="A434">
         <v>453</v>
       </c>
@@ -22713,7 +22712,7 @@
       <c r="AA434" s="1"/>
       <c r="AB434" s="1"/>
     </row>
-    <row r="435" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:28">
       <c r="A435">
         <v>454</v>
       </c>
@@ -22759,7 +22758,7 @@
       <c r="AA435" s="1"/>
       <c r="AB435" s="1"/>
     </row>
-    <row r="436" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:28">
       <c r="A436">
         <v>455</v>
       </c>
@@ -22805,7 +22804,7 @@
       <c r="AA436" s="1"/>
       <c r="AB436" s="1"/>
     </row>
-    <row r="437" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:28">
       <c r="A437">
         <v>456</v>
       </c>
@@ -22851,7 +22850,7 @@
       <c r="AA437" s="1"/>
       <c r="AB437" s="1"/>
     </row>
-    <row r="438" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:28">
       <c r="A438">
         <v>457</v>
       </c>
@@ -22897,7 +22896,7 @@
       <c r="AA438" s="1"/>
       <c r="AB438" s="1"/>
     </row>
-    <row r="439" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:28">
       <c r="A439">
         <v>458</v>
       </c>
@@ -22943,7 +22942,7 @@
       <c r="AA439" s="1"/>
       <c r="AB439" s="1"/>
     </row>
-    <row r="440" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:28">
       <c r="A440">
         <v>459</v>
       </c>
@@ -22989,7 +22988,7 @@
       <c r="AA440" s="1"/>
       <c r="AB440" s="1"/>
     </row>
-    <row r="441" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:28">
       <c r="A441">
         <v>460</v>
       </c>
@@ -23035,7 +23034,7 @@
       <c r="AA441" s="1"/>
       <c r="AB441" s="1"/>
     </row>
-    <row r="442" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:28">
       <c r="A442">
         <v>461</v>
       </c>
@@ -23081,7 +23080,7 @@
       <c r="AA442" s="1"/>
       <c r="AB442" s="1"/>
     </row>
-    <row r="443" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:28">
       <c r="A443">
         <v>462</v>
       </c>
@@ -23127,7 +23126,7 @@
       <c r="AA443" s="1"/>
       <c r="AB443" s="1"/>
     </row>
-    <row r="444" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:28">
       <c r="A444">
         <v>463</v>
       </c>
@@ -23173,7 +23172,7 @@
       <c r="AA444" s="1"/>
       <c r="AB444" s="1"/>
     </row>
-    <row r="445" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:28">
       <c r="A445">
         <v>464</v>
       </c>
@@ -23219,7 +23218,7 @@
       <c r="AA445" s="1"/>
       <c r="AB445" s="1"/>
     </row>
-    <row r="446" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:28">
       <c r="A446">
         <v>465</v>
       </c>
@@ -23265,7 +23264,7 @@
       <c r="AA446" s="1"/>
       <c r="AB446" s="1"/>
     </row>
-    <row r="447" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:28">
       <c r="A447">
         <v>466</v>
       </c>
@@ -23311,7 +23310,7 @@
       <c r="AA447" s="1"/>
       <c r="AB447" s="1"/>
     </row>
-    <row r="448" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:28">
       <c r="A448">
         <v>467</v>
       </c>
@@ -23357,7 +23356,7 @@
       <c r="AA448" s="1"/>
       <c r="AB448" s="1"/>
     </row>
-    <row r="449" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:28">
       <c r="A449">
         <v>468</v>
       </c>
@@ -23403,7 +23402,7 @@
       <c r="AA449" s="1"/>
       <c r="AB449" s="1"/>
     </row>
-    <row r="450" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:28">
       <c r="A450">
         <v>469</v>
       </c>
@@ -23449,7 +23448,7 @@
       <c r="AA450" s="1"/>
       <c r="AB450" s="1"/>
     </row>
-    <row r="451" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:28">
       <c r="A451">
         <v>470</v>
       </c>
@@ -23495,7 +23494,7 @@
       <c r="AA451" s="1"/>
       <c r="AB451" s="1"/>
     </row>
-    <row r="452" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:28">
       <c r="A452">
         <v>471</v>
       </c>
@@ -23541,7 +23540,7 @@
       <c r="AA452" s="1"/>
       <c r="AB452" s="1"/>
     </row>
-    <row r="453" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:28">
       <c r="A453">
         <v>472</v>
       </c>
@@ -23587,7 +23586,7 @@
       <c r="AA453" s="1"/>
       <c r="AB453" s="1"/>
     </row>
-    <row r="454" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:28">
       <c r="A454">
         <v>473</v>
       </c>
@@ -23633,7 +23632,7 @@
       <c r="AA454" s="1"/>
       <c r="AB454" s="1"/>
     </row>
-    <row r="455" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:28">
       <c r="A455">
         <v>474</v>
       </c>
@@ -23679,7 +23678,7 @@
       <c r="AA455" s="1"/>
       <c r="AB455" s="1"/>
     </row>
-    <row r="456" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:28">
       <c r="A456">
         <v>475</v>
       </c>
@@ -23725,7 +23724,7 @@
       <c r="AA456" s="1"/>
       <c r="AB456" s="1"/>
     </row>
-    <row r="457" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:28">
       <c r="A457">
         <v>476</v>
       </c>
@@ -23771,7 +23770,7 @@
       <c r="AA457" s="1"/>
       <c r="AB457" s="1"/>
     </row>
-    <row r="458" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:28">
       <c r="A458">
         <v>477</v>
       </c>
@@ -23817,7 +23816,7 @@
       <c r="AA458" s="1"/>
       <c r="AB458" s="1"/>
     </row>
-    <row r="459" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:28">
       <c r="A459">
         <v>478</v>
       </c>
@@ -23863,7 +23862,7 @@
       <c r="AA459" s="1"/>
       <c r="AB459" s="1"/>
     </row>
-    <row r="460" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:28">
       <c r="A460">
         <v>479</v>
       </c>
@@ -23909,7 +23908,7 @@
       <c r="AA460" s="1"/>
       <c r="AB460" s="1"/>
     </row>
-    <row r="461" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:28">
       <c r="A461">
         <v>480</v>
       </c>
@@ -23955,7 +23954,7 @@
       <c r="AA461" s="1"/>
       <c r="AB461" s="1"/>
     </row>
-    <row r="462" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:28">
       <c r="A462">
         <v>481</v>
       </c>
@@ -24001,7 +24000,7 @@
       <c r="AA462" s="1"/>
       <c r="AB462" s="1"/>
     </row>
-    <row r="463" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:28">
       <c r="A463">
         <v>482</v>
       </c>
@@ -24047,7 +24046,7 @@
       <c r="AA463" s="1"/>
       <c r="AB463" s="1"/>
     </row>
-    <row r="464" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:28">
       <c r="A464">
         <v>483</v>
       </c>
@@ -24093,7 +24092,7 @@
       <c r="AA464" s="1"/>
       <c r="AB464" s="1"/>
     </row>
-    <row r="465" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:28">
       <c r="A465">
         <v>484</v>
       </c>
@@ -24139,7 +24138,7 @@
       <c r="AA465" s="1"/>
       <c r="AB465" s="1"/>
     </row>
-    <row r="466" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:28">
       <c r="A466">
         <v>485</v>
       </c>
@@ -24185,7 +24184,7 @@
       <c r="AA466" s="1"/>
       <c r="AB466" s="1"/>
     </row>
-    <row r="467" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:28">
       <c r="A467">
         <v>486</v>
       </c>
@@ -24231,7 +24230,7 @@
       <c r="AA467" s="1"/>
       <c r="AB467" s="1"/>
     </row>
-    <row r="468" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:28">
       <c r="A468">
         <v>487</v>
       </c>
@@ -24277,7 +24276,7 @@
       <c r="AA468" s="1"/>
       <c r="AB468" s="1"/>
     </row>
-    <row r="469" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:28">
       <c r="A469">
         <v>488</v>
       </c>
@@ -24323,7 +24322,7 @@
       <c r="AA469" s="1"/>
       <c r="AB469" s="1"/>
     </row>
-    <row r="470" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:28">
       <c r="A470">
         <v>489</v>
       </c>
@@ -24369,7 +24368,7 @@
       <c r="AA470" s="1"/>
       <c r="AB470" s="1"/>
     </row>
-    <row r="471" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:28">
       <c r="A471">
         <v>490</v>
       </c>
@@ -24415,7 +24414,7 @@
       <c r="AA471" s="1"/>
       <c r="AB471" s="1"/>
     </row>
-    <row r="472" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:28">
       <c r="A472">
         <v>491</v>
       </c>
@@ -24461,7 +24460,7 @@
       <c r="AA472" s="1"/>
       <c r="AB472" s="1"/>
     </row>
-    <row r="473" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:28">
       <c r="A473">
         <v>492</v>
       </c>
@@ -24507,7 +24506,7 @@
       <c r="AA473" s="1"/>
       <c r="AB473" s="1"/>
     </row>
-    <row r="474" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:28">
       <c r="A474">
         <v>493</v>
       </c>
@@ -24553,7 +24552,7 @@
       <c r="AA474" s="1"/>
       <c r="AB474" s="1"/>
     </row>
-    <row r="475" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:28">
       <c r="A475">
         <v>494</v>
       </c>
@@ -24599,7 +24598,7 @@
       <c r="AA475" s="1"/>
       <c r="AB475" s="1"/>
     </row>
-    <row r="476" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:28">
       <c r="A476">
         <v>495</v>
       </c>
@@ -24645,7 +24644,7 @@
       <c r="AA476" s="1"/>
       <c r="AB476" s="1"/>
     </row>
-    <row r="477" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:28">
       <c r="A477">
         <v>496</v>
       </c>
@@ -24691,7 +24690,7 @@
       <c r="AA477" s="1"/>
       <c r="AB477" s="1"/>
     </row>
-    <row r="478" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:28">
       <c r="A478">
         <v>497</v>
       </c>
@@ -24737,7 +24736,7 @@
       <c r="AA478" s="1"/>
       <c r="AB478" s="1"/>
     </row>
-    <row r="479" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:28">
       <c r="A479">
         <v>498</v>
       </c>
@@ -24783,7 +24782,7 @@
       <c r="AA479" s="1"/>
       <c r="AB479" s="1"/>
     </row>
-    <row r="480" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:28">
       <c r="A480">
         <v>499</v>
       </c>
@@ -24829,7 +24828,7 @@
       <c r="AA480" s="1"/>
       <c r="AB480" s="1"/>
     </row>
-    <row r="481" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:28">
       <c r="A481">
         <v>500</v>
       </c>
@@ -24875,7 +24874,7 @@
       <c r="AA481" s="1"/>
       <c r="AB481" s="1"/>
     </row>
-    <row r="482" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:28">
       <c r="A482">
         <v>501</v>
       </c>
@@ -24921,7 +24920,7 @@
       <c r="AA482" s="1"/>
       <c r="AB482" s="1"/>
     </row>
-    <row r="483" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:28">
       <c r="A483">
         <v>502</v>
       </c>
@@ -24967,7 +24966,7 @@
       <c r="AA483" s="1"/>
       <c r="AB483" s="1"/>
     </row>
-    <row r="484" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:28">
       <c r="A484">
         <v>503</v>
       </c>
@@ -25013,7 +25012,7 @@
       <c r="AA484" s="1"/>
       <c r="AB484" s="1"/>
     </row>
-    <row r="485" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:28">
       <c r="A485">
         <v>504</v>
       </c>
@@ -25059,7 +25058,7 @@
       <c r="AA485" s="1"/>
       <c r="AB485" s="1"/>
     </row>
-    <row r="486" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:28">
       <c r="A486">
         <v>505</v>
       </c>
@@ -25105,7 +25104,7 @@
       <c r="AA486" s="1"/>
       <c r="AB486" s="1"/>
     </row>
-    <row r="487" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:28">
       <c r="A487">
         <v>506</v>
       </c>
@@ -25151,7 +25150,7 @@
       <c r="AA487" s="1"/>
       <c r="AB487" s="1"/>
     </row>
-    <row r="488" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:28">
       <c r="A488">
         <v>507</v>
       </c>
@@ -25197,7 +25196,7 @@
       <c r="AA488" s="1"/>
       <c r="AB488" s="1"/>
     </row>
-    <row r="489" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:28">
       <c r="A489">
         <v>508</v>
       </c>
@@ -25243,7 +25242,7 @@
       <c r="AA489" s="1"/>
       <c r="AB489" s="1"/>
     </row>
-    <row r="490" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:28">
       <c r="A490">
         <v>509</v>
       </c>
@@ -25289,7 +25288,7 @@
       <c r="AA490" s="1"/>
       <c r="AB490" s="1"/>
     </row>
-    <row r="491" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:28">
       <c r="A491">
         <v>510</v>
       </c>
@@ -25335,7 +25334,7 @@
       <c r="AA491" s="1"/>
       <c r="AB491" s="1"/>
     </row>
-    <row r="492" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:28">
       <c r="A492">
         <v>511</v>
       </c>
@@ -25381,7 +25380,7 @@
       <c r="AA492" s="1"/>
       <c r="AB492" s="1"/>
     </row>
-    <row r="493" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:28">
       <c r="A493">
         <v>512</v>
       </c>
@@ -25427,7 +25426,7 @@
       <c r="AA493" s="1"/>
       <c r="AB493" s="1"/>
     </row>
-    <row r="494" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:28">
       <c r="A494">
         <v>513</v>
       </c>
@@ -25473,7 +25472,7 @@
       <c r="AA494" s="1"/>
       <c r="AB494" s="1"/>
     </row>
-    <row r="495" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:28">
       <c r="A495">
         <v>514</v>
       </c>
@@ -25521,7 +25520,7 @@
       <c r="AA495" s="1"/>
       <c r="AB495" s="1"/>
     </row>
-    <row r="496" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:28">
       <c r="A496">
         <v>515</v>
       </c>
@@ -25567,7 +25566,7 @@
       <c r="AA496" s="1"/>
       <c r="AB496" s="1"/>
     </row>
-    <row r="497" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:28">
       <c r="A497">
         <v>516</v>
       </c>
@@ -25613,7 +25612,7 @@
       <c r="AA497" s="1"/>
       <c r="AB497" s="1"/>
     </row>
-    <row r="498" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:28">
       <c r="A498">
         <v>517</v>
       </c>
@@ -25659,7 +25658,7 @@
       <c r="AA498" s="1"/>
       <c r="AB498" s="1"/>
     </row>
-    <row r="499" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:28">
       <c r="A499">
         <v>518</v>
       </c>
@@ -25705,7 +25704,7 @@
       <c r="AA499" s="1"/>
       <c r="AB499" s="1"/>
     </row>
-    <row r="500" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:28">
       <c r="A500">
         <v>519</v>
       </c>
@@ -25751,7 +25750,7 @@
       <c r="AA500" s="1"/>
       <c r="AB500" s="1"/>
     </row>
-    <row r="501" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:28">
       <c r="A501">
         <v>520</v>
       </c>
@@ -25797,7 +25796,7 @@
       <c r="AA501" s="1"/>
       <c r="AB501" s="1"/>
     </row>
-    <row r="502" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:28">
       <c r="A502">
         <v>521</v>
       </c>
@@ -25843,7 +25842,7 @@
       <c r="AA502" s="1"/>
       <c r="AB502" s="1"/>
     </row>
-    <row r="503" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:28">
       <c r="A503">
         <v>522</v>
       </c>
@@ -25889,7 +25888,7 @@
       <c r="AA503" s="1"/>
       <c r="AB503" s="1"/>
     </row>
-    <row r="504" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:28">
       <c r="A504">
         <v>523</v>
       </c>
@@ -25935,7 +25934,7 @@
       <c r="AA504" s="1"/>
       <c r="AB504" s="1"/>
     </row>
-    <row r="505" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:28">
       <c r="A505">
         <v>524</v>
       </c>
@@ -25981,7 +25980,7 @@
       <c r="AA505" s="1"/>
       <c r="AB505" s="1"/>
     </row>
-    <row r="506" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:28">
       <c r="A506">
         <v>525</v>
       </c>
@@ -26027,7 +26026,7 @@
       <c r="AA506" s="1"/>
       <c r="AB506" s="1"/>
     </row>
-    <row r="507" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:28">
       <c r="A507">
         <v>526</v>
       </c>
@@ -26075,7 +26074,7 @@
       <c r="AA507" s="1"/>
       <c r="AB507" s="1"/>
     </row>
-    <row r="508" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:28">
       <c r="A508">
         <v>527</v>
       </c>
@@ -26121,7 +26120,7 @@
       <c r="AA508" s="1"/>
       <c r="AB508" s="1"/>
     </row>
-    <row r="509" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:28">
       <c r="A509">
         <v>528</v>
       </c>
@@ -26167,7 +26166,7 @@
       <c r="AA509" s="1"/>
       <c r="AB509" s="1"/>
     </row>
-    <row r="510" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:28">
       <c r="A510">
         <v>529</v>
       </c>
@@ -26213,7 +26212,7 @@
       <c r="AA510" s="1"/>
       <c r="AB510" s="1"/>
     </row>
-    <row r="511" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:28">
       <c r="A511">
         <v>530</v>
       </c>
@@ -26259,7 +26258,7 @@
       <c r="AA511" s="1"/>
       <c r="AB511" s="1"/>
     </row>
-    <row r="512" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:28">
       <c r="A512">
         <v>531</v>
       </c>
@@ -26305,7 +26304,7 @@
       <c r="AA512" s="1"/>
       <c r="AB512" s="1"/>
     </row>
-    <row r="513" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:28">
       <c r="A513">
         <v>532</v>
       </c>
@@ -26351,7 +26350,7 @@
       <c r="AA513" s="1"/>
       <c r="AB513" s="1"/>
     </row>
-    <row r="514" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:28">
       <c r="A514">
         <v>533</v>
       </c>
@@ -26397,7 +26396,7 @@
       <c r="AA514" s="1"/>
       <c r="AB514" s="1"/>
     </row>
-    <row r="515" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:28">
       <c r="A515">
         <v>534</v>
       </c>
@@ -26443,7 +26442,7 @@
       <c r="AA515" s="1"/>
       <c r="AB515" s="1"/>
     </row>
-    <row r="516" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:28">
       <c r="A516">
         <v>535</v>
       </c>
@@ -26489,7 +26488,7 @@
       <c r="AA516" s="1"/>
       <c r="AB516" s="1"/>
     </row>
-    <row r="517" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:28">
       <c r="A517">
         <v>536</v>
       </c>
@@ -26535,7 +26534,7 @@
       <c r="AA517" s="1"/>
       <c r="AB517" s="1"/>
     </row>
-    <row r="518" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:28">
       <c r="A518">
         <v>537</v>
       </c>
@@ -26581,7 +26580,7 @@
       <c r="AA518" s="1"/>
       <c r="AB518" s="1"/>
     </row>
-    <row r="519" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:28">
       <c r="A519">
         <v>538</v>
       </c>
@@ -26627,7 +26626,7 @@
       <c r="AA519" s="1"/>
       <c r="AB519" s="1"/>
     </row>
-    <row r="520" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:28">
       <c r="A520">
         <v>539</v>
       </c>
@@ -26673,7 +26672,7 @@
       <c r="AA520" s="1"/>
       <c r="AB520" s="1"/>
     </row>
-    <row r="521" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:28">
       <c r="A521">
         <v>540</v>
       </c>
@@ -26719,7 +26718,7 @@
       <c r="AA521" s="1"/>
       <c r="AB521" s="1"/>
     </row>
-    <row r="522" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:28">
       <c r="A522">
         <v>541</v>
       </c>
@@ -26765,7 +26764,7 @@
       <c r="AA522" s="1"/>
       <c r="AB522" s="1"/>
     </row>
-    <row r="523" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:28">
       <c r="A523">
         <v>542</v>
       </c>
@@ -26811,7 +26810,7 @@
       <c r="AA523" s="1"/>
       <c r="AB523" s="1"/>
     </row>
-    <row r="524" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:28">
       <c r="A524">
         <v>543</v>
       </c>
@@ -26857,7 +26856,7 @@
       <c r="AA524" s="1"/>
       <c r="AB524" s="1"/>
     </row>
-    <row r="525" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:28">
       <c r="A525">
         <v>544</v>
       </c>
@@ -26903,7 +26902,7 @@
       <c r="AA525" s="1"/>
       <c r="AB525" s="1"/>
     </row>
-    <row r="526" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:28">
       <c r="A526">
         <v>545</v>
       </c>
@@ -26951,7 +26950,7 @@
       <c r="AA526" s="1"/>
       <c r="AB526" s="1"/>
     </row>
-    <row r="527" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:28">
       <c r="A527">
         <v>546</v>
       </c>
@@ -26997,7 +26996,7 @@
       <c r="AA527" s="1"/>
       <c r="AB527" s="1"/>
     </row>
-    <row r="528" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:28">
       <c r="A528">
         <v>547</v>
       </c>
@@ -27043,7 +27042,7 @@
       <c r="AA528" s="1"/>
       <c r="AB528" s="1"/>
     </row>
-    <row r="529" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:28">
       <c r="A529">
         <v>548</v>
       </c>
@@ -27089,7 +27088,7 @@
       <c r="AA529" s="1"/>
       <c r="AB529" s="1"/>
     </row>
-    <row r="530" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:28">
       <c r="A530">
         <v>549</v>
       </c>
@@ -27135,7 +27134,7 @@
       <c r="AA530" s="1"/>
       <c r="AB530" s="1"/>
     </row>
-    <row r="531" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:28">
       <c r="A531">
         <v>550</v>
       </c>
@@ -27181,7 +27180,7 @@
       <c r="AA531" s="1"/>
       <c r="AB531" s="1"/>
     </row>
-    <row r="532" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:28">
       <c r="A532">
         <v>551</v>
       </c>
@@ -27229,7 +27228,7 @@
       <c r="AA532" s="1"/>
       <c r="AB532" s="1"/>
     </row>
-    <row r="533" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:28">
       <c r="A533">
         <v>552</v>
       </c>
@@ -27275,7 +27274,7 @@
       <c r="AA533" s="1"/>
       <c r="AB533" s="1"/>
     </row>
-    <row r="534" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:28">
       <c r="A534">
         <v>553</v>
       </c>
@@ -27321,7 +27320,7 @@
       <c r="AA534" s="1"/>
       <c r="AB534" s="1"/>
     </row>
-    <row r="535" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:28">
       <c r="A535">
         <v>554</v>
       </c>
@@ -27367,7 +27366,7 @@
       <c r="AA535" s="1"/>
       <c r="AB535" s="1"/>
     </row>
-    <row r="536" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:28">
       <c r="A536">
         <v>555</v>
       </c>
@@ -27413,7 +27412,7 @@
       <c r="AA536" s="1"/>
       <c r="AB536" s="1"/>
     </row>
-    <row r="537" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:28">
       <c r="A537">
         <v>556</v>
       </c>
@@ -27461,7 +27460,7 @@
       <c r="AA537" s="1"/>
       <c r="AB537" s="1"/>
     </row>
-    <row r="538" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:28">
       <c r="A538">
         <v>557</v>
       </c>
@@ -27507,7 +27506,7 @@
       <c r="AA538" s="1"/>
       <c r="AB538" s="1"/>
     </row>
-    <row r="539" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:28">
       <c r="A539">
         <v>558</v>
       </c>
@@ -27553,7 +27552,7 @@
       <c r="AA539" s="1"/>
       <c r="AB539" s="1"/>
     </row>
-    <row r="540" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:28">
       <c r="A540">
         <v>559</v>
       </c>
@@ -27599,7 +27598,7 @@
       <c r="AA540" s="1"/>
       <c r="AB540" s="1"/>
     </row>
-    <row r="541" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:28">
       <c r="A541">
         <v>560</v>
       </c>
@@ -27645,7 +27644,7 @@
       <c r="AA541" s="1"/>
       <c r="AB541" s="1"/>
     </row>
-    <row r="542" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:28">
       <c r="A542">
         <v>561</v>
       </c>
@@ -27691,7 +27690,7 @@
       <c r="AA542" s="1"/>
       <c r="AB542" s="1"/>
     </row>
-    <row r="543" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:28">
       <c r="A543">
         <v>562</v>
       </c>
@@ -27737,7 +27736,7 @@
       <c r="AA543" s="1"/>
       <c r="AB543" s="1"/>
     </row>
-    <row r="544" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:28">
       <c r="A544">
         <v>563</v>
       </c>
@@ -27783,7 +27782,7 @@
       <c r="AA544" s="1"/>
       <c r="AB544" s="1"/>
     </row>
-    <row r="545" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:28">
       <c r="A545">
         <v>564</v>
       </c>
@@ -27829,7 +27828,7 @@
       <c r="AA545" s="1"/>
       <c r="AB545" s="1"/>
     </row>
-    <row r="546" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:28">
       <c r="A546">
         <v>565</v>
       </c>
@@ -27875,7 +27874,7 @@
       <c r="AA546" s="1"/>
       <c r="AB546" s="1"/>
     </row>
-    <row r="547" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:28">
       <c r="A547">
         <v>566</v>
       </c>
@@ -27921,7 +27920,7 @@
       <c r="AA547" s="1"/>
       <c r="AB547" s="1"/>
     </row>
-    <row r="548" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:28">
       <c r="A548">
         <v>567</v>
       </c>
@@ -27967,7 +27966,7 @@
       <c r="AA548" s="1"/>
       <c r="AB548" s="1"/>
     </row>
-    <row r="549" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:28">
       <c r="A549">
         <v>568</v>
       </c>
@@ -28013,7 +28012,7 @@
       <c r="AA549" s="1"/>
       <c r="AB549" s="1"/>
     </row>
-    <row r="550" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:28">
       <c r="A550">
         <v>569</v>
       </c>
@@ -28059,7 +28058,7 @@
       <c r="AA550" s="1"/>
       <c r="AB550" s="1"/>
     </row>
-    <row r="551" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:28">
       <c r="A551">
         <v>570</v>
       </c>
@@ -28105,7 +28104,7 @@
       <c r="AA551" s="1"/>
       <c r="AB551" s="1"/>
     </row>
-    <row r="552" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:28">
       <c r="A552">
         <v>571</v>
       </c>
@@ -28151,7 +28150,7 @@
       <c r="AA552" s="1"/>
       <c r="AB552" s="1"/>
     </row>
-    <row r="553" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:28">
       <c r="A553">
         <v>572</v>
       </c>
@@ -28197,7 +28196,7 @@
       <c r="AA553" s="1"/>
       <c r="AB553" s="1"/>
     </row>
-    <row r="554" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:28">
       <c r="A554">
         <v>573</v>
       </c>
@@ -28243,7 +28242,7 @@
       <c r="AA554" s="1"/>
       <c r="AB554" s="1"/>
     </row>
-    <row r="555" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:28">
       <c r="A555">
         <v>574</v>
       </c>
@@ -28289,7 +28288,7 @@
       <c r="AA555" s="1"/>
       <c r="AB555" s="1"/>
     </row>
-    <row r="556" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:28">
       <c r="A556">
         <v>575</v>
       </c>
@@ -28335,7 +28334,7 @@
       <c r="AA556" s="1"/>
       <c r="AB556" s="1"/>
     </row>
-    <row r="557" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:28">
       <c r="A557">
         <v>576</v>
       </c>
@@ -28381,7 +28380,7 @@
       <c r="AA557" s="1"/>
       <c r="AB557" s="1"/>
     </row>
-    <row r="558" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:28">
       <c r="A558">
         <v>577</v>
       </c>
@@ -28427,7 +28426,7 @@
       <c r="AA558" s="1"/>
       <c r="AB558" s="1"/>
     </row>
-    <row r="559" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:28">
       <c r="A559">
         <v>578</v>
       </c>
@@ -28475,7 +28474,7 @@
       <c r="AA559" s="1"/>
       <c r="AB559" s="1"/>
     </row>
-    <row r="560" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:28">
       <c r="A560">
         <v>579</v>
       </c>
@@ -28521,7 +28520,7 @@
       <c r="AA560" s="1"/>
       <c r="AB560" s="1"/>
     </row>
-    <row r="561" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:28">
       <c r="A561">
         <v>580</v>
       </c>
@@ -28567,7 +28566,7 @@
       <c r="AA561" s="1"/>
       <c r="AB561" s="1"/>
     </row>
-    <row r="562" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:28">
       <c r="A562">
         <v>581</v>
       </c>
@@ -28613,7 +28612,7 @@
       <c r="AA562" s="1"/>
       <c r="AB562" s="1"/>
     </row>
-    <row r="563" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:28">
       <c r="A563">
         <v>582</v>
       </c>
@@ -28659,7 +28658,7 @@
       <c r="AA563" s="1"/>
       <c r="AB563" s="1"/>
     </row>
-    <row r="564" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:28">
       <c r="A564">
         <v>583</v>
       </c>
@@ -28705,7 +28704,7 @@
       <c r="AA564" s="1"/>
       <c r="AB564" s="1"/>
     </row>
-    <row r="565" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:28">
       <c r="A565">
         <v>584</v>
       </c>
@@ -28755,7 +28754,7 @@
       <c r="AA565" s="1"/>
       <c r="AB565" s="1"/>
     </row>
-    <row r="566" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:28">
       <c r="A566">
         <v>585</v>
       </c>
@@ -28805,7 +28804,7 @@
       <c r="AA566" s="1"/>
       <c r="AB566" s="1"/>
     </row>
-    <row r="567" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:28">
       <c r="A567">
         <v>586</v>
       </c>
@@ -28851,7 +28850,7 @@
       <c r="AA567" s="1"/>
       <c r="AB567" s="1"/>
     </row>
-    <row r="568" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:28">
       <c r="A568">
         <v>587</v>
       </c>
@@ -28897,7 +28896,7 @@
       <c r="AA568" s="1"/>
       <c r="AB568" s="1"/>
     </row>
-    <row r="569" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:28">
       <c r="A569">
         <v>588</v>
       </c>
@@ -28947,7 +28946,7 @@
       <c r="AA569" s="1"/>
       <c r="AB569" s="1"/>
     </row>
-    <row r="570" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:28">
       <c r="A570">
         <v>589</v>
       </c>
@@ -28997,7 +28996,7 @@
       <c r="AA570" s="1"/>
       <c r="AB570" s="1"/>
     </row>
-    <row r="571" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:28">
       <c r="A571">
         <v>590</v>
       </c>
@@ -29047,7 +29046,7 @@
       <c r="AA571" s="1"/>
       <c r="AB571" s="1"/>
     </row>
-    <row r="572" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:28">
       <c r="A572">
         <v>591</v>
       </c>
@@ -29097,7 +29096,7 @@
       <c r="AA572" s="1"/>
       <c r="AB572" s="1"/>
     </row>
-    <row r="573" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:28">
       <c r="A573">
         <v>592</v>
       </c>
@@ -29143,7 +29142,7 @@
       <c r="AA573" s="1"/>
       <c r="AB573" s="1"/>
     </row>
-    <row r="574" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:28">
       <c r="A574">
         <v>593</v>
       </c>
@@ -29189,7 +29188,7 @@
       <c r="AA574" s="1"/>
       <c r="AB574" s="1"/>
     </row>
-    <row r="575" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:28">
       <c r="A575">
         <v>594</v>
       </c>
@@ -29239,7 +29238,7 @@
       <c r="AA575" s="1"/>
       <c r="AB575" s="1"/>
     </row>
-    <row r="576" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:28">
       <c r="A576">
         <v>595</v>
       </c>
@@ -29285,7 +29284,7 @@
       <c r="AA576" s="1"/>
       <c r="AB576" s="1"/>
     </row>
-    <row r="577" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:28">
       <c r="A577">
         <v>596</v>
       </c>
@@ -29335,7 +29334,7 @@
       <c r="AA577" s="1"/>
       <c r="AB577" s="1"/>
     </row>
-    <row r="578" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:28">
       <c r="A578">
         <v>597</v>
       </c>
@@ -29381,7 +29380,7 @@
       <c r="AA578" s="1"/>
       <c r="AB578" s="1"/>
     </row>
-    <row r="579" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:28">
       <c r="A579">
         <v>598</v>
       </c>
@@ -29427,7 +29426,7 @@
       <c r="AA579" s="1"/>
       <c r="AB579" s="1"/>
     </row>
-    <row r="580" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:28">
       <c r="A580">
         <v>599</v>
       </c>
@@ -29477,7 +29476,7 @@
       <c r="AA580" s="1"/>
       <c r="AB580" s="1"/>
     </row>
-    <row r="581" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:28">
       <c r="A581">
         <v>600</v>
       </c>
@@ -29527,7 +29526,7 @@
       <c r="AA581" s="1"/>
       <c r="AB581" s="1"/>
     </row>
-    <row r="582" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:28">
       <c r="A582">
         <v>601</v>
       </c>
@@ -29577,7 +29576,7 @@
       <c r="AA582" s="1"/>
       <c r="AB582" s="1"/>
     </row>
-    <row r="583" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:28">
       <c r="A583">
         <v>602</v>
       </c>
@@ -29627,7 +29626,7 @@
       <c r="AA583" s="1"/>
       <c r="AB583" s="1"/>
     </row>
-    <row r="584" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:28">
       <c r="A584">
         <v>603</v>
       </c>
@@ -29677,7 +29676,7 @@
       <c r="AA584" s="1"/>
       <c r="AB584" s="1"/>
     </row>
-    <row r="585" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:28">
       <c r="A585">
         <v>604</v>
       </c>
@@ -29727,7 +29726,7 @@
       <c r="AA585" s="1"/>
       <c r="AB585" s="1"/>
     </row>
-    <row r="586" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:28">
       <c r="A586">
         <v>605</v>
       </c>
@@ -29777,7 +29776,7 @@
       <c r="AA586" s="1"/>
       <c r="AB586" s="1"/>
     </row>
-    <row r="587" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:28">
       <c r="A587">
         <v>606</v>
       </c>
@@ -29827,7 +29826,7 @@
       <c r="AA587" s="1"/>
       <c r="AB587" s="1"/>
     </row>
-    <row r="588" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:28">
       <c r="A588">
         <v>607</v>
       </c>
@@ -29877,7 +29876,7 @@
       <c r="AA588" s="1"/>
       <c r="AB588" s="1"/>
     </row>
-    <row r="589" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:28">
       <c r="A589">
         <v>608</v>
       </c>
@@ -29927,7 +29926,7 @@
       <c r="AA589" s="1"/>
       <c r="AB589" s="1"/>
     </row>
-    <row r="590" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:28">
       <c r="A590">
         <v>609</v>
       </c>
@@ -29977,7 +29976,7 @@
       <c r="AA590" s="1"/>
       <c r="AB590" s="1"/>
     </row>
-    <row r="591" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:28">
       <c r="A591">
         <v>610</v>
       </c>
@@ -30027,7 +30026,7 @@
       <c r="AA591" s="1"/>
       <c r="AB591" s="1"/>
     </row>
-    <row r="592" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:28">
       <c r="A592">
         <v>611</v>
       </c>
@@ -30077,7 +30076,7 @@
       <c r="AA592" s="1"/>
       <c r="AB592" s="1"/>
     </row>
-    <row r="593" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:28">
       <c r="A593">
         <v>612</v>
       </c>
@@ -30127,7 +30126,7 @@
       <c r="AA593" s="1"/>
       <c r="AB593" s="1"/>
     </row>
-    <row r="594" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:28">
       <c r="A594">
         <v>613</v>
       </c>
@@ -30177,7 +30176,7 @@
       <c r="AA594" s="1"/>
       <c r="AB594" s="1"/>
     </row>
-    <row r="595" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:28">
       <c r="A595">
         <v>614</v>
       </c>
@@ -30227,7 +30226,7 @@
       <c r="AA595" s="1"/>
       <c r="AB595" s="1"/>
     </row>
-    <row r="596" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:28">
       <c r="A596">
         <v>615</v>
       </c>
@@ -30277,7 +30276,7 @@
       <c r="AA596" s="1"/>
       <c r="AB596" s="1"/>
     </row>
-    <row r="597" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:28">
       <c r="A597">
         <v>616</v>
       </c>
@@ -30327,7 +30326,7 @@
       <c r="AA597" s="1"/>
       <c r="AB597" s="1"/>
     </row>
-    <row r="598" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:28">
       <c r="A598">
         <v>617</v>
       </c>
@@ -30377,7 +30376,7 @@
       <c r="AA598" s="1"/>
       <c r="AB598" s="1"/>
     </row>
-    <row r="599" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:28">
       <c r="A599">
         <v>618</v>
       </c>
@@ -30427,7 +30426,7 @@
       <c r="AA599" s="1"/>
       <c r="AB599" s="1"/>
     </row>
-    <row r="600" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:28">
       <c r="A600">
         <v>619</v>
       </c>
@@ -30477,7 +30476,7 @@
       <c r="AA600" s="1"/>
       <c r="AB600" s="1"/>
     </row>
-    <row r="601" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:28">
       <c r="A601">
         <v>620</v>
       </c>
@@ -30527,7 +30526,7 @@
       <c r="AA601" s="1"/>
       <c r="AB601" s="1"/>
     </row>
-    <row r="602" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:28">
       <c r="A602">
         <v>621</v>
       </c>
@@ -30577,7 +30576,7 @@
       <c r="AA602" s="1"/>
       <c r="AB602" s="1"/>
     </row>
-    <row r="603" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:28">
       <c r="A603">
         <v>622</v>
       </c>
@@ -30627,7 +30626,7 @@
       <c r="AA603" s="1"/>
       <c r="AB603" s="1"/>
     </row>
-    <row r="604" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:28">
       <c r="A604">
         <v>623</v>
       </c>
@@ -30675,7 +30674,7 @@
       <c r="AA604" s="1"/>
       <c r="AB604" s="1"/>
     </row>
-    <row r="605" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:28">
       <c r="A605">
         <v>624</v>
       </c>
@@ -30725,7 +30724,7 @@
       <c r="AA605" s="1"/>
       <c r="AB605" s="1"/>
     </row>
-    <row r="606" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:28">
       <c r="A606">
         <v>625</v>
       </c>
@@ -30775,7 +30774,7 @@
       <c r="AA606" s="1"/>
       <c r="AB606" s="1"/>
     </row>
-    <row r="607" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:28">
       <c r="A607">
         <v>626</v>
       </c>
@@ -30825,7 +30824,7 @@
       <c r="AA607" s="1"/>
       <c r="AB607" s="1"/>
     </row>
-    <row r="608" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:28">
       <c r="A608">
         <v>627</v>
       </c>
@@ -30875,7 +30874,7 @@
       <c r="AA608" s="1"/>
       <c r="AB608" s="1"/>
     </row>
-    <row r="609" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:28">
       <c r="A609">
         <v>628</v>
       </c>
@@ -30925,7 +30924,7 @@
       <c r="AA609" s="1"/>
       <c r="AB609" s="1"/>
     </row>
-    <row r="610" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:28">
       <c r="A610">
         <v>629</v>
       </c>
@@ -30975,7 +30974,7 @@
       <c r="AA610" s="1"/>
       <c r="AB610" s="1"/>
     </row>
-    <row r="611" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:28">
       <c r="A611">
         <v>630</v>
       </c>
@@ -31021,7 +31020,7 @@
       <c r="AA611" s="1"/>
       <c r="AB611" s="1"/>
     </row>
-    <row r="612" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:28">
       <c r="A612">
         <v>631</v>
       </c>
@@ -31071,7 +31070,7 @@
       <c r="AA612" s="1"/>
       <c r="AB612" s="1"/>
     </row>
-    <row r="613" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:28">
       <c r="A613">
         <v>632</v>
       </c>
@@ -31119,7 +31118,7 @@
       <c r="AA613" s="1"/>
       <c r="AB613" s="1"/>
     </row>
-    <row r="614" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:28">
       <c r="A614">
         <v>633</v>
       </c>
@@ -31165,7 +31164,7 @@
       <c r="AA614" s="1"/>
       <c r="AB614" s="1"/>
     </row>
-    <row r="615" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:28">
       <c r="A615">
         <v>634</v>
       </c>
@@ -31215,7 +31214,7 @@
       <c r="AA615" s="1"/>
       <c r="AB615" s="1"/>
     </row>
-    <row r="616" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:28">
       <c r="A616">
         <v>635</v>
       </c>
@@ -31265,7 +31264,7 @@
       <c r="AA616" s="1"/>
       <c r="AB616" s="1"/>
     </row>
-    <row r="617" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:28">
       <c r="A617">
         <v>636</v>
       </c>
@@ -31315,7 +31314,7 @@
       <c r="AA617" s="1"/>
       <c r="AB617" s="1"/>
     </row>
-    <row r="618" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:28">
       <c r="A618">
         <v>637</v>
       </c>
@@ -31365,7 +31364,7 @@
       <c r="AA618" s="1"/>
       <c r="AB618" s="1"/>
     </row>
-    <row r="619" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:28">
       <c r="A619">
         <v>638</v>
       </c>
@@ -31415,7 +31414,7 @@
       <c r="AA619" s="1"/>
       <c r="AB619" s="1"/>
     </row>
-    <row r="620" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:28">
       <c r="A620">
         <v>639</v>
       </c>
@@ -31465,7 +31464,7 @@
       <c r="AA620" s="1"/>
       <c r="AB620" s="1"/>
     </row>
-    <row r="621" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:28">
       <c r="A621">
         <v>640</v>
       </c>
@@ -31515,7 +31514,7 @@
       <c r="AA621" s="1"/>
       <c r="AB621" s="1"/>
     </row>
-    <row r="622" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:28">
       <c r="A622">
         <v>641</v>
       </c>
@@ -31565,7 +31564,7 @@
       <c r="AA622" s="1"/>
       <c r="AB622" s="1"/>
     </row>
-    <row r="623" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:28">
       <c r="A623">
         <v>642</v>
       </c>
@@ -31615,7 +31614,7 @@
       <c r="AA623" s="1"/>
       <c r="AB623" s="1"/>
     </row>
-    <row r="624" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:28">
       <c r="A624">
         <v>643</v>
       </c>
@@ -31661,7 +31660,7 @@
       <c r="AA624" s="1"/>
       <c r="AB624" s="1"/>
     </row>
-    <row r="625" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:28">
       <c r="A625">
         <v>644</v>
       </c>
@@ -31711,7 +31710,7 @@
       <c r="AA625" s="1"/>
       <c r="AB625" s="1"/>
     </row>
-    <row r="626" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:28">
       <c r="A626">
         <v>645</v>
       </c>
@@ -31761,7 +31760,7 @@
       <c r="AA626" s="1"/>
       <c r="AB626" s="1"/>
     </row>
-    <row r="627" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:28">
       <c r="A627">
         <v>646</v>
       </c>
@@ -31811,7 +31810,7 @@
       <c r="AA627" s="1"/>
       <c r="AB627" s="1"/>
     </row>
-    <row r="628" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:28">
       <c r="A628">
         <v>647</v>
       </c>
@@ -31861,7 +31860,7 @@
       <c r="AA628" s="1"/>
       <c r="AB628" s="1"/>
     </row>
-    <row r="629" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:28">
       <c r="A629">
         <v>648</v>
       </c>
@@ -31911,7 +31910,7 @@
       <c r="AA629" s="1"/>
       <c r="AB629" s="1"/>
     </row>
-    <row r="630" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:28">
       <c r="A630">
         <v>649</v>
       </c>
@@ -31961,7 +31960,7 @@
       <c r="AA630" s="1"/>
       <c r="AB630" s="1"/>
     </row>
-    <row r="631" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:28">
       <c r="A631">
         <v>650</v>
       </c>
@@ -32011,7 +32010,7 @@
       <c r="AA631" s="1"/>
       <c r="AB631" s="1"/>
     </row>
-    <row r="632" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:28">
       <c r="A632">
         <v>651</v>
       </c>
@@ -32057,7 +32056,7 @@
       <c r="AA632" s="1"/>
       <c r="AB632" s="1"/>
     </row>
-    <row r="633" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:28">
       <c r="A633">
         <v>652</v>
       </c>
@@ -32107,7 +32106,7 @@
       <c r="AA633" s="1"/>
       <c r="AB633" s="1"/>
     </row>
-    <row r="634" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:28">
       <c r="A634">
         <v>653</v>
       </c>
@@ -32157,7 +32156,7 @@
       <c r="AA634" s="1"/>
       <c r="AB634" s="1"/>
     </row>
-    <row r="635" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:28">
       <c r="A635">
         <v>654</v>
       </c>
@@ -32207,7 +32206,7 @@
       <c r="AA635" s="1"/>
       <c r="AB635" s="1"/>
     </row>
-    <row r="636" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:28">
       <c r="A636">
         <v>655</v>
       </c>
@@ -32257,7 +32256,7 @@
       <c r="AA636" s="1"/>
       <c r="AB636" s="1"/>
     </row>
-    <row r="637" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:28">
       <c r="A637">
         <v>656</v>
       </c>
@@ -32307,7 +32306,7 @@
       <c r="AA637" s="1"/>
       <c r="AB637" s="1"/>
     </row>
-    <row r="638" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:28">
       <c r="A638">
         <v>657</v>
       </c>
@@ -32357,7 +32356,7 @@
       <c r="AA638" s="1"/>
       <c r="AB638" s="1"/>
     </row>
-    <row r="639" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:28">
       <c r="A639">
         <v>658</v>
       </c>
@@ -32407,7 +32406,7 @@
       <c r="AA639" s="1"/>
       <c r="AB639" s="1"/>
     </row>
-    <row r="640" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:28">
       <c r="A640">
         <v>659</v>
       </c>
@@ -32457,7 +32456,7 @@
       <c r="AA640" s="1"/>
       <c r="AB640" s="1"/>
     </row>
-    <row r="641" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:28">
       <c r="A641">
         <v>660</v>
       </c>
@@ -32503,7 +32502,7 @@
       <c r="AA641" s="1"/>
       <c r="AB641" s="1"/>
     </row>
-    <row r="642" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:28">
       <c r="A642">
         <v>661</v>
       </c>
@@ -32549,7 +32548,7 @@
       <c r="AA642" s="1"/>
       <c r="AB642" s="1"/>
     </row>
-    <row r="643" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:28">
       <c r="A643">
         <v>662</v>
       </c>
@@ -32599,7 +32598,7 @@
       <c r="AA643" s="1"/>
       <c r="AB643" s="1"/>
     </row>
-    <row r="644" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:28">
       <c r="A644">
         <v>663</v>
       </c>
@@ -32649,7 +32648,7 @@
       <c r="AA644" s="1"/>
       <c r="AB644" s="1"/>
     </row>
-    <row r="645" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:28">
       <c r="A645">
         <v>664</v>
       </c>
@@ -32699,7 +32698,7 @@
       <c r="AA645" s="1"/>
       <c r="AB645" s="1"/>
     </row>
-    <row r="646" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:28">
       <c r="A646">
         <v>665</v>
       </c>
@@ -32749,7 +32748,7 @@
       <c r="AA646" s="1"/>
       <c r="AB646" s="1"/>
     </row>
-    <row r="647" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:28">
       <c r="A647">
         <v>666</v>
       </c>
@@ -32799,7 +32798,7 @@
       <c r="AA647" s="1"/>
       <c r="AB647" s="1"/>
     </row>
-    <row r="648" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:28">
       <c r="A648">
         <v>667</v>
       </c>
@@ -32849,7 +32848,7 @@
       <c r="AA648" s="1"/>
       <c r="AB648" s="1"/>
     </row>
-    <row r="649" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:28">
       <c r="A649">
         <v>668</v>
       </c>
@@ -32899,7 +32898,7 @@
       <c r="AA649" s="1"/>
       <c r="AB649" s="1"/>
     </row>
-    <row r="650" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:28">
       <c r="A650">
         <v>669</v>
       </c>
@@ -32949,7 +32948,7 @@
       <c r="AA650" s="1"/>
       <c r="AB650" s="1"/>
     </row>
-    <row r="651" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:28">
       <c r="A651">
         <v>670</v>
       </c>
@@ -32995,7 +32994,7 @@
       <c r="AA651" s="1"/>
       <c r="AB651" s="1"/>
     </row>
-    <row r="652" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:28">
       <c r="A652">
         <v>671</v>
       </c>
@@ -33045,7 +33044,7 @@
       <c r="AA652" s="1"/>
       <c r="AB652" s="1"/>
     </row>
-    <row r="653" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:28">
       <c r="A653">
         <v>672</v>
       </c>
@@ -33095,7 +33094,7 @@
       <c r="AA653" s="1"/>
       <c r="AB653" s="1"/>
     </row>
-    <row r="654" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:28">
       <c r="A654">
         <v>673</v>
       </c>
@@ -33145,7 +33144,7 @@
       <c r="AA654" s="1"/>
       <c r="AB654" s="1"/>
     </row>
-    <row r="655" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:28">
       <c r="A655">
         <v>674</v>
       </c>
@@ -33195,7 +33194,7 @@
       <c r="AA655" s="1"/>
       <c r="AB655" s="1"/>
     </row>
-    <row r="656" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:28">
       <c r="A656">
         <v>675</v>
       </c>
@@ -33245,7 +33244,7 @@
       <c r="AA656" s="1"/>
       <c r="AB656" s="1"/>
     </row>
-    <row r="657" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:28">
       <c r="A657">
         <v>676</v>
       </c>
@@ -33295,7 +33294,7 @@
       <c r="AA657" s="1"/>
       <c r="AB657" s="1"/>
     </row>
-    <row r="658" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:28">
       <c r="A658">
         <v>677</v>
       </c>
@@ -33345,7 +33344,7 @@
       <c r="AA658" s="1"/>
       <c r="AB658" s="1"/>
     </row>
-    <row r="659" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:28">
       <c r="A659">
         <v>678</v>
       </c>
@@ -33395,7 +33394,7 @@
       <c r="AA659" s="1"/>
       <c r="AB659" s="1"/>
     </row>
-    <row r="660" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:28">
       <c r="A660">
         <v>679</v>
       </c>
@@ -33445,7 +33444,7 @@
       <c r="AA660" s="1"/>
       <c r="AB660" s="1"/>
     </row>
-    <row r="661" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:28">
       <c r="A661">
         <v>680</v>
       </c>
@@ -33495,7 +33494,7 @@
       <c r="AA661" s="1"/>
       <c r="AB661" s="1"/>
     </row>
-    <row r="662" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:28">
       <c r="A662">
         <v>681</v>
       </c>
@@ -33545,7 +33544,7 @@
       <c r="AA662" s="1"/>
       <c r="AB662" s="1"/>
     </row>
-    <row r="663" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:28">
       <c r="A663">
         <v>682</v>
       </c>
@@ -33595,7 +33594,7 @@
       <c r="AA663" s="1"/>
       <c r="AB663" s="1"/>
     </row>
-    <row r="664" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:28">
       <c r="A664">
         <v>683</v>
       </c>
@@ -33645,7 +33644,7 @@
       <c r="AA664" s="1"/>
       <c r="AB664" s="1"/>
     </row>
-    <row r="665" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:28">
       <c r="A665">
         <v>684</v>
       </c>
@@ -33695,7 +33694,7 @@
       <c r="AA665" s="1"/>
       <c r="AB665" s="1"/>
     </row>
-    <row r="666" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:28">
       <c r="A666">
         <v>685</v>
       </c>
@@ -33745,7 +33744,7 @@
       <c r="AA666" s="1"/>
       <c r="AB666" s="1"/>
     </row>
-    <row r="667" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:28">
       <c r="A667">
         <v>686</v>
       </c>
@@ -33795,7 +33794,7 @@
       <c r="AA667" s="1"/>
       <c r="AB667" s="1"/>
     </row>
-    <row r="668" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:28">
       <c r="A668">
         <v>687</v>
       </c>
@@ -33845,7 +33844,7 @@
       <c r="AA668" s="1"/>
       <c r="AB668" s="1"/>
     </row>
-    <row r="669" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:28">
       <c r="A669">
         <v>688</v>
       </c>
@@ -33895,7 +33894,7 @@
       <c r="AA669" s="1"/>
       <c r="AB669" s="1"/>
     </row>
-    <row r="670" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:28">
       <c r="A670">
         <v>689</v>
       </c>
@@ -33945,7 +33944,7 @@
       <c r="AA670" s="1"/>
       <c r="AB670" s="1"/>
     </row>
-    <row r="671" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:28">
       <c r="A671">
         <v>690</v>
       </c>
@@ -33995,7 +33994,7 @@
       <c r="AA671" s="1"/>
       <c r="AB671" s="1"/>
     </row>
-    <row r="672" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:28">
       <c r="A672">
         <v>691</v>
       </c>
@@ -34045,7 +34044,7 @@
       <c r="AA672" s="1"/>
       <c r="AB672" s="1"/>
     </row>
-    <row r="673" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:28">
       <c r="A673">
         <v>692</v>
       </c>
@@ -34095,7 +34094,7 @@
       <c r="AA673" s="1"/>
       <c r="AB673" s="1"/>
     </row>
-    <row r="674" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:28">
       <c r="A674">
         <v>693</v>
       </c>
@@ -34145,7 +34144,7 @@
       <c r="AA674" s="1"/>
       <c r="AB674" s="1"/>
     </row>
-    <row r="675" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:28">
       <c r="A675">
         <v>694</v>
       </c>
@@ -34195,7 +34194,7 @@
       <c r="AA675" s="1"/>
       <c r="AB675" s="1"/>
     </row>
-    <row r="676" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:28">
       <c r="A676">
         <v>695</v>
       </c>
@@ -34245,7 +34244,7 @@
       <c r="AA676" s="1"/>
       <c r="AB676" s="1"/>
     </row>
-    <row r="677" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:28">
       <c r="A677">
         <v>696</v>
       </c>
@@ -34295,7 +34294,7 @@
       <c r="AA677" s="1"/>
       <c r="AB677" s="1"/>
     </row>
-    <row r="678" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:28">
       <c r="A678">
         <v>697</v>
       </c>
@@ -34345,7 +34344,7 @@
       <c r="AA678" s="1"/>
       <c r="AB678" s="1"/>
     </row>
-    <row r="679" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:28">
       <c r="A679">
         <v>698</v>
       </c>
@@ -34395,7 +34394,7 @@
       <c r="AA679" s="1"/>
       <c r="AB679" s="1"/>
     </row>
-    <row r="680" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:28">
       <c r="A680">
         <v>699</v>
       </c>
@@ -34441,7 +34440,7 @@
       <c r="AA680" s="1"/>
       <c r="AB680" s="1"/>
     </row>
-    <row r="681" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:28">
       <c r="A681">
         <v>700</v>
       </c>
@@ -34491,7 +34490,7 @@
       <c r="AA681" s="1"/>
       <c r="AB681" s="1"/>
     </row>
-    <row r="682" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:28">
       <c r="A682">
         <v>701</v>
       </c>
@@ -34537,7 +34536,7 @@
       <c r="AA682" s="1"/>
       <c r="AB682" s="1"/>
     </row>
-    <row r="683" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:28">
       <c r="A683">
         <v>702</v>
       </c>
@@ -34583,7 +34582,7 @@
       <c r="AA683" s="1"/>
       <c r="AB683" s="1"/>
     </row>
-    <row r="684" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:28">
       <c r="A684">
         <v>703</v>
       </c>
@@ -34633,7 +34632,7 @@
       <c r="AA684" s="1"/>
       <c r="AB684" s="1"/>
     </row>
-    <row r="685" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:28">
       <c r="A685">
         <v>704</v>
       </c>
@@ -34683,7 +34682,7 @@
       <c r="AA685" s="1"/>
       <c r="AB685" s="1"/>
     </row>
-    <row r="686" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:28">
       <c r="A686">
         <v>705</v>
       </c>
@@ -34733,7 +34732,7 @@
       <c r="AA686" s="1"/>
       <c r="AB686" s="1"/>
     </row>
-    <row r="687" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:28">
       <c r="A687">
         <v>706</v>
       </c>
@@ -34783,7 +34782,7 @@
       <c r="AA687" s="1"/>
       <c r="AB687" s="1"/>
     </row>
-    <row r="688" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:28">
       <c r="A688">
         <v>707</v>
       </c>
@@ -34833,7 +34832,7 @@
       <c r="AA688" s="1"/>
       <c r="AB688" s="1"/>
     </row>
-    <row r="689" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:28">
       <c r="A689">
         <v>708</v>
       </c>
@@ -34879,7 +34878,7 @@
       <c r="AA689" s="1"/>
       <c r="AB689" s="1"/>
     </row>
-    <row r="690" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:28">
       <c r="A690">
         <v>709</v>
       </c>
@@ -34925,7 +34924,7 @@
       <c r="AA690" s="1"/>
       <c r="AB690" s="1"/>
     </row>
-    <row r="691" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:28">
       <c r="A691">
         <v>710</v>
       </c>
@@ -34971,7 +34970,7 @@
       <c r="AA691" s="1"/>
       <c r="AB691" s="1"/>
     </row>
-    <row r="692" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:28">
       <c r="A692">
         <v>711</v>
       </c>
@@ -35021,7 +35020,7 @@
       <c r="AA692" s="1"/>
       <c r="AB692" s="1"/>
     </row>
-    <row r="693" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:28">
       <c r="A693">
         <v>712</v>
       </c>
@@ -35071,7 +35070,7 @@
       <c r="AA693" s="1"/>
       <c r="AB693" s="1"/>
     </row>
-    <row r="694" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:28">
       <c r="A694">
         <v>713</v>
       </c>
@@ -35117,7 +35116,7 @@
       <c r="AA694" s="1"/>
       <c r="AB694" s="1"/>
     </row>
-    <row r="695" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:28">
       <c r="A695">
         <v>714</v>
       </c>
@@ -35163,7 +35162,7 @@
       <c r="AA695" s="1"/>
       <c r="AB695" s="1"/>
     </row>
-    <row r="696" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:28">
       <c r="A696">
         <v>715</v>
       </c>
@@ -35213,7 +35212,7 @@
       <c r="AA696" s="1"/>
       <c r="AB696" s="1"/>
     </row>
-    <row r="697" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:28">
       <c r="A697">
         <v>716</v>
       </c>
@@ -35261,7 +35260,7 @@
       <c r="AA697" s="1"/>
       <c r="AB697" s="1"/>
     </row>
-    <row r="698" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:28">
       <c r="A698">
         <v>719</v>
       </c>
@@ -35313,7 +35312,7 @@
         <v>1097</v>
       </c>
     </row>
-    <row r="699" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:28">
       <c r="A699">
         <v>720</v>
       </c>
@@ -35359,7 +35358,7 @@
       <c r="AA699" s="1"/>
       <c r="AB699" s="1"/>
     </row>
-    <row r="700" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:28">
       <c r="A700">
         <v>721</v>
       </c>
@@ -35411,7 +35410,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="701" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:28">
       <c r="A701">
         <v>722</v>
       </c>
@@ -35461,7 +35460,7 @@
       <c r="AA701" s="1"/>
       <c r="AB701" s="1"/>
     </row>
-    <row r="702" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:28">
       <c r="A702">
         <v>723</v>
       </c>
@@ -35511,7 +35510,7 @@
       <c r="AA702" s="1"/>
       <c r="AB702" s="1"/>
     </row>
-    <row r="703" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:28">
       <c r="A703">
         <v>724</v>
       </c>
@@ -35561,7 +35560,7 @@
       <c r="AA703" s="1"/>
       <c r="AB703" s="1"/>
     </row>
-    <row r="704" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:28">
       <c r="A704">
         <v>725</v>
       </c>
@@ -35607,7 +35606,7 @@
       <c r="AA704" s="1"/>
       <c r="AB704" s="1"/>
     </row>
-    <row r="705" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:28">
       <c r="A705">
         <v>726</v>
       </c>
@@ -35653,7 +35652,7 @@
       <c r="AA705" s="1"/>
       <c r="AB705" s="1"/>
     </row>
-    <row r="706" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:28">
       <c r="A706">
         <v>727</v>
       </c>
@@ -35699,7 +35698,7 @@
       <c r="AA706" s="1"/>
       <c r="AB706" s="1"/>
     </row>
-    <row r="707" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:28">
       <c r="A707">
         <v>728</v>
       </c>
@@ -35751,7 +35750,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="708" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:28">
       <c r="A708">
         <v>729</v>
       </c>
@@ -35803,7 +35802,7 @@
         <v>1108</v>
       </c>
     </row>
-    <row r="709" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:28">
       <c r="A709">
         <v>730</v>
       </c>
@@ -35855,7 +35854,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="710" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:28">
       <c r="A710">
         <v>731</v>
       </c>
@@ -35903,7 +35902,7 @@
       <c r="AA710" s="1"/>
       <c r="AB710" s="1"/>
     </row>
-    <row r="711" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:28">
       <c r="A711">
         <v>732</v>
       </c>
@@ -35953,7 +35952,7 @@
       <c r="AA711" s="1"/>
       <c r="AB711" s="1"/>
     </row>
-    <row r="712" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:28">
       <c r="A712">
         <v>733</v>
       </c>
@@ -36005,7 +36004,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="713" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:28">
       <c r="A713">
         <v>734</v>
       </c>
@@ -36057,7 +36056,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="714" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:28">
       <c r="A714">
         <v>735</v>
       </c>
@@ -36109,7 +36108,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="715" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:28">
       <c r="A715">
         <v>736</v>
       </c>
@@ -36161,7 +36160,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="716" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:28">
       <c r="A716">
         <v>737</v>
       </c>
@@ -36213,7 +36212,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="717" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:28">
       <c r="A717">
         <v>738</v>
       </c>
@@ -36265,7 +36264,7 @@
         <v>1123</v>
       </c>
     </row>
-    <row r="718" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:28">
       <c r="A718">
         <v>739</v>
       </c>
@@ -36317,7 +36316,7 @@
         <v>1124</v>
       </c>
     </row>
-    <row r="719" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:28">
       <c r="A719">
         <v>740</v>
       </c>
@@ -36369,7 +36368,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="720" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:28">
       <c r="A720">
         <v>741</v>
       </c>
@@ -36421,7 +36420,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="721" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:28">
       <c r="A721">
         <v>742</v>
       </c>
@@ -36473,7 +36472,7 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="722" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:28">
       <c r="A722">
         <v>743</v>
       </c>
@@ -36525,7 +36524,7 @@
         <v>1130</v>
       </c>
     </row>
-    <row r="723" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:28">
       <c r="A723">
         <v>744</v>
       </c>
@@ -36577,7 +36576,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="724" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:28">
       <c r="A724">
         <v>745</v>
       </c>
@@ -36629,7 +36628,7 @@
         <v>1138</v>
       </c>
     </row>
-    <row r="725" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:28">
       <c r="A725">
         <v>746</v>
       </c>
@@ -36675,7 +36674,7 @@
       <c r="AA725" s="1"/>
       <c r="AB725" s="1"/>
     </row>
-    <row r="726" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:28">
       <c r="A726">
         <v>747</v>
       </c>
@@ -36727,7 +36726,7 @@
         <v>1140</v>
       </c>
     </row>
-    <row r="727" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:28">
       <c r="A727">
         <v>748</v>
       </c>
@@ -36779,7 +36778,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="728" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:28">
       <c r="A728">
         <v>749</v>
       </c>
@@ -36831,7 +36830,7 @@
         <v>1144</v>
       </c>
     </row>
-    <row r="729" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:28">
       <c r="A729">
         <v>750</v>
       </c>
@@ -36883,7 +36882,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="730" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:28">
       <c r="A730">
         <v>751</v>
       </c>
@@ -36935,7 +36934,7 @@
         <v>1148</v>
       </c>
     </row>
-    <row r="731" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:28">
       <c r="A731">
         <v>752</v>
       </c>
@@ -36987,7 +36986,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="732" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:28">
       <c r="A732">
         <v>753</v>
       </c>
@@ -37039,7 +37038,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="733" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:28">
       <c r="A733">
         <v>754</v>
       </c>
@@ -37091,7 +37090,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="734" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:28">
       <c r="A734">
         <v>755</v>
       </c>
@@ -37143,7 +37142,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="735" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:28">
       <c r="A735">
         <v>756</v>
       </c>
@@ -37195,7 +37194,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="736" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:28">
       <c r="A736">
         <v>757</v>
       </c>
@@ -37247,7 +37246,7 @@
         <v>1154</v>
       </c>
     </row>
-    <row r="737" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:28">
       <c r="A737">
         <v>758</v>
       </c>
@@ -37299,7 +37298,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="738" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:28">
       <c r="A738">
         <v>759</v>
       </c>
@@ -37345,7 +37344,7 @@
       <c r="AA738" s="1"/>
       <c r="AB738" s="1"/>
     </row>
-    <row r="739" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:28">
       <c r="A739">
         <v>760</v>
       </c>
@@ -37397,7 +37396,7 @@
         <v>1156</v>
       </c>
     </row>
-    <row r="740" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:28">
       <c r="A740">
         <v>761</v>
       </c>
@@ -37443,7 +37442,7 @@
       <c r="AA740" s="1"/>
       <c r="AB740" s="1"/>
     </row>
-    <row r="741" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:28">
       <c r="A741">
         <v>762</v>
       </c>
@@ -37495,7 +37494,7 @@
         <v>1159</v>
       </c>
     </row>
-    <row r="742" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:28">
       <c r="A742">
         <v>763</v>
       </c>
@@ -37547,7 +37546,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="743" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:28">
       <c r="A743">
         <v>764</v>
       </c>
@@ -37599,7 +37598,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="744" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:28">
       <c r="A744">
         <v>765</v>
       </c>
@@ -37651,7 +37650,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="745" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:28">
       <c r="A745">
         <v>766</v>
       </c>
@@ -37701,7 +37700,7 @@
       <c r="AA745" s="1"/>
       <c r="AB745" s="1"/>
     </row>
-    <row r="746" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:28">
       <c r="A746">
         <v>767</v>
       </c>
@@ -37753,7 +37752,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="747" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:28">
       <c r="A747">
         <v>768</v>
       </c>
@@ -37805,7 +37804,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="748" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:28">
       <c r="A748">
         <v>769</v>
       </c>
@@ -37851,7 +37850,7 @@
       <c r="AA748" s="1"/>
       <c r="AB748" s="1"/>
     </row>
-    <row r="749" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:28">
       <c r="A749">
         <v>770</v>
       </c>
@@ -37897,7 +37896,7 @@
       <c r="AA749" s="1"/>
       <c r="AB749" s="1"/>
     </row>
-    <row r="750" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:28">
       <c r="A750">
         <v>771</v>
       </c>
@@ -37949,7 +37948,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="751" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:28">
       <c r="A751">
         <v>772</v>
       </c>
@@ -38001,7 +38000,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="752" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:28">
       <c r="A752">
         <v>773</v>
       </c>
@@ -38053,7 +38052,7 @@
         <v>1171</v>
       </c>
     </row>
-    <row r="753" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:28">
       <c r="A753">
         <v>774</v>
       </c>
@@ -38105,7 +38104,7 @@
         <v>1172</v>
       </c>
     </row>
-    <row r="754" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:28">
       <c r="A754">
         <v>775</v>
       </c>
@@ -38157,7 +38156,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="755" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:28">
       <c r="A755">
         <v>776</v>
       </c>
@@ -38207,7 +38206,7 @@
       <c r="AA755" s="1"/>
       <c r="AB755" s="1"/>
     </row>
-    <row r="756" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:28">
       <c r="A756">
         <v>777</v>
       </c>
@@ -38253,7 +38252,7 @@
       <c r="AA756" s="1"/>
       <c r="AB756" s="1"/>
     </row>
-    <row r="757" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:28">
       <c r="A757">
         <v>778</v>
       </c>
@@ -38305,7 +38304,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="758" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:28">
       <c r="A758">
         <v>779</v>
       </c>
@@ -38357,7 +38356,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="759" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:28">
       <c r="A759">
         <v>780</v>
       </c>
@@ -38409,7 +38408,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="760" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:28">
       <c r="A760">
         <v>781</v>
       </c>
@@ -38461,7 +38460,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="761" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:28">
       <c r="A761">
         <v>782</v>
       </c>
@@ -38513,7 +38512,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="762" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:28">
       <c r="A762">
         <v>783</v>
       </c>
@@ -38565,7 +38564,7 @@
         <v>1182</v>
       </c>
     </row>
-    <row r="763" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:28">
       <c r="A763">
         <v>784</v>
       </c>
@@ -38611,7 +38610,7 @@
       <c r="AA763" s="1"/>
       <c r="AB763" s="1"/>
     </row>
-    <row r="764" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:28">
       <c r="A764">
         <v>785</v>
       </c>
@@ -38663,7 +38662,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="765" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:28">
       <c r="A765">
         <v>786</v>
       </c>
@@ -38715,7 +38714,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="766" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:28">
       <c r="A766">
         <v>787</v>
       </c>
@@ -38767,7 +38766,7 @@
         <v>1187</v>
       </c>
     </row>
-    <row r="767" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:28">
       <c r="A767">
         <v>788</v>
       </c>
@@ -38819,7 +38818,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="768" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:28">
       <c r="A768">
         <v>789</v>
       </c>
@@ -38871,7 +38870,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="769" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:28">
       <c r="A769">
         <v>790</v>
       </c>
@@ -38921,7 +38920,7 @@
       <c r="AA769" s="1"/>
       <c r="AB769" s="1"/>
     </row>
-    <row r="770" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:28">
       <c r="A770">
         <v>791</v>
       </c>
@@ -38967,7 +38966,7 @@
       <c r="AA770" s="1"/>
       <c r="AB770" s="1"/>
     </row>
-    <row r="771" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:28">
       <c r="A771">
         <v>792</v>
       </c>
@@ -39013,7 +39012,7 @@
       <c r="AA771" s="1"/>
       <c r="AB771" s="1"/>
     </row>
-    <row r="772" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:28">
       <c r="A772">
         <v>793</v>
       </c>
@@ -39059,7 +39058,7 @@
       <c r="AA772" s="1"/>
       <c r="AB772" s="1"/>
     </row>
-    <row r="773" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:28">
       <c r="A773">
         <v>794</v>
       </c>
@@ -39109,7 +39108,7 @@
       <c r="AA773" s="1"/>
       <c r="AB773" s="1"/>
     </row>
-    <row r="774" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:28">
       <c r="A774">
         <v>795</v>
       </c>
@@ -39155,7 +39154,7 @@
       <c r="AA774" s="1"/>
       <c r="AB774" s="1"/>
     </row>
-    <row r="775" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:28">
       <c r="A775">
         <v>796</v>
       </c>
@@ -39207,7 +39206,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="776" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:28">
       <c r="A776">
         <v>797</v>
       </c>
@@ -39259,7 +39258,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="777" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:28">
       <c r="A777">
         <v>798</v>
       </c>
@@ -39305,7 +39304,7 @@
       <c r="AA777" s="1"/>
       <c r="AB777" s="1"/>
     </row>
-    <row r="778" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:28">
       <c r="A778">
         <v>799</v>
       </c>
@@ -39355,7 +39354,7 @@
       <c r="AA778" s="1"/>
       <c r="AB778" s="1"/>
     </row>
-    <row r="779" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:28">
       <c r="A779">
         <v>800</v>
       </c>
@@ -39407,7 +39406,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="780" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:28">
       <c r="A780">
         <v>801</v>
       </c>
@@ -39459,7 +39458,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="781" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:28">
       <c r="A781">
         <v>802</v>
       </c>
@@ -39511,7 +39510,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="782" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:28">
       <c r="A782">
         <v>803</v>
       </c>
@@ -39557,7 +39556,7 @@
       <c r="AA782" s="1"/>
       <c r="AB782" s="1"/>
     </row>
-    <row r="783" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:28">
       <c r="A783" s="5">
         <v>804</v>
       </c>
@@ -39609,7 +39608,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="784" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:28">
       <c r="A784" s="5">
         <v>805</v>
       </c>
@@ -39661,7 +39660,7 @@
         <v>1203</v>
       </c>
     </row>
-    <row r="785" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:28">
       <c r="A785" s="5">
         <v>806</v>
       </c>
@@ -39713,7 +39712,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="786" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:28">
       <c r="A786" s="5">
         <v>807</v>
       </c>
@@ -39765,7 +39764,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="787" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:28">
       <c r="A787" s="5">
         <v>808</v>
       </c>
@@ -39817,6 +39816,52 @@
         <v>1206</v>
       </c>
     </row>
+    <row r="788" spans="1:28">
+      <c r="A788" s="5">
+        <v>809</v>
+      </c>
+      <c r="B788" s="2">
+        <v>46280.466979166697</v>
+      </c>
+      <c r="C788" s="2">
+        <v>46280.467418981498</v>
+      </c>
+      <c r="D788" s="1" t="s">
+        <v>347</v>
+      </c>
+      <c r="E788" s="1" t="s">
+        <v>348</v>
+      </c>
+      <c r="F788" s="5">
+        <v>38661</v>
+      </c>
+      <c r="G788" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="H788" s="1"/>
+      <c r="I788" s="1"/>
+      <c r="J788" s="1"/>
+      <c r="K788" s="1"/>
+      <c r="L788" s="1"/>
+      <c r="M788" s="1"/>
+      <c r="N788" s="1" t="s">
+        <v>1207</v>
+      </c>
+      <c r="O788" s="1"/>
+      <c r="P788" s="1"/>
+      <c r="Q788" s="1"/>
+      <c r="R788" s="1"/>
+      <c r="S788" s="1"/>
+      <c r="T788" s="1"/>
+      <c r="U788" s="1"/>
+      <c r="V788" s="3"/>
+      <c r="W788" s="3"/>
+      <c r="X788" s="1"/>
+      <c r="Y788" s="1"/>
+      <c r="Z788" s="1"/>
+      <c r="AA788" s="1"/>
+      <c r="AB788" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S71" r:id="rId1" xr:uid="{DBEDA7D9-6C97-43FD-AB0F-DEBA1D8AA177}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="94" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{158ACDF3-985F-456E-8B85-55C22790543E}"/>
+  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E6E762B-130D-465E-A604-B2AFEF08CD24}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3706" uniqueCount="1208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3795" uniqueCount="1222">
   <si>
     <t>Id</t>
   </si>
@@ -3660,6 +3660,48 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%205/IMG_8190_Starbucks%20Jinetes.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/49978caf-974c-4034-8e1d-e34a5dc85f4a_Starbucks%20Carretera.jpeg</t>
+  </si>
+  <si>
+    <t>08:30 p. m.</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894965223528201323196832553402_Starbucks%20Medica%20Nap.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Angeles%20In.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894978979435945347117469574646_Starbucks%20Av%20Stim.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Francisco%20De%20Jesus%20C.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Santa%20Fe%20I.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17894288286595565345288925183971_Ramon%20Espinosa%20Macia.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/17895072859698670235030527679797_Monica%20Luisa%20Baltaza.jpg</t>
+  </si>
+  <si>
+    <t>brenda.contreras@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Brenda Contreras Olguin</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Castorena.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/IMG_20260915_162215_Miriam%20Catharine%20Lop.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Ford%20Santa.jpg</t>
   </si>
 </sst>
 </file>
@@ -3811,8 +3853,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB788" totalsRowShown="0">
-  <autoFilter ref="A1:AB788" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB802" totalsRowShown="0">
+  <autoFilter ref="A1:AB802" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="25">
       <extLst>
@@ -4014,7 +4056,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="809" latestEventMarker="1133">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="823" latestEventMarker="1147">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4346,7 +4388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB788"/>
+  <dimension ref="A1:AB802"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -39557,7 +39599,7 @@
       <c r="AB782" s="1"/>
     </row>
     <row r="783" spans="1:28">
-      <c r="A783" s="5">
+      <c r="A783">
         <v>804</v>
       </c>
       <c r="B783" s="2">
@@ -39572,7 +39614,7 @@
       <c r="E783" s="1" t="s">
         <v>907</v>
       </c>
-      <c r="F783" s="5">
+      <c r="F783">
         <v>38499</v>
       </c>
       <c r="G783" s="1" t="s">
@@ -39609,7 +39651,7 @@
       </c>
     </row>
     <row r="784" spans="1:28">
-      <c r="A784" s="5">
+      <c r="A784">
         <v>805</v>
       </c>
       <c r="B784" s="2">
@@ -39624,7 +39666,7 @@
       <c r="E784" s="1" t="s">
         <v>1202</v>
       </c>
-      <c r="F784" s="5">
+      <c r="F784">
         <v>38292</v>
       </c>
       <c r="G784" s="1" t="s">
@@ -39661,7 +39703,7 @@
       </c>
     </row>
     <row r="785" spans="1:28">
-      <c r="A785" s="5">
+      <c r="A785">
         <v>806</v>
       </c>
       <c r="B785" s="2">
@@ -39676,7 +39718,7 @@
       <c r="E785" s="1" t="s">
         <v>805</v>
       </c>
-      <c r="F785" s="5">
+      <c r="F785">
         <v>38122</v>
       </c>
       <c r="G785" s="1" t="s">
@@ -39713,7 +39755,7 @@
       </c>
     </row>
     <row r="786" spans="1:28">
-      <c r="A786" s="5">
+      <c r="A786">
         <v>807</v>
       </c>
       <c r="B786" s="2">
@@ -39728,7 +39770,7 @@
       <c r="E786" s="1" t="s">
         <v>898</v>
       </c>
-      <c r="F786" s="5">
+      <c r="F786">
         <v>38452</v>
       </c>
       <c r="G786" s="1" t="s">
@@ -39765,7 +39807,7 @@
       </c>
     </row>
     <row r="787" spans="1:28">
-      <c r="A787" s="5">
+      <c r="A787">
         <v>808</v>
       </c>
       <c r="B787" s="2">
@@ -39780,7 +39822,7 @@
       <c r="E787" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="F787" s="5">
+      <c r="F787">
         <v>38815</v>
       </c>
       <c r="G787" s="1" t="s">
@@ -39817,7 +39859,7 @@
       </c>
     </row>
     <row r="788" spans="1:28">
-      <c r="A788" s="5">
+      <c r="A788">
         <v>809</v>
       </c>
       <c r="B788" s="2">
@@ -39832,7 +39874,7 @@
       <c r="E788" s="1" t="s">
         <v>348</v>
       </c>
-      <c r="F788" s="5">
+      <c r="F788">
         <v>38661</v>
       </c>
       <c r="G788" s="1" t="s">
@@ -39862,6 +39904,716 @@
       <c r="AA788" s="1"/>
       <c r="AB788" s="1"/>
     </row>
+    <row r="789" spans="1:28">
+      <c r="A789" s="5">
+        <v>810</v>
+      </c>
+      <c r="B789" s="2">
+        <v>46280.512708333299</v>
+      </c>
+      <c r="C789" s="2">
+        <v>46280.513206018499</v>
+      </c>
+      <c r="D789" s="1" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E789" s="1" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F789" s="5">
+        <v>43011</v>
+      </c>
+      <c r="G789" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H789" s="1"/>
+      <c r="I789" s="1"/>
+      <c r="J789" s="1"/>
+      <c r="K789" s="1"/>
+      <c r="L789" s="1"/>
+      <c r="M789" s="1"/>
+      <c r="N789" s="1"/>
+      <c r="O789" s="1"/>
+      <c r="P789" s="1"/>
+      <c r="Q789" s="1"/>
+      <c r="R789" s="1"/>
+      <c r="S789" s="1"/>
+      <c r="T789" s="1"/>
+      <c r="U789" s="1"/>
+      <c r="V789" s="3"/>
+      <c r="W789" s="3"/>
+      <c r="X789" s="1"/>
+      <c r="Y789" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z789" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA789" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB789" s="1" t="s">
+        <v>1208</v>
+      </c>
+    </row>
+    <row r="790" spans="1:28">
+      <c r="A790" s="5">
+        <v>811</v>
+      </c>
+      <c r="B790" s="2">
+        <v>46280.515069444402</v>
+      </c>
+      <c r="C790" s="2">
+        <v>46280.5154861111</v>
+      </c>
+      <c r="D790" s="1" t="s">
+        <v>810</v>
+      </c>
+      <c r="E790" s="1" t="s">
+        <v>811</v>
+      </c>
+      <c r="F790" s="5">
+        <v>38764</v>
+      </c>
+      <c r="G790" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H790" s="1"/>
+      <c r="I790" s="1"/>
+      <c r="J790" s="1"/>
+      <c r="K790" s="1"/>
+      <c r="L790" s="1"/>
+      <c r="M790" s="1"/>
+      <c r="N790" s="1"/>
+      <c r="O790" s="1"/>
+      <c r="P790" s="1"/>
+      <c r="Q790" s="1"/>
+      <c r="R790" s="1"/>
+      <c r="S790" s="1"/>
+      <c r="T790" s="1"/>
+      <c r="U790" s="1"/>
+      <c r="V790" s="3"/>
+      <c r="W790" s="3"/>
+      <c r="X790" s="1"/>
+      <c r="Y790" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z790" s="1" t="s">
+        <v>1209</v>
+      </c>
+      <c r="AA790" s="1" t="s">
+        <v>1169</v>
+      </c>
+      <c r="AB790" s="1" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="791" spans="1:28">
+      <c r="A791" s="5">
+        <v>812</v>
+      </c>
+      <c r="B791" s="2">
+        <v>46280.514398148203</v>
+      </c>
+      <c r="C791" s="2">
+        <v>46280.526203703703</v>
+      </c>
+      <c r="D791" s="1" t="s">
+        <v>828</v>
+      </c>
+      <c r="E791" s="1" t="s">
+        <v>829</v>
+      </c>
+      <c r="F791" s="5">
+        <v>38439</v>
+      </c>
+      <c r="G791" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H791" s="1"/>
+      <c r="I791" s="1"/>
+      <c r="J791" s="1"/>
+      <c r="K791" s="1"/>
+      <c r="L791" s="1"/>
+      <c r="M791" s="1"/>
+      <c r="N791" s="1"/>
+      <c r="O791" s="1"/>
+      <c r="P791" s="1"/>
+      <c r="Q791" s="1"/>
+      <c r="R791" s="1"/>
+      <c r="S791" s="1"/>
+      <c r="T791" s="1"/>
+      <c r="U791" s="1"/>
+      <c r="V791" s="3"/>
+      <c r="W791" s="3"/>
+      <c r="X791" s="1"/>
+      <c r="Y791" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z791" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA791" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB791" s="1" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="792" spans="1:28">
+      <c r="A792" s="5">
+        <v>813</v>
+      </c>
+      <c r="B792" s="2">
+        <v>46280.531180555598</v>
+      </c>
+      <c r="C792" s="2">
+        <v>46280.531493055598</v>
+      </c>
+      <c r="D792" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="E792" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="F792" s="5">
+        <v>38568</v>
+      </c>
+      <c r="G792" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H792" s="1"/>
+      <c r="I792" s="1"/>
+      <c r="J792" s="1"/>
+      <c r="K792" s="1"/>
+      <c r="L792" s="1"/>
+      <c r="M792" s="1"/>
+      <c r="N792" s="1"/>
+      <c r="O792" s="1"/>
+      <c r="P792" s="1"/>
+      <c r="Q792" s="1"/>
+      <c r="R792" s="1"/>
+      <c r="S792" s="1"/>
+      <c r="T792" s="1"/>
+      <c r="U792" s="1"/>
+      <c r="V792" s="3"/>
+      <c r="W792" s="3"/>
+      <c r="X792" s="1"/>
+      <c r="Y792" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z792" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA792" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB792" s="1" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="793" spans="1:28">
+      <c r="A793" s="5">
+        <v>814</v>
+      </c>
+      <c r="B793" s="2">
+        <v>46280.5398263889</v>
+      </c>
+      <c r="C793" s="2">
+        <v>46280.540150462999</v>
+      </c>
+      <c r="D793" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="E793" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F793" s="5">
+        <v>38508</v>
+      </c>
+      <c r="G793" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H793" s="1"/>
+      <c r="I793" s="1"/>
+      <c r="J793" s="1"/>
+      <c r="K793" s="1"/>
+      <c r="L793" s="1"/>
+      <c r="M793" s="1"/>
+      <c r="N793" s="1"/>
+      <c r="O793" s="1"/>
+      <c r="P793" s="1"/>
+      <c r="Q793" s="1"/>
+      <c r="R793" s="1"/>
+      <c r="S793" s="1"/>
+      <c r="T793" s="1"/>
+      <c r="U793" s="1"/>
+      <c r="V793" s="3"/>
+      <c r="W793" s="3"/>
+      <c r="X793" s="1"/>
+      <c r="Y793" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z793" s="1"/>
+      <c r="AA793" s="1"/>
+      <c r="AB793" s="1"/>
+    </row>
+    <row r="794" spans="1:28">
+      <c r="A794" s="5">
+        <v>815</v>
+      </c>
+      <c r="B794" s="2">
+        <v>46280.547037037002</v>
+      </c>
+      <c r="C794" s="2">
+        <v>46280.549768518496</v>
+      </c>
+      <c r="D794" s="1" t="s">
+        <v>862</v>
+      </c>
+      <c r="E794" s="1" t="s">
+        <v>863</v>
+      </c>
+      <c r="F794" s="5">
+        <v>38414</v>
+      </c>
+      <c r="G794" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H794" s="1"/>
+      <c r="I794" s="1"/>
+      <c r="J794" s="1"/>
+      <c r="K794" s="1"/>
+      <c r="L794" s="1"/>
+      <c r="M794" s="1"/>
+      <c r="N794" s="1"/>
+      <c r="O794" s="1"/>
+      <c r="P794" s="1"/>
+      <c r="Q794" s="1"/>
+      <c r="R794" s="1"/>
+      <c r="S794" s="1"/>
+      <c r="T794" s="1"/>
+      <c r="U794" s="1"/>
+      <c r="V794" s="3"/>
+      <c r="W794" s="3"/>
+      <c r="X794" s="1"/>
+      <c r="Y794" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z794" s="1" t="s">
+        <v>1133</v>
+      </c>
+      <c r="AA794" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB794" s="1" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="795" spans="1:28">
+      <c r="A795" s="5">
+        <v>816</v>
+      </c>
+      <c r="B795" s="2">
+        <v>46280.441064814797</v>
+      </c>
+      <c r="C795" s="2">
+        <v>46280.5559027778</v>
+      </c>
+      <c r="D795" s="1" t="s">
+        <v>936</v>
+      </c>
+      <c r="E795" s="1" t="s">
+        <v>937</v>
+      </c>
+      <c r="F795" s="5">
+        <v>38189</v>
+      </c>
+      <c r="G795" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H795" s="1"/>
+      <c r="I795" s="1"/>
+      <c r="J795" s="1"/>
+      <c r="K795" s="1"/>
+      <c r="L795" s="1"/>
+      <c r="M795" s="1"/>
+      <c r="N795" s="1"/>
+      <c r="O795" s="1"/>
+      <c r="P795" s="1"/>
+      <c r="Q795" s="1"/>
+      <c r="R795" s="1"/>
+      <c r="S795" s="1"/>
+      <c r="T795" s="1"/>
+      <c r="U795" s="1"/>
+      <c r="V795" s="3"/>
+      <c r="W795" s="3"/>
+      <c r="X795" s="1"/>
+      <c r="Y795" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z795" s="1" t="s">
+        <v>1095</v>
+      </c>
+      <c r="AA795" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB795" s="1" t="s">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="796" spans="1:28">
+      <c r="A796" s="5">
+        <v>817</v>
+      </c>
+      <c r="B796" s="2">
+        <v>46280.612141203703</v>
+      </c>
+      <c r="C796" s="2">
+        <v>46280.612546296303</v>
+      </c>
+      <c r="D796" s="1" t="s">
+        <v>311</v>
+      </c>
+      <c r="E796" s="1" t="s">
+        <v>312</v>
+      </c>
+      <c r="F796" s="5">
+        <v>38456</v>
+      </c>
+      <c r="G796" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H796" s="1"/>
+      <c r="I796" s="1"/>
+      <c r="J796" s="1"/>
+      <c r="K796" s="1"/>
+      <c r="L796" s="1"/>
+      <c r="M796" s="1"/>
+      <c r="N796" s="1"/>
+      <c r="O796" s="1"/>
+      <c r="P796" s="1"/>
+      <c r="Q796" s="1"/>
+      <c r="R796" s="1"/>
+      <c r="S796" s="1"/>
+      <c r="T796" s="1"/>
+      <c r="U796" s="1"/>
+      <c r="V796" s="3"/>
+      <c r="W796" s="3"/>
+      <c r="X796" s="1"/>
+      <c r="Y796" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z796" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA796" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB796" s="1" t="s">
+        <v>1215</v>
+      </c>
+    </row>
+    <row r="797" spans="1:28">
+      <c r="A797" s="5">
+        <v>818</v>
+      </c>
+      <c r="B797" s="2">
+        <v>46280.6394560185</v>
+      </c>
+      <c r="C797" s="2">
+        <v>46280.6401273148</v>
+      </c>
+      <c r="D797" s="1" t="s">
+        <v>888</v>
+      </c>
+      <c r="E797" s="1" t="s">
+        <v>889</v>
+      </c>
+      <c r="F797" s="5">
+        <v>38534</v>
+      </c>
+      <c r="G797" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H797" s="1"/>
+      <c r="I797" s="1"/>
+      <c r="J797" s="1"/>
+      <c r="K797" s="1"/>
+      <c r="L797" s="1"/>
+      <c r="M797" s="1"/>
+      <c r="N797" s="1"/>
+      <c r="O797" s="1"/>
+      <c r="P797" s="1"/>
+      <c r="Q797" s="1"/>
+      <c r="R797" s="1"/>
+      <c r="S797" s="1"/>
+      <c r="T797" s="1"/>
+      <c r="U797" s="1"/>
+      <c r="V797" s="3"/>
+      <c r="W797" s="3"/>
+      <c r="X797" s="1"/>
+      <c r="Y797" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z797" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AA797" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB797" s="1" t="s">
+        <v>1216</v>
+      </c>
+    </row>
+    <row r="798" spans="1:28">
+      <c r="A798" s="5">
+        <v>819</v>
+      </c>
+      <c r="B798" s="2">
+        <v>46280.651562500003</v>
+      </c>
+      <c r="C798" s="2">
+        <v>46280.652534722198</v>
+      </c>
+      <c r="D798" s="1" t="s">
+        <v>964</v>
+      </c>
+      <c r="E798" s="1" t="s">
+        <v>965</v>
+      </c>
+      <c r="F798" s="5">
+        <v>38148</v>
+      </c>
+      <c r="G798" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H798" s="1"/>
+      <c r="I798" s="1"/>
+      <c r="J798" s="1"/>
+      <c r="K798" s="1"/>
+      <c r="L798" s="1"/>
+      <c r="M798" s="1"/>
+      <c r="N798" s="1"/>
+      <c r="O798" s="1"/>
+      <c r="P798" s="1"/>
+      <c r="Q798" s="1"/>
+      <c r="R798" s="1"/>
+      <c r="S798" s="1"/>
+      <c r="T798" s="1"/>
+      <c r="U798" s="1"/>
+      <c r="V798" s="3"/>
+      <c r="W798" s="3"/>
+      <c r="X798" s="1"/>
+      <c r="Y798" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z798" s="1"/>
+      <c r="AA798" s="1"/>
+      <c r="AB798" s="1"/>
+    </row>
+    <row r="799" spans="1:28">
+      <c r="A799" s="5">
+        <v>820</v>
+      </c>
+      <c r="B799" s="2">
+        <v>46280.642569444397</v>
+      </c>
+      <c r="C799" s="2">
+        <v>46280.657476851797</v>
+      </c>
+      <c r="D799" s="1" t="s">
+        <v>1217</v>
+      </c>
+      <c r="E799" s="1" t="s">
+        <v>1218</v>
+      </c>
+      <c r="F799" s="5">
+        <v>38749</v>
+      </c>
+      <c r="G799" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H799" s="1"/>
+      <c r="I799" s="1"/>
+      <c r="J799" s="1"/>
+      <c r="K799" s="1"/>
+      <c r="L799" s="1"/>
+      <c r="M799" s="1"/>
+      <c r="N799" s="1"/>
+      <c r="O799" s="1"/>
+      <c r="P799" s="1"/>
+      <c r="Q799" s="1"/>
+      <c r="R799" s="1"/>
+      <c r="S799" s="1"/>
+      <c r="T799" s="1"/>
+      <c r="U799" s="1"/>
+      <c r="V799" s="3"/>
+      <c r="W799" s="3"/>
+      <c r="X799" s="1"/>
+      <c r="Y799" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z799" s="1"/>
+      <c r="AA799" s="1"/>
+      <c r="AB799" s="1"/>
+    </row>
+    <row r="800" spans="1:28">
+      <c r="A800" s="5">
+        <v>821</v>
+      </c>
+      <c r="B800" s="2">
+        <v>46280.6613194444</v>
+      </c>
+      <c r="C800" s="2">
+        <v>46280.6616782407</v>
+      </c>
+      <c r="D800" s="1" t="s">
+        <v>1052</v>
+      </c>
+      <c r="E800" s="1" t="s">
+        <v>1053</v>
+      </c>
+      <c r="F800" s="5">
+        <v>60036</v>
+      </c>
+      <c r="G800" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H800" s="1"/>
+      <c r="I800" s="1"/>
+      <c r="J800" s="1"/>
+      <c r="K800" s="1"/>
+      <c r="L800" s="1"/>
+      <c r="M800" s="1"/>
+      <c r="N800" s="1"/>
+      <c r="O800" s="1"/>
+      <c r="P800" s="1"/>
+      <c r="Q800" s="1"/>
+      <c r="R800" s="1"/>
+      <c r="S800" s="1"/>
+      <c r="T800" s="1"/>
+      <c r="U800" s="1"/>
+      <c r="V800" s="3"/>
+      <c r="W800" s="3"/>
+      <c r="X800" s="1"/>
+      <c r="Y800" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z800" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA800" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB800" s="1" t="s">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="801" spans="1:28">
+      <c r="A801" s="5">
+        <v>822</v>
+      </c>
+      <c r="B801" s="2">
+        <v>46280.682361111103</v>
+      </c>
+      <c r="C801" s="2">
+        <v>46280.682615740698</v>
+      </c>
+      <c r="D801" s="1" t="s">
+        <v>786</v>
+      </c>
+      <c r="E801" s="1" t="s">
+        <v>787</v>
+      </c>
+      <c r="F801" s="5">
+        <v>38225</v>
+      </c>
+      <c r="G801" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H801" s="1"/>
+      <c r="I801" s="1"/>
+      <c r="J801" s="1"/>
+      <c r="K801" s="1"/>
+      <c r="L801" s="1"/>
+      <c r="M801" s="1"/>
+      <c r="N801" s="1"/>
+      <c r="O801" s="1"/>
+      <c r="P801" s="1"/>
+      <c r="Q801" s="1"/>
+      <c r="R801" s="1"/>
+      <c r="S801" s="1"/>
+      <c r="T801" s="1"/>
+      <c r="U801" s="1"/>
+      <c r="V801" s="3"/>
+      <c r="W801" s="3"/>
+      <c r="X801" s="1"/>
+      <c r="Y801" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z801" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA801" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB801" s="1" t="s">
+        <v>1220</v>
+      </c>
+    </row>
+    <row r="802" spans="1:28">
+      <c r="A802" s="5">
+        <v>823</v>
+      </c>
+      <c r="B802" s="2">
+        <v>46280.7434953704</v>
+      </c>
+      <c r="C802" s="2">
+        <v>46280.745844907397</v>
+      </c>
+      <c r="D802" s="1" t="s">
+        <v>1058</v>
+      </c>
+      <c r="E802" s="1" t="s">
+        <v>1059</v>
+      </c>
+      <c r="F802" s="5">
+        <v>38150</v>
+      </c>
+      <c r="G802" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H802" s="1"/>
+      <c r="I802" s="1"/>
+      <c r="J802" s="1"/>
+      <c r="K802" s="1"/>
+      <c r="L802" s="1"/>
+      <c r="M802" s="1"/>
+      <c r="N802" s="1"/>
+      <c r="O802" s="1"/>
+      <c r="P802" s="1"/>
+      <c r="Q802" s="1"/>
+      <c r="R802" s="1"/>
+      <c r="S802" s="1"/>
+      <c r="T802" s="1"/>
+      <c r="U802" s="1"/>
+      <c r="V802" s="3"/>
+      <c r="W802" s="3"/>
+      <c r="X802" s="1"/>
+      <c r="Y802" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z802" s="1" t="s">
+        <v>1098</v>
+      </c>
+      <c r="AA802" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="AB802" s="1" t="s">
+        <v>1221</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S71" r:id="rId1" xr:uid="{DBEDA7D9-6C97-43FD-AB0F-DEBA1D8AA177}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="97" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9E6E762B-130D-465E-A604-B2AFEF08CD24}"/>
+  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E2D931-3C1E-41A2-93B7-07FD783090E1}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3795" uniqueCount="1222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3803" uniqueCount="1223">
   <si>
     <t>Id</t>
   </si>
@@ -3702,6 +3702,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/image_Starbucks%20Ford%20Santa.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/107cf806-49c3-43fb-a769-5462a9942c26_Starbucks%20Samara%20Sat.jpeg</t>
   </si>
 </sst>
 </file>
@@ -3853,8 +3856,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB802" totalsRowShown="0">
-  <autoFilter ref="A1:AB802" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB804" totalsRowShown="0">
+  <autoFilter ref="A1:AB804" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="25">
       <extLst>
@@ -4056,7 +4059,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="823" latestEventMarker="1147">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="825" latestEventMarker="1149">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4388,7 +4391,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB802"/>
+  <dimension ref="A1:AB804"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -39905,7 +39908,7 @@
       <c r="AB788" s="1"/>
     </row>
     <row r="789" spans="1:28">
-      <c r="A789" s="5">
+      <c r="A789">
         <v>810</v>
       </c>
       <c r="B789" s="2">
@@ -39920,7 +39923,7 @@
       <c r="E789" s="1" t="s">
         <v>1003</v>
       </c>
-      <c r="F789" s="5">
+      <c r="F789">
         <v>43011</v>
       </c>
       <c r="G789" s="1" t="s">
@@ -39957,7 +39960,7 @@
       </c>
     </row>
     <row r="790" spans="1:28">
-      <c r="A790" s="5">
+      <c r="A790">
         <v>811</v>
       </c>
       <c r="B790" s="2">
@@ -39972,7 +39975,7 @@
       <c r="E790" s="1" t="s">
         <v>811</v>
       </c>
-      <c r="F790" s="5">
+      <c r="F790">
         <v>38764</v>
       </c>
       <c r="G790" s="1" t="s">
@@ -40009,7 +40012,7 @@
       </c>
     </row>
     <row r="791" spans="1:28">
-      <c r="A791" s="5">
+      <c r="A791">
         <v>812</v>
       </c>
       <c r="B791" s="2">
@@ -40024,7 +40027,7 @@
       <c r="E791" s="1" t="s">
         <v>829</v>
       </c>
-      <c r="F791" s="5">
+      <c r="F791">
         <v>38439</v>
       </c>
       <c r="G791" s="1" t="s">
@@ -40061,7 +40064,7 @@
       </c>
     </row>
     <row r="792" spans="1:28">
-      <c r="A792" s="5">
+      <c r="A792">
         <v>813</v>
       </c>
       <c r="B792" s="2">
@@ -40076,7 +40079,7 @@
       <c r="E792" s="1" t="s">
         <v>873</v>
       </c>
-      <c r="F792" s="5">
+      <c r="F792">
         <v>38568</v>
       </c>
       <c r="G792" s="1" t="s">
@@ -40113,7 +40116,7 @@
       </c>
     </row>
     <row r="793" spans="1:28">
-      <c r="A793" s="5">
+      <c r="A793">
         <v>814</v>
       </c>
       <c r="B793" s="2">
@@ -40128,7 +40131,7 @@
       <c r="E793" s="1" t="s">
         <v>1013</v>
       </c>
-      <c r="F793" s="5">
+      <c r="F793">
         <v>38508</v>
       </c>
       <c r="G793" s="1" t="s">
@@ -40159,7 +40162,7 @@
       <c r="AB793" s="1"/>
     </row>
     <row r="794" spans="1:28">
-      <c r="A794" s="5">
+      <c r="A794">
         <v>815</v>
       </c>
       <c r="B794" s="2">
@@ -40174,7 +40177,7 @@
       <c r="E794" s="1" t="s">
         <v>863</v>
       </c>
-      <c r="F794" s="5">
+      <c r="F794">
         <v>38414</v>
       </c>
       <c r="G794" s="1" t="s">
@@ -40211,7 +40214,7 @@
       </c>
     </row>
     <row r="795" spans="1:28">
-      <c r="A795" s="5">
+      <c r="A795">
         <v>816</v>
       </c>
       <c r="B795" s="2">
@@ -40226,7 +40229,7 @@
       <c r="E795" s="1" t="s">
         <v>937</v>
       </c>
-      <c r="F795" s="5">
+      <c r="F795">
         <v>38189</v>
       </c>
       <c r="G795" s="1" t="s">
@@ -40263,7 +40266,7 @@
       </c>
     </row>
     <row r="796" spans="1:28">
-      <c r="A796" s="5">
+      <c r="A796">
         <v>817</v>
       </c>
       <c r="B796" s="2">
@@ -40278,7 +40281,7 @@
       <c r="E796" s="1" t="s">
         <v>312</v>
       </c>
-      <c r="F796" s="5">
+      <c r="F796">
         <v>38456</v>
       </c>
       <c r="G796" s="1" t="s">
@@ -40315,7 +40318,7 @@
       </c>
     </row>
     <row r="797" spans="1:28">
-      <c r="A797" s="5">
+      <c r="A797">
         <v>818</v>
       </c>
       <c r="B797" s="2">
@@ -40330,7 +40333,7 @@
       <c r="E797" s="1" t="s">
         <v>889</v>
       </c>
-      <c r="F797" s="5">
+      <c r="F797">
         <v>38534</v>
       </c>
       <c r="G797" s="1" t="s">
@@ -40367,7 +40370,7 @@
       </c>
     </row>
     <row r="798" spans="1:28">
-      <c r="A798" s="5">
+      <c r="A798">
         <v>819</v>
       </c>
       <c r="B798" s="2">
@@ -40382,7 +40385,7 @@
       <c r="E798" s="1" t="s">
         <v>965</v>
       </c>
-      <c r="F798" s="5">
+      <c r="F798">
         <v>38148</v>
       </c>
       <c r="G798" s="1" t="s">
@@ -40413,7 +40416,7 @@
       <c r="AB798" s="1"/>
     </row>
     <row r="799" spans="1:28">
-      <c r="A799" s="5">
+      <c r="A799">
         <v>820</v>
       </c>
       <c r="B799" s="2">
@@ -40428,7 +40431,7 @@
       <c r="E799" s="1" t="s">
         <v>1218</v>
       </c>
-      <c r="F799" s="5">
+      <c r="F799">
         <v>38749</v>
       </c>
       <c r="G799" s="1" t="s">
@@ -40459,7 +40462,7 @@
       <c r="AB799" s="1"/>
     </row>
     <row r="800" spans="1:28">
-      <c r="A800" s="5">
+      <c r="A800">
         <v>821</v>
       </c>
       <c r="B800" s="2">
@@ -40474,7 +40477,7 @@
       <c r="E800" s="1" t="s">
         <v>1053</v>
       </c>
-      <c r="F800" s="5">
+      <c r="F800">
         <v>60036</v>
       </c>
       <c r="G800" s="1" t="s">
@@ -40511,7 +40514,7 @@
       </c>
     </row>
     <row r="801" spans="1:28">
-      <c r="A801" s="5">
+      <c r="A801">
         <v>822</v>
       </c>
       <c r="B801" s="2">
@@ -40526,7 +40529,7 @@
       <c r="E801" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="F801" s="5">
+      <c r="F801">
         <v>38225</v>
       </c>
       <c r="G801" s="1" t="s">
@@ -40563,7 +40566,7 @@
       </c>
     </row>
     <row r="802" spans="1:28">
-      <c r="A802" s="5">
+      <c r="A802">
         <v>823</v>
       </c>
       <c r="B802" s="2">
@@ -40578,7 +40581,7 @@
       <c r="E802" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="F802" s="5">
+      <c r="F802">
         <v>38150</v>
       </c>
       <c r="G802" s="1" t="s">
@@ -40614,6 +40617,98 @@
         <v>1221</v>
       </c>
     </row>
+    <row r="803" spans="1:28">
+      <c r="A803" s="5">
+        <v>824</v>
+      </c>
+      <c r="B803" s="2">
+        <v>46280.7921180556</v>
+      </c>
+      <c r="C803" s="2">
+        <v>46280.792430555601</v>
+      </c>
+      <c r="D803" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E803" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F803" s="5">
+        <v>43152</v>
+      </c>
+      <c r="G803" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H803" s="1"/>
+      <c r="I803" s="1"/>
+      <c r="J803" s="1"/>
+      <c r="K803" s="1"/>
+      <c r="L803" s="1"/>
+      <c r="M803" s="1"/>
+      <c r="N803" s="1"/>
+      <c r="O803" s="1"/>
+      <c r="P803" s="1"/>
+      <c r="Q803" s="1"/>
+      <c r="R803" s="1"/>
+      <c r="S803" s="1"/>
+      <c r="T803" s="1"/>
+      <c r="U803" s="1"/>
+      <c r="V803" s="3"/>
+      <c r="W803" s="3"/>
+      <c r="X803" s="1"/>
+      <c r="Y803" s="1" t="s">
+        <v>341</v>
+      </c>
+      <c r="Z803" s="1"/>
+      <c r="AA803" s="1"/>
+      <c r="AB803" s="1"/>
+    </row>
+    <row r="804" spans="1:28">
+      <c r="A804" s="5">
+        <v>825</v>
+      </c>
+      <c r="B804" s="2">
+        <v>46280.793020833298</v>
+      </c>
+      <c r="C804" s="2">
+        <v>46280.793564814798</v>
+      </c>
+      <c r="D804" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="E804" s="1" t="s">
+        <v>153</v>
+      </c>
+      <c r="F804" s="5">
+        <v>43152</v>
+      </c>
+      <c r="G804" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="H804" s="1"/>
+      <c r="I804" s="1"/>
+      <c r="J804" s="1"/>
+      <c r="K804" s="1"/>
+      <c r="L804" s="1"/>
+      <c r="M804" s="1"/>
+      <c r="N804" s="1"/>
+      <c r="O804" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="P804" s="1"/>
+      <c r="Q804" s="1"/>
+      <c r="R804" s="1"/>
+      <c r="S804" s="1"/>
+      <c r="T804" s="1"/>
+      <c r="U804" s="1"/>
+      <c r="V804" s="3"/>
+      <c r="W804" s="3"/>
+      <c r="X804" s="1"/>
+      <c r="Y804" s="1"/>
+      <c r="Z804" s="1"/>
+      <c r="AA804" s="1"/>
+      <c r="AB804" s="1"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S71" r:id="rId1" xr:uid="{DBEDA7D9-6C97-43FD-AB0F-DEBA1D8AA177}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30502"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30516"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="100" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8E2D931-3C1E-41A2-93B7-07FD783090E1}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{60B1AF1E-5F41-4563-9E22-0AF0C74BA010}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3803" uniqueCount="1223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3810" uniqueCount="1224">
   <si>
     <t>Id</t>
   </si>
@@ -3705,6 +3705,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/107cf806-49c3-43fb-a769-5462a9942c26_Starbucks%20Samara%20Sat.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Jarras_Blender_%26_Cold_Foam/d4ccda8e-87f0-4f41-9da8-14975f266916_Starbucks%20CEMTRAM%204.jpeg</t>
   </si>
 </sst>
 </file>
@@ -3856,8 +3859,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB804" totalsRowShown="0">
-  <autoFilter ref="A1:AB804" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AB805" totalsRowShown="0">
+  <autoFilter ref="A1:AB805" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="28">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="25">
       <extLst>
@@ -4059,7 +4062,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="825" latestEventMarker="1149">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="826" latestEventMarker="1150">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -4391,7 +4394,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB804"/>
+  <dimension ref="A1:AB805"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -40618,7 +40621,7 @@
       </c>
     </row>
     <row r="803" spans="1:28">
-      <c r="A803" s="5">
+      <c r="A803">
         <v>824</v>
       </c>
       <c r="B803" s="2">
@@ -40633,7 +40636,7 @@
       <c r="E803" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F803" s="5">
+      <c r="F803">
         <v>43152</v>
       </c>
       <c r="G803" s="1" t="s">
@@ -40664,7 +40667,7 @@
       <c r="AB803" s="1"/>
     </row>
     <row r="804" spans="1:28">
-      <c r="A804" s="5">
+      <c r="A804">
         <v>825</v>
       </c>
       <c r="B804" s="2">
@@ -40679,7 +40682,7 @@
       <c r="E804" s="1" t="s">
         <v>153</v>
       </c>
-      <c r="F804" s="5">
+      <c r="F804">
         <v>43152</v>
       </c>
       <c r="G804" s="1" t="s">
@@ -40709,6 +40712,58 @@
       <c r="AA804" s="1"/>
       <c r="AB804" s="1"/>
     </row>
+    <row r="805" spans="1:28">
+      <c r="A805" s="5">
+        <v>826</v>
+      </c>
+      <c r="B805" s="2">
+        <v>46282.497013888897</v>
+      </c>
+      <c r="C805" s="2">
+        <v>46282.4978819444</v>
+      </c>
+      <c r="D805" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="E805" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="F805" s="5">
+        <v>38695</v>
+      </c>
+      <c r="G805" s="1" t="s">
+        <v>1094</v>
+      </c>
+      <c r="H805" s="1"/>
+      <c r="I805" s="1"/>
+      <c r="J805" s="1"/>
+      <c r="K805" s="1"/>
+      <c r="L805" s="1"/>
+      <c r="M805" s="1"/>
+      <c r="N805" s="1"/>
+      <c r="O805" s="1"/>
+      <c r="P805" s="1"/>
+      <c r="Q805" s="1"/>
+      <c r="R805" s="1"/>
+      <c r="S805" s="1"/>
+      <c r="T805" s="1"/>
+      <c r="U805" s="1"/>
+      <c r="V805" s="3"/>
+      <c r="W805" s="3"/>
+      <c r="X805" s="1"/>
+      <c r="Y805" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="Z805" s="1" t="s">
+        <v>1194</v>
+      </c>
+      <c r="AA805" s="1" t="s">
+        <v>1096</v>
+      </c>
+      <c r="AB805" s="1" t="s">
+        <v>1223</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="S71" r:id="rId1" xr:uid="{DBEDA7D9-6C97-43FD-AB0F-DEBA1D8AA177}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D8AA767-0C89-4813-A69C-896B5041381F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4F42714-7AA2-4E21-8B9E-13738833D1A2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
   <si>
     <t>Id</t>
   </si>
@@ -118,6 +118,93 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Lucy_24Sep/17897057552931957226119787917932_Enrique%20Cesar%20Flores.jpg</t>
+  </si>
+  <si>
+    <t>johan.arellano@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Johan Arellano Navarro</t>
+  </si>
+  <si>
+    <t>Mandil Verde</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Johan%20Arellano%20Navar.jpg</t>
+  </si>
+  <si>
+    <t>fany.jeovana@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Fany Jeovana Echeverria Beristain</t>
+  </si>
+  <si>
+    <t>Community Board</t>
+  </si>
+  <si>
+    <t>No </t>
+  </si>
+  <si>
+    <t>ricardo.romo@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Ricardo Romo Morales</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Ricardo%20Romo%20Morales.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38661@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Jinetes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_8216_Starbucks%20Jinetes.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38925@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Star Medica Lomas Verdes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_1748_Starbucks%20Star%20Medic.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43043@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Atizapan</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/a65fc51a-a078-45b3-b3fe-dc146bb64aae_Starbucks%20Atizapan.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38115@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Zona Azul</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/PEANUTS_Starbucks%20Zona%20Azul.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38674@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Mundo E</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17897885365583498999874107265144_Starbucks%20Mundo%20E.jpg</t>
+  </si>
+  <si>
+    <t>maria.reyesr@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Reyes Rivera</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_6412_Maria%20Fernanda%20Reyes.jpeg</t>
   </si>
 </sst>
 </file>
@@ -153,13 +240,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -236,8 +324,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U3" totalsRowShown="0">
-  <autoFilter ref="A1:U3" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U12" totalsRowShown="0">
+  <autoFilter ref="A1:U12" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -390,7 +478,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="828" latestEventMarker="1211">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="837" latestEventMarker="1220">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -715,16 +803,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="37.5703125" customWidth="1"/>
     <col min="5" max="5" width="22.5703125" customWidth="1"/>
-    <col min="6" max="20" width="20" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19" customWidth="1"/>
+    <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.5703125" customWidth="1"/>
+    <col min="8" max="20" width="20" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="30.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="45.75">
+    <row r="1" spans="1:21" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -866,6 +957,350 @@
         <v>26</v>
       </c>
     </row>
+    <row r="4" spans="1:21">
+      <c r="A4">
+        <v>829</v>
+      </c>
+      <c r="B4" s="1">
+        <v>46283.553090277797</v>
+      </c>
+      <c r="C4" s="1">
+        <v>46283.553935185198</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F4">
+        <v>43164</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+    </row>
+    <row r="5" spans="1:21">
+      <c r="A5">
+        <v>830</v>
+      </c>
+      <c r="B5" s="1">
+        <v>46283.5710300926</v>
+      </c>
+      <c r="C5" s="1">
+        <v>46283.5727430556</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="F5">
+        <v>38529</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+    </row>
+    <row r="6" spans="1:21">
+      <c r="A6">
+        <v>831</v>
+      </c>
+      <c r="B6" s="1">
+        <v>46283.706562500003</v>
+      </c>
+      <c r="C6" s="1">
+        <v>46283.708009259302</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6">
+        <v>38431</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21">
+      <c r="A7">
+        <v>832</v>
+      </c>
+      <c r="B7" s="1">
+        <v>46283.726446759298</v>
+      </c>
+      <c r="C7" s="1">
+        <v>46283.727754629603</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7">
+        <v>38661</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21">
+      <c r="A8">
+        <v>833</v>
+      </c>
+      <c r="B8" s="1">
+        <v>46283.741875</v>
+      </c>
+      <c r="C8" s="1">
+        <v>46283.742245370398</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F8">
+        <v>38925</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21">
+      <c r="A9">
+        <v>834</v>
+      </c>
+      <c r="B9" s="1">
+        <v>46283.752060185201</v>
+      </c>
+      <c r="C9" s="1">
+        <v>46283.752372685201</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F9">
+        <v>43043</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21">
+      <c r="A10">
+        <v>835</v>
+      </c>
+      <c r="B10" s="1">
+        <v>46283.816099536998</v>
+      </c>
+      <c r="C10" s="1">
+        <v>46283.819976851897</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="F10">
+        <v>38115</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21">
+      <c r="A11" s="4">
+        <v>836</v>
+      </c>
+      <c r="B11" s="1">
+        <v>46283.895046296297</v>
+      </c>
+      <c r="C11" s="1">
+        <v>46283.895983796298</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F11" s="4">
+        <v>38674</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="U11" s="4"/>
+    </row>
+    <row r="12" spans="1:21">
+      <c r="A12" s="4">
+        <v>837</v>
+      </c>
+      <c r="B12" s="1">
+        <v>46283.913402777798</v>
+      </c>
+      <c r="C12" s="1">
+        <v>46283.913958333302</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F12" s="4">
+        <v>38535</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="U12" s="4"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4F42714-7AA2-4E21-8B9E-13738833D1A2}"/>
+  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7596476-817A-47F5-A7AF-6F62986322F5}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="94">
   <si>
     <t>Id</t>
   </si>
@@ -205,6 +205,120 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_6412_Maria%20Fernanda%20Reyes.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38590@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Parque Toreo ll</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Parque%20Tor.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38862@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San Miguel Izcalli</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/20260919_094055-COLLAGE_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38136@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Punta Norte</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Punta%20Nort.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38197@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Echegaray</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Echegaray.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38606@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Tlalnepantla Carso</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_3010_Starbucks%20Tlalnepant.jpeg</t>
+  </si>
+  <si>
+    <t>brenda.menez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Brenda Ashanti Menez Ramos</t>
+  </si>
+  <si>
+    <t>Señaletica Back</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/AB703D04-AD60-4AE3-A9C2-93EB1A71C261_Brenda%20Ashanti%20Menez.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38230@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks ITESM Estado de Mexico</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17898438187058878408397336163510_Starbucks%20ITESM%20Esta.jpg</t>
+  </si>
+  <si>
+    <t>Señaletica Lobby</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/89984835-C593-46A6-9527-537EB05F3009_Brenda%20Ashanti%20Menez.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_7784_Brenda%20Ashanti%20Menez.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38117@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Satelite</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_5957_Starbucks%20Satelite.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38475@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Satélite Centro Cívico</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Sat%C3%A9lite%20C.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38333@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Mega Izcalli</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/66A229BD-727D-4586-A367-B22618495CAA_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>Jarras Blender | Cold Foam</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_8223_Starbucks%20Mega%20Izcal.jpeg</t>
   </si>
 </sst>
 </file>
@@ -240,7 +354,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -248,6 +362,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -324,8 +439,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U12" totalsRowShown="0">
-  <autoFilter ref="A1:U12" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U25" totalsRowShown="0">
+  <autoFilter ref="A1:U25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="21">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
       <extLst>
@@ -478,7 +593,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="837" latestEventMarker="1220">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="850" latestEventMarker="1233">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -803,7 +918,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -1224,7 +1339,7 @@
       </c>
     </row>
     <row r="11" spans="1:21">
-      <c r="A11" s="4">
+      <c r="A11">
         <v>836</v>
       </c>
       <c r="B11" s="1">
@@ -1239,7 +1354,7 @@
       <c r="E11" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11">
         <v>38674</v>
       </c>
       <c r="G11" s="2" t="s">
@@ -1260,10 +1375,9 @@
       <c r="T11" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="U11" s="4"/>
     </row>
     <row r="12" spans="1:21">
-      <c r="A12" s="4">
+      <c r="A12">
         <v>837</v>
       </c>
       <c r="B12" s="1">
@@ -1278,7 +1392,7 @@
       <c r="E12" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12">
         <v>38535</v>
       </c>
       <c r="G12" s="2" t="s">
@@ -1299,7 +1413,517 @@
       <c r="T12" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="U12" s="4"/>
+    </row>
+    <row r="13" spans="1:21">
+      <c r="A13" s="4">
+        <v>838</v>
+      </c>
+      <c r="B13" s="1">
+        <v>46284.395671296297</v>
+      </c>
+      <c r="C13" s="1">
+        <v>46284.398645833302</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="4">
+        <v>38590</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="U13" s="4"/>
+    </row>
+    <row r="14" spans="1:21">
+      <c r="A14" s="4">
+        <v>839</v>
+      </c>
+      <c r="B14" s="1">
+        <v>46284.4004166667</v>
+      </c>
+      <c r="C14" s="1">
+        <v>46284.404386574097</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="F14" s="4">
+        <v>38862</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="U14" s="4"/>
+    </row>
+    <row r="15" spans="1:21">
+      <c r="A15" s="4">
+        <v>840</v>
+      </c>
+      <c r="B15" s="1">
+        <v>46284.4081828704</v>
+      </c>
+      <c r="C15" s="1">
+        <v>46284.409502314797</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F15" s="4">
+        <v>38136</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="U15" s="4"/>
+    </row>
+    <row r="16" spans="1:21">
+      <c r="A16" s="4">
+        <v>841</v>
+      </c>
+      <c r="B16" s="1">
+        <v>46284.432268518503</v>
+      </c>
+      <c r="C16" s="1">
+        <v>46284.433622685203</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="4">
+        <v>38197</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="U16" s="4"/>
+    </row>
+    <row r="17" spans="1:21">
+      <c r="A17" s="4">
+        <v>842</v>
+      </c>
+      <c r="B17" s="1">
+        <v>46284.497638888897</v>
+      </c>
+      <c r="C17" s="1">
+        <v>46284.530243055597</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="4">
+        <v>38606</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="U17" s="4"/>
+    </row>
+    <row r="18" spans="1:21">
+      <c r="A18" s="4">
+        <v>843</v>
+      </c>
+      <c r="B18" s="1">
+        <v>46284.532268518502</v>
+      </c>
+      <c r="C18" s="1">
+        <v>46284.533553240697</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F18" s="4">
+        <v>38458</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="4"/>
+    </row>
+    <row r="19" spans="1:21">
+      <c r="A19" s="4">
+        <v>844</v>
+      </c>
+      <c r="B19" s="1">
+        <v>46284.534872685203</v>
+      </c>
+      <c r="C19" s="1">
+        <v>46284.535138888903</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F19" s="4">
+        <v>38230</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="U19" s="4"/>
+    </row>
+    <row r="20" spans="1:21">
+      <c r="A20" s="4">
+        <v>845</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46284.533622685201</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46284.542465277802</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="4">
+        <v>38458</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="4"/>
+    </row>
+    <row r="21" spans="1:21">
+      <c r="A21" s="4">
+        <v>846</v>
+      </c>
+      <c r="B21" s="1">
+        <v>46284.542500000003</v>
+      </c>
+      <c r="C21" s="1">
+        <v>46284.564814814803</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="F21" s="4">
+        <v>38458</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="U21" s="4"/>
+    </row>
+    <row r="22" spans="1:21">
+      <c r="A22" s="4">
+        <v>847</v>
+      </c>
+      <c r="B22" s="1">
+        <v>46284.579421296301</v>
+      </c>
+      <c r="C22" s="1">
+        <v>46284.579930555599</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" s="4">
+        <v>38117</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="U22" s="4"/>
+    </row>
+    <row r="23" spans="1:21">
+      <c r="A23" s="4">
+        <v>848</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46284.593229166698</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46284.5954166667</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F23" s="4">
+        <v>38475</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="U23" s="4"/>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="4">
+        <v>849</v>
+      </c>
+      <c r="B24" s="1">
+        <v>46284.594722222202</v>
+      </c>
+      <c r="C24" s="1">
+        <v>46284.597175925897</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F24" s="4">
+        <v>38333</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="4"/>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="4">
+        <v>850</v>
+      </c>
+      <c r="B25" s="1">
+        <v>46284.598599536999</v>
+      </c>
+      <c r="C25" s="1">
+        <v>46284.600231481498</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="4">
+        <v>38333</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="5" t="s">
+        <v>91</v>
+      </c>
+      <c r="R25" s="5" t="s">
+        <v>92</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="T25" s="2"/>
+      <c r="U25" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="27" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F7596476-817A-47F5-A7AF-6F62986322F5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFDD2D91-9718-4642-9A64-0CBE1E9692D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="100">
   <si>
     <t>Id</t>
   </si>
@@ -102,6 +102,10 @@
 </t>
   </si>
   <si>
+    <t xml:space="preserve">Evidencia_Organizacion_Refrigeradores_Back
+</t>
+  </si>
+  <si>
     <t>enrique.cesar@starbucks.com.mx</t>
   </si>
   <si>
@@ -319,6 +323,21 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_8223_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38995@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Encuentro Oceania II</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17898530673955615463134915162659_Starbucks%20Encuentro.jpg</t>
+  </si>
+  <si>
+    <t>Organización Refrigeradores Back</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/ChatGPT%20Image%2019%20sept%202026,%2015_22_18_Enrique%20Cesar%20Flores.png</t>
   </si>
 </sst>
 </file>
@@ -354,20 +373,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="19">
+  <dxfs count="20">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -439,10 +464,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:U25" totalsRowShown="0">
-  <autoFilter ref="A1:U25" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="21">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="18">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:V27" totalsRowShown="0">
+  <autoFilter ref="A1:V27" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="22">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="19">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -463,129 +488,136 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="17">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="18">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="16">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="15">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rb0262b9096064c5b809bdb94d2ffbed9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="14">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa200a7d03cc4a5fa91df03bac2ecf7a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="¿ Tu Tienda Aplica para Rack FHW?" dataDxfId="13">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="¿ Tu Tienda Aplica para Rack FHW?" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r18aa3467d7cf4ef2811cfac4f7798871"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Rack_FHW" dataDxfId="12">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Rack_FHW" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r722c7f4f41104c68940ef96a05bac24d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Max&amp;Min " dataDxfId="11">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Max&amp;Min " dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7e20bda30db04cc2a60f0888364bbb7b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_Mandil Verde" dataDxfId="10">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_Mandil Verde" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9b9e86be8d8a48a79e9701b423e28c21"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Lay_Out" dataDxfId="9">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Lay_Out" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5be890f9c9be4de4ba1736dba059b880"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="¿Cuentas con Community Board?" dataDxfId="8">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="¿Cuentas con Community Board?" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r142174aa4f64470ba655c0b540426c92"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Community_Board" dataDxfId="7">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Community_Board" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r31182c58e8f644128524d5583789a1ac"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Señaletica_Back" dataDxfId="6">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Señaletica_Back" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra7c6c4f162914976b398169c5d7ab4d9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidencia_Señaletica_Lobby" dataDxfId="5">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidencia_Señaletica_Lobby" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rcc34e060c9c54a4080b7790436eec34b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Jarra Blender" dataDxfId="4">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Jarra Blender" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7642d63c42e645aba2602bddc67421e7"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Jarras Cold Foam" dataDxfId="3">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Jarras Cold Foam" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="redfc16b0a10e4038bc37e9db0dfd5372"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Evidencia_Jarras_Blender_&amp;_Cold_Foam" dataDxfId="2">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Evidencia_Jarras_Blender_&amp;_Cold_Foam" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6e195f182c384a539b6062a655e437a4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Evidencia_Peanuts_Charly&amp;Lucy" dataDxfId="1">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Evidencia_Peanuts_Charly&amp;Lucy" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r389c34ea624f473d949b2c522d03c6c5"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{7F2E7CEA-564B-42A6-878F-57B35A9A0758}" name="Evidencia_Peanuts_Linus&amp;Snoopy_x000a_" dataDxfId="0">
+    <tableColumn id="21" xr3:uid="{7F2E7CEA-564B-42A6-878F-57B35A9A0758}" name="Evidencia_Peanuts_Linus&amp;Snoopy_x000a_" dataDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r814eb9c763f442ceb8102830ec06c1b4"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="22" xr3:uid="{8103E8D4-7A3A-4EAB-9703-3EFD9DEFB997}" name="Evidencia_Organizacion_Refrigeradores_Back_x000a_" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r5e3143c71cab4402900fedf974331b74"/>
         </ext>
       </extLst>
     </tableColumn>
@@ -593,7 +625,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="850" latestEventMarker="1233">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="852" latestEventMarker="1240">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -615,6 +647,7 @@
         <xlmsforms:syncedQuestionId>r6e195f182c384a539b6062a655e437a4</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r389c34ea624f473d949b2c522d03c6c5</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r814eb9c763f442ceb8102830ec06c1b4</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r5e3143c71cab4402900fedf974331b74</xlmsforms:syncedQuestionId>
       </xlmsforms:msForm>
     </ext>
   </extLst>
@@ -918,7 +951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:V27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -928,9 +961,10 @@
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="20" width="20" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="30.28515625" customWidth="1"/>
+    <col min="22" max="22" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" ht="30" customHeight="1">
+    <row r="1" spans="1:22" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -994,8 +1028,11 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="2" spans="1:21">
+      <c r="V1" s="5" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2">
         <v>827</v>
       </c>
@@ -1006,16 +1043,16 @@
         <v>46282.935717592598</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F2">
         <v>38371</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
@@ -1030,10 +1067,11 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21">
+        <v>25</v>
+      </c>
+      <c r="V2" s="6"/>
+    </row>
+    <row r="3" spans="1:22">
       <c r="A3">
         <v>828</v>
       </c>
@@ -1044,16 +1082,16 @@
         <v>46282.937152777798</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3">
         <v>38371</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
@@ -1069,10 +1107,11 @@
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21">
+        <v>27</v>
+      </c>
+      <c r="V3" s="6"/>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4">
         <v>829</v>
       </c>
@@ -1083,22 +1122,22 @@
         <v>46283.553935185198</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F4">
         <v>43164</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -1109,8 +1148,9 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
-    </row>
-    <row r="5" spans="1:21">
+      <c r="V4" s="6"/>
+    </row>
+    <row r="5" spans="1:22">
       <c r="A5">
         <v>830</v>
       </c>
@@ -1121,16 +1161,16 @@
         <v>46283.5727430556</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F5">
         <v>38529</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
@@ -1138,7 +1178,7 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1147,8 +1187,9 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
-    </row>
-    <row r="6" spans="1:21">
+      <c r="V5" s="6"/>
+    </row>
+    <row r="6" spans="1:22">
       <c r="A6">
         <v>831</v>
       </c>
@@ -1159,16 +1200,16 @@
         <v>46283.708009259302</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F6">
         <v>38431</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1183,10 +1224,11 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21">
+        <v>38</v>
+      </c>
+      <c r="V6" s="6"/>
+    </row>
+    <row r="7" spans="1:22">
       <c r="A7">
         <v>832</v>
       </c>
@@ -1197,16 +1239,16 @@
         <v>46283.727754629603</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F7">
         <v>38661</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -1221,10 +1263,11 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21">
+        <v>41</v>
+      </c>
+      <c r="V7" s="6"/>
+    </row>
+    <row r="8" spans="1:22">
       <c r="A8">
         <v>833</v>
       </c>
@@ -1235,16 +1278,16 @@
         <v>46283.742245370398</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>38925</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1259,10 +1302,11 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21">
+        <v>44</v>
+      </c>
+      <c r="V8" s="6"/>
+    </row>
+    <row r="9" spans="1:22">
       <c r="A9">
         <v>834</v>
       </c>
@@ -1273,16 +1317,16 @@
         <v>46283.752372685201</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9">
         <v>43043</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1297,10 +1341,11 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21">
+        <v>47</v>
+      </c>
+      <c r="V9" s="6"/>
+    </row>
+    <row r="10" spans="1:22">
       <c r="A10">
         <v>835</v>
       </c>
@@ -1311,16 +1356,16 @@
         <v>46283.819976851897</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F10">
         <v>38115</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1335,10 +1380,11 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21">
+        <v>50</v>
+      </c>
+      <c r="V10" s="6"/>
+    </row>
+    <row r="11" spans="1:22">
       <c r="A11">
         <v>836</v>
       </c>
@@ -1349,16 +1395,16 @@
         <v>46283.895983796298</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F11">
         <v>38674</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1373,10 +1419,11 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21">
+        <v>53</v>
+      </c>
+      <c r="V11" s="6"/>
+    </row>
+    <row r="12" spans="1:22">
       <c r="A12">
         <v>837</v>
       </c>
@@ -1387,16 +1434,16 @@
         <v>46283.913958333302</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F12">
         <v>38535</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1411,11 +1458,12 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="4">
+        <v>56</v>
+      </c>
+      <c r="V12" s="6"/>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="A13">
         <v>838</v>
       </c>
       <c r="B13" s="1">
@@ -1425,16 +1473,16 @@
         <v>46284.398645833302</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="4">
+        <v>58</v>
+      </c>
+      <c r="F13">
         <v>38590</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1449,12 +1497,12 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="U13" s="4"/>
-    </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="4">
+        <v>59</v>
+      </c>
+      <c r="V13" s="6"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="A14">
         <v>839</v>
       </c>
       <c r="B14" s="1">
@@ -1464,16 +1512,16 @@
         <v>46284.404386574097</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="4">
+        <v>61</v>
+      </c>
+      <c r="F14">
         <v>38862</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1488,12 +1536,12 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="U14" s="4"/>
-    </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="4">
+        <v>62</v>
+      </c>
+      <c r="V14" s="6"/>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="A15">
         <v>840</v>
       </c>
       <c r="B15" s="1">
@@ -1503,16 +1551,16 @@
         <v>46284.409502314797</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="F15" s="4">
+        <v>64</v>
+      </c>
+      <c r="F15">
         <v>38136</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1527,12 +1575,12 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="U15" s="4"/>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="4">
+        <v>65</v>
+      </c>
+      <c r="V15" s="6"/>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="A16">
         <v>841</v>
       </c>
       <c r="B16" s="1">
@@ -1542,16 +1590,16 @@
         <v>46284.433622685203</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="F16" s="4">
+        <v>67</v>
+      </c>
+      <c r="F16">
         <v>38197</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -1566,12 +1614,12 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
       <c r="T16" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="U16" s="4"/>
-    </row>
-    <row r="17" spans="1:21">
-      <c r="A17" s="4">
+        <v>68</v>
+      </c>
+      <c r="V16" s="6"/>
+    </row>
+    <row r="17" spans="1:22">
+      <c r="A17">
         <v>842</v>
       </c>
       <c r="B17" s="1">
@@ -1581,16 +1629,16 @@
         <v>46284.530243055597</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="4">
+        <v>70</v>
+      </c>
+      <c r="F17">
         <v>38606</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -1605,12 +1653,12 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="U17" s="4"/>
-    </row>
-    <row r="18" spans="1:21">
-      <c r="A18" s="4">
+        <v>71</v>
+      </c>
+      <c r="V17" s="6"/>
+    </row>
+    <row r="18" spans="1:22">
+      <c r="A18">
         <v>843</v>
       </c>
       <c r="B18" s="1">
@@ -1620,16 +1668,16 @@
         <v>46284.533553240697</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F18" s="4">
+        <v>73</v>
+      </c>
+      <c r="F18">
         <v>38458</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1639,17 +1687,17 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="P18" s="2"/>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
-      <c r="U18" s="4"/>
-    </row>
-    <row r="19" spans="1:21">
-      <c r="A19" s="4">
+      <c r="V18" s="6"/>
+    </row>
+    <row r="19" spans="1:22">
+      <c r="A19">
         <v>844</v>
       </c>
       <c r="B19" s="1">
@@ -1659,16 +1707,16 @@
         <v>46284.535138888903</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F19" s="4">
+        <v>77</v>
+      </c>
+      <c r="F19">
         <v>38230</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1683,12 +1731,12 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="U19" s="4"/>
-    </row>
-    <row r="20" spans="1:21">
-      <c r="A20" s="4">
+        <v>78</v>
+      </c>
+      <c r="V19" s="6"/>
+    </row>
+    <row r="20" spans="1:22">
+      <c r="A20">
         <v>845</v>
       </c>
       <c r="B20" s="1">
@@ -1698,16 +1746,16 @@
         <v>46284.542465277802</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="4">
+        <v>73</v>
+      </c>
+      <c r="F20">
         <v>38458</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -1718,16 +1766,16 @@
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
-      <c r="U20" s="4"/>
-    </row>
-    <row r="21" spans="1:21">
-      <c r="A21" s="4">
+      <c r="V20" s="6"/>
+    </row>
+    <row r="21" spans="1:22">
+      <c r="A21">
         <v>846</v>
       </c>
       <c r="B21" s="1">
@@ -1737,16 +1785,16 @@
         <v>46284.564814814803</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="4">
+        <v>73</v>
+      </c>
+      <c r="F21">
         <v>38458</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -1761,12 +1809,12 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="U21" s="4"/>
-    </row>
-    <row r="22" spans="1:21">
-      <c r="A22" s="4">
+        <v>81</v>
+      </c>
+      <c r="V21" s="6"/>
+    </row>
+    <row r="22" spans="1:22">
+      <c r="A22">
         <v>847</v>
       </c>
       <c r="B22" s="1">
@@ -1776,16 +1824,16 @@
         <v>46284.579930555599</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="F22" s="4">
+        <v>83</v>
+      </c>
+      <c r="F22">
         <v>38117</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -1800,12 +1848,12 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
       <c r="T22" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="U22" s="4"/>
-    </row>
-    <row r="23" spans="1:21">
-      <c r="A23" s="4">
+        <v>84</v>
+      </c>
+      <c r="V22" s="6"/>
+    </row>
+    <row r="23" spans="1:22">
+      <c r="A23">
         <v>848</v>
       </c>
       <c r="B23" s="1">
@@ -1815,16 +1863,16 @@
         <v>46284.5954166667</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="F23" s="4">
+        <v>86</v>
+      </c>
+      <c r="F23">
         <v>38475</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -1839,12 +1887,12 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
       <c r="T23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="U23" s="4"/>
-    </row>
-    <row r="24" spans="1:21">
-      <c r="A24" s="4">
+        <v>87</v>
+      </c>
+      <c r="V23" s="6"/>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24">
         <v>849</v>
       </c>
       <c r="B24" s="1">
@@ -1854,16 +1902,16 @@
         <v>46284.597175925897</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F24" s="4">
+        <v>89</v>
+      </c>
+      <c r="F24">
         <v>38333</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -1874,16 +1922,16 @@
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
       <c r="P24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
-      <c r="U24" s="4"/>
-    </row>
-    <row r="25" spans="1:21">
-      <c r="A25" s="4">
+      <c r="V24" s="6"/>
+    </row>
+    <row r="25" spans="1:22">
+      <c r="A25">
         <v>850</v>
       </c>
       <c r="B25" s="1">
@@ -1893,16 +1941,16 @@
         <v>46284.600231481498</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="F25" s="4">
+        <v>89</v>
+      </c>
+      <c r="F25">
         <v>38333</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1913,17 +1961,97 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
-      <c r="Q25" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="R25" s="5" t="s">
+      <c r="Q25" s="4" t="s">
         <v>92</v>
       </c>
+      <c r="R25" s="4" t="s">
+        <v>93</v>
+      </c>
       <c r="S25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="T25" s="2"/>
-      <c r="U25" s="4"/>
+      <c r="V25" s="6"/>
+    </row>
+    <row r="26" spans="1:22">
+      <c r="A26" s="6">
+        <v>851</v>
+      </c>
+      <c r="B26" s="1">
+        <v>46284.641678240703</v>
+      </c>
+      <c r="C26" s="1">
+        <v>46284.643020833297</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F26" s="6">
+        <v>38995</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="4"/>
+      <c r="R26" s="4"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="U26" s="6"/>
+      <c r="V26" s="6"/>
+    </row>
+    <row r="27" spans="1:22">
+      <c r="A27" s="6">
+        <v>852</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46284.646423611099</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46284.6467708333</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F27" s="6">
+        <v>38371</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="6"/>
+      <c r="V27" s="6" t="s">
+        <v>99</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CFDD2D91-9718-4642-9A64-0CBE1E9692D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{22A343D0-E4CA-4094-A17D-54B8BE0C8986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="100">
   <si>
     <t>Id</t>
   </si>
@@ -102,58 +102,47 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Evidencia_Organizacion_Refrigeradores_Back
+    <t xml:space="preserve">Evidencia_Organizacion_Refrigeradores_Back_Antes
 </t>
   </si>
   <si>
-    <t>enrique.cesar@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Enrique Cesar Flores</t>
+    <t xml:space="preserve">Evidencia_Organizacion_Refrigeradores_Back_Despues
+</t>
+  </si>
+  <si>
+    <t>johan.arellano@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Johan Arellano Navarro</t>
+  </si>
+  <si>
+    <t>Mandil Verde</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Johan%20Arellano%20Navar.jpg</t>
+  </si>
+  <si>
+    <t>fany.jeovana@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Fany Jeovana Echeverria Beristain</t>
+  </si>
+  <si>
+    <t>Community Board</t>
+  </si>
+  <si>
+    <t>No </t>
+  </si>
+  <si>
+    <t>ricardo.romo@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Ricardo Romo Morales</t>
   </si>
   <si>
     <t>Peanuts Charly&amp;Lucy</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17897056090625970350618027055472_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>Peanuts Linus&amp;Snoopy</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Lucy_24Sep/17897057552931957226119787917932_Enrique%20Cesar%20Flores.jpg</t>
-  </si>
-  <si>
-    <t>johan.arellano@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Johan Arellano Navarro</t>
-  </si>
-  <si>
-    <t>Mandil Verde</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Johan%20Arellano%20Navar.jpg</t>
-  </si>
-  <si>
-    <t>fany.jeovana@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Fany Jeovana Echeverria Beristain</t>
-  </si>
-  <si>
-    <t>Community Board</t>
-  </si>
-  <si>
-    <t>No </t>
-  </si>
-  <si>
-    <t>ricardo.romo@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Ricardo Romo Morales</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Ricardo%20Romo%20Morales.jpg</t>
   </si>
   <si>
@@ -334,20 +323,40 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17898530673955615463134915162659_Starbucks%20Encuentro.jpg</t>
   </si>
   <si>
-    <t>Organización Refrigeradores Back</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/ChatGPT%20Image%2019%20sept%202026,%2015_22_18_Enrique%20Cesar%20Flores.png</t>
+    <t>eduardo.reyes@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Eduardo David Reyes Chavez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Eduardo%20David%20Reyes.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38149@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Bellavista</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG-20260918-WA0067_Starbucks%20Bellavista.jpg</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -370,8 +379,9 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -381,15 +391,17 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="20">
+  <dxfs count="21">
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -464,10 +476,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:V27" totalsRowShown="0">
-  <autoFilter ref="A1:V27" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="22">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="19">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W26" totalsRowShown="0">
+  <autoFilter ref="A1:W26" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="23">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -488,136 +500,143 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="18">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="19">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="17">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="18">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="16">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rb0262b9096064c5b809bdb94d2ffbed9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="15">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa200a7d03cc4a5fa91df03bac2ecf7a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="¿ Tu Tienda Aplica para Rack FHW?" dataDxfId="14">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="¿ Tu Tienda Aplica para Rack FHW?" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r18aa3467d7cf4ef2811cfac4f7798871"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Rack_FHW" dataDxfId="13">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Rack_FHW" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r722c7f4f41104c68940ef96a05bac24d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Max&amp;Min " dataDxfId="12">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Max&amp;Min " dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7e20bda30db04cc2a60f0888364bbb7b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_Mandil Verde" dataDxfId="11">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_Mandil Verde" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9b9e86be8d8a48a79e9701b423e28c21"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Lay_Out" dataDxfId="10">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Lay_Out" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5be890f9c9be4de4ba1736dba059b880"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="¿Cuentas con Community Board?" dataDxfId="9">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="¿Cuentas con Community Board?" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r142174aa4f64470ba655c0b540426c92"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Community_Board" dataDxfId="8">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Community_Board" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r31182c58e8f644128524d5583789a1ac"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Señaletica_Back" dataDxfId="7">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Señaletica_Back" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra7c6c4f162914976b398169c5d7ab4d9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidencia_Señaletica_Lobby" dataDxfId="6">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidencia_Señaletica_Lobby" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rcc34e060c9c54a4080b7790436eec34b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Jarra Blender" dataDxfId="5">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Jarra Blender" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7642d63c42e645aba2602bddc67421e7"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Jarras Cold Foam" dataDxfId="4">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Jarras Cold Foam" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="redfc16b0a10e4038bc37e9db0dfd5372"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Evidencia_Jarras_Blender_&amp;_Cold_Foam" dataDxfId="3">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Evidencia_Jarras_Blender_&amp;_Cold_Foam" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6e195f182c384a539b6062a655e437a4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Evidencia_Peanuts_Charly&amp;Lucy" dataDxfId="2">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Evidencia_Peanuts_Charly&amp;Lucy" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r389c34ea624f473d949b2c522d03c6c5"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{7F2E7CEA-564B-42A6-878F-57B35A9A0758}" name="Evidencia_Peanuts_Linus&amp;Snoopy_x000a_" dataDxfId="1">
+    <tableColumn id="21" xr3:uid="{7F2E7CEA-564B-42A6-878F-57B35A9A0758}" name="Evidencia_Peanuts_Linus&amp;Snoopy_x000a_" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r814eb9c763f442ceb8102830ec06c1b4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{8103E8D4-7A3A-4EAB-9703-3EFD9DEFB997}" name="Evidencia_Organizacion_Refrigeradores_Back_x000a_" dataDxfId="0">
+    <tableColumn id="22" xr3:uid="{8103E8D4-7A3A-4EAB-9703-3EFD9DEFB997}" name="Evidencia_Organizacion_Refrigeradores_Back_Antes_x000a_" dataDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5e3143c71cab4402900fedf974331b74"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="23" xr3:uid="{3F498766-55C7-44EB-BC72-26CB978C2C4F}" name="Evidencia_Organizacion_Refrigeradores_Back_Despues_x000a_" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="rc24c1eaaf13e472b9df093f00fa2a223"/>
         </ext>
       </extLst>
     </tableColumn>
@@ -625,7 +644,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="852" latestEventMarker="1240">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="854" latestEventMarker="1245">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -648,6 +667,7 @@
         <xlmsforms:syncedQuestionId>r389c34ea624f473d949b2c522d03c6c5</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r814eb9c763f442ceb8102830ec06c1b4</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r5e3143c71cab4402900fedf974331b74</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>rc24c1eaaf13e472b9df093f00fa2a223</xlmsforms:syncedQuestionId>
       </xlmsforms:msForm>
     </ext>
   </extLst>
@@ -951,7 +971,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V27"/>
+  <dimension ref="A1:W26"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -961,10 +981,10 @@
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="20" width="20" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="30.28515625" customWidth="1"/>
-    <col min="22" max="22" width="19" customWidth="1"/>
+    <col min="22" max="23" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="30" customHeight="1">
+    <row r="1" spans="1:23" ht="30" customHeight="1">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1028,36 +1048,41 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" spans="1:22">
+      <c r="W1" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23">
       <c r="A2">
-        <v>827</v>
+        <v>829</v>
       </c>
       <c r="B2" s="1">
-        <v>46282.935173611098</v>
+        <v>46283.553090277797</v>
       </c>
       <c r="C2" s="1">
-        <v>46282.935717592598</v>
+        <v>46283.553935185198</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F2">
-        <v>38371</v>
+        <v>43164</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
+      <c r="K2" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
       <c r="N2" s="2"/>
@@ -1066,39 +1091,38 @@
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
-      <c r="T2" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="V2" s="6"/>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="T2" s="2"/>
+    </row>
+    <row r="3" spans="1:23">
       <c r="A3">
-        <v>828</v>
+        <v>830</v>
       </c>
       <c r="B3" s="1">
-        <v>46282.936805555597</v>
+        <v>46283.5710300926</v>
       </c>
       <c r="C3" s="1">
-        <v>46282.937152777798</v>
+        <v>46283.5727430556</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F3">
-        <v>38371</v>
+        <v>38529</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>30</v>
+      </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -1106,39 +1130,33 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
-      <c r="U3" t="s">
-        <v>27</v>
-      </c>
-      <c r="V3" s="6"/>
-    </row>
-    <row r="4" spans="1:22">
+    </row>
+    <row r="4" spans="1:23">
       <c r="A4">
-        <v>829</v>
+        <v>831</v>
       </c>
       <c r="B4" s="1">
-        <v>46283.553090277797</v>
+        <v>46283.706562500003</v>
       </c>
       <c r="C4" s="1">
-        <v>46283.553935185198</v>
+        <v>46283.708009259302</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F4">
-        <v>43164</v>
+        <v>38431</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
-      <c r="K4" s="2" t="s">
-        <v>31</v>
-      </c>
+      <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
@@ -1147,69 +1165,69 @@
       <c r="Q4" s="2"/>
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="V4" s="6"/>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="T4" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23">
       <c r="A5">
-        <v>830</v>
+        <v>832</v>
       </c>
       <c r="B5" s="1">
-        <v>46283.5710300926</v>
+        <v>46283.726446759298</v>
       </c>
       <c r="C5" s="1">
-        <v>46283.5727430556</v>
+        <v>46283.727754629603</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F5">
+        <v>38661</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="F5">
-        <v>38529</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
-        <v>35</v>
-      </c>
+      <c r="M5" s="2"/>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
       <c r="P5" s="2"/>
       <c r="Q5" s="2"/>
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="V5" s="6"/>
-    </row>
-    <row r="6" spans="1:22">
+      <c r="T5" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23">
       <c r="A6">
-        <v>831</v>
+        <v>833</v>
       </c>
       <c r="B6" s="1">
-        <v>46283.706562500003</v>
+        <v>46283.741875</v>
       </c>
       <c r="C6" s="1">
-        <v>46283.708009259302</v>
+        <v>46283.742245370398</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6">
-        <v>38431</v>
+        <v>38925</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2"/>
@@ -1224,31 +1242,30 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
       <c r="T6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V6" s="6"/>
-    </row>
-    <row r="7" spans="1:22">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23">
       <c r="A7">
-        <v>832</v>
+        <v>834</v>
       </c>
       <c r="B7" s="1">
-        <v>46283.726446759298</v>
+        <v>46283.752060185201</v>
       </c>
       <c r="C7" s="1">
-        <v>46283.727754629603</v>
+        <v>46283.752372685201</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F7">
-        <v>38661</v>
+        <v>43043</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="2"/>
@@ -1263,31 +1280,30 @@
       <c r="R7" s="2"/>
       <c r="S7" s="2"/>
       <c r="T7" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="V7" s="6"/>
-    </row>
-    <row r="8" spans="1:22">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23">
       <c r="A8">
-        <v>833</v>
+        <v>835</v>
       </c>
       <c r="B8" s="1">
-        <v>46283.741875</v>
+        <v>46283.816099536998</v>
       </c>
       <c r="C8" s="1">
-        <v>46283.742245370398</v>
+        <v>46283.819976851897</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F8">
-        <v>38925</v>
+        <v>38115</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2"/>
@@ -1302,31 +1318,30 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
       <c r="T8" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="V8" s="6"/>
-    </row>
-    <row r="9" spans="1:22">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23">
       <c r="A9">
-        <v>834</v>
+        <v>836</v>
       </c>
       <c r="B9" s="1">
-        <v>46283.752060185201</v>
+        <v>46283.895046296297</v>
       </c>
       <c r="C9" s="1">
-        <v>46283.752372685201</v>
+        <v>46283.895983796298</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F9">
-        <v>43043</v>
+        <v>38674</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2"/>
@@ -1341,31 +1356,30 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
       <c r="T9" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="V9" s="6"/>
-    </row>
-    <row r="10" spans="1:22">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23">
       <c r="A10">
-        <v>835</v>
+        <v>837</v>
       </c>
       <c r="B10" s="1">
-        <v>46283.816099536998</v>
+        <v>46283.913402777798</v>
       </c>
       <c r="C10" s="1">
-        <v>46283.819976851897</v>
+        <v>46283.913958333302</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F10">
-        <v>38115</v>
+        <v>38535</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2"/>
@@ -1380,31 +1394,30 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
       <c r="T10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="V10" s="6"/>
-    </row>
-    <row r="11" spans="1:22">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23">
       <c r="A11">
-        <v>836</v>
+        <v>838</v>
       </c>
       <c r="B11" s="1">
-        <v>46283.895046296297</v>
+        <v>46284.395671296297</v>
       </c>
       <c r="C11" s="1">
-        <v>46283.895983796298</v>
+        <v>46284.398645833302</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="F11">
-        <v>38674</v>
+        <v>38590</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2"/>
@@ -1419,31 +1432,30 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="V11" s="6"/>
-    </row>
-    <row r="12" spans="1:22">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23">
       <c r="A12">
-        <v>837</v>
+        <v>839</v>
       </c>
       <c r="B12" s="1">
-        <v>46283.913402777798</v>
+        <v>46284.4004166667</v>
       </c>
       <c r="C12" s="1">
-        <v>46283.913958333302</v>
+        <v>46284.404386574097</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F12">
-        <v>38535</v>
+        <v>38862</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2"/>
@@ -1458,31 +1470,30 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
       <c r="T12" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="V12" s="6"/>
-    </row>
-    <row r="13" spans="1:22">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23">
       <c r="A13">
-        <v>838</v>
+        <v>840</v>
       </c>
       <c r="B13" s="1">
-        <v>46284.395671296297</v>
+        <v>46284.4081828704</v>
       </c>
       <c r="C13" s="1">
-        <v>46284.398645833302</v>
+        <v>46284.409502314797</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="F13">
-        <v>38590</v>
+        <v>38136</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2"/>
@@ -1497,31 +1508,30 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
       <c r="T13" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="V13" s="6"/>
-    </row>
-    <row r="14" spans="1:22">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23">
       <c r="A14">
-        <v>839</v>
+        <v>841</v>
       </c>
       <c r="B14" s="1">
-        <v>46284.4004166667</v>
+        <v>46284.432268518503</v>
       </c>
       <c r="C14" s="1">
-        <v>46284.404386574097</v>
+        <v>46284.433622685203</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F14">
-        <v>38862</v>
+        <v>38197</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
@@ -1536,31 +1546,30 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
       <c r="T14" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="V14" s="6"/>
-    </row>
-    <row r="15" spans="1:22">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23">
       <c r="A15">
-        <v>840</v>
+        <v>842</v>
       </c>
       <c r="B15" s="1">
-        <v>46284.4081828704</v>
+        <v>46284.497638888897</v>
       </c>
       <c r="C15" s="1">
-        <v>46284.409502314797</v>
+        <v>46284.530243055597</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F15">
-        <v>38136</v>
+        <v>38606</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
@@ -1575,31 +1584,30 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
       <c r="T15" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="V15" s="6"/>
-    </row>
-    <row r="16" spans="1:22">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23">
       <c r="A16">
-        <v>841</v>
+        <v>843</v>
       </c>
       <c r="B16" s="1">
-        <v>46284.432268518503</v>
+        <v>46284.532268518502</v>
       </c>
       <c r="C16" s="1">
-        <v>46284.433622685203</v>
+        <v>46284.533553240697</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F16">
-        <v>38197</v>
+        <v>38458</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2"/>
@@ -1608,37 +1616,36 @@
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
+      <c r="O16" s="2" t="s">
+        <v>71</v>
+      </c>
       <c r="P16" s="2"/>
       <c r="Q16" s="2"/>
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
-      <c r="T16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="V16" s="6"/>
-    </row>
-    <row r="17" spans="1:22">
+      <c r="T16" s="2"/>
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17">
-        <v>842</v>
+        <v>844</v>
       </c>
       <c r="B17" s="1">
-        <v>46284.497638888897</v>
+        <v>46284.534872685203</v>
       </c>
       <c r="C17" s="1">
-        <v>46284.530243055597</v>
+        <v>46284.535138888903</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="F17">
-        <v>38606</v>
+        <v>38230</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2"/>
@@ -1653,31 +1660,30 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
       <c r="T17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="V17" s="6"/>
-    </row>
-    <row r="18" spans="1:22">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18">
-        <v>843</v>
+        <v>845</v>
       </c>
       <c r="B18" s="1">
-        <v>46284.532268518502</v>
+        <v>46284.533622685201</v>
       </c>
       <c r="C18" s="1">
-        <v>46284.533553240697</v>
+        <v>46284.542465277802</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="F18">
         <v>38458</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2"/>
@@ -1686,37 +1692,36 @@
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="P18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2" t="s">
+        <v>76</v>
+      </c>
       <c r="Q18" s="2"/>
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
-      <c r="V18" s="6"/>
-    </row>
-    <row r="19" spans="1:22">
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19">
-        <v>844</v>
+        <v>846</v>
       </c>
       <c r="B19" s="1">
-        <v>46284.534872685203</v>
+        <v>46284.542500000003</v>
       </c>
       <c r="C19" s="1">
-        <v>46284.535138888903</v>
+        <v>46284.564814814803</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="F19">
-        <v>38230</v>
+        <v>38458</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
@@ -1731,31 +1736,30 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
       <c r="T19" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23">
+      <c r="A20">
+        <v>847</v>
+      </c>
+      <c r="B20" s="1">
+        <v>46284.579421296301</v>
+      </c>
+      <c r="C20" s="1">
+        <v>46284.579930555599</v>
+      </c>
+      <c r="D20" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="V19" s="6"/>
-    </row>
-    <row r="20" spans="1:22">
-      <c r="A20">
-        <v>845</v>
-      </c>
-      <c r="B20" s="1">
-        <v>46284.533622685201</v>
-      </c>
-      <c r="C20" s="1">
-        <v>46284.542465277802</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="F20">
-        <v>38458</v>
+        <v>38117</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2"/>
@@ -1765,36 +1769,35 @@
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="2" t="s">
-        <v>80</v>
-      </c>
+      <c r="P20" s="2"/>
       <c r="Q20" s="2"/>
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="V20" s="6"/>
-    </row>
-    <row r="21" spans="1:22">
+      <c r="T20" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21">
-        <v>846</v>
+        <v>848</v>
       </c>
       <c r="B21" s="1">
-        <v>46284.542500000003</v>
+        <v>46284.593229166698</v>
       </c>
       <c r="C21" s="1">
-        <v>46284.564814814803</v>
+        <v>46284.5954166667</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>72</v>
+        <v>81</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="F21">
-        <v>38458</v>
+        <v>38475</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2"/>
@@ -1809,31 +1812,30 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
       <c r="T21" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="V21" s="6"/>
-    </row>
-    <row r="22" spans="1:22">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22">
-        <v>847</v>
+        <v>849</v>
       </c>
       <c r="B22" s="1">
-        <v>46284.579421296301</v>
+        <v>46284.594722222202</v>
       </c>
       <c r="C22" s="1">
-        <v>46284.579930555599</v>
+        <v>46284.597175925897</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F22">
-        <v>38117</v>
+        <v>38333</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>24</v>
+        <v>75</v>
       </c>
       <c r="H22" s="2"/>
       <c r="I22" s="2"/>
@@ -1843,36 +1845,35 @@
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
+      <c r="P22" s="2" t="s">
+        <v>86</v>
+      </c>
       <c r="Q22" s="2"/>
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
-      <c r="T22" s="2" t="s">
+      <c r="T22" s="2"/>
+    </row>
+    <row r="23" spans="1:23">
+      <c r="A23">
+        <v>850</v>
+      </c>
+      <c r="B23" s="1">
+        <v>46284.598599536999</v>
+      </c>
+      <c r="C23" s="1">
+        <v>46284.600231481498</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="V22" s="6"/>
-    </row>
-    <row r="23" spans="1:22">
-      <c r="A23">
-        <v>848</v>
-      </c>
-      <c r="B23" s="1">
-        <v>46284.593229166698</v>
-      </c>
-      <c r="C23" s="1">
-        <v>46284.5954166667</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="F23">
-        <v>38475</v>
+        <v>38333</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>24</v>
+        <v>87</v>
       </c>
       <c r="H23" s="2"/>
       <c r="I23" s="2"/>
@@ -1883,35 +1884,38 @@
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="V23" s="6"/>
-    </row>
-    <row r="24" spans="1:22">
+      <c r="Q23" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R23" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="T23" s="2"/>
+    </row>
+    <row r="24" spans="1:23">
       <c r="A24">
-        <v>849</v>
+        <v>851</v>
       </c>
       <c r="B24" s="1">
-        <v>46284.594722222202</v>
+        <v>46284.641678240703</v>
       </c>
       <c r="C24" s="1">
-        <v>46284.597175925897</v>
+        <v>46284.643020833297</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="F24">
-        <v>38333</v>
+        <v>38995</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="H24" s="2"/>
       <c r="I24" s="2"/>
@@ -1921,36 +1925,35 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
-      <c r="P24" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
       <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="V24" s="6"/>
-    </row>
-    <row r="25" spans="1:22">
+      <c r="T24" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23">
       <c r="A25">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="B25" s="1">
-        <v>46284.598599536999</v>
+        <v>46284.6503240741</v>
       </c>
       <c r="C25" s="1">
-        <v>46284.600231481498</v>
+        <v>46284.651006944398</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F25">
-        <v>38333</v>
+        <v>38507</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="H25" s="2"/>
       <c r="I25" s="2"/>
@@ -1961,39 +1964,34 @@
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" s="2"/>
-      <c r="Q25" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="R25" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="S25" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="T25" s="2"/>
-      <c r="V25" s="6"/>
-    </row>
-    <row r="26" spans="1:22">
+      <c r="Q25" s="4"/>
+      <c r="R25" s="4"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="5" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23">
       <c r="A26" s="6">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="B26" s="1">
-        <v>46284.641678240703</v>
+        <v>46284.6694444444</v>
       </c>
       <c r="C26" s="1">
-        <v>46284.643020833297</v>
+        <v>46284.669606481497</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F26" s="6">
-        <v>38995</v>
+        <v>38149</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="H26" s="2"/>
       <c r="I26" s="2"/>
@@ -2007,57 +2005,21 @@
       <c r="Q26" s="4"/>
       <c r="R26" s="4"/>
       <c r="S26" s="2"/>
-      <c r="T26" s="2" t="s">
-        <v>97</v>
+      <c r="T26" s="5" t="s">
+        <v>99</v>
       </c>
       <c r="U26" s="6"/>
       <c r="V26" s="6"/>
-    </row>
-    <row r="27" spans="1:22">
-      <c r="A27" s="6">
-        <v>852</v>
-      </c>
-      <c r="B27" s="1">
-        <v>46284.646423611099</v>
-      </c>
-      <c r="C27" s="1">
-        <v>46284.6467708333</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="F27" s="6">
-        <v>38371</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="2"/>
-      <c r="M27" s="2"/>
-      <c r="N27" s="2"/>
-      <c r="O27" s="2"/>
-      <c r="P27" s="2"/>
-      <c r="Q27" s="4"/>
-      <c r="R27" s="4"/>
-      <c r="S27" s="2"/>
-      <c r="T27" s="2"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6" t="s">
-        <v>99</v>
-      </c>
+      <c r="W26" s="6"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="T25" r:id="rId1" xr:uid="{62D300EA-F412-4081-9CE3-9E5EE75DBCF4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
   </tableParts>
 </worksheet>
 </file>
--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{22A343D0-E4CA-4094-A17D-54B8BE0C8986}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B38C827-3DA6-4B01-AC95-128DC0288974}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="124">
   <si>
     <t>Id</t>
   </si>
@@ -339,6 +339,78 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG-20260918-WA0067_Starbucks%20Bellavista.jpg</t>
+  </si>
+  <si>
+    <t>maria.cardenas@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Maria Veronica Cardenas Pedraza</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17898571856927231061776467732355_Maria%20Veronica%20Carde.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38515@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Patio Ecatepec</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17898572434496167251908049569087_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>Organización Refrigeradores Back</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/17898578066011103601279025610229_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/17898583584755546269641779007481_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>hector.martinez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Hector Martinez Uribe</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Hector%20Martinez%20Urib.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38656@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Viveros Santa Monica</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/9C8C2B16-63E5-4D07-975E-962DE02956A7_Starbucks%20Viveros%20Sa.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38770@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Gustavo Baz 29</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Gustavo%20Ba.jpg</t>
+  </si>
+  <si>
+    <t>david.zaragoza@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>David Zaragoza Diaz</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/WhatsApp%20Image%202026-09-19%20at%205.05.01%20PM_David%20Zaragoza%20Diaz.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38442@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Sor Juana</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Sor%20Juana.jpg</t>
   </si>
 </sst>
 </file>
@@ -476,8 +548,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W26" totalsRowShown="0">
-  <autoFilter ref="A1:W26" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W35" totalsRowShown="0">
+  <autoFilter ref="A1:W35" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -644,7 +716,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="854" latestEventMarker="1245">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="862" latestEventMarker="1253">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -971,12 +1043,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W26"/>
+  <dimension ref="A1:W35"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="37.5703125" customWidth="1"/>
-    <col min="5" max="5" width="22.5703125" customWidth="1"/>
+    <col min="5" max="5" width="30.42578125" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23.5703125" customWidth="1"/>
     <col min="8" max="20" width="20" bestFit="1" customWidth="1"/>
@@ -1972,7 +2044,7 @@
       </c>
     </row>
     <row r="26" spans="1:23">
-      <c r="A26" s="6">
+      <c r="A26">
         <v>854</v>
       </c>
       <c r="B26" s="1">
@@ -1987,7 +2059,7 @@
       <c r="E26" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26">
         <v>38149</v>
       </c>
       <c r="G26" s="2" t="s">
@@ -2008,9 +2080,378 @@
       <c r="T26" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="U26" s="6"/>
-      <c r="V26" s="6"/>
-      <c r="W26" s="6"/>
+    </row>
+    <row r="27" spans="1:23">
+      <c r="A27">
+        <v>855</v>
+      </c>
+      <c r="B27" s="1">
+        <v>46284.687916666699</v>
+      </c>
+      <c r="C27" s="1">
+        <v>46284.689861111103</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F27">
+        <v>38270</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="4"/>
+      <c r="R27" s="4"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23">
+      <c r="A28" s="6">
+        <v>855</v>
+      </c>
+      <c r="B28" s="1">
+        <v>46284.687916666699</v>
+      </c>
+      <c r="C28" s="1">
+        <v>46284.689861111103</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F28" s="6">
+        <v>38270</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="4"/>
+      <c r="R28" s="4"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="U28" s="6"/>
+      <c r="V28" s="6"/>
+      <c r="W28" s="6"/>
+    </row>
+    <row r="29" spans="1:23">
+      <c r="A29" s="6">
+        <v>856</v>
+      </c>
+      <c r="B29" s="1">
+        <v>46284.6875</v>
+      </c>
+      <c r="C29" s="1">
+        <v>46284.690474536997</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F29" s="6">
+        <v>38515</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R29" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S29" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="T29" s="5"/>
+      <c r="U29" s="6"/>
+      <c r="V29" s="6"/>
+      <c r="W29" s="6"/>
+    </row>
+    <row r="30" spans="1:23">
+      <c r="A30" s="6">
+        <v>857</v>
+      </c>
+      <c r="B30" s="1">
+        <v>46284.696099537003</v>
+      </c>
+      <c r="C30" s="1">
+        <v>46284.703773148103</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F30" s="6">
+        <v>38515</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="4"/>
+      <c r="R30" s="4"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="5"/>
+      <c r="U30" s="6"/>
+      <c r="V30" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="W30" s="6" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23">
+      <c r="A31" s="6">
+        <v>858</v>
+      </c>
+      <c r="B31" s="1">
+        <v>46284.720578703702</v>
+      </c>
+      <c r="C31" s="1">
+        <v>46284.721157407403</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="F31" s="6">
+        <v>38719</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" s="2"/>
+      <c r="Q31" s="4"/>
+      <c r="R31" s="4"/>
+      <c r="S31" s="2"/>
+      <c r="T31" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="U31" s="6"/>
+      <c r="V31" s="6"/>
+      <c r="W31" s="6"/>
+    </row>
+    <row r="32" spans="1:23">
+      <c r="A32" s="6">
+        <v>859</v>
+      </c>
+      <c r="B32" s="1">
+        <v>46284.719629629602</v>
+      </c>
+      <c r="C32" s="1">
+        <v>46284.724525463003</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F32" s="6">
+        <v>38656</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="P32" s="2"/>
+      <c r="Q32" s="4"/>
+      <c r="R32" s="4"/>
+      <c r="S32" s="2"/>
+      <c r="T32" s="5"/>
+      <c r="U32" s="6"/>
+      <c r="V32" s="6"/>
+      <c r="W32" s="6"/>
+    </row>
+    <row r="33" spans="1:23">
+      <c r="A33" s="6">
+        <v>860</v>
+      </c>
+      <c r="B33" s="1">
+        <v>46284.743472222202</v>
+      </c>
+      <c r="C33" s="1">
+        <v>46284.745300925897</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F33" s="6">
+        <v>38770</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" s="2"/>
+      <c r="Q33" s="4"/>
+      <c r="R33" s="4"/>
+      <c r="S33" s="2"/>
+      <c r="T33" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="U33" s="6"/>
+      <c r="V33" s="6"/>
+      <c r="W33" s="6"/>
+    </row>
+    <row r="34" spans="1:23">
+      <c r="A34" s="6">
+        <v>861</v>
+      </c>
+      <c r="B34" s="1">
+        <v>46284.742627314801</v>
+      </c>
+      <c r="C34" s="1">
+        <v>46284.747037036999</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="6">
+        <v>43111</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" s="2"/>
+      <c r="Q34" s="4"/>
+      <c r="R34" s="4"/>
+      <c r="S34" s="2"/>
+      <c r="T34" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="U34" s="6"/>
+      <c r="V34" s="6"/>
+      <c r="W34" s="6"/>
+    </row>
+    <row r="35" spans="1:23">
+      <c r="A35" s="6">
+        <v>862</v>
+      </c>
+      <c r="B35" s="1">
+        <v>46284.7500925926</v>
+      </c>
+      <c r="C35" s="1">
+        <v>46284.753009259301</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F35" s="6">
+        <v>38442</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" s="2"/>
+      <c r="Q35" s="4"/>
+      <c r="R35" s="4"/>
+      <c r="S35" s="2"/>
+      <c r="T35" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="U35" s="6"/>
+      <c r="V35" s="6"/>
+      <c r="W35" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="61" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B38C827-3DA6-4B01-AC95-128DC0288974}"/>
+  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80C5DB27-29AC-495B-B456-B90F396497D0}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="133">
   <si>
     <t>Id</t>
   </si>
@@ -411,6 +411,33 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Sor%20Juana.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38394@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks CC Lomas Verdes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17898635055024426475079545534074_Starbucks%20CC%20Lomas%20V.jpg</t>
+  </si>
+  <si>
+    <t>julian.flores@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Julian Alejandro Flores Garcia</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_5086_Julian%20Alejandro%20Flo.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38401@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks CC Coalcalco</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/5342bc54-3a5b-437d-b97b-399058c7ca0c_Starbucks%20CC%20Coalcal.jpeg</t>
   </si>
 </sst>
 </file>
@@ -548,8 +575,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W35" totalsRowShown="0">
-  <autoFilter ref="A1:W35" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W38" totalsRowShown="0">
+  <autoFilter ref="A1:W38" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -716,7 +743,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="862" latestEventMarker="1253">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="865" latestEventMarker="1256">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1043,7 +1070,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W35"/>
+  <dimension ref="A1:W38"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -2120,7 +2147,7 @@
       </c>
     </row>
     <row r="28" spans="1:23">
-      <c r="A28" s="6">
+      <c r="A28">
         <v>855</v>
       </c>
       <c r="B28" s="1">
@@ -2135,7 +2162,7 @@
       <c r="E28" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28">
         <v>38270</v>
       </c>
       <c r="G28" s="2" t="s">
@@ -2156,12 +2183,9 @@
       <c r="T28" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="U28" s="6"/>
-      <c r="V28" s="6"/>
-      <c r="W28" s="6"/>
     </row>
     <row r="29" spans="1:23">
-      <c r="A29" s="6">
+      <c r="A29">
         <v>856</v>
       </c>
       <c r="B29" s="1">
@@ -2176,7 +2200,7 @@
       <c r="E29" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29">
         <v>38515</v>
       </c>
       <c r="G29" s="2" t="s">
@@ -2201,12 +2225,9 @@
         <v>105</v>
       </c>
       <c r="T29" s="5"/>
-      <c r="U29" s="6"/>
-      <c r="V29" s="6"/>
-      <c r="W29" s="6"/>
     </row>
     <row r="30" spans="1:23">
-      <c r="A30" s="6">
+      <c r="A30">
         <v>857</v>
       </c>
       <c r="B30" s="1">
@@ -2221,7 +2242,7 @@
       <c r="E30" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30">
         <v>38515</v>
       </c>
       <c r="G30" s="2" t="s">
@@ -2240,16 +2261,15 @@
       <c r="R30" s="4"/>
       <c r="S30" s="2"/>
       <c r="T30" s="5"/>
-      <c r="U30" s="6"/>
-      <c r="V30" s="6" t="s">
+      <c r="V30" t="s">
         <v>107</v>
       </c>
-      <c r="W30" s="6" t="s">
+      <c r="W30" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="31" spans="1:23">
-      <c r="A31" s="6">
+      <c r="A31">
         <v>858</v>
       </c>
       <c r="B31" s="1">
@@ -2264,7 +2284,7 @@
       <c r="E31" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31">
         <v>38719</v>
       </c>
       <c r="G31" s="2" t="s">
@@ -2285,12 +2305,9 @@
       <c r="T31" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="U31" s="6"/>
-      <c r="V31" s="6"/>
-      <c r="W31" s="6"/>
     </row>
     <row r="32" spans="1:23">
-      <c r="A32" s="6">
+      <c r="A32">
         <v>859</v>
       </c>
       <c r="B32" s="1">
@@ -2305,7 +2322,7 @@
       <c r="E32" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32">
         <v>38656</v>
       </c>
       <c r="G32" s="2" t="s">
@@ -2326,12 +2343,9 @@
       <c r="R32" s="4"/>
       <c r="S32" s="2"/>
       <c r="T32" s="5"/>
-      <c r="U32" s="6"/>
-      <c r="V32" s="6"/>
-      <c r="W32" s="6"/>
     </row>
     <row r="33" spans="1:23">
-      <c r="A33" s="6">
+      <c r="A33">
         <v>860</v>
       </c>
       <c r="B33" s="1">
@@ -2346,7 +2360,7 @@
       <c r="E33" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33">
         <v>38770</v>
       </c>
       <c r="G33" s="2" t="s">
@@ -2367,12 +2381,9 @@
       <c r="T33" s="5" t="s">
         <v>117</v>
       </c>
-      <c r="U33" s="6"/>
-      <c r="V33" s="6"/>
-      <c r="W33" s="6"/>
     </row>
     <row r="34" spans="1:23">
-      <c r="A34" s="6">
+      <c r="A34">
         <v>861</v>
       </c>
       <c r="B34" s="1">
@@ -2387,7 +2398,7 @@
       <c r="E34" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34">
         <v>43111</v>
       </c>
       <c r="G34" s="2" t="s">
@@ -2408,12 +2419,9 @@
       <c r="T34" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
     </row>
     <row r="35" spans="1:23">
-      <c r="A35" s="6">
+      <c r="A35">
         <v>862</v>
       </c>
       <c r="B35" s="1">
@@ -2428,7 +2436,7 @@
       <c r="E35" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35">
         <v>38442</v>
       </c>
       <c r="G35" s="2" t="s">
@@ -2449,9 +2457,127 @@
       <c r="T35" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="U35" s="6"/>
-      <c r="V35" s="6"/>
-      <c r="W35" s="6"/>
+    </row>
+    <row r="36" spans="1:23">
+      <c r="A36">
+        <v>863</v>
+      </c>
+      <c r="B36" s="1">
+        <v>46284.761944444399</v>
+      </c>
+      <c r="C36" s="1">
+        <v>46284.763206018499</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="F36">
+        <v>38394</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="4"/>
+      <c r="R36" s="4"/>
+      <c r="S36" s="2"/>
+      <c r="T36" s="5" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="37" spans="1:23">
+      <c r="A37">
+        <v>864</v>
+      </c>
+      <c r="B37" s="1">
+        <v>46284.754780092597</v>
+      </c>
+      <c r="C37" s="1">
+        <v>46284.7643171296</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="F37">
+        <v>38205</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" s="2"/>
+      <c r="Q37" s="4"/>
+      <c r="R37" s="4"/>
+      <c r="S37" s="2"/>
+      <c r="T37" s="5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="38" spans="1:23">
+      <c r="A38" s="6">
+        <v>865</v>
+      </c>
+      <c r="B38" s="1">
+        <v>46284.781863425902</v>
+      </c>
+      <c r="C38" s="1">
+        <v>46284.7820601852</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F38" s="6">
+        <v>38401</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2"/>
+      <c r="L38" s="2"/>
+      <c r="M38" s="2"/>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R38" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="S38" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="T38" s="5"/>
+      <c r="U38" s="6"/>
+      <c r="V38" s="6"/>
+      <c r="W38" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="67" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{80C5DB27-29AC-495B-B456-B90F396497D0}"/>
+  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFBA5AD1-CF75-4043-940E-F48624E3E95D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="163">
   <si>
     <t>Id</t>
   </si>
@@ -438,6 +438,96 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/5342bc54-3a5b-437d-b97b-399058c7ca0c_Starbucks%20CC%20Coalcal.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38266@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San Mateo</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_9870_Starbucks%20San%20Mateo.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38418@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Oriente</t>
+  </si>
+  <si>
+    <t>Lay Out</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/82D608F5-BE6B-4F2E-B86B-8E83504FDF66_Starbucks%20Plaza%20Orie.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38119@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Lomas Verdes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17898661582432321788420269936635_Starbucks%20Lomas%20Verd.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38339@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San Marcos</t>
+  </si>
+  <si>
+    <t>Rack FHW</t>
+  </si>
+  <si>
+    <t>Si</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17898686780892615247131284453131_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>Max &amp; Min </t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/17898688920937210256645077063927_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17898689716204195918867095245985_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>daniel.bustos@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Daniel Bustos Martinez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Daniel%20Bustos%20Martin.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17898690177589028917725967468681_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/1789869064821271285516039601533_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Lucy_24Sep/image_Daniel%20Bustos%20Martin.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/17898692834943720844565823759975_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/17898693192304841577590189157423_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17898694453017719363453178036313_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38427@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks CC Plaza Satélite</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/5E9551ED-DBE7-4A4A-8279-17F12D33E143_Starbucks%20CC%20Plaza%20S.jpeg</t>
   </si>
 </sst>
 </file>
@@ -575,8 +665,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W38" totalsRowShown="0">
-  <autoFilter ref="A1:W38" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W52" totalsRowShown="0">
+  <autoFilter ref="A1:W52" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -743,7 +833,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="865" latestEventMarker="1256">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="879" latestEventMarker="1270">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1070,7 +1160,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W38"/>
+  <dimension ref="A1:W52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -2535,7 +2625,7 @@
       </c>
     </row>
     <row r="38" spans="1:23">
-      <c r="A38" s="6">
+      <c r="A38">
         <v>865</v>
       </c>
       <c r="B38" s="1">
@@ -2550,7 +2640,7 @@
       <c r="E38" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38">
         <v>38401</v>
       </c>
       <c r="G38" s="2" t="s">
@@ -2575,9 +2665,588 @@
         <v>132</v>
       </c>
       <c r="T38" s="5"/>
-      <c r="U38" s="6"/>
-      <c r="V38" s="6"/>
-      <c r="W38" s="6"/>
+    </row>
+    <row r="39" spans="1:23">
+      <c r="A39" s="6">
+        <v>866</v>
+      </c>
+      <c r="B39" s="1">
+        <v>46284.784421296303</v>
+      </c>
+      <c r="C39" s="1">
+        <v>46284.787569444401</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F39" s="6">
+        <v>38266</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2"/>
+      <c r="L39" s="2"/>
+      <c r="M39" s="2"/>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" s="2"/>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="2"/>
+      <c r="T39" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="U39" s="6"/>
+      <c r="V39" s="6"/>
+      <c r="W39" s="6"/>
+    </row>
+    <row r="40" spans="1:23">
+      <c r="A40" s="6">
+        <v>867</v>
+      </c>
+      <c r="B40" s="1">
+        <v>46284.792303240698</v>
+      </c>
+      <c r="C40" s="1">
+        <v>46284.793460648099</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F40" s="6">
+        <v>38418</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2"/>
+      <c r="L40" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="M40" s="2"/>
+      <c r="N40" s="2"/>
+      <c r="O40" s="2"/>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="2"/>
+      <c r="T40" s="5"/>
+      <c r="U40" s="6"/>
+      <c r="V40" s="6"/>
+      <c r="W40" s="6"/>
+    </row>
+    <row r="41" spans="1:23">
+      <c r="A41" s="6">
+        <v>868</v>
+      </c>
+      <c r="B41" s="1">
+        <v>46284.792152777802</v>
+      </c>
+      <c r="C41" s="1">
+        <v>46284.793726851902</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F41" s="6">
+        <v>38119</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2"/>
+      <c r="L41" s="2"/>
+      <c r="M41" s="2"/>
+      <c r="N41" s="2"/>
+      <c r="O41" s="2"/>
+      <c r="P41" s="2"/>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="2"/>
+      <c r="T41" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="U41" s="6"/>
+      <c r="V41" s="6"/>
+      <c r="W41" s="6"/>
+    </row>
+    <row r="42" spans="1:23">
+      <c r="A42" s="6">
+        <v>869</v>
+      </c>
+      <c r="B42" s="1">
+        <v>46284.822141203702</v>
+      </c>
+      <c r="C42" s="1">
+        <v>46284.8230555556</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" s="6">
+        <v>38339</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2"/>
+      <c r="L42" s="2"/>
+      <c r="M42" s="2"/>
+      <c r="N42" s="2"/>
+      <c r="O42" s="2"/>
+      <c r="P42" s="2"/>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="2"/>
+      <c r="T42" s="5"/>
+      <c r="U42" s="6"/>
+      <c r="V42" s="6"/>
+      <c r="W42" s="6"/>
+    </row>
+    <row r="43" spans="1:23">
+      <c r="A43" s="6">
+        <v>870</v>
+      </c>
+      <c r="B43" s="1">
+        <v>46284.823738425897</v>
+      </c>
+      <c r="C43" s="1">
+        <v>46284.825856481497</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F43" s="6">
+        <v>38339</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="J43" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="K43" s="2"/>
+      <c r="L43" s="2"/>
+      <c r="M43" s="2"/>
+      <c r="N43" s="2"/>
+      <c r="O43" s="2"/>
+      <c r="P43" s="2"/>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="2"/>
+      <c r="T43" s="5"/>
+      <c r="U43" s="6"/>
+      <c r="V43" s="6"/>
+      <c r="W43" s="6"/>
+    </row>
+    <row r="44" spans="1:23">
+      <c r="A44" s="6">
+        <v>871</v>
+      </c>
+      <c r="B44" s="1">
+        <v>46284.825914351903</v>
+      </c>
+      <c r="C44" s="1">
+        <v>46284.8262384259</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F44" s="6">
+        <v>38339</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="L44" s="2"/>
+      <c r="M44" s="2"/>
+      <c r="N44" s="2"/>
+      <c r="O44" s="2"/>
+      <c r="P44" s="2"/>
+      <c r="Q44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="2"/>
+      <c r="T44" s="5"/>
+      <c r="U44" s="6"/>
+      <c r="V44" s="6"/>
+      <c r="W44" s="6"/>
+    </row>
+    <row r="45" spans="1:23">
+      <c r="A45" s="6">
+        <v>872</v>
+      </c>
+      <c r="B45" s="1">
+        <v>46284.825960648101</v>
+      </c>
+      <c r="C45" s="1">
+        <v>46284.8268171296</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F45" s="6">
+        <v>38411</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2"/>
+      <c r="L45" s="2"/>
+      <c r="M45" s="2"/>
+      <c r="N45" s="2"/>
+      <c r="O45" s="2"/>
+      <c r="P45" s="2"/>
+      <c r="Q45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="2"/>
+      <c r="T45" s="5" t="s">
+        <v>153</v>
+      </c>
+      <c r="U45" s="6"/>
+      <c r="V45" s="6"/>
+      <c r="W45" s="6"/>
+    </row>
+    <row r="46" spans="1:23">
+      <c r="A46" s="6">
+        <v>873</v>
+      </c>
+      <c r="B46" s="1">
+        <v>46284.826273148203</v>
+      </c>
+      <c r="C46" s="1">
+        <v>46284.826921296299</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F46" s="6">
+        <v>38339</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2"/>
+      <c r="L46" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="M46" s="2"/>
+      <c r="N46" s="2"/>
+      <c r="O46" s="2"/>
+      <c r="P46" s="2"/>
+      <c r="Q46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="2"/>
+      <c r="T46" s="5"/>
+      <c r="U46" s="6"/>
+      <c r="V46" s="6"/>
+      <c r="W46" s="6"/>
+    </row>
+    <row r="47" spans="1:23">
+      <c r="A47" s="6">
+        <v>874</v>
+      </c>
+      <c r="B47" s="1">
+        <v>46284.826979166697</v>
+      </c>
+      <c r="C47" s="1">
+        <v>46284.827430555597</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F47" s="6">
+        <v>38339</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2"/>
+      <c r="L47" s="2"/>
+      <c r="M47" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+      <c r="Q47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="2"/>
+      <c r="T47" s="5"/>
+      <c r="U47" s="6"/>
+      <c r="V47" s="6"/>
+      <c r="W47" s="6"/>
+    </row>
+    <row r="48" spans="1:23">
+      <c r="A48" s="6">
+        <v>875</v>
+      </c>
+      <c r="B48" s="1">
+        <v>46284.828043981499</v>
+      </c>
+      <c r="C48" s="1">
+        <v>46284.828472222202</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F48" s="6">
+        <v>38411</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2"/>
+      <c r="L48" s="2"/>
+      <c r="M48" s="2"/>
+      <c r="N48" s="2"/>
+      <c r="O48" s="2"/>
+      <c r="P48" s="2"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="2"/>
+      <c r="T48" s="5"/>
+      <c r="U48" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="V48" s="6"/>
+      <c r="W48" s="6"/>
+    </row>
+    <row r="49" spans="1:23">
+      <c r="A49" s="6">
+        <v>876</v>
+      </c>
+      <c r="B49" s="1">
+        <v>46284.827870370398</v>
+      </c>
+      <c r="C49" s="1">
+        <v>46284.829895833303</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F49" s="6">
+        <v>38339</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2"/>
+      <c r="L49" s="2"/>
+      <c r="M49" s="2"/>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="P49" s="2"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="2"/>
+      <c r="T49" s="5"/>
+      <c r="U49" s="6"/>
+      <c r="V49" s="6"/>
+      <c r="W49" s="6"/>
+    </row>
+    <row r="50" spans="1:23">
+      <c r="A50" s="6">
+        <v>877</v>
+      </c>
+      <c r="B50" s="1">
+        <v>46284.829930555599</v>
+      </c>
+      <c r="C50" s="1">
+        <v>46284.830428240697</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F50" s="6">
+        <v>38339</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="J50" s="2"/>
+      <c r="K50" s="2"/>
+      <c r="L50" s="2"/>
+      <c r="M50" s="2"/>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="2"/>
+      <c r="T50" s="5"/>
+      <c r="U50" s="6"/>
+      <c r="V50" s="6"/>
+      <c r="W50" s="6"/>
+    </row>
+    <row r="51" spans="1:23">
+      <c r="A51" s="6">
+        <v>878</v>
+      </c>
+      <c r="B51" s="1">
+        <v>46284.8305092593</v>
+      </c>
+      <c r="C51" s="1">
+        <v>46284.831921296303</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="F51" s="6">
+        <v>38339</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2"/>
+      <c r="L51" s="2"/>
+      <c r="M51" s="2"/>
+      <c r="N51" s="2"/>
+      <c r="O51" s="2"/>
+      <c r="P51" s="2"/>
+      <c r="Q51" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R51" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S51" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="T51" s="5"/>
+      <c r="U51" s="6"/>
+      <c r="V51" s="6"/>
+      <c r="W51" s="6"/>
+    </row>
+    <row r="52" spans="1:23">
+      <c r="A52" s="6">
+        <v>879</v>
+      </c>
+      <c r="B52" s="1">
+        <v>46284.919097222199</v>
+      </c>
+      <c r="C52" s="1">
+        <v>46284.921307870398</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="F52" s="6">
+        <v>38427</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2"/>
+      <c r="L52" s="2"/>
+      <c r="M52" s="2"/>
+      <c r="N52" s="2"/>
+      <c r="O52" s="2"/>
+      <c r="P52" s="2"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="2"/>
+      <c r="T52" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="U52" s="6"/>
+      <c r="V52" s="6"/>
+      <c r="W52" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="71" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFBA5AD1-CF75-4043-940E-F48624E3E95D}"/>
+  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C2CF55-BC42-4210-9A03-9FC77637A3A3}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="172">
   <si>
     <t>Id</t>
   </si>
@@ -528,6 +528,33 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/5E9551ED-DBE7-4A4A-8279-17F12D33E143_Starbucks%20CC%20Plaza%20S.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38186@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Arboledas</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Arboledas.jpg</t>
+  </si>
+  <si>
+    <t>sergio.parra@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Sergio Daniel Parra Barrera</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17899334241135267361703018309650_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38368@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Luna Park</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/17899335580904355345414881985998_Starbucks%20Luna%20Park.jpg</t>
   </si>
 </sst>
 </file>
@@ -665,8 +692,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W52" totalsRowShown="0">
-  <autoFilter ref="A1:W52" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W55" totalsRowShown="0">
+  <autoFilter ref="A1:W55" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -833,7 +860,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="879" latestEventMarker="1270">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="882" latestEventMarker="1273">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1160,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W52"/>
+  <dimension ref="A1:W55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -2434,7 +2461,7 @@
       <c r="S32" s="2"/>
       <c r="T32" s="5"/>
     </row>
-    <row r="33" spans="1:23">
+    <row r="33" spans="1:21">
       <c r="A33">
         <v>860</v>
       </c>
@@ -2472,7 +2499,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="34" spans="1:23">
+    <row r="34" spans="1:21">
       <c r="A34">
         <v>861</v>
       </c>
@@ -2510,7 +2537,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:21">
       <c r="A35">
         <v>862</v>
       </c>
@@ -2548,7 +2575,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:21">
       <c r="A36">
         <v>863</v>
       </c>
@@ -2586,7 +2613,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="37" spans="1:23">
+    <row r="37" spans="1:21">
       <c r="A37">
         <v>864</v>
       </c>
@@ -2624,7 +2651,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:23">
+    <row r="38" spans="1:21">
       <c r="A38">
         <v>865</v>
       </c>
@@ -2666,8 +2693,8 @@
       </c>
       <c r="T38" s="5"/>
     </row>
-    <row r="39" spans="1:23">
-      <c r="A39" s="6">
+    <row r="39" spans="1:21">
+      <c r="A39">
         <v>866</v>
       </c>
       <c r="B39" s="1">
@@ -2682,7 +2709,7 @@
       <c r="E39" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39">
         <v>38266</v>
       </c>
       <c r="G39" s="2" t="s">
@@ -2703,12 +2730,9 @@
       <c r="T39" s="5" t="s">
         <v>135</v>
       </c>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-    </row>
-    <row r="40" spans="1:23">
-      <c r="A40" s="6">
+    </row>
+    <row r="40" spans="1:21">
+      <c r="A40">
         <v>867</v>
       </c>
       <c r="B40" s="1">
@@ -2723,7 +2747,7 @@
       <c r="E40" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40">
         <v>38418</v>
       </c>
       <c r="G40" s="2" t="s">
@@ -2744,12 +2768,9 @@
       <c r="R40" s="4"/>
       <c r="S40" s="2"/>
       <c r="T40" s="5"/>
-      <c r="U40" s="6"/>
-      <c r="V40" s="6"/>
-      <c r="W40" s="6"/>
-    </row>
-    <row r="41" spans="1:23">
-      <c r="A41" s="6">
+    </row>
+    <row r="41" spans="1:21">
+      <c r="A41">
         <v>868</v>
       </c>
       <c r="B41" s="1">
@@ -2764,7 +2785,7 @@
       <c r="E41" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F41" s="6">
+      <c r="F41">
         <v>38119</v>
       </c>
       <c r="G41" s="2" t="s">
@@ -2785,12 +2806,9 @@
       <c r="T41" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="U41" s="6"/>
-      <c r="V41" s="6"/>
-      <c r="W41" s="6"/>
-    </row>
-    <row r="42" spans="1:23">
-      <c r="A42" s="6">
+    </row>
+    <row r="42" spans="1:21">
+      <c r="A42">
         <v>869</v>
       </c>
       <c r="B42" s="1">
@@ -2805,7 +2823,7 @@
       <c r="E42" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F42" s="6">
+      <c r="F42">
         <v>38339</v>
       </c>
       <c r="G42" s="2" t="s">
@@ -2828,12 +2846,9 @@
       <c r="R42" s="4"/>
       <c r="S42" s="2"/>
       <c r="T42" s="5"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-    </row>
-    <row r="43" spans="1:23">
-      <c r="A43" s="6">
+    </row>
+    <row r="43" spans="1:21">
+      <c r="A43">
         <v>870</v>
       </c>
       <c r="B43" s="1">
@@ -2848,7 +2863,7 @@
       <c r="E43" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F43" s="6">
+      <c r="F43">
         <v>38339</v>
       </c>
       <c r="G43" s="2" t="s">
@@ -2869,12 +2884,9 @@
       <c r="R43" s="4"/>
       <c r="S43" s="2"/>
       <c r="T43" s="5"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-    </row>
-    <row r="44" spans="1:23">
-      <c r="A44" s="6">
+    </row>
+    <row r="44" spans="1:21">
+      <c r="A44">
         <v>871</v>
       </c>
       <c r="B44" s="1">
@@ -2889,7 +2901,7 @@
       <c r="E44" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F44" s="6">
+      <c r="F44">
         <v>38339</v>
       </c>
       <c r="G44" s="2" t="s">
@@ -2910,12 +2922,9 @@
       <c r="R44" s="4"/>
       <c r="S44" s="2"/>
       <c r="T44" s="5"/>
-      <c r="U44" s="6"/>
-      <c r="V44" s="6"/>
-      <c r="W44" s="6"/>
-    </row>
-    <row r="45" spans="1:23">
-      <c r="A45" s="6">
+    </row>
+    <row r="45" spans="1:21">
+      <c r="A45">
         <v>872</v>
       </c>
       <c r="B45" s="1">
@@ -2930,7 +2939,7 @@
       <c r="E45" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F45" s="6">
+      <c r="F45">
         <v>38411</v>
       </c>
       <c r="G45" s="2" t="s">
@@ -2951,12 +2960,9 @@
       <c r="T45" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="U45" s="6"/>
-      <c r="V45" s="6"/>
-      <c r="W45" s="6"/>
-    </row>
-    <row r="46" spans="1:23">
-      <c r="A46" s="6">
+    </row>
+    <row r="46" spans="1:21">
+      <c r="A46">
         <v>873</v>
       </c>
       <c r="B46" s="1">
@@ -2971,7 +2977,7 @@
       <c r="E46" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F46" s="6">
+      <c r="F46">
         <v>38339</v>
       </c>
       <c r="G46" s="2" t="s">
@@ -2992,12 +2998,9 @@
       <c r="R46" s="4"/>
       <c r="S46" s="2"/>
       <c r="T46" s="5"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-    </row>
-    <row r="47" spans="1:23">
-      <c r="A47" s="6">
+    </row>
+    <row r="47" spans="1:21">
+      <c r="A47">
         <v>874</v>
       </c>
       <c r="B47" s="1">
@@ -3012,7 +3015,7 @@
       <c r="E47" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F47" s="6">
+      <c r="F47">
         <v>38339</v>
       </c>
       <c r="G47" s="2" t="s">
@@ -3035,12 +3038,9 @@
       <c r="R47" s="4"/>
       <c r="S47" s="2"/>
       <c r="T47" s="5"/>
-      <c r="U47" s="6"/>
-      <c r="V47" s="6"/>
-      <c r="W47" s="6"/>
-    </row>
-    <row r="48" spans="1:23">
-      <c r="A48" s="6">
+    </row>
+    <row r="48" spans="1:21">
+      <c r="A48">
         <v>875</v>
       </c>
       <c r="B48" s="1">
@@ -3055,7 +3055,7 @@
       <c r="E48" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F48" s="6">
+      <c r="F48">
         <v>38411</v>
       </c>
       <c r="G48" s="2" t="s">
@@ -3074,14 +3074,12 @@
       <c r="R48" s="4"/>
       <c r="S48" s="2"/>
       <c r="T48" s="5"/>
-      <c r="U48" s="6" t="s">
+      <c r="U48" t="s">
         <v>156</v>
       </c>
-      <c r="V48" s="6"/>
-      <c r="W48" s="6"/>
     </row>
     <row r="49" spans="1:23">
-      <c r="A49" s="6">
+      <c r="A49">
         <v>876</v>
       </c>
       <c r="B49" s="1">
@@ -3096,7 +3094,7 @@
       <c r="E49" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F49" s="6">
+      <c r="F49">
         <v>38339</v>
       </c>
       <c r="G49" s="2" t="s">
@@ -3117,12 +3115,9 @@
       <c r="R49" s="4"/>
       <c r="S49" s="2"/>
       <c r="T49" s="5"/>
-      <c r="U49" s="6"/>
-      <c r="V49" s="6"/>
-      <c r="W49" s="6"/>
     </row>
     <row r="50" spans="1:23">
-      <c r="A50" s="6">
+      <c r="A50">
         <v>877</v>
       </c>
       <c r="B50" s="1">
@@ -3137,7 +3132,7 @@
       <c r="E50" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F50" s="6">
+      <c r="F50">
         <v>38339</v>
       </c>
       <c r="G50" s="2" t="s">
@@ -3158,12 +3153,9 @@
       <c r="R50" s="4"/>
       <c r="S50" s="2"/>
       <c r="T50" s="5"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
     </row>
     <row r="51" spans="1:23">
-      <c r="A51" s="6">
+      <c r="A51">
         <v>878</v>
       </c>
       <c r="B51" s="1">
@@ -3178,7 +3170,7 @@
       <c r="E51" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F51" s="6">
+      <c r="F51">
         <v>38339</v>
       </c>
       <c r="G51" s="2" t="s">
@@ -3203,12 +3195,9 @@
         <v>159</v>
       </c>
       <c r="T51" s="5"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
     </row>
     <row r="52" spans="1:23">
-      <c r="A52" s="6">
+      <c r="A52">
         <v>879</v>
       </c>
       <c r="B52" s="1">
@@ -3223,7 +3212,7 @@
       <c r="E52" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="F52" s="6">
+      <c r="F52">
         <v>38427</v>
       </c>
       <c r="G52" s="2" t="s">
@@ -3244,9 +3233,131 @@
       <c r="T52" s="5" t="s">
         <v>162</v>
       </c>
-      <c r="U52" s="6"/>
-      <c r="V52" s="6"/>
-      <c r="W52" s="6"/>
+    </row>
+    <row r="53" spans="1:23">
+      <c r="A53" s="6">
+        <v>880</v>
+      </c>
+      <c r="B53" s="1">
+        <v>46285.504050925898</v>
+      </c>
+      <c r="C53" s="1">
+        <v>46285.504502314798</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="F53" s="6">
+        <v>38186</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2"/>
+      <c r="L53" s="2"/>
+      <c r="M53" s="2"/>
+      <c r="N53" s="2"/>
+      <c r="O53" s="2"/>
+      <c r="P53" s="2"/>
+      <c r="Q53" s="4"/>
+      <c r="R53" s="4"/>
+      <c r="S53" s="2"/>
+      <c r="T53" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="U53" s="6"/>
+      <c r="V53" s="6"/>
+      <c r="W53" s="6"/>
+    </row>
+    <row r="54" spans="1:23">
+      <c r="A54" s="6">
+        <v>881</v>
+      </c>
+      <c r="B54" s="1">
+        <v>46285.571921296301</v>
+      </c>
+      <c r="C54" s="1">
+        <v>46285.572222222203</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F54" s="6">
+        <v>38561</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2"/>
+      <c r="L54" s="2"/>
+      <c r="M54" s="2"/>
+      <c r="N54" s="2"/>
+      <c r="O54" s="2"/>
+      <c r="P54" s="2"/>
+      <c r="Q54" s="4"/>
+      <c r="R54" s="4"/>
+      <c r="S54" s="2"/>
+      <c r="T54" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="U54" s="6"/>
+      <c r="V54" s="6"/>
+      <c r="W54" s="6"/>
+    </row>
+    <row r="55" spans="1:23">
+      <c r="A55" s="6">
+        <v>882</v>
+      </c>
+      <c r="B55" s="1">
+        <v>46285.572731481501</v>
+      </c>
+      <c r="C55" s="1">
+        <v>46285.574131944399</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F55" s="6">
+        <v>38368</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2"/>
+      <c r="L55" s="2"/>
+      <c r="M55" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N55" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="O55" s="2"/>
+      <c r="P55" s="2"/>
+      <c r="Q55" s="4"/>
+      <c r="R55" s="4"/>
+      <c r="S55" s="2"/>
+      <c r="T55" s="5"/>
+      <c r="U55" s="6"/>
+      <c r="V55" s="6"/>
+      <c r="W55" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{44C2CF55-BC42-4210-9A03-9FC77637A3A3}"/>
+  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29BA6740-EFEF-4604-8B7F-078D37A35A17}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="173">
   <si>
     <t>Id</t>
   </si>
@@ -555,6 +555,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/17899335580904355345414881985998_Starbucks%20Luna%20Park.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/51453A22-3233-4913-B78D-3D37C71F4E9B_Starbucks%20CC%20Coalcal.jpeg</t>
   </si>
 </sst>
 </file>
@@ -692,8 +695,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W55" totalsRowShown="0">
-  <autoFilter ref="A1:W55" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W56" totalsRowShown="0">
+  <autoFilter ref="A1:W56" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -860,7 +863,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="882" latestEventMarker="1273">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="883" latestEventMarker="1274">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1187,7 +1190,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W55"/>
+  <dimension ref="A1:W56"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3235,7 +3238,7 @@
       </c>
     </row>
     <row r="53" spans="1:23">
-      <c r="A53" s="6">
+      <c r="A53">
         <v>880</v>
       </c>
       <c r="B53" s="1">
@@ -3250,7 +3253,7 @@
       <c r="E53" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="F53" s="6">
+      <c r="F53">
         <v>38186</v>
       </c>
       <c r="G53" s="2" t="s">
@@ -3271,12 +3274,9 @@
       <c r="T53" s="5" t="s">
         <v>165</v>
       </c>
-      <c r="U53" s="6"/>
-      <c r="V53" s="6"/>
-      <c r="W53" s="6"/>
     </row>
     <row r="54" spans="1:23">
-      <c r="A54" s="6">
+      <c r="A54">
         <v>881</v>
       </c>
       <c r="B54" s="1">
@@ -3291,7 +3291,7 @@
       <c r="E54" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="F54" s="6">
+      <c r="F54">
         <v>38561</v>
       </c>
       <c r="G54" s="2" t="s">
@@ -3312,12 +3312,9 @@
       <c r="T54" s="5" t="s">
         <v>168</v>
       </c>
-      <c r="U54" s="6"/>
-      <c r="V54" s="6"/>
-      <c r="W54" s="6"/>
     </row>
     <row r="55" spans="1:23">
-      <c r="A55" s="6">
+      <c r="A55">
         <v>882</v>
       </c>
       <c r="B55" s="1">
@@ -3332,7 +3329,7 @@
       <c r="E55" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F55" s="6">
+      <c r="F55">
         <v>38368</v>
       </c>
       <c r="G55" s="2" t="s">
@@ -3355,9 +3352,47 @@
       <c r="R55" s="4"/>
       <c r="S55" s="2"/>
       <c r="T55" s="5"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
+    </row>
+    <row r="56" spans="1:23">
+      <c r="A56" s="6">
+        <v>883</v>
+      </c>
+      <c r="B56" s="1">
+        <v>46285.621018518497</v>
+      </c>
+      <c r="C56" s="1">
+        <v>46285.621180555601</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F56" s="6">
+        <v>38401</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="2"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="4"/>
+      <c r="R56" s="4"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="5" t="s">
+        <v>172</v>
+      </c>
+      <c r="U56" s="6"/>
+      <c r="V56" s="6"/>
+      <c r="W56" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="77" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29BA6740-EFEF-4604-8B7F-078D37A35A17}"/>
+  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC3D38D-1D6A-4AAA-8867-9332FCC097FE}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="191">
   <si>
     <t>Id</t>
   </si>
@@ -558,6 +558,60 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/51453A22-3233-4913-B78D-3D37C71F4E9B_Starbucks%20CC%20Coalcal.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38992@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Tapo puerta Oriente</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17899391722237790240458250031517_Starbucks%20Tapo%20puert.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17899412792641588234003423497223_Fany%20Jeovana%20Echever.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38695@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks CEMTRAM 4 Caminos carso</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20CEMTRAM%204.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17899435349878571305100755418908_Starbucks%20Luna%20Park.jpg</t>
+  </si>
+  <si>
+    <t>kevin.suarez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Kevin Arturo Suarez Gonzalez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17899458723764813265646328844394_Kevin%20Arturo%20Suarez.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38363@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Galerias Atizapan</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/c5a010ad-8fdc-48c6-b3f0-ecb149151cb2_Starbucks%20Galerias%20A.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38604@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Cosmopol</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17899466022497977760900645677473_Starbucks%20Cosmopol.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17899472479666534303915902308565_Starbucks%20Patio%20Ecat.jpg</t>
   </si>
 </sst>
 </file>
@@ -695,8 +749,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W56" totalsRowShown="0">
-  <autoFilter ref="A1:W56" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W64" totalsRowShown="0">
+  <autoFilter ref="A1:W64" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -863,7 +917,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="883" latestEventMarker="1274">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="891" latestEventMarker="1282">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1190,7 +1244,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W56"/>
+  <dimension ref="A1:W64"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3354,7 +3408,7 @@
       <c r="T55" s="5"/>
     </row>
     <row r="56" spans="1:23">
-      <c r="A56" s="6">
+      <c r="A56">
         <v>883</v>
       </c>
       <c r="B56" s="1">
@@ -3369,7 +3423,7 @@
       <c r="E56" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F56" s="6">
+      <c r="F56">
         <v>38401</v>
       </c>
       <c r="G56" s="2" t="s">
@@ -3390,9 +3444,334 @@
       <c r="T56" s="5" t="s">
         <v>172</v>
       </c>
-      <c r="U56" s="6"/>
-      <c r="V56" s="6"/>
-      <c r="W56" s="6"/>
+    </row>
+    <row r="57" spans="1:23">
+      <c r="A57" s="6">
+        <v>884</v>
+      </c>
+      <c r="B57" s="1">
+        <v>46285.638113425899</v>
+      </c>
+      <c r="C57" s="1">
+        <v>46285.638946759304</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F57" s="6">
+        <v>38992</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2"/>
+      <c r="L57" s="2"/>
+      <c r="M57" s="2"/>
+      <c r="N57" s="2"/>
+      <c r="O57" s="2"/>
+      <c r="P57" s="2"/>
+      <c r="Q57" s="4"/>
+      <c r="R57" s="4"/>
+      <c r="S57" s="2"/>
+      <c r="T57" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="U57" s="6"/>
+      <c r="V57" s="6"/>
+      <c r="W57" s="6"/>
+    </row>
+    <row r="58" spans="1:23">
+      <c r="A58" s="6">
+        <v>885</v>
+      </c>
+      <c r="B58" s="1">
+        <v>46285.662870370397</v>
+      </c>
+      <c r="C58" s="1">
+        <v>46285.663576388899</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="F58" s="6">
+        <v>38529</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2"/>
+      <c r="L58" s="2"/>
+      <c r="M58" s="2"/>
+      <c r="N58" s="2"/>
+      <c r="O58" s="2"/>
+      <c r="P58" s="2"/>
+      <c r="Q58" s="4"/>
+      <c r="R58" s="4"/>
+      <c r="S58" s="2"/>
+      <c r="T58" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="U58" s="6"/>
+      <c r="V58" s="6"/>
+      <c r="W58" s="6"/>
+    </row>
+    <row r="59" spans="1:23">
+      <c r="A59" s="6">
+        <v>886</v>
+      </c>
+      <c r="B59" s="1">
+        <v>46285.669421296298</v>
+      </c>
+      <c r="C59" s="1">
+        <v>46285.670185185198</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F59" s="6">
+        <v>38695</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2"/>
+      <c r="L59" s="2"/>
+      <c r="M59" s="2"/>
+      <c r="N59" s="2"/>
+      <c r="O59" s="2"/>
+      <c r="P59" s="2"/>
+      <c r="Q59" s="4"/>
+      <c r="R59" s="4"/>
+      <c r="S59" s="2"/>
+      <c r="T59" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="U59" s="6"/>
+      <c r="V59" s="6"/>
+      <c r="W59" s="6"/>
+    </row>
+    <row r="60" spans="1:23">
+      <c r="A60" s="6">
+        <v>887</v>
+      </c>
+      <c r="B60" s="1">
+        <v>46285.688738425903</v>
+      </c>
+      <c r="C60" s="1">
+        <v>46285.689282407402</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F60" s="6">
+        <v>38368</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2"/>
+      <c r="L60" s="2"/>
+      <c r="M60" s="2"/>
+      <c r="N60" s="2"/>
+      <c r="O60" s="2"/>
+      <c r="P60" s="2"/>
+      <c r="Q60" s="4"/>
+      <c r="R60" s="4"/>
+      <c r="S60" s="2"/>
+      <c r="T60" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="U60" s="6"/>
+      <c r="V60" s="6"/>
+      <c r="W60" s="6"/>
+    </row>
+    <row r="61" spans="1:23">
+      <c r="A61" s="6">
+        <v>888</v>
+      </c>
+      <c r="B61" s="1">
+        <v>46285.715972222199</v>
+      </c>
+      <c r="C61" s="1">
+        <v>46285.7163194444</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F61" s="6">
+        <v>43130</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2"/>
+      <c r="L61" s="2"/>
+      <c r="M61" s="2"/>
+      <c r="N61" s="2"/>
+      <c r="O61" s="2"/>
+      <c r="P61" s="2"/>
+      <c r="Q61" s="4"/>
+      <c r="R61" s="4"/>
+      <c r="S61" s="2"/>
+      <c r="T61" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="U61" s="6"/>
+      <c r="V61" s="6"/>
+      <c r="W61" s="6"/>
+    </row>
+    <row r="62" spans="1:23">
+      <c r="A62" s="6">
+        <v>889</v>
+      </c>
+      <c r="B62" s="1">
+        <v>46285.716342592597</v>
+      </c>
+      <c r="C62" s="1">
+        <v>46285.718784722201</v>
+      </c>
+      <c r="D62" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E62" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F62" s="6">
+        <v>38363</v>
+      </c>
+      <c r="G62" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="J62" s="2"/>
+      <c r="K62" s="2"/>
+      <c r="L62" s="2"/>
+      <c r="M62" s="2"/>
+      <c r="N62" s="2"/>
+      <c r="O62" s="2"/>
+      <c r="P62" s="2"/>
+      <c r="Q62" s="4"/>
+      <c r="R62" s="4"/>
+      <c r="S62" s="2"/>
+      <c r="T62" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="U62" s="6"/>
+      <c r="V62" s="6"/>
+      <c r="W62" s="6"/>
+    </row>
+    <row r="63" spans="1:23">
+      <c r="A63" s="6">
+        <v>890</v>
+      </c>
+      <c r="B63" s="1">
+        <v>46285.697152777801</v>
+      </c>
+      <c r="C63" s="1">
+        <v>46285.725115740701</v>
+      </c>
+      <c r="D63" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E63" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F63" s="6">
+        <v>38604</v>
+      </c>
+      <c r="G63" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="J63" s="2"/>
+      <c r="K63" s="2"/>
+      <c r="L63" s="2"/>
+      <c r="M63" s="2"/>
+      <c r="N63" s="2"/>
+      <c r="O63" s="2"/>
+      <c r="P63" s="2"/>
+      <c r="Q63" s="4"/>
+      <c r="R63" s="4"/>
+      <c r="S63" s="2"/>
+      <c r="T63" s="5" t="s">
+        <v>189</v>
+      </c>
+      <c r="U63" s="6"/>
+      <c r="V63" s="6"/>
+      <c r="W63" s="6"/>
+    </row>
+    <row r="64" spans="1:23">
+      <c r="A64" s="6">
+        <v>891</v>
+      </c>
+      <c r="B64" s="1">
+        <v>46285.727719907401</v>
+      </c>
+      <c r="C64" s="1">
+        <v>46285.732407407399</v>
+      </c>
+      <c r="D64" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E64" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F64" s="6">
+        <v>38515</v>
+      </c>
+      <c r="G64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="J64" s="2"/>
+      <c r="K64" s="2"/>
+      <c r="L64" s="2"/>
+      <c r="M64" s="2"/>
+      <c r="N64" s="2"/>
+      <c r="O64" s="2"/>
+      <c r="P64" s="2"/>
+      <c r="Q64" s="4"/>
+      <c r="R64" s="4"/>
+      <c r="S64" s="2"/>
+      <c r="T64" s="5" t="s">
+        <v>190</v>
+      </c>
+      <c r="U64" s="6"/>
+      <c r="V64" s="6"/>
+      <c r="W64" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="80" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1EC3D38D-1D6A-4AAA-8867-9332FCC097FE}"/>
+  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6C44C5A-1507-45E2-96B9-EB11232DF38D}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="200">
   <si>
     <t>Id</t>
   </si>
@@ -612,6 +612,33 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17899472479666534303915902308565_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_3490_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38511@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Ciudad Jardin II</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Ciudad%20Jar.jpg</t>
+  </si>
+  <si>
+    <t>hector.estevez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Hector Ruben Estevez Torres</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Hector%20Ruben%20Estevez.jpg</t>
+  </si>
+  <si>
+    <t>Peanuts Linus&amp;Snoopy</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Lucy_24Sep/IMG_3490_Starbucks%20Mega%20Izcal.jpeg</t>
   </si>
 </sst>
 </file>
@@ -749,8 +776,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W64" totalsRowShown="0">
-  <autoFilter ref="A1:W64" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W68" totalsRowShown="0">
+  <autoFilter ref="A1:W68" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -917,7 +944,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="891" latestEventMarker="1282">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="895" latestEventMarker="1286">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1244,7 +1271,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W64"/>
+  <dimension ref="A1:W68"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3135,7 +3162,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:20">
       <c r="A49">
         <v>876</v>
       </c>
@@ -3173,7 +3200,7 @@
       <c r="S49" s="2"/>
       <c r="T49" s="5"/>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:20">
       <c r="A50">
         <v>877</v>
       </c>
@@ -3211,7 +3238,7 @@
       <c r="S50" s="2"/>
       <c r="T50" s="5"/>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:20">
       <c r="A51">
         <v>878</v>
       </c>
@@ -3253,7 +3280,7 @@
       </c>
       <c r="T51" s="5"/>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:20">
       <c r="A52">
         <v>879</v>
       </c>
@@ -3291,7 +3318,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:20">
       <c r="A53">
         <v>880</v>
       </c>
@@ -3329,7 +3356,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:20">
       <c r="A54">
         <v>881</v>
       </c>
@@ -3367,7 +3394,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:20">
       <c r="A55">
         <v>882</v>
       </c>
@@ -3407,7 +3434,7 @@
       <c r="S55" s="2"/>
       <c r="T55" s="5"/>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:20">
       <c r="A56">
         <v>883</v>
       </c>
@@ -3445,8 +3472,8 @@
         <v>172</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
-      <c r="A57" s="6">
+    <row r="57" spans="1:20">
+      <c r="A57">
         <v>884</v>
       </c>
       <c r="B57" s="1">
@@ -3461,7 +3488,7 @@
       <c r="E57" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F57" s="6">
+      <c r="F57">
         <v>38992</v>
       </c>
       <c r="G57" s="2" t="s">
@@ -3482,12 +3509,9 @@
       <c r="T57" s="5" t="s">
         <v>175</v>
       </c>
-      <c r="U57" s="6"/>
-      <c r="V57" s="6"/>
-      <c r="W57" s="6"/>
-    </row>
-    <row r="58" spans="1:23">
-      <c r="A58" s="6">
+    </row>
+    <row r="58" spans="1:20">
+      <c r="A58">
         <v>885</v>
       </c>
       <c r="B58" s="1">
@@ -3502,7 +3526,7 @@
       <c r="E58" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="F58" s="6">
+      <c r="F58">
         <v>38529</v>
       </c>
       <c r="G58" s="2" t="s">
@@ -3523,12 +3547,9 @@
       <c r="T58" s="5" t="s">
         <v>176</v>
       </c>
-      <c r="U58" s="6"/>
-      <c r="V58" s="6"/>
-      <c r="W58" s="6"/>
-    </row>
-    <row r="59" spans="1:23">
-      <c r="A59" s="6">
+    </row>
+    <row r="59" spans="1:20">
+      <c r="A59">
         <v>886</v>
       </c>
       <c r="B59" s="1">
@@ -3543,7 +3564,7 @@
       <c r="E59" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="F59" s="6">
+      <c r="F59">
         <v>38695</v>
       </c>
       <c r="G59" s="2" t="s">
@@ -3564,12 +3585,9 @@
       <c r="T59" s="5" t="s">
         <v>179</v>
       </c>
-      <c r="U59" s="6"/>
-      <c r="V59" s="6"/>
-      <c r="W59" s="6"/>
-    </row>
-    <row r="60" spans="1:23">
-      <c r="A60" s="6">
+    </row>
+    <row r="60" spans="1:20">
+      <c r="A60">
         <v>887</v>
       </c>
       <c r="B60" s="1">
@@ -3584,7 +3602,7 @@
       <c r="E60" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F60" s="6">
+      <c r="F60">
         <v>38368</v>
       </c>
       <c r="G60" s="2" t="s">
@@ -3605,12 +3623,9 @@
       <c r="T60" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="U60" s="6"/>
-      <c r="V60" s="6"/>
-      <c r="W60" s="6"/>
-    </row>
-    <row r="61" spans="1:23">
-      <c r="A61" s="6">
+    </row>
+    <row r="61" spans="1:20">
+      <c r="A61">
         <v>888</v>
       </c>
       <c r="B61" s="1">
@@ -3625,7 +3640,7 @@
       <c r="E61" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="F61" s="6">
+      <c r="F61">
         <v>43130</v>
       </c>
       <c r="G61" s="2" t="s">
@@ -3646,12 +3661,9 @@
       <c r="T61" s="5" t="s">
         <v>183</v>
       </c>
-      <c r="U61" s="6"/>
-      <c r="V61" s="6"/>
-      <c r="W61" s="6"/>
-    </row>
-    <row r="62" spans="1:23">
-      <c r="A62" s="6">
+    </row>
+    <row r="62" spans="1:20">
+      <c r="A62">
         <v>889</v>
       </c>
       <c r="B62" s="1">
@@ -3666,7 +3678,7 @@
       <c r="E62" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F62" s="6">
+      <c r="F62">
         <v>38363</v>
       </c>
       <c r="G62" s="2" t="s">
@@ -3687,12 +3699,9 @@
       <c r="T62" s="5" t="s">
         <v>186</v>
       </c>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-    </row>
-    <row r="63" spans="1:23">
-      <c r="A63" s="6">
+    </row>
+    <row r="63" spans="1:20">
+      <c r="A63">
         <v>890</v>
       </c>
       <c r="B63" s="1">
@@ -3707,7 +3716,7 @@
       <c r="E63" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F63" s="6">
+      <c r="F63">
         <v>38604</v>
       </c>
       <c r="G63" s="2" t="s">
@@ -3728,12 +3737,9 @@
       <c r="T63" s="5" t="s">
         <v>189</v>
       </c>
-      <c r="U63" s="6"/>
-      <c r="V63" s="6"/>
-      <c r="W63" s="6"/>
-    </row>
-    <row r="64" spans="1:23">
-      <c r="A64" s="6">
+    </row>
+    <row r="64" spans="1:20">
+      <c r="A64">
         <v>891</v>
       </c>
       <c r="B64" s="1">
@@ -3748,7 +3754,7 @@
       <c r="E64" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="F64" s="6">
+      <c r="F64">
         <v>38515</v>
       </c>
       <c r="G64" s="2" t="s">
@@ -3769,9 +3775,170 @@
       <c r="T64" s="5" t="s">
         <v>190</v>
       </c>
-      <c r="U64" s="6"/>
-      <c r="V64" s="6"/>
-      <c r="W64" s="6"/>
+    </row>
+    <row r="65" spans="1:23">
+      <c r="A65" s="6">
+        <v>892</v>
+      </c>
+      <c r="B65" s="1">
+        <v>46285.737418981502</v>
+      </c>
+      <c r="C65" s="1">
+        <v>46285.740914351903</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E65" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F65" s="6">
+        <v>38333</v>
+      </c>
+      <c r="G65" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="J65" s="2"/>
+      <c r="K65" s="2"/>
+      <c r="L65" s="2"/>
+      <c r="M65" s="2"/>
+      <c r="N65" s="2"/>
+      <c r="O65" s="2"/>
+      <c r="P65" s="2"/>
+      <c r="Q65" s="4"/>
+      <c r="R65" s="4"/>
+      <c r="S65" s="2"/>
+      <c r="T65" s="5" t="s">
+        <v>191</v>
+      </c>
+      <c r="U65" s="6"/>
+      <c r="V65" s="6"/>
+      <c r="W65" s="6"/>
+    </row>
+    <row r="66" spans="1:23">
+      <c r="A66" s="6">
+        <v>893</v>
+      </c>
+      <c r="B66" s="1">
+        <v>46285.753125000003</v>
+      </c>
+      <c r="C66" s="1">
+        <v>46285.754803240699</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="E66" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F66" s="6">
+        <v>38511</v>
+      </c>
+      <c r="G66" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="J66" s="2"/>
+      <c r="K66" s="2"/>
+      <c r="L66" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="M66" s="2"/>
+      <c r="N66" s="2"/>
+      <c r="O66" s="2"/>
+      <c r="P66" s="2"/>
+      <c r="Q66" s="4"/>
+      <c r="R66" s="4"/>
+      <c r="S66" s="2"/>
+      <c r="T66" s="5"/>
+      <c r="U66" s="6"/>
+      <c r="V66" s="6"/>
+      <c r="W66" s="6"/>
+    </row>
+    <row r="67" spans="1:23">
+      <c r="A67" s="6">
+        <v>894</v>
+      </c>
+      <c r="B67" s="1">
+        <v>46285.757152777798</v>
+      </c>
+      <c r="C67" s="1">
+        <v>46285.7577199074</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E67" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="F67" s="6">
+        <v>38143</v>
+      </c>
+      <c r="G67" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="2"/>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
+      <c r="O67" s="2"/>
+      <c r="P67" s="2"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="2"/>
+      <c r="T67" s="5" t="s">
+        <v>197</v>
+      </c>
+      <c r="U67" s="6"/>
+      <c r="V67" s="6"/>
+      <c r="W67" s="6"/>
+    </row>
+    <row r="68" spans="1:23">
+      <c r="A68" s="6">
+        <v>895</v>
+      </c>
+      <c r="B68" s="1">
+        <v>46285.756018518499</v>
+      </c>
+      <c r="C68" s="1">
+        <v>46285.758657407401</v>
+      </c>
+      <c r="D68" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E68" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="F68" s="6">
+        <v>38333</v>
+      </c>
+      <c r="G68" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="J68" s="2"/>
+      <c r="K68" s="2"/>
+      <c r="L68" s="2"/>
+      <c r="M68" s="2"/>
+      <c r="N68" s="2"/>
+      <c r="O68" s="2"/>
+      <c r="P68" s="2"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="2"/>
+      <c r="T68" s="5"/>
+      <c r="U68" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="V68" s="6"/>
+      <c r="W68" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D6C44C5A-1507-45E2-96B9-EB11232DF38D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0D7936D-9650-4734-82CD-7D8F8FF1C0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="303" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="207">
   <si>
     <t>Id</t>
   </si>
@@ -639,6 +639,27 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Lucy_24Sep/IMG_3490_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43070@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Rojo Gomez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Rojo%20Gomez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Lucy_24Sep/20260919_094055-COLLAGE_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>diego.conde@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Diego Conde Merino</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/1789953621847314136934969667231_Diego%20Conde%20Merino.jpg</t>
   </si>
 </sst>
 </file>
@@ -776,8 +797,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W68" totalsRowShown="0">
-  <autoFilter ref="A1:W68" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W71" totalsRowShown="0">
+  <autoFilter ref="A1:W71" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -944,7 +965,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="895" latestEventMarker="1286">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="898" latestEventMarker="1289">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1271,7 +1292,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W68"/>
+  <dimension ref="A1:W71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3777,7 +3798,7 @@
       </c>
     </row>
     <row r="65" spans="1:23">
-      <c r="A65" s="6">
+      <c r="A65">
         <v>892</v>
       </c>
       <c r="B65" s="1">
@@ -3792,7 +3813,7 @@
       <c r="E65" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F65" s="6">
+      <c r="F65">
         <v>38333</v>
       </c>
       <c r="G65" s="2" t="s">
@@ -3813,12 +3834,9 @@
       <c r="T65" s="5" t="s">
         <v>191</v>
       </c>
-      <c r="U65" s="6"/>
-      <c r="V65" s="6"/>
-      <c r="W65" s="6"/>
     </row>
     <row r="66" spans="1:23">
-      <c r="A66" s="6">
+      <c r="A66">
         <v>893</v>
       </c>
       <c r="B66" s="1">
@@ -3833,7 +3851,7 @@
       <c r="E66" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="F66" s="6">
+      <c r="F66">
         <v>38511</v>
       </c>
       <c r="G66" s="2" t="s">
@@ -3854,12 +3872,9 @@
       <c r="R66" s="4"/>
       <c r="S66" s="2"/>
       <c r="T66" s="5"/>
-      <c r="U66" s="6"/>
-      <c r="V66" s="6"/>
-      <c r="W66" s="6"/>
     </row>
     <row r="67" spans="1:23">
-      <c r="A67" s="6">
+      <c r="A67">
         <v>894</v>
       </c>
       <c r="B67" s="1">
@@ -3874,7 +3889,7 @@
       <c r="E67" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="F67" s="6">
+      <c r="F67">
         <v>38143</v>
       </c>
       <c r="G67" s="2" t="s">
@@ -3895,12 +3910,9 @@
       <c r="T67" s="5" t="s">
         <v>197</v>
       </c>
-      <c r="U67" s="6"/>
-      <c r="V67" s="6"/>
-      <c r="W67" s="6"/>
     </row>
     <row r="68" spans="1:23">
-      <c r="A68" s="6">
+      <c r="A68">
         <v>895</v>
       </c>
       <c r="B68" s="1">
@@ -3915,7 +3927,7 @@
       <c r="E68" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F68" s="6">
+      <c r="F68">
         <v>38333</v>
       </c>
       <c r="G68" s="2" t="s">
@@ -3934,11 +3946,132 @@
       <c r="R68" s="4"/>
       <c r="S68" s="2"/>
       <c r="T68" s="5"/>
-      <c r="U68" s="6" t="s">
+      <c r="U68" t="s">
         <v>199</v>
       </c>
-      <c r="V68" s="6"/>
-      <c r="W68" s="6"/>
+    </row>
+    <row r="69" spans="1:23">
+      <c r="A69" s="6">
+        <v>896</v>
+      </c>
+      <c r="B69" s="1">
+        <v>46285.776655092603</v>
+      </c>
+      <c r="C69" s="1">
+        <v>46285.777777777803</v>
+      </c>
+      <c r="D69" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E69" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F69" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G69" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="J69" s="2"/>
+      <c r="K69" s="2"/>
+      <c r="L69" s="2"/>
+      <c r="M69" s="2"/>
+      <c r="N69" s="2"/>
+      <c r="O69" s="2"/>
+      <c r="P69" s="2"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="2"/>
+      <c r="T69" s="5" t="s">
+        <v>202</v>
+      </c>
+      <c r="U69" s="6"/>
+      <c r="V69" s="6"/>
+      <c r="W69" s="6"/>
+    </row>
+    <row r="70" spans="1:23">
+      <c r="A70" s="6">
+        <v>897</v>
+      </c>
+      <c r="B70" s="1">
+        <v>46285.803402777798</v>
+      </c>
+      <c r="C70" s="1">
+        <v>46285.8035648148</v>
+      </c>
+      <c r="D70" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E70" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F70" s="6">
+        <v>38862</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="J70" s="2"/>
+      <c r="K70" s="2"/>
+      <c r="L70" s="2"/>
+      <c r="M70" s="2"/>
+      <c r="N70" s="2"/>
+      <c r="O70" s="2"/>
+      <c r="P70" s="2"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="2"/>
+      <c r="T70" s="5"/>
+      <c r="U70" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="V70" s="6"/>
+      <c r="W70" s="6"/>
+    </row>
+    <row r="71" spans="1:23">
+      <c r="A71" s="6">
+        <v>898</v>
+      </c>
+      <c r="B71" s="1">
+        <v>46285.804432870398</v>
+      </c>
+      <c r="C71" s="1">
+        <v>46285.8059490741</v>
+      </c>
+      <c r="D71" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="E71" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="F71" s="6">
+        <v>38339</v>
+      </c>
+      <c r="G71" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="J71" s="2"/>
+      <c r="K71" s="2"/>
+      <c r="L71" s="2"/>
+      <c r="M71" s="2"/>
+      <c r="N71" s="2"/>
+      <c r="O71" s="2"/>
+      <c r="P71" s="2"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="2"/>
+      <c r="T71" s="5" t="s">
+        <v>206</v>
+      </c>
+      <c r="U71" s="6"/>
+      <c r="V71" s="6"/>
+      <c r="W71" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D0D7936D-9650-4734-82CD-7D8F8FF1C0A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EBA9F8F-2EFA-474A-8EF8-AF6C772A8ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="211">
   <si>
     <t>Id</t>
   </si>
@@ -660,6 +660,18 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/1789953621847314136934969667231_Diego%20Conde%20Merino.jpg</t>
+  </si>
+  <si>
+    <t>thelma.melendez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Thelma Edith Melendez Galvan</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/94EC3CDE-6080-497D-BB28-B591958924E2_Thelma%20Edith%20Melende.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Viveros%20Sa.jpg</t>
   </si>
 </sst>
 </file>
@@ -797,8 +809,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W71" totalsRowShown="0">
-  <autoFilter ref="A1:W71" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W73" totalsRowShown="0">
+  <autoFilter ref="A1:W73" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -965,7 +977,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="898" latestEventMarker="1289">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="900" latestEventMarker="1291">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1292,7 +1304,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W71"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -4073,6 +4085,88 @@
       <c r="V71" s="6"/>
       <c r="W71" s="6"/>
     </row>
+    <row r="72" spans="1:23">
+      <c r="A72" s="6">
+        <v>899</v>
+      </c>
+      <c r="B72" s="1">
+        <v>46285.818182870396</v>
+      </c>
+      <c r="C72" s="1">
+        <v>46285.818715277797</v>
+      </c>
+      <c r="D72" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E72" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F72" s="6">
+        <v>38351</v>
+      </c>
+      <c r="G72" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="J72" s="2"/>
+      <c r="K72" s="2"/>
+      <c r="L72" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="M72" s="2"/>
+      <c r="N72" s="2"/>
+      <c r="O72" s="2"/>
+      <c r="P72" s="2"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="2"/>
+      <c r="T72" s="5"/>
+      <c r="U72" s="6"/>
+      <c r="V72" s="6"/>
+      <c r="W72" s="6"/>
+    </row>
+    <row r="73" spans="1:23">
+      <c r="A73" s="6">
+        <v>900</v>
+      </c>
+      <c r="B73" s="1">
+        <v>46285.839664351799</v>
+      </c>
+      <c r="C73" s="1">
+        <v>46285.84</v>
+      </c>
+      <c r="D73" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E73" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F73" s="6">
+        <v>38656</v>
+      </c>
+      <c r="G73" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="J73" s="2"/>
+      <c r="K73" s="2"/>
+      <c r="L73" s="2"/>
+      <c r="M73" s="2"/>
+      <c r="N73" s="2"/>
+      <c r="O73" s="2"/>
+      <c r="P73" s="2"/>
+      <c r="Q73" s="4"/>
+      <c r="R73" s="4"/>
+      <c r="S73" s="2"/>
+      <c r="T73" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="U73" s="6"/>
+      <c r="V73" s="6"/>
+      <c r="W73" s="6"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="T25" r:id="rId1" xr:uid="{62D300EA-F412-4081-9CE3-9E5EE75DBCF4}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4EBA9F8F-2EFA-474A-8EF8-AF6C772A8ECB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E39CD740-88BE-47ED-9BA2-629456E4AED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="323" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="214">
   <si>
     <t>Id</t>
   </si>
@@ -672,6 +672,15 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Viveros%20Sa.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38456@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Las Flores</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Plaza%20Las.jpg</t>
   </si>
 </sst>
 </file>
@@ -809,8 +818,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W73" totalsRowShown="0">
-  <autoFilter ref="A1:W73" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W74" totalsRowShown="0">
+  <autoFilter ref="A1:W74" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -977,7 +986,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="900" latestEventMarker="1291">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="901" latestEventMarker="1292">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1304,7 +1313,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:W74"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -4167,6 +4176,47 @@
       <c r="V73" s="6"/>
       <c r="W73" s="6"/>
     </row>
+    <row r="74" spans="1:23">
+      <c r="A74" s="6">
+        <v>901</v>
+      </c>
+      <c r="B74" s="1">
+        <v>46285.849097222199</v>
+      </c>
+      <c r="C74" s="1">
+        <v>46285.849733796298</v>
+      </c>
+      <c r="D74" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E74" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="F74" s="6">
+        <v>38456</v>
+      </c>
+      <c r="G74" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="J74" s="2"/>
+      <c r="K74" s="2"/>
+      <c r="L74" s="2"/>
+      <c r="M74" s="2"/>
+      <c r="N74" s="2"/>
+      <c r="O74" s="2"/>
+      <c r="P74" s="2"/>
+      <c r="Q74" s="4"/>
+      <c r="R74" s="4"/>
+      <c r="S74" s="2"/>
+      <c r="T74" s="5" t="s">
+        <v>213</v>
+      </c>
+      <c r="U74" s="6"/>
+      <c r="V74" s="6"/>
+      <c r="W74" s="6"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="T25" r:id="rId1" xr:uid="{62D300EA-F412-4081-9CE3-9E5EE75DBCF4}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E39CD740-88BE-47ED-9BA2-629456E4AED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{435C16FB-93B0-40E2-BD69-231312A54AE2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="220">
   <si>
     <t>Id</t>
   </si>
@@ -681,6 +681,24 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Plaza%20Las.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38894@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Galerias Perinorte</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Galerias%20P.jpg</t>
+  </si>
+  <si>
+    <t>luis.perez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Luis Javier Perez Mojica</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/6CF6CDF9-27B3-4DC2-8174-97DA0633FCF6_Luis%20Javier%20Perez%20Mo.jpeg</t>
   </si>
 </sst>
 </file>
@@ -818,8 +836,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W74" totalsRowShown="0">
-  <autoFilter ref="A1:W74" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W76" totalsRowShown="0">
+  <autoFilter ref="A1:W76" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -986,7 +1004,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="901" latestEventMarker="1292">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="903" latestEventMarker="1294">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1313,7 +1331,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W74"/>
+  <dimension ref="A1:W76"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -4217,6 +4235,88 @@
       <c r="V74" s="6"/>
       <c r="W74" s="6"/>
     </row>
+    <row r="75" spans="1:23">
+      <c r="A75" s="6">
+        <v>902</v>
+      </c>
+      <c r="B75" s="1">
+        <v>46285.860462962999</v>
+      </c>
+      <c r="C75" s="1">
+        <v>46285.861203703702</v>
+      </c>
+      <c r="D75" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E75" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F75" s="6">
+        <v>38894</v>
+      </c>
+      <c r="G75" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="J75" s="2"/>
+      <c r="K75" s="2"/>
+      <c r="L75" s="2"/>
+      <c r="M75" s="2"/>
+      <c r="N75" s="2"/>
+      <c r="O75" s="2"/>
+      <c r="P75" s="2"/>
+      <c r="Q75" s="4"/>
+      <c r="R75" s="4"/>
+      <c r="S75" s="2"/>
+      <c r="T75" s="5" t="s">
+        <v>216</v>
+      </c>
+      <c r="U75" s="6"/>
+      <c r="V75" s="6"/>
+      <c r="W75" s="6"/>
+    </row>
+    <row r="76" spans="1:23">
+      <c r="A76" s="6">
+        <v>903</v>
+      </c>
+      <c r="B76" s="1">
+        <v>46285.870069444398</v>
+      </c>
+      <c r="C76" s="1">
+        <v>46285.870717592603</v>
+      </c>
+      <c r="D76" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E76" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="F76" s="6">
+        <v>43193</v>
+      </c>
+      <c r="G76" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="J76" s="2"/>
+      <c r="K76" s="2"/>
+      <c r="L76" s="2"/>
+      <c r="M76" s="2"/>
+      <c r="N76" s="2"/>
+      <c r="O76" s="2"/>
+      <c r="P76" s="2"/>
+      <c r="Q76" s="4"/>
+      <c r="R76" s="4"/>
+      <c r="S76" s="2"/>
+      <c r="T76" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="U76" s="6"/>
+      <c r="V76" s="6"/>
+      <c r="W76" s="6"/>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="T25" r:id="rId1" xr:uid="{62D300EA-F412-4081-9CE3-9E5EE75DBCF4}"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="101" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{435C16FB-93B0-40E2-BD69-231312A54AE2}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CEE60D6-3EA9-433D-9E0A-151A37D74DD8}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="335" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="233">
   <si>
     <t>Id</t>
   </si>
@@ -699,6 +699,45 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/6CF6CDF9-27B3-4DC2-8174-97DA0633FCF6_Luis%20Javier%20Perez%20Mo.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38176@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks DT Periferico Satelite</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/WhatsApp%20Image%202026-09-20%20at%207.39.59%20PM_Starbucks%20DT%20Perifer.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/WhatsApp%20Image%202026-09-20%20at%208.13.27%20PM_Starbucks%20DT%20Perifer.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43152@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Samara Satélite</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Samara%20Sat.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38460@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Santa Monica</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Santa%20Moni.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38930@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Boulevard Aeropuerto DT</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Boulevard.jpg</t>
   </si>
 </sst>
 </file>
@@ -836,8 +875,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W76" totalsRowShown="0">
-  <autoFilter ref="A1:W76" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W81" totalsRowShown="0">
+  <autoFilter ref="A1:W81" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -1004,7 +1043,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="903" latestEventMarker="1294">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="908" latestEventMarker="1299">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1331,7 +1370,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W76"/>
+  <dimension ref="A1:W81"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3990,7 +4029,7 @@
       </c>
     </row>
     <row r="69" spans="1:23">
-      <c r="A69" s="6">
+      <c r="A69">
         <v>896</v>
       </c>
       <c r="B69" s="1">
@@ -4005,7 +4044,7 @@
       <c r="E69" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F69" s="6">
+      <c r="F69">
         <v>43070</v>
       </c>
       <c r="G69" s="2" t="s">
@@ -4026,12 +4065,9 @@
       <c r="T69" s="5" t="s">
         <v>202</v>
       </c>
-      <c r="U69" s="6"/>
-      <c r="V69" s="6"/>
-      <c r="W69" s="6"/>
     </row>
     <row r="70" spans="1:23">
-      <c r="A70" s="6">
+      <c r="A70">
         <v>897</v>
       </c>
       <c r="B70" s="1">
@@ -4046,7 +4082,7 @@
       <c r="E70" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F70" s="6">
+      <c r="F70">
         <v>38862</v>
       </c>
       <c r="G70" s="2" t="s">
@@ -4065,14 +4101,12 @@
       <c r="R70" s="4"/>
       <c r="S70" s="2"/>
       <c r="T70" s="5"/>
-      <c r="U70" s="6" t="s">
+      <c r="U70" t="s">
         <v>203</v>
       </c>
-      <c r="V70" s="6"/>
-      <c r="W70" s="6"/>
     </row>
     <row r="71" spans="1:23">
-      <c r="A71" s="6">
+      <c r="A71">
         <v>898</v>
       </c>
       <c r="B71" s="1">
@@ -4087,7 +4121,7 @@
       <c r="E71" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="F71" s="6">
+      <c r="F71">
         <v>38339</v>
       </c>
       <c r="G71" s="2" t="s">
@@ -4108,12 +4142,9 @@
       <c r="T71" s="5" t="s">
         <v>206</v>
       </c>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
     </row>
     <row r="72" spans="1:23">
-      <c r="A72" s="6">
+      <c r="A72">
         <v>899</v>
       </c>
       <c r="B72" s="1">
@@ -4128,7 +4159,7 @@
       <c r="E72" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F72" s="6">
+      <c r="F72">
         <v>38351</v>
       </c>
       <c r="G72" s="2" t="s">
@@ -4149,12 +4180,9 @@
       <c r="R72" s="4"/>
       <c r="S72" s="2"/>
       <c r="T72" s="5"/>
-      <c r="U72" s="6"/>
-      <c r="V72" s="6"/>
-      <c r="W72" s="6"/>
     </row>
     <row r="73" spans="1:23">
-      <c r="A73" s="6">
+      <c r="A73">
         <v>900</v>
       </c>
       <c r="B73" s="1">
@@ -4169,7 +4197,7 @@
       <c r="E73" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F73" s="6">
+      <c r="F73">
         <v>38656</v>
       </c>
       <c r="G73" s="2" t="s">
@@ -4190,12 +4218,9 @@
       <c r="T73" s="5" t="s">
         <v>210</v>
       </c>
-      <c r="U73" s="6"/>
-      <c r="V73" s="6"/>
-      <c r="W73" s="6"/>
     </row>
     <row r="74" spans="1:23">
-      <c r="A74" s="6">
+      <c r="A74">
         <v>901</v>
       </c>
       <c r="B74" s="1">
@@ -4210,7 +4235,7 @@
       <c r="E74" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="F74" s="6">
+      <c r="F74">
         <v>38456</v>
       </c>
       <c r="G74" s="2" t="s">
@@ -4231,12 +4256,9 @@
       <c r="T74" s="5" t="s">
         <v>213</v>
       </c>
-      <c r="U74" s="6"/>
-      <c r="V74" s="6"/>
-      <c r="W74" s="6"/>
     </row>
     <row r="75" spans="1:23">
-      <c r="A75" s="6">
+      <c r="A75">
         <v>902</v>
       </c>
       <c r="B75" s="1">
@@ -4251,7 +4273,7 @@
       <c r="E75" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="F75" s="6">
+      <c r="F75">
         <v>38894</v>
       </c>
       <c r="G75" s="2" t="s">
@@ -4272,12 +4294,9 @@
       <c r="T75" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
     </row>
     <row r="76" spans="1:23">
-      <c r="A76" s="6">
+      <c r="A76">
         <v>903</v>
       </c>
       <c r="B76" s="1">
@@ -4292,7 +4311,7 @@
       <c r="E76" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="F76" s="6">
+      <c r="F76">
         <v>43193</v>
       </c>
       <c r="G76" s="2" t="s">
@@ -4313,9 +4332,209 @@
       <c r="T76" s="5" t="s">
         <v>219</v>
       </c>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
+    </row>
+    <row r="77" spans="1:23">
+      <c r="A77">
+        <v>904</v>
+      </c>
+      <c r="B77" s="1">
+        <v>46285.902222222197</v>
+      </c>
+      <c r="C77" s="1">
+        <v>46285.902743055602</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F77">
+        <v>38176</v>
+      </c>
+      <c r="G77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="J77" s="2"/>
+      <c r="K77" s="2"/>
+      <c r="L77" s="2"/>
+      <c r="M77" s="2"/>
+      <c r="N77" s="2"/>
+      <c r="O77" s="2"/>
+      <c r="P77" s="2"/>
+      <c r="Q77" s="4"/>
+      <c r="R77" s="4"/>
+      <c r="S77" s="2"/>
+      <c r="T77" s="5" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23">
+      <c r="A78">
+        <v>905</v>
+      </c>
+      <c r="B78" s="1">
+        <v>46285.903032407397</v>
+      </c>
+      <c r="C78" s="1">
+        <v>46285.908125000002</v>
+      </c>
+      <c r="D78" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E78" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="F78">
+        <v>38176</v>
+      </c>
+      <c r="G78" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="J78" s="2"/>
+      <c r="K78" s="2"/>
+      <c r="L78" s="2"/>
+      <c r="M78" s="2"/>
+      <c r="N78" s="2"/>
+      <c r="O78" s="2"/>
+      <c r="P78" s="2"/>
+      <c r="Q78" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R78" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S78" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="T78" s="5"/>
+    </row>
+    <row r="79" spans="1:23">
+      <c r="A79" s="6">
+        <v>906</v>
+      </c>
+      <c r="B79" s="1">
+        <v>46285.883113425902</v>
+      </c>
+      <c r="C79" s="1">
+        <v>46285.955520833297</v>
+      </c>
+      <c r="D79" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E79" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F79" s="6">
+        <v>43152</v>
+      </c>
+      <c r="G79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="J79" s="2"/>
+      <c r="K79" s="2"/>
+      <c r="L79" s="2"/>
+      <c r="M79" s="2"/>
+      <c r="N79" s="2"/>
+      <c r="O79" s="2"/>
+      <c r="P79" s="2"/>
+      <c r="Q79" s="4"/>
+      <c r="R79" s="4"/>
+      <c r="S79" s="2"/>
+      <c r="T79" s="5" t="s">
+        <v>226</v>
+      </c>
+      <c r="U79" s="6"/>
+      <c r="V79" s="6"/>
+      <c r="W79" s="6"/>
+    </row>
+    <row r="80" spans="1:23">
+      <c r="A80" s="6">
+        <v>907</v>
+      </c>
+      <c r="B80" s="1">
+        <v>46285.965312499997</v>
+      </c>
+      <c r="C80" s="1">
+        <v>46285.968553240702</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E80" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F80" s="6">
+        <v>38460</v>
+      </c>
+      <c r="G80" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="J80" s="2"/>
+      <c r="K80" s="2"/>
+      <c r="L80" s="2"/>
+      <c r="M80" s="2"/>
+      <c r="N80" s="2"/>
+      <c r="O80" s="2"/>
+      <c r="P80" s="2"/>
+      <c r="Q80" s="4"/>
+      <c r="R80" s="4"/>
+      <c r="S80" s="2"/>
+      <c r="T80" s="5" t="s">
+        <v>229</v>
+      </c>
+      <c r="U80" s="6"/>
+      <c r="V80" s="6"/>
+      <c r="W80" s="6"/>
+    </row>
+    <row r="81" spans="1:23">
+      <c r="A81" s="6">
+        <v>908</v>
+      </c>
+      <c r="B81" s="1">
+        <v>46285.9909259259</v>
+      </c>
+      <c r="C81" s="1">
+        <v>46285.991226851896</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E81" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F81" s="6">
+        <v>38930</v>
+      </c>
+      <c r="G81" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="J81" s="2"/>
+      <c r="K81" s="2"/>
+      <c r="L81" s="2"/>
+      <c r="M81" s="2"/>
+      <c r="N81" s="2"/>
+      <c r="O81" s="2"/>
+      <c r="P81" s="2"/>
+      <c r="Q81" s="4"/>
+      <c r="R81" s="4"/>
+      <c r="S81" s="2"/>
+      <c r="T81" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="U81" s="6"/>
+      <c r="V81" s="6"/>
+      <c r="W81" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0CEE60D6-3EA9-433D-9E0A-151A37D74DD8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA95BF3E-D697-4423-91F7-02AA4A5E5863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="357" uniqueCount="233">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="239">
   <si>
     <t>Id</t>
   </si>
@@ -738,6 +738,24 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Boulevard.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38845@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Mundo E II</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17899920774881324015647729161528_Starbucks%20Mundo%20E%20II.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38374@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Valle Dorado</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/174D2FF3-C520-40E0-881E-A5648C6DC477_Starbucks%20Valle%20Dora.jpeg</t>
   </si>
 </sst>
 </file>
@@ -875,8 +893,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W81" totalsRowShown="0">
-  <autoFilter ref="A1:W81" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W83" totalsRowShown="0">
+  <autoFilter ref="A1:W83" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -1043,7 +1061,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="908" latestEventMarker="1299">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="910" latestEventMarker="1301">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1370,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W81"/>
+  <dimension ref="A1:W83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3875,7 +3893,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="65" spans="1:23">
+    <row r="65" spans="1:21">
       <c r="A65">
         <v>892</v>
       </c>
@@ -3913,7 +3931,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="66" spans="1:23">
+    <row r="66" spans="1:21">
       <c r="A66">
         <v>893</v>
       </c>
@@ -3951,7 +3969,7 @@
       <c r="S66" s="2"/>
       <c r="T66" s="5"/>
     </row>
-    <row r="67" spans="1:23">
+    <row r="67" spans="1:21">
       <c r="A67">
         <v>894</v>
       </c>
@@ -3989,7 +4007,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="68" spans="1:23">
+    <row r="68" spans="1:21">
       <c r="A68">
         <v>895</v>
       </c>
@@ -4028,7 +4046,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="69" spans="1:23">
+    <row r="69" spans="1:21">
       <c r="A69">
         <v>896</v>
       </c>
@@ -4066,7 +4084,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="70" spans="1:23">
+    <row r="70" spans="1:21">
       <c r="A70">
         <v>897</v>
       </c>
@@ -4105,7 +4123,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="71" spans="1:23">
+    <row r="71" spans="1:21">
       <c r="A71">
         <v>898</v>
       </c>
@@ -4143,7 +4161,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="72" spans="1:23">
+    <row r="72" spans="1:21">
       <c r="A72">
         <v>899</v>
       </c>
@@ -4181,7 +4199,7 @@
       <c r="S72" s="2"/>
       <c r="T72" s="5"/>
     </row>
-    <row r="73" spans="1:23">
+    <row r="73" spans="1:21">
       <c r="A73">
         <v>900</v>
       </c>
@@ -4219,7 +4237,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="74" spans="1:23">
+    <row r="74" spans="1:21">
       <c r="A74">
         <v>901</v>
       </c>
@@ -4257,7 +4275,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="75" spans="1:23">
+    <row r="75" spans="1:21">
       <c r="A75">
         <v>902</v>
       </c>
@@ -4295,7 +4313,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="76" spans="1:23">
+    <row r="76" spans="1:21">
       <c r="A76">
         <v>903</v>
       </c>
@@ -4333,7 +4351,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="77" spans="1:23">
+    <row r="77" spans="1:21">
       <c r="A77">
         <v>904</v>
       </c>
@@ -4371,7 +4389,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="78" spans="1:23">
+    <row r="78" spans="1:21">
       <c r="A78">
         <v>905</v>
       </c>
@@ -4413,8 +4431,8 @@
       </c>
       <c r="T78" s="5"/>
     </row>
-    <row r="79" spans="1:23">
-      <c r="A79" s="6">
+    <row r="79" spans="1:21">
+      <c r="A79">
         <v>906</v>
       </c>
       <c r="B79" s="1">
@@ -4429,7 +4447,7 @@
       <c r="E79" s="2" t="s">
         <v>225</v>
       </c>
-      <c r="F79" s="6">
+      <c r="F79">
         <v>43152</v>
       </c>
       <c r="G79" s="2" t="s">
@@ -4450,12 +4468,9 @@
       <c r="T79" s="5" t="s">
         <v>226</v>
       </c>
-      <c r="U79" s="6"/>
-      <c r="V79" s="6"/>
-      <c r="W79" s="6"/>
-    </row>
-    <row r="80" spans="1:23">
-      <c r="A80" s="6">
+    </row>
+    <row r="80" spans="1:21">
+      <c r="A80">
         <v>907</v>
       </c>
       <c r="B80" s="1">
@@ -4470,7 +4485,7 @@
       <c r="E80" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="F80" s="6">
+      <c r="F80">
         <v>38460</v>
       </c>
       <c r="G80" s="2" t="s">
@@ -4491,12 +4506,9 @@
       <c r="T80" s="5" t="s">
         <v>229</v>
       </c>
-      <c r="U80" s="6"/>
-      <c r="V80" s="6"/>
-      <c r="W80" s="6"/>
     </row>
     <row r="81" spans="1:23">
-      <c r="A81" s="6">
+      <c r="A81">
         <v>908</v>
       </c>
       <c r="B81" s="1">
@@ -4511,7 +4523,7 @@
       <c r="E81" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="F81" s="6">
+      <c r="F81">
         <v>38930</v>
       </c>
       <c r="G81" s="2" t="s">
@@ -4532,9 +4544,88 @@
       <c r="T81" s="5" t="s">
         <v>232</v>
       </c>
-      <c r="U81" s="6"/>
-      <c r="V81" s="6"/>
-      <c r="W81" s="6"/>
+    </row>
+    <row r="82" spans="1:23">
+      <c r="A82" s="6">
+        <v>909</v>
+      </c>
+      <c r="B82" s="1">
+        <v>46286.250625000001</v>
+      </c>
+      <c r="C82" s="1">
+        <v>46286.252256944397</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E82" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F82" s="6">
+        <v>38845</v>
+      </c>
+      <c r="G82" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="J82" s="2"/>
+      <c r="K82" s="2"/>
+      <c r="L82" s="2"/>
+      <c r="M82" s="2"/>
+      <c r="N82" s="2"/>
+      <c r="O82" s="2"/>
+      <c r="P82" s="2"/>
+      <c r="Q82" s="4"/>
+      <c r="R82" s="4"/>
+      <c r="S82" s="2"/>
+      <c r="T82" s="5" t="s">
+        <v>235</v>
+      </c>
+      <c r="U82" s="6"/>
+      <c r="V82" s="6"/>
+      <c r="W82" s="6"/>
+    </row>
+    <row r="83" spans="1:23">
+      <c r="A83" s="6">
+        <v>910</v>
+      </c>
+      <c r="B83" s="1">
+        <v>46286.264837962997</v>
+      </c>
+      <c r="C83" s="1">
+        <v>46286.265972222202</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E83" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F83" s="6">
+        <v>38374</v>
+      </c>
+      <c r="G83" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="J83" s="2"/>
+      <c r="K83" s="2"/>
+      <c r="L83" s="2"/>
+      <c r="M83" s="2"/>
+      <c r="N83" s="2"/>
+      <c r="O83" s="2"/>
+      <c r="P83" s="2"/>
+      <c r="Q83" s="4"/>
+      <c r="R83" s="4"/>
+      <c r="S83" s="2"/>
+      <c r="T83" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="U83" s="6"/>
+      <c r="V83" s="6"/>
+      <c r="W83" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{DA95BF3E-D697-4423-91F7-02AA4A5E5863}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{64313F7A-AB1D-41FB-98F3-E906499D6391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="242">
   <si>
     <t>Id</t>
   </si>
@@ -756,6 +756,15 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/174D2FF3-C520-40E0-881E-A5648C6DC477_Starbucks%20Valle%20Dora.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG_4338_Starbucks%20CEMTRAM%204.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/FD2A41AF-E2BB-42C7-9634-0B964A106189_Starbucks%20Gustavo%20Ba.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/DCE3998D-8289-4330-B730-ED55D6A2A656_Starbucks%20Gustavo%20Ba.jpeg</t>
   </si>
 </sst>
 </file>
@@ -893,8 +902,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W83" totalsRowShown="0">
-  <autoFilter ref="A1:W83" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W86" totalsRowShown="0">
+  <autoFilter ref="A1:W86" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -1061,7 +1070,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="910" latestEventMarker="1301">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="913" latestEventMarker="1304">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1388,7 +1397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W83"/>
+  <dimension ref="A1:W86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -4546,7 +4555,7 @@
       </c>
     </row>
     <row r="82" spans="1:23">
-      <c r="A82" s="6">
+      <c r="A82">
         <v>909</v>
       </c>
       <c r="B82" s="1">
@@ -4561,7 +4570,7 @@
       <c r="E82" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="F82" s="6">
+      <c r="F82">
         <v>38845</v>
       </c>
       <c r="G82" s="2" t="s">
@@ -4582,12 +4591,9 @@
       <c r="T82" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="U82" s="6"/>
-      <c r="V82" s="6"/>
-      <c r="W82" s="6"/>
     </row>
     <row r="83" spans="1:23">
-      <c r="A83" s="6">
+      <c r="A83">
         <v>910</v>
       </c>
       <c r="B83" s="1">
@@ -4602,7 +4608,7 @@
       <c r="E83" s="2" t="s">
         <v>237</v>
       </c>
-      <c r="F83" s="6">
+      <c r="F83">
         <v>38374</v>
       </c>
       <c r="G83" s="2" t="s">
@@ -4623,9 +4629,130 @@
       <c r="T83" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="U83" s="6"/>
-      <c r="V83" s="6"/>
-      <c r="W83" s="6"/>
+    </row>
+    <row r="84" spans="1:23">
+      <c r="A84">
+        <v>911</v>
+      </c>
+      <c r="B84" s="1">
+        <v>46286.315277777801</v>
+      </c>
+      <c r="C84" s="1">
+        <v>46286.317291666703</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E84" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F84">
+        <v>38695</v>
+      </c>
+      <c r="G84" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="J84" s="2"/>
+      <c r="K84" s="2"/>
+      <c r="L84" s="2"/>
+      <c r="M84" s="2"/>
+      <c r="N84" s="2"/>
+      <c r="O84" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="P84" s="2"/>
+      <c r="Q84" s="4"/>
+      <c r="R84" s="4"/>
+      <c r="S84" s="2"/>
+      <c r="T84" s="5"/>
+    </row>
+    <row r="85" spans="1:23">
+      <c r="A85" s="6">
+        <v>912</v>
+      </c>
+      <c r="B85" s="1">
+        <v>46286.342835648102</v>
+      </c>
+      <c r="C85" s="1">
+        <v>46286.3452777778</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E85" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F85" s="6">
+        <v>38770</v>
+      </c>
+      <c r="G85" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="J85" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K85" s="2"/>
+      <c r="L85" s="2"/>
+      <c r="M85" s="2"/>
+      <c r="N85" s="2"/>
+      <c r="O85" s="2"/>
+      <c r="P85" s="2"/>
+      <c r="Q85" s="4"/>
+      <c r="R85" s="4"/>
+      <c r="S85" s="2"/>
+      <c r="T85" s="5"/>
+      <c r="U85" s="6"/>
+      <c r="V85" s="6"/>
+      <c r="W85" s="6"/>
+    </row>
+    <row r="86" spans="1:23">
+      <c r="A86" s="6">
+        <v>913</v>
+      </c>
+      <c r="B86" s="1">
+        <v>46286.345578703702</v>
+      </c>
+      <c r="C86" s="1">
+        <v>46286.349328703698</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E86" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F86" s="6">
+        <v>38770</v>
+      </c>
+      <c r="G86" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="J86" s="2"/>
+      <c r="K86" s="2"/>
+      <c r="L86" s="2"/>
+      <c r="M86" s="2"/>
+      <c r="N86" s="2"/>
+      <c r="O86" s="2"/>
+      <c r="P86" s="2"/>
+      <c r="Q86" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R86" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S86" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="T86" s="5"/>
+      <c r="U86" s="6"/>
+      <c r="V86" s="6"/>
+      <c r="W86" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{64313F7A-AB1D-41FB-98F3-E906499D6391}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C5E6579-2465-422F-A104-F6F2E4A9D79C}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="379" uniqueCount="242">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="310">
   <si>
     <t>Id</t>
   </si>
@@ -765,6 +765,210 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/DCE3998D-8289-4330-B730-ED55D6A2A656_Starbucks%20Gustavo%20Ba.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG_4348_Starbucks%20CEMTRAM%204.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/94EC3CDE-6080-497D-BB28-B591958924E2_Thelma%20Edith%20Melende%201.png</t>
+  </si>
+  <si>
+    <t>sbmx38800@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Antenas PA</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/20260921_104836_Starbucks%20Antenas%20PA.jpg</t>
+  </si>
+  <si>
+    <t>sbmx43169@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Tepozán</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/collage_layouts_plaza_tepozan_Starbucks%20Plaza%20Tepo.png</t>
+  </si>
+  <si>
+    <t>sbmx38502@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San Marcos DT</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/Captura%20de%20pantalla%202026-09-21%20a%20la(s)%2011.15._Starbucks%20San%20Marcos.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38594@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Carretera México-Puebla</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17900109651253392560454380281814_Starbucks%20Carretera.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/Captura%20de%20pantalla%202026-09-21%20a%20la(s)%2011.20._Starbucks%20San%20Marcos.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/B4897F50-5909-4313-BD11-178E45F6AC3A_Starbucks%20San%20Marcos.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38859@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Satelite II (N1)</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG-20260920-WA0040_Starbucks%20Plaza%20Sate.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/E9257EBB-FA15-415F-9F3A-3FC16EDC4B54_Starbucks%20Rojo%20Gomez.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Rojo%20Gomez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20San%20Marcos.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Starbucks%20Rojo%20Gomez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Rojo%20Gomez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Starbucks%20Rojo%20Gomez.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38657@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Patio Lomas Estrella</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/351B82AB-4432-4A0C-9B85-CBE8626904A3_Starbucks%20Patio%20Loma.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38855@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Zapotitlan</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17900131498944984186324606561468_Starbucks%20Plaza%20Zapo.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38659@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Sendero Ixtapaluca</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Sendero%20Ix.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/D0AD8D6D-E8DB-4E35-A8CD-9AC7F4B4B7B9_Starbucks%20Rojo%20Gomez.png</t>
+  </si>
+  <si>
+    <t>SBMX38569@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Universidad</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/original-9D7A689F-54DB-4850-8128-166B68319E01_Starbucks%20Plaza%20Univ.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/Captura%20de%20pantalla%202026-09-21%20a%20la(s)%2011.15._Starbucks%20San%20Marcos%201.png</t>
+  </si>
+  <si>
+    <t>marlene.hernandez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Marlene Danaee Hernandez Carmona</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_6137_Marlene%20Danaee%20Herna.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/CF254CCF-8242-439B-84F7-FFC47B9E3007_Starbucks%20Rojo%20Gomez.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20San%20Marcos%201.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/Captura%20de%20pantalla%202026-09-21%20a%20la(s)%2011.20._Starbucks%20San%20Marcos%201.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_6137_Marlene%20Danaee%20Herna%201.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/B4897F50-5909-4313-BD11-178E45F6AC3A_Starbucks%20San%20Marcos%201.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/9EE421A5-169A-465F-A4FA-84F88821DCD5_Starbucks%20San%20Marcos.jpeg</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Rojo%20Gomez.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20San%20Marcos%201.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Lucy_24Sep/image_Starbucks%20Rojo%20Gomez.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38447@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Hospital Angeles del Pedregal</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/1D53C3AD-FFEA-4D04-84B1-A2F5DCE9849D-COLLAGE_Starbucks%20Hospital%20A.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38567@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Aragón II</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Arag%C3%B3n%20II.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/85a00fe0-7cf9-445c-a250-3d68aacc3729_Starbucks%20Rojo%20Gomez.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/image_Starbucks%20Rojo%20Gomez.jpg</t>
+  </si>
+  <si>
+    <t>sbmx43026@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Ermita</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Plaza%20Ermi.jpg</t>
+  </si>
+  <si>
+    <t>irving.pichardo@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Irving Gonzalez Pichardo</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Irving%20Gonzalez%20Pich.jpg</t>
   </si>
 </sst>
 </file>
@@ -902,8 +1106,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W86" totalsRowShown="0">
-  <autoFilter ref="A1:W86" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W124" totalsRowShown="0">
+  <autoFilter ref="A1:W124" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -1070,7 +1274,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="913" latestEventMarker="1304">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="951" latestEventMarker="1342">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1397,7 +1601,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W86"/>
+  <dimension ref="A1:W124"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -4516,7 +4720,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="81" spans="1:23">
+    <row r="81" spans="1:20">
       <c r="A81">
         <v>908</v>
       </c>
@@ -4554,7 +4758,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="82" spans="1:23">
+    <row r="82" spans="1:20">
       <c r="A82">
         <v>909</v>
       </c>
@@ -4592,7 +4796,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="83" spans="1:23">
+    <row r="83" spans="1:20">
       <c r="A83">
         <v>910</v>
       </c>
@@ -4630,7 +4834,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="84" spans="1:23">
+    <row r="84" spans="1:20">
       <c r="A84">
         <v>911</v>
       </c>
@@ -4668,8 +4872,8 @@
       <c r="S84" s="2"/>
       <c r="T84" s="5"/>
     </row>
-    <row r="85" spans="1:23">
-      <c r="A85" s="6">
+    <row r="85" spans="1:20">
+      <c r="A85">
         <v>912</v>
       </c>
       <c r="B85" s="1">
@@ -4684,7 +4888,7 @@
       <c r="E85" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F85" s="6">
+      <c r="F85">
         <v>38770</v>
       </c>
       <c r="G85" s="2" t="s">
@@ -4705,12 +4909,9 @@
       <c r="R85" s="4"/>
       <c r="S85" s="2"/>
       <c r="T85" s="5"/>
-      <c r="U85" s="6"/>
-      <c r="V85" s="6"/>
-      <c r="W85" s="6"/>
-    </row>
-    <row r="86" spans="1:23">
-      <c r="A86" s="6">
+    </row>
+    <row r="86" spans="1:20">
+      <c r="A86">
         <v>913</v>
       </c>
       <c r="B86" s="1">
@@ -4725,7 +4926,7 @@
       <c r="E86" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="F86" s="6">
+      <c r="F86">
         <v>38770</v>
       </c>
       <c r="G86" s="2" t="s">
@@ -4750,9 +4951,1556 @@
         <v>241</v>
       </c>
       <c r="T86" s="5"/>
-      <c r="U86" s="6"/>
-      <c r="V86" s="6"/>
-      <c r="W86" s="6"/>
+    </row>
+    <row r="87" spans="1:20">
+      <c r="A87">
+        <v>914</v>
+      </c>
+      <c r="B87" s="1">
+        <v>46286.439895833297</v>
+      </c>
+      <c r="C87" s="1">
+        <v>46286.440069444398</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E87" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="F87">
+        <v>38695</v>
+      </c>
+      <c r="G87" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="J87" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K87" s="2"/>
+      <c r="L87" s="2"/>
+      <c r="M87" s="2"/>
+      <c r="N87" s="2"/>
+      <c r="O87" s="2"/>
+      <c r="P87" s="2"/>
+      <c r="Q87" s="4"/>
+      <c r="R87" s="4"/>
+      <c r="S87" s="2"/>
+      <c r="T87" s="5"/>
+    </row>
+    <row r="88" spans="1:20">
+      <c r="A88">
+        <v>915</v>
+      </c>
+      <c r="B88" s="1">
+        <v>46286.4461226852</v>
+      </c>
+      <c r="C88" s="1">
+        <v>46286.446469907401</v>
+      </c>
+      <c r="D88" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E88" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F88">
+        <v>38351</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="J88" s="2"/>
+      <c r="K88" s="2"/>
+      <c r="L88" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="M88" s="2"/>
+      <c r="N88" s="2"/>
+      <c r="O88" s="2"/>
+      <c r="P88" s="2"/>
+      <c r="Q88" s="4"/>
+      <c r="R88" s="4"/>
+      <c r="S88" s="2"/>
+      <c r="T88" s="5"/>
+    </row>
+    <row r="89" spans="1:20">
+      <c r="A89">
+        <v>916</v>
+      </c>
+      <c r="B89" s="1">
+        <v>46286.449942129599</v>
+      </c>
+      <c r="C89" s="1">
+        <v>46286.450671296298</v>
+      </c>
+      <c r="D89" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E89" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="F89">
+        <v>38800</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="J89" s="2"/>
+      <c r="K89" s="2"/>
+      <c r="L89" s="2"/>
+      <c r="M89" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N89" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="O89" s="2"/>
+      <c r="P89" s="2"/>
+      <c r="Q89" s="4"/>
+      <c r="R89" s="4"/>
+      <c r="S89" s="2"/>
+      <c r="T89" s="5"/>
+    </row>
+    <row r="90" spans="1:20">
+      <c r="A90">
+        <v>917</v>
+      </c>
+      <c r="B90" s="1">
+        <v>46286.457835648202</v>
+      </c>
+      <c r="C90" s="1">
+        <v>46286.460810185199</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E90" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F90">
+        <v>43169</v>
+      </c>
+      <c r="G90" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="J90" s="2"/>
+      <c r="K90" s="2"/>
+      <c r="L90" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="M90" s="2"/>
+      <c r="N90" s="2"/>
+      <c r="O90" s="2"/>
+      <c r="P90" s="2"/>
+      <c r="Q90" s="4"/>
+      <c r="R90" s="4"/>
+      <c r="S90" s="2"/>
+      <c r="T90" s="5"/>
+    </row>
+    <row r="91" spans="1:20">
+      <c r="A91">
+        <v>918</v>
+      </c>
+      <c r="B91" s="1">
+        <v>46286.4628240741</v>
+      </c>
+      <c r="C91" s="1">
+        <v>46286.469953703701</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E91" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F91">
+        <v>38502</v>
+      </c>
+      <c r="G91" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="J91" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="K91" s="2"/>
+      <c r="L91" s="2"/>
+      <c r="M91" s="2"/>
+      <c r="N91" s="2"/>
+      <c r="O91" s="2"/>
+      <c r="P91" s="2"/>
+      <c r="Q91" s="4"/>
+      <c r="R91" s="4"/>
+      <c r="S91" s="2"/>
+      <c r="T91" s="5"/>
+    </row>
+    <row r="92" spans="1:20">
+      <c r="A92">
+        <v>919</v>
+      </c>
+      <c r="B92" s="1">
+        <v>46286.470115740703</v>
+      </c>
+      <c r="C92" s="1">
+        <v>46286.4706365741</v>
+      </c>
+      <c r="D92" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E92" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F92">
+        <v>38502</v>
+      </c>
+      <c r="G92" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="J92" s="2"/>
+      <c r="K92" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="L92" s="2"/>
+      <c r="M92" s="2"/>
+      <c r="N92" s="2"/>
+      <c r="O92" s="2"/>
+      <c r="P92" s="2"/>
+      <c r="Q92" s="4"/>
+      <c r="R92" s="4"/>
+      <c r="S92" s="2"/>
+      <c r="T92" s="5"/>
+    </row>
+    <row r="93" spans="1:20">
+      <c r="A93">
+        <v>920</v>
+      </c>
+      <c r="B93" s="1">
+        <v>46286.468009259297</v>
+      </c>
+      <c r="C93" s="1">
+        <v>46286.471527777801</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="E93" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="F93">
+        <v>38594</v>
+      </c>
+      <c r="G93" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="J93" s="2"/>
+      <c r="K93" s="2"/>
+      <c r="L93" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="M93" s="2"/>
+      <c r="N93" s="2"/>
+      <c r="O93" s="2"/>
+      <c r="P93" s="2"/>
+      <c r="Q93" s="4"/>
+      <c r="R93" s="4"/>
+      <c r="S93" s="2"/>
+      <c r="T93" s="5"/>
+    </row>
+    <row r="94" spans="1:20">
+      <c r="A94">
+        <v>921</v>
+      </c>
+      <c r="B94" s="1">
+        <v>46286.471122685201</v>
+      </c>
+      <c r="C94" s="1">
+        <v>46286.472835648201</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E94" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F94">
+        <v>38502</v>
+      </c>
+      <c r="G94" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="J94" s="2"/>
+      <c r="K94" s="2"/>
+      <c r="L94" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="M94" s="2"/>
+      <c r="N94" s="2"/>
+      <c r="O94" s="2"/>
+      <c r="P94" s="2"/>
+      <c r="Q94" s="4"/>
+      <c r="R94" s="4"/>
+      <c r="S94" s="2"/>
+      <c r="T94" s="5"/>
+    </row>
+    <row r="95" spans="1:20">
+      <c r="A95">
+        <v>922</v>
+      </c>
+      <c r="B95" s="1">
+        <v>46286.473715277803</v>
+      </c>
+      <c r="C95" s="1">
+        <v>46286.476759259298</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E95" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F95">
+        <v>38502</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="J95" s="2"/>
+      <c r="K95" s="2"/>
+      <c r="L95" s="2"/>
+      <c r="M95" s="2"/>
+      <c r="N95" s="2"/>
+      <c r="O95" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="P95" s="2"/>
+      <c r="Q95" s="4"/>
+      <c r="R95" s="4"/>
+      <c r="S95" s="2"/>
+      <c r="T95" s="5"/>
+    </row>
+    <row r="96" spans="1:20">
+      <c r="A96">
+        <v>923</v>
+      </c>
+      <c r="B96" s="1">
+        <v>46286.476898148103</v>
+      </c>
+      <c r="C96" s="1">
+        <v>46286.478599536997</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E96" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F96">
+        <v>38502</v>
+      </c>
+      <c r="G96" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="J96" s="2"/>
+      <c r="K96" s="2"/>
+      <c r="L96" s="2"/>
+      <c r="M96" s="2"/>
+      <c r="N96" s="2"/>
+      <c r="O96" s="2"/>
+      <c r="P96" s="2"/>
+      <c r="Q96" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R96" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S96" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="T96" s="5"/>
+    </row>
+    <row r="97" spans="1:23">
+      <c r="A97" s="6">
+        <v>924</v>
+      </c>
+      <c r="B97" s="1">
+        <v>46286.482465277797</v>
+      </c>
+      <c r="C97" s="1">
+        <v>46286.484652777799</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E97" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F97" s="6">
+        <v>38859</v>
+      </c>
+      <c r="G97" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="J97" s="2"/>
+      <c r="K97" s="2"/>
+      <c r="L97" s="2"/>
+      <c r="M97" s="2"/>
+      <c r="N97" s="2"/>
+      <c r="O97" s="2"/>
+      <c r="P97" s="2"/>
+      <c r="Q97" s="4"/>
+      <c r="R97" s="4"/>
+      <c r="S97" s="2"/>
+      <c r="T97" s="5" t="s">
+        <v>262</v>
+      </c>
+      <c r="U97" s="6"/>
+      <c r="V97" s="6"/>
+      <c r="W97" s="6"/>
+    </row>
+    <row r="98" spans="1:23">
+      <c r="A98" s="6">
+        <v>925</v>
+      </c>
+      <c r="B98" s="1">
+        <v>46286.485300925902</v>
+      </c>
+      <c r="C98" s="1">
+        <v>46286.488240740699</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E98" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F98" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G98" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="J98" s="2"/>
+      <c r="K98" s="2"/>
+      <c r="L98" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="M98" s="2"/>
+      <c r="N98" s="2"/>
+      <c r="O98" s="2"/>
+      <c r="P98" s="2"/>
+      <c r="Q98" s="4"/>
+      <c r="R98" s="4"/>
+      <c r="S98" s="2"/>
+      <c r="T98" s="5"/>
+      <c r="U98" s="6"/>
+      <c r="V98" s="6"/>
+      <c r="W98" s="6"/>
+    </row>
+    <row r="99" spans="1:23">
+      <c r="A99" s="6">
+        <v>926</v>
+      </c>
+      <c r="B99" s="1">
+        <v>46286.488402777803</v>
+      </c>
+      <c r="C99" s="1">
+        <v>46286.489004629599</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E99" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F99" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G99" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H99" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I99" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="J99" s="2"/>
+      <c r="K99" s="2"/>
+      <c r="L99" s="2"/>
+      <c r="M99" s="2"/>
+      <c r="N99" s="2"/>
+      <c r="O99" s="2"/>
+      <c r="P99" s="2"/>
+      <c r="Q99" s="4"/>
+      <c r="R99" s="4"/>
+      <c r="S99" s="2"/>
+      <c r="T99" s="5"/>
+      <c r="U99" s="6"/>
+      <c r="V99" s="6"/>
+      <c r="W99" s="6"/>
+    </row>
+    <row r="100" spans="1:23">
+      <c r="A100" s="6">
+        <v>927</v>
+      </c>
+      <c r="B100" s="1">
+        <v>46286.488599536999</v>
+      </c>
+      <c r="C100" s="1">
+        <v>46286.490428240701</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E100" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F100" s="6">
+        <v>38502</v>
+      </c>
+      <c r="G100" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="J100" s="2"/>
+      <c r="K100" s="2"/>
+      <c r="L100" s="2"/>
+      <c r="M100" s="2"/>
+      <c r="N100" s="2"/>
+      <c r="O100" s="2"/>
+      <c r="P100" s="2"/>
+      <c r="Q100" s="4"/>
+      <c r="R100" s="4"/>
+      <c r="S100" s="2"/>
+      <c r="T100" s="5" t="s">
+        <v>265</v>
+      </c>
+      <c r="U100" s="6"/>
+      <c r="V100" s="6"/>
+      <c r="W100" s="6"/>
+    </row>
+    <row r="101" spans="1:23">
+      <c r="A101" s="6">
+        <v>928</v>
+      </c>
+      <c r="B101" s="1">
+        <v>46286.4908796296</v>
+      </c>
+      <c r="C101" s="1">
+        <v>46286.491307870398</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F101" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2"/>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="4"/>
+      <c r="R101" s="4"/>
+      <c r="S101" s="2"/>
+      <c r="T101" s="5"/>
+      <c r="U101" s="6"/>
+      <c r="V101" s="6"/>
+      <c r="W101" s="6"/>
+    </row>
+    <row r="102" spans="1:23">
+      <c r="A102" s="6">
+        <v>929</v>
+      </c>
+      <c r="B102" s="1">
+        <v>46286.491527777798</v>
+      </c>
+      <c r="C102" s="1">
+        <v>46286.4919212963</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E102" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F102" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="J102" s="2"/>
+      <c r="K102" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="L102" s="2"/>
+      <c r="M102" s="2"/>
+      <c r="N102" s="2"/>
+      <c r="O102" s="2"/>
+      <c r="P102" s="2"/>
+      <c r="Q102" s="4"/>
+      <c r="R102" s="4"/>
+      <c r="S102" s="2"/>
+      <c r="T102" s="5"/>
+      <c r="U102" s="6"/>
+      <c r="V102" s="6"/>
+      <c r="W102" s="6"/>
+    </row>
+    <row r="103" spans="1:23">
+      <c r="A103" s="6">
+        <v>930</v>
+      </c>
+      <c r="B103" s="1">
+        <v>46286.4922337963</v>
+      </c>
+      <c r="C103" s="1">
+        <v>46286.492511574099</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E103" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F103" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="J103" s="2"/>
+      <c r="K103" s="2"/>
+      <c r="L103" s="2"/>
+      <c r="M103" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="N103" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="O103" s="2"/>
+      <c r="P103" s="2"/>
+      <c r="Q103" s="4"/>
+      <c r="R103" s="4"/>
+      <c r="S103" s="2"/>
+      <c r="T103" s="5"/>
+      <c r="U103" s="6"/>
+      <c r="V103" s="6"/>
+      <c r="W103" s="6"/>
+    </row>
+    <row r="104" spans="1:23">
+      <c r="A104" s="6">
+        <v>931</v>
+      </c>
+      <c r="B104" s="1">
+        <v>46286.487812500003</v>
+      </c>
+      <c r="C104" s="1">
+        <v>46286.493483796301</v>
+      </c>
+      <c r="D104" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="E104" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="F104" s="6">
+        <v>38657</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="J104" s="2"/>
+      <c r="K104" s="2"/>
+      <c r="L104" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="M104" s="2"/>
+      <c r="N104" s="2"/>
+      <c r="O104" s="2"/>
+      <c r="P104" s="2"/>
+      <c r="Q104" s="4"/>
+      <c r="R104" s="4"/>
+      <c r="S104" s="2"/>
+      <c r="T104" s="5"/>
+      <c r="U104" s="6"/>
+      <c r="V104" s="6"/>
+      <c r="W104" s="6"/>
+    </row>
+    <row r="105" spans="1:23">
+      <c r="A105" s="6">
+        <v>932</v>
+      </c>
+      <c r="B105" s="1">
+        <v>46286.494513888902</v>
+      </c>
+      <c r="C105" s="1">
+        <v>46286.495289351798</v>
+      </c>
+      <c r="D105" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E105" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F105" s="6">
+        <v>38855</v>
+      </c>
+      <c r="G105" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="J105" s="2"/>
+      <c r="K105" s="2"/>
+      <c r="L105" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="M105" s="2"/>
+      <c r="N105" s="2"/>
+      <c r="O105" s="2"/>
+      <c r="P105" s="2"/>
+      <c r="Q105" s="4"/>
+      <c r="R105" s="4"/>
+      <c r="S105" s="2"/>
+      <c r="T105" s="5"/>
+      <c r="U105" s="6"/>
+      <c r="V105" s="6"/>
+      <c r="W105" s="6"/>
+    </row>
+    <row r="106" spans="1:23">
+      <c r="A106" s="6">
+        <v>933</v>
+      </c>
+      <c r="B106" s="1">
+        <v>46286.495729166701</v>
+      </c>
+      <c r="C106" s="1">
+        <v>46286.497175925899</v>
+      </c>
+      <c r="D106" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E106" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F106" s="6">
+        <v>38659</v>
+      </c>
+      <c r="G106" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H106" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I106" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="J106" s="2"/>
+      <c r="K106" s="2"/>
+      <c r="L106" s="2"/>
+      <c r="M106" s="2"/>
+      <c r="N106" s="2"/>
+      <c r="O106" s="2"/>
+      <c r="P106" s="2"/>
+      <c r="Q106" s="4"/>
+      <c r="R106" s="4"/>
+      <c r="S106" s="2"/>
+      <c r="T106" s="5"/>
+      <c r="U106" s="6"/>
+      <c r="V106" s="6"/>
+      <c r="W106" s="6"/>
+    </row>
+    <row r="107" spans="1:23">
+      <c r="A107" s="6">
+        <v>934</v>
+      </c>
+      <c r="B107" s="1">
+        <v>46286.4929513889</v>
+      </c>
+      <c r="C107" s="1">
+        <v>46286.497870370396</v>
+      </c>
+      <c r="D107" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E107" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F107" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G107" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="J107" s="2"/>
+      <c r="K107" s="2"/>
+      <c r="L107" s="2"/>
+      <c r="M107" s="2"/>
+      <c r="N107" s="2"/>
+      <c r="O107" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="P107" s="2"/>
+      <c r="Q107" s="4"/>
+      <c r="R107" s="4"/>
+      <c r="S107" s="2"/>
+      <c r="T107" s="5"/>
+      <c r="U107" s="6"/>
+      <c r="V107" s="6"/>
+      <c r="W107" s="6"/>
+    </row>
+    <row r="108" spans="1:23">
+      <c r="A108" s="6">
+        <v>935</v>
+      </c>
+      <c r="B108" s="1">
+        <v>46286.494375000002</v>
+      </c>
+      <c r="C108" s="1">
+        <v>46286.498495370397</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="F108" s="6">
+        <v>38569</v>
+      </c>
+      <c r="G108" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="J108" s="2"/>
+      <c r="K108" s="2"/>
+      <c r="L108" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="M108" s="2"/>
+      <c r="N108" s="2"/>
+      <c r="O108" s="2"/>
+      <c r="P108" s="2"/>
+      <c r="Q108" s="4"/>
+      <c r="R108" s="4"/>
+      <c r="S108" s="2"/>
+      <c r="T108" s="5"/>
+      <c r="U108" s="6"/>
+      <c r="V108" s="6"/>
+      <c r="W108" s="6"/>
+    </row>
+    <row r="109" spans="1:23">
+      <c r="A109" s="6">
+        <v>936</v>
+      </c>
+      <c r="B109" s="1">
+        <v>46286.503425925897</v>
+      </c>
+      <c r="C109" s="1">
+        <v>46286.503865740699</v>
+      </c>
+      <c r="D109" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E109" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F109" s="6">
+        <v>38502</v>
+      </c>
+      <c r="G109" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="J109" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="K109" s="2"/>
+      <c r="L109" s="2"/>
+      <c r="M109" s="2"/>
+      <c r="N109" s="2"/>
+      <c r="O109" s="2"/>
+      <c r="P109" s="2"/>
+      <c r="Q109" s="4"/>
+      <c r="R109" s="4"/>
+      <c r="S109" s="2"/>
+      <c r="T109" s="5"/>
+      <c r="U109" s="6"/>
+      <c r="V109" s="6"/>
+      <c r="W109" s="6"/>
+    </row>
+    <row r="110" spans="1:23">
+      <c r="A110" s="6">
+        <v>937</v>
+      </c>
+      <c r="B110" s="1">
+        <v>46286.503703703696</v>
+      </c>
+      <c r="C110" s="1">
+        <v>46286.505370370403</v>
+      </c>
+      <c r="D110" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E110" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F110" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G110" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="J110" s="2"/>
+      <c r="K110" s="2"/>
+      <c r="L110" s="2"/>
+      <c r="M110" s="2"/>
+      <c r="N110" s="2"/>
+      <c r="O110" s="2"/>
+      <c r="P110" s="2"/>
+      <c r="Q110" s="4"/>
+      <c r="R110" s="4"/>
+      <c r="S110" s="2"/>
+      <c r="T110" s="5" t="s">
+        <v>285</v>
+      </c>
+      <c r="U110" s="6"/>
+      <c r="V110" s="6"/>
+      <c r="W110" s="6"/>
+    </row>
+    <row r="111" spans="1:23">
+      <c r="A111" s="6">
+        <v>938</v>
+      </c>
+      <c r="B111" s="1">
+        <v>46286.501562500001</v>
+      </c>
+      <c r="C111" s="1">
+        <v>46286.505509259303</v>
+      </c>
+      <c r="D111" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E111" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F111" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H111" s="2"/>
+      <c r="I111" s="2"/>
+      <c r="J111" s="2"/>
+      <c r="K111" s="2"/>
+      <c r="L111" s="2"/>
+      <c r="M111" s="2"/>
+      <c r="N111" s="2"/>
+      <c r="O111" s="2"/>
+      <c r="P111" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="Q111" s="4"/>
+      <c r="R111" s="4"/>
+      <c r="S111" s="2"/>
+      <c r="T111" s="5"/>
+      <c r="U111" s="6"/>
+      <c r="V111" s="6"/>
+      <c r="W111" s="6"/>
+    </row>
+    <row r="112" spans="1:23">
+      <c r="A112" s="6">
+        <v>939</v>
+      </c>
+      <c r="B112" s="1">
+        <v>46286.505266203698</v>
+      </c>
+      <c r="C112" s="1">
+        <v>46286.505532407398</v>
+      </c>
+      <c r="D112" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E112" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F112" s="6">
+        <v>38502</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H112" s="2"/>
+      <c r="I112" s="2"/>
+      <c r="J112" s="2"/>
+      <c r="K112" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="L112" s="2"/>
+      <c r="M112" s="2"/>
+      <c r="N112" s="2"/>
+      <c r="O112" s="2"/>
+      <c r="P112" s="2"/>
+      <c r="Q112" s="4"/>
+      <c r="R112" s="4"/>
+      <c r="S112" s="2"/>
+      <c r="T112" s="5"/>
+      <c r="U112" s="6"/>
+      <c r="V112" s="6"/>
+      <c r="W112" s="6"/>
+    </row>
+    <row r="113" spans="1:23">
+      <c r="A113" s="6">
+        <v>940</v>
+      </c>
+      <c r="B113" s="1">
+        <v>46286.505682870396</v>
+      </c>
+      <c r="C113" s="1">
+        <v>46286.5059259259</v>
+      </c>
+      <c r="D113" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E113" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F113" s="6">
+        <v>38502</v>
+      </c>
+      <c r="G113" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H113" s="2"/>
+      <c r="I113" s="2"/>
+      <c r="J113" s="2"/>
+      <c r="K113" s="2"/>
+      <c r="L113" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="M113" s="2"/>
+      <c r="N113" s="2"/>
+      <c r="O113" s="2"/>
+      <c r="P113" s="2"/>
+      <c r="Q113" s="4"/>
+      <c r="R113" s="4"/>
+      <c r="S113" s="2"/>
+      <c r="T113" s="5"/>
+      <c r="U113" s="6"/>
+      <c r="V113" s="6"/>
+      <c r="W113" s="6"/>
+    </row>
+    <row r="114" spans="1:23">
+      <c r="A114" s="6">
+        <v>941</v>
+      </c>
+      <c r="B114" s="1">
+        <v>46286.505636574097</v>
+      </c>
+      <c r="C114" s="1">
+        <v>46286.5062384259</v>
+      </c>
+      <c r="D114" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E114" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F114" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G114" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H114" s="2"/>
+      <c r="I114" s="2"/>
+      <c r="J114" s="2"/>
+      <c r="K114" s="2"/>
+      <c r="L114" s="2"/>
+      <c r="M114" s="2"/>
+      <c r="N114" s="2"/>
+      <c r="O114" s="2"/>
+      <c r="P114" s="2"/>
+      <c r="Q114" s="4"/>
+      <c r="R114" s="4"/>
+      <c r="S114" s="2"/>
+      <c r="T114" s="5" t="s">
+        <v>289</v>
+      </c>
+      <c r="U114" s="6"/>
+      <c r="V114" s="6"/>
+      <c r="W114" s="6"/>
+    </row>
+    <row r="115" spans="1:23">
+      <c r="A115" s="6">
+        <v>942</v>
+      </c>
+      <c r="B115" s="1">
+        <v>46286.506018518499</v>
+      </c>
+      <c r="C115" s="1">
+        <v>46286.5062847222</v>
+      </c>
+      <c r="D115" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E115" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F115" s="6">
+        <v>38502</v>
+      </c>
+      <c r="G115" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H115" s="2"/>
+      <c r="I115" s="2"/>
+      <c r="J115" s="2"/>
+      <c r="K115" s="2"/>
+      <c r="L115" s="2"/>
+      <c r="M115" s="2"/>
+      <c r="N115" s="2"/>
+      <c r="O115" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="P115" s="2"/>
+      <c r="Q115" s="4"/>
+      <c r="R115" s="4"/>
+      <c r="S115" s="2"/>
+      <c r="T115" s="5"/>
+      <c r="U115" s="6"/>
+      <c r="V115" s="6"/>
+      <c r="W115" s="6"/>
+    </row>
+    <row r="116" spans="1:23">
+      <c r="A116" s="6">
+        <v>943</v>
+      </c>
+      <c r="B116" s="1">
+        <v>46286.506365740701</v>
+      </c>
+      <c r="C116" s="1">
+        <v>46286.508009259298</v>
+      </c>
+      <c r="D116" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E116" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F116" s="6">
+        <v>38502</v>
+      </c>
+      <c r="G116" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="H116" s="2"/>
+      <c r="I116" s="2"/>
+      <c r="J116" s="2"/>
+      <c r="K116" s="2"/>
+      <c r="L116" s="2"/>
+      <c r="M116" s="2"/>
+      <c r="N116" s="2"/>
+      <c r="O116" s="2"/>
+      <c r="P116" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="Q116" s="4"/>
+      <c r="R116" s="4"/>
+      <c r="S116" s="2"/>
+      <c r="T116" s="5"/>
+      <c r="U116" s="6"/>
+      <c r="V116" s="6"/>
+      <c r="W116" s="6"/>
+    </row>
+    <row r="117" spans="1:23">
+      <c r="A117" s="6">
+        <v>944</v>
+      </c>
+      <c r="B117" s="1">
+        <v>46286.506435185198</v>
+      </c>
+      <c r="C117" s="1">
+        <v>46286.508738425902</v>
+      </c>
+      <c r="D117" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E117" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F117" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G117" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H117" s="2"/>
+      <c r="I117" s="2"/>
+      <c r="J117" s="2"/>
+      <c r="K117" s="2"/>
+      <c r="L117" s="2"/>
+      <c r="M117" s="2"/>
+      <c r="N117" s="2"/>
+      <c r="O117" s="2"/>
+      <c r="P117" s="2"/>
+      <c r="Q117" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="R117" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="S117" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="T117" s="5"/>
+      <c r="U117" s="6"/>
+      <c r="V117" s="6"/>
+      <c r="W117" s="6"/>
+    </row>
+    <row r="118" spans="1:23">
+      <c r="A118" s="6">
+        <v>945</v>
+      </c>
+      <c r="B118" s="1">
+        <v>46286.5081712963</v>
+      </c>
+      <c r="C118" s="1">
+        <v>46286.508993055599</v>
+      </c>
+      <c r="D118" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E118" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F118" s="6">
+        <v>38502</v>
+      </c>
+      <c r="G118" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H118" s="2"/>
+      <c r="I118" s="2"/>
+      <c r="J118" s="2"/>
+      <c r="K118" s="2"/>
+      <c r="L118" s="2"/>
+      <c r="M118" s="2"/>
+      <c r="N118" s="2"/>
+      <c r="O118" s="2"/>
+      <c r="P118" s="2"/>
+      <c r="Q118" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R118" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S118" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="T118" s="5"/>
+      <c r="U118" s="6"/>
+      <c r="V118" s="6"/>
+      <c r="W118" s="6"/>
+    </row>
+    <row r="119" spans="1:23">
+      <c r="A119" s="6">
+        <v>946</v>
+      </c>
+      <c r="B119" s="1">
+        <v>46286.509004629603</v>
+      </c>
+      <c r="C119" s="1">
+        <v>46286.510370370401</v>
+      </c>
+      <c r="D119" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E119" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F119" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G119" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="H119" s="2"/>
+      <c r="I119" s="2"/>
+      <c r="J119" s="2"/>
+      <c r="K119" s="2"/>
+      <c r="L119" s="2"/>
+      <c r="M119" s="2"/>
+      <c r="N119" s="2"/>
+      <c r="O119" s="2"/>
+      <c r="P119" s="2"/>
+      <c r="Q119" s="4"/>
+      <c r="R119" s="4"/>
+      <c r="S119" s="2"/>
+      <c r="T119" s="5"/>
+      <c r="U119" s="6" t="s">
+        <v>295</v>
+      </c>
+      <c r="V119" s="6"/>
+      <c r="W119" s="6"/>
+    </row>
+    <row r="120" spans="1:23">
+      <c r="A120" s="6">
+        <v>947</v>
+      </c>
+      <c r="B120" s="1">
+        <v>46286.506446759297</v>
+      </c>
+      <c r="C120" s="1">
+        <v>46286.510763888902</v>
+      </c>
+      <c r="D120" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E120" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F120" s="6">
+        <v>38447</v>
+      </c>
+      <c r="G120" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H120" s="2"/>
+      <c r="I120" s="2"/>
+      <c r="J120" s="2"/>
+      <c r="K120" s="2"/>
+      <c r="L120" s="2"/>
+      <c r="M120" s="2"/>
+      <c r="N120" s="2"/>
+      <c r="O120" s="2"/>
+      <c r="P120" s="2"/>
+      <c r="Q120" s="4"/>
+      <c r="R120" s="4"/>
+      <c r="S120" s="2"/>
+      <c r="T120" s="5" t="s">
+        <v>298</v>
+      </c>
+      <c r="U120" s="6"/>
+      <c r="V120" s="6"/>
+      <c r="W120" s="6"/>
+    </row>
+    <row r="121" spans="1:23">
+      <c r="A121" s="6">
+        <v>948</v>
+      </c>
+      <c r="B121" s="1">
+        <v>46286.514178240701</v>
+      </c>
+      <c r="C121" s="1">
+        <v>46286.514999999999</v>
+      </c>
+      <c r="D121" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="E121" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F121" s="6">
+        <v>38567</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H121" s="2"/>
+      <c r="I121" s="2"/>
+      <c r="J121" s="2"/>
+      <c r="K121" s="2"/>
+      <c r="L121" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="M121" s="2"/>
+      <c r="N121" s="2"/>
+      <c r="O121" s="2"/>
+      <c r="P121" s="2"/>
+      <c r="Q121" s="4"/>
+      <c r="R121" s="4"/>
+      <c r="S121" s="2"/>
+      <c r="T121" s="5"/>
+      <c r="U121" s="6"/>
+      <c r="V121" s="6"/>
+      <c r="W121" s="6"/>
+    </row>
+    <row r="122" spans="1:23">
+      <c r="A122" s="6">
+        <v>949</v>
+      </c>
+      <c r="B122" s="1">
+        <v>46286.510474536997</v>
+      </c>
+      <c r="C122" s="1">
+        <v>46286.515381944402</v>
+      </c>
+      <c r="D122" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E122" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="F122" s="6">
+        <v>43070</v>
+      </c>
+      <c r="G122" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H122" s="2"/>
+      <c r="I122" s="2"/>
+      <c r="J122" s="2"/>
+      <c r="K122" s="2"/>
+      <c r="L122" s="2"/>
+      <c r="M122" s="2"/>
+      <c r="N122" s="2"/>
+      <c r="O122" s="2"/>
+      <c r="P122" s="2"/>
+      <c r="Q122" s="4"/>
+      <c r="R122" s="4"/>
+      <c r="S122" s="2"/>
+      <c r="T122" s="5"/>
+      <c r="U122" s="6"/>
+      <c r="V122" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="W122" s="6" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="123" spans="1:23">
+      <c r="A123" s="6">
+        <v>950</v>
+      </c>
+      <c r="B123" s="1">
+        <v>46286.508946759299</v>
+      </c>
+      <c r="C123" s="1">
+        <v>46286.516493055598</v>
+      </c>
+      <c r="D123" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E123" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F123" s="6">
+        <v>43026</v>
+      </c>
+      <c r="G123" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H123" s="2"/>
+      <c r="I123" s="2"/>
+      <c r="J123" s="2"/>
+      <c r="K123" s="2"/>
+      <c r="L123" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="M123" s="2"/>
+      <c r="N123" s="2"/>
+      <c r="O123" s="2"/>
+      <c r="P123" s="2"/>
+      <c r="Q123" s="4"/>
+      <c r="R123" s="4"/>
+      <c r="S123" s="2"/>
+      <c r="T123" s="5"/>
+      <c r="U123" s="6"/>
+      <c r="V123" s="6"/>
+      <c r="W123" s="6"/>
+    </row>
+    <row r="124" spans="1:23">
+      <c r="A124" s="6">
+        <v>951</v>
+      </c>
+      <c r="B124" s="1">
+        <v>46286.516319444403</v>
+      </c>
+      <c r="C124" s="1">
+        <v>46286.517048611102</v>
+      </c>
+      <c r="D124" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E124" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F124" s="6">
+        <v>38375</v>
+      </c>
+      <c r="G124" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H124" s="2"/>
+      <c r="I124" s="2"/>
+      <c r="J124" s="2"/>
+      <c r="K124" s="2"/>
+      <c r="L124" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="M124" s="2"/>
+      <c r="N124" s="2"/>
+      <c r="O124" s="2"/>
+      <c r="P124" s="2"/>
+      <c r="Q124" s="4"/>
+      <c r="R124" s="4"/>
+      <c r="S124" s="2"/>
+      <c r="T124" s="5"/>
+      <c r="U124" s="6"/>
+      <c r="V124" s="6"/>
+      <c r="W124" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="130" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5C5E6579-2465-422F-A104-F6F2E4A9D79C}"/>
+  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB07984-5FE0-43F4-BDD1-EAC504ACDFA9}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="310">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="362">
   <si>
     <t>Id</t>
   </si>
@@ -969,6 +969,162 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Irving%20Gonzalez%20Pich.jpg</t>
+  </si>
+  <si>
+    <t>eloisa.rosas@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Eloisa Adriana Rosas Loyola</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/ESPRESSO_Eloisa%20Adriana%20Rosas.jpeg</t>
+  </si>
+  <si>
+    <t>axa.montano@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Axa Yunuen Montaño Martinez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Axa%20Yunuen%20Monta%C3%B1o%20M.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/4c33b8c1-1adb-4d1d-9ef3-90e355452f1b_Johan%20Arellano%20Navar.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38615@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Grand San Jerónimo</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17900154633627772337840385731009_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/fcd2f50b-4f13-43a1-aa77-776026856ad0_Starbucks%20Sendero%20Ix.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/SNOOPY_Eloisa%20Adriana%20Rosas.jpeg</t>
+  </si>
+  <si>
+    <t>rosa.aguilar@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Rosa Patricia Aguilar Contreras</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Rosa%20Patricia%20Aguila.jpg</t>
+  </si>
+  <si>
+    <t>guadalupe.camacho@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Guadalupe Camacho Contreras</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/photocollage_2026921123832243_Guadalupe%20Camacho%20Co.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38107@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Pedregal</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17900160861104206752862281451647_Starbucks%20Pedregal.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38124@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San Jeronimo</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG-20260921-WA0000_Starbucks%20San%20Jeroni.jpg</t>
+  </si>
+  <si>
+    <t>helman.sosa@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Helman Sosa Bernal</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG20260921125114_Helman%20Sosa%20Bernal.jpg</t>
+  </si>
+  <si>
+    <t>jose.ocampo@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Jose Arturo Ocampo Marin</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Jose%20Arturo%20Ocampo%20M.jpg</t>
+  </si>
+  <si>
+    <t>laila.munoz@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Laila America Muñoz Gonzalez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17900170841512694640017362946685_Laila%20America%20Mu%C3%B1oz.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG-20260921-WA0060_Starbucks%20Plaza%20Sate.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38496@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Taxqueña</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/27c349bf-709d-4acb-91f8-1985280a19c5_Starbucks%20Taxque%C3%B1a.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38468@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Portal Churubusco</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/Screenshot_20260921_131656_Drive_Starbucks%20Portal%20Chu.jpg</t>
+  </si>
+  <si>
+    <t>amparo.delgado@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Amparo Delgado Reséndiz</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/1790018487122840761057146394949_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>sbmx43159@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Hospital Angeles Pedregal II</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/7C1B0A15-652B-4566-8D70-B13D8F8C7E3C_Starbucks%20Hospital%20A.jpeg</t>
+  </si>
+  <si>
+    <t>SBMX38116@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Santa Teresa</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/D15444CA-54E6-4CD4-BB23-BF27AB121A9C-COLLAGE_Starbucks%20Santa%20Tere.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38429@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Aragón</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Plaza%20Arag.jpg</t>
   </si>
 </sst>
 </file>
@@ -1106,8 +1262,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W124" totalsRowShown="0">
-  <autoFilter ref="A1:W124" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W144" totalsRowShown="0">
+  <autoFilter ref="A1:W144" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -1274,7 +1430,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="951" latestEventMarker="1342">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="971" latestEventMarker="1362">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1601,7 +1757,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W124"/>
+  <dimension ref="A1:W144"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -5338,8 +5494,8 @@
       </c>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" spans="1:23">
-      <c r="A97" s="6">
+    <row r="97" spans="1:20">
+      <c r="A97">
         <v>924</v>
       </c>
       <c r="B97" s="1">
@@ -5354,7 +5510,7 @@
       <c r="E97" s="2" t="s">
         <v>261</v>
       </c>
-      <c r="F97" s="6">
+      <c r="F97">
         <v>38859</v>
       </c>
       <c r="G97" s="2" t="s">
@@ -5375,12 +5531,9 @@
       <c r="T97" s="5" t="s">
         <v>262</v>
       </c>
-      <c r="U97" s="6"/>
-      <c r="V97" s="6"/>
-      <c r="W97" s="6"/>
-    </row>
-    <row r="98" spans="1:23">
-      <c r="A98" s="6">
+    </row>
+    <row r="98" spans="1:20">
+      <c r="A98">
         <v>925</v>
       </c>
       <c r="B98" s="1">
@@ -5395,7 +5548,7 @@
       <c r="E98" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F98" s="6">
+      <c r="F98">
         <v>43070</v>
       </c>
       <c r="G98" s="2" t="s">
@@ -5416,12 +5569,9 @@
       <c r="R98" s="4"/>
       <c r="S98" s="2"/>
       <c r="T98" s="5"/>
-      <c r="U98" s="6"/>
-      <c r="V98" s="6"/>
-      <c r="W98" s="6"/>
-    </row>
-    <row r="99" spans="1:23">
-      <c r="A99" s="6">
+    </row>
+    <row r="99" spans="1:20">
+      <c r="A99">
         <v>926</v>
       </c>
       <c r="B99" s="1">
@@ -5436,7 +5586,7 @@
       <c r="E99" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F99" s="6">
+      <c r="F99">
         <v>43070</v>
       </c>
       <c r="G99" s="2" t="s">
@@ -5459,12 +5609,9 @@
       <c r="R99" s="4"/>
       <c r="S99" s="2"/>
       <c r="T99" s="5"/>
-      <c r="U99" s="6"/>
-      <c r="V99" s="6"/>
-      <c r="W99" s="6"/>
-    </row>
-    <row r="100" spans="1:23">
-      <c r="A100" s="6">
+    </row>
+    <row r="100" spans="1:20">
+      <c r="A100">
         <v>927</v>
       </c>
       <c r="B100" s="1">
@@ -5479,7 +5626,7 @@
       <c r="E100" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F100" s="6">
+      <c r="F100">
         <v>38502</v>
       </c>
       <c r="G100" s="2" t="s">
@@ -5500,12 +5647,9 @@
       <c r="T100" s="5" t="s">
         <v>265</v>
       </c>
-      <c r="U100" s="6"/>
-      <c r="V100" s="6"/>
-      <c r="W100" s="6"/>
-    </row>
-    <row r="101" spans="1:23">
-      <c r="A101" s="6">
+    </row>
+    <row r="101" spans="1:20">
+      <c r="A101">
         <v>928</v>
       </c>
       <c r="B101" s="1">
@@ -5520,7 +5664,7 @@
       <c r="E101" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F101" s="6">
+      <c r="F101">
         <v>43070</v>
       </c>
       <c r="G101" s="2" t="s">
@@ -5541,12 +5685,9 @@
       <c r="R101" s="4"/>
       <c r="S101" s="2"/>
       <c r="T101" s="5"/>
-      <c r="U101" s="6"/>
-      <c r="V101" s="6"/>
-      <c r="W101" s="6"/>
-    </row>
-    <row r="102" spans="1:23">
-      <c r="A102" s="6">
+    </row>
+    <row r="102" spans="1:20">
+      <c r="A102">
         <v>929</v>
       </c>
       <c r="B102" s="1">
@@ -5561,7 +5702,7 @@
       <c r="E102" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F102" s="6">
+      <c r="F102">
         <v>43070</v>
       </c>
       <c r="G102" s="2" t="s">
@@ -5582,12 +5723,9 @@
       <c r="R102" s="4"/>
       <c r="S102" s="2"/>
       <c r="T102" s="5"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-    </row>
-    <row r="103" spans="1:23">
-      <c r="A103" s="6">
+    </row>
+    <row r="103" spans="1:20">
+      <c r="A103">
         <v>930</v>
       </c>
       <c r="B103" s="1">
@@ -5602,7 +5740,7 @@
       <c r="E103" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F103" s="6">
+      <c r="F103">
         <v>43070</v>
       </c>
       <c r="G103" s="2" t="s">
@@ -5625,12 +5763,9 @@
       <c r="R103" s="4"/>
       <c r="S103" s="2"/>
       <c r="T103" s="5"/>
-      <c r="U103" s="6"/>
-      <c r="V103" s="6"/>
-      <c r="W103" s="6"/>
-    </row>
-    <row r="104" spans="1:23">
-      <c r="A104" s="6">
+    </row>
+    <row r="104" spans="1:20">
+      <c r="A104">
         <v>931</v>
       </c>
       <c r="B104" s="1">
@@ -5645,7 +5780,7 @@
       <c r="E104" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="F104" s="6">
+      <c r="F104">
         <v>38657</v>
       </c>
       <c r="G104" s="2" t="s">
@@ -5666,12 +5801,9 @@
       <c r="R104" s="4"/>
       <c r="S104" s="2"/>
       <c r="T104" s="5"/>
-      <c r="U104" s="6"/>
-      <c r="V104" s="6"/>
-      <c r="W104" s="6"/>
-    </row>
-    <row r="105" spans="1:23">
-      <c r="A105" s="6">
+    </row>
+    <row r="105" spans="1:20">
+      <c r="A105">
         <v>932</v>
       </c>
       <c r="B105" s="1">
@@ -5686,7 +5818,7 @@
       <c r="E105" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="F105" s="6">
+      <c r="F105">
         <v>38855</v>
       </c>
       <c r="G105" s="2" t="s">
@@ -5707,12 +5839,9 @@
       <c r="R105" s="4"/>
       <c r="S105" s="2"/>
       <c r="T105" s="5"/>
-      <c r="U105" s="6"/>
-      <c r="V105" s="6"/>
-      <c r="W105" s="6"/>
-    </row>
-    <row r="106" spans="1:23">
-      <c r="A106" s="6">
+    </row>
+    <row r="106" spans="1:20">
+      <c r="A106">
         <v>933</v>
       </c>
       <c r="B106" s="1">
@@ -5727,7 +5856,7 @@
       <c r="E106" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F106" s="6">
+      <c r="F106">
         <v>38659</v>
       </c>
       <c r="G106" s="2" t="s">
@@ -5750,12 +5879,9 @@
       <c r="R106" s="4"/>
       <c r="S106" s="2"/>
       <c r="T106" s="5"/>
-      <c r="U106" s="6"/>
-      <c r="V106" s="6"/>
-      <c r="W106" s="6"/>
-    </row>
-    <row r="107" spans="1:23">
-      <c r="A107" s="6">
+    </row>
+    <row r="107" spans="1:20">
+      <c r="A107">
         <v>934</v>
       </c>
       <c r="B107" s="1">
@@ -5770,7 +5896,7 @@
       <c r="E107" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F107" s="6">
+      <c r="F107">
         <v>43070</v>
       </c>
       <c r="G107" s="2" t="s">
@@ -5791,12 +5917,9 @@
       <c r="R107" s="4"/>
       <c r="S107" s="2"/>
       <c r="T107" s="5"/>
-      <c r="U107" s="6"/>
-      <c r="V107" s="6"/>
-      <c r="W107" s="6"/>
-    </row>
-    <row r="108" spans="1:23">
-      <c r="A108" s="6">
+    </row>
+    <row r="108" spans="1:20">
+      <c r="A108">
         <v>935</v>
       </c>
       <c r="B108" s="1">
@@ -5811,7 +5934,7 @@
       <c r="E108" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="F108" s="6">
+      <c r="F108">
         <v>38569</v>
       </c>
       <c r="G108" s="2" t="s">
@@ -5832,12 +5955,9 @@
       <c r="R108" s="4"/>
       <c r="S108" s="2"/>
       <c r="T108" s="5"/>
-      <c r="U108" s="6"/>
-      <c r="V108" s="6"/>
-      <c r="W108" s="6"/>
-    </row>
-    <row r="109" spans="1:23">
-      <c r="A109" s="6">
+    </row>
+    <row r="109" spans="1:20">
+      <c r="A109">
         <v>936</v>
       </c>
       <c r="B109" s="1">
@@ -5852,7 +5972,7 @@
       <c r="E109" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F109" s="6">
+      <c r="F109">
         <v>38502</v>
       </c>
       <c r="G109" s="2" t="s">
@@ -5873,12 +5993,9 @@
       <c r="R109" s="4"/>
       <c r="S109" s="2"/>
       <c r="T109" s="5"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-    </row>
-    <row r="110" spans="1:23">
-      <c r="A110" s="6">
+    </row>
+    <row r="110" spans="1:20">
+      <c r="A110">
         <v>937</v>
       </c>
       <c r="B110" s="1">
@@ -5893,7 +6010,7 @@
       <c r="E110" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F110" s="6">
+      <c r="F110">
         <v>38129</v>
       </c>
       <c r="G110" s="2" t="s">
@@ -5914,12 +6031,9 @@
       <c r="T110" s="5" t="s">
         <v>285</v>
       </c>
-      <c r="U110" s="6"/>
-      <c r="V110" s="6"/>
-      <c r="W110" s="6"/>
-    </row>
-    <row r="111" spans="1:23">
-      <c r="A111" s="6">
+    </row>
+    <row r="111" spans="1:20">
+      <c r="A111">
         <v>938</v>
       </c>
       <c r="B111" s="1">
@@ -5934,7 +6048,7 @@
       <c r="E111" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F111" s="6">
+      <c r="F111">
         <v>43070</v>
       </c>
       <c r="G111" s="2" t="s">
@@ -5955,12 +6069,9 @@
       <c r="R111" s="4"/>
       <c r="S111" s="2"/>
       <c r="T111" s="5"/>
-      <c r="U111" s="6"/>
-      <c r="V111" s="6"/>
-      <c r="W111" s="6"/>
-    </row>
-    <row r="112" spans="1:23">
-      <c r="A112" s="6">
+    </row>
+    <row r="112" spans="1:20">
+      <c r="A112">
         <v>939</v>
       </c>
       <c r="B112" s="1">
@@ -5975,7 +6086,7 @@
       <c r="E112" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F112" s="6">
+      <c r="F112">
         <v>38502</v>
       </c>
       <c r="G112" s="2" t="s">
@@ -5996,12 +6107,9 @@
       <c r="R112" s="4"/>
       <c r="S112" s="2"/>
       <c r="T112" s="5"/>
-      <c r="U112" s="6"/>
-      <c r="V112" s="6"/>
-      <c r="W112" s="6"/>
     </row>
     <row r="113" spans="1:23">
-      <c r="A113" s="6">
+      <c r="A113">
         <v>940</v>
       </c>
       <c r="B113" s="1">
@@ -6016,7 +6124,7 @@
       <c r="E113" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F113" s="6">
+      <c r="F113">
         <v>38502</v>
       </c>
       <c r="G113" s="2" t="s">
@@ -6037,12 +6145,9 @@
       <c r="R113" s="4"/>
       <c r="S113" s="2"/>
       <c r="T113" s="5"/>
-      <c r="U113" s="6"/>
-      <c r="V113" s="6"/>
-      <c r="W113" s="6"/>
     </row>
     <row r="114" spans="1:23">
-      <c r="A114" s="6">
+      <c r="A114">
         <v>941</v>
       </c>
       <c r="B114" s="1">
@@ -6057,7 +6162,7 @@
       <c r="E114" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F114" s="6">
+      <c r="F114">
         <v>38129</v>
       </c>
       <c r="G114" s="2" t="s">
@@ -6078,12 +6183,9 @@
       <c r="T114" s="5" t="s">
         <v>289</v>
       </c>
-      <c r="U114" s="6"/>
-      <c r="V114" s="6"/>
-      <c r="W114" s="6"/>
     </row>
     <row r="115" spans="1:23">
-      <c r="A115" s="6">
+      <c r="A115">
         <v>942</v>
       </c>
       <c r="B115" s="1">
@@ -6098,7 +6200,7 @@
       <c r="E115" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F115" s="6">
+      <c r="F115">
         <v>38502</v>
       </c>
       <c r="G115" s="2" t="s">
@@ -6119,12 +6221,9 @@
       <c r="R115" s="4"/>
       <c r="S115" s="2"/>
       <c r="T115" s="5"/>
-      <c r="U115" s="6"/>
-      <c r="V115" s="6"/>
-      <c r="W115" s="6"/>
     </row>
     <row r="116" spans="1:23">
-      <c r="A116" s="6">
+      <c r="A116">
         <v>943</v>
       </c>
       <c r="B116" s="1">
@@ -6139,7 +6238,7 @@
       <c r="E116" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F116" s="6">
+      <c r="F116">
         <v>38502</v>
       </c>
       <c r="G116" s="2" t="s">
@@ -6160,12 +6259,9 @@
       <c r="R116" s="4"/>
       <c r="S116" s="2"/>
       <c r="T116" s="5"/>
-      <c r="U116" s="6"/>
-      <c r="V116" s="6"/>
-      <c r="W116" s="6"/>
     </row>
     <row r="117" spans="1:23">
-      <c r="A117" s="6">
+      <c r="A117">
         <v>944</v>
       </c>
       <c r="B117" s="1">
@@ -6180,7 +6276,7 @@
       <c r="E117" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117">
         <v>43070</v>
       </c>
       <c r="G117" s="2" t="s">
@@ -6205,12 +6301,9 @@
         <v>293</v>
       </c>
       <c r="T117" s="5"/>
-      <c r="U117" s="6"/>
-      <c r="V117" s="6"/>
-      <c r="W117" s="6"/>
     </row>
     <row r="118" spans="1:23">
-      <c r="A118" s="6">
+      <c r="A118">
         <v>945</v>
       </c>
       <c r="B118" s="1">
@@ -6225,7 +6318,7 @@
       <c r="E118" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F118">
         <v>38502</v>
       </c>
       <c r="G118" s="2" t="s">
@@ -6250,12 +6343,9 @@
         <v>294</v>
       </c>
       <c r="T118" s="5"/>
-      <c r="U118" s="6"/>
-      <c r="V118" s="6"/>
-      <c r="W118" s="6"/>
     </row>
     <row r="119" spans="1:23">
-      <c r="A119" s="6">
+      <c r="A119">
         <v>946</v>
       </c>
       <c r="B119" s="1">
@@ -6270,7 +6360,7 @@
       <c r="E119" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119">
         <v>43070</v>
       </c>
       <c r="G119" s="2" t="s">
@@ -6289,14 +6379,12 @@
       <c r="R119" s="4"/>
       <c r="S119" s="2"/>
       <c r="T119" s="5"/>
-      <c r="U119" s="6" t="s">
+      <c r="U119" t="s">
         <v>295</v>
       </c>
-      <c r="V119" s="6"/>
-      <c r="W119" s="6"/>
     </row>
     <row r="120" spans="1:23">
-      <c r="A120" s="6">
+      <c r="A120">
         <v>947</v>
       </c>
       <c r="B120" s="1">
@@ -6311,7 +6399,7 @@
       <c r="E120" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F120">
         <v>38447</v>
       </c>
       <c r="G120" s="2" t="s">
@@ -6332,12 +6420,9 @@
       <c r="T120" s="5" t="s">
         <v>298</v>
       </c>
-      <c r="U120" s="6"/>
-      <c r="V120" s="6"/>
-      <c r="W120" s="6"/>
     </row>
     <row r="121" spans="1:23">
-      <c r="A121" s="6">
+      <c r="A121">
         <v>948</v>
       </c>
       <c r="B121" s="1">
@@ -6352,7 +6437,7 @@
       <c r="E121" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="F121" s="6">
+      <c r="F121">
         <v>38567</v>
       </c>
       <c r="G121" s="2" t="s">
@@ -6373,12 +6458,9 @@
       <c r="R121" s="4"/>
       <c r="S121" s="2"/>
       <c r="T121" s="5"/>
-      <c r="U121" s="6"/>
-      <c r="V121" s="6"/>
-      <c r="W121" s="6"/>
     </row>
     <row r="122" spans="1:23">
-      <c r="A122" s="6">
+      <c r="A122">
         <v>949</v>
       </c>
       <c r="B122" s="1">
@@ -6393,7 +6475,7 @@
       <c r="E122" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122">
         <v>43070</v>
       </c>
       <c r="G122" s="2" t="s">
@@ -6412,16 +6494,15 @@
       <c r="R122" s="4"/>
       <c r="S122" s="2"/>
       <c r="T122" s="5"/>
-      <c r="U122" s="6"/>
-      <c r="V122" s="6" t="s">
+      <c r="V122" t="s">
         <v>302</v>
       </c>
-      <c r="W122" s="6" t="s">
+      <c r="W122" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="123" spans="1:23">
-      <c r="A123" s="6">
+      <c r="A123">
         <v>950</v>
       </c>
       <c r="B123" s="1">
@@ -6436,7 +6517,7 @@
       <c r="E123" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F123">
         <v>43026</v>
       </c>
       <c r="G123" s="2" t="s">
@@ -6457,12 +6538,9 @@
       <c r="R123" s="4"/>
       <c r="S123" s="2"/>
       <c r="T123" s="5"/>
-      <c r="U123" s="6"/>
-      <c r="V123" s="6"/>
-      <c r="W123" s="6"/>
     </row>
     <row r="124" spans="1:23">
-      <c r="A124" s="6">
+      <c r="A124">
         <v>951</v>
       </c>
       <c r="B124" s="1">
@@ -6477,7 +6555,7 @@
       <c r="E124" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F124">
         <v>38375</v>
       </c>
       <c r="G124" s="2" t="s">
@@ -6498,9 +6576,830 @@
       <c r="R124" s="4"/>
       <c r="S124" s="2"/>
       <c r="T124" s="5"/>
-      <c r="U124" s="6"/>
-      <c r="V124" s="6"/>
-      <c r="W124" s="6"/>
+    </row>
+    <row r="125" spans="1:23">
+      <c r="A125" s="6">
+        <v>952</v>
+      </c>
+      <c r="B125" s="1">
+        <v>46286.511018518497</v>
+      </c>
+      <c r="C125" s="1">
+        <v>46286.519918981503</v>
+      </c>
+      <c r="D125" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E125" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F125" s="6">
+        <v>38801</v>
+      </c>
+      <c r="G125" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H125" s="2"/>
+      <c r="I125" s="2"/>
+      <c r="J125" s="2"/>
+      <c r="K125" s="2"/>
+      <c r="L125" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="M125" s="2"/>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
+      <c r="P125" s="2"/>
+      <c r="Q125" s="4"/>
+      <c r="R125" s="4"/>
+      <c r="S125" s="2"/>
+      <c r="T125" s="5"/>
+      <c r="U125" s="6"/>
+      <c r="V125" s="6"/>
+      <c r="W125" s="6"/>
+    </row>
+    <row r="126" spans="1:23">
+      <c r="A126" s="6">
+        <v>953</v>
+      </c>
+      <c r="B126" s="1">
+        <v>46286.506793981498</v>
+      </c>
+      <c r="C126" s="1">
+        <v>46286.520104166702</v>
+      </c>
+      <c r="D126" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E126" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F126" s="6">
+        <v>43163</v>
+      </c>
+      <c r="G126" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H126" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I126" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="J126" s="2"/>
+      <c r="K126" s="2"/>
+      <c r="L126" s="2"/>
+      <c r="M126" s="2"/>
+      <c r="N126" s="2"/>
+      <c r="O126" s="2"/>
+      <c r="P126" s="2"/>
+      <c r="Q126" s="4"/>
+      <c r="R126" s="4"/>
+      <c r="S126" s="2"/>
+      <c r="T126" s="5"/>
+      <c r="U126" s="6"/>
+      <c r="V126" s="6"/>
+      <c r="W126" s="6"/>
+    </row>
+    <row r="127" spans="1:23">
+      <c r="A127" s="6">
+        <v>954</v>
+      </c>
+      <c r="B127" s="1">
+        <v>46286.520219907397</v>
+      </c>
+      <c r="C127" s="1">
+        <v>46286.5206481481</v>
+      </c>
+      <c r="D127" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E127" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="F127" s="6">
+        <v>43164</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H127" s="2"/>
+      <c r="I127" s="2"/>
+      <c r="J127" s="2"/>
+      <c r="K127" s="2"/>
+      <c r="L127" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="M127" s="2"/>
+      <c r="N127" s="2"/>
+      <c r="O127" s="2"/>
+      <c r="P127" s="2"/>
+      <c r="Q127" s="4"/>
+      <c r="R127" s="4"/>
+      <c r="S127" s="2"/>
+      <c r="T127" s="5"/>
+      <c r="U127" s="6"/>
+      <c r="V127" s="6"/>
+      <c r="W127" s="6"/>
+    </row>
+    <row r="128" spans="1:23">
+      <c r="A128" s="6">
+        <v>955</v>
+      </c>
+      <c r="B128" s="1">
+        <v>46286.517719907402</v>
+      </c>
+      <c r="C128" s="1">
+        <v>46286.5221296296</v>
+      </c>
+      <c r="D128" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="E128" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="F128" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G128" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H128" s="2"/>
+      <c r="I128" s="2"/>
+      <c r="J128" s="2"/>
+      <c r="K128" s="2"/>
+      <c r="L128" s="2"/>
+      <c r="M128" s="2"/>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" s="2"/>
+      <c r="Q128" s="4"/>
+      <c r="R128" s="4"/>
+      <c r="S128" s="2"/>
+      <c r="T128" s="5" t="s">
+        <v>319</v>
+      </c>
+      <c r="U128" s="6"/>
+      <c r="V128" s="6"/>
+      <c r="W128" s="6"/>
+    </row>
+    <row r="129" spans="1:23">
+      <c r="A129" s="6">
+        <v>956</v>
+      </c>
+      <c r="B129" s="1">
+        <v>46286.522499999999</v>
+      </c>
+      <c r="C129" s="1">
+        <v>46286.522916666698</v>
+      </c>
+      <c r="D129" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E129" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F129" s="6">
+        <v>38659</v>
+      </c>
+      <c r="G129" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H129" s="2"/>
+      <c r="I129" s="2"/>
+      <c r="J129" s="2"/>
+      <c r="K129" s="2"/>
+      <c r="L129" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="M129" s="2"/>
+      <c r="N129" s="2"/>
+      <c r="O129" s="2"/>
+      <c r="P129" s="2"/>
+      <c r="Q129" s="4"/>
+      <c r="R129" s="4"/>
+      <c r="S129" s="2"/>
+      <c r="T129" s="5"/>
+      <c r="U129" s="6"/>
+      <c r="V129" s="6"/>
+      <c r="W129" s="6"/>
+    </row>
+    <row r="130" spans="1:23">
+      <c r="A130" s="6">
+        <v>957</v>
+      </c>
+      <c r="B130" s="1">
+        <v>46286.520439814798</v>
+      </c>
+      <c r="C130" s="1">
+        <v>46286.5242939815</v>
+      </c>
+      <c r="D130" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E130" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F130" s="6">
+        <v>38801</v>
+      </c>
+      <c r="G130" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H130" s="2"/>
+      <c r="I130" s="2"/>
+      <c r="J130" s="2"/>
+      <c r="K130" s="2"/>
+      <c r="L130" s="2"/>
+      <c r="M130" s="2"/>
+      <c r="N130" s="2"/>
+      <c r="O130" s="2"/>
+      <c r="P130" s="2"/>
+      <c r="Q130" s="4"/>
+      <c r="R130" s="4"/>
+      <c r="S130" s="2"/>
+      <c r="T130" s="5" t="s">
+        <v>321</v>
+      </c>
+      <c r="U130" s="6"/>
+      <c r="V130" s="6"/>
+      <c r="W130" s="6"/>
+    </row>
+    <row r="131" spans="1:23">
+      <c r="A131" s="6">
+        <v>958</v>
+      </c>
+      <c r="B131" s="1">
+        <v>46286.524942129603</v>
+      </c>
+      <c r="C131" s="1">
+        <v>46286.527488425898</v>
+      </c>
+      <c r="D131" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E131" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F131" s="6">
+        <v>38691</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H131" s="2"/>
+      <c r="I131" s="2"/>
+      <c r="J131" s="2"/>
+      <c r="K131" s="2"/>
+      <c r="L131" s="2"/>
+      <c r="M131" s="2"/>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" s="2"/>
+      <c r="Q131" s="4"/>
+      <c r="R131" s="4"/>
+      <c r="S131" s="2"/>
+      <c r="T131" s="5" t="s">
+        <v>324</v>
+      </c>
+      <c r="U131" s="6"/>
+      <c r="V131" s="6"/>
+      <c r="W131" s="6"/>
+    </row>
+    <row r="132" spans="1:23">
+      <c r="A132" s="6">
+        <v>959</v>
+      </c>
+      <c r="B132" s="1">
+        <v>46286.519363425898</v>
+      </c>
+      <c r="C132" s="1">
+        <v>46286.527997685203</v>
+      </c>
+      <c r="D132" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E132" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F132" s="6">
+        <v>38718</v>
+      </c>
+      <c r="G132" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H132" s="2"/>
+      <c r="I132" s="2"/>
+      <c r="J132" s="2"/>
+      <c r="K132" s="2"/>
+      <c r="L132" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="M132" s="2"/>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" s="2"/>
+      <c r="Q132" s="4"/>
+      <c r="R132" s="4"/>
+      <c r="S132" s="2"/>
+      <c r="T132" s="5"/>
+      <c r="U132" s="6"/>
+      <c r="V132" s="6"/>
+      <c r="W132" s="6"/>
+    </row>
+    <row r="133" spans="1:23">
+      <c r="A133" s="6">
+        <v>960</v>
+      </c>
+      <c r="B133" s="1">
+        <v>46286.526423611103</v>
+      </c>
+      <c r="C133" s="1">
+        <v>46286.529050925899</v>
+      </c>
+      <c r="D133" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E133" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="F133" s="6">
+        <v>38107</v>
+      </c>
+      <c r="G133" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H133" s="2"/>
+      <c r="I133" s="2"/>
+      <c r="J133" s="2"/>
+      <c r="K133" s="2"/>
+      <c r="L133" s="2"/>
+      <c r="M133" s="2"/>
+      <c r="N133" s="2"/>
+      <c r="O133" s="2"/>
+      <c r="P133" s="2"/>
+      <c r="Q133" s="4"/>
+      <c r="R133" s="4"/>
+      <c r="S133" s="2"/>
+      <c r="T133" s="5" t="s">
+        <v>330</v>
+      </c>
+      <c r="U133" s="6"/>
+      <c r="V133" s="6"/>
+      <c r="W133" s="6"/>
+    </row>
+    <row r="134" spans="1:23">
+      <c r="A134" s="6">
+        <v>961</v>
+      </c>
+      <c r="B134" s="1">
+        <v>46286.532395833303</v>
+      </c>
+      <c r="C134" s="1">
+        <v>46286.534803240698</v>
+      </c>
+      <c r="D134" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E134" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="F134" s="6">
+        <v>38124</v>
+      </c>
+      <c r="G134" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H134" s="2"/>
+      <c r="I134" s="2"/>
+      <c r="J134" s="2"/>
+      <c r="K134" s="2"/>
+      <c r="L134" s="2"/>
+      <c r="M134" s="2"/>
+      <c r="N134" s="2"/>
+      <c r="O134" s="2"/>
+      <c r="P134" s="2"/>
+      <c r="Q134" s="4"/>
+      <c r="R134" s="4"/>
+      <c r="S134" s="2"/>
+      <c r="T134" s="5" t="s">
+        <v>333</v>
+      </c>
+      <c r="U134" s="6"/>
+      <c r="V134" s="6"/>
+      <c r="W134" s="6"/>
+    </row>
+    <row r="135" spans="1:23">
+      <c r="A135" s="6">
+        <v>962</v>
+      </c>
+      <c r="B135" s="1">
+        <v>46286.535266203697</v>
+      </c>
+      <c r="C135" s="1">
+        <v>46286.5360069444</v>
+      </c>
+      <c r="D135" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E135" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="F135" s="6">
+        <v>38464</v>
+      </c>
+      <c r="G135" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="H135" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I135" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="J135" s="2"/>
+      <c r="K135" s="2"/>
+      <c r="L135" s="2"/>
+      <c r="M135" s="2"/>
+      <c r="N135" s="2"/>
+      <c r="O135" s="2"/>
+      <c r="P135" s="2"/>
+      <c r="Q135" s="4"/>
+      <c r="R135" s="4"/>
+      <c r="S135" s="2"/>
+      <c r="T135" s="5"/>
+      <c r="U135" s="6"/>
+      <c r="V135" s="6"/>
+      <c r="W135" s="6"/>
+    </row>
+    <row r="136" spans="1:23">
+      <c r="A136" s="6">
+        <v>963</v>
+      </c>
+      <c r="B136" s="1">
+        <v>46286.512754629599</v>
+      </c>
+      <c r="C136" s="1">
+        <v>46286.536527777796</v>
+      </c>
+      <c r="D136" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E136" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="F136" s="6">
+        <v>38428</v>
+      </c>
+      <c r="G136" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H136" s="2"/>
+      <c r="I136" s="2"/>
+      <c r="J136" s="2"/>
+      <c r="K136" s="2"/>
+      <c r="L136" s="2"/>
+      <c r="M136" s="2"/>
+      <c r="N136" s="2"/>
+      <c r="O136" s="2"/>
+      <c r="P136" s="2"/>
+      <c r="Q136" s="4"/>
+      <c r="R136" s="4"/>
+      <c r="S136" s="2"/>
+      <c r="T136" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="U136" s="6"/>
+      <c r="V136" s="6"/>
+      <c r="W136" s="6"/>
+    </row>
+    <row r="137" spans="1:23">
+      <c r="A137" s="6">
+        <v>964</v>
+      </c>
+      <c r="B137" s="1">
+        <v>46286.539525462998</v>
+      </c>
+      <c r="C137" s="1">
+        <v>46286.540520833303</v>
+      </c>
+      <c r="D137" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E137" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="F137" s="6">
+        <v>38571</v>
+      </c>
+      <c r="G137" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
+      <c r="J137" s="2"/>
+      <c r="K137" s="2"/>
+      <c r="L137" s="2"/>
+      <c r="M137" s="2"/>
+      <c r="N137" s="2"/>
+      <c r="O137" s="2"/>
+      <c r="P137" s="2"/>
+      <c r="Q137" s="4"/>
+      <c r="R137" s="4"/>
+      <c r="S137" s="2"/>
+      <c r="T137" s="5" t="s">
+        <v>342</v>
+      </c>
+      <c r="U137" s="6"/>
+      <c r="V137" s="6"/>
+      <c r="W137" s="6"/>
+    </row>
+    <row r="138" spans="1:23">
+      <c r="A138" s="6">
+        <v>965</v>
+      </c>
+      <c r="B138" s="1">
+        <v>46286.4847800926</v>
+      </c>
+      <c r="C138" s="1">
+        <v>46286.549421296302</v>
+      </c>
+      <c r="D138" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="E138" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="F138" s="6">
+        <v>38859</v>
+      </c>
+      <c r="G138" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H138" s="2"/>
+      <c r="I138" s="2"/>
+      <c r="J138" s="2"/>
+      <c r="K138" s="2"/>
+      <c r="L138" s="2"/>
+      <c r="M138" s="2"/>
+      <c r="N138" s="2"/>
+      <c r="O138" s="2"/>
+      <c r="P138" s="2"/>
+      <c r="Q138" s="4"/>
+      <c r="R138" s="4"/>
+      <c r="S138" s="2"/>
+      <c r="T138" s="5" t="s">
+        <v>343</v>
+      </c>
+      <c r="U138" s="6"/>
+      <c r="V138" s="6"/>
+      <c r="W138" s="6"/>
+    </row>
+    <row r="139" spans="1:23">
+      <c r="A139" s="6">
+        <v>966</v>
+      </c>
+      <c r="B139" s="1">
+        <v>46286.553229166697</v>
+      </c>
+      <c r="C139" s="1">
+        <v>46286.5534259259</v>
+      </c>
+      <c r="D139" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E139" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="F139" s="6">
+        <v>38496</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H139" s="2"/>
+      <c r="I139" s="2"/>
+      <c r="J139" s="2"/>
+      <c r="K139" s="2"/>
+      <c r="L139" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="M139" s="2"/>
+      <c r="N139" s="2"/>
+      <c r="O139" s="2"/>
+      <c r="P139" s="2"/>
+      <c r="Q139" s="4"/>
+      <c r="R139" s="4"/>
+      <c r="S139" s="2"/>
+      <c r="T139" s="5"/>
+      <c r="U139" s="6"/>
+      <c r="V139" s="6"/>
+      <c r="W139" s="6"/>
+    </row>
+    <row r="140" spans="1:23">
+      <c r="A140" s="6">
+        <v>967</v>
+      </c>
+      <c r="B140" s="1">
+        <v>46286.547881944403</v>
+      </c>
+      <c r="C140" s="1">
+        <v>46286.553715277798</v>
+      </c>
+      <c r="D140" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E140" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="F140" s="6">
+        <v>38468</v>
+      </c>
+      <c r="G140" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H140" s="2"/>
+      <c r="I140" s="2"/>
+      <c r="J140" s="2"/>
+      <c r="K140" s="2"/>
+      <c r="L140" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="M140" s="2"/>
+      <c r="N140" s="2"/>
+      <c r="O140" s="2"/>
+      <c r="P140" s="2"/>
+      <c r="Q140" s="4"/>
+      <c r="R140" s="4"/>
+      <c r="S140" s="2"/>
+      <c r="T140" s="5"/>
+      <c r="U140" s="6"/>
+      <c r="V140" s="6"/>
+      <c r="W140" s="6"/>
+    </row>
+    <row r="141" spans="1:23">
+      <c r="A141" s="6">
+        <v>968</v>
+      </c>
+      <c r="B141" s="1">
+        <v>46286.556145833303</v>
+      </c>
+      <c r="C141" s="1">
+        <v>46286.556898148097</v>
+      </c>
+      <c r="D141" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E141" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F141" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G141" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H141" s="2"/>
+      <c r="I141" s="2"/>
+      <c r="J141" s="2"/>
+      <c r="K141" s="2"/>
+      <c r="L141" s="2"/>
+      <c r="M141" s="2"/>
+      <c r="N141" s="2"/>
+      <c r="O141" s="2"/>
+      <c r="P141" s="2"/>
+      <c r="Q141" s="4"/>
+      <c r="R141" s="4"/>
+      <c r="S141" s="2"/>
+      <c r="T141" s="5" t="s">
+        <v>352</v>
+      </c>
+      <c r="U141" s="6"/>
+      <c r="V141" s="6"/>
+      <c r="W141" s="6"/>
+    </row>
+    <row r="142" spans="1:23">
+      <c r="A142" s="6">
+        <v>969</v>
+      </c>
+      <c r="B142" s="1">
+        <v>46286.558020833298</v>
+      </c>
+      <c r="C142" s="1">
+        <v>46286.5603819444</v>
+      </c>
+      <c r="D142" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E142" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F142" s="6">
+        <v>43159</v>
+      </c>
+      <c r="G142" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H142" s="2"/>
+      <c r="I142" s="2"/>
+      <c r="J142" s="2"/>
+      <c r="K142" s="2"/>
+      <c r="L142" s="2"/>
+      <c r="M142" s="2"/>
+      <c r="N142" s="2"/>
+      <c r="O142" s="2"/>
+      <c r="P142" s="2"/>
+      <c r="Q142" s="4"/>
+      <c r="R142" s="4"/>
+      <c r="S142" s="2"/>
+      <c r="T142" s="5" t="s">
+        <v>355</v>
+      </c>
+      <c r="U142" s="6"/>
+      <c r="V142" s="6"/>
+      <c r="W142" s="6"/>
+    </row>
+    <row r="143" spans="1:23">
+      <c r="A143" s="6">
+        <v>970</v>
+      </c>
+      <c r="B143" s="1">
+        <v>46286.561041666697</v>
+      </c>
+      <c r="C143" s="1">
+        <v>46286.561851851897</v>
+      </c>
+      <c r="D143" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E143" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="F143" s="6">
+        <v>38116</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H143" s="2"/>
+      <c r="I143" s="2"/>
+      <c r="J143" s="2"/>
+      <c r="K143" s="2"/>
+      <c r="L143" s="2"/>
+      <c r="M143" s="2"/>
+      <c r="N143" s="2"/>
+      <c r="O143" s="2"/>
+      <c r="P143" s="2"/>
+      <c r="Q143" s="4"/>
+      <c r="R143" s="4"/>
+      <c r="S143" s="2"/>
+      <c r="T143" s="5" t="s">
+        <v>358</v>
+      </c>
+      <c r="U143" s="6"/>
+      <c r="V143" s="6"/>
+      <c r="W143" s="6"/>
+    </row>
+    <row r="144" spans="1:23">
+      <c r="A144" s="6">
+        <v>971</v>
+      </c>
+      <c r="B144" s="1">
+        <v>46286.690682870401</v>
+      </c>
+      <c r="C144" s="1">
+        <v>46286.692245370403</v>
+      </c>
+      <c r="D144" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E144" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="F144" s="6">
+        <v>38429</v>
+      </c>
+      <c r="G144" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="H144" s="2"/>
+      <c r="I144" s="2"/>
+      <c r="J144" s="2"/>
+      <c r="K144" s="2"/>
+      <c r="L144" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="M144" s="2"/>
+      <c r="N144" s="2"/>
+      <c r="O144" s="2"/>
+      <c r="P144" s="2"/>
+      <c r="Q144" s="4"/>
+      <c r="R144" s="4"/>
+      <c r="S144" s="2"/>
+      <c r="T144" s="5"/>
+      <c r="U144" s="6"/>
+      <c r="V144" s="6"/>
+      <c r="W144" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="133" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2BB07984-5FE0-43F4-BDD1-EAC504ACDFA9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4F99BF8C-3E3D-42D6-BFA8-EEFB0288612A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="624" uniqueCount="362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="308">
   <si>
     <t>Id</t>
   </si>
@@ -449,18 +449,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_9870_Starbucks%20San%20Mateo.jpeg</t>
   </si>
   <si>
-    <t>sbmx38418@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Plaza Oriente</t>
-  </si>
-  <si>
-    <t>Lay Out</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/82D608F5-BE6B-4F2E-B86B-8E83504FDF66_Starbucks%20Plaza%20Orie.jpeg</t>
-  </si>
-  <si>
     <t>SBMX38119@starbucks.com.mx</t>
   </si>
   <si>
@@ -503,9 +491,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Daniel%20Bustos%20Martin.jpg</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17898690177589028917725967468681_Starbucks%20San%20Marcos.jpg</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/1789869064821271285516039601533_Starbucks%20San%20Marcos.jpg</t>
   </si>
   <si>
@@ -617,15 +602,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_3490_Starbucks%20Mega%20Izcal.jpeg</t>
   </si>
   <si>
-    <t>sbmx38511@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Ciudad Jardin II</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Ciudad%20Jar.jpg</t>
-  </si>
-  <si>
     <t>hector.estevez@starbucks.com.mx</t>
   </si>
   <si>
@@ -662,15 +638,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/1789953621847314136934969667231_Diego%20Conde%20Merino.jpg</t>
   </si>
   <si>
-    <t>thelma.melendez@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Thelma Edith Melendez Galvan</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/94EC3CDE-6080-497D-BB28-B591958924E2_Thelma%20Edith%20Melende.png</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Starbucks%20Viveros%20Sa.jpg</t>
   </si>
   <si>
@@ -770,9 +737,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG_4348_Starbucks%20CEMTRAM%204.jpeg</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/94EC3CDE-6080-497D-BB28-B591958924E2_Thelma%20Edith%20Melende%201.png</t>
-  </si>
-  <si>
     <t>sbmx38800@starbucks.com.mx</t>
   </si>
   <si>
@@ -782,15 +746,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/20260921_104836_Starbucks%20Antenas%20PA.jpg</t>
   </si>
   <si>
-    <t>sbmx43169@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Plaza Tepozán</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/collage_layouts_plaza_tepozan_Starbucks%20Plaza%20Tepo.png</t>
-  </si>
-  <si>
     <t>sbmx38502@starbucks.com.mx</t>
   </si>
   <si>
@@ -803,18 +758,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20San%20Marcos.jpg</t>
   </si>
   <si>
-    <t>SBMX38594@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Carretera México-Puebla</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17900109651253392560454380281814_Starbucks%20Carretera.jpg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/Captura%20de%20pantalla%202026-09-21%20a%20la(s)%2011.20._Starbucks%20San%20Marcos.png</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/B4897F50-5909-4313-BD11-178E45F6AC3A_Starbucks%20San%20Marcos.jpeg</t>
   </si>
   <si>
@@ -830,9 +773,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG-20260920-WA0040_Starbucks%20Plaza%20Sate.jpg</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/E9257EBB-FA15-415F-9F3A-3FC16EDC4B54_Starbucks%20Rojo%20Gomez.png</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Rojo%20Gomez.jpg</t>
   </si>
   <si>
@@ -848,24 +788,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Starbucks%20Rojo%20Gomez.jpg</t>
   </si>
   <si>
-    <t>sbmx38657@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Patio Lomas Estrella</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/351B82AB-4432-4A0C-9B85-CBE8626904A3_Starbucks%20Patio%20Loma.jpeg</t>
-  </si>
-  <si>
-    <t>sbmx38855@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Plaza Zapotitlan</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17900131498944984186324606561468_Starbucks%20Plaza%20Zapo.jpg</t>
-  </si>
-  <si>
     <t>sbmx38659@starbucks.com.mx</t>
   </si>
   <si>
@@ -878,15 +800,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/D0AD8D6D-E8DB-4E35-A8CD-9AC7F4B4B7B9_Starbucks%20Rojo%20Gomez.png</t>
   </si>
   <si>
-    <t>SBMX38569@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Plaza Universidad</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/original-9D7A689F-54DB-4850-8128-166B68319E01_Starbucks%20Plaza%20Univ.jpeg</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/Captura%20de%20pantalla%202026-09-21%20a%20la(s)%2011.15._Starbucks%20San%20Marcos%201.png</t>
   </si>
   <si>
@@ -905,9 +818,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20San%20Marcos%201.jpg</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/Captura%20de%20pantalla%202026-09-21%20a%20la(s)%2011.20._Starbucks%20San%20Marcos%201.png</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG_6137_Marlene%20Danaee%20Herna%201.jpeg</t>
   </si>
   <si>
@@ -938,37 +848,28 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/1D53C3AD-FFEA-4D04-84B1-A2F5DCE9849D-COLLAGE_Starbucks%20Hospital%20A.jpeg</t>
   </si>
   <si>
-    <t>sbmx38567@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Aragón II</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Arag%C3%B3n%20II.jpg</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/85a00fe0-7cf9-445c-a250-3d68aacc3729_Starbucks%20Rojo%20Gomez.jpeg</t>
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/image_Starbucks%20Rojo%20Gomez.jpg</t>
   </si>
   <si>
-    <t>sbmx43026@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Plaza Ermita</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Plaza%20Ermi.jpg</t>
-  </si>
-  <si>
-    <t>irving.pichardo@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Irving Gonzalez Pichardo</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Irving%20Gonzalez%20Pich.jpg</t>
+    <t>axa.montano@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Axa Yunuen Montaño Martinez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Axa%20Yunuen%20Monta%C3%B1o%20M.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38615@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Grand San Jerónimo</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17900154633627772337840385731009_Starbucks%20Grand%20San.jpg</t>
   </si>
   <si>
     <t>eloisa.rosas@starbucks.com.mx</t>
@@ -977,33 +878,6 @@
     <t>Eloisa Adriana Rosas Loyola</t>
   </si>
   <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/ESPRESSO_Eloisa%20Adriana%20Rosas.jpeg</t>
-  </si>
-  <si>
-    <t>axa.montano@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Axa Yunuen Montaño Martinez</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Axa%20Yunuen%20Monta%C3%B1o%20M.jpg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/4c33b8c1-1adb-4d1d-9ef3-90e355452f1b_Johan%20Arellano%20Navar.jpeg</t>
-  </si>
-  <si>
-    <t>sbmx38615@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Grand San Jerónimo</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/17900154633627772337840385731009_Starbucks%20Grand%20San.jpg</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/fcd2f50b-4f13-43a1-aa77-776026856ad0_Starbucks%20Sendero%20Ix.jpeg</t>
-  </si>
-  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/SNOOPY_Eloisa%20Adriana%20Rosas.jpeg</t>
   </si>
   <si>
@@ -1016,15 +890,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/image_Rosa%20Patricia%20Aguila.jpg</t>
   </si>
   <si>
-    <t>guadalupe.camacho@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Guadalupe Camacho Contreras</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/photocollage_2026921123832243_Guadalupe%20Camacho%20Co.jpg</t>
-  </si>
-  <si>
     <t>SBMX38107@starbucks.com.mx</t>
   </si>
   <si>
@@ -1073,24 +938,6 @@
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/IMG-20260921-WA0060_Starbucks%20Plaza%20Sate.jpg</t>
   </si>
   <si>
-    <t>sbmx38496@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Taxqueña</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/27c349bf-709d-4acb-91f8-1985280a19c5_Starbucks%20Taxque%C3%B1a.jpeg</t>
-  </si>
-  <si>
-    <t>sbmx38468@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Portal Churubusco</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/Screenshot_20260921_131656_Drive_Starbucks%20Portal%20Chu.jpg</t>
-  </si>
-  <si>
     <t>amparo.delgado@starbucks.com.mx</t>
   </si>
   <si>
@@ -1116,15 +963,6 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%202/D15444CA-54E6-4CD4-BB23-BF27AB121A9C-COLLAGE_Starbucks%20Santa%20Tere.jpeg</t>
-  </si>
-  <si>
-    <t>sbmx38429@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Plaza Aragón</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/image_Starbucks%20Plaza%20Arag.jpg</t>
   </si>
 </sst>
 </file>
@@ -1169,7 +1007,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1178,7 +1016,6 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1262,8 +1099,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W144" totalsRowShown="0">
-  <autoFilter ref="A1:W144" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:W121" totalsRowShown="0">
+  <autoFilter ref="A1:W121" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="23">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="20">
       <extLst>
@@ -1430,7 +1267,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="971" latestEventMarker="1362">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="973" latestEventMarker="1364">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1757,7 +1594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W144"/>
+  <dimension ref="A1:W121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="3" width="20" bestFit="1" customWidth="1"/>
@@ -3303,13 +3140,13 @@
     </row>
     <row r="40" spans="1:21">
       <c r="A40">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B40" s="1">
-        <v>46284.792303240698</v>
+        <v>46284.792152777802</v>
       </c>
       <c r="C40" s="1">
-        <v>46284.793460648099</v>
+        <v>46284.793726851902</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>136</v>
@@ -3318,18 +3155,16 @@
         <v>137</v>
       </c>
       <c r="F40">
-        <v>38418</v>
+        <v>38119</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="H40" s="2"/>
       <c r="I40" s="2"/>
       <c r="J40" s="2"/>
       <c r="K40" s="2"/>
-      <c r="L40" s="2" t="s">
-        <v>139</v>
-      </c>
+      <c r="L40" s="2"/>
       <c r="M40" s="2"/>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -3337,32 +3172,38 @@
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
       <c r="S40" s="2"/>
-      <c r="T40" s="5"/>
+      <c r="T40" s="5" t="s">
+        <v>138</v>
+      </c>
     </row>
     <row r="41" spans="1:21">
       <c r="A41">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B41" s="1">
-        <v>46284.792152777802</v>
+        <v>46284.822141203702</v>
       </c>
       <c r="C41" s="1">
-        <v>46284.793726851902</v>
+        <v>46284.8230555556</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="F41">
+        <v>38339</v>
+      </c>
+      <c r="G41" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F41">
-        <v>38119</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H41" s="2"/>
-      <c r="I41" s="2"/>
+      <c r="H41" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>143</v>
+      </c>
       <c r="J41" s="2"/>
       <c r="K41" s="2"/>
       <c r="L41" s="2"/>
@@ -3373,39 +3214,35 @@
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
       <c r="S41" s="2"/>
-      <c r="T41" s="5" t="s">
-        <v>142</v>
-      </c>
+      <c r="T41" s="5"/>
     </row>
     <row r="42" spans="1:21">
       <c r="A42">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B42" s="1">
-        <v>46284.822141203702</v>
+        <v>46284.823738425897</v>
       </c>
       <c r="C42" s="1">
-        <v>46284.8230555556</v>
+        <v>46284.825856481497</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F42">
         <v>38339</v>
       </c>
       <c r="G42" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="J42" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="H42" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="J42" s="2"/>
       <c r="K42" s="2"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2"/>
@@ -3419,32 +3256,32 @@
     </row>
     <row r="43" spans="1:21">
       <c r="A43">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B43" s="1">
-        <v>46284.823738425897</v>
+        <v>46284.825914351903</v>
       </c>
       <c r="C43" s="1">
-        <v>46284.825856481497</v>
+        <v>46284.8262384259</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F43">
         <v>38339</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>148</v>
+        <v>25</v>
       </c>
       <c r="H43" s="2"/>
       <c r="I43" s="2"/>
-      <c r="J43" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="K43" s="2"/>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
       <c r="N43" s="2"/>
@@ -3457,32 +3294,30 @@
     </row>
     <row r="44" spans="1:21">
       <c r="A44">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B44" s="1">
-        <v>46284.825914351903</v>
+        <v>46284.825960648101</v>
       </c>
       <c r="C44" s="1">
-        <v>46284.8262384259</v>
+        <v>46284.8268171296</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F44">
-        <v>38339</v>
+        <v>38411</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H44" s="2"/>
       <c r="I44" s="2"/>
       <c r="J44" s="2"/>
-      <c r="K44" s="2" t="s">
-        <v>150</v>
-      </c>
+      <c r="K44" s="2"/>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
       <c r="N44" s="2"/>
@@ -3491,75 +3326,77 @@
       <c r="Q44" s="4"/>
       <c r="R44" s="4"/>
       <c r="S44" s="2"/>
-      <c r="T44" s="5"/>
+      <c r="T44" s="5" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="45" spans="1:21">
       <c r="A45">
-        <v>872</v>
+        <v>874</v>
       </c>
       <c r="B45" s="1">
-        <v>46284.825960648101</v>
+        <v>46284.826979166697</v>
       </c>
       <c r="C45" s="1">
-        <v>46284.8268171296</v>
+        <v>46284.827430555597</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F45">
-        <v>38411</v>
+        <v>38339</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H45" s="2"/>
       <c r="I45" s="2"/>
       <c r="J45" s="2"/>
       <c r="K45" s="2"/>
       <c r="L45" s="2"/>
-      <c r="M45" s="2"/>
-      <c r="N45" s="2"/>
+      <c r="M45" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N45" s="2" t="s">
+        <v>150</v>
+      </c>
       <c r="O45" s="2"/>
       <c r="P45" s="2"/>
       <c r="Q45" s="4"/>
       <c r="R45" s="4"/>
       <c r="S45" s="2"/>
-      <c r="T45" s="5" t="s">
-        <v>153</v>
-      </c>
+      <c r="T45" s="5"/>
     </row>
     <row r="46" spans="1:21">
       <c r="A46">
-        <v>873</v>
+        <v>875</v>
       </c>
       <c r="B46" s="1">
-        <v>46284.826273148203</v>
+        <v>46284.828043981499</v>
       </c>
       <c r="C46" s="1">
-        <v>46284.826921296299</v>
+        <v>46284.828472222202</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F46">
-        <v>38339</v>
+        <v>38411</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="H46" s="2"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
-      <c r="L46" s="2" t="s">
-        <v>154</v>
-      </c>
+      <c r="L46" s="2"/>
       <c r="M46" s="2"/>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -3568,41 +3405,42 @@
       <c r="R46" s="4"/>
       <c r="S46" s="2"/>
       <c r="T46" s="5"/>
+      <c r="U46" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="47" spans="1:21">
       <c r="A47">
-        <v>874</v>
+        <v>876</v>
       </c>
       <c r="B47" s="1">
-        <v>46284.826979166697</v>
+        <v>46284.827870370398</v>
       </c>
       <c r="C47" s="1">
-        <v>46284.827430555597</v>
+        <v>46284.829895833303</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F47">
         <v>38339</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>29</v>
+        <v>70</v>
       </c>
       <c r="H47" s="2"/>
       <c r="I47" s="2"/>
       <c r="J47" s="2"/>
       <c r="K47" s="2"/>
       <c r="L47" s="2"/>
-      <c r="M47" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="O47" s="2"/>
+      <c r="M47" s="2"/>
+      <c r="N47" s="2"/>
+      <c r="O47" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="P47" s="2"/>
       <c r="Q47" s="4"/>
       <c r="R47" s="4"/>
@@ -3611,25 +3449,25 @@
     </row>
     <row r="48" spans="1:21">
       <c r="A48">
-        <v>875</v>
+        <v>877</v>
       </c>
       <c r="B48" s="1">
-        <v>46284.828043981499</v>
+        <v>46284.829930555599</v>
       </c>
       <c r="C48" s="1">
-        <v>46284.828472222202</v>
+        <v>46284.830428240697</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="F48">
-        <v>38411</v>
+        <v>38339</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>33</v>
+        <v>75</v>
       </c>
       <c r="H48" s="2"/>
       <c r="I48" s="2"/>
@@ -3639,36 +3477,35 @@
       <c r="M48" s="2"/>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
-      <c r="P48" s="2"/>
+      <c r="P48" s="2" t="s">
+        <v>153</v>
+      </c>
       <c r="Q48" s="4"/>
       <c r="R48" s="4"/>
       <c r="S48" s="2"/>
       <c r="T48" s="5"/>
-      <c r="U48" t="s">
-        <v>156</v>
-      </c>
     </row>
     <row r="49" spans="1:20">
       <c r="A49">
-        <v>876</v>
+        <v>878</v>
       </c>
       <c r="B49" s="1">
-        <v>46284.827870370398</v>
+        <v>46284.8305092593</v>
       </c>
       <c r="C49" s="1">
-        <v>46284.829895833303</v>
+        <v>46284.831921296303</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F49">
         <v>38339</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="H49" s="2"/>
       <c r="I49" s="2"/>
@@ -3677,36 +3514,40 @@
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
       <c r="N49" s="2"/>
-      <c r="O49" s="2" t="s">
-        <v>157</v>
-      </c>
+      <c r="O49" s="2"/>
       <c r="P49" s="2"/>
-      <c r="Q49" s="4"/>
-      <c r="R49" s="4"/>
-      <c r="S49" s="2"/>
+      <c r="Q49" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R49" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S49" s="2" t="s">
+        <v>154</v>
+      </c>
       <c r="T49" s="5"/>
     </row>
     <row r="50" spans="1:20">
       <c r="A50">
-        <v>877</v>
+        <v>879</v>
       </c>
       <c r="B50" s="1">
-        <v>46284.829930555599</v>
+        <v>46284.919097222199</v>
       </c>
       <c r="C50" s="1">
-        <v>46284.830428240697</v>
+        <v>46284.921307870398</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>143</v>
+        <v>155</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>144</v>
+        <v>156</v>
       </c>
       <c r="F50">
-        <v>38339</v>
+        <v>38427</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="H50" s="2"/>
       <c r="I50" s="2"/>
@@ -3716,35 +3557,35 @@
       <c r="M50" s="2"/>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
-      <c r="P50" s="2" t="s">
-        <v>158</v>
-      </c>
+      <c r="P50" s="2"/>
       <c r="Q50" s="4"/>
       <c r="R50" s="4"/>
       <c r="S50" s="2"/>
-      <c r="T50" s="5"/>
+      <c r="T50" s="5" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="51" spans="1:20">
       <c r="A51">
-        <v>878</v>
+        <v>880</v>
       </c>
       <c r="B51" s="1">
-        <v>46284.8305092593</v>
+        <v>46285.504050925898</v>
       </c>
       <c r="C51" s="1">
-        <v>46284.831921296303</v>
+        <v>46285.504502314798</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>144</v>
+        <v>159</v>
       </c>
       <c r="F51">
-        <v>38339</v>
+        <v>38186</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="H51" s="2"/>
       <c r="I51" s="2"/>
@@ -3755,35 +3596,31 @@
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
       <c r="P51" s="2"/>
-      <c r="Q51" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="R51" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="S51" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="T51" s="5"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="2"/>
+      <c r="T51" s="5" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="52" spans="1:20">
       <c r="A52">
-        <v>879</v>
+        <v>881</v>
       </c>
       <c r="B52" s="1">
-        <v>46284.919097222199</v>
+        <v>46285.571921296301</v>
       </c>
       <c r="C52" s="1">
-        <v>46284.921307870398</v>
+        <v>46285.572222222203</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F52">
-        <v>38427</v>
+        <v>38561</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>33</v>
@@ -3801,65 +3638,67 @@
       <c r="R52" s="4"/>
       <c r="S52" s="2"/>
       <c r="T52" s="5" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="53" spans="1:20">
       <c r="A53">
-        <v>880</v>
+        <v>882</v>
       </c>
       <c r="B53" s="1">
-        <v>46285.504050925898</v>
+        <v>46285.572731481501</v>
       </c>
       <c r="C53" s="1">
-        <v>46285.504502314798</v>
+        <v>46285.574131944399</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F53">
-        <v>38186</v>
+        <v>38368</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H53" s="2"/>
       <c r="I53" s="2"/>
       <c r="J53" s="2"/>
       <c r="K53" s="2"/>
       <c r="L53" s="2"/>
-      <c r="M53" s="2"/>
-      <c r="N53" s="2"/>
+      <c r="M53" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N53" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="O53" s="2"/>
       <c r="P53" s="2"/>
       <c r="Q53" s="4"/>
       <c r="R53" s="4"/>
       <c r="S53" s="2"/>
-      <c r="T53" s="5" t="s">
-        <v>165</v>
-      </c>
+      <c r="T53" s="5"/>
     </row>
     <row r="54" spans="1:20">
       <c r="A54">
-        <v>881</v>
+        <v>883</v>
       </c>
       <c r="B54" s="1">
-        <v>46285.571921296301</v>
+        <v>46285.621018518497</v>
       </c>
       <c r="C54" s="1">
-        <v>46285.572222222203</v>
+        <v>46285.621180555601</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>166</v>
+        <v>130</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>167</v>
+        <v>131</v>
       </c>
       <c r="F54">
-        <v>38561</v>
+        <v>38401</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>33</v>
@@ -3877,67 +3716,65 @@
       <c r="R54" s="4"/>
       <c r="S54" s="2"/>
       <c r="T54" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:20">
       <c r="A55">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="B55" s="1">
-        <v>46285.572731481501</v>
+        <v>46285.638113425899</v>
       </c>
       <c r="C55" s="1">
-        <v>46285.574131944399</v>
+        <v>46285.638946759304</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>170</v>
-      </c>
       <c r="F55">
-        <v>38368</v>
+        <v>38992</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H55" s="2"/>
       <c r="I55" s="2"/>
       <c r="J55" s="2"/>
       <c r="K55" s="2"/>
       <c r="L55" s="2"/>
-      <c r="M55" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="N55" s="2" t="s">
-        <v>171</v>
-      </c>
+      <c r="M55" s="2"/>
+      <c r="N55" s="2"/>
       <c r="O55" s="2"/>
       <c r="P55" s="2"/>
       <c r="Q55" s="4"/>
       <c r="R55" s="4"/>
       <c r="S55" s="2"/>
-      <c r="T55" s="5"/>
+      <c r="T55" s="5" t="s">
+        <v>170</v>
+      </c>
     </row>
     <row r="56" spans="1:20">
       <c r="A56">
-        <v>883</v>
+        <v>885</v>
       </c>
       <c r="B56" s="1">
-        <v>46285.621018518497</v>
+        <v>46285.662870370397</v>
       </c>
       <c r="C56" s="1">
-        <v>46285.621180555601</v>
+        <v>46285.663576388899</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>130</v>
+        <v>27</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>131</v>
+        <v>28</v>
       </c>
       <c r="F56">
-        <v>38401</v>
+        <v>38529</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>33</v>
@@ -3955,27 +3792,27 @@
       <c r="R56" s="4"/>
       <c r="S56" s="2"/>
       <c r="T56" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="57" spans="1:20">
       <c r="A57">
-        <v>884</v>
+        <v>886</v>
       </c>
       <c r="B57" s="1">
-        <v>46285.638113425899</v>
+        <v>46285.669421296298</v>
       </c>
       <c r="C57" s="1">
-        <v>46285.638946759304</v>
+        <v>46285.670185185198</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="F57">
-        <v>38992</v>
+        <v>38695</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>33</v>
@@ -3993,27 +3830,27 @@
       <c r="R57" s="4"/>
       <c r="S57" s="2"/>
       <c r="T57" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="58" spans="1:20">
       <c r="A58">
-        <v>885</v>
+        <v>887</v>
       </c>
       <c r="B58" s="1">
-        <v>46285.662870370397</v>
+        <v>46285.688738425903</v>
       </c>
       <c r="C58" s="1">
-        <v>46285.663576388899</v>
+        <v>46285.689282407402</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>27</v>
+        <v>164</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>28</v>
+        <v>165</v>
       </c>
       <c r="F58">
-        <v>38529</v>
+        <v>38368</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>33</v>
@@ -4031,27 +3868,27 @@
       <c r="R58" s="4"/>
       <c r="S58" s="2"/>
       <c r="T58" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="59" spans="1:20">
       <c r="A59">
-        <v>886</v>
+        <v>888</v>
       </c>
       <c r="B59" s="1">
-        <v>46285.669421296298</v>
+        <v>46285.715972222199</v>
       </c>
       <c r="C59" s="1">
-        <v>46285.670185185198</v>
+        <v>46285.7163194444</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>178</v>
-      </c>
       <c r="F59">
-        <v>38695</v>
+        <v>43130</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>33</v>
@@ -4069,27 +3906,27 @@
       <c r="R59" s="4"/>
       <c r="S59" s="2"/>
       <c r="T59" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="60" spans="1:20">
       <c r="A60">
-        <v>887</v>
+        <v>889</v>
       </c>
       <c r="B60" s="1">
-        <v>46285.688738425903</v>
+        <v>46285.716342592597</v>
       </c>
       <c r="C60" s="1">
-        <v>46285.689282407402</v>
+        <v>46285.718784722201</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>169</v>
+        <v>179</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>170</v>
+        <v>180</v>
       </c>
       <c r="F60">
-        <v>38368</v>
+        <v>38363</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>33</v>
@@ -4107,27 +3944,27 @@
       <c r="R60" s="4"/>
       <c r="S60" s="2"/>
       <c r="T60" s="5" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="61" spans="1:20">
       <c r="A61">
-        <v>888</v>
+        <v>890</v>
       </c>
       <c r="B61" s="1">
-        <v>46285.715972222199</v>
+        <v>46285.697152777801</v>
       </c>
       <c r="C61" s="1">
-        <v>46285.7163194444</v>
+        <v>46285.725115740701</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F61">
-        <v>43130</v>
+        <v>38604</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>33</v>
@@ -4145,27 +3982,27 @@
       <c r="R61" s="4"/>
       <c r="S61" s="2"/>
       <c r="T61" s="5" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
     </row>
     <row r="62" spans="1:20">
       <c r="A62">
-        <v>889</v>
+        <v>891</v>
       </c>
       <c r="B62" s="1">
-        <v>46285.716342592597</v>
+        <v>46285.727719907401</v>
       </c>
       <c r="C62" s="1">
-        <v>46285.718784722201</v>
+        <v>46285.732407407399</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>184</v>
+        <v>103</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>185</v>
+        <v>104</v>
       </c>
       <c r="F62">
-        <v>38363</v>
+        <v>38515</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>33</v>
@@ -4183,27 +4020,27 @@
       <c r="R62" s="4"/>
       <c r="S62" s="2"/>
       <c r="T62" s="5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:20">
       <c r="A63">
-        <v>890</v>
+        <v>892</v>
       </c>
       <c r="B63" s="1">
-        <v>46285.697152777801</v>
+        <v>46285.737418981502</v>
       </c>
       <c r="C63" s="1">
-        <v>46285.725115740701</v>
+        <v>46285.740914351903</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>187</v>
+        <v>84</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>188</v>
+        <v>85</v>
       </c>
       <c r="F63">
-        <v>38604</v>
+        <v>38333</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>33</v>
@@ -4221,27 +4058,27 @@
       <c r="R63" s="4"/>
       <c r="S63" s="2"/>
       <c r="T63" s="5" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="64" spans="1:20">
       <c r="A64">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="B64" s="1">
-        <v>46285.727719907401</v>
+        <v>46285.757152777798</v>
       </c>
       <c r="C64" s="1">
-        <v>46285.732407407399</v>
+        <v>46285.7577199074</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>103</v>
+        <v>187</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>104</v>
+        <v>188</v>
       </c>
       <c r="F64">
-        <v>38515</v>
+        <v>38143</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>33</v>
@@ -4259,18 +4096,18 @@
       <c r="R64" s="4"/>
       <c r="S64" s="2"/>
       <c r="T64" s="5" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="65" spans="1:21">
       <c r="A65">
-        <v>892</v>
+        <v>895</v>
       </c>
       <c r="B65" s="1">
-        <v>46285.737418981502</v>
+        <v>46285.756018518499</v>
       </c>
       <c r="C65" s="1">
-        <v>46285.740914351903</v>
+        <v>46285.758657407401</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>84</v>
@@ -4282,7 +4119,7 @@
         <v>38333</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
       <c r="H65" s="2"/>
       <c r="I65" s="2"/>
@@ -4296,19 +4133,20 @@
       <c r="Q65" s="4"/>
       <c r="R65" s="4"/>
       <c r="S65" s="2"/>
-      <c r="T65" s="5" t="s">
+      <c r="T65" s="5"/>
+      <c r="U65" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="66" spans="1:21">
       <c r="A66">
-        <v>893</v>
+        <v>896</v>
       </c>
       <c r="B66" s="1">
-        <v>46285.753125000003</v>
+        <v>46285.776655092603</v>
       </c>
       <c r="C66" s="1">
-        <v>46285.754803240699</v>
+        <v>46285.777777777803</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>192</v>
@@ -4317,18 +4155,16 @@
         <v>193</v>
       </c>
       <c r="F66">
-        <v>38511</v>
+        <v>43070</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="H66" s="2"/>
       <c r="I66" s="2"/>
       <c r="J66" s="2"/>
       <c r="K66" s="2"/>
-      <c r="L66" s="2" t="s">
-        <v>194</v>
-      </c>
+      <c r="L66" s="2"/>
       <c r="M66" s="2"/>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -4336,29 +4172,31 @@
       <c r="Q66" s="4"/>
       <c r="R66" s="4"/>
       <c r="S66" s="2"/>
-      <c r="T66" s="5"/>
+      <c r="T66" s="5" t="s">
+        <v>194</v>
+      </c>
     </row>
     <row r="67" spans="1:21">
       <c r="A67">
-        <v>894</v>
+        <v>897</v>
       </c>
       <c r="B67" s="1">
-        <v>46285.757152777798</v>
+        <v>46285.803402777798</v>
       </c>
       <c r="C67" s="1">
-        <v>46285.7577199074</v>
+        <v>46285.8035648148</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>195</v>
+        <v>56</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>196</v>
+        <v>57</v>
       </c>
       <c r="F67">
-        <v>38143</v>
+        <v>38862</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>33</v>
+        <v>190</v>
       </c>
       <c r="H67" s="2"/>
       <c r="I67" s="2"/>
@@ -4372,31 +4210,32 @@
       <c r="Q67" s="4"/>
       <c r="R67" s="4"/>
       <c r="S67" s="2"/>
-      <c r="T67" s="5" t="s">
-        <v>197</v>
+      <c r="T67" s="5"/>
+      <c r="U67" t="s">
+        <v>195</v>
       </c>
     </row>
     <row r="68" spans="1:21">
       <c r="A68">
-        <v>895</v>
+        <v>898</v>
       </c>
       <c r="B68" s="1">
-        <v>46285.756018518499</v>
+        <v>46285.804432870398</v>
       </c>
       <c r="C68" s="1">
-        <v>46285.758657407401</v>
+        <v>46285.8059490741</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>84</v>
+        <v>196</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>85</v>
+        <v>197</v>
       </c>
       <c r="F68">
-        <v>38333</v>
+        <v>38339</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="H68" s="2"/>
       <c r="I68" s="2"/>
@@ -4410,29 +4249,28 @@
       <c r="Q68" s="4"/>
       <c r="R68" s="4"/>
       <c r="S68" s="2"/>
-      <c r="T68" s="5"/>
-      <c r="U68" t="s">
-        <v>199</v>
+      <c r="T68" s="5" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="69" spans="1:21">
       <c r="A69">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B69" s="1">
-        <v>46285.776655092603</v>
+        <v>46285.839664351799</v>
       </c>
       <c r="C69" s="1">
-        <v>46285.777777777803</v>
+        <v>46285.84</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>200</v>
+        <v>112</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>201</v>
+        <v>113</v>
       </c>
       <c r="F69">
-        <v>43070</v>
+        <v>38656</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>33</v>
@@ -4450,30 +4288,30 @@
       <c r="R69" s="4"/>
       <c r="S69" s="2"/>
       <c r="T69" s="5" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
     </row>
     <row r="70" spans="1:21">
       <c r="A70">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="B70" s="1">
-        <v>46285.803402777798</v>
+        <v>46285.849097222199</v>
       </c>
       <c r="C70" s="1">
-        <v>46285.8035648148</v>
+        <v>46285.849733796298</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>56</v>
+        <v>200</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>57</v>
+        <v>201</v>
       </c>
       <c r="F70">
-        <v>38862</v>
+        <v>38456</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="H70" s="2"/>
       <c r="I70" s="2"/>
@@ -4487,29 +4325,28 @@
       <c r="Q70" s="4"/>
       <c r="R70" s="4"/>
       <c r="S70" s="2"/>
-      <c r="T70" s="5"/>
-      <c r="U70" t="s">
-        <v>203</v>
+      <c r="T70" s="5" t="s">
+        <v>202</v>
       </c>
     </row>
     <row r="71" spans="1:21">
       <c r="A71">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B71" s="1">
-        <v>46285.804432870398</v>
+        <v>46285.860462962999</v>
       </c>
       <c r="C71" s="1">
-        <v>46285.8059490741</v>
+        <v>46285.861203703702</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="F71">
-        <v>38339</v>
+        <v>38894</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>33</v>
@@ -4527,38 +4364,36 @@
       <c r="R71" s="4"/>
       <c r="S71" s="2"/>
       <c r="T71" s="5" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="72" spans="1:21">
       <c r="A72">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="B72" s="1">
-        <v>46285.818182870396</v>
+        <v>46285.870069444398</v>
       </c>
       <c r="C72" s="1">
-        <v>46285.818715277797</v>
+        <v>46285.870717592603</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>208</v>
-      </c>
       <c r="F72">
-        <v>38351</v>
+        <v>43193</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="H72" s="2"/>
       <c r="I72" s="2"/>
       <c r="J72" s="2"/>
       <c r="K72" s="2"/>
-      <c r="L72" s="2" t="s">
-        <v>209</v>
-      </c>
+      <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -4566,26 +4401,28 @@
       <c r="Q72" s="4"/>
       <c r="R72" s="4"/>
       <c r="S72" s="2"/>
-      <c r="T72" s="5"/>
+      <c r="T72" s="5" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="73" spans="1:21">
       <c r="A73">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B73" s="1">
-        <v>46285.839664351799</v>
+        <v>46285.902222222197</v>
       </c>
       <c r="C73" s="1">
-        <v>46285.84</v>
+        <v>46285.902743055602</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>112</v>
+        <v>209</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>113</v>
+        <v>210</v>
       </c>
       <c r="F73">
-        <v>38656</v>
+        <v>38176</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>33</v>
@@ -4603,30 +4440,30 @@
       <c r="R73" s="4"/>
       <c r="S73" s="2"/>
       <c r="T73" s="5" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
     </row>
     <row r="74" spans="1:21">
       <c r="A74">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="B74" s="1">
-        <v>46285.849097222199</v>
+        <v>46285.903032407397</v>
       </c>
       <c r="C74" s="1">
-        <v>46285.849733796298</v>
+        <v>46285.908125000002</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F74">
-        <v>38456</v>
+        <v>38176</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="H74" s="2"/>
       <c r="I74" s="2"/>
@@ -4637,31 +4474,35 @@
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
       <c r="P74" s="2"/>
-      <c r="Q74" s="4"/>
-      <c r="R74" s="4"/>
-      <c r="S74" s="2"/>
-      <c r="T74" s="5" t="s">
-        <v>213</v>
-      </c>
+      <c r="Q74" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R74" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S74" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="T74" s="5"/>
     </row>
     <row r="75" spans="1:21">
       <c r="A75">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B75" s="1">
-        <v>46285.860462962999</v>
+        <v>46285.883113425902</v>
       </c>
       <c r="C75" s="1">
-        <v>46285.861203703702</v>
+        <v>46285.955520833297</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="F75">
-        <v>38894</v>
+        <v>43152</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>33</v>
@@ -4679,27 +4520,27 @@
       <c r="R75" s="4"/>
       <c r="S75" s="2"/>
       <c r="T75" s="5" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="76" spans="1:21">
       <c r="A76">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="B76" s="1">
-        <v>46285.870069444398</v>
+        <v>46285.965312499997</v>
       </c>
       <c r="C76" s="1">
-        <v>46285.870717592603</v>
+        <v>46285.968553240702</v>
       </c>
       <c r="D76" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>218</v>
-      </c>
       <c r="F76">
-        <v>43193</v>
+        <v>38460</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>33</v>
@@ -4717,27 +4558,27 @@
       <c r="R76" s="4"/>
       <c r="S76" s="2"/>
       <c r="T76" s="5" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
     </row>
     <row r="77" spans="1:21">
       <c r="A77">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B77" s="1">
-        <v>46285.902222222197</v>
+        <v>46285.9909259259</v>
       </c>
       <c r="C77" s="1">
-        <v>46285.902743055602</v>
+        <v>46285.991226851896</v>
       </c>
       <c r="D77" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="F77">
-        <v>38176</v>
+        <v>38930</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>33</v>
@@ -4755,30 +4596,30 @@
       <c r="R77" s="4"/>
       <c r="S77" s="2"/>
       <c r="T77" s="5" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="78" spans="1:21">
       <c r="A78">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="B78" s="1">
-        <v>46285.903032407397</v>
+        <v>46286.250625000001</v>
       </c>
       <c r="C78" s="1">
-        <v>46285.908125000002</v>
+        <v>46286.252256944397</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="F78">
-        <v>38176</v>
+        <v>38845</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="H78" s="2"/>
       <c r="I78" s="2"/>
@@ -4789,35 +4630,31 @@
       <c r="N78" s="2"/>
       <c r="O78" s="2"/>
       <c r="P78" s="2"/>
-      <c r="Q78" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="R78" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="S78" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="T78" s="5"/>
+      <c r="Q78" s="4"/>
+      <c r="R78" s="4"/>
+      <c r="S78" s="2"/>
+      <c r="T78" s="5" t="s">
+        <v>224</v>
+      </c>
     </row>
     <row r="79" spans="1:21">
       <c r="A79">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B79" s="1">
-        <v>46285.883113425902</v>
+        <v>46286.264837962997</v>
       </c>
       <c r="C79" s="1">
-        <v>46285.955520833297</v>
+        <v>46286.265972222202</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F79">
-        <v>43152</v>
+        <v>38374</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>33</v>
@@ -4835,30 +4672,30 @@
       <c r="R79" s="4"/>
       <c r="S79" s="2"/>
       <c r="T79" s="5" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
     </row>
     <row r="80" spans="1:21">
       <c r="A80">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="B80" s="1">
-        <v>46285.965312499997</v>
+        <v>46286.315277777801</v>
       </c>
       <c r="C80" s="1">
-        <v>46285.968553240702</v>
+        <v>46286.317291666703</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>227</v>
+        <v>172</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>228</v>
+        <v>173</v>
       </c>
       <c r="F80">
-        <v>38460</v>
+        <v>38695</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="H80" s="2"/>
       <c r="I80" s="2"/>
@@ -4867,40 +4704,42 @@
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
       <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
+      <c r="O80" s="2" t="s">
+        <v>228</v>
+      </c>
       <c r="P80" s="2"/>
       <c r="Q80" s="4"/>
       <c r="R80" s="4"/>
       <c r="S80" s="2"/>
-      <c r="T80" s="5" t="s">
-        <v>229</v>
-      </c>
+      <c r="T80" s="5"/>
     </row>
     <row r="81" spans="1:20">
       <c r="A81">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B81" s="1">
-        <v>46285.9909259259</v>
+        <v>46286.342835648102</v>
       </c>
       <c r="C81" s="1">
-        <v>46285.991226851896</v>
+        <v>46286.3452777778</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>230</v>
+        <v>115</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>231</v>
+        <v>116</v>
       </c>
       <c r="F81">
-        <v>38930</v>
+        <v>38770</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="H81" s="2"/>
       <c r="I81" s="2"/>
-      <c r="J81" s="2"/>
+      <c r="J81" s="2" t="s">
+        <v>229</v>
+      </c>
       <c r="K81" s="2"/>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
@@ -4910,31 +4749,29 @@
       <c r="Q81" s="4"/>
       <c r="R81" s="4"/>
       <c r="S81" s="2"/>
-      <c r="T81" s="5" t="s">
-        <v>232</v>
-      </c>
+      <c r="T81" s="5"/>
     </row>
     <row r="82" spans="1:20">
       <c r="A82">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="B82" s="1">
-        <v>46286.250625000001</v>
+        <v>46286.345578703702</v>
       </c>
       <c r="C82" s="1">
-        <v>46286.252256944397</v>
+        <v>46286.349328703698</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>233</v>
+        <v>115</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>234</v>
+        <v>116</v>
       </c>
       <c r="F82">
-        <v>38845</v>
+        <v>38770</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>33</v>
+        <v>87</v>
       </c>
       <c r="H82" s="2"/>
       <c r="I82" s="2"/>
@@ -4945,38 +4782,44 @@
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
       <c r="P82" s="2"/>
-      <c r="Q82" s="4"/>
-      <c r="R82" s="4"/>
-      <c r="S82" s="2"/>
-      <c r="T82" s="5" t="s">
-        <v>235</v>
-      </c>
+      <c r="Q82" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R82" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S82" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="T82" s="5"/>
     </row>
     <row r="83" spans="1:20">
       <c r="A83">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B83" s="1">
-        <v>46286.264837962997</v>
+        <v>46286.439895833297</v>
       </c>
       <c r="C83" s="1">
-        <v>46286.265972222202</v>
+        <v>46286.440069444398</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>236</v>
+        <v>172</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>237</v>
+        <v>173</v>
       </c>
       <c r="F83">
-        <v>38374</v>
+        <v>38695</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="H83" s="2"/>
       <c r="I83" s="2"/>
-      <c r="J83" s="2"/>
+      <c r="J83" s="2" t="s">
+        <v>231</v>
+      </c>
       <c r="K83" s="2"/>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
@@ -4986,42 +4829,42 @@
       <c r="Q83" s="4"/>
       <c r="R83" s="4"/>
       <c r="S83" s="2"/>
-      <c r="T83" s="5" t="s">
-        <v>238</v>
-      </c>
+      <c r="T83" s="5"/>
     </row>
     <row r="84" spans="1:20">
       <c r="A84">
-        <v>911</v>
+        <v>916</v>
       </c>
       <c r="B84" s="1">
-        <v>46286.315277777801</v>
+        <v>46286.449942129599</v>
       </c>
       <c r="C84" s="1">
-        <v>46286.317291666703</v>
+        <v>46286.450671296298</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>177</v>
+        <v>232</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>178</v>
+        <v>233</v>
       </c>
       <c r="F84">
-        <v>38695</v>
+        <v>38800</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>70</v>
+        <v>29</v>
       </c>
       <c r="H84" s="2"/>
       <c r="I84" s="2"/>
       <c r="J84" s="2"/>
       <c r="K84" s="2"/>
       <c r="L84" s="2"/>
-      <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2" t="s">
-        <v>239</v>
-      </c>
+      <c r="M84" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N84" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="O84" s="2"/>
       <c r="P84" s="2"/>
       <c r="Q84" s="4"/>
       <c r="R84" s="4"/>
@@ -5030,30 +4873,30 @@
     </row>
     <row r="85" spans="1:20">
       <c r="A85">
-        <v>912</v>
+        <v>918</v>
       </c>
       <c r="B85" s="1">
-        <v>46286.342835648102</v>
+        <v>46286.4628240741</v>
       </c>
       <c r="C85" s="1">
-        <v>46286.3452777778</v>
+        <v>46286.469953703701</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>116</v>
+        <v>236</v>
       </c>
       <c r="F85">
-        <v>38770</v>
+        <v>38502</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="H85" s="2"/>
       <c r="I85" s="2"/>
       <c r="J85" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="K85" s="2"/>
       <c r="L85" s="2"/>
@@ -5068,78 +4911,74 @@
     </row>
     <row r="86" spans="1:20">
       <c r="A86">
-        <v>913</v>
+        <v>919</v>
       </c>
       <c r="B86" s="1">
-        <v>46286.345578703702</v>
+        <v>46286.470115740703</v>
       </c>
       <c r="C86" s="1">
-        <v>46286.349328703698</v>
+        <v>46286.4706365741</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>116</v>
+        <v>236</v>
       </c>
       <c r="F86">
-        <v>38770</v>
+        <v>38502</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>87</v>
+        <v>25</v>
       </c>
       <c r="H86" s="2"/>
       <c r="I86" s="2"/>
       <c r="J86" s="2"/>
-      <c r="K86" s="2"/>
+      <c r="K86" s="2" t="s">
+        <v>238</v>
+      </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
       <c r="P86" s="2"/>
-      <c r="Q86" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="R86" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="S86" s="2" t="s">
-        <v>241</v>
-      </c>
+      <c r="Q86" s="4"/>
+      <c r="R86" s="4"/>
+      <c r="S86" s="2"/>
       <c r="T86" s="5"/>
     </row>
     <row r="87" spans="1:20">
       <c r="A87">
-        <v>914</v>
+        <v>922</v>
       </c>
       <c r="B87" s="1">
-        <v>46286.439895833297</v>
+        <v>46286.473715277803</v>
       </c>
       <c r="C87" s="1">
-        <v>46286.440069444398</v>
+        <v>46286.476759259298</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>177</v>
+        <v>235</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>178</v>
+        <v>236</v>
       </c>
       <c r="F87">
-        <v>38695</v>
+        <v>38502</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>148</v>
+        <v>70</v>
       </c>
       <c r="H87" s="2"/>
       <c r="I87" s="2"/>
-      <c r="J87" s="2" t="s">
-        <v>242</v>
-      </c>
+      <c r="J87" s="2"/>
       <c r="K87" s="2"/>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
       <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
+      <c r="O87" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="P87" s="2"/>
       <c r="Q87" s="4"/>
       <c r="R87" s="4"/>
@@ -5148,111 +4987,115 @@
     </row>
     <row r="88" spans="1:20">
       <c r="A88">
-        <v>915</v>
+        <v>923</v>
       </c>
       <c r="B88" s="1">
-        <v>46286.4461226852</v>
+        <v>46286.476898148103</v>
       </c>
       <c r="C88" s="1">
-        <v>46286.446469907401</v>
+        <v>46286.478599536997</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>207</v>
+        <v>235</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>208</v>
+        <v>236</v>
       </c>
       <c r="F88">
-        <v>38351</v>
+        <v>38502</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="H88" s="2"/>
       <c r="I88" s="2"/>
       <c r="J88" s="2"/>
       <c r="K88" s="2"/>
-      <c r="L88" s="2" t="s">
-        <v>243</v>
-      </c>
+      <c r="L88" s="2"/>
       <c r="M88" s="2"/>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
       <c r="P88" s="2"/>
-      <c r="Q88" s="4"/>
-      <c r="R88" s="4"/>
-      <c r="S88" s="2"/>
+      <c r="Q88" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R88" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S88" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="T88" s="5"/>
     </row>
     <row r="89" spans="1:20">
       <c r="A89">
-        <v>916</v>
+        <v>924</v>
       </c>
       <c r="B89" s="1">
-        <v>46286.449942129599</v>
+        <v>46286.482465277797</v>
       </c>
       <c r="C89" s="1">
-        <v>46286.450671296298</v>
+        <v>46286.484652777799</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F89">
-        <v>38800</v>
+        <v>38859</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="H89" s="2"/>
       <c r="I89" s="2"/>
       <c r="J89" s="2"/>
       <c r="K89" s="2"/>
       <c r="L89" s="2"/>
-      <c r="M89" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="N89" s="2" t="s">
-        <v>246</v>
-      </c>
+      <c r="M89" s="2"/>
+      <c r="N89" s="2"/>
       <c r="O89" s="2"/>
       <c r="P89" s="2"/>
       <c r="Q89" s="4"/>
       <c r="R89" s="4"/>
       <c r="S89" s="2"/>
-      <c r="T89" s="5"/>
+      <c r="T89" s="5" t="s">
+        <v>243</v>
+      </c>
     </row>
     <row r="90" spans="1:20">
       <c r="A90">
-        <v>917</v>
+        <v>926</v>
       </c>
       <c r="B90" s="1">
-        <v>46286.457835648202</v>
+        <v>46286.488402777803</v>
       </c>
       <c r="C90" s="1">
-        <v>46286.460810185199</v>
+        <v>46286.489004629599</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>247</v>
+        <v>192</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>248</v>
+        <v>193</v>
       </c>
       <c r="F90">
-        <v>43169</v>
+        <v>43070</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H90" s="2"/>
-      <c r="I90" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="H90" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I90" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="J90" s="2"/>
       <c r="K90" s="2"/>
-      <c r="L90" s="2" t="s">
-        <v>249</v>
-      </c>
+      <c r="L90" s="2"/>
       <c r="M90" s="2"/>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -5264,31 +5107,29 @@
     </row>
     <row r="91" spans="1:20">
       <c r="A91">
-        <v>918</v>
+        <v>927</v>
       </c>
       <c r="B91" s="1">
-        <v>46286.4628240741</v>
+        <v>46286.488599536999</v>
       </c>
       <c r="C91" s="1">
-        <v>46286.469953703701</v>
+        <v>46286.490428240701</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="F91">
         <v>38502</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>148</v>
+        <v>33</v>
       </c>
       <c r="H91" s="2"/>
       <c r="I91" s="2"/>
-      <c r="J91" s="2" t="s">
-        <v>252</v>
-      </c>
+      <c r="J91" s="2"/>
       <c r="K91" s="2"/>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
@@ -5298,36 +5139,38 @@
       <c r="Q91" s="4"/>
       <c r="R91" s="4"/>
       <c r="S91" s="2"/>
-      <c r="T91" s="5"/>
+      <c r="T91" s="5" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="92" spans="1:20">
       <c r="A92">
-        <v>919</v>
+        <v>928</v>
       </c>
       <c r="B92" s="1">
-        <v>46286.470115740703</v>
+        <v>46286.4908796296</v>
       </c>
       <c r="C92" s="1">
-        <v>46286.4706365741</v>
+        <v>46286.491307870398</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="F92">
-        <v>38502</v>
+        <v>43070</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>25</v>
+        <v>144</v>
       </c>
       <c r="H92" s="2"/>
       <c r="I92" s="2"/>
-      <c r="J92" s="2"/>
-      <c r="K92" s="2" t="s">
-        <v>253</v>
-      </c>
+      <c r="J92" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="K92" s="2"/>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
       <c r="N92" s="2"/>
@@ -5340,33 +5183,33 @@
     </row>
     <row r="93" spans="1:20">
       <c r="A93">
-        <v>920</v>
+        <v>929</v>
       </c>
       <c r="B93" s="1">
-        <v>46286.468009259297</v>
+        <v>46286.491527777798</v>
       </c>
       <c r="C93" s="1">
-        <v>46286.471527777801</v>
+        <v>46286.4919212963</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>254</v>
+        <v>192</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>255</v>
+        <v>193</v>
       </c>
       <c r="F93">
-        <v>38594</v>
+        <v>43070</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>138</v>
+        <v>25</v>
       </c>
       <c r="H93" s="2"/>
       <c r="I93" s="2"/>
       <c r="J93" s="2"/>
-      <c r="K93" s="2"/>
-      <c r="L93" s="2" t="s">
-        <v>256</v>
-      </c>
+      <c r="K93" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="L93" s="2"/>
       <c r="M93" s="2"/>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -5378,35 +5221,37 @@
     </row>
     <row r="94" spans="1:20">
       <c r="A94">
-        <v>921</v>
+        <v>930</v>
       </c>
       <c r="B94" s="1">
-        <v>46286.471122685201</v>
+        <v>46286.4922337963</v>
       </c>
       <c r="C94" s="1">
-        <v>46286.472835648201</v>
+        <v>46286.492511574099</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="F94">
-        <v>38502</v>
+        <v>43070</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>138</v>
+        <v>29</v>
       </c>
       <c r="H94" s="2"/>
       <c r="I94" s="2"/>
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
-      <c r="L94" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
+      <c r="L94" s="2"/>
+      <c r="M94" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N94" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="O94" s="2"/>
       <c r="P94" s="2"/>
       <c r="Q94" s="4"/>
@@ -5416,36 +5261,38 @@
     </row>
     <row r="95" spans="1:20">
       <c r="A95">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="B95" s="1">
-        <v>46286.473715277803</v>
+        <v>46286.495729166701</v>
       </c>
       <c r="C95" s="1">
-        <v>46286.476759259298</v>
+        <v>46286.497175925899</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E95" s="2" t="s">
+      <c r="F95">
+        <v>38659</v>
+      </c>
+      <c r="G95" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H95" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I95" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="F95">
-        <v>38502</v>
-      </c>
-      <c r="G95" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H95" s="2"/>
-      <c r="I95" s="2"/>
       <c r="J95" s="2"/>
       <c r="K95" s="2"/>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
       <c r="N95" s="2"/>
-      <c r="O95" s="2" t="s">
-        <v>258</v>
-      </c>
+      <c r="O95" s="2"/>
       <c r="P95" s="2"/>
       <c r="Q95" s="4"/>
       <c r="R95" s="4"/>
@@ -5454,25 +5301,25 @@
     </row>
     <row r="96" spans="1:20">
       <c r="A96">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="B96" s="1">
-        <v>46286.476898148103</v>
+        <v>46286.4929513889</v>
       </c>
       <c r="C96" s="1">
-        <v>46286.478599536997</v>
+        <v>46286.497870370396</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>251</v>
+        <v>193</v>
       </c>
       <c r="F96">
-        <v>38502</v>
+        <v>43070</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="H96" s="2"/>
       <c r="I96" s="2"/>
@@ -5481,44 +5328,42 @@
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
       <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
+      <c r="O96" s="2" t="s">
+        <v>252</v>
+      </c>
       <c r="P96" s="2"/>
-      <c r="Q96" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="R96" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="S96" s="2" t="s">
-        <v>259</v>
-      </c>
+      <c r="Q96" s="4"/>
+      <c r="R96" s="4"/>
+      <c r="S96" s="2"/>
       <c r="T96" s="5"/>
     </row>
-    <row r="97" spans="1:20">
+    <row r="97" spans="1:23">
       <c r="A97">
-        <v>924</v>
+        <v>936</v>
       </c>
       <c r="B97" s="1">
-        <v>46286.482465277797</v>
+        <v>46286.503425925897</v>
       </c>
       <c r="C97" s="1">
-        <v>46286.484652777799</v>
+        <v>46286.503865740699</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="F97">
-        <v>38859</v>
+        <v>38502</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>33</v>
+        <v>144</v>
       </c>
       <c r="H97" s="2"/>
       <c r="I97" s="2"/>
-      <c r="J97" s="2"/>
+      <c r="J97" s="2" t="s">
+        <v>253</v>
+      </c>
       <c r="K97" s="2"/>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
@@ -5528,39 +5373,35 @@
       <c r="Q97" s="4"/>
       <c r="R97" s="4"/>
       <c r="S97" s="2"/>
-      <c r="T97" s="5" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="98" spans="1:20">
+      <c r="T97" s="5"/>
+    </row>
+    <row r="98" spans="1:23">
       <c r="A98">
-        <v>925</v>
+        <v>937</v>
       </c>
       <c r="B98" s="1">
-        <v>46286.485300925902</v>
+        <v>46286.503703703696</v>
       </c>
       <c r="C98" s="1">
-        <v>46286.488240740699</v>
+        <v>46286.505370370403</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>201</v>
+        <v>255</v>
       </c>
       <c r="F98">
-        <v>43070</v>
+        <v>38129</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="H98" s="2"/>
       <c r="I98" s="2"/>
       <c r="J98" s="2"/>
       <c r="K98" s="2"/>
-      <c r="L98" s="2" t="s">
-        <v>263</v>
-      </c>
+      <c r="L98" s="2"/>
       <c r="M98" s="2"/>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -5568,74 +5409,76 @@
       <c r="Q98" s="4"/>
       <c r="R98" s="4"/>
       <c r="S98" s="2"/>
-      <c r="T98" s="5"/>
-    </row>
-    <row r="99" spans="1:20">
+      <c r="T98" s="5" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23">
       <c r="A99">
-        <v>926</v>
+        <v>938</v>
       </c>
       <c r="B99" s="1">
-        <v>46286.488402777803</v>
+        <v>46286.501562500001</v>
       </c>
       <c r="C99" s="1">
-        <v>46286.489004629599</v>
+        <v>46286.505509259303</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="F99">
         <v>43070</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I99" s="2" t="s">
-        <v>264</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
       <c r="J99" s="2"/>
       <c r="K99" s="2"/>
       <c r="L99" s="2"/>
       <c r="M99" s="2"/>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
-      <c r="P99" s="2"/>
+      <c r="P99" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="Q99" s="4"/>
       <c r="R99" s="4"/>
       <c r="S99" s="2"/>
       <c r="T99" s="5"/>
     </row>
-    <row r="100" spans="1:20">
+    <row r="100" spans="1:23">
       <c r="A100">
-        <v>927</v>
+        <v>939</v>
       </c>
       <c r="B100" s="1">
-        <v>46286.488599536999</v>
+        <v>46286.505266203698</v>
       </c>
       <c r="C100" s="1">
-        <v>46286.490428240701</v>
+        <v>46286.505532407398</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="F100">
         <v>38502</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="H100" s="2"/>
       <c r="I100" s="2"/>
       <c r="J100" s="2"/>
-      <c r="K100" s="2"/>
+      <c r="K100" s="2" t="s">
+        <v>258</v>
+      </c>
       <c r="L100" s="2"/>
       <c r="M100" s="2"/>
       <c r="N100" s="2"/>
@@ -5644,37 +5487,33 @@
       <c r="Q100" s="4"/>
       <c r="R100" s="4"/>
       <c r="S100" s="2"/>
-      <c r="T100" s="5" t="s">
-        <v>265</v>
-      </c>
-    </row>
-    <row r="101" spans="1:20">
+      <c r="T100" s="5"/>
+    </row>
+    <row r="101" spans="1:23">
       <c r="A101">
-        <v>928</v>
+        <v>941</v>
       </c>
       <c r="B101" s="1">
-        <v>46286.4908796296</v>
+        <v>46286.505636574097</v>
       </c>
       <c r="C101" s="1">
-        <v>46286.491307870398</v>
+        <v>46286.5062384259</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>200</v>
+        <v>254</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>201</v>
+        <v>255</v>
       </c>
       <c r="F101">
-        <v>43070</v>
+        <v>38129</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>148</v>
+        <v>33</v>
       </c>
       <c r="H101" s="2"/>
       <c r="I101" s="2"/>
-      <c r="J101" s="2" t="s">
-        <v>266</v>
-      </c>
+      <c r="J101" s="2"/>
       <c r="K101" s="2"/>
       <c r="L101" s="2"/>
       <c r="M101" s="2"/>
@@ -5684,190 +5523,194 @@
       <c r="Q101" s="4"/>
       <c r="R101" s="4"/>
       <c r="S101" s="2"/>
-      <c r="T101" s="5"/>
-    </row>
-    <row r="102" spans="1:20">
+      <c r="T101" s="5" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="102" spans="1:23">
       <c r="A102">
-        <v>929</v>
+        <v>942</v>
       </c>
       <c r="B102" s="1">
-        <v>46286.491527777798</v>
+        <v>46286.506018518499</v>
       </c>
       <c r="C102" s="1">
-        <v>46286.4919212963</v>
+        <v>46286.5062847222</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="F102">
-        <v>43070</v>
+        <v>38502</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>25</v>
+        <v>70</v>
       </c>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
       <c r="J102" s="2"/>
-      <c r="K102" s="2" t="s">
-        <v>267</v>
-      </c>
+      <c r="K102" s="2"/>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
       <c r="N102" s="2"/>
-      <c r="O102" s="2"/>
+      <c r="O102" s="2" t="s">
+        <v>260</v>
+      </c>
       <c r="P102" s="2"/>
       <c r="Q102" s="4"/>
       <c r="R102" s="4"/>
       <c r="S102" s="2"/>
       <c r="T102" s="5"/>
     </row>
-    <row r="103" spans="1:20">
+    <row r="103" spans="1:23">
       <c r="A103">
-        <v>930</v>
+        <v>943</v>
       </c>
       <c r="B103" s="1">
-        <v>46286.4922337963</v>
+        <v>46286.506365740701</v>
       </c>
       <c r="C103" s="1">
-        <v>46286.492511574099</v>
+        <v>46286.508009259298</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>200</v>
+        <v>235</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>201</v>
+        <v>236</v>
       </c>
       <c r="F103">
-        <v>43070</v>
+        <v>38502</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>29</v>
+        <v>75</v>
       </c>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2"/>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
-      <c r="M103" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="N103" s="2" t="s">
-        <v>268</v>
-      </c>
+      <c r="M103" s="2"/>
+      <c r="N103" s="2"/>
       <c r="O103" s="2"/>
-      <c r="P103" s="2"/>
+      <c r="P103" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="Q103" s="4"/>
       <c r="R103" s="4"/>
       <c r="S103" s="2"/>
       <c r="T103" s="5"/>
     </row>
-    <row r="104" spans="1:20">
+    <row r="104" spans="1:23">
       <c r="A104">
-        <v>931</v>
+        <v>944</v>
       </c>
       <c r="B104" s="1">
-        <v>46286.487812500003</v>
+        <v>46286.506435185198</v>
       </c>
       <c r="C104" s="1">
-        <v>46286.493483796301</v>
+        <v>46286.508738425902</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>269</v>
+        <v>192</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>270</v>
+        <v>193</v>
       </c>
       <c r="F104">
-        <v>38657</v>
+        <v>43070</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
       <c r="K104" s="2"/>
-      <c r="L104" s="2" t="s">
-        <v>271</v>
-      </c>
+      <c r="L104" s="2"/>
       <c r="M104" s="2"/>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
-      <c r="Q104" s="4"/>
-      <c r="R104" s="4"/>
-      <c r="S104" s="2"/>
+      <c r="Q104" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="R104" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="S104" s="2" t="s">
+        <v>263</v>
+      </c>
       <c r="T104" s="5"/>
     </row>
-    <row r="105" spans="1:20">
+    <row r="105" spans="1:23">
       <c r="A105">
-        <v>932</v>
+        <v>945</v>
       </c>
       <c r="B105" s="1">
-        <v>46286.494513888902</v>
+        <v>46286.5081712963</v>
       </c>
       <c r="C105" s="1">
-        <v>46286.495289351798</v>
+        <v>46286.508993055599</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>272</v>
+        <v>235</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>273</v>
+        <v>236</v>
       </c>
       <c r="F105">
-        <v>38855</v>
+        <v>38502</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>138</v>
+        <v>87</v>
       </c>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
-      <c r="L105" s="2" t="s">
-        <v>274</v>
-      </c>
+      <c r="L105" s="2"/>
       <c r="M105" s="2"/>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
-      <c r="Q105" s="4"/>
-      <c r="R105" s="4"/>
-      <c r="S105" s="2"/>
+      <c r="Q105" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="R105" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="S105" s="2" t="s">
+        <v>264</v>
+      </c>
       <c r="T105" s="5"/>
     </row>
-    <row r="106" spans="1:20">
+    <row r="106" spans="1:23">
       <c r="A106">
-        <v>933</v>
+        <v>946</v>
       </c>
       <c r="B106" s="1">
-        <v>46286.495729166701</v>
+        <v>46286.509004629603</v>
       </c>
       <c r="C106" s="1">
-        <v>46286.497175925899</v>
+        <v>46286.510370370401</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>275</v>
+        <v>192</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>276</v>
+        <v>193</v>
       </c>
       <c r="F106">
-        <v>38659</v>
+        <v>43070</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H106" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I106" s="2" t="s">
-        <v>277</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2"/>
@@ -5879,28 +5722,31 @@
       <c r="R106" s="4"/>
       <c r="S106" s="2"/>
       <c r="T106" s="5"/>
-    </row>
-    <row r="107" spans="1:20">
+      <c r="U106" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="107" spans="1:23">
       <c r="A107">
-        <v>934</v>
+        <v>947</v>
       </c>
       <c r="B107" s="1">
-        <v>46286.4929513889</v>
+        <v>46286.506446759297</v>
       </c>
       <c r="C107" s="1">
-        <v>46286.497870370396</v>
+        <v>46286.510763888902</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>201</v>
+        <v>267</v>
       </c>
       <c r="F107">
-        <v>43070</v>
+        <v>38447</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
@@ -5909,44 +5755,42 @@
       <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
-      <c r="O107" s="2" t="s">
-        <v>278</v>
-      </c>
+      <c r="O107" s="2"/>
       <c r="P107" s="2"/>
       <c r="Q107" s="4"/>
       <c r="R107" s="4"/>
       <c r="S107" s="2"/>
-      <c r="T107" s="5"/>
-    </row>
-    <row r="108" spans="1:20">
+      <c r="T107" s="5" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="108" spans="1:23">
       <c r="A108">
-        <v>935</v>
+        <v>949</v>
       </c>
       <c r="B108" s="1">
-        <v>46286.494375000002</v>
+        <v>46286.510474536997</v>
       </c>
       <c r="C108" s="1">
-        <v>46286.498495370397</v>
+        <v>46286.515381944402</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>279</v>
+        <v>192</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>280</v>
+        <v>193</v>
       </c>
       <c r="F108">
-        <v>38569</v>
+        <v>43070</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="H108" s="2"/>
       <c r="I108" s="2"/>
       <c r="J108" s="2"/>
       <c r="K108" s="2"/>
-      <c r="L108" s="2" t="s">
-        <v>281</v>
-      </c>
+      <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -5955,34 +5799,42 @@
       <c r="R108" s="4"/>
       <c r="S108" s="2"/>
       <c r="T108" s="5"/>
-    </row>
-    <row r="109" spans="1:20">
+      <c r="V108" t="s">
+        <v>269</v>
+      </c>
+      <c r="W108" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="109" spans="1:23">
       <c r="A109">
-        <v>936</v>
+        <v>953</v>
       </c>
       <c r="B109" s="1">
-        <v>46286.503425925897</v>
+        <v>46286.506793981498</v>
       </c>
       <c r="C109" s="1">
-        <v>46286.503865740699</v>
+        <v>46286.520104166702</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>250</v>
+        <v>271</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>251</v>
+        <v>272</v>
       </c>
       <c r="F109">
-        <v>38502</v>
+        <v>43163</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="H109" s="2"/>
-      <c r="I109" s="2"/>
-      <c r="J109" s="2" t="s">
-        <v>282</v>
-      </c>
+        <v>141</v>
+      </c>
+      <c r="H109" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I109" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="J109" s="2"/>
       <c r="K109" s="2"/>
       <c r="L109" s="2"/>
       <c r="M109" s="2"/>
@@ -5994,24 +5846,24 @@
       <c r="S109" s="2"/>
       <c r="T109" s="5"/>
     </row>
-    <row r="110" spans="1:20">
+    <row r="110" spans="1:23">
       <c r="A110">
-        <v>937</v>
+        <v>955</v>
       </c>
       <c r="B110" s="1">
-        <v>46286.503703703696</v>
+        <v>46286.517719907402</v>
       </c>
       <c r="C110" s="1">
-        <v>46286.505370370403</v>
+        <v>46286.5221296296</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="F110">
-        <v>38129</v>
+        <v>38615</v>
       </c>
       <c r="G110" s="2" t="s">
         <v>33</v>
@@ -6029,30 +5881,30 @@
       <c r="R110" s="4"/>
       <c r="S110" s="2"/>
       <c r="T110" s="5" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="111" spans="1:20">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="111" spans="1:23">
       <c r="A111">
-        <v>938</v>
+        <v>957</v>
       </c>
       <c r="B111" s="1">
-        <v>46286.501562500001</v>
+        <v>46286.520439814798</v>
       </c>
       <c r="C111" s="1">
-        <v>46286.505509259303</v>
+        <v>46286.5242939815</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>200</v>
+        <v>277</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>201</v>
+        <v>278</v>
       </c>
       <c r="F111">
-        <v>43070</v>
+        <v>38801</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
@@ -6062,42 +5914,40 @@
       <c r="M111" s="2"/>
       <c r="N111" s="2"/>
       <c r="O111" s="2"/>
-      <c r="P111" s="2" t="s">
-        <v>286</v>
-      </c>
+      <c r="P111" s="2"/>
       <c r="Q111" s="4"/>
       <c r="R111" s="4"/>
       <c r="S111" s="2"/>
-      <c r="T111" s="5"/>
-    </row>
-    <row r="112" spans="1:20">
+      <c r="T111" s="5" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="112" spans="1:23">
       <c r="A112">
-        <v>939</v>
+        <v>958</v>
       </c>
       <c r="B112" s="1">
-        <v>46286.505266203698</v>
+        <v>46286.524942129603</v>
       </c>
       <c r="C112" s="1">
-        <v>46286.505532407398</v>
+        <v>46286.527488425898</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>250</v>
+        <v>280</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="F112">
-        <v>38502</v>
+        <v>38691</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
       <c r="J112" s="2"/>
-      <c r="K112" s="2" t="s">
-        <v>287</v>
-      </c>
+      <c r="K112" s="2"/>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
@@ -6106,37 +5956,37 @@
       <c r="Q112" s="4"/>
       <c r="R112" s="4"/>
       <c r="S112" s="2"/>
-      <c r="T112" s="5"/>
-    </row>
-    <row r="113" spans="1:23">
+      <c r="T112" s="5" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="113" spans="1:20">
       <c r="A113">
-        <v>940</v>
+        <v>960</v>
       </c>
       <c r="B113" s="1">
-        <v>46286.505682870396</v>
+        <v>46286.526423611103</v>
       </c>
       <c r="C113" s="1">
-        <v>46286.5059259259</v>
+        <v>46286.529050925899</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>250</v>
+        <v>283</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>251</v>
+        <v>284</v>
       </c>
       <c r="F113">
-        <v>38502</v>
+        <v>38107</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
       <c r="K113" s="2"/>
-      <c r="L113" s="2" t="s">
-        <v>288</v>
-      </c>
+      <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
@@ -6144,26 +5994,28 @@
       <c r="Q113" s="4"/>
       <c r="R113" s="4"/>
       <c r="S113" s="2"/>
-      <c r="T113" s="5"/>
-    </row>
-    <row r="114" spans="1:23">
+      <c r="T113" s="5" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="114" spans="1:20">
       <c r="A114">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="B114" s="1">
-        <v>46286.505636574097</v>
+        <v>46286.532395833303</v>
       </c>
       <c r="C114" s="1">
-        <v>46286.5062384259</v>
+        <v>46286.534803240698</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="F114">
-        <v>38129</v>
+        <v>38124</v>
       </c>
       <c r="G114" s="2" t="s">
         <v>33</v>
@@ -6181,68 +6033,70 @@
       <c r="R114" s="4"/>
       <c r="S114" s="2"/>
       <c r="T114" s="5" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="115" spans="1:20">
+      <c r="A115">
+        <v>962</v>
+      </c>
+      <c r="B115" s="1">
+        <v>46286.535266203697</v>
+      </c>
+      <c r="C115" s="1">
+        <v>46286.5360069444</v>
+      </c>
+      <c r="D115" s="2" t="s">
         <v>289</v>
       </c>
-    </row>
-    <row r="115" spans="1:23">
-      <c r="A115">
-        <v>942</v>
-      </c>
-      <c r="B115" s="1">
-        <v>46286.506018518499</v>
-      </c>
-      <c r="C115" s="1">
-        <v>46286.5062847222</v>
-      </c>
-      <c r="D115" s="2" t="s">
-        <v>250</v>
-      </c>
       <c r="E115" s="2" t="s">
-        <v>251</v>
+        <v>290</v>
       </c>
       <c r="F115">
-        <v>38502</v>
+        <v>38464</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H115" s="2"/>
-      <c r="I115" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="H115" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I115" s="2" t="s">
+        <v>291</v>
+      </c>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
       <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
-      <c r="O115" s="2" t="s">
-        <v>290</v>
-      </c>
+      <c r="O115" s="2"/>
       <c r="P115" s="2"/>
       <c r="Q115" s="4"/>
       <c r="R115" s="4"/>
       <c r="S115" s="2"/>
       <c r="T115" s="5"/>
     </row>
-    <row r="116" spans="1:23">
+    <row r="116" spans="1:20">
       <c r="A116">
-        <v>943</v>
+        <v>963</v>
       </c>
       <c r="B116" s="1">
-        <v>46286.506365740701</v>
+        <v>46286.512754629599</v>
       </c>
       <c r="C116" s="1">
-        <v>46286.508009259298</v>
+        <v>46286.536527777796</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>250</v>
+        <v>292</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>251</v>
+        <v>293</v>
       </c>
       <c r="F116">
-        <v>38502</v>
+        <v>38428</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>75</v>
+        <v>33</v>
       </c>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
@@ -6252,35 +6106,35 @@
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
-      <c r="P116" s="2" t="s">
-        <v>291</v>
-      </c>
+      <c r="P116" s="2"/>
       <c r="Q116" s="4"/>
       <c r="R116" s="4"/>
       <c r="S116" s="2"/>
-      <c r="T116" s="5"/>
-    </row>
-    <row r="117" spans="1:23">
+      <c r="T116" s="5" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="117" spans="1:20">
       <c r="A117">
-        <v>944</v>
+        <v>964</v>
       </c>
       <c r="B117" s="1">
-        <v>46286.506435185198</v>
+        <v>46286.539525462998</v>
       </c>
       <c r="C117" s="1">
-        <v>46286.508738425902</v>
+        <v>46286.540520833303</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>200</v>
+        <v>295</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>201</v>
+        <v>296</v>
       </c>
       <c r="F117">
-        <v>43070</v>
+        <v>38571</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
@@ -6291,38 +6145,34 @@
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" s="2"/>
-      <c r="Q117" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="R117" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="S117" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="T117" s="5"/>
-    </row>
-    <row r="118" spans="1:23">
+      <c r="Q117" s="4"/>
+      <c r="R117" s="4"/>
+      <c r="S117" s="2"/>
+      <c r="T117" s="5" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="118" spans="1:20">
       <c r="A118">
-        <v>945</v>
+        <v>965</v>
       </c>
       <c r="B118" s="1">
-        <v>46286.5081712963</v>
+        <v>46286.4847800926</v>
       </c>
       <c r="C118" s="1">
-        <v>46286.508993055599</v>
+        <v>46286.549421296302</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="F118">
-        <v>38502</v>
+        <v>38859</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
@@ -6333,38 +6183,34 @@
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" s="2"/>
-      <c r="Q118" s="4" t="s">
-        <v>88</v>
-      </c>
-      <c r="R118" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="S118" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="T118" s="5"/>
-    </row>
-    <row r="119" spans="1:23">
+      <c r="Q118" s="4"/>
+      <c r="R118" s="4"/>
+      <c r="S118" s="2"/>
+      <c r="T118" s="5" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="119" spans="1:20">
       <c r="A119">
-        <v>946</v>
+        <v>968</v>
       </c>
       <c r="B119" s="1">
-        <v>46286.509004629603</v>
+        <v>46286.556145833303</v>
       </c>
       <c r="C119" s="1">
-        <v>46286.510370370401</v>
+        <v>46286.556898148097</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>200</v>
+        <v>299</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>201</v>
+        <v>300</v>
       </c>
       <c r="F119">
-        <v>43070</v>
+        <v>38580</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>198</v>
+        <v>33</v>
       </c>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
@@ -6378,29 +6224,28 @@
       <c r="Q119" s="4"/>
       <c r="R119" s="4"/>
       <c r="S119" s="2"/>
-      <c r="T119" s="5"/>
-      <c r="U119" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="120" spans="1:23">
+      <c r="T119" s="5" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="120" spans="1:20">
       <c r="A120">
-        <v>947</v>
+        <v>969</v>
       </c>
       <c r="B120" s="1">
-        <v>46286.506446759297</v>
+        <v>46286.558020833298</v>
       </c>
       <c r="C120" s="1">
-        <v>46286.510763888902</v>
+        <v>46286.5603819444</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="F120">
-        <v>38447</v>
+        <v>43159</v>
       </c>
       <c r="G120" s="2" t="s">
         <v>33</v>
@@ -6418,38 +6263,36 @@
       <c r="R120" s="4"/>
       <c r="S120" s="2"/>
       <c r="T120" s="5" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="121" spans="1:23">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="121" spans="1:20">
       <c r="A121">
-        <v>948</v>
+        <v>970</v>
       </c>
       <c r="B121" s="1">
-        <v>46286.514178240701</v>
+        <v>46286.561041666697</v>
       </c>
       <c r="C121" s="1">
-        <v>46286.514999999999</v>
+        <v>46286.561851851897</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F121">
-        <v>38567</v>
+        <v>38116</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>138</v>
+        <v>33</v>
       </c>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
       <c r="J121" s="2"/>
       <c r="K121" s="2"/>
-      <c r="L121" s="2" t="s">
-        <v>301</v>
-      </c>
+      <c r="L121" s="2"/>
       <c r="M121" s="2"/>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -6457,949 +6300,9 @@
       <c r="Q121" s="4"/>
       <c r="R121" s="4"/>
       <c r="S121" s="2"/>
-      <c r="T121" s="5"/>
-    </row>
-    <row r="122" spans="1:23">
-      <c r="A122">
-        <v>949</v>
-      </c>
-      <c r="B122" s="1">
-        <v>46286.510474536997</v>
-      </c>
-      <c r="C122" s="1">
-        <v>46286.515381944402</v>
-      </c>
-      <c r="D122" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E122" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F122">
-        <v>43070</v>
-      </c>
-      <c r="G122" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="H122" s="2"/>
-      <c r="I122" s="2"/>
-      <c r="J122" s="2"/>
-      <c r="K122" s="2"/>
-      <c r="L122" s="2"/>
-      <c r="M122" s="2"/>
-      <c r="N122" s="2"/>
-      <c r="O122" s="2"/>
-      <c r="P122" s="2"/>
-      <c r="Q122" s="4"/>
-      <c r="R122" s="4"/>
-      <c r="S122" s="2"/>
-      <c r="T122" s="5"/>
-      <c r="V122" t="s">
-        <v>302</v>
-      </c>
-      <c r="W122" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="123" spans="1:23">
-      <c r="A123">
-        <v>950</v>
-      </c>
-      <c r="B123" s="1">
-        <v>46286.508946759299</v>
-      </c>
-      <c r="C123" s="1">
-        <v>46286.516493055598</v>
-      </c>
-      <c r="D123" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E123" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="F123">
-        <v>43026</v>
-      </c>
-      <c r="G123" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H123" s="2"/>
-      <c r="I123" s="2"/>
-      <c r="J123" s="2"/>
-      <c r="K123" s="2"/>
-      <c r="L123" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="M123" s="2"/>
-      <c r="N123" s="2"/>
-      <c r="O123" s="2"/>
-      <c r="P123" s="2"/>
-      <c r="Q123" s="4"/>
-      <c r="R123" s="4"/>
-      <c r="S123" s="2"/>
-      <c r="T123" s="5"/>
-    </row>
-    <row r="124" spans="1:23">
-      <c r="A124">
-        <v>951</v>
-      </c>
-      <c r="B124" s="1">
-        <v>46286.516319444403</v>
-      </c>
-      <c r="C124" s="1">
-        <v>46286.517048611102</v>
-      </c>
-      <c r="D124" s="2" t="s">
+      <c r="T121" s="5" t="s">
         <v>307</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F124">
-        <v>38375</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H124" s="2"/>
-      <c r="I124" s="2"/>
-      <c r="J124" s="2"/>
-      <c r="K124" s="2"/>
-      <c r="L124" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="M124" s="2"/>
-      <c r="N124" s="2"/>
-      <c r="O124" s="2"/>
-      <c r="P124" s="2"/>
-      <c r="Q124" s="4"/>
-      <c r="R124" s="4"/>
-      <c r="S124" s="2"/>
-      <c r="T124" s="5"/>
-    </row>
-    <row r="125" spans="1:23">
-      <c r="A125" s="6">
-        <v>952</v>
-      </c>
-      <c r="B125" s="1">
-        <v>46286.511018518497</v>
-      </c>
-      <c r="C125" s="1">
-        <v>46286.519918981503</v>
-      </c>
-      <c r="D125" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E125" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F125" s="6">
-        <v>38801</v>
-      </c>
-      <c r="G125" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H125" s="2"/>
-      <c r="I125" s="2"/>
-      <c r="J125" s="2"/>
-      <c r="K125" s="2"/>
-      <c r="L125" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="M125" s="2"/>
-      <c r="N125" s="2"/>
-      <c r="O125" s="2"/>
-      <c r="P125" s="2"/>
-      <c r="Q125" s="4"/>
-      <c r="R125" s="4"/>
-      <c r="S125" s="2"/>
-      <c r="T125" s="5"/>
-      <c r="U125" s="6"/>
-      <c r="V125" s="6"/>
-      <c r="W125" s="6"/>
-    </row>
-    <row r="126" spans="1:23">
-      <c r="A126" s="6">
-        <v>953</v>
-      </c>
-      <c r="B126" s="1">
-        <v>46286.506793981498</v>
-      </c>
-      <c r="C126" s="1">
-        <v>46286.520104166702</v>
-      </c>
-      <c r="D126" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E126" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="F126" s="6">
-        <v>43163</v>
-      </c>
-      <c r="G126" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H126" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I126" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="J126" s="2"/>
-      <c r="K126" s="2"/>
-      <c r="L126" s="2"/>
-      <c r="M126" s="2"/>
-      <c r="N126" s="2"/>
-      <c r="O126" s="2"/>
-      <c r="P126" s="2"/>
-      <c r="Q126" s="4"/>
-      <c r="R126" s="4"/>
-      <c r="S126" s="2"/>
-      <c r="T126" s="5"/>
-      <c r="U126" s="6"/>
-      <c r="V126" s="6"/>
-      <c r="W126" s="6"/>
-    </row>
-    <row r="127" spans="1:23">
-      <c r="A127" s="6">
-        <v>954</v>
-      </c>
-      <c r="B127" s="1">
-        <v>46286.520219907397</v>
-      </c>
-      <c r="C127" s="1">
-        <v>46286.5206481481</v>
-      </c>
-      <c r="D127" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="E127" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F127" s="6">
-        <v>43164</v>
-      </c>
-      <c r="G127" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
-      <c r="J127" s="2"/>
-      <c r="K127" s="2"/>
-      <c r="L127" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="M127" s="2"/>
-      <c r="N127" s="2"/>
-      <c r="O127" s="2"/>
-      <c r="P127" s="2"/>
-      <c r="Q127" s="4"/>
-      <c r="R127" s="4"/>
-      <c r="S127" s="2"/>
-      <c r="T127" s="5"/>
-      <c r="U127" s="6"/>
-      <c r="V127" s="6"/>
-      <c r="W127" s="6"/>
-    </row>
-    <row r="128" spans="1:23">
-      <c r="A128" s="6">
-        <v>955</v>
-      </c>
-      <c r="B128" s="1">
-        <v>46286.517719907402</v>
-      </c>
-      <c r="C128" s="1">
-        <v>46286.5221296296</v>
-      </c>
-      <c r="D128" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E128" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="F128" s="6">
-        <v>38615</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H128" s="2"/>
-      <c r="I128" s="2"/>
-      <c r="J128" s="2"/>
-      <c r="K128" s="2"/>
-      <c r="L128" s="2"/>
-      <c r="M128" s="2"/>
-      <c r="N128" s="2"/>
-      <c r="O128" s="2"/>
-      <c r="P128" s="2"/>
-      <c r="Q128" s="4"/>
-      <c r="R128" s="4"/>
-      <c r="S128" s="2"/>
-      <c r="T128" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="U128" s="6"/>
-      <c r="V128" s="6"/>
-      <c r="W128" s="6"/>
-    </row>
-    <row r="129" spans="1:23">
-      <c r="A129" s="6">
-        <v>956</v>
-      </c>
-      <c r="B129" s="1">
-        <v>46286.522499999999</v>
-      </c>
-      <c r="C129" s="1">
-        <v>46286.522916666698</v>
-      </c>
-      <c r="D129" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="E129" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="F129" s="6">
-        <v>38659</v>
-      </c>
-      <c r="G129" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H129" s="2"/>
-      <c r="I129" s="2"/>
-      <c r="J129" s="2"/>
-      <c r="K129" s="2"/>
-      <c r="L129" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="M129" s="2"/>
-      <c r="N129" s="2"/>
-      <c r="O129" s="2"/>
-      <c r="P129" s="2"/>
-      <c r="Q129" s="4"/>
-      <c r="R129" s="4"/>
-      <c r="S129" s="2"/>
-      <c r="T129" s="5"/>
-      <c r="U129" s="6"/>
-      <c r="V129" s="6"/>
-      <c r="W129" s="6"/>
-    </row>
-    <row r="130" spans="1:23">
-      <c r="A130" s="6">
-        <v>957</v>
-      </c>
-      <c r="B130" s="1">
-        <v>46286.520439814798</v>
-      </c>
-      <c r="C130" s="1">
-        <v>46286.5242939815</v>
-      </c>
-      <c r="D130" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E130" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="F130" s="6">
-        <v>38801</v>
-      </c>
-      <c r="G130" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H130" s="2"/>
-      <c r="I130" s="2"/>
-      <c r="J130" s="2"/>
-      <c r="K130" s="2"/>
-      <c r="L130" s="2"/>
-      <c r="M130" s="2"/>
-      <c r="N130" s="2"/>
-      <c r="O130" s="2"/>
-      <c r="P130" s="2"/>
-      <c r="Q130" s="4"/>
-      <c r="R130" s="4"/>
-      <c r="S130" s="2"/>
-      <c r="T130" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="U130" s="6"/>
-      <c r="V130" s="6"/>
-      <c r="W130" s="6"/>
-    </row>
-    <row r="131" spans="1:23">
-      <c r="A131" s="6">
-        <v>958</v>
-      </c>
-      <c r="B131" s="1">
-        <v>46286.524942129603</v>
-      </c>
-      <c r="C131" s="1">
-        <v>46286.527488425898</v>
-      </c>
-      <c r="D131" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E131" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F131" s="6">
-        <v>38691</v>
-      </c>
-      <c r="G131" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
-      <c r="J131" s="2"/>
-      <c r="K131" s="2"/>
-      <c r="L131" s="2"/>
-      <c r="M131" s="2"/>
-      <c r="N131" s="2"/>
-      <c r="O131" s="2"/>
-      <c r="P131" s="2"/>
-      <c r="Q131" s="4"/>
-      <c r="R131" s="4"/>
-      <c r="S131" s="2"/>
-      <c r="T131" s="5" t="s">
-        <v>324</v>
-      </c>
-      <c r="U131" s="6"/>
-      <c r="V131" s="6"/>
-      <c r="W131" s="6"/>
-    </row>
-    <row r="132" spans="1:23">
-      <c r="A132" s="6">
-        <v>959</v>
-      </c>
-      <c r="B132" s="1">
-        <v>46286.519363425898</v>
-      </c>
-      <c r="C132" s="1">
-        <v>46286.527997685203</v>
-      </c>
-      <c r="D132" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E132" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="F132" s="6">
-        <v>38718</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H132" s="2"/>
-      <c r="I132" s="2"/>
-      <c r="J132" s="2"/>
-      <c r="K132" s="2"/>
-      <c r="L132" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="M132" s="2"/>
-      <c r="N132" s="2"/>
-      <c r="O132" s="2"/>
-      <c r="P132" s="2"/>
-      <c r="Q132" s="4"/>
-      <c r="R132" s="4"/>
-      <c r="S132" s="2"/>
-      <c r="T132" s="5"/>
-      <c r="U132" s="6"/>
-      <c r="V132" s="6"/>
-      <c r="W132" s="6"/>
-    </row>
-    <row r="133" spans="1:23">
-      <c r="A133" s="6">
-        <v>960</v>
-      </c>
-      <c r="B133" s="1">
-        <v>46286.526423611103</v>
-      </c>
-      <c r="C133" s="1">
-        <v>46286.529050925899</v>
-      </c>
-      <c r="D133" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E133" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="F133" s="6">
-        <v>38107</v>
-      </c>
-      <c r="G133" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H133" s="2"/>
-      <c r="I133" s="2"/>
-      <c r="J133" s="2"/>
-      <c r="K133" s="2"/>
-      <c r="L133" s="2"/>
-      <c r="M133" s="2"/>
-      <c r="N133" s="2"/>
-      <c r="O133" s="2"/>
-      <c r="P133" s="2"/>
-      <c r="Q133" s="4"/>
-      <c r="R133" s="4"/>
-      <c r="S133" s="2"/>
-      <c r="T133" s="5" t="s">
-        <v>330</v>
-      </c>
-      <c r="U133" s="6"/>
-      <c r="V133" s="6"/>
-      <c r="W133" s="6"/>
-    </row>
-    <row r="134" spans="1:23">
-      <c r="A134" s="6">
-        <v>961</v>
-      </c>
-      <c r="B134" s="1">
-        <v>46286.532395833303</v>
-      </c>
-      <c r="C134" s="1">
-        <v>46286.534803240698</v>
-      </c>
-      <c r="D134" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E134" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F134" s="6">
-        <v>38124</v>
-      </c>
-      <c r="G134" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H134" s="2"/>
-      <c r="I134" s="2"/>
-      <c r="J134" s="2"/>
-      <c r="K134" s="2"/>
-      <c r="L134" s="2"/>
-      <c r="M134" s="2"/>
-      <c r="N134" s="2"/>
-      <c r="O134" s="2"/>
-      <c r="P134" s="2"/>
-      <c r="Q134" s="4"/>
-      <c r="R134" s="4"/>
-      <c r="S134" s="2"/>
-      <c r="T134" s="5" t="s">
-        <v>333</v>
-      </c>
-      <c r="U134" s="6"/>
-      <c r="V134" s="6"/>
-      <c r="W134" s="6"/>
-    </row>
-    <row r="135" spans="1:23">
-      <c r="A135" s="6">
-        <v>962</v>
-      </c>
-      <c r="B135" s="1">
-        <v>46286.535266203697</v>
-      </c>
-      <c r="C135" s="1">
-        <v>46286.5360069444</v>
-      </c>
-      <c r="D135" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E135" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F135" s="6">
-        <v>38464</v>
-      </c>
-      <c r="G135" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="H135" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="I135" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="J135" s="2"/>
-      <c r="K135" s="2"/>
-      <c r="L135" s="2"/>
-      <c r="M135" s="2"/>
-      <c r="N135" s="2"/>
-      <c r="O135" s="2"/>
-      <c r="P135" s="2"/>
-      <c r="Q135" s="4"/>
-      <c r="R135" s="4"/>
-      <c r="S135" s="2"/>
-      <c r="T135" s="5"/>
-      <c r="U135" s="6"/>
-      <c r="V135" s="6"/>
-      <c r="W135" s="6"/>
-    </row>
-    <row r="136" spans="1:23">
-      <c r="A136" s="6">
-        <v>963</v>
-      </c>
-      <c r="B136" s="1">
-        <v>46286.512754629599</v>
-      </c>
-      <c r="C136" s="1">
-        <v>46286.536527777796</v>
-      </c>
-      <c r="D136" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E136" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="F136" s="6">
-        <v>38428</v>
-      </c>
-      <c r="G136" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H136" s="2"/>
-      <c r="I136" s="2"/>
-      <c r="J136" s="2"/>
-      <c r="K136" s="2"/>
-      <c r="L136" s="2"/>
-      <c r="M136" s="2"/>
-      <c r="N136" s="2"/>
-      <c r="O136" s="2"/>
-      <c r="P136" s="2"/>
-      <c r="Q136" s="4"/>
-      <c r="R136" s="4"/>
-      <c r="S136" s="2"/>
-      <c r="T136" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="U136" s="6"/>
-      <c r="V136" s="6"/>
-      <c r="W136" s="6"/>
-    </row>
-    <row r="137" spans="1:23">
-      <c r="A137" s="6">
-        <v>964</v>
-      </c>
-      <c r="B137" s="1">
-        <v>46286.539525462998</v>
-      </c>
-      <c r="C137" s="1">
-        <v>46286.540520833303</v>
-      </c>
-      <c r="D137" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E137" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F137" s="6">
-        <v>38571</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H137" s="2"/>
-      <c r="I137" s="2"/>
-      <c r="J137" s="2"/>
-      <c r="K137" s="2"/>
-      <c r="L137" s="2"/>
-      <c r="M137" s="2"/>
-      <c r="N137" s="2"/>
-      <c r="O137" s="2"/>
-      <c r="P137" s="2"/>
-      <c r="Q137" s="4"/>
-      <c r="R137" s="4"/>
-      <c r="S137" s="2"/>
-      <c r="T137" s="5" t="s">
-        <v>342</v>
-      </c>
-      <c r="U137" s="6"/>
-      <c r="V137" s="6"/>
-      <c r="W137" s="6"/>
-    </row>
-    <row r="138" spans="1:23">
-      <c r="A138" s="6">
-        <v>965</v>
-      </c>
-      <c r="B138" s="1">
-        <v>46286.4847800926</v>
-      </c>
-      <c r="C138" s="1">
-        <v>46286.549421296302</v>
-      </c>
-      <c r="D138" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="E138" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F138" s="6">
-        <v>38859</v>
-      </c>
-      <c r="G138" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H138" s="2"/>
-      <c r="I138" s="2"/>
-      <c r="J138" s="2"/>
-      <c r="K138" s="2"/>
-      <c r="L138" s="2"/>
-      <c r="M138" s="2"/>
-      <c r="N138" s="2"/>
-      <c r="O138" s="2"/>
-      <c r="P138" s="2"/>
-      <c r="Q138" s="4"/>
-      <c r="R138" s="4"/>
-      <c r="S138" s="2"/>
-      <c r="T138" s="5" t="s">
-        <v>343</v>
-      </c>
-      <c r="U138" s="6"/>
-      <c r="V138" s="6"/>
-      <c r="W138" s="6"/>
-    </row>
-    <row r="139" spans="1:23">
-      <c r="A139" s="6">
-        <v>966</v>
-      </c>
-      <c r="B139" s="1">
-        <v>46286.553229166697</v>
-      </c>
-      <c r="C139" s="1">
-        <v>46286.5534259259</v>
-      </c>
-      <c r="D139" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E139" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F139" s="6">
-        <v>38496</v>
-      </c>
-      <c r="G139" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H139" s="2"/>
-      <c r="I139" s="2"/>
-      <c r="J139" s="2"/>
-      <c r="K139" s="2"/>
-      <c r="L139" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="M139" s="2"/>
-      <c r="N139" s="2"/>
-      <c r="O139" s="2"/>
-      <c r="P139" s="2"/>
-      <c r="Q139" s="4"/>
-      <c r="R139" s="4"/>
-      <c r="S139" s="2"/>
-      <c r="T139" s="5"/>
-      <c r="U139" s="6"/>
-      <c r="V139" s="6"/>
-      <c r="W139" s="6"/>
-    </row>
-    <row r="140" spans="1:23">
-      <c r="A140" s="6">
-        <v>967</v>
-      </c>
-      <c r="B140" s="1">
-        <v>46286.547881944403</v>
-      </c>
-      <c r="C140" s="1">
-        <v>46286.553715277798</v>
-      </c>
-      <c r="D140" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E140" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="F140" s="6">
-        <v>38468</v>
-      </c>
-      <c r="G140" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2"/>
-      <c r="J140" s="2"/>
-      <c r="K140" s="2"/>
-      <c r="L140" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="M140" s="2"/>
-      <c r="N140" s="2"/>
-      <c r="O140" s="2"/>
-      <c r="P140" s="2"/>
-      <c r="Q140" s="4"/>
-      <c r="R140" s="4"/>
-      <c r="S140" s="2"/>
-      <c r="T140" s="5"/>
-      <c r="U140" s="6"/>
-      <c r="V140" s="6"/>
-      <c r="W140" s="6"/>
-    </row>
-    <row r="141" spans="1:23">
-      <c r="A141" s="6">
-        <v>968</v>
-      </c>
-      <c r="B141" s="1">
-        <v>46286.556145833303</v>
-      </c>
-      <c r="C141" s="1">
-        <v>46286.556898148097</v>
-      </c>
-      <c r="D141" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E141" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F141" s="6">
-        <v>38580</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H141" s="2"/>
-      <c r="I141" s="2"/>
-      <c r="J141" s="2"/>
-      <c r="K141" s="2"/>
-      <c r="L141" s="2"/>
-      <c r="M141" s="2"/>
-      <c r="N141" s="2"/>
-      <c r="O141" s="2"/>
-      <c r="P141" s="2"/>
-      <c r="Q141" s="4"/>
-      <c r="R141" s="4"/>
-      <c r="S141" s="2"/>
-      <c r="T141" s="5" t="s">
-        <v>352</v>
-      </c>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-    </row>
-    <row r="142" spans="1:23">
-      <c r="A142" s="6">
-        <v>969</v>
-      </c>
-      <c r="B142" s="1">
-        <v>46286.558020833298</v>
-      </c>
-      <c r="C142" s="1">
-        <v>46286.5603819444</v>
-      </c>
-      <c r="D142" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E142" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F142" s="6">
-        <v>43159</v>
-      </c>
-      <c r="G142" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H142" s="2"/>
-      <c r="I142" s="2"/>
-      <c r="J142" s="2"/>
-      <c r="K142" s="2"/>
-      <c r="L142" s="2"/>
-      <c r="M142" s="2"/>
-      <c r="N142" s="2"/>
-      <c r="O142" s="2"/>
-      <c r="P142" s="2"/>
-      <c r="Q142" s="4"/>
-      <c r="R142" s="4"/>
-      <c r="S142" s="2"/>
-      <c r="T142" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="U142" s="6"/>
-      <c r="V142" s="6"/>
-      <c r="W142" s="6"/>
-    </row>
-    <row r="143" spans="1:23">
-      <c r="A143" s="6">
-        <v>970</v>
-      </c>
-      <c r="B143" s="1">
-        <v>46286.561041666697</v>
-      </c>
-      <c r="C143" s="1">
-        <v>46286.561851851897</v>
-      </c>
-      <c r="D143" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E143" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F143" s="6">
-        <v>38116</v>
-      </c>
-      <c r="G143" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H143" s="2"/>
-      <c r="I143" s="2"/>
-      <c r="J143" s="2"/>
-      <c r="K143" s="2"/>
-      <c r="L143" s="2"/>
-      <c r="M143" s="2"/>
-      <c r="N143" s="2"/>
-      <c r="O143" s="2"/>
-      <c r="P143" s="2"/>
-      <c r="Q143" s="4"/>
-      <c r="R143" s="4"/>
-      <c r="S143" s="2"/>
-      <c r="T143" s="5" t="s">
-        <v>358</v>
-      </c>
-      <c r="U143" s="6"/>
-      <c r="V143" s="6"/>
-      <c r="W143" s="6"/>
-    </row>
-    <row r="144" spans="1:23">
-      <c r="A144" s="6">
-        <v>971</v>
-      </c>
-      <c r="B144" s="1">
-        <v>46286.690682870401</v>
-      </c>
-      <c r="C144" s="1">
-        <v>46286.692245370403</v>
-      </c>
-      <c r="D144" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E144" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F144" s="6">
-        <v>38429</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="H144" s="2"/>
-      <c r="I144" s="2"/>
-      <c r="J144" s="2"/>
-      <c r="K144" s="2"/>
-      <c r="L144" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="M144" s="2"/>
-      <c r="N144" s="2"/>
-      <c r="O144" s="2"/>
-      <c r="P144" s="2"/>
-      <c r="Q144" s="4"/>
-      <c r="R144" s="4"/>
-      <c r="S144" s="2"/>
-      <c r="T144" s="5"/>
-      <c r="U144" s="6"/>
-      <c r="V144" s="6"/>
-      <c r="W144" s="6"/>
     </row>
   </sheetData>
   <hyperlinks>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3A8A40C8-1508-4E16-B871-3B361F2E865C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{63E916CA-3E37-4E88-9B5A-F207BF51EC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="371">
   <si>
     <t>Id</t>
   </si>
@@ -99,9 +99,6 @@
   </si>
   <si>
     <t>No Dona</t>
-  </si>
-  <si>
-    <t>Evidencia_Va_X_Cuenta</t>
   </si>
   <si>
     <t xml:space="preserve">Evidencia_Organizacion_Refrigeradores_Back_Antes
@@ -112,6 +109,16 @@
 </t>
   </si>
   <si>
+    <t>Cubiertos FHW</t>
+  </si>
+  <si>
+    <t>Tazas 3 Oz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Evidencia_FHW
+</t>
+  </si>
+  <si>
     <t>enrique.cesar@starbucks.com.mx</t>
   </si>
   <si>
@@ -1039,6 +1046,12 @@
     <t>Luis Eduardo Saucedo Aguilar</t>
   </si>
   <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_2994_Luis%20Eduardo%20Saucedo.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_2995_Luis%20Eduardo%20Saucedo.png</t>
+  </si>
+  <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_2996_Luis%20Eduardo%20Saucedo.png</t>
   </si>
   <si>
@@ -1076,6 +1089,69 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/LayOut_Distrital_Cesar_Alfonso_Castillo_Romer_Starbucks%20Hospital%20A%201.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38430@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Prisma Insurgentes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17904507892586859638888024589976_Starbucks%20Prisma%20Ins.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38289@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Tezontle</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17905332347338258649593852294530_Starbucks%20Tezontle.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/17905363291005096352290417547468_Starbucks%20Tezontle.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17905409283343111364720168768447_Starbucks%20Via%20515%20Ki.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/17905410261288703079577566209805_Starbucks%20Via%20515%20Ki.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17905411384285127109932030182708_Starbucks%20Via%20515%20Ki.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/1790541241117953011283015265567_Starbucks%20Via%20515%20Ki.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/17905412966355443828689864925311_Starbucks%20Via%20515%20Ki.jpg</t>
+  </si>
+  <si>
+    <t>Va X Cuenta</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/17905414969817677405354813048964_Starbucks%20Via%20515%20Ki.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38611@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Basica</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17905420290301168743671732672744_Starbucks%20Plaza%20Basi.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/1790542158367636061683927823618_Starbucks%20Plaza%20Basi.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38417@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks San José Insurgentes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_7174_Starbucks%20San%20Jos%C3%A9%20I.jpeg</t>
   </si>
 </sst>
 </file>
@@ -1111,20 +1187,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="24">
     <dxf>
-      <numFmt numFmtId="30" formatCode="@"/>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
@@ -1203,10 +1288,10 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:X181" totalsRowShown="0">
-  <autoFilter ref="A1:X181" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="24">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z197" totalsRowShown="0">
+  <autoFilter ref="A1:Z197" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="26">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -1227,150 +1312,164 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="20">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="Correo electrónico" dataDxfId="22">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="19">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Nombre" dataDxfId="21">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="18">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="CeCo" dataDxfId="20">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rb0262b9096064c5b809bdb94d2ffbed9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="17">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Selecciona la actividad que deseas registrar" dataDxfId="19">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rfa200a7d03cc4a5fa91df03bac2ecf7a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="¿ Tu Tienda Aplica para Rack FHW?" dataDxfId="16">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="¿ Tu Tienda Aplica para Rack FHW?" dataDxfId="18">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r18aa3467d7cf4ef2811cfac4f7798871"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Rack_FHW" dataDxfId="15">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Evidencia_Rack_FHW" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r722c7f4f41104c68940ef96a05bac24d"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Max&amp;Min " dataDxfId="14">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Evidencia_Max&amp;Min " dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7e20bda30db04cc2a60f0888364bbb7b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_Mandil Verde" dataDxfId="13">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Evidencia_Mandil Verde" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9b9e86be8d8a48a79e9701b423e28c21"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Lay_Out" dataDxfId="12">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Evidencia_Lay_Out" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5be890f9c9be4de4ba1736dba059b880"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="¿Cuentas con Community Board?" dataDxfId="11">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="¿Cuentas con Community Board?" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r142174aa4f64470ba655c0b540426c92"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Community_Board" dataDxfId="10">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Evidencia_Community_Board" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r31182c58e8f644128524d5583789a1ac"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Señaletica_Back" dataDxfId="9">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Evidencia_Señaletica_Back" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra7c6c4f162914976b398169c5d7ab4d9"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidencia_Señaletica_Lobby" dataDxfId="8">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Evidencia_Señaletica_Lobby" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rcc34e060c9c54a4080b7790436eec34b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Jarra Blender" dataDxfId="7">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="Jarra Blender" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r7642d63c42e645aba2602bddc67421e7"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Jarras Cold Foam" dataDxfId="6">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Jarras Cold Foam" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="redfc16b0a10e4038bc37e9db0dfd5372"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Evidencia_Jarras_Blender_&amp;_Cold_Foam" dataDxfId="5">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="Evidencia_Jarras_Blender_&amp;_Cold_Foam" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r6e195f182c384a539b6062a655e437a4"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Si Dona" dataDxfId="4">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Si Dona" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r987b34d6d2994e9a8129243b568832c1"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="No Dona" dataDxfId="3">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="No Dona" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r399ca94746e5429780f99305f61e6efe"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Evidencia_Va_X_Cuenta" dataDxfId="2">
-      <extLst>
-        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
-          <xlmsforms:question id="r91fe8e3b4efb4080a3d945974b84a687"/>
-        </ext>
-      </extLst>
-    </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Evidencia_Organizacion_Refrigeradores_Back_Antes_x000a_" dataDxfId="1">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Evidencia_Organizacion_Refrigeradores_Back_Antes_x000a_" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5e3143c71cab4402900fedf974331b74"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Evidencia_Organizacion_Refrigeradores_Back_Despues_x000a_" dataDxfId="0">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Evidencia_Organizacion_Refrigeradores_Back_Despues_x000a_" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rc24c1eaaf13e472b9df093f00fa2a223"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="24" xr3:uid="{D6CB1A86-DF44-460F-9741-85B5911B104E}" name="Cubiertos FHW" dataDxfId="2">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r70765bfd70ef46b2a27117b9f5093b01"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="25" xr3:uid="{54AFB965-266D-46D9-AA00-C28AC3A47BD2}" name="Tazas 3 Oz" dataDxfId="1">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="ra36b43c97a7d4724aca27c5269ab24aa"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="26" xr3:uid="{8214B125-AB60-4709-98A9-6AEB718FF69B}" name="Evidencia_FHW_x000a_" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r19ede9588efa4679a729d0e3606da3ad"/>
         </ext>
       </extLst>
     </tableColumn>
@@ -1378,7 +1477,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1008" latestEventMarker="1421">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1022" latestEventMarker="1468">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1400,9 +1499,11 @@
         <xlmsforms:syncedQuestionId>r6e195f182c384a539b6062a655e437a4</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r987b34d6d2994e9a8129243b568832c1</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r399ca94746e5429780f99305f61e6efe</xlmsforms:syncedQuestionId>
-        <xlmsforms:syncedQuestionId>r91fe8e3b4efb4080a3d945974b84a687</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r5e3143c71cab4402900fedf974331b74</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>rc24c1eaaf13e472b9df093f00fa2a223</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r70765bfd70ef46b2a27117b9f5093b01</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>ra36b43c97a7d4724aca27c5269ab24aa</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r19ede9588efa4679a729d0e3606da3ad</xlmsforms:syncedQuestionId>
       </xlmsforms:msForm>
     </ext>
   </extLst>
@@ -1706,13 +1807,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X181"/>
+  <dimension ref="A1:Z197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="24" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
+    <col min="24" max="26" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:26" ht="30.75">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1782,11 +1884,17 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" s="5" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="2" spans="1:24">
+      <c r="Y1" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26">
       <c r="A2">
         <v>827</v>
       </c>
@@ -1797,19 +1905,22 @@
         <v>46282.935717592591</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2">
         <v>38371</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X2" s="5"/>
+      <c r="Y2" s="5"/>
+      <c r="Z2" s="5"/>
+    </row>
+    <row r="3" spans="1:26">
       <c r="A3">
         <v>828</v>
       </c>
@@ -1820,19 +1931,22 @@
         <v>46282.937152777777</v>
       </c>
       <c r="D3" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F3">
         <v>38371</v>
       </c>
       <c r="G3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:24">
+        <v>29</v>
+      </c>
+      <c r="X3" s="5"/>
+      <c r="Y3" s="5"/>
+      <c r="Z3" s="5"/>
+    </row>
+    <row r="4" spans="1:26">
       <c r="A4">
         <v>829</v>
       </c>
@@ -1843,22 +1957,25 @@
         <v>46283.553935185184</v>
       </c>
       <c r="D4" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E4" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F4">
         <v>43164</v>
       </c>
       <c r="G4" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K4" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:24">
+        <v>33</v>
+      </c>
+      <c r="X4" s="5"/>
+      <c r="Y4" s="5"/>
+      <c r="Z4" s="5"/>
+    </row>
+    <row r="5" spans="1:26">
       <c r="A5">
         <v>830</v>
       </c>
@@ -1869,22 +1986,25 @@
         <v>46283.572743055556</v>
       </c>
       <c r="D5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F5">
         <v>38529</v>
       </c>
       <c r="G5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M5" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24">
+        <v>37</v>
+      </c>
+      <c r="X5" s="5"/>
+      <c r="Y5" s="5"/>
+      <c r="Z5" s="5"/>
+    </row>
+    <row r="6" spans="1:26">
       <c r="A6">
         <v>831</v>
       </c>
@@ -1895,19 +2015,22 @@
         <v>46283.708009259259</v>
       </c>
       <c r="D6" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E6" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F6">
         <v>38431</v>
       </c>
       <c r="G6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X6" s="5"/>
+      <c r="Y6" s="5"/>
+      <c r="Z6" s="5"/>
+    </row>
+    <row r="7" spans="1:26">
       <c r="A7">
         <v>832</v>
       </c>
@@ -1918,19 +2041,22 @@
         <v>46283.727754629632</v>
       </c>
       <c r="D7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7">
         <v>38661</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X7" s="5"/>
+      <c r="Y7" s="5"/>
+      <c r="Z7" s="5"/>
+    </row>
+    <row r="8" spans="1:26">
       <c r="A8">
         <v>833</v>
       </c>
@@ -1941,19 +2067,22 @@
         <v>46283.742245370369</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F8">
         <v>38925</v>
       </c>
       <c r="G8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X8" s="5"/>
+      <c r="Y8" s="5"/>
+      <c r="Z8" s="5"/>
+    </row>
+    <row r="9" spans="1:26">
       <c r="A9">
         <v>834</v>
       </c>
@@ -1964,19 +2093,22 @@
         <v>46283.752372685187</v>
       </c>
       <c r="D9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F9">
         <v>43043</v>
       </c>
       <c r="G9" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X9" s="5"/>
+      <c r="Y9" s="5"/>
+      <c r="Z9" s="5"/>
+    </row>
+    <row r="10" spans="1:26">
       <c r="A10">
         <v>835</v>
       </c>
@@ -1987,19 +2119,22 @@
         <v>46283.819976851853</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="E10" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F10">
         <v>38115</v>
       </c>
       <c r="G10" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X10" s="5"/>
+      <c r="Y10" s="5"/>
+      <c r="Z10" s="5"/>
+    </row>
+    <row r="11" spans="1:26">
       <c r="A11">
         <v>836</v>
       </c>
@@ -2010,19 +2145,22 @@
         <v>46283.895983796298</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11">
         <v>38674</v>
       </c>
       <c r="G11" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X11" s="5"/>
+      <c r="Y11" s="5"/>
+      <c r="Z11" s="5"/>
+    </row>
+    <row r="12" spans="1:26">
       <c r="A12">
         <v>837</v>
       </c>
@@ -2033,19 +2171,22 @@
         <v>46283.913958333331</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E12" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F12">
         <v>38535</v>
       </c>
       <c r="G12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X12" s="5"/>
+      <c r="Y12" s="5"/>
+      <c r="Z12" s="5"/>
+    </row>
+    <row r="13" spans="1:26">
       <c r="A13">
         <v>838</v>
       </c>
@@ -2056,19 +2197,22 @@
         <v>46284.398645833331</v>
       </c>
       <c r="D13" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E13" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F13">
         <v>38590</v>
       </c>
       <c r="G13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X13" s="5"/>
+      <c r="Y13" s="5"/>
+      <c r="Z13" s="5"/>
+    </row>
+    <row r="14" spans="1:26">
       <c r="A14">
         <v>839</v>
       </c>
@@ -2079,19 +2223,22 @@
         <v>46284.404386574075</v>
       </c>
       <c r="D14" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F14">
         <v>38862</v>
       </c>
       <c r="G14" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X14" s="5"/>
+      <c r="Y14" s="5"/>
+      <c r="Z14" s="5"/>
+    </row>
+    <row r="15" spans="1:26">
       <c r="A15">
         <v>840</v>
       </c>
@@ -2102,19 +2249,22 @@
         <v>46284.409502314818</v>
       </c>
       <c r="D15" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F15">
         <v>38136</v>
       </c>
       <c r="G15" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X15" s="5"/>
+      <c r="Y15" s="5"/>
+      <c r="Z15" s="5"/>
+    </row>
+    <row r="16" spans="1:26">
       <c r="A16">
         <v>841</v>
       </c>
@@ -2125,19 +2275,22 @@
         <v>46284.433622685188</v>
       </c>
       <c r="D16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E16" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="F16">
         <v>38197</v>
       </c>
       <c r="G16" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="17" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X16" s="5"/>
+      <c r="Y16" s="5"/>
+      <c r="Z16" s="5"/>
+    </row>
+    <row r="17" spans="1:26">
       <c r="A17">
         <v>842</v>
       </c>
@@ -2148,19 +2301,22 @@
         <v>46284.530243055553</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F17">
         <v>38606</v>
       </c>
       <c r="G17" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="18" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X17" s="5"/>
+      <c r="Y17" s="5"/>
+      <c r="Z17" s="5"/>
+    </row>
+    <row r="18" spans="1:26">
       <c r="A18">
         <v>843</v>
       </c>
@@ -2171,22 +2327,25 @@
         <v>46284.533553240741</v>
       </c>
       <c r="D18" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F18">
         <v>38458</v>
       </c>
       <c r="G18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O18" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="19" spans="1:24">
+        <v>65</v>
+      </c>
+      <c r="X18" s="5"/>
+      <c r="Y18" s="5"/>
+      <c r="Z18" s="5"/>
+    </row>
+    <row r="19" spans="1:26">
       <c r="A19">
         <v>844</v>
       </c>
@@ -2197,19 +2356,22 @@
         <v>46284.535138888888</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E19" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F19">
         <v>38230</v>
       </c>
       <c r="G19" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="20" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X19" s="5"/>
+      <c r="Y19" s="5"/>
+      <c r="Z19" s="5"/>
+    </row>
+    <row r="20" spans="1:26">
       <c r="A20">
         <v>845</v>
       </c>
@@ -2220,22 +2382,25 @@
         <v>46284.54246527778</v>
       </c>
       <c r="D20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F20">
         <v>38458</v>
       </c>
       <c r="G20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:24">
+        <v>69</v>
+      </c>
+      <c r="X20" s="5"/>
+      <c r="Y20" s="5"/>
+      <c r="Z20" s="5"/>
+    </row>
+    <row r="21" spans="1:26">
       <c r="A21">
         <v>846</v>
       </c>
@@ -2246,19 +2411,22 @@
         <v>46284.564814814818</v>
       </c>
       <c r="D21" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F21">
         <v>38458</v>
       </c>
       <c r="G21" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X21" s="5"/>
+      <c r="Y21" s="5"/>
+      <c r="Z21" s="5"/>
+    </row>
+    <row r="22" spans="1:26">
       <c r="A22">
         <v>847</v>
       </c>
@@ -2269,19 +2437,22 @@
         <v>46284.579930555556</v>
       </c>
       <c r="D22" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E22" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F22">
         <v>38117</v>
       </c>
       <c r="G22" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="23" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X22" s="5"/>
+      <c r="Y22" s="5"/>
+      <c r="Z22" s="5"/>
+    </row>
+    <row r="23" spans="1:26">
       <c r="A23">
         <v>848</v>
       </c>
@@ -2292,19 +2463,22 @@
         <v>46284.595416666663</v>
       </c>
       <c r="D23" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E23" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F23">
         <v>38475</v>
       </c>
       <c r="G23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="24" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X23" s="5"/>
+      <c r="Y23" s="5"/>
+      <c r="Z23" s="5"/>
+    </row>
+    <row r="24" spans="1:26">
       <c r="A24">
         <v>849</v>
       </c>
@@ -2315,22 +2489,25 @@
         <v>46284.597175925926</v>
       </c>
       <c r="D24" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E24" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F24">
         <v>38333</v>
       </c>
       <c r="G24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P24" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="25" spans="1:24">
+        <v>76</v>
+      </c>
+      <c r="X24" s="5"/>
+      <c r="Y24" s="5"/>
+      <c r="Z24" s="5"/>
+    </row>
+    <row r="25" spans="1:26">
       <c r="A25">
         <v>850</v>
       </c>
@@ -2341,28 +2518,31 @@
         <v>46284.600231481483</v>
       </c>
       <c r="D25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E25" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F25">
         <v>38333</v>
       </c>
       <c r="G25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S25" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="26" spans="1:24">
+        <v>80</v>
+      </c>
+      <c r="X25" s="5"/>
+      <c r="Y25" s="5"/>
+      <c r="Z25" s="5"/>
+    </row>
+    <row r="26" spans="1:26">
       <c r="A26">
         <v>851</v>
       </c>
@@ -2373,19 +2553,22 @@
         <v>46284.643020833333</v>
       </c>
       <c r="D26" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F26">
         <v>38995</v>
       </c>
       <c r="G26" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X26" s="5"/>
+      <c r="Y26" s="5"/>
+      <c r="Z26" s="5"/>
+    </row>
+    <row r="27" spans="1:26">
       <c r="A27">
         <v>852</v>
       </c>
@@ -2396,22 +2579,25 @@
         <v>46284.646770833337</v>
       </c>
       <c r="D27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E27" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F27">
         <v>38371</v>
       </c>
       <c r="G27" t="s">
-        <v>81</v>
-      </c>
-      <c r="W27" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="28" spans="1:24">
+        <v>83</v>
+      </c>
+      <c r="V27" t="s">
+        <v>84</v>
+      </c>
+      <c r="X27" s="5"/>
+      <c r="Y27" s="5"/>
+      <c r="Z27" s="5"/>
+    </row>
+    <row r="28" spans="1:26">
       <c r="A28">
         <v>853</v>
       </c>
@@ -2422,19 +2608,22 @@
         <v>46284.651006944441</v>
       </c>
       <c r="D28" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="F28">
         <v>38507</v>
       </c>
       <c r="G28" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X28" s="5"/>
+      <c r="Y28" s="5"/>
+      <c r="Z28" s="5"/>
+    </row>
+    <row r="29" spans="1:26">
       <c r="A29">
         <v>854</v>
       </c>
@@ -2445,19 +2634,22 @@
         <v>46284.669606481482</v>
       </c>
       <c r="D29" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F29">
         <v>38149</v>
       </c>
       <c r="G29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X29" s="5"/>
+      <c r="Y29" s="5"/>
+      <c r="Z29" s="5"/>
+    </row>
+    <row r="30" spans="1:26">
       <c r="A30">
         <v>855</v>
       </c>
@@ -2468,19 +2660,22 @@
         <v>46284.68986111111</v>
       </c>
       <c r="D30" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E30" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="F30">
         <v>38270</v>
       </c>
       <c r="G30" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X30" s="5"/>
+      <c r="Y30" s="5"/>
+      <c r="Z30" s="5"/>
+    </row>
+    <row r="31" spans="1:26">
       <c r="A31">
         <v>856</v>
       </c>
@@ -2491,28 +2686,31 @@
         <v>46284.690474537034</v>
       </c>
       <c r="D31" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E31" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F31">
         <v>38515</v>
       </c>
       <c r="G31" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S31" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="32" spans="1:24">
+        <v>93</v>
+      </c>
+      <c r="X31" s="5"/>
+      <c r="Y31" s="5"/>
+      <c r="Z31" s="5"/>
+    </row>
+    <row r="32" spans="1:26">
       <c r="A32">
         <v>857</v>
       </c>
@@ -2523,25 +2721,28 @@
         <v>46284.703773148147</v>
       </c>
       <c r="D32" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E32" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F32">
         <v>38515</v>
       </c>
       <c r="G32" t="s">
-        <v>81</v>
+        <v>83</v>
+      </c>
+      <c r="V32" t="s">
+        <v>94</v>
       </c>
       <c r="W32" t="s">
-        <v>92</v>
-      </c>
-      <c r="X32" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="33" spans="1:19">
+        <v>95</v>
+      </c>
+      <c r="X32" s="5"/>
+      <c r="Y32" s="5"/>
+      <c r="Z32" s="5"/>
+    </row>
+    <row r="33" spans="1:26">
       <c r="A33">
         <v>858</v>
       </c>
@@ -2552,19 +2753,22 @@
         <v>46284.72115740741</v>
       </c>
       <c r="D33" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="E33" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="F33">
         <v>38719</v>
       </c>
       <c r="G33" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X33" s="5"/>
+      <c r="Y33" s="5"/>
+      <c r="Z33" s="5"/>
+    </row>
+    <row r="34" spans="1:26">
       <c r="A34">
         <v>859</v>
       </c>
@@ -2575,22 +2779,25 @@
         <v>46284.72452546296</v>
       </c>
       <c r="D34" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E34" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F34">
         <v>38656</v>
       </c>
       <c r="G34" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O34" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
+        <v>100</v>
+      </c>
+      <c r="X34" s="5"/>
+      <c r="Y34" s="5"/>
+      <c r="Z34" s="5"/>
+    </row>
+    <row r="35" spans="1:26">
       <c r="A35">
         <v>860</v>
       </c>
@@ -2601,19 +2808,22 @@
         <v>46284.745300925926</v>
       </c>
       <c r="D35" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E35" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F35">
         <v>38770</v>
       </c>
       <c r="G35" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="36" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X35" s="5"/>
+      <c r="Y35" s="5"/>
+      <c r="Z35" s="5"/>
+    </row>
+    <row r="36" spans="1:26">
       <c r="A36">
         <v>861</v>
       </c>
@@ -2624,19 +2834,22 @@
         <v>46284.747037037036</v>
       </c>
       <c r="D36" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E36" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F36">
         <v>43111</v>
       </c>
       <c r="G36" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X36" s="5"/>
+      <c r="Y36" s="5"/>
+      <c r="Z36" s="5"/>
+    </row>
+    <row r="37" spans="1:26">
       <c r="A37">
         <v>862</v>
       </c>
@@ -2647,19 +2860,22 @@
         <v>46284.753009259257</v>
       </c>
       <c r="D37" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="E37" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="F37">
         <v>38442</v>
       </c>
       <c r="G37" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X37" s="5"/>
+      <c r="Y37" s="5"/>
+      <c r="Z37" s="5"/>
+    </row>
+    <row r="38" spans="1:26">
       <c r="A38">
         <v>863</v>
       </c>
@@ -2670,19 +2886,22 @@
         <v>46284.763206018521</v>
       </c>
       <c r="D38" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E38" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F38">
         <v>38394</v>
       </c>
       <c r="G38" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X38" s="5"/>
+      <c r="Y38" s="5"/>
+      <c r="Z38" s="5"/>
+    </row>
+    <row r="39" spans="1:26">
       <c r="A39">
         <v>864</v>
       </c>
@@ -2693,19 +2912,22 @@
         <v>46284.764317129629</v>
       </c>
       <c r="D39" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="E39" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="F39">
         <v>38205</v>
       </c>
       <c r="G39" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="40" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X39" s="5"/>
+      <c r="Y39" s="5"/>
+      <c r="Z39" s="5"/>
+    </row>
+    <row r="40" spans="1:26">
       <c r="A40">
         <v>865</v>
       </c>
@@ -2716,28 +2938,31 @@
         <v>46284.782060185185</v>
       </c>
       <c r="D40" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E40" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F40">
         <v>38401</v>
       </c>
       <c r="G40" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="S40" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19">
+        <v>113</v>
+      </c>
+      <c r="X40" s="5"/>
+      <c r="Y40" s="5"/>
+      <c r="Z40" s="5"/>
+    </row>
+    <row r="41" spans="1:26">
       <c r="A41">
         <v>866</v>
       </c>
@@ -2748,19 +2973,22 @@
         <v>46284.787569444445</v>
       </c>
       <c r="D41" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="E41" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="F41">
         <v>38266</v>
       </c>
       <c r="G41" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X41" s="5"/>
+      <c r="Y41" s="5"/>
+      <c r="Z41" s="5"/>
+    </row>
+    <row r="42" spans="1:26">
       <c r="A42">
         <v>867</v>
       </c>
@@ -2771,22 +2999,25 @@
         <v>46284.79346064815</v>
       </c>
       <c r="D42" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E42" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F42">
         <v>38418</v>
       </c>
       <c r="G42" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L42" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="43" spans="1:19">
+        <v>119</v>
+      </c>
+      <c r="X42" s="5"/>
+      <c r="Y42" s="5"/>
+      <c r="Z42" s="5"/>
+    </row>
+    <row r="43" spans="1:26">
       <c r="A43">
         <v>868</v>
       </c>
@@ -2797,19 +3028,22 @@
         <v>46284.793726851851</v>
       </c>
       <c r="D43" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="E43" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="F43">
         <v>38119</v>
       </c>
       <c r="G43" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X43" s="5"/>
+      <c r="Y43" s="5"/>
+      <c r="Z43" s="5"/>
+    </row>
+    <row r="44" spans="1:26">
       <c r="A44">
         <v>869</v>
       </c>
@@ -2820,25 +3054,28 @@
         <v>46284.823055555556</v>
       </c>
       <c r="D44" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E44" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F44">
         <v>38339</v>
       </c>
       <c r="G44" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H44" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I44" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="45" spans="1:19">
+        <v>126</v>
+      </c>
+      <c r="X44" s="5"/>
+      <c r="Y44" s="5"/>
+      <c r="Z44" s="5"/>
+    </row>
+    <row r="45" spans="1:26">
       <c r="A45">
         <v>870</v>
       </c>
@@ -2849,22 +3086,25 @@
         <v>46284.825856481482</v>
       </c>
       <c r="D45" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E45" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F45">
         <v>38339</v>
       </c>
       <c r="G45" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J45" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="46" spans="1:19">
+        <v>128</v>
+      </c>
+      <c r="X45" s="5"/>
+      <c r="Y45" s="5"/>
+      <c r="Z45" s="5"/>
+    </row>
+    <row r="46" spans="1:26">
       <c r="A46">
         <v>871</v>
       </c>
@@ -2875,22 +3115,25 @@
         <v>46284.826238425929</v>
       </c>
       <c r="D46" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E46" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F46">
         <v>38339</v>
       </c>
       <c r="G46" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K46" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="47" spans="1:19">
+        <v>129</v>
+      </c>
+      <c r="X46" s="5"/>
+      <c r="Y46" s="5"/>
+      <c r="Z46" s="5"/>
+    </row>
+    <row r="47" spans="1:26">
       <c r="A47">
         <v>872</v>
       </c>
@@ -2901,19 +3144,22 @@
         <v>46284.826817129629</v>
       </c>
       <c r="D47" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F47">
         <v>38411</v>
       </c>
       <c r="G47" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X47" s="5"/>
+      <c r="Y47" s="5"/>
+      <c r="Z47" s="5"/>
+    </row>
+    <row r="48" spans="1:26">
       <c r="A48">
         <v>873</v>
       </c>
@@ -2924,22 +3170,25 @@
         <v>46284.826921296299</v>
       </c>
       <c r="D48" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E48" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F48">
         <v>38339</v>
       </c>
       <c r="G48" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L48" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="49" spans="1:19">
+        <v>132</v>
+      </c>
+      <c r="X48" s="5"/>
+      <c r="Y48" s="5"/>
+      <c r="Z48" s="5"/>
+    </row>
+    <row r="49" spans="1:26">
       <c r="A49">
         <v>874</v>
       </c>
@@ -2950,25 +3199,28 @@
         <v>46284.827430555553</v>
       </c>
       <c r="D49" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E49" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F49">
         <v>38339</v>
       </c>
       <c r="G49" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M49" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N49" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="50" spans="1:19">
+        <v>133</v>
+      </c>
+      <c r="X49" s="5"/>
+      <c r="Y49" s="5"/>
+      <c r="Z49" s="5"/>
+    </row>
+    <row r="50" spans="1:26">
       <c r="A50">
         <v>875</v>
       </c>
@@ -2979,19 +3231,22 @@
         <v>46284.828472222223</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E50" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F50">
         <v>38411</v>
       </c>
       <c r="G50" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51" spans="1:19">
+        <v>29</v>
+      </c>
+      <c r="X50" s="5"/>
+      <c r="Y50" s="5"/>
+      <c r="Z50" s="5"/>
+    </row>
+    <row r="51" spans="1:26">
       <c r="A51">
         <v>876</v>
       </c>
@@ -3002,22 +3257,25 @@
         <v>46284.829895833333</v>
       </c>
       <c r="D51" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E51" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F51">
         <v>38339</v>
       </c>
       <c r="G51" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O51" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="52" spans="1:19">
+        <v>134</v>
+      </c>
+      <c r="X51" s="5"/>
+      <c r="Y51" s="5"/>
+      <c r="Z51" s="5"/>
+    </row>
+    <row r="52" spans="1:26">
       <c r="A52">
         <v>877</v>
       </c>
@@ -3028,22 +3286,25 @@
         <v>46284.830428240741</v>
       </c>
       <c r="D52" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E52" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F52">
         <v>38339</v>
       </c>
       <c r="G52" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="P52" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="53" spans="1:19">
+        <v>135</v>
+      </c>
+      <c r="X52" s="5"/>
+      <c r="Y52" s="5"/>
+      <c r="Z52" s="5"/>
+    </row>
+    <row r="53" spans="1:26">
       <c r="A53">
         <v>878</v>
       </c>
@@ -3054,28 +3315,31 @@
         <v>46284.831921296296</v>
       </c>
       <c r="D53" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="E53" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="F53">
         <v>38339</v>
       </c>
       <c r="G53" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q53" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R53" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S53" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="54" spans="1:19">
+        <v>136</v>
+      </c>
+      <c r="X53" s="5"/>
+      <c r="Y53" s="5"/>
+      <c r="Z53" s="5"/>
+    </row>
+    <row r="54" spans="1:26">
       <c r="A54">
         <v>879</v>
       </c>
@@ -3086,19 +3350,22 @@
         <v>46284.921307870369</v>
       </c>
       <c r="D54" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E54" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="F54">
         <v>38427</v>
       </c>
       <c r="G54" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="55" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X54" s="5"/>
+      <c r="Y54" s="5"/>
+      <c r="Z54" s="5"/>
+    </row>
+    <row r="55" spans="1:26">
       <c r="A55">
         <v>880</v>
       </c>
@@ -3109,19 +3376,22 @@
         <v>46285.504502314812</v>
       </c>
       <c r="D55" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E55" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="F55">
         <v>38186</v>
       </c>
       <c r="G55" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="56" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X55" s="5"/>
+      <c r="Y55" s="5"/>
+      <c r="Z55" s="5"/>
+    </row>
+    <row r="56" spans="1:26">
       <c r="A56">
         <v>881</v>
       </c>
@@ -3132,19 +3402,22 @@
         <v>46285.572222222225</v>
       </c>
       <c r="D56" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E56" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="F56">
         <v>38561</v>
       </c>
       <c r="G56" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="57" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X56" s="5"/>
+      <c r="Y56" s="5"/>
+      <c r="Z56" s="5"/>
+    </row>
+    <row r="57" spans="1:26">
       <c r="A57">
         <v>882</v>
       </c>
@@ -3155,25 +3428,28 @@
         <v>46285.574131944442</v>
       </c>
       <c r="D57" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E57" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F57">
         <v>38368</v>
       </c>
       <c r="G57" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M57" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N57" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:19">
+        <v>145</v>
+      </c>
+      <c r="X57" s="5"/>
+      <c r="Y57" s="5"/>
+      <c r="Z57" s="5"/>
+    </row>
+    <row r="58" spans="1:26">
       <c r="A58">
         <v>883</v>
       </c>
@@ -3184,19 +3460,22 @@
         <v>46285.621180555558</v>
       </c>
       <c r="D58" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E58" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F58">
         <v>38401</v>
       </c>
       <c r="G58" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="59" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X58" s="5"/>
+      <c r="Y58" s="5"/>
+      <c r="Z58" s="5"/>
+    </row>
+    <row r="59" spans="1:26">
       <c r="A59">
         <v>884</v>
       </c>
@@ -3207,19 +3486,22 @@
         <v>46285.63894675926</v>
       </c>
       <c r="D59" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E59" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F59">
         <v>38992</v>
       </c>
       <c r="G59" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="60" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X59" s="5"/>
+      <c r="Y59" s="5"/>
+      <c r="Z59" s="5"/>
+    </row>
+    <row r="60" spans="1:26">
       <c r="A60">
         <v>885</v>
       </c>
@@ -3230,19 +3512,22 @@
         <v>46285.663576388892</v>
       </c>
       <c r="D60" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E60" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F60">
         <v>38529</v>
       </c>
       <c r="G60" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="61" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X60" s="5"/>
+      <c r="Y60" s="5"/>
+      <c r="Z60" s="5"/>
+    </row>
+    <row r="61" spans="1:26">
       <c r="A61">
         <v>886</v>
       </c>
@@ -3253,19 +3538,22 @@
         <v>46285.670185185183</v>
       </c>
       <c r="D61" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E61" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F61">
         <v>38695</v>
       </c>
       <c r="G61" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="62" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X61" s="5"/>
+      <c r="Y61" s="5"/>
+      <c r="Z61" s="5"/>
+    </row>
+    <row r="62" spans="1:26">
       <c r="A62">
         <v>887</v>
       </c>
@@ -3276,19 +3564,22 @@
         <v>46285.689282407409</v>
       </c>
       <c r="D62" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E62" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F62">
         <v>38368</v>
       </c>
       <c r="G62" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="63" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X62" s="5"/>
+      <c r="Y62" s="5"/>
+      <c r="Z62" s="5"/>
+    </row>
+    <row r="63" spans="1:26">
       <c r="A63">
         <v>888</v>
       </c>
@@ -3299,19 +3590,22 @@
         <v>46285.716319444444</v>
       </c>
       <c r="D63" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E63" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="F63">
         <v>43130</v>
       </c>
       <c r="G63" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="64" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X63" s="5"/>
+      <c r="Y63" s="5"/>
+      <c r="Z63" s="5"/>
+    </row>
+    <row r="64" spans="1:26">
       <c r="A64">
         <v>889</v>
       </c>
@@ -3322,19 +3616,22 @@
         <v>46285.718784722223</v>
       </c>
       <c r="D64" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E64" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="F64">
         <v>38363</v>
       </c>
       <c r="G64" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="65" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X64" s="5"/>
+      <c r="Y64" s="5"/>
+      <c r="Z64" s="5"/>
+    </row>
+    <row r="65" spans="1:26">
       <c r="A65">
         <v>890</v>
       </c>
@@ -3345,19 +3642,22 @@
         <v>46285.725115740737</v>
       </c>
       <c r="D65" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E65" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="F65">
         <v>38604</v>
       </c>
       <c r="G65" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="66" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X65" s="5"/>
+      <c r="Y65" s="5"/>
+      <c r="Z65" s="5"/>
+    </row>
+    <row r="66" spans="1:26">
       <c r="A66">
         <v>891</v>
       </c>
@@ -3368,19 +3668,22 @@
         <v>46285.732407407406</v>
       </c>
       <c r="D66" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E66" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="F66">
         <v>38515</v>
       </c>
       <c r="G66" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="67" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X66" s="5"/>
+      <c r="Y66" s="5"/>
+      <c r="Z66" s="5"/>
+    </row>
+    <row r="67" spans="1:26">
       <c r="A67">
         <v>892</v>
       </c>
@@ -3391,19 +3694,22 @@
         <v>46285.740914351853</v>
       </c>
       <c r="D67" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E67" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F67">
         <v>38333</v>
       </c>
       <c r="G67" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="68" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X67" s="5"/>
+      <c r="Y67" s="5"/>
+      <c r="Z67" s="5"/>
+    </row>
+    <row r="68" spans="1:26">
       <c r="A68">
         <v>893</v>
       </c>
@@ -3414,22 +3720,25 @@
         <v>46285.754803240743</v>
       </c>
       <c r="D68" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E68" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F68">
         <v>38511</v>
       </c>
       <c r="G68" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L68" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="69" spans="1:19">
+        <v>158</v>
+      </c>
+      <c r="X68" s="5"/>
+      <c r="Y68" s="5"/>
+      <c r="Z68" s="5"/>
+    </row>
+    <row r="69" spans="1:26">
       <c r="A69">
         <v>894</v>
       </c>
@@ -3440,19 +3749,22 @@
         <v>46285.757719907408</v>
       </c>
       <c r="D69" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E69" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="F69">
         <v>38143</v>
       </c>
       <c r="G69" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="70" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X69" s="5"/>
+      <c r="Y69" s="5"/>
+      <c r="Z69" s="5"/>
+    </row>
+    <row r="70" spans="1:26">
       <c r="A70">
         <v>895</v>
       </c>
@@ -3463,19 +3775,22 @@
         <v>46285.758657407408</v>
       </c>
       <c r="D70" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E70" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F70">
         <v>38333</v>
       </c>
       <c r="G70" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="71" spans="1:19">
+        <v>29</v>
+      </c>
+      <c r="X70" s="5"/>
+      <c r="Y70" s="5"/>
+      <c r="Z70" s="5"/>
+    </row>
+    <row r="71" spans="1:26">
       <c r="A71">
         <v>896</v>
       </c>
@@ -3486,19 +3801,22 @@
         <v>46285.777777777781</v>
       </c>
       <c r="D71" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E71" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F71">
         <v>43070</v>
       </c>
       <c r="G71" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="72" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X71" s="5"/>
+      <c r="Y71" s="5"/>
+      <c r="Z71" s="5"/>
+    </row>
+    <row r="72" spans="1:26">
       <c r="A72">
         <v>897</v>
       </c>
@@ -3509,19 +3827,22 @@
         <v>46285.803564814814</v>
       </c>
       <c r="D72" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E72" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F72">
         <v>38862</v>
       </c>
       <c r="G72" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73" spans="1:19">
+        <v>29</v>
+      </c>
+      <c r="X72" s="5"/>
+      <c r="Y72" s="5"/>
+      <c r="Z72" s="5"/>
+    </row>
+    <row r="73" spans="1:26">
       <c r="A73">
         <v>898</v>
       </c>
@@ -3532,19 +3853,22 @@
         <v>46285.805949074071</v>
       </c>
       <c r="D73" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E73" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F73">
         <v>38339</v>
       </c>
       <c r="G73" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="74" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X73" s="5"/>
+      <c r="Y73" s="5"/>
+      <c r="Z73" s="5"/>
+    </row>
+    <row r="74" spans="1:26">
       <c r="A74">
         <v>899</v>
       </c>
@@ -3555,22 +3879,25 @@
         <v>46285.818715277775</v>
       </c>
       <c r="D74" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E74" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F74">
         <v>38351</v>
       </c>
       <c r="G74" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L74" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="75" spans="1:19">
+        <v>167</v>
+      </c>
+      <c r="X74" s="5"/>
+      <c r="Y74" s="5"/>
+      <c r="Z74" s="5"/>
+    </row>
+    <row r="75" spans="1:26">
       <c r="A75">
         <v>900</v>
       </c>
@@ -3581,19 +3908,22 @@
         <v>46285.84</v>
       </c>
       <c r="D75" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E75" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F75">
         <v>38656</v>
       </c>
       <c r="G75" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="76" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X75" s="5"/>
+      <c r="Y75" s="5"/>
+      <c r="Z75" s="5"/>
+    </row>
+    <row r="76" spans="1:26">
       <c r="A76">
         <v>901</v>
       </c>
@@ -3604,19 +3934,22 @@
         <v>46285.849733796298</v>
       </c>
       <c r="D76" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E76" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F76">
         <v>38456</v>
       </c>
       <c r="G76" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="77" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X76" s="5"/>
+      <c r="Y76" s="5"/>
+      <c r="Z76" s="5"/>
+    </row>
+    <row r="77" spans="1:26">
       <c r="A77">
         <v>902</v>
       </c>
@@ -3627,19 +3960,22 @@
         <v>46285.861203703702</v>
       </c>
       <c r="D77" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E77" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F77">
         <v>38894</v>
       </c>
       <c r="G77" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="78" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X77" s="5"/>
+      <c r="Y77" s="5"/>
+      <c r="Z77" s="5"/>
+    </row>
+    <row r="78" spans="1:26">
       <c r="A78">
         <v>903</v>
       </c>
@@ -3650,19 +3986,22 @@
         <v>46285.870717592596</v>
       </c>
       <c r="D78" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E78" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F78">
         <v>43193</v>
       </c>
       <c r="G78" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="79" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X78" s="5"/>
+      <c r="Y78" s="5"/>
+      <c r="Z78" s="5"/>
+    </row>
+    <row r="79" spans="1:26">
       <c r="A79">
         <v>904</v>
       </c>
@@ -3673,19 +4012,22 @@
         <v>46285.902743055558</v>
       </c>
       <c r="D79" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E79" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F79">
         <v>38176</v>
       </c>
       <c r="G79" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="80" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X79" s="5"/>
+      <c r="Y79" s="5"/>
+      <c r="Z79" s="5"/>
+    </row>
+    <row r="80" spans="1:26">
       <c r="A80">
         <v>905</v>
       </c>
@@ -3696,28 +4038,31 @@
         <v>46285.908125000002</v>
       </c>
       <c r="D80" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E80" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="F80">
         <v>38176</v>
       </c>
       <c r="G80" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q80" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R80" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S80" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="81" spans="1:19">
+        <v>176</v>
+      </c>
+      <c r="X80" s="5"/>
+      <c r="Y80" s="5"/>
+      <c r="Z80" s="5"/>
+    </row>
+    <row r="81" spans="1:26">
       <c r="A81">
         <v>906</v>
       </c>
@@ -3728,19 +4073,22 @@
         <v>46285.955520833333</v>
       </c>
       <c r="D81" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E81" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F81">
         <v>43152</v>
       </c>
       <c r="G81" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="82" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X81" s="5"/>
+      <c r="Y81" s="5"/>
+      <c r="Z81" s="5"/>
+    </row>
+    <row r="82" spans="1:26">
       <c r="A82">
         <v>907</v>
       </c>
@@ -3751,19 +4099,22 @@
         <v>46285.968553240738</v>
       </c>
       <c r="D82" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E82" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F82">
         <v>38460</v>
       </c>
       <c r="G82" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X82" s="5"/>
+      <c r="Y82" s="5"/>
+      <c r="Z82" s="5"/>
+    </row>
+    <row r="83" spans="1:26">
       <c r="A83">
         <v>908</v>
       </c>
@@ -3774,19 +4125,22 @@
         <v>46285.991226851853</v>
       </c>
       <c r="D83" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E83" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="F83">
         <v>38930</v>
       </c>
       <c r="G83" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="84" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X83" s="5"/>
+      <c r="Y83" s="5"/>
+      <c r="Z83" s="5"/>
+    </row>
+    <row r="84" spans="1:26">
       <c r="A84">
         <v>909</v>
       </c>
@@ -3797,19 +4151,22 @@
         <v>46286.252256944441</v>
       </c>
       <c r="D84" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E84" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="F84">
         <v>38845</v>
       </c>
       <c r="G84" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="85" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X84" s="5"/>
+      <c r="Y84" s="5"/>
+      <c r="Z84" s="5"/>
+    </row>
+    <row r="85" spans="1:26">
       <c r="A85">
         <v>910</v>
       </c>
@@ -3820,19 +4177,22 @@
         <v>46286.265972222223</v>
       </c>
       <c r="D85" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E85" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F85">
         <v>38374</v>
       </c>
       <c r="G85" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="86" spans="1:19">
+        <v>28</v>
+      </c>
+      <c r="X85" s="5"/>
+      <c r="Y85" s="5"/>
+      <c r="Z85" s="5"/>
+    </row>
+    <row r="86" spans="1:26">
       <c r="A86">
         <v>911</v>
       </c>
@@ -3843,22 +4203,25 @@
         <v>46286.317291666666</v>
       </c>
       <c r="D86" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E86" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F86">
         <v>38695</v>
       </c>
       <c r="G86" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O86" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="87" spans="1:19">
+        <v>187</v>
+      </c>
+      <c r="X86" s="5"/>
+      <c r="Y86" s="5"/>
+      <c r="Z86" s="5"/>
+    </row>
+    <row r="87" spans="1:26">
       <c r="A87">
         <v>912</v>
       </c>
@@ -3869,22 +4232,25 @@
         <v>46286.345277777778</v>
       </c>
       <c r="D87" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E87" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F87">
         <v>38770</v>
       </c>
       <c r="G87" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J87" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="88" spans="1:19">
+        <v>188</v>
+      </c>
+      <c r="X87" s="5"/>
+      <c r="Y87" s="5"/>
+      <c r="Z87" s="5"/>
+    </row>
+    <row r="88" spans="1:26">
       <c r="A88">
         <v>913</v>
       </c>
@@ -3895,28 +4261,31 @@
         <v>46286.349328703705</v>
       </c>
       <c r="D88" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="E88" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="F88">
         <v>38770</v>
       </c>
       <c r="G88" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q88" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R88" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S88" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="89" spans="1:19">
+        <v>189</v>
+      </c>
+      <c r="X88" s="5"/>
+      <c r="Y88" s="5"/>
+      <c r="Z88" s="5"/>
+    </row>
+    <row r="89" spans="1:26">
       <c r="A89">
         <v>914</v>
       </c>
@@ -3927,22 +4296,25 @@
         <v>46286.440069444441</v>
       </c>
       <c r="D89" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E89" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F89">
         <v>38695</v>
       </c>
       <c r="G89" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J89" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="90" spans="1:19">
+        <v>190</v>
+      </c>
+      <c r="X89" s="5"/>
+      <c r="Y89" s="5"/>
+      <c r="Z89" s="5"/>
+    </row>
+    <row r="90" spans="1:26">
       <c r="A90">
         <v>915</v>
       </c>
@@ -3953,22 +4325,25 @@
         <v>46286.446469907409</v>
       </c>
       <c r="D90" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E90" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F90">
         <v>38351</v>
       </c>
       <c r="G90" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L90" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="91" spans="1:19">
+        <v>191</v>
+      </c>
+      <c r="X90" s="5"/>
+      <c r="Y90" s="5"/>
+      <c r="Z90" s="5"/>
+    </row>
+    <row r="91" spans="1:26">
       <c r="A91">
         <v>916</v>
       </c>
@@ -3979,25 +4354,28 @@
         <v>46286.450671296298</v>
       </c>
       <c r="D91" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E91" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="F91">
         <v>38800</v>
       </c>
       <c r="G91" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M91" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N91" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="92" spans="1:19">
+        <v>194</v>
+      </c>
+      <c r="X91" s="5"/>
+      <c r="Y91" s="5"/>
+      <c r="Z91" s="5"/>
+    </row>
+    <row r="92" spans="1:26">
       <c r="A92">
         <v>917</v>
       </c>
@@ -4008,22 +4386,25 @@
         <v>46286.460810185185</v>
       </c>
       <c r="D92" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E92" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F92">
         <v>43169</v>
       </c>
       <c r="G92" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L92" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="93" spans="1:19">
+        <v>197</v>
+      </c>
+      <c r="X92" s="5"/>
+      <c r="Y92" s="5"/>
+      <c r="Z92" s="5"/>
+    </row>
+    <row r="93" spans="1:26">
       <c r="A93">
         <v>918</v>
       </c>
@@ -4034,22 +4415,25 @@
         <v>46286.469953703701</v>
       </c>
       <c r="D93" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E93" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F93">
         <v>38502</v>
       </c>
       <c r="G93" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="J93" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="94" spans="1:19">
+        <v>200</v>
+      </c>
+      <c r="X93" s="5"/>
+      <c r="Y93" s="5"/>
+      <c r="Z93" s="5"/>
+    </row>
+    <row r="94" spans="1:26">
       <c r="A94">
         <v>919</v>
       </c>
@@ -4060,22 +4444,25 @@
         <v>46286.470636574071</v>
       </c>
       <c r="D94" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E94" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F94">
         <v>38502</v>
       </c>
       <c r="G94" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K94" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="95" spans="1:19">
+        <v>201</v>
+      </c>
+      <c r="X94" s="5"/>
+      <c r="Y94" s="5"/>
+      <c r="Z94" s="5"/>
+    </row>
+    <row r="95" spans="1:26">
       <c r="A95">
         <v>920</v>
       </c>
@@ -4086,22 +4473,25 @@
         <v>46286.47152777778</v>
       </c>
       <c r="D95" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E95" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F95">
         <v>38594</v>
       </c>
       <c r="G95" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L95" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="96" spans="1:19">
+        <v>204</v>
+      </c>
+      <c r="X95" s="5"/>
+      <c r="Y95" s="5"/>
+      <c r="Z95" s="5"/>
+    </row>
+    <row r="96" spans="1:26">
       <c r="A96">
         <v>921</v>
       </c>
@@ -4112,22 +4502,25 @@
         <v>46286.47283564815</v>
       </c>
       <c r="D96" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E96" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F96">
         <v>38502</v>
       </c>
       <c r="G96" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L96" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="97" spans="1:24">
+        <v>205</v>
+      </c>
+      <c r="X96" s="5"/>
+      <c r="Y96" s="5"/>
+      <c r="Z96" s="5"/>
+    </row>
+    <row r="97" spans="1:26">
       <c r="A97">
         <v>922</v>
       </c>
@@ -4138,22 +4531,25 @@
         <v>46286.476759259262</v>
       </c>
       <c r="D97" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E97" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F97">
         <v>38502</v>
       </c>
       <c r="G97" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="O97" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="98" spans="1:24">
+        <v>206</v>
+      </c>
+      <c r="X97" s="5"/>
+      <c r="Y97" s="5"/>
+      <c r="Z97" s="5"/>
+    </row>
+    <row r="98" spans="1:26">
       <c r="A98">
         <v>923</v>
       </c>
@@ -4164,28 +4560,31 @@
         <v>46286.47859953704</v>
       </c>
       <c r="D98" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E98" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F98">
         <v>38502</v>
       </c>
       <c r="G98" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="Q98" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="R98" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="S98" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="99" spans="1:24">
+        <v>207</v>
+      </c>
+      <c r="X98" s="5"/>
+      <c r="Y98" s="5"/>
+      <c r="Z98" s="5"/>
+    </row>
+    <row r="99" spans="1:26">
       <c r="A99">
         <v>924</v>
       </c>
@@ -4196,19 +4595,22 @@
         <v>46286.484652777777</v>
       </c>
       <c r="D99" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E99" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F99">
         <v>38859</v>
       </c>
       <c r="G99" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="100" spans="1:24">
+        <v>28</v>
+      </c>
+      <c r="X99" s="5"/>
+      <c r="Y99" s="5"/>
+      <c r="Z99" s="5"/>
+    </row>
+    <row r="100" spans="1:26">
       <c r="A100">
         <v>925</v>
       </c>
@@ -4219,22 +4621,25 @@
         <v>46286.488240740742</v>
       </c>
       <c r="D100" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E100" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F100">
         <v>43070</v>
       </c>
       <c r="G100" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L100" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="101" spans="1:24">
+        <v>210</v>
+      </c>
+      <c r="X100" s="5"/>
+      <c r="Y100" s="5"/>
+      <c r="Z100" s="5"/>
+    </row>
+    <row r="101" spans="1:26">
       <c r="A101">
         <v>926</v>
       </c>
@@ -4245,26 +4650,29 @@
         <v>46286.489004629628</v>
       </c>
       <c r="D101" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E101" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F101">
         <v>43070</v>
       </c>
       <c r="G101" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H101" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I101" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="102" spans="1:24">
-      <c r="A102" s="4">
+        <v>211</v>
+      </c>
+      <c r="X101" s="5"/>
+      <c r="Y101" s="5"/>
+      <c r="Z101" s="5"/>
+    </row>
+    <row r="102" spans="1:26">
+      <c r="A102">
         <v>927</v>
       </c>
       <c r="B102" s="3">
@@ -4274,16 +4682,16 @@
         <v>46286.490428240701</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F102" s="4">
+        <v>199</v>
+      </c>
+      <c r="F102">
         <v>38502</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
@@ -4297,14 +4705,14 @@
       <c r="Q102" s="2"/>
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
-      <c r="T102" s="4"/>
-      <c r="U102" s="4"/>
       <c r="V102" s="2"/>
       <c r="W102" s="2"/>
-      <c r="X102" s="2"/>
-    </row>
-    <row r="103" spans="1:24">
-      <c r="A103" s="4">
+      <c r="X102" s="5"/>
+      <c r="Y102" s="5"/>
+      <c r="Z102" s="5"/>
+    </row>
+    <row r="103" spans="1:26">
+      <c r="A103">
         <v>928</v>
       </c>
       <c r="B103" s="3">
@@ -4314,21 +4722,21 @@
         <v>46286.491307870398</v>
       </c>
       <c r="D103" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F103" s="4">
+        <v>162</v>
+      </c>
+      <c r="F103">
         <v>43070</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
       <c r="J103" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K103" s="2"/>
       <c r="L103" s="2"/>
@@ -4339,14 +4747,14 @@
       <c r="Q103" s="2"/>
       <c r="R103" s="2"/>
       <c r="S103" s="2"/>
-      <c r="T103" s="4"/>
-      <c r="U103" s="4"/>
       <c r="V103" s="2"/>
       <c r="W103" s="2"/>
-      <c r="X103" s="2"/>
-    </row>
-    <row r="104" spans="1:24">
-      <c r="A104" s="4">
+      <c r="X103" s="5"/>
+      <c r="Y103" s="5"/>
+      <c r="Z103" s="5"/>
+    </row>
+    <row r="104" spans="1:26">
+      <c r="A104">
         <v>929</v>
       </c>
       <c r="B104" s="3">
@@ -4356,22 +4764,22 @@
         <v>46286.4919212963</v>
       </c>
       <c r="D104" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F104" s="4">
+        <v>162</v>
+      </c>
+      <c r="F104">
         <v>43070</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
       <c r="K104" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="L104" s="2"/>
       <c r="M104" s="2"/>
@@ -4381,14 +4789,14 @@
       <c r="Q104" s="2"/>
       <c r="R104" s="2"/>
       <c r="S104" s="2"/>
-      <c r="T104" s="4"/>
-      <c r="U104" s="4"/>
       <c r="V104" s="2"/>
       <c r="W104" s="2"/>
-      <c r="X104" s="2"/>
-    </row>
-    <row r="105" spans="1:24">
-      <c r="A105" s="4">
+      <c r="X104" s="5"/>
+      <c r="Y104" s="5"/>
+      <c r="Z104" s="5"/>
+    </row>
+    <row r="105" spans="1:26">
+      <c r="A105">
         <v>930</v>
       </c>
       <c r="B105" s="3">
@@ -4398,16 +4806,16 @@
         <v>46286.492511574099</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F105" s="4">
+        <v>162</v>
+      </c>
+      <c r="F105">
         <v>43070</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
@@ -4415,24 +4823,24 @@
       <c r="K105" s="2"/>
       <c r="L105" s="2"/>
       <c r="M105" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
       <c r="Q105" s="2"/>
       <c r="R105" s="2"/>
       <c r="S105" s="2"/>
-      <c r="T105" s="4"/>
-      <c r="U105" s="4"/>
       <c r="V105" s="2"/>
       <c r="W105" s="2"/>
-      <c r="X105" s="2"/>
-    </row>
-    <row r="106" spans="1:24">
-      <c r="A106" s="4">
+      <c r="X105" s="5"/>
+      <c r="Y105" s="5"/>
+      <c r="Z105" s="5"/>
+    </row>
+    <row r="106" spans="1:26">
+      <c r="A106">
         <v>931</v>
       </c>
       <c r="B106" s="3">
@@ -4442,23 +4850,23 @@
         <v>46286.493483796301</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="F106" s="4">
+        <v>216</v>
+      </c>
+      <c r="F106">
         <v>38657</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -4467,14 +4875,14 @@
       <c r="Q106" s="2"/>
       <c r="R106" s="2"/>
       <c r="S106" s="2"/>
-      <c r="T106" s="4"/>
-      <c r="U106" s="4"/>
       <c r="V106" s="2"/>
       <c r="W106" s="2"/>
-      <c r="X106" s="2"/>
-    </row>
-    <row r="107" spans="1:24">
-      <c r="A107" s="4">
+      <c r="X106" s="5"/>
+      <c r="Y106" s="5"/>
+      <c r="Z106" s="5"/>
+    </row>
+    <row r="107" spans="1:26">
+      <c r="A107">
         <v>932</v>
       </c>
       <c r="B107" s="3">
@@ -4484,23 +4892,23 @@
         <v>46286.495289351798</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F107" s="4">
+        <v>219</v>
+      </c>
+      <c r="F107">
         <v>38855</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H107" s="2"/>
       <c r="I107" s="2"/>
       <c r="J107" s="2"/>
       <c r="K107" s="2"/>
       <c r="L107" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
@@ -4509,14 +4917,14 @@
       <c r="Q107" s="2"/>
       <c r="R107" s="2"/>
       <c r="S107" s="2"/>
-      <c r="T107" s="4"/>
-      <c r="U107" s="4"/>
       <c r="V107" s="2"/>
       <c r="W107" s="2"/>
-      <c r="X107" s="2"/>
-    </row>
-    <row r="108" spans="1:24">
-      <c r="A108" s="4">
+      <c r="X107" s="5"/>
+      <c r="Y107" s="5"/>
+      <c r="Z107" s="5"/>
+    </row>
+    <row r="108" spans="1:26">
+      <c r="A108">
         <v>933</v>
       </c>
       <c r="B108" s="3">
@@ -4526,22 +4934,22 @@
         <v>46286.497175925899</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F108" s="4">
+        <v>222</v>
+      </c>
+      <c r="F108">
         <v>38659</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I108" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="J108" s="2"/>
       <c r="K108" s="2"/>
@@ -4553,14 +4961,14 @@
       <c r="Q108" s="2"/>
       <c r="R108" s="2"/>
       <c r="S108" s="2"/>
-      <c r="T108" s="4"/>
-      <c r="U108" s="4"/>
       <c r="V108" s="2"/>
       <c r="W108" s="2"/>
-      <c r="X108" s="2"/>
-    </row>
-    <row r="109" spans="1:24">
-      <c r="A109" s="4">
+      <c r="X108" s="5"/>
+      <c r="Y108" s="5"/>
+      <c r="Z108" s="5"/>
+    </row>
+    <row r="109" spans="1:26">
+      <c r="A109">
         <v>934</v>
       </c>
       <c r="B109" s="3">
@@ -4570,16 +4978,16 @@
         <v>46286.497870370396</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F109" s="4">
+        <v>162</v>
+      </c>
+      <c r="F109">
         <v>43070</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
@@ -4589,20 +4997,20 @@
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
       <c r="O109" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="P109" s="2"/>
       <c r="Q109" s="2"/>
       <c r="R109" s="2"/>
       <c r="S109" s="2"/>
-      <c r="T109" s="4"/>
-      <c r="U109" s="4"/>
       <c r="V109" s="2"/>
       <c r="W109" s="2"/>
-      <c r="X109" s="2"/>
-    </row>
-    <row r="110" spans="1:24">
-      <c r="A110" s="4">
+      <c r="X109" s="5"/>
+      <c r="Y109" s="5"/>
+      <c r="Z109" s="5"/>
+    </row>
+    <row r="110" spans="1:26">
+      <c r="A110">
         <v>935</v>
       </c>
       <c r="B110" s="3">
@@ -4612,23 +5020,23 @@
         <v>46286.498495370397</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F110" s="4">
+        <v>226</v>
+      </c>
+      <c r="F110">
         <v>38569</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
       <c r="J110" s="2"/>
       <c r="K110" s="2"/>
       <c r="L110" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
@@ -4637,14 +5045,14 @@
       <c r="Q110" s="2"/>
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
-      <c r="T110" s="4"/>
-      <c r="U110" s="4"/>
       <c r="V110" s="2"/>
       <c r="W110" s="2"/>
-      <c r="X110" s="2"/>
-    </row>
-    <row r="111" spans="1:24">
-      <c r="A111" s="4">
+      <c r="X110" s="5"/>
+      <c r="Y110" s="5"/>
+      <c r="Z110" s="5"/>
+    </row>
+    <row r="111" spans="1:26">
+      <c r="A111">
         <v>936</v>
       </c>
       <c r="B111" s="3">
@@ -4654,21 +5062,21 @@
         <v>46286.503865740699</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F111" s="4">
+        <v>199</v>
+      </c>
+      <c r="F111">
         <v>38502</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
       <c r="J111" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
@@ -4679,14 +5087,14 @@
       <c r="Q111" s="2"/>
       <c r="R111" s="2"/>
       <c r="S111" s="2"/>
-      <c r="T111" s="4"/>
-      <c r="U111" s="4"/>
       <c r="V111" s="2"/>
       <c r="W111" s="2"/>
-      <c r="X111" s="2"/>
-    </row>
-    <row r="112" spans="1:24">
-      <c r="A112" s="4">
+      <c r="X111" s="5"/>
+      <c r="Y111" s="5"/>
+      <c r="Z111" s="5"/>
+    </row>
+    <row r="112" spans="1:26">
+      <c r="A112">
         <v>937</v>
       </c>
       <c r="B112" s="3">
@@ -4696,16 +5104,16 @@
         <v>46286.505370370403</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F112" s="4">
+        <v>230</v>
+      </c>
+      <c r="F112">
         <v>38129</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
@@ -4719,14 +5127,14 @@
       <c r="Q112" s="2"/>
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
-      <c r="T112" s="4"/>
-      <c r="U112" s="4"/>
       <c r="V112" s="2"/>
       <c r="W112" s="2"/>
-      <c r="X112" s="2"/>
-    </row>
-    <row r="113" spans="1:24">
-      <c r="A113" s="4">
+      <c r="X112" s="5"/>
+      <c r="Y112" s="5"/>
+      <c r="Z112" s="5"/>
+    </row>
+    <row r="113" spans="1:26">
+      <c r="A113">
         <v>938</v>
       </c>
       <c r="B113" s="3">
@@ -4736,16 +5144,16 @@
         <v>46286.505509259303</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F113" s="4">
+        <v>162</v>
+      </c>
+      <c r="F113">
         <v>43070</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
@@ -4756,19 +5164,19 @@
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Q113" s="2"/>
       <c r="R113" s="2"/>
       <c r="S113" s="2"/>
-      <c r="T113" s="4"/>
-      <c r="U113" s="4"/>
       <c r="V113" s="2"/>
       <c r="W113" s="2"/>
-      <c r="X113" s="2"/>
-    </row>
-    <row r="114" spans="1:24">
-      <c r="A114" s="4">
+      <c r="X113" s="5"/>
+      <c r="Y113" s="5"/>
+      <c r="Z113" s="5"/>
+    </row>
+    <row r="114" spans="1:26">
+      <c r="A114">
         <v>939</v>
       </c>
       <c r="B114" s="3">
@@ -4778,22 +5186,22 @@
         <v>46286.505532407398</v>
       </c>
       <c r="D114" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F114" s="4">
+        <v>199</v>
+      </c>
+      <c r="F114">
         <v>38502</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
       <c r="K114" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="L114" s="2"/>
       <c r="M114" s="2"/>
@@ -4803,14 +5211,14 @@
       <c r="Q114" s="2"/>
       <c r="R114" s="2"/>
       <c r="S114" s="2"/>
-      <c r="T114" s="4"/>
-      <c r="U114" s="4"/>
       <c r="V114" s="2"/>
       <c r="W114" s="2"/>
-      <c r="X114" s="2"/>
-    </row>
-    <row r="115" spans="1:24">
-      <c r="A115" s="4">
+      <c r="X114" s="5"/>
+      <c r="Y114" s="5"/>
+      <c r="Z114" s="5"/>
+    </row>
+    <row r="115" spans="1:26">
+      <c r="A115">
         <v>940</v>
       </c>
       <c r="B115" s="3">
@@ -4820,23 +5228,23 @@
         <v>46286.5059259259</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F115" s="4">
+        <v>199</v>
+      </c>
+      <c r="F115">
         <v>38502</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
       <c r="L115" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
@@ -4845,14 +5253,14 @@
       <c r="Q115" s="2"/>
       <c r="R115" s="2"/>
       <c r="S115" s="2"/>
-      <c r="T115" s="4"/>
-      <c r="U115" s="4"/>
       <c r="V115" s="2"/>
       <c r="W115" s="2"/>
-      <c r="X115" s="2"/>
-    </row>
-    <row r="116" spans="1:24">
-      <c r="A116" s="4">
+      <c r="X115" s="5"/>
+      <c r="Y115" s="5"/>
+      <c r="Z115" s="5"/>
+    </row>
+    <row r="116" spans="1:26">
+      <c r="A116">
         <v>941</v>
       </c>
       <c r="B116" s="3">
@@ -4862,16 +5270,16 @@
         <v>46286.5062384259</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="F116" s="4">
+        <v>230</v>
+      </c>
+      <c r="F116">
         <v>38129</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
@@ -4885,14 +5293,14 @@
       <c r="Q116" s="2"/>
       <c r="R116" s="2"/>
       <c r="S116" s="2"/>
-      <c r="T116" s="4"/>
-      <c r="U116" s="4"/>
       <c r="V116" s="2"/>
       <c r="W116" s="2"/>
-      <c r="X116" s="2"/>
-    </row>
-    <row r="117" spans="1:24">
-      <c r="A117" s="4">
+      <c r="X116" s="5"/>
+      <c r="Y116" s="5"/>
+      <c r="Z116" s="5"/>
+    </row>
+    <row r="117" spans="1:26">
+      <c r="A117">
         <v>942</v>
       </c>
       <c r="B117" s="3">
@@ -4902,16 +5310,16 @@
         <v>46286.5062847222</v>
       </c>
       <c r="D117" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F117" s="4">
+        <v>199</v>
+      </c>
+      <c r="F117">
         <v>38502</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
@@ -4921,20 +5329,20 @@
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
       <c r="O117" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="P117" s="2"/>
       <c r="Q117" s="2"/>
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
-      <c r="T117" s="4"/>
-      <c r="U117" s="4"/>
       <c r="V117" s="2"/>
       <c r="W117" s="2"/>
-      <c r="X117" s="2"/>
-    </row>
-    <row r="118" spans="1:24">
-      <c r="A118" s="4">
+      <c r="X117" s="5"/>
+      <c r="Y117" s="5"/>
+      <c r="Z117" s="5"/>
+    </row>
+    <row r="118" spans="1:26">
+      <c r="A118">
         <v>943</v>
       </c>
       <c r="B118" s="3">
@@ -4944,16 +5352,16 @@
         <v>46286.508009259298</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F118" s="4">
+        <v>199</v>
+      </c>
+      <c r="F118">
         <v>38502</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
@@ -4964,19 +5372,19 @@
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
       <c r="P118" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="Q118" s="2"/>
       <c r="R118" s="2"/>
       <c r="S118" s="2"/>
-      <c r="T118" s="4"/>
-      <c r="U118" s="4"/>
       <c r="V118" s="2"/>
       <c r="W118" s="2"/>
-      <c r="X118" s="2"/>
-    </row>
-    <row r="119" spans="1:24">
-      <c r="A119" s="4">
+      <c r="X118" s="5"/>
+      <c r="Y118" s="5"/>
+      <c r="Z118" s="5"/>
+    </row>
+    <row r="119" spans="1:26">
+      <c r="A119">
         <v>944</v>
       </c>
       <c r="B119" s="3">
@@ -4986,16 +5394,16 @@
         <v>46286.508738425902</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F119" s="4">
+        <v>162</v>
+      </c>
+      <c r="F119">
         <v>43070</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H119" s="2"/>
       <c r="I119" s="2"/>
@@ -5006,23 +5414,23 @@
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
-      <c r="Q119" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="R119" s="5" t="s">
-        <v>234</v>
+      <c r="Q119" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R119" s="4" t="s">
+        <v>236</v>
       </c>
       <c r="S119" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="T119" s="4"/>
-      <c r="U119" s="4"/>
+        <v>237</v>
+      </c>
       <c r="V119" s="2"/>
       <c r="W119" s="2"/>
-      <c r="X119" s="2"/>
-    </row>
-    <row r="120" spans="1:24">
-      <c r="A120" s="4">
+      <c r="X119" s="5"/>
+      <c r="Y119" s="5"/>
+      <c r="Z119" s="5"/>
+    </row>
+    <row r="120" spans="1:26">
+      <c r="A120">
         <v>945</v>
       </c>
       <c r="B120" s="3">
@@ -5032,16 +5440,16 @@
         <v>46286.508993055599</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F120" s="4">
+        <v>199</v>
+      </c>
+      <c r="F120">
         <v>38502</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
@@ -5052,23 +5460,23 @@
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
-      <c r="Q120" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="R120" s="5" t="s">
-        <v>77</v>
+      <c r="Q120" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R120" s="4" t="s">
+        <v>79</v>
       </c>
       <c r="S120" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="T120" s="4"/>
-      <c r="U120" s="4"/>
+        <v>238</v>
+      </c>
       <c r="V120" s="2"/>
       <c r="W120" s="2"/>
-      <c r="X120" s="2"/>
-    </row>
-    <row r="121" spans="1:24">
-      <c r="A121" s="4">
+      <c r="X120" s="5"/>
+      <c r="Y120" s="5"/>
+      <c r="Z120" s="5"/>
+    </row>
+    <row r="121" spans="1:26">
+      <c r="A121">
         <v>946</v>
       </c>
       <c r="B121" s="3">
@@ -5078,16 +5486,16 @@
         <v>46286.510370370401</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F121" s="4">
+        <v>162</v>
+      </c>
+      <c r="F121">
         <v>43070</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
@@ -5101,14 +5509,14 @@
       <c r="Q121" s="2"/>
       <c r="R121" s="2"/>
       <c r="S121" s="2"/>
-      <c r="T121" s="4"/>
-      <c r="U121" s="4"/>
       <c r="V121" s="2"/>
       <c r="W121" s="2"/>
-      <c r="X121" s="2"/>
-    </row>
-    <row r="122" spans="1:24">
-      <c r="A122" s="4">
+      <c r="X121" s="5"/>
+      <c r="Y121" s="5"/>
+      <c r="Z121" s="5"/>
+    </row>
+    <row r="122" spans="1:26">
+      <c r="A122">
         <v>947</v>
       </c>
       <c r="B122" s="3">
@@ -5118,16 +5526,16 @@
         <v>46286.510763888902</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F122" s="4">
+        <v>240</v>
+      </c>
+      <c r="F122">
         <v>38447</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
@@ -5141,14 +5549,14 @@
       <c r="Q122" s="2"/>
       <c r="R122" s="2"/>
       <c r="S122" s="2"/>
-      <c r="T122" s="4"/>
-      <c r="U122" s="4"/>
       <c r="V122" s="2"/>
       <c r="W122" s="2"/>
-      <c r="X122" s="2"/>
-    </row>
-    <row r="123" spans="1:24">
-      <c r="A123" s="4">
+      <c r="X122" s="5"/>
+      <c r="Y122" s="5"/>
+      <c r="Z122" s="5"/>
+    </row>
+    <row r="123" spans="1:26">
+      <c r="A123">
         <v>948</v>
       </c>
       <c r="B123" s="3">
@@ -5158,23 +5566,23 @@
         <v>46286.514999999999</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="F123" s="4">
+        <v>242</v>
+      </c>
+      <c r="F123">
         <v>38567</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
       <c r="L123" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
@@ -5183,14 +5591,14 @@
       <c r="Q123" s="2"/>
       <c r="R123" s="2"/>
       <c r="S123" s="2"/>
-      <c r="T123" s="4"/>
-      <c r="U123" s="4"/>
       <c r="V123" s="2"/>
       <c r="W123" s="2"/>
-      <c r="X123" s="2"/>
-    </row>
-    <row r="124" spans="1:24">
-      <c r="A124" s="4">
+      <c r="X123" s="5"/>
+      <c r="Y123" s="5"/>
+      <c r="Z123" s="5"/>
+    </row>
+    <row r="124" spans="1:26">
+      <c r="A124">
         <v>949</v>
       </c>
       <c r="B124" s="3">
@@ -5200,16 +5608,16 @@
         <v>46286.515381944402</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="F124" s="4">
+        <v>162</v>
+      </c>
+      <c r="F124">
         <v>43070</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
@@ -5223,18 +5631,18 @@
       <c r="Q124" s="2"/>
       <c r="R124" s="2"/>
       <c r="S124" s="2"/>
-      <c r="T124" s="4"/>
-      <c r="U124" s="4"/>
-      <c r="V124" s="2"/>
+      <c r="V124" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="W124" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="X124" s="2" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="125" spans="1:24">
-      <c r="A125" s="4">
+        <v>245</v>
+      </c>
+      <c r="X124" s="5"/>
+      <c r="Y124" s="5"/>
+      <c r="Z124" s="5"/>
+    </row>
+    <row r="125" spans="1:26">
+      <c r="A125">
         <v>950</v>
       </c>
       <c r="B125" s="3">
@@ -5244,23 +5652,23 @@
         <v>46286.516493055598</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F125" s="4">
+        <v>247</v>
+      </c>
+      <c r="F125">
         <v>43026</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
       <c r="L125" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -5269,14 +5677,14 @@
       <c r="Q125" s="2"/>
       <c r="R125" s="2"/>
       <c r="S125" s="2"/>
-      <c r="T125" s="4"/>
-      <c r="U125" s="4"/>
       <c r="V125" s="2"/>
       <c r="W125" s="2"/>
-      <c r="X125" s="2"/>
-    </row>
-    <row r="126" spans="1:24">
-      <c r="A126" s="4">
+      <c r="X125" s="5"/>
+      <c r="Y125" s="5"/>
+      <c r="Z125" s="5"/>
+    </row>
+    <row r="126" spans="1:26">
+      <c r="A126">
         <v>951</v>
       </c>
       <c r="B126" s="3">
@@ -5286,23 +5694,23 @@
         <v>46286.517048611102</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="F126" s="4">
+        <v>250</v>
+      </c>
+      <c r="F126">
         <v>38375</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -5311,14 +5719,14 @@
       <c r="Q126" s="2"/>
       <c r="R126" s="2"/>
       <c r="S126" s="2"/>
-      <c r="T126" s="4"/>
-      <c r="U126" s="4"/>
       <c r="V126" s="2"/>
       <c r="W126" s="2"/>
-      <c r="X126" s="2"/>
-    </row>
-    <row r="127" spans="1:24">
-      <c r="A127" s="4">
+      <c r="X126" s="5"/>
+      <c r="Y126" s="5"/>
+      <c r="Z126" s="5"/>
+    </row>
+    <row r="127" spans="1:26">
+      <c r="A127">
         <v>952</v>
       </c>
       <c r="B127" s="3">
@@ -5328,23 +5736,23 @@
         <v>46286.519918981503</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F127" s="4">
+        <v>253</v>
+      </c>
+      <c r="F127">
         <v>38801</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H127" s="2"/>
       <c r="I127" s="2"/>
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
       <c r="L127" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
@@ -5353,14 +5761,14 @@
       <c r="Q127" s="2"/>
       <c r="R127" s="2"/>
       <c r="S127" s="2"/>
-      <c r="T127" s="4"/>
-      <c r="U127" s="4"/>
       <c r="V127" s="2"/>
       <c r="W127" s="2"/>
-      <c r="X127" s="2"/>
-    </row>
-    <row r="128" spans="1:24">
-      <c r="A128" s="4">
+      <c r="X127" s="5"/>
+      <c r="Y127" s="5"/>
+      <c r="Z127" s="5"/>
+    </row>
+    <row r="128" spans="1:26">
+      <c r="A128">
         <v>953</v>
       </c>
       <c r="B128" s="3">
@@ -5370,22 +5778,22 @@
         <v>46286.520104166702</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="F128" s="4">
+        <v>256</v>
+      </c>
+      <c r="F128">
         <v>43163</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H128" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I128" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
@@ -5397,14 +5805,14 @@
       <c r="Q128" s="2"/>
       <c r="R128" s="2"/>
       <c r="S128" s="2"/>
-      <c r="T128" s="4"/>
-      <c r="U128" s="4"/>
       <c r="V128" s="2"/>
       <c r="W128" s="2"/>
-      <c r="X128" s="2"/>
-    </row>
-    <row r="129" spans="1:24">
-      <c r="A129" s="4">
+      <c r="X128" s="5"/>
+      <c r="Y128" s="5"/>
+      <c r="Z128" s="5"/>
+    </row>
+    <row r="129" spans="1:26">
+      <c r="A129">
         <v>954</v>
       </c>
       <c r="B129" s="3">
@@ -5414,23 +5822,23 @@
         <v>46286.5206481481</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F129" s="4">
+        <v>31</v>
+      </c>
+      <c r="F129">
         <v>43164</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
       <c r="L129" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
@@ -5439,14 +5847,14 @@
       <c r="Q129" s="2"/>
       <c r="R129" s="2"/>
       <c r="S129" s="2"/>
-      <c r="T129" s="4"/>
-      <c r="U129" s="4"/>
       <c r="V129" s="2"/>
       <c r="W129" s="2"/>
-      <c r="X129" s="2"/>
-    </row>
-    <row r="130" spans="1:24">
-      <c r="A130" s="4">
+      <c r="X129" s="5"/>
+      <c r="Y129" s="5"/>
+      <c r="Z129" s="5"/>
+    </row>
+    <row r="130" spans="1:26">
+      <c r="A130">
         <v>955</v>
       </c>
       <c r="B130" s="3">
@@ -5456,16 +5864,16 @@
         <v>46286.5221296296</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="F130" s="4">
+        <v>260</v>
+      </c>
+      <c r="F130">
         <v>38615</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
@@ -5479,14 +5887,14 @@
       <c r="Q130" s="2"/>
       <c r="R130" s="2"/>
       <c r="S130" s="2"/>
-      <c r="T130" s="4"/>
-      <c r="U130" s="4"/>
       <c r="V130" s="2"/>
       <c r="W130" s="2"/>
-      <c r="X130" s="2"/>
-    </row>
-    <row r="131" spans="1:24">
-      <c r="A131" s="4">
+      <c r="X130" s="5"/>
+      <c r="Y130" s="5"/>
+      <c r="Z130" s="5"/>
+    </row>
+    <row r="131" spans="1:26">
+      <c r="A131">
         <v>956</v>
       </c>
       <c r="B131" s="3">
@@ -5496,23 +5904,23 @@
         <v>46286.522916666698</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="F131" s="4">
+        <v>222</v>
+      </c>
+      <c r="F131">
         <v>38659</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
       <c r="L131" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
@@ -5521,14 +5929,14 @@
       <c r="Q131" s="2"/>
       <c r="R131" s="2"/>
       <c r="S131" s="2"/>
-      <c r="T131" s="4"/>
-      <c r="U131" s="4"/>
       <c r="V131" s="2"/>
       <c r="W131" s="2"/>
-      <c r="X131" s="2"/>
-    </row>
-    <row r="132" spans="1:24">
-      <c r="A132" s="4">
+      <c r="X131" s="5"/>
+      <c r="Y131" s="5"/>
+      <c r="Z131" s="5"/>
+    </row>
+    <row r="132" spans="1:26">
+      <c r="A132">
         <v>957</v>
       </c>
       <c r="B132" s="3">
@@ -5538,16 +5946,16 @@
         <v>46286.5242939815</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="F132" s="4">
+        <v>253</v>
+      </c>
+      <c r="F132">
         <v>38801</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H132" s="2"/>
       <c r="I132" s="2"/>
@@ -5561,14 +5969,14 @@
       <c r="Q132" s="2"/>
       <c r="R132" s="2"/>
       <c r="S132" s="2"/>
-      <c r="T132" s="4"/>
-      <c r="U132" s="4"/>
       <c r="V132" s="2"/>
       <c r="W132" s="2"/>
-      <c r="X132" s="2"/>
-    </row>
-    <row r="133" spans="1:24">
-      <c r="A133" s="4">
+      <c r="X132" s="5"/>
+      <c r="Y132" s="5"/>
+      <c r="Z132" s="5"/>
+    </row>
+    <row r="133" spans="1:26">
+      <c r="A133">
         <v>958</v>
       </c>
       <c r="B133" s="3">
@@ -5578,16 +5986,16 @@
         <v>46286.527488425898</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F133" s="4">
+        <v>263</v>
+      </c>
+      <c r="F133">
         <v>38691</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
@@ -5601,14 +6009,14 @@
       <c r="Q133" s="2"/>
       <c r="R133" s="2"/>
       <c r="S133" s="2"/>
-      <c r="T133" s="4"/>
-      <c r="U133" s="4"/>
       <c r="V133" s="2"/>
       <c r="W133" s="2"/>
-      <c r="X133" s="2"/>
-    </row>
-    <row r="134" spans="1:24">
-      <c r="A134" s="4">
+      <c r="X133" s="5"/>
+      <c r="Y133" s="5"/>
+      <c r="Z133" s="5"/>
+    </row>
+    <row r="134" spans="1:26">
+      <c r="A134">
         <v>959</v>
       </c>
       <c r="B134" s="3">
@@ -5618,23 +6026,23 @@
         <v>46286.527997685203</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="F134" s="4">
+        <v>265</v>
+      </c>
+      <c r="F134">
         <v>38718</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
       <c r="L134" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
@@ -5643,14 +6051,14 @@
       <c r="Q134" s="2"/>
       <c r="R134" s="2"/>
       <c r="S134" s="2"/>
-      <c r="T134" s="4"/>
-      <c r="U134" s="4"/>
       <c r="V134" s="2"/>
       <c r="W134" s="2"/>
-      <c r="X134" s="2"/>
-    </row>
-    <row r="135" spans="1:24">
-      <c r="A135" s="4">
+      <c r="X134" s="5"/>
+      <c r="Y134" s="5"/>
+      <c r="Z134" s="5"/>
+    </row>
+    <row r="135" spans="1:26">
+      <c r="A135">
         <v>960</v>
       </c>
       <c r="B135" s="3">
@@ -5660,16 +6068,16 @@
         <v>46286.529050925899</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>266</v>
-      </c>
-      <c r="F135" s="4">
+        <v>268</v>
+      </c>
+      <c r="F135">
         <v>38107</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H135" s="2"/>
       <c r="I135" s="2"/>
@@ -5683,14 +6091,14 @@
       <c r="Q135" s="2"/>
       <c r="R135" s="2"/>
       <c r="S135" s="2"/>
-      <c r="T135" s="4"/>
-      <c r="U135" s="4"/>
       <c r="V135" s="2"/>
       <c r="W135" s="2"/>
-      <c r="X135" s="2"/>
-    </row>
-    <row r="136" spans="1:24">
-      <c r="A136" s="4">
+      <c r="X135" s="5"/>
+      <c r="Y135" s="5"/>
+      <c r="Z135" s="5"/>
+    </row>
+    <row r="136" spans="1:26">
+      <c r="A136">
         <v>961</v>
       </c>
       <c r="B136" s="3">
@@ -5700,16 +6108,16 @@
         <v>46286.534803240698</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F136" s="4">
+        <v>270</v>
+      </c>
+      <c r="F136">
         <v>38124</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H136" s="2"/>
       <c r="I136" s="2"/>
@@ -5723,14 +6131,14 @@
       <c r="Q136" s="2"/>
       <c r="R136" s="2"/>
       <c r="S136" s="2"/>
-      <c r="T136" s="4"/>
-      <c r="U136" s="4"/>
       <c r="V136" s="2"/>
       <c r="W136" s="2"/>
-      <c r="X136" s="2"/>
-    </row>
-    <row r="137" spans="1:24">
-      <c r="A137" s="4">
+      <c r="X136" s="5"/>
+      <c r="Y136" s="5"/>
+      <c r="Z136" s="5"/>
+    </row>
+    <row r="137" spans="1:26">
+      <c r="A137">
         <v>962</v>
       </c>
       <c r="B137" s="3">
@@ -5740,22 +6148,22 @@
         <v>46286.5360069444</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="F137" s="4">
+        <v>272</v>
+      </c>
+      <c r="F137">
         <v>38464</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H137" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="I137" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
@@ -5767,14 +6175,14 @@
       <c r="Q137" s="2"/>
       <c r="R137" s="2"/>
       <c r="S137" s="2"/>
-      <c r="T137" s="4"/>
-      <c r="U137" s="4"/>
       <c r="V137" s="2"/>
       <c r="W137" s="2"/>
-      <c r="X137" s="2"/>
-    </row>
-    <row r="138" spans="1:24">
-      <c r="A138" s="4">
+      <c r="X137" s="5"/>
+      <c r="Y137" s="5"/>
+      <c r="Z137" s="5"/>
+    </row>
+    <row r="138" spans="1:26">
+      <c r="A138">
         <v>963</v>
       </c>
       <c r="B138" s="3">
@@ -5784,16 +6192,16 @@
         <v>46286.536527777796</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F138" s="4">
+        <v>275</v>
+      </c>
+      <c r="F138">
         <v>38428</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H138" s="2"/>
       <c r="I138" s="2"/>
@@ -5807,14 +6215,14 @@
       <c r="Q138" s="2"/>
       <c r="R138" s="2"/>
       <c r="S138" s="2"/>
-      <c r="T138" s="4"/>
-      <c r="U138" s="4"/>
       <c r="V138" s="2"/>
       <c r="W138" s="2"/>
-      <c r="X138" s="2"/>
-    </row>
-    <row r="139" spans="1:24">
-      <c r="A139" s="4">
+      <c r="X138" s="5"/>
+      <c r="Y138" s="5"/>
+      <c r="Z138" s="5"/>
+    </row>
+    <row r="139" spans="1:26">
+      <c r="A139">
         <v>964</v>
       </c>
       <c r="B139" s="3">
@@ -5824,16 +6232,16 @@
         <v>46286.540520833303</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F139" s="4">
+        <v>277</v>
+      </c>
+      <c r="F139">
         <v>38571</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H139" s="2"/>
       <c r="I139" s="2"/>
@@ -5847,14 +6255,14 @@
       <c r="Q139" s="2"/>
       <c r="R139" s="2"/>
       <c r="S139" s="2"/>
-      <c r="T139" s="4"/>
-      <c r="U139" s="4"/>
       <c r="V139" s="2"/>
       <c r="W139" s="2"/>
-      <c r="X139" s="2"/>
-    </row>
-    <row r="140" spans="1:24">
-      <c r="A140" s="4">
+      <c r="X139" s="5"/>
+      <c r="Y139" s="5"/>
+      <c r="Z139" s="5"/>
+    </row>
+    <row r="140" spans="1:26">
+      <c r="A140">
         <v>965</v>
       </c>
       <c r="B140" s="3">
@@ -5864,16 +6272,16 @@
         <v>46286.549421296302</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="F140" s="4">
+        <v>209</v>
+      </c>
+      <c r="F140">
         <v>38859</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
@@ -5887,14 +6295,14 @@
       <c r="Q140" s="2"/>
       <c r="R140" s="2"/>
       <c r="S140" s="2"/>
-      <c r="T140" s="4"/>
-      <c r="U140" s="4"/>
       <c r="V140" s="2"/>
       <c r="W140" s="2"/>
-      <c r="X140" s="2"/>
-    </row>
-    <row r="141" spans="1:24">
-      <c r="A141" s="4">
+      <c r="X140" s="5"/>
+      <c r="Y140" s="5"/>
+      <c r="Z140" s="5"/>
+    </row>
+    <row r="141" spans="1:26">
+      <c r="A141">
         <v>966</v>
       </c>
       <c r="B141" s="3">
@@ -5904,23 +6312,23 @@
         <v>46286.5534259259</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F141" s="4">
+        <v>279</v>
+      </c>
+      <c r="F141">
         <v>38496</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
       <c r="L141" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
@@ -5929,14 +6337,14 @@
       <c r="Q141" s="2"/>
       <c r="R141" s="2"/>
       <c r="S141" s="2"/>
-      <c r="T141" s="4"/>
-      <c r="U141" s="4"/>
       <c r="V141" s="2"/>
       <c r="W141" s="2"/>
-      <c r="X141" s="2"/>
-    </row>
-    <row r="142" spans="1:24">
-      <c r="A142" s="4">
+      <c r="X141" s="5"/>
+      <c r="Y141" s="5"/>
+      <c r="Z141" s="5"/>
+    </row>
+    <row r="142" spans="1:26">
+      <c r="A142">
         <v>967</v>
       </c>
       <c r="B142" s="3">
@@ -5946,23 +6354,23 @@
         <v>46286.553715277798</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F142" s="4">
+        <v>282</v>
+      </c>
+      <c r="F142">
         <v>38468</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
       <c r="L142" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
@@ -5971,14 +6379,14 @@
       <c r="Q142" s="2"/>
       <c r="R142" s="2"/>
       <c r="S142" s="2"/>
-      <c r="T142" s="4"/>
-      <c r="U142" s="4"/>
       <c r="V142" s="2"/>
       <c r="W142" s="2"/>
-      <c r="X142" s="2"/>
-    </row>
-    <row r="143" spans="1:24">
-      <c r="A143" s="4">
+      <c r="X142" s="5"/>
+      <c r="Y142" s="5"/>
+      <c r="Z142" s="5"/>
+    </row>
+    <row r="143" spans="1:26">
+      <c r="A143">
         <v>968</v>
       </c>
       <c r="B143" s="3">
@@ -5988,16 +6396,16 @@
         <v>46286.556898148097</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F143" s="4">
+        <v>285</v>
+      </c>
+      <c r="F143">
         <v>38580</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H143" s="2"/>
       <c r="I143" s="2"/>
@@ -6011,14 +6419,14 @@
       <c r="Q143" s="2"/>
       <c r="R143" s="2"/>
       <c r="S143" s="2"/>
-      <c r="T143" s="4"/>
-      <c r="U143" s="4"/>
       <c r="V143" s="2"/>
       <c r="W143" s="2"/>
-      <c r="X143" s="2"/>
-    </row>
-    <row r="144" spans="1:24">
-      <c r="A144" s="4">
+      <c r="X143" s="5"/>
+      <c r="Y143" s="5"/>
+      <c r="Z143" s="5"/>
+    </row>
+    <row r="144" spans="1:26">
+      <c r="A144">
         <v>969</v>
       </c>
       <c r="B144" s="3">
@@ -6028,16 +6436,16 @@
         <v>46286.5603819444</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F144" s="4">
+        <v>287</v>
+      </c>
+      <c r="F144">
         <v>43159</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H144" s="2"/>
       <c r="I144" s="2"/>
@@ -6051,14 +6459,14 @@
       <c r="Q144" s="2"/>
       <c r="R144" s="2"/>
       <c r="S144" s="2"/>
-      <c r="T144" s="4"/>
-      <c r="U144" s="4"/>
       <c r="V144" s="2"/>
       <c r="W144" s="2"/>
-      <c r="X144" s="2"/>
-    </row>
-    <row r="145" spans="1:24">
-      <c r="A145" s="4">
+      <c r="X144" s="5"/>
+      <c r="Y144" s="5"/>
+      <c r="Z144" s="5"/>
+    </row>
+    <row r="145" spans="1:26">
+      <c r="A145">
         <v>970</v>
       </c>
       <c r="B145" s="3">
@@ -6068,16 +6476,16 @@
         <v>46286.561851851897</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F145" s="4">
+        <v>289</v>
+      </c>
+      <c r="F145">
         <v>38116</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
@@ -6091,14 +6499,14 @@
       <c r="Q145" s="2"/>
       <c r="R145" s="2"/>
       <c r="S145" s="2"/>
-      <c r="T145" s="4"/>
-      <c r="U145" s="4"/>
       <c r="V145" s="2"/>
       <c r="W145" s="2"/>
-      <c r="X145" s="2"/>
-    </row>
-    <row r="146" spans="1:24">
-      <c r="A146" s="4">
+      <c r="X145" s="5"/>
+      <c r="Y145" s="5"/>
+      <c r="Z145" s="5"/>
+    </row>
+    <row r="146" spans="1:26">
+      <c r="A146">
         <v>971</v>
       </c>
       <c r="B146" s="3">
@@ -6108,23 +6516,23 @@
         <v>46286.692245370403</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="F146" s="4">
+        <v>291</v>
+      </c>
+      <c r="F146">
         <v>38429</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
@@ -6133,14 +6541,14 @@
       <c r="Q146" s="2"/>
       <c r="R146" s="2"/>
       <c r="S146" s="2"/>
-      <c r="T146" s="4"/>
-      <c r="U146" s="4"/>
       <c r="V146" s="2"/>
       <c r="W146" s="2"/>
-      <c r="X146" s="2"/>
-    </row>
-    <row r="147" spans="1:24">
-      <c r="A147" s="4">
+      <c r="X146" s="5"/>
+      <c r="Y146" s="5"/>
+      <c r="Z146" s="5"/>
+    </row>
+    <row r="147" spans="1:26">
+      <c r="A147">
         <v>972</v>
       </c>
       <c r="B147" s="3">
@@ -6150,23 +6558,23 @@
         <v>46286.781875000001</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F147" s="4">
+        <v>294</v>
+      </c>
+      <c r="F147">
         <v>43034</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
       <c r="L147" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
@@ -6175,14 +6583,14 @@
       <c r="Q147" s="2"/>
       <c r="R147" s="2"/>
       <c r="S147" s="2"/>
-      <c r="T147" s="4"/>
-      <c r="U147" s="4"/>
       <c r="V147" s="2"/>
       <c r="W147" s="2"/>
-      <c r="X147" s="2"/>
-    </row>
-    <row r="148" spans="1:24">
-      <c r="A148" s="4">
+      <c r="X147" s="5"/>
+      <c r="Y147" s="5"/>
+      <c r="Z147" s="5"/>
+    </row>
+    <row r="148" spans="1:26">
+      <c r="A148">
         <v>973</v>
       </c>
       <c r="B148" s="3">
@@ -6192,23 +6600,23 @@
         <v>46286.974409722199</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F148" s="4">
+        <v>297</v>
+      </c>
+      <c r="F148">
         <v>38570</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
@@ -6217,14 +6625,14 @@
       <c r="Q148" s="2"/>
       <c r="R148" s="2"/>
       <c r="S148" s="2"/>
-      <c r="T148" s="4"/>
-      <c r="U148" s="4"/>
       <c r="V148" s="2"/>
       <c r="W148" s="2"/>
-      <c r="X148" s="2"/>
-    </row>
-    <row r="149" spans="1:24">
-      <c r="A149" s="4">
+      <c r="X148" s="5"/>
+      <c r="Y148" s="5"/>
+      <c r="Z148" s="5"/>
+    </row>
+    <row r="149" spans="1:26">
+      <c r="A149">
         <v>974</v>
       </c>
       <c r="B149" s="3">
@@ -6234,23 +6642,23 @@
         <v>46287.578206018501</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F149" s="4">
+        <v>300</v>
+      </c>
+      <c r="F149">
         <v>38472</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
       <c r="J149" s="2"/>
       <c r="K149" s="2"/>
       <c r="L149" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="M149" s="2"/>
       <c r="N149" s="2"/>
@@ -6259,14 +6667,14 @@
       <c r="Q149" s="2"/>
       <c r="R149" s="2"/>
       <c r="S149" s="2"/>
-      <c r="T149" s="4"/>
-      <c r="U149" s="4"/>
       <c r="V149" s="2"/>
       <c r="W149" s="2"/>
-      <c r="X149" s="2"/>
-    </row>
-    <row r="150" spans="1:24">
-      <c r="A150" s="4">
+      <c r="X149" s="5"/>
+      <c r="Y149" s="5"/>
+      <c r="Z149" s="5"/>
+    </row>
+    <row r="150" spans="1:26">
+      <c r="A150">
         <v>975</v>
       </c>
       <c r="B150" s="3">
@@ -6276,23 +6684,23 @@
         <v>46287.578726851803</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F150" s="4">
+        <v>300</v>
+      </c>
+      <c r="F150">
         <v>38472</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
       <c r="J150" s="2"/>
       <c r="K150" s="2"/>
       <c r="L150" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M150" s="2"/>
       <c r="N150" s="2"/>
@@ -6301,14 +6709,14 @@
       <c r="Q150" s="2"/>
       <c r="R150" s="2"/>
       <c r="S150" s="2"/>
-      <c r="T150" s="4"/>
-      <c r="U150" s="4"/>
       <c r="V150" s="2"/>
       <c r="W150" s="2"/>
-      <c r="X150" s="2"/>
-    </row>
-    <row r="151" spans="1:24">
-      <c r="A151" s="4">
+      <c r="X150" s="5"/>
+      <c r="Y150" s="5"/>
+      <c r="Z150" s="5"/>
+    </row>
+    <row r="151" spans="1:26">
+      <c r="A151">
         <v>976</v>
       </c>
       <c r="B151" s="3">
@@ -6318,23 +6726,23 @@
         <v>46287.579120370399</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F151" s="4">
+        <v>300</v>
+      </c>
+      <c r="F151">
         <v>38472</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
       <c r="J151" s="2"/>
       <c r="K151" s="2"/>
       <c r="L151" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="M151" s="2"/>
       <c r="N151" s="2"/>
@@ -6343,14 +6751,14 @@
       <c r="Q151" s="2"/>
       <c r="R151" s="2"/>
       <c r="S151" s="2"/>
-      <c r="T151" s="4"/>
-      <c r="U151" s="4"/>
       <c r="V151" s="2"/>
       <c r="W151" s="2"/>
-      <c r="X151" s="2"/>
-    </row>
-    <row r="152" spans="1:24">
-      <c r="A152" s="4">
+      <c r="X151" s="5"/>
+      <c r="Y151" s="5"/>
+      <c r="Z151" s="5"/>
+    </row>
+    <row r="152" spans="1:26">
+      <c r="A152">
         <v>977</v>
       </c>
       <c r="B152" s="3">
@@ -6360,23 +6768,23 @@
         <v>46287.579409722202</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F152" s="4">
+        <v>300</v>
+      </c>
+      <c r="F152">
         <v>38472</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
       <c r="J152" s="2"/>
       <c r="K152" s="2"/>
       <c r="L152" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M152" s="2"/>
       <c r="N152" s="2"/>
@@ -6385,14 +6793,14 @@
       <c r="Q152" s="2"/>
       <c r="R152" s="2"/>
       <c r="S152" s="2"/>
-      <c r="T152" s="4"/>
-      <c r="U152" s="4"/>
       <c r="V152" s="2"/>
       <c r="W152" s="2"/>
-      <c r="X152" s="2"/>
-    </row>
-    <row r="153" spans="1:24">
-      <c r="A153" s="4">
+      <c r="X152" s="5"/>
+      <c r="Y152" s="5"/>
+      <c r="Z152" s="5"/>
+    </row>
+    <row r="153" spans="1:26">
+      <c r="A153">
         <v>978</v>
       </c>
       <c r="B153" s="3">
@@ -6402,23 +6810,23 @@
         <v>46287.579664351899</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F153" s="4">
+        <v>300</v>
+      </c>
+      <c r="F153">
         <v>38472</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
       <c r="J153" s="2"/>
       <c r="K153" s="2"/>
       <c r="L153" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="M153" s="2"/>
       <c r="N153" s="2"/>
@@ -6427,14 +6835,14 @@
       <c r="Q153" s="2"/>
       <c r="R153" s="2"/>
       <c r="S153" s="2"/>
-      <c r="T153" s="4"/>
-      <c r="U153" s="4"/>
       <c r="V153" s="2"/>
       <c r="W153" s="2"/>
-      <c r="X153" s="2"/>
-    </row>
-    <row r="154" spans="1:24">
-      <c r="A154" s="4">
+      <c r="X153" s="5"/>
+      <c r="Y153" s="5"/>
+      <c r="Z153" s="5"/>
+    </row>
+    <row r="154" spans="1:26">
+      <c r="A154">
         <v>979</v>
       </c>
       <c r="B154" s="3">
@@ -6444,23 +6852,23 @@
         <v>46287.727974537003</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F154" s="4">
+        <v>275</v>
+      </c>
+      <c r="F154">
         <v>38428</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
       <c r="J154" s="2"/>
       <c r="K154" s="2"/>
       <c r="L154" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="M154" s="2"/>
       <c r="N154" s="2"/>
@@ -6469,14 +6877,14 @@
       <c r="Q154" s="2"/>
       <c r="R154" s="2"/>
       <c r="S154" s="2"/>
-      <c r="T154" s="4"/>
-      <c r="U154" s="4"/>
       <c r="V154" s="2"/>
       <c r="W154" s="2"/>
-      <c r="X154" s="2"/>
-    </row>
-    <row r="155" spans="1:24">
-      <c r="A155" s="4">
+      <c r="X154" s="5"/>
+      <c r="Y154" s="5"/>
+      <c r="Z154" s="5"/>
+    </row>
+    <row r="155" spans="1:26">
+      <c r="A155">
         <v>980</v>
       </c>
       <c r="B155" s="3">
@@ -6486,23 +6894,23 @@
         <v>46287.825254629599</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F155" s="4">
+        <v>240</v>
+      </c>
+      <c r="F155">
         <v>38447</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
       <c r="J155" s="2"/>
       <c r="K155" s="2"/>
       <c r="L155" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M155" s="2"/>
       <c r="N155" s="2"/>
@@ -6511,14 +6919,14 @@
       <c r="Q155" s="2"/>
       <c r="R155" s="2"/>
       <c r="S155" s="2"/>
-      <c r="T155" s="4"/>
-      <c r="U155" s="4"/>
       <c r="V155" s="2"/>
       <c r="W155" s="2"/>
-      <c r="X155" s="2"/>
-    </row>
-    <row r="156" spans="1:24">
-      <c r="A156" s="4">
+      <c r="X155" s="5"/>
+      <c r="Y155" s="5"/>
+      <c r="Z155" s="5"/>
+    </row>
+    <row r="156" spans="1:26">
+      <c r="A156">
         <v>981</v>
       </c>
       <c r="B156" s="3">
@@ -6528,23 +6936,23 @@
         <v>46287.864837963003</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="F156" s="4">
+        <v>263</v>
+      </c>
+      <c r="F156">
         <v>38691</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
       <c r="J156" s="2"/>
       <c r="K156" s="2"/>
       <c r="L156" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="M156" s="2"/>
       <c r="N156" s="2"/>
@@ -6553,14 +6961,14 @@
       <c r="Q156" s="2"/>
       <c r="R156" s="2"/>
       <c r="S156" s="2"/>
-      <c r="T156" s="4"/>
-      <c r="U156" s="4"/>
       <c r="V156" s="2"/>
       <c r="W156" s="2"/>
-      <c r="X156" s="2"/>
-    </row>
-    <row r="157" spans="1:24">
-      <c r="A157" s="4">
+      <c r="X156" s="5"/>
+      <c r="Y156" s="5"/>
+      <c r="Z156" s="5"/>
+    </row>
+    <row r="157" spans="1:26">
+      <c r="A157">
         <v>982</v>
       </c>
       <c r="B157" s="3">
@@ -6570,23 +6978,23 @@
         <v>46287.882569444402</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F157" s="4">
+        <v>289</v>
+      </c>
+      <c r="F157">
         <v>38116</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
       <c r="L157" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
@@ -6595,14 +7003,14 @@
       <c r="Q157" s="2"/>
       <c r="R157" s="2"/>
       <c r="S157" s="2"/>
-      <c r="T157" s="4"/>
-      <c r="U157" s="4"/>
       <c r="V157" s="2"/>
       <c r="W157" s="2"/>
-      <c r="X157" s="2"/>
-    </row>
-    <row r="158" spans="1:24">
-      <c r="A158" s="4">
+      <c r="X157" s="5"/>
+      <c r="Y157" s="5"/>
+      <c r="Z157" s="5"/>
+    </row>
+    <row r="158" spans="1:26">
+      <c r="A158">
         <v>983</v>
       </c>
       <c r="B158" s="3">
@@ -6612,23 +7020,23 @@
         <v>46288.395624999997</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="F158" s="4">
+        <v>311</v>
+      </c>
+      <c r="F158">
         <v>38678</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
       <c r="L158" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
@@ -6637,14 +7045,14 @@
       <c r="Q158" s="2"/>
       <c r="R158" s="2"/>
       <c r="S158" s="2"/>
-      <c r="T158" s="4"/>
-      <c r="U158" s="4"/>
       <c r="V158" s="2"/>
       <c r="W158" s="2"/>
-      <c r="X158" s="2"/>
-    </row>
-    <row r="159" spans="1:24">
-      <c r="A159" s="4">
+      <c r="X158" s="5"/>
+      <c r="Y158" s="5"/>
+      <c r="Z158" s="5"/>
+    </row>
+    <row r="159" spans="1:26">
+      <c r="A159">
         <v>984</v>
       </c>
       <c r="B159" s="3">
@@ -6654,23 +7062,23 @@
         <v>46288.494097222203</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="F159" s="4">
+        <v>314</v>
+      </c>
+      <c r="F159">
         <v>3850</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
       <c r="L159" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
@@ -6679,14 +7087,14 @@
       <c r="Q159" s="2"/>
       <c r="R159" s="2"/>
       <c r="S159" s="2"/>
-      <c r="T159" s="4"/>
-      <c r="U159" s="4"/>
       <c r="V159" s="2"/>
       <c r="W159" s="2"/>
-      <c r="X159" s="2"/>
-    </row>
-    <row r="160" spans="1:24">
-      <c r="A160" s="4">
+      <c r="X159" s="5"/>
+      <c r="Y159" s="5"/>
+      <c r="Z159" s="5"/>
+    </row>
+    <row r="160" spans="1:26">
+      <c r="A160">
         <v>985</v>
       </c>
       <c r="B160" s="3">
@@ -6696,16 +7104,16 @@
         <v>46288.545266203699</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F160" s="4">
+        <v>317</v>
+      </c>
+      <c r="F160">
         <v>38590</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
@@ -6716,23 +7124,23 @@
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
-      <c r="Q160" s="5" t="s">
-        <v>77</v>
-      </c>
-      <c r="R160" s="5" t="s">
-        <v>76</v>
+      <c r="Q160" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R160" s="4" t="s">
+        <v>78</v>
       </c>
       <c r="S160" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="T160" s="4"/>
-      <c r="U160" s="4"/>
+        <v>318</v>
+      </c>
       <c r="V160" s="2"/>
       <c r="W160" s="2"/>
-      <c r="X160" s="2"/>
-    </row>
-    <row r="161" spans="1:24">
-      <c r="A161" s="4">
+      <c r="X160" s="5"/>
+      <c r="Y160" s="5"/>
+      <c r="Z160" s="5"/>
+    </row>
+    <row r="161" spans="1:26">
+      <c r="A161">
         <v>986</v>
       </c>
       <c r="B161" s="3">
@@ -6742,16 +7150,16 @@
         <v>46288.549490740697</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F161" s="4">
+        <v>317</v>
+      </c>
+      <c r="F161">
         <v>38590</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
@@ -6765,14 +7173,14 @@
       <c r="Q161" s="2"/>
       <c r="R161" s="2"/>
       <c r="S161" s="2"/>
-      <c r="T161" s="4"/>
-      <c r="U161" s="4"/>
       <c r="V161" s="2"/>
       <c r="W161" s="2"/>
-      <c r="X161" s="2"/>
-    </row>
-    <row r="162" spans="1:24">
-      <c r="A162" s="4">
+      <c r="X161" s="5"/>
+      <c r="Y161" s="5"/>
+      <c r="Z161" s="5"/>
+    </row>
+    <row r="162" spans="1:26">
+      <c r="A162">
         <v>987</v>
       </c>
       <c r="B162" s="3">
@@ -6782,22 +7190,22 @@
         <v>46288.5518981481</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F162" s="4">
+        <v>317</v>
+      </c>
+      <c r="F162">
         <v>38590</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
       <c r="K162" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
@@ -6807,14 +7215,14 @@
       <c r="Q162" s="2"/>
       <c r="R162" s="2"/>
       <c r="S162" s="2"/>
-      <c r="T162" s="4"/>
-      <c r="U162" s="4"/>
       <c r="V162" s="2"/>
       <c r="W162" s="2"/>
-      <c r="X162" s="2"/>
-    </row>
-    <row r="163" spans="1:24">
-      <c r="A163" s="4">
+      <c r="X162" s="5"/>
+      <c r="Y162" s="5"/>
+      <c r="Z162" s="5"/>
+    </row>
+    <row r="163" spans="1:26">
+      <c r="A163">
         <v>988</v>
       </c>
       <c r="B163" s="3">
@@ -6824,16 +7232,16 @@
         <v>46288.563287037003</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F163" s="4">
+        <v>285</v>
+      </c>
+      <c r="F163">
         <v>38580</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
@@ -6847,14 +7255,14 @@
       <c r="Q163" s="2"/>
       <c r="R163" s="2"/>
       <c r="S163" s="2"/>
-      <c r="T163" s="4"/>
-      <c r="U163" s="4"/>
       <c r="V163" s="2"/>
       <c r="W163" s="2"/>
-      <c r="X163" s="2"/>
-    </row>
-    <row r="164" spans="1:24">
-      <c r="A164" s="4">
+      <c r="X163" s="5"/>
+      <c r="Y163" s="5"/>
+      <c r="Z163" s="5"/>
+    </row>
+    <row r="164" spans="1:26">
+      <c r="A164">
         <v>989</v>
       </c>
       <c r="B164" s="3">
@@ -6864,16 +7272,16 @@
         <v>46288.566412036998</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="F164" s="4">
+        <v>317</v>
+      </c>
+      <c r="F164">
         <v>38590</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
@@ -6881,7 +7289,7 @@
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
       <c r="M164" s="2" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -6889,14 +7297,14 @@
       <c r="Q164" s="2"/>
       <c r="R164" s="2"/>
       <c r="S164" s="2"/>
-      <c r="T164" s="4"/>
-      <c r="U164" s="4"/>
       <c r="V164" s="2"/>
       <c r="W164" s="2"/>
-      <c r="X164" s="2"/>
-    </row>
-    <row r="165" spans="1:24">
-      <c r="A165" s="4">
+      <c r="X164" s="5"/>
+      <c r="Y164" s="5"/>
+      <c r="Z164" s="5"/>
+    </row>
+    <row r="165" spans="1:26">
+      <c r="A165">
         <v>990</v>
       </c>
       <c r="B165" s="3">
@@ -6906,21 +7314,21 @@
         <v>46288.579918981501</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F165" s="4">
+        <v>285</v>
+      </c>
+      <c r="F165">
         <v>38580</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
       <c r="J165" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="K165" s="2"/>
       <c r="L165" s="2"/>
@@ -6931,14 +7339,14 @@
       <c r="Q165" s="2"/>
       <c r="R165" s="2"/>
       <c r="S165" s="2"/>
-      <c r="T165" s="4"/>
-      <c r="U165" s="4"/>
       <c r="V165" s="2"/>
       <c r="W165" s="2"/>
-      <c r="X165" s="2"/>
-    </row>
-    <row r="166" spans="1:24">
-      <c r="A166" s="4">
+      <c r="X165" s="5"/>
+      <c r="Y165" s="5"/>
+      <c r="Z165" s="5"/>
+    </row>
+    <row r="166" spans="1:26">
+      <c r="A166">
         <v>991</v>
       </c>
       <c r="B166" s="3">
@@ -6948,22 +7356,22 @@
         <v>46288.581747685203</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F166" s="4">
+        <v>285</v>
+      </c>
+      <c r="F166">
         <v>38580</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
       <c r="K166" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" s="2"/>
@@ -6973,14 +7381,14 @@
       <c r="Q166" s="2"/>
       <c r="R166" s="2"/>
       <c r="S166" s="2"/>
-      <c r="T166" s="4"/>
-      <c r="U166" s="4"/>
       <c r="V166" s="2"/>
       <c r="W166" s="2"/>
-      <c r="X166" s="2"/>
-    </row>
-    <row r="167" spans="1:24">
-      <c r="A167" s="4">
+      <c r="X166" s="5"/>
+      <c r="Y166" s="5"/>
+      <c r="Z166" s="5"/>
+    </row>
+    <row r="167" spans="1:26">
+      <c r="A167">
         <v>992</v>
       </c>
       <c r="B167" s="3">
@@ -6990,23 +7398,23 @@
         <v>46288.585659722201</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F167" s="4">
+        <v>285</v>
+      </c>
+      <c r="F167">
         <v>38580</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
       <c r="J167" s="2"/>
       <c r="K167" s="2"/>
       <c r="L167" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M167" s="2"/>
       <c r="N167" s="2"/>
@@ -7015,14 +7423,14 @@
       <c r="Q167" s="2"/>
       <c r="R167" s="2"/>
       <c r="S167" s="2"/>
-      <c r="T167" s="4"/>
-      <c r="U167" s="4"/>
       <c r="V167" s="2"/>
       <c r="W167" s="2"/>
-      <c r="X167" s="2"/>
-    </row>
-    <row r="168" spans="1:24">
-      <c r="A168" s="4">
+      <c r="X167" s="5"/>
+      <c r="Y167" s="5"/>
+      <c r="Z167" s="5"/>
+    </row>
+    <row r="168" spans="1:26">
+      <c r="A168">
         <v>993</v>
       </c>
       <c r="B168" s="3">
@@ -7032,23 +7440,23 @@
         <v>46288.6043518519</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="F168" s="4">
+        <v>277</v>
+      </c>
+      <c r="F168">
         <v>38571</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
       <c r="K168" s="2"/>
       <c r="L168" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
@@ -7057,14 +7465,14 @@
       <c r="Q168" s="2"/>
       <c r="R168" s="2"/>
       <c r="S168" s="2"/>
-      <c r="T168" s="4"/>
-      <c r="U168" s="4"/>
       <c r="V168" s="2"/>
       <c r="W168" s="2"/>
-      <c r="X168" s="2"/>
-    </row>
-    <row r="169" spans="1:24">
-      <c r="A169" s="4">
+      <c r="X168" s="5"/>
+      <c r="Y168" s="5"/>
+      <c r="Z168" s="5"/>
+    </row>
+    <row r="169" spans="1:26">
+      <c r="A169">
         <v>994</v>
       </c>
       <c r="B169" s="3">
@@ -7074,23 +7482,23 @@
         <v>46288.654687499999</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F169" s="4">
+        <v>325</v>
+      </c>
+      <c r="F169">
         <v>38279</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
       <c r="J169" s="2"/>
       <c r="K169" s="2"/>
       <c r="L169" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="M169" s="2"/>
       <c r="N169" s="2"/>
@@ -7099,14 +7507,14 @@
       <c r="Q169" s="2"/>
       <c r="R169" s="2"/>
       <c r="S169" s="2"/>
-      <c r="T169" s="4"/>
-      <c r="U169" s="4"/>
       <c r="V169" s="2"/>
       <c r="W169" s="2"/>
-      <c r="X169" s="2"/>
-    </row>
-    <row r="170" spans="1:24">
-      <c r="A170" s="4">
+      <c r="X169" s="5"/>
+      <c r="Y169" s="5"/>
+      <c r="Z169" s="5"/>
+    </row>
+    <row r="170" spans="1:26">
+      <c r="A170">
         <v>995</v>
       </c>
       <c r="B170" s="3">
@@ -7116,23 +7524,23 @@
         <v>46288.7015509259</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="F170" s="4">
+        <v>325</v>
+      </c>
+      <c r="F170">
         <v>38279</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
       <c r="K170" s="2"/>
       <c r="L170" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
@@ -7141,14 +7549,14 @@
       <c r="Q170" s="2"/>
       <c r="R170" s="2"/>
       <c r="S170" s="2"/>
-      <c r="T170" s="4"/>
-      <c r="U170" s="4"/>
       <c r="V170" s="2"/>
       <c r="W170" s="2"/>
-      <c r="X170" s="2"/>
-    </row>
-    <row r="171" spans="1:24">
-      <c r="A171" s="4">
+      <c r="X170" s="5"/>
+      <c r="Y170" s="5"/>
+      <c r="Z170" s="5"/>
+    </row>
+    <row r="171" spans="1:26">
+      <c r="A171">
         <v>996</v>
       </c>
       <c r="B171" s="3">
@@ -7158,23 +7566,23 @@
         <v>46288.759062500001</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="F171" s="4">
+        <v>329</v>
+      </c>
+      <c r="F171">
         <v>43183</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
       <c r="L171" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
@@ -7183,14 +7591,14 @@
       <c r="Q171" s="2"/>
       <c r="R171" s="2"/>
       <c r="S171" s="2"/>
-      <c r="T171" s="4"/>
-      <c r="U171" s="4"/>
       <c r="V171" s="2"/>
       <c r="W171" s="2"/>
-      <c r="X171" s="2"/>
-    </row>
-    <row r="172" spans="1:24">
-      <c r="A172" s="4">
+      <c r="X171" s="5"/>
+      <c r="Y171" s="5"/>
+      <c r="Z171" s="5"/>
+    </row>
+    <row r="172" spans="1:26">
+      <c r="A172">
         <v>997</v>
       </c>
       <c r="B172" s="3">
@@ -7200,16 +7608,16 @@
         <v>46288.808229166701</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="F172" s="4">
+        <v>289</v>
+      </c>
+      <c r="F172">
         <v>38116</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
@@ -7223,44 +7631,44 @@
       <c r="Q172" s="2"/>
       <c r="R172" s="2"/>
       <c r="S172" s="2"/>
-      <c r="T172" s="4"/>
-      <c r="U172" s="4"/>
-      <c r="V172" s="2"/>
+      <c r="V172" s="2" t="s">
+        <v>331</v>
+      </c>
       <c r="W172" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="X172" s="2" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="173" spans="1:24">
-      <c r="A173" s="4">
-        <v>1000</v>
+        <v>332</v>
+      </c>
+      <c r="X172" s="5"/>
+      <c r="Y172" s="5"/>
+      <c r="Z172" s="5"/>
+    </row>
+    <row r="173" spans="1:26">
+      <c r="A173">
+        <v>998</v>
       </c>
       <c r="B173" s="3">
-        <v>46288.916701388902</v>
+        <v>46288.913425925901</v>
       </c>
       <c r="C173" s="3">
-        <v>46288.916990740698</v>
+        <v>46288.916087963</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="F173" s="4">
+        <v>334</v>
+      </c>
+      <c r="F173">
         <v>38725</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
       <c r="J173" s="2"/>
       <c r="K173" s="2"/>
       <c r="L173" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="M173" s="2"/>
       <c r="N173" s="2"/>
@@ -7269,33 +7677,33 @@
       <c r="Q173" s="2"/>
       <c r="R173" s="2"/>
       <c r="S173" s="2"/>
-      <c r="T173" s="4"/>
-      <c r="U173" s="4"/>
       <c r="V173" s="2"/>
       <c r="W173" s="2"/>
-      <c r="X173" s="2"/>
-    </row>
-    <row r="174" spans="1:24">
-      <c r="A174" s="4">
-        <v>1001</v>
+      <c r="X173" s="5"/>
+      <c r="Y173" s="5"/>
+      <c r="Z173" s="5"/>
+    </row>
+    <row r="174" spans="1:26">
+      <c r="A174">
+        <v>999</v>
       </c>
       <c r="B174" s="3">
-        <v>46289.207476851901</v>
+        <v>46288.916319444397</v>
       </c>
       <c r="C174" s="3">
-        <v>46289.209525462997</v>
+        <v>46288.916643518503</v>
       </c>
       <c r="D174" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E174" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="E174" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F174" s="4">
-        <v>38226</v>
+      <c r="F174">
+        <v>38725</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
@@ -7311,39 +7719,41 @@
       <c r="Q174" s="2"/>
       <c r="R174" s="2"/>
       <c r="S174" s="2"/>
-      <c r="T174" s="4"/>
-      <c r="U174" s="4"/>
       <c r="V174" s="2"/>
       <c r="W174" s="2"/>
-      <c r="X174" s="2"/>
-    </row>
-    <row r="175" spans="1:24">
-      <c r="A175" s="4">
-        <v>1002</v>
+      <c r="X174" s="5"/>
+      <c r="Y174" s="5"/>
+      <c r="Z174" s="5"/>
+    </row>
+    <row r="175" spans="1:26">
+      <c r="A175">
+        <v>1000</v>
       </c>
       <c r="B175" s="3">
-        <v>46289.210185185198</v>
+        <v>46288.916701388902</v>
       </c>
       <c r="C175" s="3">
-        <v>46289.2116550926</v>
+        <v>46288.916990740698</v>
       </c>
       <c r="D175" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E175" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="E175" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F175" s="4">
-        <v>38226</v>
+      <c r="F175">
+        <v>38725</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>81</v>
+        <v>118</v>
       </c>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
       <c r="K175" s="2"/>
-      <c r="L175" s="2"/>
+      <c r="L175" s="2" t="s">
+        <v>337</v>
+      </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -7351,47 +7761,41 @@
       <c r="Q175" s="2"/>
       <c r="R175" s="2"/>
       <c r="S175" s="2"/>
-      <c r="T175" s="4"/>
-      <c r="U175" s="4"/>
       <c r="V175" s="2"/>
-      <c r="W175" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="X175" s="2" t="s">
+      <c r="W175" s="2"/>
+      <c r="X175" s="5"/>
+      <c r="Y175" s="5"/>
+      <c r="Z175" s="5"/>
+    </row>
+    <row r="176" spans="1:26">
+      <c r="A176">
+        <v>1001</v>
+      </c>
+      <c r="B176" s="3">
+        <v>46289.207476851901</v>
+      </c>
+      <c r="C176" s="3">
+        <v>46289.209525462997</v>
+      </c>
+      <c r="D176" s="2" t="s">
         <v>338</v>
       </c>
-    </row>
-    <row r="176" spans="1:24">
-      <c r="A176" s="4">
-        <v>1003</v>
-      </c>
-      <c r="B176" s="3">
-        <v>46289.211770833303</v>
-      </c>
-      <c r="C176" s="3">
-        <v>46289.212280092601</v>
-      </c>
-      <c r="D176" s="2" t="s">
-        <v>334</v>
-      </c>
       <c r="E176" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F176" s="4">
+        <v>339</v>
+      </c>
+      <c r="F176">
         <v>38226</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H176" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="I176" s="2" t="s">
-        <v>339</v>
-      </c>
+        <v>118</v>
+      </c>
+      <c r="H176" s="2"/>
+      <c r="I176" s="2"/>
       <c r="J176" s="2"/>
       <c r="K176" s="2"/>
-      <c r="L176" s="2"/>
+      <c r="L176" s="2" t="s">
+        <v>340</v>
+      </c>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -7399,33 +7803,33 @@
       <c r="Q176" s="2"/>
       <c r="R176" s="2"/>
       <c r="S176" s="2"/>
-      <c r="T176" s="4"/>
-      <c r="U176" s="4"/>
       <c r="V176" s="2"/>
       <c r="W176" s="2"/>
-      <c r="X176" s="2"/>
-    </row>
-    <row r="177" spans="1:24">
-      <c r="A177" s="4">
-        <v>1004</v>
+      <c r="X176" s="5"/>
+      <c r="Y176" s="5"/>
+      <c r="Z176" s="5"/>
+    </row>
+    <row r="177" spans="1:26">
+      <c r="A177">
+        <v>1002</v>
       </c>
       <c r="B177" s="3">
-        <v>46289.212314814802</v>
+        <v>46289.210185185198</v>
       </c>
       <c r="C177" s="3">
-        <v>46289.213564814803</v>
+        <v>46289.2116550926</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F177" s="4">
+        <v>339</v>
+      </c>
+      <c r="F177">
         <v>38226</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>27</v>
+        <v>83</v>
       </c>
       <c r="H177" s="2"/>
       <c r="I177" s="2"/>
@@ -7439,36 +7843,44 @@
       <c r="Q177" s="2"/>
       <c r="R177" s="2"/>
       <c r="S177" s="2"/>
-      <c r="T177" s="4"/>
-      <c r="U177" s="4"/>
-      <c r="V177" s="2"/>
-      <c r="W177" s="2"/>
-      <c r="X177" s="2"/>
-    </row>
-    <row r="178" spans="1:24">
-      <c r="A178" s="4">
-        <v>1005</v>
+      <c r="V177" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="W177" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="X177" s="5"/>
+      <c r="Y177" s="5"/>
+      <c r="Z177" s="5"/>
+    </row>
+    <row r="178" spans="1:26">
+      <c r="A178">
+        <v>1003</v>
       </c>
       <c r="B178" s="3">
-        <v>46289.213599536997</v>
+        <v>46289.211770833303</v>
       </c>
       <c r="C178" s="3">
-        <v>46289.214085648098</v>
+        <v>46289.212280092601</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="F178" s="4">
+        <v>339</v>
+      </c>
+      <c r="F178">
         <v>38226</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H178" s="2"/>
-      <c r="I178" s="2"/>
+        <v>124</v>
+      </c>
+      <c r="H178" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I178" s="2" t="s">
+        <v>343</v>
+      </c>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
@@ -7479,33 +7891,33 @@
       <c r="Q178" s="2"/>
       <c r="R178" s="2"/>
       <c r="S178" s="2"/>
-      <c r="T178" s="4"/>
-      <c r="U178" s="4"/>
       <c r="V178" s="2"/>
       <c r="W178" s="2"/>
-      <c r="X178" s="2"/>
-    </row>
-    <row r="179" spans="1:24">
-      <c r="A179" s="4">
-        <v>1006</v>
+      <c r="X178" s="5"/>
+      <c r="Y178" s="5"/>
+      <c r="Z178" s="5"/>
+    </row>
+    <row r="179" spans="1:26">
+      <c r="A179">
+        <v>1004</v>
       </c>
       <c r="B179" s="3">
-        <v>46289.3444675926</v>
+        <v>46289.212314814802</v>
       </c>
       <c r="C179" s="3">
-        <v>46289.401377314804</v>
+        <v>46289.213564814803</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>60</v>
+        <v>338</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F179" s="4">
-        <v>38458</v>
+        <v>339</v>
+      </c>
+      <c r="F179">
+        <v>38226</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
@@ -7519,45 +7931,39 @@
       <c r="Q179" s="2"/>
       <c r="R179" s="2"/>
       <c r="S179" s="2"/>
-      <c r="T179" s="4"/>
-      <c r="U179" s="4"/>
       <c r="V179" s="2"/>
-      <c r="W179" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="X179" s="2" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="180" spans="1:24">
-      <c r="A180" s="4">
-        <v>1007</v>
+      <c r="W179" s="2"/>
+      <c r="X179" s="5"/>
+      <c r="Y179" s="5"/>
+      <c r="Z179" s="5"/>
+    </row>
+    <row r="180" spans="1:26">
+      <c r="A180">
+        <v>1005</v>
       </c>
       <c r="B180" s="3">
-        <v>46289.488472222198</v>
+        <v>46289.213599536997</v>
       </c>
       <c r="C180" s="3">
-        <v>46289.489976851903</v>
+        <v>46289.214085648098</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="F180" s="4">
-        <v>38716</v>
+        <v>339</v>
+      </c>
+      <c r="F180">
+        <v>38226</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>116</v>
+        <v>28</v>
       </c>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
       <c r="J180" s="2"/>
       <c r="K180" s="2"/>
-      <c r="L180" s="2" t="s">
-        <v>344</v>
-      </c>
+      <c r="L180" s="2"/>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -7565,41 +7971,39 @@
       <c r="Q180" s="2"/>
       <c r="R180" s="2"/>
       <c r="S180" s="2"/>
-      <c r="T180" s="4"/>
-      <c r="U180" s="4"/>
       <c r="V180" s="2"/>
       <c r="W180" s="2"/>
-      <c r="X180" s="2"/>
-    </row>
-    <row r="181" spans="1:24">
-      <c r="A181" s="4">
-        <v>1008</v>
+      <c r="X180" s="5"/>
+      <c r="Y180" s="5"/>
+      <c r="Z180" s="5"/>
+    </row>
+    <row r="181" spans="1:26">
+      <c r="A181">
+        <v>1006</v>
       </c>
       <c r="B181" s="3">
-        <v>46289.488611111097</v>
+        <v>46289.3444675926</v>
       </c>
       <c r="C181" s="3">
-        <v>46289.493692129603</v>
+        <v>46289.401377314804</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>284</v>
+        <v>62</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="F181" s="4">
-        <v>43159</v>
+        <v>63</v>
+      </c>
+      <c r="F181">
+        <v>38458</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
-      <c r="L181" s="2" t="s">
-        <v>345</v>
-      </c>
+      <c r="L181" s="2"/>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -7607,11 +8011,723 @@
       <c r="Q181" s="2"/>
       <c r="R181" s="2"/>
       <c r="S181" s="2"/>
-      <c r="T181" s="4"/>
-      <c r="U181" s="4"/>
-      <c r="V181" s="2"/>
-      <c r="W181" s="2"/>
-      <c r="X181" s="2"/>
+      <c r="V181" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="W181" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="X181" s="5"/>
+      <c r="Y181" s="5"/>
+      <c r="Z181" s="5"/>
+    </row>
+    <row r="182" spans="1:26">
+      <c r="A182">
+        <v>1007</v>
+      </c>
+      <c r="B182" s="3">
+        <v>46289.488472222198</v>
+      </c>
+      <c r="C182" s="3">
+        <v>46289.489976851903</v>
+      </c>
+      <c r="D182" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E182" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="F182">
+        <v>38716</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H182" s="2"/>
+      <c r="I182" s="2"/>
+      <c r="J182" s="2"/>
+      <c r="K182" s="2"/>
+      <c r="L182" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="M182" s="2"/>
+      <c r="N182" s="2"/>
+      <c r="O182" s="2"/>
+      <c r="P182" s="2"/>
+      <c r="Q182" s="2"/>
+      <c r="R182" s="2"/>
+      <c r="S182" s="2"/>
+      <c r="V182" s="2"/>
+      <c r="W182" s="2"/>
+      <c r="X182" s="5"/>
+      <c r="Y182" s="5"/>
+      <c r="Z182" s="5"/>
+    </row>
+    <row r="183" spans="1:26">
+      <c r="A183">
+        <v>1008</v>
+      </c>
+      <c r="B183" s="3">
+        <v>46289.488611111097</v>
+      </c>
+      <c r="C183" s="3">
+        <v>46289.493692129603</v>
+      </c>
+      <c r="D183" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E183" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F183">
+        <v>43159</v>
+      </c>
+      <c r="G183" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H183" s="2"/>
+      <c r="I183" s="2"/>
+      <c r="J183" s="2"/>
+      <c r="K183" s="2"/>
+      <c r="L183" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="M183" s="2"/>
+      <c r="N183" s="2"/>
+      <c r="O183" s="2"/>
+      <c r="P183" s="2"/>
+      <c r="Q183" s="2"/>
+      <c r="R183" s="2"/>
+      <c r="S183" s="2"/>
+      <c r="V183" s="2"/>
+      <c r="W183" s="2"/>
+      <c r="X183" s="5"/>
+      <c r="Y183" s="5"/>
+      <c r="Z183" s="5"/>
+    </row>
+    <row r="184" spans="1:26">
+      <c r="A184">
+        <v>1009</v>
+      </c>
+      <c r="B184" s="3">
+        <v>46291.559664351902</v>
+      </c>
+      <c r="C184" s="3">
+        <v>46291.560659722199</v>
+      </c>
+      <c r="D184" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E184" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="F184">
+        <v>38430</v>
+      </c>
+      <c r="G184" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H184" s="2"/>
+      <c r="I184" s="2"/>
+      <c r="J184" s="2"/>
+      <c r="K184" s="2"/>
+      <c r="L184" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="M184" s="2"/>
+      <c r="N184" s="2"/>
+      <c r="O184" s="2"/>
+      <c r="P184" s="2"/>
+      <c r="Q184" s="2"/>
+      <c r="R184" s="2"/>
+      <c r="S184" s="2"/>
+      <c r="V184" s="2"/>
+      <c r="W184" s="2"/>
+      <c r="X184" s="5"/>
+      <c r="Y184" s="5"/>
+      <c r="Z184" s="5"/>
+    </row>
+    <row r="185" spans="1:26">
+      <c r="A185">
+        <v>1010</v>
+      </c>
+      <c r="B185" s="3">
+        <v>46292.512986111098</v>
+      </c>
+      <c r="C185" s="3">
+        <v>46292.5158912037</v>
+      </c>
+      <c r="D185" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E185" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F185">
+        <v>38289</v>
+      </c>
+      <c r="G185" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="H185" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="I185" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="J185" s="2"/>
+      <c r="K185" s="2"/>
+      <c r="L185" s="2"/>
+      <c r="M185" s="2"/>
+      <c r="N185" s="2"/>
+      <c r="O185" s="2"/>
+      <c r="P185" s="2"/>
+      <c r="Q185" s="2"/>
+      <c r="R185" s="2"/>
+      <c r="S185" s="2"/>
+      <c r="V185" s="2"/>
+      <c r="W185" s="2"/>
+      <c r="X185" s="5"/>
+      <c r="Y185" s="5"/>
+      <c r="Z185" s="5"/>
+    </row>
+    <row r="186" spans="1:26">
+      <c r="A186" s="5">
+        <v>1011</v>
+      </c>
+      <c r="B186" s="3">
+        <v>46292.533703703702</v>
+      </c>
+      <c r="C186" s="3">
+        <v>46292.550416666701</v>
+      </c>
+      <c r="D186" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="F186" s="5">
+        <v>38289</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H186" s="2"/>
+      <c r="I186" s="2"/>
+      <c r="J186" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="K186" s="2"/>
+      <c r="L186" s="2"/>
+      <c r="M186" s="2"/>
+      <c r="N186" s="2"/>
+      <c r="O186" s="2"/>
+      <c r="P186" s="2"/>
+      <c r="Q186" s="2"/>
+      <c r="R186" s="2"/>
+      <c r="S186" s="2"/>
+      <c r="T186" s="5"/>
+      <c r="U186" s="5"/>
+      <c r="V186" s="2"/>
+      <c r="W186" s="2"/>
+      <c r="X186" s="5"/>
+      <c r="Y186" s="5"/>
+      <c r="Z186" s="5"/>
+    </row>
+    <row r="187" spans="1:26">
+      <c r="A187" s="5">
+        <v>1012</v>
+      </c>
+      <c r="B187" s="3">
+        <v>46292.6031365741</v>
+      </c>
+      <c r="C187" s="3">
+        <v>46292.604108796302</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E187" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F187" s="5">
+        <v>38226</v>
+      </c>
+      <c r="G187" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H187" s="2"/>
+      <c r="I187" s="2"/>
+      <c r="J187" s="2"/>
+      <c r="K187" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="L187" s="2"/>
+      <c r="M187" s="2"/>
+      <c r="N187" s="2"/>
+      <c r="O187" s="2"/>
+      <c r="P187" s="2"/>
+      <c r="Q187" s="2"/>
+      <c r="R187" s="2"/>
+      <c r="S187" s="2"/>
+      <c r="T187" s="5"/>
+      <c r="U187" s="5"/>
+      <c r="V187" s="2"/>
+      <c r="W187" s="2"/>
+      <c r="X187" s="5"/>
+      <c r="Y187" s="5"/>
+      <c r="Z187" s="5"/>
+    </row>
+    <row r="188" spans="1:26">
+      <c r="A188" s="5">
+        <v>1013</v>
+      </c>
+      <c r="B188" s="3">
+        <v>46292.604155092602</v>
+      </c>
+      <c r="C188" s="3">
+        <v>46292.604745370401</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E188" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F188" s="5">
+        <v>38226</v>
+      </c>
+      <c r="G188" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H188" s="2"/>
+      <c r="I188" s="2"/>
+      <c r="J188" s="2"/>
+      <c r="K188" s="2"/>
+      <c r="L188" s="2"/>
+      <c r="M188" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="N188" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="O188" s="2"/>
+      <c r="P188" s="2"/>
+      <c r="Q188" s="2"/>
+      <c r="R188" s="2"/>
+      <c r="S188" s="2"/>
+      <c r="T188" s="5"/>
+      <c r="U188" s="5"/>
+      <c r="V188" s="2"/>
+      <c r="W188" s="2"/>
+      <c r="X188" s="5"/>
+      <c r="Y188" s="5"/>
+      <c r="Z188" s="5"/>
+    </row>
+    <row r="189" spans="1:26">
+      <c r="A189" s="5">
+        <v>1014</v>
+      </c>
+      <c r="B189" s="3">
+        <v>46292.604849536998</v>
+      </c>
+      <c r="C189" s="3">
+        <v>46292.606469907398</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E189" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F189" s="5">
+        <v>38226</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H189" s="2"/>
+      <c r="I189" s="2"/>
+      <c r="J189" s="2"/>
+      <c r="K189" s="2"/>
+      <c r="L189" s="2"/>
+      <c r="M189" s="2"/>
+      <c r="N189" s="2"/>
+      <c r="O189" s="2"/>
+      <c r="P189" s="2"/>
+      <c r="Q189" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R189" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S189" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="T189" s="5"/>
+      <c r="U189" s="5"/>
+      <c r="V189" s="2"/>
+      <c r="W189" s="2"/>
+      <c r="X189" s="5"/>
+      <c r="Y189" s="5"/>
+      <c r="Z189" s="5"/>
+    </row>
+    <row r="190" spans="1:26">
+      <c r="A190" s="5">
+        <v>1015</v>
+      </c>
+      <c r="B190" s="3">
+        <v>46292.606504629599</v>
+      </c>
+      <c r="C190" s="3">
+        <v>46292.607291666704</v>
+      </c>
+      <c r="D190" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E190" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F190" s="5">
+        <v>38226</v>
+      </c>
+      <c r="G190" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H190" s="2"/>
+      <c r="I190" s="2"/>
+      <c r="J190" s="2"/>
+      <c r="K190" s="2"/>
+      <c r="L190" s="2"/>
+      <c r="M190" s="2"/>
+      <c r="N190" s="2"/>
+      <c r="O190" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="P190" s="2"/>
+      <c r="Q190" s="2"/>
+      <c r="R190" s="2"/>
+      <c r="S190" s="2"/>
+      <c r="T190" s="5"/>
+      <c r="U190" s="5"/>
+      <c r="V190" s="2"/>
+      <c r="W190" s="2"/>
+      <c r="X190" s="5"/>
+      <c r="Y190" s="5"/>
+      <c r="Z190" s="5"/>
+    </row>
+    <row r="191" spans="1:26">
+      <c r="A191" s="5">
+        <v>1016</v>
+      </c>
+      <c r="B191" s="3">
+        <v>46292.607337963003</v>
+      </c>
+      <c r="C191" s="3">
+        <v>46292.6078935185</v>
+      </c>
+      <c r="D191" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E191" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F191" s="5">
+        <v>38226</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H191" s="2"/>
+      <c r="I191" s="2"/>
+      <c r="J191" s="2"/>
+      <c r="K191" s="2"/>
+      <c r="L191" s="2"/>
+      <c r="M191" s="2"/>
+      <c r="N191" s="2"/>
+      <c r="O191" s="2"/>
+      <c r="P191" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="Q191" s="2"/>
+      <c r="R191" s="2"/>
+      <c r="S191" s="2"/>
+      <c r="T191" s="5"/>
+      <c r="U191" s="5"/>
+      <c r="V191" s="2"/>
+      <c r="W191" s="2"/>
+      <c r="X191" s="5"/>
+      <c r="Y191" s="5"/>
+      <c r="Z191" s="5"/>
+    </row>
+    <row r="192" spans="1:26">
+      <c r="A192" s="5">
+        <v>1017</v>
+      </c>
+      <c r="B192" s="3">
+        <v>46292.607928240701</v>
+      </c>
+      <c r="C192" s="3">
+        <v>46292.608599537001</v>
+      </c>
+      <c r="D192" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E192" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F192" s="5">
+        <v>38226</v>
+      </c>
+      <c r="G192" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H192" s="2"/>
+      <c r="I192" s="2"/>
+      <c r="J192" s="2"/>
+      <c r="K192" s="2"/>
+      <c r="L192" s="2"/>
+      <c r="M192" s="2"/>
+      <c r="N192" s="2"/>
+      <c r="O192" s="2"/>
+      <c r="P192" s="2"/>
+      <c r="Q192" s="2"/>
+      <c r="R192" s="2"/>
+      <c r="S192" s="2"/>
+      <c r="T192" s="5">
+        <v>5</v>
+      </c>
+      <c r="U192" s="5">
+        <v>2</v>
+      </c>
+      <c r="V192" s="2"/>
+      <c r="W192" s="2"/>
+      <c r="X192" s="5"/>
+      <c r="Y192" s="5"/>
+      <c r="Z192" s="5"/>
+    </row>
+    <row r="193" spans="1:26">
+      <c r="A193" s="5">
+        <v>1018</v>
+      </c>
+      <c r="B193" s="3">
+        <v>46292.608634259297</v>
+      </c>
+      <c r="C193" s="3">
+        <v>46292.610162037003</v>
+      </c>
+      <c r="D193" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E193" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F193" s="5">
+        <v>38226</v>
+      </c>
+      <c r="G193" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="H193" s="2"/>
+      <c r="I193" s="2"/>
+      <c r="J193" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="K193" s="2"/>
+      <c r="L193" s="2"/>
+      <c r="M193" s="2"/>
+      <c r="N193" s="2"/>
+      <c r="O193" s="2"/>
+      <c r="P193" s="2"/>
+      <c r="Q193" s="2"/>
+      <c r="R193" s="2"/>
+      <c r="S193" s="2"/>
+      <c r="T193" s="5"/>
+      <c r="U193" s="5"/>
+      <c r="V193" s="2"/>
+      <c r="W193" s="2"/>
+      <c r="X193" s="5"/>
+      <c r="Y193" s="5"/>
+      <c r="Z193" s="5"/>
+    </row>
+    <row r="194" spans="1:26">
+      <c r="A194" s="5">
+        <v>1019</v>
+      </c>
+      <c r="B194" s="3">
+        <v>46292.605960648099</v>
+      </c>
+      <c r="C194" s="3">
+        <v>46292.616666666698</v>
+      </c>
+      <c r="D194" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E194" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F194" s="5">
+        <v>38611</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H194" s="2"/>
+      <c r="I194" s="2"/>
+      <c r="J194" s="2"/>
+      <c r="K194" s="2"/>
+      <c r="L194" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="M194" s="2"/>
+      <c r="N194" s="2"/>
+      <c r="O194" s="2"/>
+      <c r="P194" s="2"/>
+      <c r="Q194" s="2"/>
+      <c r="R194" s="2"/>
+      <c r="S194" s="2"/>
+      <c r="T194" s="5"/>
+      <c r="U194" s="5"/>
+      <c r="V194" s="2"/>
+      <c r="W194" s="2"/>
+      <c r="X194" s="5"/>
+      <c r="Y194" s="5"/>
+      <c r="Z194" s="5"/>
+    </row>
+    <row r="195" spans="1:26">
+      <c r="A195" s="5">
+        <v>1020</v>
+      </c>
+      <c r="B195" s="3">
+        <v>46292.617418981499</v>
+      </c>
+      <c r="C195" s="3">
+        <v>46292.618321759299</v>
+      </c>
+      <c r="D195" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E195" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="F195" s="5">
+        <v>38611</v>
+      </c>
+      <c r="G195" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H195" s="2"/>
+      <c r="I195" s="2"/>
+      <c r="J195" s="2"/>
+      <c r="K195" s="2"/>
+      <c r="L195" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="M195" s="2"/>
+      <c r="N195" s="2"/>
+      <c r="O195" s="2"/>
+      <c r="P195" s="2"/>
+      <c r="Q195" s="2"/>
+      <c r="R195" s="2"/>
+      <c r="S195" s="2"/>
+      <c r="T195" s="5"/>
+      <c r="U195" s="5"/>
+      <c r="V195" s="2"/>
+      <c r="W195" s="2"/>
+      <c r="X195" s="5"/>
+      <c r="Y195" s="5"/>
+      <c r="Z195" s="5"/>
+    </row>
+    <row r="196" spans="1:26">
+      <c r="A196" s="5">
+        <v>1021</v>
+      </c>
+      <c r="B196" s="3">
+        <v>46292.649178240703</v>
+      </c>
+      <c r="C196" s="3">
+        <v>46292.650381944397</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="F196" s="5">
+        <v>38925</v>
+      </c>
+      <c r="G196" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="H196" s="2"/>
+      <c r="I196" s="2"/>
+      <c r="J196" s="2"/>
+      <c r="K196" s="2"/>
+      <c r="L196" s="2"/>
+      <c r="M196" s="2"/>
+      <c r="N196" s="2"/>
+      <c r="O196" s="2"/>
+      <c r="P196" s="2"/>
+      <c r="Q196" s="2"/>
+      <c r="R196" s="2"/>
+      <c r="S196" s="2"/>
+      <c r="T196" s="5">
+        <v>8</v>
+      </c>
+      <c r="U196" s="5">
+        <v>0</v>
+      </c>
+      <c r="V196" s="2"/>
+      <c r="W196" s="2"/>
+      <c r="X196" s="5"/>
+      <c r="Y196" s="5"/>
+      <c r="Z196" s="5"/>
+    </row>
+    <row r="197" spans="1:26">
+      <c r="A197" s="5">
+        <v>1022</v>
+      </c>
+      <c r="B197" s="3">
+        <v>46292.706770833298</v>
+      </c>
+      <c r="C197" s="3">
+        <v>46292.707048611097</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="F197" s="5">
+        <v>38417</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H197" s="2"/>
+      <c r="I197" s="2"/>
+      <c r="J197" s="2"/>
+      <c r="K197" s="2"/>
+      <c r="L197" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="M197" s="2"/>
+      <c r="N197" s="2"/>
+      <c r="O197" s="2"/>
+      <c r="P197" s="2"/>
+      <c r="Q197" s="2"/>
+      <c r="R197" s="2"/>
+      <c r="S197" s="2"/>
+      <c r="T197" s="5"/>
+      <c r="U197" s="5"/>
+      <c r="V197" s="2"/>
+      <c r="W197" s="2"/>
+      <c r="X197" s="5"/>
+      <c r="Y197" s="5"/>
+      <c r="Z197" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63E916CA-3E37-4E88-9B5A-F207BF51EC94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{441FD118-9812-4EC8-A282-A5E2CE9C50DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="370">
   <si>
     <t>Id</t>
   </si>
@@ -290,37 +290,34 @@
     <t>Starbucks Encuentro Oceania II</t>
   </si>
   <si>
+    <t>eduardo.reyes@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Eduardo David Reyes Chavez</t>
+  </si>
+  <si>
+    <t>SBMX38149@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Bellavista</t>
+  </si>
+  <si>
+    <t>maria.cardenas@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Maria Veronica Cardenas Pedraza</t>
+  </si>
+  <si>
+    <t>sbmx38515@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Patio Ecatepec</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17898572434496167251908049569087_Starbucks%20Patio%20Ecat.jpg</t>
+  </si>
+  <si>
     <t>Organización Refrigeradores Back</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/ChatGPT%20Image%2019%20sept%202026,%2015_22_18_Enrique%20Cesar%20Flores.png</t>
-  </si>
-  <si>
-    <t>eduardo.reyes@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Eduardo David Reyes Chavez</t>
-  </si>
-  <si>
-    <t>SBMX38149@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Bellavista</t>
-  </si>
-  <si>
-    <t>maria.cardenas@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Maria Veronica Cardenas Pedraza</t>
-  </si>
-  <si>
-    <t>sbmx38515@starbucks.com.mx</t>
-  </si>
-  <si>
-    <t>Starbucks Patio Ecatepec</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17898572434496167251908049569087_Starbucks%20Patio%20Ecat.jpg</t>
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/17898578066011103601279025610229_Starbucks%20Patio%20Ecat.jpg</t>
@@ -1288,8 +1285,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z197" totalsRowShown="0">
-  <autoFilter ref="A1:Z197" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z196" totalsRowShown="0">
+  <autoFilter ref="A1:Z196" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1807,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z197"/>
+  <dimension ref="A1:Z196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -2570,28 +2567,25 @@
     </row>
     <row r="27" spans="1:26">
       <c r="A27">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="B27" s="3">
-        <v>46284.646423611113</v>
+        <v>46284.650324074071</v>
       </c>
       <c r="C27" s="3">
-        <v>46284.646770833337</v>
+        <v>46284.651006944441</v>
       </c>
       <c r="D27" t="s">
-        <v>26</v>
+        <v>83</v>
       </c>
       <c r="E27" t="s">
-        <v>27</v>
+        <v>84</v>
       </c>
       <c r="F27">
-        <v>38371</v>
+        <v>38507</v>
       </c>
       <c r="G27" t="s">
-        <v>83</v>
-      </c>
-      <c r="V27" t="s">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="X27" s="5"/>
       <c r="Y27" s="5"/>
@@ -2599,13 +2593,13 @@
     </row>
     <row r="28" spans="1:26">
       <c r="A28">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B28" s="3">
-        <v>46284.650324074071</v>
+        <v>46284.669444444444</v>
       </c>
       <c r="C28" s="3">
-        <v>46284.651006944441</v>
+        <v>46284.669606481482</v>
       </c>
       <c r="D28" t="s">
         <v>85</v>
@@ -2614,7 +2608,7 @@
         <v>86</v>
       </c>
       <c r="F28">
-        <v>38507</v>
+        <v>38149</v>
       </c>
       <c r="G28" t="s">
         <v>28</v>
@@ -2625,13 +2619,13 @@
     </row>
     <row r="29" spans="1:26">
       <c r="A29">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="B29" s="3">
-        <v>46284.669444444444</v>
+        <v>46284.687916666669</v>
       </c>
       <c r="C29" s="3">
-        <v>46284.669606481482</v>
+        <v>46284.68986111111</v>
       </c>
       <c r="D29" t="s">
         <v>87</v>
@@ -2640,7 +2634,7 @@
         <v>88</v>
       </c>
       <c r="F29">
-        <v>38149</v>
+        <v>38270</v>
       </c>
       <c r="G29" t="s">
         <v>28</v>
@@ -2651,13 +2645,13 @@
     </row>
     <row r="30" spans="1:26">
       <c r="A30">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="B30" s="3">
-        <v>46284.687916666669</v>
+        <v>46284.6875</v>
       </c>
       <c r="C30" s="3">
-        <v>46284.68986111111</v>
+        <v>46284.690474537034</v>
       </c>
       <c r="D30" t="s">
         <v>89</v>
@@ -2666,10 +2660,19 @@
         <v>90</v>
       </c>
       <c r="F30">
-        <v>38270</v>
+        <v>38515</v>
       </c>
       <c r="G30" t="s">
-        <v>28</v>
+        <v>77</v>
+      </c>
+      <c r="Q30" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R30" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S30" t="s">
+        <v>91</v>
       </c>
       <c r="X30" s="5"/>
       <c r="Y30" s="5"/>
@@ -2677,34 +2680,31 @@
     </row>
     <row r="31" spans="1:26">
       <c r="A31">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="B31" s="3">
-        <v>46284.6875</v>
+        <v>46284.696099537039</v>
       </c>
       <c r="C31" s="3">
-        <v>46284.690474537034</v>
+        <v>46284.703773148147</v>
       </c>
       <c r="D31" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E31" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="F31">
         <v>38515</v>
       </c>
       <c r="G31" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q31" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R31" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="S31" t="s">
+        <v>92</v>
+      </c>
+      <c r="V31" t="s">
         <v>93</v>
+      </c>
+      <c r="W31" t="s">
+        <v>94</v>
       </c>
       <c r="X31" s="5"/>
       <c r="Y31" s="5"/>
@@ -2712,31 +2712,25 @@
     </row>
     <row r="32" spans="1:26">
       <c r="A32">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B32" s="3">
-        <v>46284.696099537039</v>
+        <v>46284.720578703702</v>
       </c>
       <c r="C32" s="3">
-        <v>46284.703773148147</v>
+        <v>46284.72115740741</v>
       </c>
       <c r="D32" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E32" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="F32">
-        <v>38515</v>
+        <v>38719</v>
       </c>
       <c r="G32" t="s">
-        <v>83</v>
-      </c>
-      <c r="V32" t="s">
-        <v>94</v>
-      </c>
-      <c r="W32" t="s">
-        <v>95</v>
+        <v>28</v>
       </c>
       <c r="X32" s="5"/>
       <c r="Y32" s="5"/>
@@ -2744,25 +2738,28 @@
     </row>
     <row r="33" spans="1:26">
       <c r="A33">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B33" s="3">
-        <v>46284.720578703702</v>
+        <v>46284.719629629632</v>
       </c>
       <c r="C33" s="3">
-        <v>46284.72115740741</v>
+        <v>46284.72452546296</v>
       </c>
       <c r="D33" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="E33" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F33">
-        <v>38719</v>
+        <v>38656</v>
       </c>
       <c r="G33" t="s">
-        <v>28</v>
+        <v>64</v>
+      </c>
+      <c r="O33" t="s">
+        <v>99</v>
       </c>
       <c r="X33" s="5"/>
       <c r="Y33" s="5"/>
@@ -2770,28 +2767,25 @@
     </row>
     <row r="34" spans="1:26">
       <c r="A34">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="B34" s="3">
-        <v>46284.719629629632</v>
+        <v>46284.743472222224</v>
       </c>
       <c r="C34" s="3">
-        <v>46284.72452546296</v>
+        <v>46284.745300925926</v>
       </c>
       <c r="D34" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="E34" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="F34">
-        <v>38656</v>
+        <v>38770</v>
       </c>
       <c r="G34" t="s">
-        <v>64</v>
-      </c>
-      <c r="O34" t="s">
-        <v>100</v>
+        <v>28</v>
       </c>
       <c r="X34" s="5"/>
       <c r="Y34" s="5"/>
@@ -2799,22 +2793,22 @@
     </row>
     <row r="35" spans="1:26">
       <c r="A35">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="B35" s="3">
-        <v>46284.743472222224</v>
+        <v>46284.742627314816</v>
       </c>
       <c r="C35" s="3">
-        <v>46284.745300925926</v>
+        <v>46284.747037037036</v>
       </c>
       <c r="D35" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F35">
-        <v>38770</v>
+        <v>43111</v>
       </c>
       <c r="G35" t="s">
         <v>28</v>
@@ -2825,22 +2819,22 @@
     </row>
     <row r="36" spans="1:26">
       <c r="A36">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B36" s="3">
-        <v>46284.742627314816</v>
+        <v>46284.750092592592</v>
       </c>
       <c r="C36" s="3">
-        <v>46284.747037037036</v>
+        <v>46284.753009259257</v>
       </c>
       <c r="D36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E36" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F36">
-        <v>43111</v>
+        <v>38442</v>
       </c>
       <c r="G36" t="s">
         <v>28</v>
@@ -2851,22 +2845,22 @@
     </row>
     <row r="37" spans="1:26">
       <c r="A37">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B37" s="3">
-        <v>46284.750092592592</v>
+        <v>46284.761944444443</v>
       </c>
       <c r="C37" s="3">
-        <v>46284.753009259257</v>
+        <v>46284.763206018521</v>
       </c>
       <c r="D37" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E37" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F37">
-        <v>38442</v>
+        <v>38394</v>
       </c>
       <c r="G37" t="s">
         <v>28</v>
@@ -2877,22 +2871,22 @@
     </row>
     <row r="38" spans="1:26">
       <c r="A38">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B38" s="3">
-        <v>46284.761944444443</v>
+        <v>46284.754780092589</v>
       </c>
       <c r="C38" s="3">
-        <v>46284.763206018521</v>
+        <v>46284.764317129629</v>
       </c>
       <c r="D38" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E38" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F38">
-        <v>38394</v>
+        <v>38205</v>
       </c>
       <c r="G38" t="s">
         <v>28</v>
@@ -2903,25 +2897,34 @@
     </row>
     <row r="39" spans="1:26">
       <c r="A39">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="B39" s="3">
-        <v>46284.754780092589</v>
+        <v>46284.781863425924</v>
       </c>
       <c r="C39" s="3">
-        <v>46284.764317129629</v>
+        <v>46284.782060185185</v>
       </c>
       <c r="D39" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="F39">
-        <v>38205</v>
+        <v>38401</v>
       </c>
       <c r="G39" t="s">
-        <v>28</v>
+        <v>77</v>
+      </c>
+      <c r="Q39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R39" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S39" t="s">
+        <v>112</v>
       </c>
       <c r="X39" s="5"/>
       <c r="Y39" s="5"/>
@@ -2929,34 +2932,25 @@
     </row>
     <row r="40" spans="1:26">
       <c r="A40">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B40" s="3">
-        <v>46284.781863425924</v>
+        <v>46284.784421296295</v>
       </c>
       <c r="C40" s="3">
-        <v>46284.782060185185</v>
+        <v>46284.787569444445</v>
       </c>
       <c r="D40" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="E40" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="F40">
-        <v>38401</v>
+        <v>38266</v>
       </c>
       <c r="G40" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R40" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="S40" t="s">
-        <v>113</v>
+        <v>28</v>
       </c>
       <c r="X40" s="5"/>
       <c r="Y40" s="5"/>
@@ -2964,25 +2958,28 @@
     </row>
     <row r="41" spans="1:26">
       <c r="A41">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="B41" s="3">
-        <v>46284.784421296295</v>
+        <v>46284.792303240742</v>
       </c>
       <c r="C41" s="3">
-        <v>46284.787569444445</v>
+        <v>46284.79346064815</v>
       </c>
       <c r="D41" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E41" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F41">
-        <v>38266</v>
+        <v>38418</v>
       </c>
       <c r="G41" t="s">
-        <v>28</v>
+        <v>117</v>
+      </c>
+      <c r="L41" t="s">
+        <v>118</v>
       </c>
       <c r="X41" s="5"/>
       <c r="Y41" s="5"/>
@@ -2990,28 +2987,25 @@
     </row>
     <row r="42" spans="1:26">
       <c r="A42">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B42" s="3">
-        <v>46284.792303240742</v>
+        <v>46284.79215277778</v>
       </c>
       <c r="C42" s="3">
-        <v>46284.79346064815</v>
+        <v>46284.793726851851</v>
       </c>
       <c r="D42" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="E42" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="F42">
-        <v>38418</v>
+        <v>38119</v>
       </c>
       <c r="G42" t="s">
-        <v>118</v>
-      </c>
-      <c r="L42" t="s">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="X42" s="5"/>
       <c r="Y42" s="5"/>
@@ -3019,25 +3013,31 @@
     </row>
     <row r="43" spans="1:26">
       <c r="A43">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B43" s="3">
-        <v>46284.79215277778</v>
+        <v>46284.822141203702</v>
       </c>
       <c r="C43" s="3">
-        <v>46284.793726851851</v>
+        <v>46284.823055555556</v>
       </c>
       <c r="D43" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E43" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F43">
-        <v>38119</v>
+        <v>38339</v>
       </c>
       <c r="G43" t="s">
-        <v>28</v>
+        <v>123</v>
+      </c>
+      <c r="H43" t="s">
+        <v>124</v>
+      </c>
+      <c r="I43" t="s">
+        <v>125</v>
       </c>
       <c r="X43" s="5"/>
       <c r="Y43" s="5"/>
@@ -3045,31 +3045,28 @@
     </row>
     <row r="44" spans="1:26">
       <c r="A44">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B44" s="3">
-        <v>46284.822141203702</v>
+        <v>46284.823738425926</v>
       </c>
       <c r="C44" s="3">
-        <v>46284.823055555556</v>
+        <v>46284.825856481482</v>
       </c>
       <c r="D44" t="s">
+        <v>121</v>
+      </c>
+      <c r="E44" t="s">
         <v>122</v>
-      </c>
-      <c r="E44" t="s">
-        <v>123</v>
       </c>
       <c r="F44">
         <v>38339</v>
       </c>
       <c r="G44" t="s">
-        <v>124</v>
-      </c>
-      <c r="H44" t="s">
-        <v>125</v>
-      </c>
-      <c r="I44" t="s">
         <v>126</v>
+      </c>
+      <c r="J44" t="s">
+        <v>127</v>
       </c>
       <c r="X44" s="5"/>
       <c r="Y44" s="5"/>
@@ -3077,27 +3074,27 @@
     </row>
     <row r="45" spans="1:26">
       <c r="A45">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="B45" s="3">
-        <v>46284.823738425926</v>
+        <v>46284.825914351852</v>
       </c>
       <c r="C45" s="3">
-        <v>46284.825856481482</v>
+        <v>46284.826238425929</v>
       </c>
       <c r="D45" t="s">
+        <v>121</v>
+      </c>
+      <c r="E45" t="s">
         <v>122</v>
-      </c>
-      <c r="E45" t="s">
-        <v>123</v>
       </c>
       <c r="F45">
         <v>38339</v>
       </c>
       <c r="G45" t="s">
-        <v>127</v>
-      </c>
-      <c r="J45" t="s">
+        <v>32</v>
+      </c>
+      <c r="K45" t="s">
         <v>128</v>
       </c>
       <c r="X45" s="5"/>
@@ -3106,28 +3103,25 @@
     </row>
     <row r="46" spans="1:26">
       <c r="A46">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B46" s="3">
-        <v>46284.825914351852</v>
+        <v>46284.825960648152</v>
       </c>
       <c r="C46" s="3">
-        <v>46284.826238425929</v>
+        <v>46284.826817129629</v>
       </c>
       <c r="D46" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E46" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F46">
-        <v>38339</v>
+        <v>38411</v>
       </c>
       <c r="G46" t="s">
-        <v>32</v>
-      </c>
-      <c r="K46" t="s">
-        <v>129</v>
+        <v>28</v>
       </c>
       <c r="X46" s="5"/>
       <c r="Y46" s="5"/>
@@ -3135,25 +3129,28 @@
     </row>
     <row r="47" spans="1:26">
       <c r="A47">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B47" s="3">
-        <v>46284.825960648152</v>
+        <v>46284.826273148145</v>
       </c>
       <c r="C47" s="3">
-        <v>46284.826817129629</v>
+        <v>46284.826921296299</v>
       </c>
       <c r="D47" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E47" t="s">
+        <v>122</v>
+      </c>
+      <c r="F47">
+        <v>38339</v>
+      </c>
+      <c r="G47" t="s">
+        <v>117</v>
+      </c>
+      <c r="L47" t="s">
         <v>131</v>
-      </c>
-      <c r="F47">
-        <v>38411</v>
-      </c>
-      <c r="G47" t="s">
-        <v>28</v>
       </c>
       <c r="X47" s="5"/>
       <c r="Y47" s="5"/>
@@ -3161,27 +3158,30 @@
     </row>
     <row r="48" spans="1:26">
       <c r="A48">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B48" s="3">
-        <v>46284.826273148145</v>
+        <v>46284.826979166668</v>
       </c>
       <c r="C48" s="3">
-        <v>46284.826921296299</v>
+        <v>46284.827430555553</v>
       </c>
       <c r="D48" t="s">
+        <v>121</v>
+      </c>
+      <c r="E48" t="s">
         <v>122</v>
-      </c>
-      <c r="E48" t="s">
-        <v>123</v>
       </c>
       <c r="F48">
         <v>38339</v>
       </c>
       <c r="G48" t="s">
-        <v>118</v>
-      </c>
-      <c r="L48" t="s">
+        <v>36</v>
+      </c>
+      <c r="M48" t="s">
+        <v>124</v>
+      </c>
+      <c r="N48" t="s">
         <v>132</v>
       </c>
       <c r="X48" s="5"/>
@@ -3190,31 +3190,25 @@
     </row>
     <row r="49" spans="1:26">
       <c r="A49">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="B49" s="3">
-        <v>46284.826979166668</v>
+        <v>46284.828043981484</v>
       </c>
       <c r="C49" s="3">
-        <v>46284.827430555553</v>
+        <v>46284.828472222223</v>
       </c>
       <c r="D49" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E49" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F49">
-        <v>38339</v>
+        <v>38411</v>
       </c>
       <c r="G49" t="s">
-        <v>36</v>
-      </c>
-      <c r="M49" t="s">
-        <v>125</v>
-      </c>
-      <c r="N49" t="s">
-        <v>133</v>
+        <v>29</v>
       </c>
       <c r="X49" s="5"/>
       <c r="Y49" s="5"/>
@@ -3222,25 +3216,28 @@
     </row>
     <row r="50" spans="1:26">
       <c r="A50">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B50" s="3">
-        <v>46284.828043981484</v>
+        <v>46284.827870370369</v>
       </c>
       <c r="C50" s="3">
-        <v>46284.828472222223</v>
+        <v>46284.829895833333</v>
       </c>
       <c r="D50" t="s">
-        <v>130</v>
+        <v>121</v>
       </c>
       <c r="E50" t="s">
-        <v>131</v>
+        <v>122</v>
       </c>
       <c r="F50">
-        <v>38411</v>
+        <v>38339</v>
       </c>
       <c r="G50" t="s">
-        <v>29</v>
+        <v>64</v>
+      </c>
+      <c r="O50" t="s">
+        <v>133</v>
       </c>
       <c r="X50" s="5"/>
       <c r="Y50" s="5"/>
@@ -3248,27 +3245,27 @@
     </row>
     <row r="51" spans="1:26">
       <c r="A51">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B51" s="3">
-        <v>46284.827870370369</v>
+        <v>46284.829930555556</v>
       </c>
       <c r="C51" s="3">
-        <v>46284.829895833333</v>
+        <v>46284.830428240741</v>
       </c>
       <c r="D51" t="s">
+        <v>121</v>
+      </c>
+      <c r="E51" t="s">
         <v>122</v>
-      </c>
-      <c r="E51" t="s">
-        <v>123</v>
       </c>
       <c r="F51">
         <v>38339</v>
       </c>
       <c r="G51" t="s">
-        <v>64</v>
-      </c>
-      <c r="O51" t="s">
+        <v>68</v>
+      </c>
+      <c r="P51" t="s">
         <v>134</v>
       </c>
       <c r="X51" s="5"/>
@@ -3277,27 +3274,33 @@
     </row>
     <row r="52" spans="1:26">
       <c r="A52">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B52" s="3">
-        <v>46284.829930555556</v>
+        <v>46284.830509259256</v>
       </c>
       <c r="C52" s="3">
-        <v>46284.830428240741</v>
+        <v>46284.831921296296</v>
       </c>
       <c r="D52" t="s">
+        <v>121</v>
+      </c>
+      <c r="E52" t="s">
         <v>122</v>
-      </c>
-      <c r="E52" t="s">
-        <v>123</v>
       </c>
       <c r="F52">
         <v>38339</v>
       </c>
       <c r="G52" t="s">
-        <v>68</v>
-      </c>
-      <c r="P52" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q52" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R52" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S52" t="s">
         <v>135</v>
       </c>
       <c r="X52" s="5"/>
@@ -3306,34 +3309,25 @@
     </row>
     <row r="53" spans="1:26">
       <c r="A53">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B53" s="3">
-        <v>46284.830509259256</v>
+        <v>46284.91909722222</v>
       </c>
       <c r="C53" s="3">
-        <v>46284.831921296296</v>
+        <v>46284.921307870369</v>
       </c>
       <c r="D53" t="s">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="E53" t="s">
-        <v>123</v>
+        <v>137</v>
       </c>
       <c r="F53">
-        <v>38339</v>
+        <v>38427</v>
       </c>
       <c r="G53" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R53" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="S53" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="X53" s="5"/>
       <c r="Y53" s="5"/>
@@ -3341,22 +3335,22 @@
     </row>
     <row r="54" spans="1:26">
       <c r="A54">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B54" s="3">
-        <v>46284.91909722222</v>
+        <v>46285.504050925927</v>
       </c>
       <c r="C54" s="3">
-        <v>46284.921307870369</v>
+        <v>46285.504502314812</v>
       </c>
       <c r="D54" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E54" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F54">
-        <v>38427</v>
+        <v>38186</v>
       </c>
       <c r="G54" t="s">
         <v>28</v>
@@ -3367,22 +3361,22 @@
     </row>
     <row r="55" spans="1:26">
       <c r="A55">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B55" s="3">
-        <v>46285.504050925927</v>
+        <v>46285.571921296294</v>
       </c>
       <c r="C55" s="3">
-        <v>46285.504502314812</v>
+        <v>46285.572222222225</v>
       </c>
       <c r="D55" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E55" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F55">
-        <v>38186</v>
+        <v>38561</v>
       </c>
       <c r="G55" t="s">
         <v>28</v>
@@ -3393,25 +3387,31 @@
     </row>
     <row r="56" spans="1:26">
       <c r="A56">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B56" s="3">
-        <v>46285.571921296294</v>
+        <v>46285.572731481479</v>
       </c>
       <c r="C56" s="3">
-        <v>46285.572222222225</v>
+        <v>46285.574131944442</v>
       </c>
       <c r="D56" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E56" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F56">
-        <v>38561</v>
+        <v>38368</v>
       </c>
       <c r="G56" t="s">
-        <v>28</v>
+        <v>36</v>
+      </c>
+      <c r="M56" t="s">
+        <v>124</v>
+      </c>
+      <c r="N56" t="s">
+        <v>144</v>
       </c>
       <c r="X56" s="5"/>
       <c r="Y56" s="5"/>
@@ -3419,31 +3419,25 @@
     </row>
     <row r="57" spans="1:26">
       <c r="A57">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="B57" s="3">
-        <v>46285.572731481479</v>
+        <v>46285.621018518519</v>
       </c>
       <c r="C57" s="3">
-        <v>46285.574131944442</v>
+        <v>46285.621180555558</v>
       </c>
       <c r="D57" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="E57" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="F57">
-        <v>38368</v>
+        <v>38401</v>
       </c>
       <c r="G57" t="s">
-        <v>36</v>
-      </c>
-      <c r="M57" t="s">
-        <v>125</v>
-      </c>
-      <c r="N57" t="s">
-        <v>145</v>
+        <v>28</v>
       </c>
       <c r="X57" s="5"/>
       <c r="Y57" s="5"/>
@@ -3451,22 +3445,22 @@
     </row>
     <row r="58" spans="1:26">
       <c r="A58">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B58" s="3">
-        <v>46285.621018518519</v>
+        <v>46285.638113425928</v>
       </c>
       <c r="C58" s="3">
-        <v>46285.621180555558</v>
+        <v>46285.63894675926</v>
       </c>
       <c r="D58" t="s">
-        <v>111</v>
+        <v>145</v>
       </c>
       <c r="E58" t="s">
-        <v>112</v>
+        <v>146</v>
       </c>
       <c r="F58">
-        <v>38401</v>
+        <v>38992</v>
       </c>
       <c r="G58" t="s">
         <v>28</v>
@@ -3477,22 +3471,22 @@
     </row>
     <row r="59" spans="1:26">
       <c r="A59">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="B59" s="3">
-        <v>46285.638113425928</v>
+        <v>46285.662870370368</v>
       </c>
       <c r="C59" s="3">
-        <v>46285.63894675926</v>
+        <v>46285.663576388892</v>
       </c>
       <c r="D59" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="E59" t="s">
-        <v>147</v>
+        <v>35</v>
       </c>
       <c r="F59">
-        <v>38992</v>
+        <v>38529</v>
       </c>
       <c r="G59" t="s">
         <v>28</v>
@@ -3503,22 +3497,22 @@
     </row>
     <row r="60" spans="1:26">
       <c r="A60">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B60" s="3">
-        <v>46285.662870370368</v>
+        <v>46285.669421296298</v>
       </c>
       <c r="C60" s="3">
-        <v>46285.663576388892</v>
+        <v>46285.670185185183</v>
       </c>
       <c r="D60" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="E60" t="s">
-        <v>35</v>
+        <v>148</v>
       </c>
       <c r="F60">
-        <v>38529</v>
+        <v>38695</v>
       </c>
       <c r="G60" t="s">
         <v>28</v>
@@ -3529,22 +3523,22 @@
     </row>
     <row r="61" spans="1:26">
       <c r="A61">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B61" s="3">
-        <v>46285.669421296298</v>
+        <v>46285.688738425924</v>
       </c>
       <c r="C61" s="3">
-        <v>46285.670185185183</v>
+        <v>46285.689282407409</v>
       </c>
       <c r="D61" t="s">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="E61" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F61">
-        <v>38695</v>
+        <v>38368</v>
       </c>
       <c r="G61" t="s">
         <v>28</v>
@@ -3555,22 +3549,22 @@
     </row>
     <row r="62" spans="1:26">
       <c r="A62">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B62" s="3">
-        <v>46285.688738425924</v>
+        <v>46285.71597222222</v>
       </c>
       <c r="C62" s="3">
-        <v>46285.689282407409</v>
+        <v>46285.716319444444</v>
       </c>
       <c r="D62" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E62" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="F62">
-        <v>38368</v>
+        <v>43130</v>
       </c>
       <c r="G62" t="s">
         <v>28</v>
@@ -3581,22 +3575,22 @@
     </row>
     <row r="63" spans="1:26">
       <c r="A63">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B63" s="3">
-        <v>46285.71597222222</v>
+        <v>46285.71634259259</v>
       </c>
       <c r="C63" s="3">
-        <v>46285.716319444444</v>
+        <v>46285.718784722223</v>
       </c>
       <c r="D63" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E63" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F63">
-        <v>43130</v>
+        <v>38363</v>
       </c>
       <c r="G63" t="s">
         <v>28</v>
@@ -3607,22 +3601,22 @@
     </row>
     <row r="64" spans="1:26">
       <c r="A64">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B64" s="3">
-        <v>46285.71634259259</v>
+        <v>46285.697152777779</v>
       </c>
       <c r="C64" s="3">
-        <v>46285.718784722223</v>
+        <v>46285.725115740737</v>
       </c>
       <c r="D64" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E64" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F64">
-        <v>38363</v>
+        <v>38604</v>
       </c>
       <c r="G64" t="s">
         <v>28</v>
@@ -3633,22 +3627,22 @@
     </row>
     <row r="65" spans="1:26">
       <c r="A65">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B65" s="3">
-        <v>46285.697152777779</v>
+        <v>46285.727719907409</v>
       </c>
       <c r="C65" s="3">
-        <v>46285.725115740737</v>
+        <v>46285.732407407406</v>
       </c>
       <c r="D65" t="s">
-        <v>154</v>
+        <v>89</v>
       </c>
       <c r="E65" t="s">
-        <v>155</v>
+        <v>90</v>
       </c>
       <c r="F65">
-        <v>38604</v>
+        <v>38515</v>
       </c>
       <c r="G65" t="s">
         <v>28</v>
@@ -3659,22 +3653,22 @@
     </row>
     <row r="66" spans="1:26">
       <c r="A66">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B66" s="3">
-        <v>46285.727719907409</v>
+        <v>46285.73741898148</v>
       </c>
       <c r="C66" s="3">
-        <v>46285.732407407406</v>
+        <v>46285.740914351853</v>
       </c>
       <c r="D66" t="s">
-        <v>91</v>
+        <v>74</v>
       </c>
       <c r="E66" t="s">
-        <v>92</v>
+        <v>75</v>
       </c>
       <c r="F66">
-        <v>38515</v>
+        <v>38333</v>
       </c>
       <c r="G66" t="s">
         <v>28</v>
@@ -3685,25 +3679,28 @@
     </row>
     <row r="67" spans="1:26">
       <c r="A67">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B67" s="3">
-        <v>46285.73741898148</v>
+        <v>46285.753125000003</v>
       </c>
       <c r="C67" s="3">
-        <v>46285.740914351853</v>
+        <v>46285.754803240743</v>
       </c>
       <c r="D67" t="s">
-        <v>74</v>
+        <v>155</v>
       </c>
       <c r="E67" t="s">
-        <v>75</v>
+        <v>156</v>
       </c>
       <c r="F67">
-        <v>38333</v>
+        <v>38511</v>
       </c>
       <c r="G67" t="s">
-        <v>28</v>
+        <v>117</v>
+      </c>
+      <c r="L67" t="s">
+        <v>157</v>
       </c>
       <c r="X67" s="5"/>
       <c r="Y67" s="5"/>
@@ -3711,28 +3708,25 @@
     </row>
     <row r="68" spans="1:26">
       <c r="A68">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B68" s="3">
-        <v>46285.753125000003</v>
+        <v>46285.757152777776</v>
       </c>
       <c r="C68" s="3">
-        <v>46285.754803240743</v>
+        <v>46285.757719907408</v>
       </c>
       <c r="D68" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E68" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="F68">
-        <v>38511</v>
+        <v>38143</v>
       </c>
       <c r="G68" t="s">
-        <v>118</v>
-      </c>
-      <c r="L68" t="s">
-        <v>158</v>
+        <v>28</v>
       </c>
       <c r="X68" s="5"/>
       <c r="Y68" s="5"/>
@@ -3740,25 +3734,25 @@
     </row>
     <row r="69" spans="1:26">
       <c r="A69">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="B69" s="3">
-        <v>46285.757152777776</v>
+        <v>46285.756018518521</v>
       </c>
       <c r="C69" s="3">
-        <v>46285.757719907408</v>
+        <v>46285.758657407408</v>
       </c>
       <c r="D69" t="s">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="E69" t="s">
-        <v>160</v>
+        <v>75</v>
       </c>
       <c r="F69">
-        <v>38143</v>
+        <v>38333</v>
       </c>
       <c r="G69" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X69" s="5"/>
       <c r="Y69" s="5"/>
@@ -3766,25 +3760,25 @@
     </row>
     <row r="70" spans="1:26">
       <c r="A70">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B70" s="3">
-        <v>46285.756018518521</v>
+        <v>46285.776655092595</v>
       </c>
       <c r="C70" s="3">
-        <v>46285.758657407408</v>
+        <v>46285.777777777781</v>
       </c>
       <c r="D70" t="s">
-        <v>74</v>
+        <v>160</v>
       </c>
       <c r="E70" t="s">
-        <v>75</v>
+        <v>161</v>
       </c>
       <c r="F70">
-        <v>38333</v>
+        <v>43070</v>
       </c>
       <c r="G70" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X70" s="5"/>
       <c r="Y70" s="5"/>
@@ -3792,25 +3786,25 @@
     </row>
     <row r="71" spans="1:26">
       <c r="A71">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B71" s="3">
-        <v>46285.776655092595</v>
+        <v>46285.803402777776</v>
       </c>
       <c r="C71" s="3">
-        <v>46285.777777777781</v>
+        <v>46285.803564814814</v>
       </c>
       <c r="D71" t="s">
-        <v>161</v>
+        <v>54</v>
       </c>
       <c r="E71" t="s">
-        <v>162</v>
+        <v>55</v>
       </c>
       <c r="F71">
-        <v>43070</v>
+        <v>38862</v>
       </c>
       <c r="G71" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="X71" s="5"/>
       <c r="Y71" s="5"/>
@@ -3818,25 +3812,25 @@
     </row>
     <row r="72" spans="1:26">
       <c r="A72">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="B72" s="3">
-        <v>46285.803402777776</v>
+        <v>46285.804432870369</v>
       </c>
       <c r="C72" s="3">
-        <v>46285.803564814814</v>
+        <v>46285.805949074071</v>
       </c>
       <c r="D72" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="E72" t="s">
-        <v>55</v>
+        <v>163</v>
       </c>
       <c r="F72">
-        <v>38862</v>
+        <v>38339</v>
       </c>
       <c r="G72" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="X72" s="5"/>
       <c r="Y72" s="5"/>
@@ -3844,25 +3838,28 @@
     </row>
     <row r="73" spans="1:26">
       <c r="A73">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B73" s="3">
-        <v>46285.804432870369</v>
+        <v>46285.818182870367</v>
       </c>
       <c r="C73" s="3">
-        <v>46285.805949074071</v>
+        <v>46285.818715277775</v>
       </c>
       <c r="D73" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E73" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F73">
-        <v>38339</v>
+        <v>38351</v>
       </c>
       <c r="G73" t="s">
-        <v>28</v>
+        <v>117</v>
+      </c>
+      <c r="L73" t="s">
+        <v>166</v>
       </c>
       <c r="X73" s="5"/>
       <c r="Y73" s="5"/>
@@ -3870,28 +3867,25 @@
     </row>
     <row r="74" spans="1:26">
       <c r="A74">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B74" s="3">
-        <v>46285.818182870367</v>
+        <v>46285.83966435185</v>
       </c>
       <c r="C74" s="3">
-        <v>46285.818715277775</v>
+        <v>46285.84</v>
       </c>
       <c r="D74" t="s">
-        <v>165</v>
+        <v>97</v>
       </c>
       <c r="E74" t="s">
-        <v>166</v>
+        <v>98</v>
       </c>
       <c r="F74">
-        <v>38351</v>
+        <v>38656</v>
       </c>
       <c r="G74" t="s">
-        <v>118</v>
-      </c>
-      <c r="L74" t="s">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="X74" s="5"/>
       <c r="Y74" s="5"/>
@@ -3899,22 +3893,22 @@
     </row>
     <row r="75" spans="1:26">
       <c r="A75">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B75" s="3">
-        <v>46285.83966435185</v>
+        <v>46285.849097222221</v>
       </c>
       <c r="C75" s="3">
-        <v>46285.84</v>
+        <v>46285.849733796298</v>
       </c>
       <c r="D75" t="s">
-        <v>98</v>
+        <v>167</v>
       </c>
       <c r="E75" t="s">
-        <v>99</v>
+        <v>168</v>
       </c>
       <c r="F75">
-        <v>38656</v>
+        <v>38456</v>
       </c>
       <c r="G75" t="s">
         <v>28</v>
@@ -3925,22 +3919,22 @@
     </row>
     <row r="76" spans="1:26">
       <c r="A76">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B76" s="3">
-        <v>46285.849097222221</v>
+        <v>46285.860462962963</v>
       </c>
       <c r="C76" s="3">
-        <v>46285.849733796298</v>
+        <v>46285.861203703702</v>
       </c>
       <c r="D76" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E76" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F76">
-        <v>38456</v>
+        <v>38894</v>
       </c>
       <c r="G76" t="s">
         <v>28</v>
@@ -3951,22 +3945,22 @@
     </row>
     <row r="77" spans="1:26">
       <c r="A77">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B77" s="3">
-        <v>46285.860462962963</v>
+        <v>46285.870069444441</v>
       </c>
       <c r="C77" s="3">
-        <v>46285.861203703702</v>
+        <v>46285.870717592596</v>
       </c>
       <c r="D77" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E77" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F77">
-        <v>38894</v>
+        <v>43193</v>
       </c>
       <c r="G77" t="s">
         <v>28</v>
@@ -3977,22 +3971,22 @@
     </row>
     <row r="78" spans="1:26">
       <c r="A78">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="B78" s="3">
-        <v>46285.870069444441</v>
+        <v>46285.902222222219</v>
       </c>
       <c r="C78" s="3">
-        <v>46285.870717592596</v>
+        <v>46285.902743055558</v>
       </c>
       <c r="D78" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="E78" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F78">
-        <v>43193</v>
+        <v>38176</v>
       </c>
       <c r="G78" t="s">
         <v>28</v>
@@ -4003,25 +3997,34 @@
     </row>
     <row r="79" spans="1:26">
       <c r="A79">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="B79" s="3">
-        <v>46285.902222222219</v>
+        <v>46285.903032407405</v>
       </c>
       <c r="C79" s="3">
-        <v>46285.902743055558</v>
+        <v>46285.908125000002</v>
       </c>
       <c r="D79" t="s">
+        <v>173</v>
+      </c>
+      <c r="E79" t="s">
         <v>174</v>
-      </c>
-      <c r="E79" t="s">
-        <v>175</v>
       </c>
       <c r="F79">
         <v>38176</v>
       </c>
       <c r="G79" t="s">
-        <v>28</v>
+        <v>77</v>
+      </c>
+      <c r="Q79" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R79" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S79" t="s">
+        <v>175</v>
       </c>
       <c r="X79" s="5"/>
       <c r="Y79" s="5"/>
@@ -4029,34 +4032,25 @@
     </row>
     <row r="80" spans="1:26">
       <c r="A80">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="B80" s="3">
-        <v>46285.903032407405</v>
+        <v>46285.883113425924</v>
       </c>
       <c r="C80" s="3">
-        <v>46285.908125000002</v>
+        <v>46285.955520833333</v>
       </c>
       <c r="D80" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E80" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F80">
-        <v>38176</v>
+        <v>43152</v>
       </c>
       <c r="G80" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q80" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R80" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="S80" t="s">
-        <v>176</v>
+        <v>28</v>
       </c>
       <c r="X80" s="5"/>
       <c r="Y80" s="5"/>
@@ -4064,22 +4058,22 @@
     </row>
     <row r="81" spans="1:26">
       <c r="A81">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B81" s="3">
-        <v>46285.883113425924</v>
+        <v>46285.965312499997</v>
       </c>
       <c r="C81" s="3">
-        <v>46285.955520833333</v>
+        <v>46285.968553240738</v>
       </c>
       <c r="D81" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E81" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="F81">
-        <v>43152</v>
+        <v>38460</v>
       </c>
       <c r="G81" t="s">
         <v>28</v>
@@ -4090,22 +4084,22 @@
     </row>
     <row r="82" spans="1:26">
       <c r="A82">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B82" s="3">
-        <v>46285.965312499997</v>
+        <v>46285.990925925929</v>
       </c>
       <c r="C82" s="3">
-        <v>46285.968553240738</v>
+        <v>46285.991226851853</v>
       </c>
       <c r="D82" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E82" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F82">
-        <v>38460</v>
+        <v>38930</v>
       </c>
       <c r="G82" t="s">
         <v>28</v>
@@ -4116,22 +4110,22 @@
     </row>
     <row r="83" spans="1:26">
       <c r="A83">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="B83" s="3">
-        <v>46285.990925925929</v>
+        <v>46286.250625000001</v>
       </c>
       <c r="C83" s="3">
-        <v>46285.991226851853</v>
+        <v>46286.252256944441</v>
       </c>
       <c r="D83" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E83" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="F83">
-        <v>38930</v>
+        <v>38845</v>
       </c>
       <c r="G83" t="s">
         <v>28</v>
@@ -4142,22 +4136,22 @@
     </row>
     <row r="84" spans="1:26">
       <c r="A84">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="B84" s="3">
-        <v>46286.250625000001</v>
+        <v>46286.264837962961</v>
       </c>
       <c r="C84" s="3">
-        <v>46286.252256944441</v>
+        <v>46286.265972222223</v>
       </c>
       <c r="D84" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E84" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F84">
-        <v>38845</v>
+        <v>38374</v>
       </c>
       <c r="G84" t="s">
         <v>28</v>
@@ -4168,25 +4162,28 @@
     </row>
     <row r="85" spans="1:26">
       <c r="A85">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B85" s="3">
-        <v>46286.264837962961</v>
+        <v>46286.31527777778</v>
       </c>
       <c r="C85" s="3">
-        <v>46286.265972222223</v>
+        <v>46286.317291666666</v>
       </c>
       <c r="D85" t="s">
-        <v>185</v>
+        <v>147</v>
       </c>
       <c r="E85" t="s">
+        <v>148</v>
+      </c>
+      <c r="F85">
+        <v>38695</v>
+      </c>
+      <c r="G85" t="s">
+        <v>64</v>
+      </c>
+      <c r="O85" t="s">
         <v>186</v>
-      </c>
-      <c r="F85">
-        <v>38374</v>
-      </c>
-      <c r="G85" t="s">
-        <v>28</v>
       </c>
       <c r="X85" s="5"/>
       <c r="Y85" s="5"/>
@@ -4194,27 +4191,27 @@
     </row>
     <row r="86" spans="1:26">
       <c r="A86">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B86" s="3">
-        <v>46286.31527777778</v>
+        <v>46286.342835648145</v>
       </c>
       <c r="C86" s="3">
-        <v>46286.317291666666</v>
+        <v>46286.345277777778</v>
       </c>
       <c r="D86" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="E86" t="s">
-        <v>149</v>
+        <v>101</v>
       </c>
       <c r="F86">
-        <v>38695</v>
+        <v>38770</v>
       </c>
       <c r="G86" t="s">
-        <v>64</v>
-      </c>
-      <c r="O86" t="s">
+        <v>126</v>
+      </c>
+      <c r="J86" t="s">
         <v>187</v>
       </c>
       <c r="X86" s="5"/>
@@ -4223,27 +4220,33 @@
     </row>
     <row r="87" spans="1:26">
       <c r="A87">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B87" s="3">
-        <v>46286.342835648145</v>
+        <v>46286.345578703702</v>
       </c>
       <c r="C87" s="3">
-        <v>46286.345277777778</v>
+        <v>46286.349328703705</v>
       </c>
       <c r="D87" t="s">
+        <v>100</v>
+      </c>
+      <c r="E87" t="s">
         <v>101</v>
-      </c>
-      <c r="E87" t="s">
-        <v>102</v>
       </c>
       <c r="F87">
         <v>38770</v>
       </c>
       <c r="G87" t="s">
-        <v>127</v>
-      </c>
-      <c r="J87" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q87" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R87" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S87" t="s">
         <v>188</v>
       </c>
       <c r="X87" s="5"/>
@@ -4252,33 +4255,27 @@
     </row>
     <row r="88" spans="1:26">
       <c r="A88">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="B88" s="3">
-        <v>46286.345578703702</v>
+        <v>46286.439895833333</v>
       </c>
       <c r="C88" s="3">
-        <v>46286.349328703705</v>
+        <v>46286.440069444441</v>
       </c>
       <c r="D88" t="s">
-        <v>101</v>
+        <v>147</v>
       </c>
       <c r="E88" t="s">
-        <v>102</v>
+        <v>148</v>
       </c>
       <c r="F88">
-        <v>38770</v>
+        <v>38695</v>
       </c>
       <c r="G88" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q88" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R88" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="S88" t="s">
+        <v>126</v>
+      </c>
+      <c r="J88" t="s">
         <v>189</v>
       </c>
       <c r="X88" s="5"/>
@@ -4287,27 +4284,27 @@
     </row>
     <row r="89" spans="1:26">
       <c r="A89">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B89" s="3">
-        <v>46286.439895833333</v>
+        <v>46286.446122685185</v>
       </c>
       <c r="C89" s="3">
-        <v>46286.440069444441</v>
+        <v>46286.446469907409</v>
       </c>
       <c r="D89" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E89" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="F89">
-        <v>38695</v>
+        <v>38351</v>
       </c>
       <c r="G89" t="s">
-        <v>127</v>
-      </c>
-      <c r="J89" t="s">
+        <v>117</v>
+      </c>
+      <c r="L89" t="s">
         <v>190</v>
       </c>
       <c r="X89" s="5"/>
@@ -4316,28 +4313,31 @@
     </row>
     <row r="90" spans="1:26">
       <c r="A90">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B90" s="3">
-        <v>46286.446122685185</v>
+        <v>46286.449942129628</v>
       </c>
       <c r="C90" s="3">
-        <v>46286.446469907409</v>
+        <v>46286.450671296298</v>
       </c>
       <c r="D90" t="s">
-        <v>165</v>
+        <v>191</v>
       </c>
       <c r="E90" t="s">
-        <v>166</v>
+        <v>192</v>
       </c>
       <c r="F90">
-        <v>38351</v>
+        <v>38800</v>
       </c>
       <c r="G90" t="s">
-        <v>118</v>
-      </c>
-      <c r="L90" t="s">
-        <v>191</v>
+        <v>36</v>
+      </c>
+      <c r="M90" t="s">
+        <v>124</v>
+      </c>
+      <c r="N90" t="s">
+        <v>193</v>
       </c>
       <c r="X90" s="5"/>
       <c r="Y90" s="5"/>
@@ -4345,31 +4345,28 @@
     </row>
     <row r="91" spans="1:26">
       <c r="A91">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B91" s="3">
-        <v>46286.449942129628</v>
+        <v>46286.457835648151</v>
       </c>
       <c r="C91" s="3">
-        <v>46286.450671296298</v>
+        <v>46286.460810185185</v>
       </c>
       <c r="D91" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E91" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F91">
-        <v>38800</v>
+        <v>43169</v>
       </c>
       <c r="G91" t="s">
-        <v>36</v>
-      </c>
-      <c r="M91" t="s">
-        <v>125</v>
-      </c>
-      <c r="N91" t="s">
-        <v>194</v>
+        <v>117</v>
+      </c>
+      <c r="L91" t="s">
+        <v>196</v>
       </c>
       <c r="X91" s="5"/>
       <c r="Y91" s="5"/>
@@ -4377,28 +4374,28 @@
     </row>
     <row r="92" spans="1:26">
       <c r="A92">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B92" s="3">
-        <v>46286.457835648151</v>
+        <v>46286.462824074071</v>
       </c>
       <c r="C92" s="3">
-        <v>46286.460810185185</v>
+        <v>46286.469953703701</v>
       </c>
       <c r="D92" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E92" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F92">
-        <v>43169</v>
+        <v>38502</v>
       </c>
       <c r="G92" t="s">
-        <v>118</v>
-      </c>
-      <c r="L92" t="s">
-        <v>197</v>
+        <v>126</v>
+      </c>
+      <c r="J92" t="s">
+        <v>199</v>
       </c>
       <c r="X92" s="5"/>
       <c r="Y92" s="5"/>
@@ -4406,27 +4403,27 @@
     </row>
     <row r="93" spans="1:26">
       <c r="A93">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B93" s="3">
-        <v>46286.462824074071</v>
+        <v>46286.47011574074</v>
       </c>
       <c r="C93" s="3">
-        <v>46286.469953703701</v>
+        <v>46286.470636574071</v>
       </c>
       <c r="D93" t="s">
+        <v>197</v>
+      </c>
+      <c r="E93" t="s">
         <v>198</v>
-      </c>
-      <c r="E93" t="s">
-        <v>199</v>
       </c>
       <c r="F93">
         <v>38502</v>
       </c>
       <c r="G93" t="s">
-        <v>127</v>
-      </c>
-      <c r="J93" t="s">
+        <v>32</v>
+      </c>
+      <c r="K93" t="s">
         <v>200</v>
       </c>
       <c r="X93" s="5"/>
@@ -4435,28 +4432,28 @@
     </row>
     <row r="94" spans="1:26">
       <c r="A94">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B94" s="3">
-        <v>46286.47011574074</v>
+        <v>46286.468009259261</v>
       </c>
       <c r="C94" s="3">
-        <v>46286.470636574071</v>
+        <v>46286.47152777778</v>
       </c>
       <c r="D94" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="E94" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F94">
-        <v>38502</v>
+        <v>38594</v>
       </c>
       <c r="G94" t="s">
-        <v>32</v>
-      </c>
-      <c r="K94" t="s">
-        <v>201</v>
+        <v>117</v>
+      </c>
+      <c r="L94" t="s">
+        <v>203</v>
       </c>
       <c r="X94" s="5"/>
       <c r="Y94" s="5"/>
@@ -4464,25 +4461,25 @@
     </row>
     <row r="95" spans="1:26">
       <c r="A95">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B95" s="3">
-        <v>46286.468009259261</v>
+        <v>46286.471122685187</v>
       </c>
       <c r="C95" s="3">
-        <v>46286.47152777778</v>
+        <v>46286.47283564815</v>
       </c>
       <c r="D95" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="E95" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="F95">
-        <v>38594</v>
+        <v>38502</v>
       </c>
       <c r="G95" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="L95" t="s">
         <v>204</v>
@@ -4493,27 +4490,27 @@
     </row>
     <row r="96" spans="1:26">
       <c r="A96">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="B96" s="3">
-        <v>46286.471122685187</v>
+        <v>46286.473715277774</v>
       </c>
       <c r="C96" s="3">
-        <v>46286.47283564815</v>
+        <v>46286.476759259262</v>
       </c>
       <c r="D96" t="s">
+        <v>197</v>
+      </c>
+      <c r="E96" t="s">
         <v>198</v>
-      </c>
-      <c r="E96" t="s">
-        <v>199</v>
       </c>
       <c r="F96">
         <v>38502</v>
       </c>
       <c r="G96" t="s">
-        <v>118</v>
-      </c>
-      <c r="L96" t="s">
+        <v>64</v>
+      </c>
+      <c r="O96" t="s">
         <v>205</v>
       </c>
       <c r="X96" s="5"/>
@@ -4522,27 +4519,33 @@
     </row>
     <row r="97" spans="1:26">
       <c r="A97">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B97" s="3">
-        <v>46286.473715277774</v>
+        <v>46286.476898148147</v>
       </c>
       <c r="C97" s="3">
-        <v>46286.476759259262</v>
+        <v>46286.47859953704</v>
       </c>
       <c r="D97" t="s">
+        <v>197</v>
+      </c>
+      <c r="E97" t="s">
         <v>198</v>
-      </c>
-      <c r="E97" t="s">
-        <v>199</v>
       </c>
       <c r="F97">
         <v>38502</v>
       </c>
       <c r="G97" t="s">
-        <v>64</v>
-      </c>
-      <c r="O97" t="s">
+        <v>77</v>
+      </c>
+      <c r="Q97" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="R97" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="S97" t="s">
         <v>206</v>
       </c>
       <c r="X97" s="5"/>
@@ -4551,34 +4554,25 @@
     </row>
     <row r="98" spans="1:26">
       <c r="A98">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="B98" s="3">
-        <v>46286.476898148147</v>
+        <v>46286.482465277775</v>
       </c>
       <c r="C98" s="3">
-        <v>46286.47859953704</v>
+        <v>46286.484652777777</v>
       </c>
       <c r="D98" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="E98" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="F98">
-        <v>38502</v>
+        <v>38859</v>
       </c>
       <c r="G98" t="s">
-        <v>77</v>
-      </c>
-      <c r="Q98" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="R98" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="S98" t="s">
-        <v>207</v>
+        <v>28</v>
       </c>
       <c r="X98" s="5"/>
       <c r="Y98" s="5"/>
@@ -4586,25 +4580,28 @@
     </row>
     <row r="99" spans="1:26">
       <c r="A99">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B99" s="3">
-        <v>46286.482465277775</v>
+        <v>46286.485300925924</v>
       </c>
       <c r="C99" s="3">
-        <v>46286.484652777777</v>
+        <v>46286.488240740742</v>
       </c>
       <c r="D99" t="s">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="E99" t="s">
+        <v>161</v>
+      </c>
+      <c r="F99">
+        <v>43070</v>
+      </c>
+      <c r="G99" t="s">
+        <v>117</v>
+      </c>
+      <c r="L99" t="s">
         <v>209</v>
-      </c>
-      <c r="F99">
-        <v>38859</v>
-      </c>
-      <c r="G99" t="s">
-        <v>28</v>
       </c>
       <c r="X99" s="5"/>
       <c r="Y99" s="5"/>
@@ -4612,27 +4609,30 @@
     </row>
     <row r="100" spans="1:26">
       <c r="A100">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="B100" s="3">
-        <v>46286.485300925924</v>
+        <v>46286.488402777781</v>
       </c>
       <c r="C100" s="3">
-        <v>46286.488240740742</v>
+        <v>46286.489004629628</v>
       </c>
       <c r="D100" t="s">
+        <v>160</v>
+      </c>
+      <c r="E100" t="s">
         <v>161</v>
-      </c>
-      <c r="E100" t="s">
-        <v>162</v>
       </c>
       <c r="F100">
         <v>43070</v>
       </c>
       <c r="G100" t="s">
-        <v>118</v>
-      </c>
-      <c r="L100" t="s">
+        <v>123</v>
+      </c>
+      <c r="H100" t="s">
+        <v>124</v>
+      </c>
+      <c r="I100" t="s">
         <v>210</v>
       </c>
       <c r="X100" s="5"/>
@@ -4641,61 +4641,71 @@
     </row>
     <row r="101" spans="1:26">
       <c r="A101">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B101" s="3">
-        <v>46286.488402777781</v>
+        <v>46286.488599536999</v>
       </c>
       <c r="C101" s="3">
-        <v>46286.489004629628</v>
-      </c>
-      <c r="D101" t="s">
-        <v>161</v>
-      </c>
-      <c r="E101" t="s">
-        <v>162</v>
+        <v>46286.490428240701</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E101" s="2" t="s">
+        <v>198</v>
       </c>
       <c r="F101">
-        <v>43070</v>
-      </c>
-      <c r="G101" t="s">
-        <v>124</v>
-      </c>
-      <c r="H101" t="s">
-        <v>125</v>
-      </c>
-      <c r="I101" t="s">
-        <v>211</v>
-      </c>
+        <v>38502</v>
+      </c>
+      <c r="G101" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="J101" s="2"/>
+      <c r="K101" s="2"/>
+      <c r="L101" s="2"/>
+      <c r="M101" s="2"/>
+      <c r="N101" s="2"/>
+      <c r="O101" s="2"/>
+      <c r="P101" s="2"/>
+      <c r="Q101" s="2"/>
+      <c r="R101" s="2"/>
+      <c r="S101" s="2"/>
+      <c r="V101" s="2"/>
+      <c r="W101" s="2"/>
       <c r="X101" s="5"/>
       <c r="Y101" s="5"/>
       <c r="Z101" s="5"/>
     </row>
     <row r="102" spans="1:26">
       <c r="A102">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B102" s="3">
-        <v>46286.488599536999</v>
+        <v>46286.4908796296</v>
       </c>
       <c r="C102" s="3">
-        <v>46286.490428240701</v>
+        <v>46286.491307870398</v>
       </c>
       <c r="D102" s="2" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="F102">
-        <v>38502</v>
+        <v>43070</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>28</v>
+        <v>126</v>
       </c>
       <c r="H102" s="2"/>
       <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
+      <c r="J102" s="2" t="s">
+        <v>211</v>
+      </c>
       <c r="K102" s="2"/>
       <c r="L102" s="2"/>
       <c r="M102" s="2"/>
@@ -4713,32 +4723,32 @@
     </row>
     <row r="103" spans="1:26">
       <c r="A103">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B103" s="3">
-        <v>46286.4908796296</v>
+        <v>46286.491527777798</v>
       </c>
       <c r="C103" s="3">
-        <v>46286.491307870398</v>
+        <v>46286.4919212963</v>
       </c>
       <c r="D103" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="E103" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="F103">
         <v>43070</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="H103" s="2"/>
       <c r="I103" s="2"/>
-      <c r="J103" s="2" t="s">
+      <c r="J103" s="2"/>
+      <c r="K103" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="K103" s="2"/>
       <c r="L103" s="2"/>
       <c r="M103" s="2"/>
       <c r="N103" s="2"/>
@@ -4755,35 +4765,37 @@
     </row>
     <row r="104" spans="1:26">
       <c r="A104">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B104" s="3">
-        <v>46286.491527777798</v>
+        <v>46286.4922337963</v>
       </c>
       <c r="C104" s="3">
-        <v>46286.4919212963</v>
+        <v>46286.492511574099</v>
       </c>
       <c r="D104" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="E104" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="F104">
         <v>43070</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H104" s="2"/>
       <c r="I104" s="2"/>
       <c r="J104" s="2"/>
-      <c r="K104" s="2" t="s">
+      <c r="K104" s="2"/>
+      <c r="L104" s="2"/>
+      <c r="M104" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="N104" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="L104" s="2"/>
-      <c r="M104" s="2"/>
-      <c r="N104" s="2"/>
       <c r="O104" s="2"/>
       <c r="P104" s="2"/>
       <c r="Q104" s="2"/>
@@ -4797,37 +4809,35 @@
     </row>
     <row r="105" spans="1:26">
       <c r="A105">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B105" s="3">
-        <v>46286.4922337963</v>
+        <v>46286.487812500003</v>
       </c>
       <c r="C105" s="3">
-        <v>46286.492511574099</v>
+        <v>46286.493483796301</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>161</v>
+        <v>214</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>162</v>
+        <v>215</v>
       </c>
       <c r="F105">
-        <v>43070</v>
+        <v>38657</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>36</v>
+        <v>117</v>
       </c>
       <c r="H105" s="2"/>
       <c r="I105" s="2"/>
       <c r="J105" s="2"/>
       <c r="K105" s="2"/>
-      <c r="L105" s="2"/>
-      <c r="M105" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="N105" s="2" t="s">
-        <v>214</v>
-      </c>
+      <c r="L105" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="M105" s="2"/>
+      <c r="N105" s="2"/>
       <c r="O105" s="2"/>
       <c r="P105" s="2"/>
       <c r="Q105" s="2"/>
@@ -4841,32 +4851,32 @@
     </row>
     <row r="106" spans="1:26">
       <c r="A106">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="B106" s="3">
-        <v>46286.487812500003</v>
+        <v>46286.494513888902</v>
       </c>
       <c r="C106" s="3">
-        <v>46286.493483796301</v>
+        <v>46286.495289351798</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F106">
-        <v>38657</v>
+        <v>38855</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H106" s="2"/>
       <c r="I106" s="2"/>
       <c r="J106" s="2"/>
       <c r="K106" s="2"/>
       <c r="L106" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="M106" s="2"/>
       <c r="N106" s="2"/>
@@ -4883,33 +4893,35 @@
     </row>
     <row r="107" spans="1:26">
       <c r="A107">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B107" s="3">
-        <v>46286.494513888902</v>
+        <v>46286.495729166701</v>
       </c>
       <c r="C107" s="3">
-        <v>46286.495289351798</v>
+        <v>46286.497175925899</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F107">
-        <v>38855</v>
+        <v>38659</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H107" s="2"/>
-      <c r="I107" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="H107" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I107" s="2" t="s">
+        <v>222</v>
+      </c>
       <c r="J107" s="2"/>
       <c r="K107" s="2"/>
-      <c r="L107" s="2" t="s">
-        <v>220</v>
-      </c>
+      <c r="L107" s="2"/>
       <c r="M107" s="2"/>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -4925,38 +4937,36 @@
     </row>
     <row r="108" spans="1:26">
       <c r="A108">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="B108" s="3">
-        <v>46286.495729166701</v>
+        <v>46286.4929513889</v>
       </c>
       <c r="C108" s="3">
-        <v>46286.497175925899</v>
+        <v>46286.497870370396</v>
       </c>
       <c r="D108" s="2" t="s">
-        <v>221</v>
+        <v>160</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>222</v>
+        <v>161</v>
       </c>
       <c r="F108">
-        <v>38659</v>
+        <v>43070</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H108" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I108" s="2" t="s">
-        <v>223</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
       <c r="J108" s="2"/>
       <c r="K108" s="2"/>
       <c r="L108" s="2"/>
       <c r="M108" s="2"/>
       <c r="N108" s="2"/>
-      <c r="O108" s="2"/>
+      <c r="O108" s="2" t="s">
+        <v>223</v>
+      </c>
       <c r="P108" s="2"/>
       <c r="Q108" s="2"/>
       <c r="R108" s="2"/>
@@ -4969,36 +4979,36 @@
     </row>
     <row r="109" spans="1:26">
       <c r="A109">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B109" s="3">
-        <v>46286.4929513889</v>
+        <v>46286.494375000002</v>
       </c>
       <c r="C109" s="3">
-        <v>46286.497870370396</v>
+        <v>46286.498495370397</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>161</v>
+        <v>224</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>162</v>
+        <v>225</v>
       </c>
       <c r="F109">
-        <v>43070</v>
+        <v>38569</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
       <c r="H109" s="2"/>
       <c r="I109" s="2"/>
       <c r="J109" s="2"/>
       <c r="K109" s="2"/>
-      <c r="L109" s="2"/>
+      <c r="L109" s="2" t="s">
+        <v>226</v>
+      </c>
       <c r="M109" s="2"/>
       <c r="N109" s="2"/>
-      <c r="O109" s="2" t="s">
-        <v>224</v>
-      </c>
+      <c r="O109" s="2"/>
       <c r="P109" s="2"/>
       <c r="Q109" s="2"/>
       <c r="R109" s="2"/>
@@ -5011,33 +5021,33 @@
     </row>
     <row r="110" spans="1:26">
       <c r="A110">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="B110" s="3">
-        <v>46286.494375000002</v>
+        <v>46286.503425925897</v>
       </c>
       <c r="C110" s="3">
-        <v>46286.498495370397</v>
+        <v>46286.503865740699</v>
       </c>
       <c r="D110" s="2" t="s">
-        <v>225</v>
+        <v>197</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>226</v>
+        <v>198</v>
       </c>
       <c r="F110">
-        <v>38569</v>
+        <v>38502</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="H110" s="2"/>
       <c r="I110" s="2"/>
-      <c r="J110" s="2"/>
+      <c r="J110" s="2" t="s">
+        <v>227</v>
+      </c>
       <c r="K110" s="2"/>
-      <c r="L110" s="2" t="s">
-        <v>227</v>
-      </c>
+      <c r="L110" s="2"/>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -5053,31 +5063,29 @@
     </row>
     <row r="111" spans="1:26">
       <c r="A111">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B111" s="3">
-        <v>46286.503425925897</v>
+        <v>46286.503703703696</v>
       </c>
       <c r="C111" s="3">
-        <v>46286.503865740699</v>
+        <v>46286.505370370403</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="F111">
-        <v>38502</v>
+        <v>38129</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>127</v>
+        <v>28</v>
       </c>
       <c r="H111" s="2"/>
       <c r="I111" s="2"/>
-      <c r="J111" s="2" t="s">
-        <v>228</v>
-      </c>
+      <c r="J111" s="2"/>
       <c r="K111" s="2"/>
       <c r="L111" s="2"/>
       <c r="M111" s="2"/>
@@ -5095,25 +5103,25 @@
     </row>
     <row r="112" spans="1:26">
       <c r="A112">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B112" s="3">
-        <v>46286.503703703696</v>
+        <v>46286.501562500001</v>
       </c>
       <c r="C112" s="3">
-        <v>46286.505370370403</v>
+        <v>46286.505509259303</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>229</v>
+        <v>160</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>230</v>
+        <v>161</v>
       </c>
       <c r="F112">
-        <v>38129</v>
+        <v>43070</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="H112" s="2"/>
       <c r="I112" s="2"/>
@@ -5123,7 +5131,9 @@
       <c r="M112" s="2"/>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
-      <c r="P112" s="2"/>
+      <c r="P112" s="2" t="s">
+        <v>230</v>
+      </c>
       <c r="Q112" s="2"/>
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
@@ -5135,37 +5145,37 @@
     </row>
     <row r="113" spans="1:26">
       <c r="A113">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B113" s="3">
-        <v>46286.501562500001</v>
+        <v>46286.505266203698</v>
       </c>
       <c r="C113" s="3">
-        <v>46286.505509259303</v>
+        <v>46286.505532407398</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="F113">
-        <v>43070</v>
+        <v>38502</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="H113" s="2"/>
       <c r="I113" s="2"/>
       <c r="J113" s="2"/>
-      <c r="K113" s="2"/>
+      <c r="K113" s="2" t="s">
+        <v>231</v>
+      </c>
       <c r="L113" s="2"/>
       <c r="M113" s="2"/>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
-      <c r="P113" s="2" t="s">
-        <v>231</v>
-      </c>
+      <c r="P113" s="2"/>
       <c r="Q113" s="2"/>
       <c r="R113" s="2"/>
       <c r="S113" s="2"/>
@@ -5177,33 +5187,33 @@
     </row>
     <row r="114" spans="1:26">
       <c r="A114">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="B114" s="3">
-        <v>46286.505266203698</v>
+        <v>46286.505682870396</v>
       </c>
       <c r="C114" s="3">
-        <v>46286.505532407398</v>
+        <v>46286.5059259259</v>
       </c>
       <c r="D114" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="E114" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="F114">
         <v>38502</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="H114" s="2"/>
       <c r="I114" s="2"/>
       <c r="J114" s="2"/>
-      <c r="K114" s="2" t="s">
+      <c r="K114" s="2"/>
+      <c r="L114" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="L114" s="2"/>
       <c r="M114" s="2"/>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -5219,33 +5229,31 @@
     </row>
     <row r="115" spans="1:26">
       <c r="A115">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B115" s="3">
-        <v>46286.505682870396</v>
+        <v>46286.505636574097</v>
       </c>
       <c r="C115" s="3">
-        <v>46286.5059259259</v>
+        <v>46286.5062384259</v>
       </c>
       <c r="D115" s="2" t="s">
-        <v>198</v>
+        <v>228</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>199</v>
+        <v>229</v>
       </c>
       <c r="F115">
-        <v>38502</v>
+        <v>38129</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="H115" s="2"/>
       <c r="I115" s="2"/>
       <c r="J115" s="2"/>
       <c r="K115" s="2"/>
-      <c r="L115" s="2" t="s">
-        <v>233</v>
-      </c>
+      <c r="L115" s="2"/>
       <c r="M115" s="2"/>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -5261,25 +5269,25 @@
     </row>
     <row r="116" spans="1:26">
       <c r="A116">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="B116" s="3">
-        <v>46286.505636574097</v>
+        <v>46286.506018518499</v>
       </c>
       <c r="C116" s="3">
-        <v>46286.5062384259</v>
+        <v>46286.5062847222</v>
       </c>
       <c r="D116" s="2" t="s">
-        <v>229</v>
+        <v>197</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>230</v>
+        <v>198</v>
       </c>
       <c r="F116">
-        <v>38129</v>
+        <v>38502</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>28</v>
+        <v>64</v>
       </c>
       <c r="H116" s="2"/>
       <c r="I116" s="2"/>
@@ -5288,7 +5296,9 @@
       <c r="L116" s="2"/>
       <c r="M116" s="2"/>
       <c r="N116" s="2"/>
-      <c r="O116" s="2"/>
+      <c r="O116" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="P116" s="2"/>
       <c r="Q116" s="2"/>
       <c r="R116" s="2"/>
@@ -5301,25 +5311,25 @@
     </row>
     <row r="117" spans="1:26">
       <c r="A117">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B117" s="3">
-        <v>46286.506018518499</v>
+        <v>46286.506365740701</v>
       </c>
       <c r="C117" s="3">
-        <v>46286.5062847222</v>
+        <v>46286.508009259298</v>
       </c>
       <c r="D117" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="E117" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="F117">
         <v>38502</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H117" s="2"/>
       <c r="I117" s="2"/>
@@ -5328,10 +5338,10 @@
       <c r="L117" s="2"/>
       <c r="M117" s="2"/>
       <c r="N117" s="2"/>
-      <c r="O117" s="2" t="s">
+      <c r="O117" s="2"/>
+      <c r="P117" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="P117" s="2"/>
       <c r="Q117" s="2"/>
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
@@ -5343,25 +5353,25 @@
     </row>
     <row r="118" spans="1:26">
       <c r="A118">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="B118" s="3">
-        <v>46286.506365740701</v>
+        <v>46286.506435185198</v>
       </c>
       <c r="C118" s="3">
-        <v>46286.508009259298</v>
+        <v>46286.508738425902</v>
       </c>
       <c r="D118" s="2" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="F118">
-        <v>38502</v>
+        <v>43070</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="H118" s="2"/>
       <c r="I118" s="2"/>
@@ -5371,12 +5381,16 @@
       <c r="M118" s="2"/>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
-      <c r="P118" s="2" t="s">
+      <c r="P118" s="2"/>
+      <c r="Q118" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R118" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="Q118" s="2"/>
-      <c r="R118" s="2"/>
-      <c r="S118" s="2"/>
+      <c r="S118" s="2" t="s">
+        <v>236</v>
+      </c>
       <c r="V118" s="2"/>
       <c r="W118" s="2"/>
       <c r="X118" s="5"/>
@@ -5385,22 +5399,22 @@
     </row>
     <row r="119" spans="1:26">
       <c r="A119">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B119" s="3">
-        <v>46286.506435185198</v>
+        <v>46286.5081712963</v>
       </c>
       <c r="C119" s="3">
-        <v>46286.508738425902</v>
+        <v>46286.508993055599</v>
       </c>
       <c r="D119" s="2" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>162</v>
+        <v>198</v>
       </c>
       <c r="F119">
-        <v>43070</v>
+        <v>38502</v>
       </c>
       <c r="G119" s="2" t="s">
         <v>77</v>
@@ -5415,10 +5429,10 @@
       <c r="O119" s="2"/>
       <c r="P119" s="2"/>
       <c r="Q119" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R119" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="R119" s="4" t="s">
-        <v>236</v>
       </c>
       <c r="S119" s="2" t="s">
         <v>237</v>
@@ -5431,25 +5445,25 @@
     </row>
     <row r="120" spans="1:26">
       <c r="A120">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="B120" s="3">
-        <v>46286.5081712963</v>
+        <v>46286.509004629603</v>
       </c>
       <c r="C120" s="3">
-        <v>46286.508993055599</v>
+        <v>46286.510370370401</v>
       </c>
       <c r="D120" s="2" t="s">
-        <v>198</v>
+        <v>160</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>199</v>
+        <v>161</v>
       </c>
       <c r="F120">
-        <v>38502</v>
+        <v>43070</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="H120" s="2"/>
       <c r="I120" s="2"/>
@@ -5460,15 +5474,9 @@
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
       <c r="P120" s="2"/>
-      <c r="Q120" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R120" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S120" s="2" t="s">
-        <v>238</v>
-      </c>
+      <c r="Q120" s="2"/>
+      <c r="R120" s="2"/>
+      <c r="S120" s="2"/>
       <c r="V120" s="2"/>
       <c r="W120" s="2"/>
       <c r="X120" s="5"/>
@@ -5477,25 +5485,25 @@
     </row>
     <row r="121" spans="1:26">
       <c r="A121">
-        <v>946</v>
+        <v>947</v>
       </c>
       <c r="B121" s="3">
-        <v>46286.509004629603</v>
+        <v>46286.506446759297</v>
       </c>
       <c r="C121" s="3">
-        <v>46286.510370370401</v>
+        <v>46286.510763888902</v>
       </c>
       <c r="D121" s="2" t="s">
-        <v>161</v>
+        <v>238</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>162</v>
+        <v>239</v>
       </c>
       <c r="F121">
-        <v>43070</v>
+        <v>38447</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H121" s="2"/>
       <c r="I121" s="2"/>
@@ -5517,31 +5525,33 @@
     </row>
     <row r="122" spans="1:26">
       <c r="A122">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B122" s="3">
-        <v>46286.506446759297</v>
+        <v>46286.514178240701</v>
       </c>
       <c r="C122" s="3">
-        <v>46286.510763888902</v>
+        <v>46286.514999999999</v>
       </c>
       <c r="D122" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="F122">
-        <v>38447</v>
+        <v>38567</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="H122" s="2"/>
       <c r="I122" s="2"/>
       <c r="J122" s="2"/>
       <c r="K122" s="2"/>
-      <c r="L122" s="2"/>
+      <c r="L122" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="M122" s="2"/>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -5557,33 +5567,31 @@
     </row>
     <row r="123" spans="1:26">
       <c r="A123">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B123" s="3">
-        <v>46286.514178240701</v>
+        <v>46286.510474536997</v>
       </c>
       <c r="C123" s="3">
-        <v>46286.514999999999</v>
+        <v>46286.515381944402</v>
       </c>
       <c r="D123" s="2" t="s">
-        <v>241</v>
+        <v>160</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>242</v>
+        <v>161</v>
       </c>
       <c r="F123">
-        <v>38567</v>
+        <v>43070</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="H123" s="2"/>
       <c r="I123" s="2"/>
       <c r="J123" s="2"/>
       <c r="K123" s="2"/>
-      <c r="L123" s="2" t="s">
-        <v>243</v>
-      </c>
+      <c r="L123" s="2"/>
       <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -5591,39 +5599,45 @@
       <c r="Q123" s="2"/>
       <c r="R123" s="2"/>
       <c r="S123" s="2"/>
-      <c r="V123" s="2"/>
-      <c r="W123" s="2"/>
+      <c r="V123" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="W123" s="2" t="s">
+        <v>244</v>
+      </c>
       <c r="X123" s="5"/>
       <c r="Y123" s="5"/>
       <c r="Z123" s="5"/>
     </row>
     <row r="124" spans="1:26">
       <c r="A124">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="B124" s="3">
-        <v>46286.510474536997</v>
+        <v>46286.508946759299</v>
       </c>
       <c r="C124" s="3">
-        <v>46286.515381944402</v>
+        <v>46286.516493055598</v>
       </c>
       <c r="D124" s="2" t="s">
-        <v>161</v>
+        <v>245</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>162</v>
+        <v>246</v>
       </c>
       <c r="F124">
-        <v>43070</v>
+        <v>43026</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="H124" s="2"/>
       <c r="I124" s="2"/>
       <c r="J124" s="2"/>
       <c r="K124" s="2"/>
-      <c r="L124" s="2"/>
+      <c r="L124" s="2" t="s">
+        <v>247</v>
+      </c>
       <c r="M124" s="2"/>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
@@ -5631,44 +5645,40 @@
       <c r="Q124" s="2"/>
       <c r="R124" s="2"/>
       <c r="S124" s="2"/>
-      <c r="V124" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="W124" s="2" t="s">
-        <v>245</v>
-      </c>
+      <c r="V124" s="2"/>
+      <c r="W124" s="2"/>
       <c r="X124" s="5"/>
       <c r="Y124" s="5"/>
       <c r="Z124" s="5"/>
     </row>
     <row r="125" spans="1:26">
       <c r="A125">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B125" s="3">
-        <v>46286.508946759299</v>
+        <v>46286.516319444403</v>
       </c>
       <c r="C125" s="3">
-        <v>46286.516493055598</v>
+        <v>46286.517048611102</v>
       </c>
       <c r="D125" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F125">
-        <v>43026</v>
+        <v>38375</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H125" s="2"/>
       <c r="I125" s="2"/>
       <c r="J125" s="2"/>
       <c r="K125" s="2"/>
       <c r="L125" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="M125" s="2"/>
       <c r="N125" s="2"/>
@@ -5685,32 +5695,32 @@
     </row>
     <row r="126" spans="1:26">
       <c r="A126">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B126" s="3">
-        <v>46286.516319444403</v>
+        <v>46286.511018518497</v>
       </c>
       <c r="C126" s="3">
-        <v>46286.517048611102</v>
+        <v>46286.519918981503</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F126">
-        <v>38375</v>
+        <v>38801</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H126" s="2"/>
       <c r="I126" s="2"/>
       <c r="J126" s="2"/>
       <c r="K126" s="2"/>
       <c r="L126" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M126" s="2"/>
       <c r="N126" s="2"/>
@@ -5727,33 +5737,35 @@
     </row>
     <row r="127" spans="1:26">
       <c r="A127">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B127" s="3">
-        <v>46286.511018518497</v>
+        <v>46286.506793981498</v>
       </c>
       <c r="C127" s="3">
-        <v>46286.519918981503</v>
+        <v>46286.520104166702</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F127">
-        <v>38801</v>
+        <v>43163</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="H127" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I127" s="2" t="s">
+        <v>256</v>
+      </c>
       <c r="J127" s="2"/>
       <c r="K127" s="2"/>
-      <c r="L127" s="2" t="s">
-        <v>254</v>
-      </c>
+      <c r="L127" s="2"/>
       <c r="M127" s="2"/>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -5769,35 +5781,33 @@
     </row>
     <row r="128" spans="1:26">
       <c r="A128">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="B128" s="3">
-        <v>46286.506793981498</v>
+        <v>46286.520219907397</v>
       </c>
       <c r="C128" s="3">
-        <v>46286.520104166702</v>
+        <v>46286.5206481481</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>255</v>
+        <v>30</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>256</v>
+        <v>31</v>
       </c>
       <c r="F128">
-        <v>43163</v>
+        <v>43164</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H128" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I128" s="2" t="s">
-        <v>257</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="H128" s="2"/>
+      <c r="I128" s="2"/>
       <c r="J128" s="2"/>
       <c r="K128" s="2"/>
-      <c r="L128" s="2"/>
+      <c r="L128" s="2" t="s">
+        <v>257</v>
+      </c>
       <c r="M128" s="2"/>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -5813,33 +5823,31 @@
     </row>
     <row r="129" spans="1:26">
       <c r="A129">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B129" s="3">
-        <v>46286.520219907397</v>
+        <v>46286.517719907402</v>
       </c>
       <c r="C129" s="3">
-        <v>46286.5206481481</v>
+        <v>46286.5221296296</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>30</v>
+        <v>258</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>31</v>
+        <v>259</v>
       </c>
       <c r="F129">
-        <v>43164</v>
+        <v>38615</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="H129" s="2"/>
       <c r="I129" s="2"/>
       <c r="J129" s="2"/>
       <c r="K129" s="2"/>
-      <c r="L129" s="2" t="s">
-        <v>258</v>
-      </c>
+      <c r="L129" s="2"/>
       <c r="M129" s="2"/>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -5855,31 +5863,33 @@
     </row>
     <row r="130" spans="1:26">
       <c r="A130">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="B130" s="3">
-        <v>46286.517719907402</v>
+        <v>46286.522499999999</v>
       </c>
       <c r="C130" s="3">
-        <v>46286.5221296296</v>
+        <v>46286.522916666698</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>259</v>
+        <v>220</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>260</v>
+        <v>221</v>
       </c>
       <c r="F130">
-        <v>38615</v>
+        <v>38659</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="H130" s="2"/>
       <c r="I130" s="2"/>
       <c r="J130" s="2"/>
       <c r="K130" s="2"/>
-      <c r="L130" s="2"/>
+      <c r="L130" s="2" t="s">
+        <v>260</v>
+      </c>
       <c r="M130" s="2"/>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -5895,33 +5905,31 @@
     </row>
     <row r="131" spans="1:26">
       <c r="A131">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B131" s="3">
-        <v>46286.522499999999</v>
+        <v>46286.520439814798</v>
       </c>
       <c r="C131" s="3">
-        <v>46286.522916666698</v>
+        <v>46286.5242939815</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>221</v>
+        <v>251</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>222</v>
+        <v>252</v>
       </c>
       <c r="F131">
-        <v>38659</v>
+        <v>38801</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="H131" s="2"/>
       <c r="I131" s="2"/>
       <c r="J131" s="2"/>
       <c r="K131" s="2"/>
-      <c r="L131" s="2" t="s">
-        <v>261</v>
-      </c>
+      <c r="L131" s="2"/>
       <c r="M131" s="2"/>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -5937,22 +5945,22 @@
     </row>
     <row r="132" spans="1:26">
       <c r="A132">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B132" s="3">
-        <v>46286.520439814798</v>
+        <v>46286.524942129603</v>
       </c>
       <c r="C132" s="3">
-        <v>46286.5242939815</v>
+        <v>46286.527488425898</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="F132">
-        <v>38801</v>
+        <v>38691</v>
       </c>
       <c r="G132" s="2" t="s">
         <v>28</v>
@@ -5977,31 +5985,33 @@
     </row>
     <row r="133" spans="1:26">
       <c r="A133">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B133" s="3">
-        <v>46286.524942129603</v>
+        <v>46286.519363425898</v>
       </c>
       <c r="C133" s="3">
-        <v>46286.527488425898</v>
+        <v>46286.527997685203</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="F133">
-        <v>38691</v>
+        <v>38718</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="H133" s="2"/>
       <c r="I133" s="2"/>
       <c r="J133" s="2"/>
       <c r="K133" s="2"/>
-      <c r="L133" s="2"/>
+      <c r="L133" s="2" t="s">
+        <v>265</v>
+      </c>
       <c r="M133" s="2"/>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -6017,33 +6027,31 @@
     </row>
     <row r="134" spans="1:26">
       <c r="A134">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="B134" s="3">
-        <v>46286.519363425898</v>
+        <v>46286.526423611103</v>
       </c>
       <c r="C134" s="3">
-        <v>46286.527997685203</v>
+        <v>46286.529050925899</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F134">
-        <v>38718</v>
+        <v>38107</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="H134" s="2"/>
       <c r="I134" s="2"/>
       <c r="J134" s="2"/>
       <c r="K134" s="2"/>
-      <c r="L134" s="2" t="s">
-        <v>266</v>
-      </c>
+      <c r="L134" s="2"/>
       <c r="M134" s="2"/>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -6059,22 +6067,22 @@
     </row>
     <row r="135" spans="1:26">
       <c r="A135">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B135" s="3">
-        <v>46286.526423611103</v>
+        <v>46286.532395833303</v>
       </c>
       <c r="C135" s="3">
-        <v>46286.529050925899</v>
+        <v>46286.534803240698</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F135">
-        <v>38107</v>
+        <v>38124</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>28</v>
@@ -6099,28 +6107,32 @@
     </row>
     <row r="136" spans="1:26">
       <c r="A136">
-        <v>961</v>
+        <v>962</v>
       </c>
       <c r="B136" s="3">
-        <v>46286.532395833303</v>
+        <v>46286.535266203697</v>
       </c>
       <c r="C136" s="3">
-        <v>46286.534803240698</v>
+        <v>46286.5360069444</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="F136">
-        <v>38124</v>
+        <v>38464</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="H136" s="2"/>
-      <c r="I136" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="H136" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I136" s="2" t="s">
+        <v>272</v>
+      </c>
       <c r="J136" s="2"/>
       <c r="K136" s="2"/>
       <c r="L136" s="2"/>
@@ -6139,32 +6151,28 @@
     </row>
     <row r="137" spans="1:26">
       <c r="A137">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B137" s="3">
-        <v>46286.535266203697</v>
+        <v>46286.512754629599</v>
       </c>
       <c r="C137" s="3">
-        <v>46286.5360069444</v>
+        <v>46286.536527777796</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F137">
-        <v>38464</v>
+        <v>38428</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H137" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I137" s="2" t="s">
-        <v>273</v>
-      </c>
+        <v>28</v>
+      </c>
+      <c r="H137" s="2"/>
+      <c r="I137" s="2"/>
       <c r="J137" s="2"/>
       <c r="K137" s="2"/>
       <c r="L137" s="2"/>
@@ -6183,22 +6191,22 @@
     </row>
     <row r="138" spans="1:26">
       <c r="A138">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="B138" s="3">
-        <v>46286.512754629599</v>
+        <v>46286.539525462998</v>
       </c>
       <c r="C138" s="3">
-        <v>46286.536527777796</v>
+        <v>46286.540520833303</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="F138">
-        <v>38428</v>
+        <v>38571</v>
       </c>
       <c r="G138" s="2" t="s">
         <v>28</v>
@@ -6223,22 +6231,22 @@
     </row>
     <row r="139" spans="1:26">
       <c r="A139">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B139" s="3">
-        <v>46286.539525462998</v>
+        <v>46286.4847800926</v>
       </c>
       <c r="C139" s="3">
-        <v>46286.540520833303</v>
+        <v>46286.549421296302</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>276</v>
+        <v>207</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>277</v>
+        <v>208</v>
       </c>
       <c r="F139">
-        <v>38571</v>
+        <v>38859</v>
       </c>
       <c r="G139" s="2" t="s">
         <v>28</v>
@@ -6263,31 +6271,33 @@
     </row>
     <row r="140" spans="1:26">
       <c r="A140">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="B140" s="3">
-        <v>46286.4847800926</v>
+        <v>46286.553229166697</v>
       </c>
       <c r="C140" s="3">
-        <v>46286.549421296302</v>
+        <v>46286.5534259259</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>208</v>
+        <v>277</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>209</v>
+        <v>278</v>
       </c>
       <c r="F140">
-        <v>38859</v>
+        <v>38496</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="H140" s="2"/>
       <c r="I140" s="2"/>
       <c r="J140" s="2"/>
       <c r="K140" s="2"/>
-      <c r="L140" s="2"/>
+      <c r="L140" s="2" t="s">
+        <v>279</v>
+      </c>
       <c r="M140" s="2"/>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -6303,32 +6313,32 @@
     </row>
     <row r="141" spans="1:26">
       <c r="A141">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B141" s="3">
-        <v>46286.553229166697</v>
+        <v>46286.547881944403</v>
       </c>
       <c r="C141" s="3">
-        <v>46286.5534259259</v>
+        <v>46286.553715277798</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="F141">
-        <v>38496</v>
+        <v>38468</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H141" s="2"/>
       <c r="I141" s="2"/>
       <c r="J141" s="2"/>
       <c r="K141" s="2"/>
       <c r="L141" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M141" s="2"/>
       <c r="N141" s="2"/>
@@ -6345,33 +6355,31 @@
     </row>
     <row r="142" spans="1:26">
       <c r="A142">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B142" s="3">
-        <v>46286.547881944403</v>
+        <v>46286.556145833303</v>
       </c>
       <c r="C142" s="3">
-        <v>46286.553715277798</v>
+        <v>46286.556898148097</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="F142">
-        <v>38468</v>
+        <v>38580</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="H142" s="2"/>
       <c r="I142" s="2"/>
       <c r="J142" s="2"/>
       <c r="K142" s="2"/>
-      <c r="L142" s="2" t="s">
-        <v>283</v>
-      </c>
+      <c r="L142" s="2"/>
       <c r="M142" s="2"/>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -6387,22 +6395,22 @@
     </row>
     <row r="143" spans="1:26">
       <c r="A143">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B143" s="3">
-        <v>46286.556145833303</v>
+        <v>46286.558020833298</v>
       </c>
       <c r="C143" s="3">
-        <v>46286.556898148097</v>
+        <v>46286.5603819444</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="F143">
-        <v>38580</v>
+        <v>43159</v>
       </c>
       <c r="G143" s="2" t="s">
         <v>28</v>
@@ -6427,22 +6435,22 @@
     </row>
     <row r="144" spans="1:26">
       <c r="A144">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="B144" s="3">
-        <v>46286.558020833298</v>
+        <v>46286.561041666697</v>
       </c>
       <c r="C144" s="3">
-        <v>46286.5603819444</v>
+        <v>46286.561851851897</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="F144">
-        <v>43159</v>
+        <v>38116</v>
       </c>
       <c r="G144" s="2" t="s">
         <v>28</v>
@@ -6467,31 +6475,33 @@
     </row>
     <row r="145" spans="1:26">
       <c r="A145">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="B145" s="3">
-        <v>46286.561041666697</v>
+        <v>46286.690682870401</v>
       </c>
       <c r="C145" s="3">
-        <v>46286.561851851897</v>
+        <v>46286.692245370403</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="F145">
-        <v>38116</v>
+        <v>38429</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>28</v>
+        <v>117</v>
       </c>
       <c r="H145" s="2"/>
       <c r="I145" s="2"/>
       <c r="J145" s="2"/>
       <c r="K145" s="2"/>
-      <c r="L145" s="2"/>
+      <c r="L145" s="2" t="s">
+        <v>291</v>
+      </c>
       <c r="M145" s="2"/>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
@@ -6507,32 +6517,32 @@
     </row>
     <row r="146" spans="1:26">
       <c r="A146">
-        <v>971</v>
+        <v>972</v>
       </c>
       <c r="B146" s="3">
-        <v>46286.690682870401</v>
+        <v>46286.778807870403</v>
       </c>
       <c r="C146" s="3">
-        <v>46286.692245370403</v>
+        <v>46286.781875000001</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="F146">
-        <v>38429</v>
+        <v>43034</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H146" s="2"/>
       <c r="I146" s="2"/>
       <c r="J146" s="2"/>
       <c r="K146" s="2"/>
       <c r="L146" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="M146" s="2"/>
       <c r="N146" s="2"/>
@@ -6549,32 +6559,32 @@
     </row>
     <row r="147" spans="1:26">
       <c r="A147">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B147" s="3">
-        <v>46286.778807870403</v>
+        <v>46286.968009259297</v>
       </c>
       <c r="C147" s="3">
-        <v>46286.781875000001</v>
+        <v>46286.974409722199</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F147">
-        <v>43034</v>
+        <v>38570</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H147" s="2"/>
       <c r="I147" s="2"/>
       <c r="J147" s="2"/>
       <c r="K147" s="2"/>
       <c r="L147" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M147" s="2"/>
       <c r="N147" s="2"/>
@@ -6591,32 +6601,32 @@
     </row>
     <row r="148" spans="1:26">
       <c r="A148">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="B148" s="3">
-        <v>46286.968009259297</v>
+        <v>46287.558356481502</v>
       </c>
       <c r="C148" s="3">
-        <v>46286.974409722199</v>
+        <v>46287.578206018501</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="F148">
-        <v>38570</v>
+        <v>38472</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H148" s="2"/>
       <c r="I148" s="2"/>
       <c r="J148" s="2"/>
       <c r="K148" s="2"/>
       <c r="L148" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M148" s="2"/>
       <c r="N148" s="2"/>
@@ -6633,25 +6643,25 @@
     </row>
     <row r="149" spans="1:26">
       <c r="A149">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="B149" s="3">
-        <v>46287.558356481502</v>
+        <v>46287.578344907401</v>
       </c>
       <c r="C149" s="3">
-        <v>46287.578206018501</v>
+        <v>46287.578726851803</v>
       </c>
       <c r="D149" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E149" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="E149" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="F149">
         <v>38472</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H149" s="2"/>
       <c r="I149" s="2"/>
@@ -6675,25 +6685,25 @@
     </row>
     <row r="150" spans="1:26">
       <c r="A150">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="B150" s="3">
-        <v>46287.578344907401</v>
+        <v>46287.578831018502</v>
       </c>
       <c r="C150" s="3">
-        <v>46287.578726851803</v>
+        <v>46287.579120370399</v>
       </c>
       <c r="D150" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E150" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="E150" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="F150">
         <v>38472</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H150" s="2"/>
       <c r="I150" s="2"/>
@@ -6717,25 +6727,25 @@
     </row>
     <row r="151" spans="1:26">
       <c r="A151">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B151" s="3">
-        <v>46287.578831018502</v>
+        <v>46287.579155092601</v>
       </c>
       <c r="C151" s="3">
-        <v>46287.579120370399</v>
+        <v>46287.579409722202</v>
       </c>
       <c r="D151" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E151" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="E151" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="F151">
         <v>38472</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H151" s="2"/>
       <c r="I151" s="2"/>
@@ -6759,25 +6769,25 @@
     </row>
     <row r="152" spans="1:26">
       <c r="A152">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B152" s="3">
-        <v>46287.579155092601</v>
+        <v>46287.579444444404</v>
       </c>
       <c r="C152" s="3">
-        <v>46287.579409722202</v>
+        <v>46287.579664351899</v>
       </c>
       <c r="D152" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E152" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="E152" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="F152">
         <v>38472</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H152" s="2"/>
       <c r="I152" s="2"/>
@@ -6801,25 +6811,25 @@
     </row>
     <row r="153" spans="1:26">
       <c r="A153">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B153" s="3">
-        <v>46287.579444444404</v>
+        <v>46287.727094907401</v>
       </c>
       <c r="C153" s="3">
-        <v>46287.579664351899</v>
+        <v>46287.727974537003</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>299</v>
+        <v>273</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>300</v>
+        <v>274</v>
       </c>
       <c r="F153">
-        <v>38472</v>
+        <v>38428</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H153" s="2"/>
       <c r="I153" s="2"/>
@@ -6843,25 +6853,25 @@
     </row>
     <row r="154" spans="1:26">
       <c r="A154">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="B154" s="3">
-        <v>46287.727094907401</v>
+        <v>46287.824976851902</v>
       </c>
       <c r="C154" s="3">
-        <v>46287.727974537003</v>
+        <v>46287.825254629599</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>274</v>
+        <v>238</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>275</v>
+        <v>239</v>
       </c>
       <c r="F154">
-        <v>38428</v>
+        <v>38447</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H154" s="2"/>
       <c r="I154" s="2"/>
@@ -6885,25 +6895,25 @@
     </row>
     <row r="155" spans="1:26">
       <c r="A155">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B155" s="3">
-        <v>46287.824976851902</v>
+        <v>46287.864421296297</v>
       </c>
       <c r="C155" s="3">
-        <v>46287.825254629599</v>
+        <v>46287.864837963003</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>239</v>
+        <v>261</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>240</v>
+        <v>262</v>
       </c>
       <c r="F155">
-        <v>38447</v>
+        <v>38691</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H155" s="2"/>
       <c r="I155" s="2"/>
@@ -6927,25 +6937,25 @@
     </row>
     <row r="156" spans="1:26">
       <c r="A156">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B156" s="3">
-        <v>46287.864421296297</v>
+        <v>46287.882118055597</v>
       </c>
       <c r="C156" s="3">
-        <v>46287.864837963003</v>
+        <v>46287.882569444402</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>262</v>
+        <v>287</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>263</v>
+        <v>288</v>
       </c>
       <c r="F156">
-        <v>38691</v>
+        <v>38116</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H156" s="2"/>
       <c r="I156" s="2"/>
@@ -6969,32 +6979,32 @@
     </row>
     <row r="157" spans="1:26">
       <c r="A157">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B157" s="3">
-        <v>46287.882118055597</v>
+        <v>46288.377581018503</v>
       </c>
       <c r="C157" s="3">
-        <v>46287.882569444402</v>
+        <v>46288.395624999997</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>288</v>
+        <v>309</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>289</v>
+        <v>310</v>
       </c>
       <c r="F157">
-        <v>38116</v>
+        <v>38678</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H157" s="2"/>
       <c r="I157" s="2"/>
       <c r="J157" s="2"/>
       <c r="K157" s="2"/>
       <c r="L157" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M157" s="2"/>
       <c r="N157" s="2"/>
@@ -7011,32 +7021,32 @@
     </row>
     <row r="158" spans="1:26">
       <c r="A158">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B158" s="3">
-        <v>46288.377581018503</v>
+        <v>46288.478645833296</v>
       </c>
       <c r="C158" s="3">
-        <v>46288.395624999997</v>
+        <v>46288.494097222203</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F158">
-        <v>38678</v>
+        <v>3850</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H158" s="2"/>
       <c r="I158" s="2"/>
       <c r="J158" s="2"/>
       <c r="K158" s="2"/>
       <c r="L158" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="M158" s="2"/>
       <c r="N158" s="2"/>
@@ -7053,40 +7063,44 @@
     </row>
     <row r="159" spans="1:26">
       <c r="A159">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B159" s="3">
-        <v>46288.478645833296</v>
+        <v>46288.520902777796</v>
       </c>
       <c r="C159" s="3">
-        <v>46288.494097222203</v>
+        <v>46288.545266203699</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F159">
-        <v>3850</v>
+        <v>38590</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>118</v>
+        <v>77</v>
       </c>
       <c r="H159" s="2"/>
       <c r="I159" s="2"/>
       <c r="J159" s="2"/>
       <c r="K159" s="2"/>
-      <c r="L159" s="2" t="s">
-        <v>315</v>
-      </c>
+      <c r="L159" s="2"/>
       <c r="M159" s="2"/>
       <c r="N159" s="2"/>
       <c r="O159" s="2"/>
       <c r="P159" s="2"/>
-      <c r="Q159" s="2"/>
-      <c r="R159" s="2"/>
-      <c r="S159" s="2"/>
+      <c r="Q159" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R159" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S159" s="2" t="s">
+        <v>317</v>
+      </c>
       <c r="V159" s="2"/>
       <c r="W159" s="2"/>
       <c r="X159" s="5"/>
@@ -7095,25 +7109,25 @@
     </row>
     <row r="160" spans="1:26">
       <c r="A160">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="B160" s="3">
-        <v>46288.520902777796</v>
+        <v>46288.545324074097</v>
       </c>
       <c r="C160" s="3">
-        <v>46288.545266203699</v>
+        <v>46288.549490740697</v>
       </c>
       <c r="D160" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E160" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="E160" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="F160">
         <v>38590</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>77</v>
+        <v>29</v>
       </c>
       <c r="H160" s="2"/>
       <c r="I160" s="2"/>
@@ -7124,15 +7138,9 @@
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
       <c r="P160" s="2"/>
-      <c r="Q160" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="R160" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="S160" s="2" t="s">
-        <v>318</v>
-      </c>
+      <c r="Q160" s="2"/>
+      <c r="R160" s="2"/>
+      <c r="S160" s="2"/>
       <c r="V160" s="2"/>
       <c r="W160" s="2"/>
       <c r="X160" s="5"/>
@@ -7141,30 +7149,32 @@
     </row>
     <row r="161" spans="1:26">
       <c r="A161">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="B161" s="3">
-        <v>46288.545324074097</v>
+        <v>46288.549537036997</v>
       </c>
       <c r="C161" s="3">
-        <v>46288.549490740697</v>
+        <v>46288.5518981481</v>
       </c>
       <c r="D161" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E161" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="E161" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="F161">
         <v>38590</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H161" s="2"/>
       <c r="I161" s="2"/>
       <c r="J161" s="2"/>
-      <c r="K161" s="2"/>
+      <c r="K161" s="2" t="s">
+        <v>318</v>
+      </c>
       <c r="L161" s="2"/>
       <c r="M161" s="2"/>
       <c r="N161" s="2"/>
@@ -7181,32 +7191,30 @@
     </row>
     <row r="162" spans="1:26">
       <c r="A162">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B162" s="3">
-        <v>46288.549537036997</v>
+        <v>46288.561805555597</v>
       </c>
       <c r="C162" s="3">
-        <v>46288.5518981481</v>
+        <v>46288.563287037003</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="F162">
-        <v>38590</v>
+        <v>38580</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="H162" s="2"/>
       <c r="I162" s="2"/>
       <c r="J162" s="2"/>
-      <c r="K162" s="2" t="s">
-        <v>319</v>
-      </c>
+      <c r="K162" s="2"/>
       <c r="L162" s="2"/>
       <c r="M162" s="2"/>
       <c r="N162" s="2"/>
@@ -7223,32 +7231,34 @@
     </row>
     <row r="163" spans="1:26">
       <c r="A163">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B163" s="3">
-        <v>46288.561805555597</v>
+        <v>46288.5519907407</v>
       </c>
       <c r="C163" s="3">
-        <v>46288.563287037003</v>
+        <v>46288.566412036998</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>284</v>
+        <v>315</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>285</v>
+        <v>316</v>
       </c>
       <c r="F163">
-        <v>38580</v>
+        <v>38590</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="H163" s="2"/>
       <c r="I163" s="2"/>
       <c r="J163" s="2"/>
       <c r="K163" s="2"/>
       <c r="L163" s="2"/>
-      <c r="M163" s="2"/>
+      <c r="M163" s="2" t="s">
+        <v>37</v>
+      </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
@@ -7263,34 +7273,34 @@
     </row>
     <row r="164" spans="1:26">
       <c r="A164">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="B164" s="3">
-        <v>46288.5519907407</v>
+        <v>46288.578055555598</v>
       </c>
       <c r="C164" s="3">
-        <v>46288.566412036998</v>
+        <v>46288.579918981501</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>316</v>
+        <v>283</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>317</v>
+        <v>284</v>
       </c>
       <c r="F164">
-        <v>38590</v>
+        <v>38580</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>36</v>
+        <v>126</v>
       </c>
       <c r="H164" s="2"/>
       <c r="I164" s="2"/>
-      <c r="J164" s="2"/>
+      <c r="J164" s="2" t="s">
+        <v>319</v>
+      </c>
       <c r="K164" s="2"/>
       <c r="L164" s="2"/>
-      <c r="M164" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="M164" s="2"/>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
       <c r="P164" s="2"/>
@@ -7305,32 +7315,32 @@
     </row>
     <row r="165" spans="1:26">
       <c r="A165">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="B165" s="3">
-        <v>46288.578055555598</v>
+        <v>46288.580254629604</v>
       </c>
       <c r="C165" s="3">
-        <v>46288.579918981501</v>
+        <v>46288.581747685203</v>
       </c>
       <c r="D165" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E165" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E165" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F165">
         <v>38580</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="H165" s="2"/>
       <c r="I165" s="2"/>
-      <c r="J165" s="2" t="s">
+      <c r="J165" s="2"/>
+      <c r="K165" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="K165" s="2"/>
       <c r="L165" s="2"/>
       <c r="M165" s="2"/>
       <c r="N165" s="2"/>
@@ -7347,33 +7357,33 @@
     </row>
     <row r="166" spans="1:26">
       <c r="A166">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B166" s="3">
-        <v>46288.580254629604</v>
+        <v>46288.5855324074</v>
       </c>
       <c r="C166" s="3">
-        <v>46288.581747685203</v>
+        <v>46288.585659722201</v>
       </c>
       <c r="D166" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E166" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="E166" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F166">
         <v>38580</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="H166" s="2"/>
       <c r="I166" s="2"/>
       <c r="J166" s="2"/>
-      <c r="K166" s="2" t="s">
+      <c r="K166" s="2"/>
+      <c r="L166" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="L166" s="2"/>
       <c r="M166" s="2"/>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -7389,25 +7399,25 @@
     </row>
     <row r="167" spans="1:26">
       <c r="A167">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B167" s="3">
-        <v>46288.5855324074</v>
+        <v>46288.603425925903</v>
       </c>
       <c r="C167" s="3">
-        <v>46288.585659722201</v>
+        <v>46288.6043518519</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="F167">
-        <v>38580</v>
+        <v>38571</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H167" s="2"/>
       <c r="I167" s="2"/>
@@ -7431,32 +7441,32 @@
     </row>
     <row r="168" spans="1:26">
       <c r="A168">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B168" s="3">
-        <v>46288.603425925903</v>
+        <v>46288.653773148202</v>
       </c>
       <c r="C168" s="3">
-        <v>46288.6043518519</v>
+        <v>46288.654687499999</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>276</v>
+        <v>323</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>277</v>
+        <v>324</v>
       </c>
       <c r="F168">
-        <v>38571</v>
+        <v>38279</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H168" s="2"/>
       <c r="I168" s="2"/>
       <c r="J168" s="2"/>
       <c r="K168" s="2"/>
       <c r="L168" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M168" s="2"/>
       <c r="N168" s="2"/>
@@ -7473,25 +7483,25 @@
     </row>
     <row r="169" spans="1:26">
       <c r="A169">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B169" s="3">
-        <v>46288.653773148202</v>
+        <v>46288.701111111099</v>
       </c>
       <c r="C169" s="3">
-        <v>46288.654687499999</v>
+        <v>46288.7015509259</v>
       </c>
       <c r="D169" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="E169" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="E169" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="F169">
         <v>38279</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H169" s="2"/>
       <c r="I169" s="2"/>
@@ -7515,32 +7525,32 @@
     </row>
     <row r="170" spans="1:26">
       <c r="A170">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B170" s="3">
-        <v>46288.701111111099</v>
+        <v>46288.758877314802</v>
       </c>
       <c r="C170" s="3">
-        <v>46288.7015509259</v>
+        <v>46288.759062500001</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="F170">
-        <v>38279</v>
+        <v>43183</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H170" s="2"/>
       <c r="I170" s="2"/>
       <c r="J170" s="2"/>
       <c r="K170" s="2"/>
       <c r="L170" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M170" s="2"/>
       <c r="N170" s="2"/>
@@ -7557,33 +7567,31 @@
     </row>
     <row r="171" spans="1:26">
       <c r="A171">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="B171" s="3">
-        <v>46288.758877314802</v>
+        <v>46288.806956018503</v>
       </c>
       <c r="C171" s="3">
-        <v>46288.759062500001</v>
+        <v>46288.808229166701</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>328</v>
+        <v>287</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>329</v>
+        <v>288</v>
       </c>
       <c r="F171">
-        <v>43183</v>
+        <v>38116</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="H171" s="2"/>
       <c r="I171" s="2"/>
       <c r="J171" s="2"/>
       <c r="K171" s="2"/>
-      <c r="L171" s="2" t="s">
-        <v>330</v>
-      </c>
+      <c r="L171" s="2"/>
       <c r="M171" s="2"/>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
@@ -7591,39 +7599,45 @@
       <c r="Q171" s="2"/>
       <c r="R171" s="2"/>
       <c r="S171" s="2"/>
-      <c r="V171" s="2"/>
-      <c r="W171" s="2"/>
+      <c r="V171" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="W171" s="2" t="s">
+        <v>331</v>
+      </c>
       <c r="X171" s="5"/>
       <c r="Y171" s="5"/>
       <c r="Z171" s="5"/>
     </row>
     <row r="172" spans="1:26">
       <c r="A172">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B172" s="3">
-        <v>46288.806956018503</v>
+        <v>46288.913425925901</v>
       </c>
       <c r="C172" s="3">
-        <v>46288.808229166701</v>
+        <v>46288.916087963</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>288</v>
+        <v>332</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>289</v>
+        <v>333</v>
       </c>
       <c r="F172">
-        <v>38116</v>
+        <v>38725</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="H172" s="2"/>
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
-      <c r="L172" s="2"/>
+      <c r="L172" s="2" t="s">
+        <v>334</v>
+      </c>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
@@ -7631,37 +7645,33 @@
       <c r="Q172" s="2"/>
       <c r="R172" s="2"/>
       <c r="S172" s="2"/>
-      <c r="V172" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="W172" s="2" t="s">
-        <v>332</v>
-      </c>
+      <c r="V172" s="2"/>
+      <c r="W172" s="2"/>
       <c r="X172" s="5"/>
       <c r="Y172" s="5"/>
       <c r="Z172" s="5"/>
     </row>
     <row r="173" spans="1:26">
       <c r="A173">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B173" s="3">
-        <v>46288.913425925901</v>
+        <v>46288.916319444397</v>
       </c>
       <c r="C173" s="3">
-        <v>46288.916087963</v>
+        <v>46288.916643518503</v>
       </c>
       <c r="D173" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E173" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="E173" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="F173">
         <v>38725</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H173" s="2"/>
       <c r="I173" s="2"/>
@@ -7685,25 +7695,25 @@
     </row>
     <row r="174" spans="1:26">
       <c r="A174">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B174" s="3">
-        <v>46288.916319444397</v>
+        <v>46288.916701388902</v>
       </c>
       <c r="C174" s="3">
-        <v>46288.916643518503</v>
+        <v>46288.916990740698</v>
       </c>
       <c r="D174" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E174" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="E174" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="F174">
         <v>38725</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H174" s="2"/>
       <c r="I174" s="2"/>
@@ -7727,32 +7737,32 @@
     </row>
     <row r="175" spans="1:26">
       <c r="A175">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B175" s="3">
-        <v>46288.916701388902</v>
+        <v>46289.207476851901</v>
       </c>
       <c r="C175" s="3">
-        <v>46288.916990740698</v>
+        <v>46289.209525462997</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="F175">
-        <v>38725</v>
+        <v>38226</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H175" s="2"/>
       <c r="I175" s="2"/>
       <c r="J175" s="2"/>
       <c r="K175" s="2"/>
       <c r="L175" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
@@ -7769,33 +7779,31 @@
     </row>
     <row r="176" spans="1:26">
       <c r="A176">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="B176" s="3">
-        <v>46289.207476851901</v>
+        <v>46289.210185185198</v>
       </c>
       <c r="C176" s="3">
-        <v>46289.209525462997</v>
+        <v>46289.2116550926</v>
       </c>
       <c r="D176" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E176" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E176" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F176">
         <v>38226</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>118</v>
+        <v>92</v>
       </c>
       <c r="H176" s="2"/>
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
       <c r="K176" s="2"/>
-      <c r="L176" s="2" t="s">
-        <v>340</v>
-      </c>
+      <c r="L176" s="2"/>
       <c r="M176" s="2"/>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -7803,36 +7811,44 @@
       <c r="Q176" s="2"/>
       <c r="R176" s="2"/>
       <c r="S176" s="2"/>
-      <c r="V176" s="2"/>
-      <c r="W176" s="2"/>
+      <c r="V176" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="W176" s="2" t="s">
+        <v>341</v>
+      </c>
       <c r="X176" s="5"/>
       <c r="Y176" s="5"/>
       <c r="Z176" s="5"/>
     </row>
     <row r="177" spans="1:26">
       <c r="A177">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B177" s="3">
-        <v>46289.210185185198</v>
+        <v>46289.211770833303</v>
       </c>
       <c r="C177" s="3">
-        <v>46289.2116550926</v>
+        <v>46289.212280092601</v>
       </c>
       <c r="D177" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E177" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E177" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F177">
         <v>38226</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H177" s="2"/>
-      <c r="I177" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="H177" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I177" s="2" t="s">
+        <v>342</v>
+      </c>
       <c r="J177" s="2"/>
       <c r="K177" s="2"/>
       <c r="L177" s="2"/>
@@ -7843,44 +7859,36 @@
       <c r="Q177" s="2"/>
       <c r="R177" s="2"/>
       <c r="S177" s="2"/>
-      <c r="V177" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="W177" s="2" t="s">
-        <v>342</v>
-      </c>
+      <c r="V177" s="2"/>
+      <c r="W177" s="2"/>
       <c r="X177" s="5"/>
       <c r="Y177" s="5"/>
       <c r="Z177" s="5"/>
     </row>
     <row r="178" spans="1:26">
       <c r="A178">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B178" s="3">
-        <v>46289.211770833303</v>
+        <v>46289.212314814802</v>
       </c>
       <c r="C178" s="3">
-        <v>46289.212280092601</v>
+        <v>46289.213564814803</v>
       </c>
       <c r="D178" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E178" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E178" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F178">
         <v>38226</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H178" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I178" s="2" t="s">
-        <v>343</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="H178" s="2"/>
+      <c r="I178" s="2"/>
       <c r="J178" s="2"/>
       <c r="K178" s="2"/>
       <c r="L178" s="2"/>
@@ -7899,25 +7907,25 @@
     </row>
     <row r="179" spans="1:26">
       <c r="A179">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="B179" s="3">
-        <v>46289.212314814802</v>
+        <v>46289.213599536997</v>
       </c>
       <c r="C179" s="3">
-        <v>46289.213564814803</v>
+        <v>46289.214085648098</v>
       </c>
       <c r="D179" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E179" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E179" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F179">
         <v>38226</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H179" s="2"/>
       <c r="I179" s="2"/>
@@ -7939,25 +7947,25 @@
     </row>
     <row r="180" spans="1:26">
       <c r="A180">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="B180" s="3">
-        <v>46289.213599536997</v>
+        <v>46289.3444675926</v>
       </c>
       <c r="C180" s="3">
-        <v>46289.214085648098</v>
+        <v>46289.401377314804</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>338</v>
+        <v>62</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>339</v>
+        <v>63</v>
       </c>
       <c r="F180">
-        <v>38226</v>
+        <v>38458</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="H180" s="2"/>
       <c r="I180" s="2"/>
@@ -7971,39 +7979,45 @@
       <c r="Q180" s="2"/>
       <c r="R180" s="2"/>
       <c r="S180" s="2"/>
-      <c r="V180" s="2"/>
-      <c r="W180" s="2"/>
+      <c r="V180" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="W180" s="2" t="s">
+        <v>344</v>
+      </c>
       <c r="X180" s="5"/>
       <c r="Y180" s="5"/>
       <c r="Z180" s="5"/>
     </row>
     <row r="181" spans="1:26">
       <c r="A181">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B181" s="3">
-        <v>46289.3444675926</v>
+        <v>46289.488472222198</v>
       </c>
       <c r="C181" s="3">
-        <v>46289.401377314804</v>
+        <v>46289.489976851903</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>62</v>
+        <v>345</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>63</v>
+        <v>346</v>
       </c>
       <c r="F181">
-        <v>38458</v>
+        <v>38716</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>83</v>
+        <v>117</v>
       </c>
       <c r="H181" s="2"/>
       <c r="I181" s="2"/>
       <c r="J181" s="2"/>
       <c r="K181" s="2"/>
-      <c r="L181" s="2"/>
+      <c r="L181" s="2" t="s">
+        <v>347</v>
+      </c>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -8011,37 +8025,33 @@
       <c r="Q181" s="2"/>
       <c r="R181" s="2"/>
       <c r="S181" s="2"/>
-      <c r="V181" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="W181" s="2" t="s">
-        <v>345</v>
-      </c>
+      <c r="V181" s="2"/>
+      <c r="W181" s="2"/>
       <c r="X181" s="5"/>
       <c r="Y181" s="5"/>
       <c r="Z181" s="5"/>
     </row>
     <row r="182" spans="1:26">
       <c r="A182">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B182" s="3">
-        <v>46289.488472222198</v>
+        <v>46289.488611111097</v>
       </c>
       <c r="C182" s="3">
-        <v>46289.489976851903</v>
+        <v>46289.493692129603</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>346</v>
+        <v>285</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>347</v>
+        <v>286</v>
       </c>
       <c r="F182">
-        <v>38716</v>
+        <v>43159</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H182" s="2"/>
       <c r="I182" s="2"/>
@@ -8065,32 +8075,32 @@
     </row>
     <row r="183" spans="1:26">
       <c r="A183">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="B183" s="3">
-        <v>46289.488611111097</v>
+        <v>46291.559664351902</v>
       </c>
       <c r="C183" s="3">
-        <v>46289.493692129603</v>
+        <v>46291.560659722199</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>286</v>
+        <v>349</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>287</v>
+        <v>350</v>
       </c>
       <c r="F183">
-        <v>43159</v>
+        <v>38430</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H183" s="2"/>
       <c r="I183" s="2"/>
       <c r="J183" s="2"/>
       <c r="K183" s="2"/>
       <c r="L183" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="M183" s="2"/>
       <c r="N183" s="2"/>
@@ -8107,33 +8117,35 @@
     </row>
     <row r="184" spans="1:26">
       <c r="A184">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="B184" s="3">
-        <v>46291.559664351902</v>
+        <v>46292.512986111098</v>
       </c>
       <c r="C184" s="3">
-        <v>46291.560659722199</v>
+        <v>46292.5158912037</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F184">
-        <v>38430</v>
+        <v>38289</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H184" s="2"/>
-      <c r="I184" s="2"/>
+        <v>123</v>
+      </c>
+      <c r="H184" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I184" s="2" t="s">
+        <v>354</v>
+      </c>
       <c r="J184" s="2"/>
       <c r="K184" s="2"/>
-      <c r="L184" s="2" t="s">
-        <v>352</v>
-      </c>
+      <c r="L184" s="2"/>
       <c r="M184" s="2"/>
       <c r="N184" s="2"/>
       <c r="O184" s="2"/>
@@ -8148,34 +8160,32 @@
       <c r="Z184" s="5"/>
     </row>
     <row r="185" spans="1:26">
-      <c r="A185">
-        <v>1010</v>
+      <c r="A185" s="5">
+        <v>1011</v>
       </c>
       <c r="B185" s="3">
-        <v>46292.512986111098</v>
+        <v>46292.533703703702</v>
       </c>
       <c r="C185" s="3">
-        <v>46292.5158912037</v>
+        <v>46292.550416666701</v>
       </c>
       <c r="D185" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E185" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="E185" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F185">
+      <c r="F185" s="5">
         <v>38289</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="H185" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="I185" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H185" s="2"/>
+      <c r="I185" s="2"/>
+      <c r="J185" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="J185" s="2"/>
       <c r="K185" s="2"/>
       <c r="L185" s="2"/>
       <c r="M185" s="2"/>
@@ -8185,6 +8195,8 @@
       <c r="Q185" s="2"/>
       <c r="R185" s="2"/>
       <c r="S185" s="2"/>
+      <c r="T185" s="5"/>
+      <c r="U185" s="5"/>
       <c r="V185" s="2"/>
       <c r="W185" s="2"/>
       <c r="X185" s="5"/>
@@ -8193,32 +8205,32 @@
     </row>
     <row r="186" spans="1:26">
       <c r="A186" s="5">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="B186" s="3">
-        <v>46292.533703703702</v>
+        <v>46292.6031365741</v>
       </c>
       <c r="C186" s="3">
-        <v>46292.550416666701</v>
+        <v>46292.604108796302</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>353</v>
+        <v>337</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>354</v>
+        <v>338</v>
       </c>
       <c r="F186" s="5">
-        <v>38289</v>
+        <v>38226</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>127</v>
+        <v>32</v>
       </c>
       <c r="H186" s="2"/>
       <c r="I186" s="2"/>
-      <c r="J186" s="2" t="s">
+      <c r="J186" s="2"/>
+      <c r="K186" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="K186" s="2"/>
       <c r="L186" s="2"/>
       <c r="M186" s="2"/>
       <c r="N186" s="2"/>
@@ -8237,35 +8249,37 @@
     </row>
     <row r="187" spans="1:26">
       <c r="A187" s="5">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B187" s="3">
-        <v>46292.6031365741</v>
+        <v>46292.604155092602</v>
       </c>
       <c r="C187" s="3">
-        <v>46292.604108796302</v>
+        <v>46292.604745370401</v>
       </c>
       <c r="D187" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E187" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F187" s="5">
         <v>38226</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H187" s="2"/>
       <c r="I187" s="2"/>
       <c r="J187" s="2"/>
-      <c r="K187" s="2" t="s">
+      <c r="K187" s="2"/>
+      <c r="L187" s="2"/>
+      <c r="M187" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="N187" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="L187" s="2"/>
-      <c r="M187" s="2"/>
-      <c r="N187" s="2"/>
       <c r="O187" s="2"/>
       <c r="P187" s="2"/>
       <c r="Q187" s="2"/>
@@ -8281,42 +8295,44 @@
     </row>
     <row r="188" spans="1:26">
       <c r="A188" s="5">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="B188" s="3">
-        <v>46292.604155092602</v>
+        <v>46292.604849536998</v>
       </c>
       <c r="C188" s="3">
-        <v>46292.604745370401</v>
+        <v>46292.606469907398</v>
       </c>
       <c r="D188" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E188" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F188" s="5">
         <v>38226</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="H188" s="2"/>
       <c r="I188" s="2"/>
       <c r="J188" s="2"/>
       <c r="K188" s="2"/>
       <c r="L188" s="2"/>
-      <c r="M188" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="N188" s="2" t="s">
-        <v>358</v>
-      </c>
+      <c r="M188" s="2"/>
+      <c r="N188" s="2"/>
       <c r="O188" s="2"/>
       <c r="P188" s="2"/>
-      <c r="Q188" s="2"/>
-      <c r="R188" s="2"/>
-      <c r="S188" s="2"/>
+      <c r="Q188" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R188" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S188" s="2" t="s">
+        <v>358</v>
+      </c>
       <c r="T188" s="5"/>
       <c r="U188" s="5"/>
       <c r="V188" s="2"/>
@@ -8327,25 +8343,25 @@
     </row>
     <row r="189" spans="1:26">
       <c r="A189" s="5">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B189" s="3">
-        <v>46292.604849536998</v>
+        <v>46292.606504629599</v>
       </c>
       <c r="C189" s="3">
-        <v>46292.606469907398</v>
+        <v>46292.607291666704</v>
       </c>
       <c r="D189" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E189" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F189" s="5">
         <v>38226</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="H189" s="2"/>
       <c r="I189" s="2"/>
@@ -8354,17 +8370,13 @@
       <c r="L189" s="2"/>
       <c r="M189" s="2"/>
       <c r="N189" s="2"/>
-      <c r="O189" s="2"/>
+      <c r="O189" s="2" t="s">
+        <v>359</v>
+      </c>
       <c r="P189" s="2"/>
-      <c r="Q189" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="R189" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="S189" s="2" t="s">
-        <v>359</v>
-      </c>
+      <c r="Q189" s="2"/>
+      <c r="R189" s="2"/>
+      <c r="S189" s="2"/>
       <c r="T189" s="5"/>
       <c r="U189" s="5"/>
       <c r="V189" s="2"/>
@@ -8375,25 +8387,25 @@
     </row>
     <row r="190" spans="1:26">
       <c r="A190" s="5">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="B190" s="3">
-        <v>46292.606504629599</v>
+        <v>46292.607337963003</v>
       </c>
       <c r="C190" s="3">
-        <v>46292.607291666704</v>
+        <v>46292.6078935185</v>
       </c>
       <c r="D190" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E190" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E190" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F190" s="5">
         <v>38226</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H190" s="2"/>
       <c r="I190" s="2"/>
@@ -8402,10 +8414,10 @@
       <c r="L190" s="2"/>
       <c r="M190" s="2"/>
       <c r="N190" s="2"/>
-      <c r="O190" s="2" t="s">
+      <c r="O190" s="2"/>
+      <c r="P190" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="P190" s="2"/>
       <c r="Q190" s="2"/>
       <c r="R190" s="2"/>
       <c r="S190" s="2"/>
@@ -8419,25 +8431,25 @@
     </row>
     <row r="191" spans="1:26">
       <c r="A191" s="5">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B191" s="3">
-        <v>46292.607337963003</v>
+        <v>46292.607928240701</v>
       </c>
       <c r="C191" s="3">
-        <v>46292.6078935185</v>
+        <v>46292.608599537001</v>
       </c>
       <c r="D191" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E191" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E191" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F191" s="5">
         <v>38226</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>68</v>
+        <v>361</v>
       </c>
       <c r="H191" s="2"/>
       <c r="I191" s="2"/>
@@ -8447,14 +8459,16 @@
       <c r="M191" s="2"/>
       <c r="N191" s="2"/>
       <c r="O191" s="2"/>
-      <c r="P191" s="2" t="s">
-        <v>361</v>
-      </c>
+      <c r="P191" s="2"/>
       <c r="Q191" s="2"/>
       <c r="R191" s="2"/>
       <c r="S191" s="2"/>
-      <c r="T191" s="5"/>
-      <c r="U191" s="5"/>
+      <c r="T191" s="5">
+        <v>5</v>
+      </c>
+      <c r="U191" s="5">
+        <v>2</v>
+      </c>
       <c r="V191" s="2"/>
       <c r="W191" s="2"/>
       <c r="X191" s="5"/>
@@ -8463,29 +8477,31 @@
     </row>
     <row r="192" spans="1:26">
       <c r="A192" s="5">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="B192" s="3">
-        <v>46292.607928240701</v>
+        <v>46292.608634259297</v>
       </c>
       <c r="C192" s="3">
-        <v>46292.608599537001</v>
+        <v>46292.610162037003</v>
       </c>
       <c r="D192" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="E192" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F192" s="5">
         <v>38226</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>362</v>
+        <v>126</v>
       </c>
       <c r="H192" s="2"/>
       <c r="I192" s="2"/>
-      <c r="J192" s="2"/>
+      <c r="J192" s="2" t="s">
+        <v>362</v>
+      </c>
       <c r="K192" s="2"/>
       <c r="L192" s="2"/>
       <c r="M192" s="2"/>
@@ -8495,12 +8511,8 @@
       <c r="Q192" s="2"/>
       <c r="R192" s="2"/>
       <c r="S192" s="2"/>
-      <c r="T192" s="5">
-        <v>5</v>
-      </c>
-      <c r="U192" s="5">
-        <v>2</v>
-      </c>
+      <c r="T192" s="5"/>
+      <c r="U192" s="5"/>
       <c r="V192" s="2"/>
       <c r="W192" s="2"/>
       <c r="X192" s="5"/>
@@ -8509,33 +8521,33 @@
     </row>
     <row r="193" spans="1:26">
       <c r="A193" s="5">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B193" s="3">
-        <v>46292.608634259297</v>
+        <v>46292.605960648099</v>
       </c>
       <c r="C193" s="3">
-        <v>46292.610162037003</v>
+        <v>46292.616666666698</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>338</v>
+        <v>363</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>339</v>
+        <v>364</v>
       </c>
       <c r="F193" s="5">
-        <v>38226</v>
+        <v>38611</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="H193" s="2"/>
       <c r="I193" s="2"/>
-      <c r="J193" s="2" t="s">
-        <v>363</v>
-      </c>
+      <c r="J193" s="2"/>
       <c r="K193" s="2"/>
-      <c r="L193" s="2"/>
+      <c r="L193" s="2" t="s">
+        <v>365</v>
+      </c>
       <c r="M193" s="2"/>
       <c r="N193" s="2"/>
       <c r="O193" s="2"/>
@@ -8553,25 +8565,25 @@
     </row>
     <row r="194" spans="1:26">
       <c r="A194" s="5">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B194" s="3">
-        <v>46292.605960648099</v>
+        <v>46292.617418981499</v>
       </c>
       <c r="C194" s="3">
-        <v>46292.616666666698</v>
+        <v>46292.618321759299</v>
       </c>
       <c r="D194" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E194" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="E194" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="F194" s="5">
         <v>38611</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H194" s="2"/>
       <c r="I194" s="2"/>
@@ -8597,33 +8609,31 @@
     </row>
     <row r="195" spans="1:26">
       <c r="A195" s="5">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B195" s="3">
-        <v>46292.617418981499</v>
+        <v>46292.649178240703</v>
       </c>
       <c r="C195" s="3">
-        <v>46292.618321759299</v>
+        <v>46292.650381944397</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>364</v>
+        <v>42</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>365</v>
+        <v>43</v>
       </c>
       <c r="F195" s="5">
-        <v>38611</v>
+        <v>38925</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>118</v>
+        <v>361</v>
       </c>
       <c r="H195" s="2"/>
       <c r="I195" s="2"/>
       <c r="J195" s="2"/>
       <c r="K195" s="2"/>
-      <c r="L195" s="2" t="s">
-        <v>367</v>
-      </c>
+      <c r="L195" s="2"/>
       <c r="M195" s="2"/>
       <c r="N195" s="2"/>
       <c r="O195" s="2"/>
@@ -8631,8 +8641,12 @@
       <c r="Q195" s="2"/>
       <c r="R195" s="2"/>
       <c r="S195" s="2"/>
-      <c r="T195" s="5"/>
-      <c r="U195" s="5"/>
+      <c r="T195" s="5">
+        <v>8</v>
+      </c>
+      <c r="U195" s="5">
+        <v>0</v>
+      </c>
       <c r="V195" s="2"/>
       <c r="W195" s="2"/>
       <c r="X195" s="5"/>
@@ -8641,31 +8655,33 @@
     </row>
     <row r="196" spans="1:26">
       <c r="A196" s="5">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="B196" s="3">
-        <v>46292.649178240703</v>
+        <v>46292.706770833298</v>
       </c>
       <c r="C196" s="3">
-        <v>46292.650381944397</v>
+        <v>46292.707048611097</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>42</v>
+        <v>367</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>43</v>
+        <v>368</v>
       </c>
       <c r="F196" s="5">
-        <v>38925</v>
+        <v>38417</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>362</v>
+        <v>117</v>
       </c>
       <c r="H196" s="2"/>
       <c r="I196" s="2"/>
       <c r="J196" s="2"/>
       <c r="K196" s="2"/>
-      <c r="L196" s="2"/>
+      <c r="L196" s="2" t="s">
+        <v>369</v>
+      </c>
       <c r="M196" s="2"/>
       <c r="N196" s="2"/>
       <c r="O196" s="2"/>
@@ -8673,61 +8689,13 @@
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
       <c r="S196" s="2"/>
-      <c r="T196" s="5">
-        <v>8</v>
-      </c>
-      <c r="U196" s="5">
-        <v>0</v>
-      </c>
+      <c r="T196" s="5"/>
+      <c r="U196" s="5"/>
       <c r="V196" s="2"/>
       <c r="W196" s="2"/>
       <c r="X196" s="5"/>
       <c r="Y196" s="5"/>
       <c r="Z196" s="5"/>
-    </row>
-    <row r="197" spans="1:26">
-      <c r="A197" s="5">
-        <v>1022</v>
-      </c>
-      <c r="B197" s="3">
-        <v>46292.706770833298</v>
-      </c>
-      <c r="C197" s="3">
-        <v>46292.707048611097</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F197" s="5">
-        <v>38417</v>
-      </c>
-      <c r="G197" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2"/>
-      <c r="J197" s="2"/>
-      <c r="K197" s="2"/>
-      <c r="L197" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="M197" s="2"/>
-      <c r="N197" s="2"/>
-      <c r="O197" s="2"/>
-      <c r="P197" s="2"/>
-      <c r="Q197" s="2"/>
-      <c r="R197" s="2"/>
-      <c r="S197" s="2"/>
-      <c r="T197" s="5"/>
-      <c r="U197" s="5"/>
-      <c r="V197" s="2"/>
-      <c r="W197" s="2"/>
-      <c r="X197" s="5"/>
-      <c r="Y197" s="5"/>
-      <c r="Z197" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{441FD118-9812-4EC8-A282-A5E2CE9C50DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{998619E9-6D62-47D4-B898-54AEEBAEA6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{998619E9-6D62-47D4-B898-54AEEBAEA6C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F9F410C-C125-4AAD-92F2-744F3018B232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="372">
   <si>
     <t>Id</t>
   </si>
@@ -1149,6 +1149,12 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_7174_Starbucks%20San%20Jos%C3%A9%20I.jpeg</t>
+  </si>
+  <si>
+    <t>FHW</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/1790574487010220296208446313782_Enrique%20Cesar%20Flores.jpg</t>
   </si>
 </sst>
 </file>
@@ -1285,8 +1291,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z196" totalsRowShown="0">
-  <autoFilter ref="A1:Z196" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z197" totalsRowShown="0">
+  <autoFilter ref="A1:Z197" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1474,7 +1480,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1022" latestEventMarker="1468">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1023" latestEventMarker="1469">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1804,7 +1810,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z196"/>
+  <dimension ref="A1:Z197"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -8697,6 +8703,54 @@
       <c r="Y196" s="5"/>
       <c r="Z196" s="5"/>
     </row>
+    <row r="197" spans="1:26">
+      <c r="A197" s="5">
+        <v>1023</v>
+      </c>
+      <c r="B197" s="3">
+        <v>46292.983020833301</v>
+      </c>
+      <c r="C197" s="3">
+        <v>46292.991898148102</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F197" s="5">
+        <v>38371</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="H197" s="2"/>
+      <c r="I197" s="2"/>
+      <c r="J197" s="2"/>
+      <c r="K197" s="2"/>
+      <c r="L197" s="2"/>
+      <c r="M197" s="2"/>
+      <c r="N197" s="2"/>
+      <c r="O197" s="2"/>
+      <c r="P197" s="2"/>
+      <c r="Q197" s="2"/>
+      <c r="R197" s="2"/>
+      <c r="S197" s="2"/>
+      <c r="T197" s="5"/>
+      <c r="U197" s="5"/>
+      <c r="V197" s="2"/>
+      <c r="W197" s="2"/>
+      <c r="X197" s="5">
+        <v>12</v>
+      </c>
+      <c r="Y197" s="5">
+        <v>6</v>
+      </c>
+      <c r="Z197" s="5" t="s">
+        <v>371</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F9F410C-C125-4AAD-92F2-744F3018B232}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3474FFD-B792-4828-8568-C7E383EF5D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="766" uniqueCount="372">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="370">
   <si>
     <t>Id</t>
   </si>
@@ -1149,12 +1149,6 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_7174_Starbucks%20San%20Jos%C3%A9%20I.jpeg</t>
-  </si>
-  <si>
-    <t>FHW</t>
-  </si>
-  <si>
-    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/1790574487010220296208446313782_Enrique%20Cesar%20Flores.jpg</t>
   </si>
 </sst>
 </file>
@@ -1291,8 +1285,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z197" totalsRowShown="0">
-  <autoFilter ref="A1:Z197" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z196" totalsRowShown="0">
+  <autoFilter ref="A1:Z196" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1810,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z197"/>
+  <dimension ref="A1:Z196"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -8703,54 +8697,6 @@
       <c r="Y196" s="5"/>
       <c r="Z196" s="5"/>
     </row>
-    <row r="197" spans="1:26">
-      <c r="A197" s="5">
-        <v>1023</v>
-      </c>
-      <c r="B197" s="3">
-        <v>46292.983020833301</v>
-      </c>
-      <c r="C197" s="3">
-        <v>46292.991898148102</v>
-      </c>
-      <c r="D197" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E197" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F197" s="5">
-        <v>38371</v>
-      </c>
-      <c r="G197" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2"/>
-      <c r="J197" s="2"/>
-      <c r="K197" s="2"/>
-      <c r="L197" s="2"/>
-      <c r="M197" s="2"/>
-      <c r="N197" s="2"/>
-      <c r="O197" s="2"/>
-      <c r="P197" s="2"/>
-      <c r="Q197" s="2"/>
-      <c r="R197" s="2"/>
-      <c r="S197" s="2"/>
-      <c r="T197" s="5"/>
-      <c r="U197" s="5"/>
-      <c r="V197" s="2"/>
-      <c r="W197" s="2"/>
-      <c r="X197" s="5">
-        <v>12</v>
-      </c>
-      <c r="Y197" s="5">
-        <v>6</v>
-      </c>
-      <c r="Z197" s="5" t="s">
-        <v>371</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F3474FFD-B792-4828-8568-C7E383EF5D41}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EDE03E9-ECC0-4B3A-9DC1-3F2C29A3F26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="762" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="370">
   <si>
     <t>Id</t>
   </si>
@@ -1285,8 +1285,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z196" totalsRowShown="0">
-  <autoFilter ref="A1:Z196" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z206" totalsRowShown="0">
+  <autoFilter ref="A1:Z206" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1474,7 +1474,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1023" latestEventMarker="1469">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1033" latestEventMarker="1479">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1804,7 +1804,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z196"/>
+  <dimension ref="A1:Z206"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -8697,6 +8697,466 @@
       <c r="Y196" s="5"/>
       <c r="Z196" s="5"/>
     </row>
+    <row r="197" spans="1:26">
+      <c r="A197" s="5">
+        <v>1024</v>
+      </c>
+      <c r="B197" s="3">
+        <v>46293.019016203703</v>
+      </c>
+      <c r="C197" s="3">
+        <v>46293.019328703696</v>
+      </c>
+      <c r="D197" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E197" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F197" s="5">
+        <v>38333</v>
+      </c>
+      <c r="G197" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H197" s="2"/>
+      <c r="I197" s="2"/>
+      <c r="J197" s="2"/>
+      <c r="K197" s="2"/>
+      <c r="L197" s="2"/>
+      <c r="M197" s="2"/>
+      <c r="N197" s="2"/>
+      <c r="O197" s="2"/>
+      <c r="P197" s="2"/>
+      <c r="Q197" s="2"/>
+      <c r="R197" s="2"/>
+      <c r="S197" s="2"/>
+      <c r="T197" s="5">
+        <v>18</v>
+      </c>
+      <c r="U197" s="5">
+        <v>0</v>
+      </c>
+      <c r="V197" s="2"/>
+      <c r="W197" s="2"/>
+      <c r="X197" s="5"/>
+      <c r="Y197" s="5"/>
+      <c r="Z197" s="5"/>
+    </row>
+    <row r="198" spans="1:26">
+      <c r="A198" s="5">
+        <v>1025</v>
+      </c>
+      <c r="B198" s="3">
+        <v>46293.019340277802</v>
+      </c>
+      <c r="C198" s="3">
+        <v>46293.019710648201</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F198" s="5">
+        <v>38339</v>
+      </c>
+      <c r="G198" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H198" s="2"/>
+      <c r="I198" s="2"/>
+      <c r="J198" s="2"/>
+      <c r="K198" s="2"/>
+      <c r="L198" s="2"/>
+      <c r="M198" s="2"/>
+      <c r="N198" s="2"/>
+      <c r="O198" s="2"/>
+      <c r="P198" s="2"/>
+      <c r="Q198" s="2"/>
+      <c r="R198" s="2"/>
+      <c r="S198" s="2"/>
+      <c r="T198" s="5">
+        <v>15</v>
+      </c>
+      <c r="U198" s="5">
+        <v>0</v>
+      </c>
+      <c r="V198" s="2"/>
+      <c r="W198" s="2"/>
+      <c r="X198" s="5"/>
+      <c r="Y198" s="5"/>
+      <c r="Z198" s="5"/>
+    </row>
+    <row r="199" spans="1:26">
+      <c r="A199" s="5">
+        <v>1026</v>
+      </c>
+      <c r="B199" s="3">
+        <v>46293.019756944399</v>
+      </c>
+      <c r="C199" s="3">
+        <v>46293.020439814798</v>
+      </c>
+      <c r="D199" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E199" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F199" s="5">
+        <v>38368</v>
+      </c>
+      <c r="G199" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H199" s="2"/>
+      <c r="I199" s="2"/>
+      <c r="J199" s="2"/>
+      <c r="K199" s="2"/>
+      <c r="L199" s="2"/>
+      <c r="M199" s="2"/>
+      <c r="N199" s="2"/>
+      <c r="O199" s="2"/>
+      <c r="P199" s="2"/>
+      <c r="Q199" s="2"/>
+      <c r="R199" s="2"/>
+      <c r="S199" s="2"/>
+      <c r="T199" s="5">
+        <v>14</v>
+      </c>
+      <c r="U199" s="5">
+        <v>2</v>
+      </c>
+      <c r="V199" s="2"/>
+      <c r="W199" s="2"/>
+      <c r="X199" s="5"/>
+      <c r="Y199" s="5"/>
+      <c r="Z199" s="5"/>
+    </row>
+    <row r="200" spans="1:26">
+      <c r="A200" s="5">
+        <v>1027</v>
+      </c>
+      <c r="B200" s="3">
+        <v>46293.020729166703</v>
+      </c>
+      <c r="C200" s="3">
+        <v>46293.020914351902</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E200" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F200" s="5">
+        <v>38401</v>
+      </c>
+      <c r="G200" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H200" s="2"/>
+      <c r="I200" s="2"/>
+      <c r="J200" s="2"/>
+      <c r="K200" s="2"/>
+      <c r="L200" s="2"/>
+      <c r="M200" s="2"/>
+      <c r="N200" s="2"/>
+      <c r="O200" s="2"/>
+      <c r="P200" s="2"/>
+      <c r="Q200" s="2"/>
+      <c r="R200" s="2"/>
+      <c r="S200" s="2"/>
+      <c r="T200" s="5">
+        <v>8</v>
+      </c>
+      <c r="U200" s="5">
+        <v>0</v>
+      </c>
+      <c r="V200" s="2"/>
+      <c r="W200" s="2"/>
+      <c r="X200" s="5"/>
+      <c r="Y200" s="5"/>
+      <c r="Z200" s="5"/>
+    </row>
+    <row r="201" spans="1:26">
+      <c r="A201" s="5">
+        <v>1028</v>
+      </c>
+      <c r="B201" s="3">
+        <v>46293.020949074104</v>
+      </c>
+      <c r="C201" s="3">
+        <v>46293.021168981497</v>
+      </c>
+      <c r="D201" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E201" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F201" s="5">
+        <v>38456</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H201" s="2"/>
+      <c r="I201" s="2"/>
+      <c r="J201" s="2"/>
+      <c r="K201" s="2"/>
+      <c r="L201" s="2"/>
+      <c r="M201" s="2"/>
+      <c r="N201" s="2"/>
+      <c r="O201" s="2"/>
+      <c r="P201" s="2"/>
+      <c r="Q201" s="2"/>
+      <c r="R201" s="2"/>
+      <c r="S201" s="2"/>
+      <c r="T201" s="5">
+        <v>12</v>
+      </c>
+      <c r="U201" s="5">
+        <v>0</v>
+      </c>
+      <c r="V201" s="2"/>
+      <c r="W201" s="2"/>
+      <c r="X201" s="5"/>
+      <c r="Y201" s="5"/>
+      <c r="Z201" s="5"/>
+    </row>
+    <row r="202" spans="1:26">
+      <c r="A202" s="5">
+        <v>1029</v>
+      </c>
+      <c r="B202" s="3">
+        <v>46293.021203703698</v>
+      </c>
+      <c r="C202" s="3">
+        <v>46293.021620370397</v>
+      </c>
+      <c r="D202" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E202" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F202" s="5">
+        <v>38515</v>
+      </c>
+      <c r="G202" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H202" s="2"/>
+      <c r="I202" s="2"/>
+      <c r="J202" s="2"/>
+      <c r="K202" s="2"/>
+      <c r="L202" s="2"/>
+      <c r="M202" s="2"/>
+      <c r="N202" s="2"/>
+      <c r="O202" s="2"/>
+      <c r="P202" s="2"/>
+      <c r="Q202" s="2"/>
+      <c r="R202" s="2"/>
+      <c r="S202" s="2"/>
+      <c r="T202" s="5">
+        <v>15</v>
+      </c>
+      <c r="U202" s="5">
+        <v>0</v>
+      </c>
+      <c r="V202" s="2"/>
+      <c r="W202" s="2"/>
+      <c r="X202" s="5"/>
+      <c r="Y202" s="5"/>
+      <c r="Z202" s="5"/>
+    </row>
+    <row r="203" spans="1:26">
+      <c r="A203" s="5">
+        <v>1030</v>
+      </c>
+      <c r="B203" s="3">
+        <v>46293.021724537</v>
+      </c>
+      <c r="C203" s="3">
+        <v>46293.021990740701</v>
+      </c>
+      <c r="D203" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E203" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F203" s="5">
+        <v>38604</v>
+      </c>
+      <c r="G203" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H203" s="2"/>
+      <c r="I203" s="2"/>
+      <c r="J203" s="2"/>
+      <c r="K203" s="2"/>
+      <c r="L203" s="2"/>
+      <c r="M203" s="2"/>
+      <c r="N203" s="2"/>
+      <c r="O203" s="2"/>
+      <c r="P203" s="2"/>
+      <c r="Q203" s="2"/>
+      <c r="R203" s="2"/>
+      <c r="S203" s="2"/>
+      <c r="T203" s="5">
+        <v>16</v>
+      </c>
+      <c r="U203" s="5">
+        <v>0</v>
+      </c>
+      <c r="V203" s="2"/>
+      <c r="W203" s="2"/>
+      <c r="X203" s="5"/>
+      <c r="Y203" s="5"/>
+      <c r="Z203" s="5"/>
+    </row>
+    <row r="204" spans="1:26">
+      <c r="A204" s="5">
+        <v>1031</v>
+      </c>
+      <c r="B204" s="3">
+        <v>46293.022013888898</v>
+      </c>
+      <c r="C204" s="3">
+        <v>46293.022256944401</v>
+      </c>
+      <c r="D204" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E204" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F204" s="5">
+        <v>38862</v>
+      </c>
+      <c r="G204" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H204" s="2"/>
+      <c r="I204" s="2"/>
+      <c r="J204" s="2"/>
+      <c r="K204" s="2"/>
+      <c r="L204" s="2"/>
+      <c r="M204" s="2"/>
+      <c r="N204" s="2"/>
+      <c r="O204" s="2"/>
+      <c r="P204" s="2"/>
+      <c r="Q204" s="2"/>
+      <c r="R204" s="2"/>
+      <c r="S204" s="2"/>
+      <c r="T204" s="5">
+        <v>17</v>
+      </c>
+      <c r="U204" s="5">
+        <v>0</v>
+      </c>
+      <c r="V204" s="2"/>
+      <c r="W204" s="2"/>
+      <c r="X204" s="5"/>
+      <c r="Y204" s="5"/>
+      <c r="Z204" s="5"/>
+    </row>
+    <row r="205" spans="1:26">
+      <c r="A205" s="5">
+        <v>1032</v>
+      </c>
+      <c r="B205" s="3">
+        <v>46293.022430555597</v>
+      </c>
+      <c r="C205" s="3">
+        <v>46293.022615740701</v>
+      </c>
+      <c r="D205" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E205" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F205" s="5">
+        <v>38894</v>
+      </c>
+      <c r="G205" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H205" s="2"/>
+      <c r="I205" s="2"/>
+      <c r="J205" s="2"/>
+      <c r="K205" s="2"/>
+      <c r="L205" s="2"/>
+      <c r="M205" s="2"/>
+      <c r="N205" s="2"/>
+      <c r="O205" s="2"/>
+      <c r="P205" s="2"/>
+      <c r="Q205" s="2"/>
+      <c r="R205" s="2"/>
+      <c r="S205" s="2"/>
+      <c r="T205" s="5">
+        <v>15</v>
+      </c>
+      <c r="U205" s="5">
+        <v>0</v>
+      </c>
+      <c r="V205" s="2"/>
+      <c r="W205" s="2"/>
+      <c r="X205" s="5"/>
+      <c r="Y205" s="5"/>
+      <c r="Z205" s="5"/>
+    </row>
+    <row r="206" spans="1:26">
+      <c r="A206" s="5">
+        <v>1033</v>
+      </c>
+      <c r="B206" s="3">
+        <v>46293.022638888899</v>
+      </c>
+      <c r="C206" s="3">
+        <v>46293.0228935185</v>
+      </c>
+      <c r="D206" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E206" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F206" s="5">
+        <v>43193</v>
+      </c>
+      <c r="G206" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H206" s="2"/>
+      <c r="I206" s="2"/>
+      <c r="J206" s="2"/>
+      <c r="K206" s="2"/>
+      <c r="L206" s="2"/>
+      <c r="M206" s="2"/>
+      <c r="N206" s="2"/>
+      <c r="O206" s="2"/>
+      <c r="P206" s="2"/>
+      <c r="Q206" s="2"/>
+      <c r="R206" s="2"/>
+      <c r="S206" s="2"/>
+      <c r="T206" s="5">
+        <v>9</v>
+      </c>
+      <c r="U206" s="5">
+        <v>0</v>
+      </c>
+      <c r="V206" s="2"/>
+      <c r="W206" s="2"/>
+      <c r="X206" s="5"/>
+      <c r="Y206" s="5"/>
+      <c r="Z206" s="5"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2EDE03E9-ECC0-4B3A-9DC1-3F2C29A3F26C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ECA31B5-F78C-491A-9FE6-B586FF883743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30516"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30524"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0ECA31B5-F78C-491A-9FE6-B586FF883743}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{48D7B1FB-56F5-4795-9781-3EF0608CA620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="792" uniqueCount="370">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="395">
   <si>
     <t>Id</t>
   </si>
@@ -1149,6 +1149,81 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_7174_Starbucks%20San%20Jos%C3%A9%20I.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38903@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks ENCUENTRO OCEANIA PB</t>
+  </si>
+  <si>
+    <t>ramon.espinosa@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Ramon Espinosa Macias</t>
+  </si>
+  <si>
+    <t>berenice.sanchez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Berenice Ivon Sanchez Lopez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/IMG20260921065014_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/IMG20260928094806_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38371@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Montevideo</t>
+  </si>
+  <si>
+    <t>martin-gerardo.martin@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Martin Gerardo Herrera Vazquez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/17906105971725611291123384245563_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>sbmx43194@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Atana Lindavista</t>
+  </si>
+  <si>
+    <t>sbmx38837@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Centenario Azcapotzalco</t>
+  </si>
+  <si>
+    <t>FHW</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17906107821271010478677792272711_Sergio%20Daniel%20Parra.jpg</t>
+  </si>
+  <si>
+    <t>sbmx43132@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Vista Norte</t>
+  </si>
+  <si>
+    <t>sbmx38527@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Camarones</t>
+  </si>
+  <si>
+    <t>sbmx38458@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks El Rosario</t>
   </si>
 </sst>
 </file>
@@ -1190,10 +1265,10 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1285,8 +1360,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z206" totalsRowShown="0">
-  <autoFilter ref="A1:Z206" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z238" totalsRowShown="0">
+  <autoFilter ref="A1:Z238" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1474,7 +1549,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1033" latestEventMarker="1479">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1065" latestEventMarker="1511">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1804,7 +1879,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z206"/>
+  <dimension ref="A1:Z238"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -1881,13 +1956,13 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-      <c r="X1" s="5" t="s">
+      <c r="X1" t="s">
         <v>23</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" t="s">
         <v>24</v>
       </c>
-      <c r="Z1" s="6" t="s">
+      <c r="Z1" s="5" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1913,9 +1988,6 @@
       <c r="G2" t="s">
         <v>28</v>
       </c>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
     </row>
     <row r="3" spans="1:26">
       <c r="A3">
@@ -1939,9 +2011,6 @@
       <c r="G3" t="s">
         <v>29</v>
       </c>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
     </row>
     <row r="4" spans="1:26">
       <c r="A4">
@@ -1968,9 +2037,6 @@
       <c r="K4" t="s">
         <v>33</v>
       </c>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
     </row>
     <row r="5" spans="1:26">
       <c r="A5">
@@ -1997,9 +2063,6 @@
       <c r="M5" t="s">
         <v>37</v>
       </c>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5"/>
     </row>
     <row r="6" spans="1:26">
       <c r="A6">
@@ -2023,9 +2086,6 @@
       <c r="G6" t="s">
         <v>28</v>
       </c>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
     </row>
     <row r="7" spans="1:26">
       <c r="A7">
@@ -2049,9 +2109,6 @@
       <c r="G7" t="s">
         <v>28</v>
       </c>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
     </row>
     <row r="8" spans="1:26">
       <c r="A8">
@@ -2075,9 +2132,6 @@
       <c r="G8" t="s">
         <v>28</v>
       </c>
-      <c r="X8" s="5"/>
-      <c r="Y8" s="5"/>
-      <c r="Z8" s="5"/>
     </row>
     <row r="9" spans="1:26">
       <c r="A9">
@@ -2101,9 +2155,6 @@
       <c r="G9" t="s">
         <v>28</v>
       </c>
-      <c r="X9" s="5"/>
-      <c r="Y9" s="5"/>
-      <c r="Z9" s="5"/>
     </row>
     <row r="10" spans="1:26">
       <c r="A10">
@@ -2127,9 +2178,6 @@
       <c r="G10" t="s">
         <v>28</v>
       </c>
-      <c r="X10" s="5"/>
-      <c r="Y10" s="5"/>
-      <c r="Z10" s="5"/>
     </row>
     <row r="11" spans="1:26">
       <c r="A11">
@@ -2153,9 +2201,6 @@
       <c r="G11" t="s">
         <v>28</v>
       </c>
-      <c r="X11" s="5"/>
-      <c r="Y11" s="5"/>
-      <c r="Z11" s="5"/>
     </row>
     <row r="12" spans="1:26">
       <c r="A12">
@@ -2179,9 +2224,6 @@
       <c r="G12" t="s">
         <v>28</v>
       </c>
-      <c r="X12" s="5"/>
-      <c r="Y12" s="5"/>
-      <c r="Z12" s="5"/>
     </row>
     <row r="13" spans="1:26">
       <c r="A13">
@@ -2205,9 +2247,6 @@
       <c r="G13" t="s">
         <v>28</v>
       </c>
-      <c r="X13" s="5"/>
-      <c r="Y13" s="5"/>
-      <c r="Z13" s="5"/>
     </row>
     <row r="14" spans="1:26">
       <c r="A14">
@@ -2231,9 +2270,6 @@
       <c r="G14" t="s">
         <v>28</v>
       </c>
-      <c r="X14" s="5"/>
-      <c r="Y14" s="5"/>
-      <c r="Z14" s="5"/>
     </row>
     <row r="15" spans="1:26">
       <c r="A15">
@@ -2257,9 +2293,6 @@
       <c r="G15" t="s">
         <v>28</v>
       </c>
-      <c r="X15" s="5"/>
-      <c r="Y15" s="5"/>
-      <c r="Z15" s="5"/>
     </row>
     <row r="16" spans="1:26">
       <c r="A16">
@@ -2283,11 +2316,8 @@
       <c r="G16" t="s">
         <v>28</v>
       </c>
-      <c r="X16" s="5"/>
-      <c r="Y16" s="5"/>
-      <c r="Z16" s="5"/>
-    </row>
-    <row r="17" spans="1:26">
+    </row>
+    <row r="17" spans="1:23">
       <c r="A17">
         <v>842</v>
       </c>
@@ -2309,11 +2339,8 @@
       <c r="G17" t="s">
         <v>28</v>
       </c>
-      <c r="X17" s="5"/>
-      <c r="Y17" s="5"/>
-      <c r="Z17" s="5"/>
-    </row>
-    <row r="18" spans="1:26">
+    </row>
+    <row r="18" spans="1:23">
       <c r="A18">
         <v>843</v>
       </c>
@@ -2338,11 +2365,8 @@
       <c r="O18" t="s">
         <v>65</v>
       </c>
-      <c r="X18" s="5"/>
-      <c r="Y18" s="5"/>
-      <c r="Z18" s="5"/>
-    </row>
-    <row r="19" spans="1:26">
+    </row>
+    <row r="19" spans="1:23">
       <c r="A19">
         <v>844</v>
       </c>
@@ -2364,11 +2388,8 @@
       <c r="G19" t="s">
         <v>28</v>
       </c>
-      <c r="X19" s="5"/>
-      <c r="Y19" s="5"/>
-      <c r="Z19" s="5"/>
-    </row>
-    <row r="20" spans="1:26">
+    </row>
+    <row r="20" spans="1:23">
       <c r="A20">
         <v>845</v>
       </c>
@@ -2393,11 +2414,8 @@
       <c r="P20" t="s">
         <v>69</v>
       </c>
-      <c r="X20" s="5"/>
-      <c r="Y20" s="5"/>
-      <c r="Z20" s="5"/>
-    </row>
-    <row r="21" spans="1:26">
+    </row>
+    <row r="21" spans="1:23">
       <c r="A21">
         <v>846</v>
       </c>
@@ -2419,11 +2437,8 @@
       <c r="G21" t="s">
         <v>28</v>
       </c>
-      <c r="X21" s="5"/>
-      <c r="Y21" s="5"/>
-      <c r="Z21" s="5"/>
-    </row>
-    <row r="22" spans="1:26">
+    </row>
+    <row r="22" spans="1:23">
       <c r="A22">
         <v>847</v>
       </c>
@@ -2445,11 +2460,8 @@
       <c r="G22" t="s">
         <v>28</v>
       </c>
-      <c r="X22" s="5"/>
-      <c r="Y22" s="5"/>
-      <c r="Z22" s="5"/>
-    </row>
-    <row r="23" spans="1:26">
+    </row>
+    <row r="23" spans="1:23">
       <c r="A23">
         <v>848</v>
       </c>
@@ -2471,11 +2483,8 @@
       <c r="G23" t="s">
         <v>28</v>
       </c>
-      <c r="X23" s="5"/>
-      <c r="Y23" s="5"/>
-      <c r="Z23" s="5"/>
-    </row>
-    <row r="24" spans="1:26">
+    </row>
+    <row r="24" spans="1:23">
       <c r="A24">
         <v>849</v>
       </c>
@@ -2500,11 +2509,8 @@
       <c r="P24" t="s">
         <v>76</v>
       </c>
-      <c r="X24" s="5"/>
-      <c r="Y24" s="5"/>
-      <c r="Z24" s="5"/>
-    </row>
-    <row r="25" spans="1:26">
+    </row>
+    <row r="25" spans="1:23">
       <c r="A25">
         <v>850</v>
       </c>
@@ -2535,11 +2541,8 @@
       <c r="S25" t="s">
         <v>80</v>
       </c>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="5"/>
-    </row>
-    <row r="26" spans="1:26">
+    </row>
+    <row r="26" spans="1:23">
       <c r="A26">
         <v>851</v>
       </c>
@@ -2561,11 +2564,8 @@
       <c r="G26" t="s">
         <v>28</v>
       </c>
-      <c r="X26" s="5"/>
-      <c r="Y26" s="5"/>
-      <c r="Z26" s="5"/>
-    </row>
-    <row r="27" spans="1:26">
+    </row>
+    <row r="27" spans="1:23">
       <c r="A27">
         <v>853</v>
       </c>
@@ -2587,11 +2587,8 @@
       <c r="G27" t="s">
         <v>28</v>
       </c>
-      <c r="X27" s="5"/>
-      <c r="Y27" s="5"/>
-      <c r="Z27" s="5"/>
-    </row>
-    <row r="28" spans="1:26">
+    </row>
+    <row r="28" spans="1:23">
       <c r="A28">
         <v>854</v>
       </c>
@@ -2613,11 +2610,8 @@
       <c r="G28" t="s">
         <v>28</v>
       </c>
-      <c r="X28" s="5"/>
-      <c r="Y28" s="5"/>
-      <c r="Z28" s="5"/>
-    </row>
-    <row r="29" spans="1:26">
+    </row>
+    <row r="29" spans="1:23">
       <c r="A29">
         <v>855</v>
       </c>
@@ -2639,11 +2633,8 @@
       <c r="G29" t="s">
         <v>28</v>
       </c>
-      <c r="X29" s="5"/>
-      <c r="Y29" s="5"/>
-      <c r="Z29" s="5"/>
-    </row>
-    <row r="30" spans="1:26">
+    </row>
+    <row r="30" spans="1:23">
       <c r="A30">
         <v>856</v>
       </c>
@@ -2674,11 +2665,8 @@
       <c r="S30" t="s">
         <v>91</v>
       </c>
-      <c r="X30" s="5"/>
-      <c r="Y30" s="5"/>
-      <c r="Z30" s="5"/>
-    </row>
-    <row r="31" spans="1:26">
+    </row>
+    <row r="31" spans="1:23">
       <c r="A31">
         <v>857</v>
       </c>
@@ -2706,11 +2694,8 @@
       <c r="W31" t="s">
         <v>94</v>
       </c>
-      <c r="X31" s="5"/>
-      <c r="Y31" s="5"/>
-      <c r="Z31" s="5"/>
-    </row>
-    <row r="32" spans="1:26">
+    </row>
+    <row r="32" spans="1:23">
       <c r="A32">
         <v>858</v>
       </c>
@@ -2732,11 +2717,8 @@
       <c r="G32" t="s">
         <v>28</v>
       </c>
-      <c r="X32" s="5"/>
-      <c r="Y32" s="5"/>
-      <c r="Z32" s="5"/>
-    </row>
-    <row r="33" spans="1:26">
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33">
         <v>859</v>
       </c>
@@ -2761,11 +2743,8 @@
       <c r="O33" t="s">
         <v>99</v>
       </c>
-      <c r="X33" s="5"/>
-      <c r="Y33" s="5"/>
-      <c r="Z33" s="5"/>
-    </row>
-    <row r="34" spans="1:26">
+    </row>
+    <row r="34" spans="1:19">
       <c r="A34">
         <v>860</v>
       </c>
@@ -2787,11 +2766,8 @@
       <c r="G34" t="s">
         <v>28</v>
       </c>
-      <c r="X34" s="5"/>
-      <c r="Y34" s="5"/>
-      <c r="Z34" s="5"/>
-    </row>
-    <row r="35" spans="1:26">
+    </row>
+    <row r="35" spans="1:19">
       <c r="A35">
         <v>861</v>
       </c>
@@ -2813,11 +2789,8 @@
       <c r="G35" t="s">
         <v>28</v>
       </c>
-      <c r="X35" s="5"/>
-      <c r="Y35" s="5"/>
-      <c r="Z35" s="5"/>
-    </row>
-    <row r="36" spans="1:26">
+    </row>
+    <row r="36" spans="1:19">
       <c r="A36">
         <v>862</v>
       </c>
@@ -2839,11 +2812,8 @@
       <c r="G36" t="s">
         <v>28</v>
       </c>
-      <c r="X36" s="5"/>
-      <c r="Y36" s="5"/>
-      <c r="Z36" s="5"/>
-    </row>
-    <row r="37" spans="1:26">
+    </row>
+    <row r="37" spans="1:19">
       <c r="A37">
         <v>863</v>
       </c>
@@ -2865,11 +2835,8 @@
       <c r="G37" t="s">
         <v>28</v>
       </c>
-      <c r="X37" s="5"/>
-      <c r="Y37" s="5"/>
-      <c r="Z37" s="5"/>
-    </row>
-    <row r="38" spans="1:26">
+    </row>
+    <row r="38" spans="1:19">
       <c r="A38">
         <v>864</v>
       </c>
@@ -2891,11 +2858,8 @@
       <c r="G38" t="s">
         <v>28</v>
       </c>
-      <c r="X38" s="5"/>
-      <c r="Y38" s="5"/>
-      <c r="Z38" s="5"/>
-    </row>
-    <row r="39" spans="1:26">
+    </row>
+    <row r="39" spans="1:19">
       <c r="A39">
         <v>865</v>
       </c>
@@ -2926,11 +2890,8 @@
       <c r="S39" t="s">
         <v>112</v>
       </c>
-      <c r="X39" s="5"/>
-      <c r="Y39" s="5"/>
-      <c r="Z39" s="5"/>
-    </row>
-    <row r="40" spans="1:26">
+    </row>
+    <row r="40" spans="1:19">
       <c r="A40">
         <v>866</v>
       </c>
@@ -2952,11 +2913,8 @@
       <c r="G40" t="s">
         <v>28</v>
       </c>
-      <c r="X40" s="5"/>
-      <c r="Y40" s="5"/>
-      <c r="Z40" s="5"/>
-    </row>
-    <row r="41" spans="1:26">
+    </row>
+    <row r="41" spans="1:19">
       <c r="A41">
         <v>867</v>
       </c>
@@ -2981,11 +2939,8 @@
       <c r="L41" t="s">
         <v>118</v>
       </c>
-      <c r="X41" s="5"/>
-      <c r="Y41" s="5"/>
-      <c r="Z41" s="5"/>
-    </row>
-    <row r="42" spans="1:26">
+    </row>
+    <row r="42" spans="1:19">
       <c r="A42">
         <v>868</v>
       </c>
@@ -3007,11 +2962,8 @@
       <c r="G42" t="s">
         <v>28</v>
       </c>
-      <c r="X42" s="5"/>
-      <c r="Y42" s="5"/>
-      <c r="Z42" s="5"/>
-    </row>
-    <row r="43" spans="1:26">
+    </row>
+    <row r="43" spans="1:19">
       <c r="A43">
         <v>869</v>
       </c>
@@ -3039,11 +2991,8 @@
       <c r="I43" t="s">
         <v>125</v>
       </c>
-      <c r="X43" s="5"/>
-      <c r="Y43" s="5"/>
-      <c r="Z43" s="5"/>
-    </row>
-    <row r="44" spans="1:26">
+    </row>
+    <row r="44" spans="1:19">
       <c r="A44">
         <v>870</v>
       </c>
@@ -3068,11 +3017,8 @@
       <c r="J44" t="s">
         <v>127</v>
       </c>
-      <c r="X44" s="5"/>
-      <c r="Y44" s="5"/>
-      <c r="Z44" s="5"/>
-    </row>
-    <row r="45" spans="1:26">
+    </row>
+    <row r="45" spans="1:19">
       <c r="A45">
         <v>871</v>
       </c>
@@ -3097,11 +3043,8 @@
       <c r="K45" t="s">
         <v>128</v>
       </c>
-      <c r="X45" s="5"/>
-      <c r="Y45" s="5"/>
-      <c r="Z45" s="5"/>
-    </row>
-    <row r="46" spans="1:26">
+    </row>
+    <row r="46" spans="1:19">
       <c r="A46">
         <v>872</v>
       </c>
@@ -3123,11 +3066,8 @@
       <c r="G46" t="s">
         <v>28</v>
       </c>
-      <c r="X46" s="5"/>
-      <c r="Y46" s="5"/>
-      <c r="Z46" s="5"/>
-    </row>
-    <row r="47" spans="1:26">
+    </row>
+    <row r="47" spans="1:19">
       <c r="A47">
         <v>873</v>
       </c>
@@ -3152,11 +3092,8 @@
       <c r="L47" t="s">
         <v>131</v>
       </c>
-      <c r="X47" s="5"/>
-      <c r="Y47" s="5"/>
-      <c r="Z47" s="5"/>
-    </row>
-    <row r="48" spans="1:26">
+    </row>
+    <row r="48" spans="1:19">
       <c r="A48">
         <v>874</v>
       </c>
@@ -3184,11 +3121,8 @@
       <c r="N48" t="s">
         <v>132</v>
       </c>
-      <c r="X48" s="5"/>
-      <c r="Y48" s="5"/>
-      <c r="Z48" s="5"/>
-    </row>
-    <row r="49" spans="1:26">
+    </row>
+    <row r="49" spans="1:19">
       <c r="A49">
         <v>875</v>
       </c>
@@ -3210,11 +3144,8 @@
       <c r="G49" t="s">
         <v>29</v>
       </c>
-      <c r="X49" s="5"/>
-      <c r="Y49" s="5"/>
-      <c r="Z49" s="5"/>
-    </row>
-    <row r="50" spans="1:26">
+    </row>
+    <row r="50" spans="1:19">
       <c r="A50">
         <v>876</v>
       </c>
@@ -3239,11 +3170,8 @@
       <c r="O50" t="s">
         <v>133</v>
       </c>
-      <c r="X50" s="5"/>
-      <c r="Y50" s="5"/>
-      <c r="Z50" s="5"/>
-    </row>
-    <row r="51" spans="1:26">
+    </row>
+    <row r="51" spans="1:19">
       <c r="A51">
         <v>877</v>
       </c>
@@ -3268,11 +3196,8 @@
       <c r="P51" t="s">
         <v>134</v>
       </c>
-      <c r="X51" s="5"/>
-      <c r="Y51" s="5"/>
-      <c r="Z51" s="5"/>
-    </row>
-    <row r="52" spans="1:26">
+    </row>
+    <row r="52" spans="1:19">
       <c r="A52">
         <v>878</v>
       </c>
@@ -3303,11 +3228,8 @@
       <c r="S52" t="s">
         <v>135</v>
       </c>
-      <c r="X52" s="5"/>
-      <c r="Y52" s="5"/>
-      <c r="Z52" s="5"/>
-    </row>
-    <row r="53" spans="1:26">
+    </row>
+    <row r="53" spans="1:19">
       <c r="A53">
         <v>879</v>
       </c>
@@ -3329,11 +3251,8 @@
       <c r="G53" t="s">
         <v>28</v>
       </c>
-      <c r="X53" s="5"/>
-      <c r="Y53" s="5"/>
-      <c r="Z53" s="5"/>
-    </row>
-    <row r="54" spans="1:26">
+    </row>
+    <row r="54" spans="1:19">
       <c r="A54">
         <v>880</v>
       </c>
@@ -3355,11 +3274,8 @@
       <c r="G54" t="s">
         <v>28</v>
       </c>
-      <c r="X54" s="5"/>
-      <c r="Y54" s="5"/>
-      <c r="Z54" s="5"/>
-    </row>
-    <row r="55" spans="1:26">
+    </row>
+    <row r="55" spans="1:19">
       <c r="A55">
         <v>881</v>
       </c>
@@ -3381,11 +3297,8 @@
       <c r="G55" t="s">
         <v>28</v>
       </c>
-      <c r="X55" s="5"/>
-      <c r="Y55" s="5"/>
-      <c r="Z55" s="5"/>
-    </row>
-    <row r="56" spans="1:26">
+    </row>
+    <row r="56" spans="1:19">
       <c r="A56">
         <v>882</v>
       </c>
@@ -3413,11 +3326,8 @@
       <c r="N56" t="s">
         <v>144</v>
       </c>
-      <c r="X56" s="5"/>
-      <c r="Y56" s="5"/>
-      <c r="Z56" s="5"/>
-    </row>
-    <row r="57" spans="1:26">
+    </row>
+    <row r="57" spans="1:19">
       <c r="A57">
         <v>883</v>
       </c>
@@ -3439,11 +3349,8 @@
       <c r="G57" t="s">
         <v>28</v>
       </c>
-      <c r="X57" s="5"/>
-      <c r="Y57" s="5"/>
-      <c r="Z57" s="5"/>
-    </row>
-    <row r="58" spans="1:26">
+    </row>
+    <row r="58" spans="1:19">
       <c r="A58">
         <v>884</v>
       </c>
@@ -3465,11 +3372,8 @@
       <c r="G58" t="s">
         <v>28</v>
       </c>
-      <c r="X58" s="5"/>
-      <c r="Y58" s="5"/>
-      <c r="Z58" s="5"/>
-    </row>
-    <row r="59" spans="1:26">
+    </row>
+    <row r="59" spans="1:19">
       <c r="A59">
         <v>885</v>
       </c>
@@ -3491,11 +3395,8 @@
       <c r="G59" t="s">
         <v>28</v>
       </c>
-      <c r="X59" s="5"/>
-      <c r="Y59" s="5"/>
-      <c r="Z59" s="5"/>
-    </row>
-    <row r="60" spans="1:26">
+    </row>
+    <row r="60" spans="1:19">
       <c r="A60">
         <v>886</v>
       </c>
@@ -3517,11 +3418,8 @@
       <c r="G60" t="s">
         <v>28</v>
       </c>
-      <c r="X60" s="5"/>
-      <c r="Y60" s="5"/>
-      <c r="Z60" s="5"/>
-    </row>
-    <row r="61" spans="1:26">
+    </row>
+    <row r="61" spans="1:19">
       <c r="A61">
         <v>887</v>
       </c>
@@ -3543,11 +3441,8 @@
       <c r="G61" t="s">
         <v>28</v>
       </c>
-      <c r="X61" s="5"/>
-      <c r="Y61" s="5"/>
-      <c r="Z61" s="5"/>
-    </row>
-    <row r="62" spans="1:26">
+    </row>
+    <row r="62" spans="1:19">
       <c r="A62">
         <v>888</v>
       </c>
@@ -3569,11 +3464,8 @@
       <c r="G62" t="s">
         <v>28</v>
       </c>
-      <c r="X62" s="5"/>
-      <c r="Y62" s="5"/>
-      <c r="Z62" s="5"/>
-    </row>
-    <row r="63" spans="1:26">
+    </row>
+    <row r="63" spans="1:19">
       <c r="A63">
         <v>889</v>
       </c>
@@ -3595,11 +3487,8 @@
       <c r="G63" t="s">
         <v>28</v>
       </c>
-      <c r="X63" s="5"/>
-      <c r="Y63" s="5"/>
-      <c r="Z63" s="5"/>
-    </row>
-    <row r="64" spans="1:26">
+    </row>
+    <row r="64" spans="1:19">
       <c r="A64">
         <v>890</v>
       </c>
@@ -3621,11 +3510,8 @@
       <c r="G64" t="s">
         <v>28</v>
       </c>
-      <c r="X64" s="5"/>
-      <c r="Y64" s="5"/>
-      <c r="Z64" s="5"/>
-    </row>
-    <row r="65" spans="1:26">
+    </row>
+    <row r="65" spans="1:19">
       <c r="A65">
         <v>891</v>
       </c>
@@ -3647,11 +3533,8 @@
       <c r="G65" t="s">
         <v>28</v>
       </c>
-      <c r="X65" s="5"/>
-      <c r="Y65" s="5"/>
-      <c r="Z65" s="5"/>
-    </row>
-    <row r="66" spans="1:26">
+    </row>
+    <row r="66" spans="1:19">
       <c r="A66">
         <v>892</v>
       </c>
@@ -3673,11 +3556,8 @@
       <c r="G66" t="s">
         <v>28</v>
       </c>
-      <c r="X66" s="5"/>
-      <c r="Y66" s="5"/>
-      <c r="Z66" s="5"/>
-    </row>
-    <row r="67" spans="1:26">
+    </row>
+    <row r="67" spans="1:19">
       <c r="A67">
         <v>893</v>
       </c>
@@ -3702,11 +3582,8 @@
       <c r="L67" t="s">
         <v>157</v>
       </c>
-      <c r="X67" s="5"/>
-      <c r="Y67" s="5"/>
-      <c r="Z67" s="5"/>
-    </row>
-    <row r="68" spans="1:26">
+    </row>
+    <row r="68" spans="1:19">
       <c r="A68">
         <v>894</v>
       </c>
@@ -3728,11 +3605,8 @@
       <c r="G68" t="s">
         <v>28</v>
       </c>
-      <c r="X68" s="5"/>
-      <c r="Y68" s="5"/>
-      <c r="Z68" s="5"/>
-    </row>
-    <row r="69" spans="1:26">
+    </row>
+    <row r="69" spans="1:19">
       <c r="A69">
         <v>895</v>
       </c>
@@ -3754,11 +3628,8 @@
       <c r="G69" t="s">
         <v>29</v>
       </c>
-      <c r="X69" s="5"/>
-      <c r="Y69" s="5"/>
-      <c r="Z69" s="5"/>
-    </row>
-    <row r="70" spans="1:26">
+    </row>
+    <row r="70" spans="1:19">
       <c r="A70">
         <v>896</v>
       </c>
@@ -3780,11 +3651,8 @@
       <c r="G70" t="s">
         <v>28</v>
       </c>
-      <c r="X70" s="5"/>
-      <c r="Y70" s="5"/>
-      <c r="Z70" s="5"/>
-    </row>
-    <row r="71" spans="1:26">
+    </row>
+    <row r="71" spans="1:19">
       <c r="A71">
         <v>897</v>
       </c>
@@ -3806,11 +3674,8 @@
       <c r="G71" t="s">
         <v>29</v>
       </c>
-      <c r="X71" s="5"/>
-      <c r="Y71" s="5"/>
-      <c r="Z71" s="5"/>
-    </row>
-    <row r="72" spans="1:26">
+    </row>
+    <row r="72" spans="1:19">
       <c r="A72">
         <v>898</v>
       </c>
@@ -3832,11 +3697,8 @@
       <c r="G72" t="s">
         <v>28</v>
       </c>
-      <c r="X72" s="5"/>
-      <c r="Y72" s="5"/>
-      <c r="Z72" s="5"/>
-    </row>
-    <row r="73" spans="1:26">
+    </row>
+    <row r="73" spans="1:19">
       <c r="A73">
         <v>899</v>
       </c>
@@ -3861,11 +3723,8 @@
       <c r="L73" t="s">
         <v>166</v>
       </c>
-      <c r="X73" s="5"/>
-      <c r="Y73" s="5"/>
-      <c r="Z73" s="5"/>
-    </row>
-    <row r="74" spans="1:26">
+    </row>
+    <row r="74" spans="1:19">
       <c r="A74">
         <v>900</v>
       </c>
@@ -3887,11 +3746,8 @@
       <c r="G74" t="s">
         <v>28</v>
       </c>
-      <c r="X74" s="5"/>
-      <c r="Y74" s="5"/>
-      <c r="Z74" s="5"/>
-    </row>
-    <row r="75" spans="1:26">
+    </row>
+    <row r="75" spans="1:19">
       <c r="A75">
         <v>901</v>
       </c>
@@ -3913,11 +3769,8 @@
       <c r="G75" t="s">
         <v>28</v>
       </c>
-      <c r="X75" s="5"/>
-      <c r="Y75" s="5"/>
-      <c r="Z75" s="5"/>
-    </row>
-    <row r="76" spans="1:26">
+    </row>
+    <row r="76" spans="1:19">
       <c r="A76">
         <v>902</v>
       </c>
@@ -3939,11 +3792,8 @@
       <c r="G76" t="s">
         <v>28</v>
       </c>
-      <c r="X76" s="5"/>
-      <c r="Y76" s="5"/>
-      <c r="Z76" s="5"/>
-    </row>
-    <row r="77" spans="1:26">
+    </row>
+    <row r="77" spans="1:19">
       <c r="A77">
         <v>903</v>
       </c>
@@ -3965,11 +3815,8 @@
       <c r="G77" t="s">
         <v>28</v>
       </c>
-      <c r="X77" s="5"/>
-      <c r="Y77" s="5"/>
-      <c r="Z77" s="5"/>
-    </row>
-    <row r="78" spans="1:26">
+    </row>
+    <row r="78" spans="1:19">
       <c r="A78">
         <v>904</v>
       </c>
@@ -3991,11 +3838,8 @@
       <c r="G78" t="s">
         <v>28</v>
       </c>
-      <c r="X78" s="5"/>
-      <c r="Y78" s="5"/>
-      <c r="Z78" s="5"/>
-    </row>
-    <row r="79" spans="1:26">
+    </row>
+    <row r="79" spans="1:19">
       <c r="A79">
         <v>905</v>
       </c>
@@ -4026,11 +3870,8 @@
       <c r="S79" t="s">
         <v>175</v>
       </c>
-      <c r="X79" s="5"/>
-      <c r="Y79" s="5"/>
-      <c r="Z79" s="5"/>
-    </row>
-    <row r="80" spans="1:26">
+    </row>
+    <row r="80" spans="1:19">
       <c r="A80">
         <v>906</v>
       </c>
@@ -4052,11 +3893,8 @@
       <c r="G80" t="s">
         <v>28</v>
       </c>
-      <c r="X80" s="5"/>
-      <c r="Y80" s="5"/>
-      <c r="Z80" s="5"/>
-    </row>
-    <row r="81" spans="1:26">
+    </row>
+    <row r="81" spans="1:19">
       <c r="A81">
         <v>907</v>
       </c>
@@ -4078,11 +3916,8 @@
       <c r="G81" t="s">
         <v>28</v>
       </c>
-      <c r="X81" s="5"/>
-      <c r="Y81" s="5"/>
-      <c r="Z81" s="5"/>
-    </row>
-    <row r="82" spans="1:26">
+    </row>
+    <row r="82" spans="1:19">
       <c r="A82">
         <v>908</v>
       </c>
@@ -4104,11 +3939,8 @@
       <c r="G82" t="s">
         <v>28</v>
       </c>
-      <c r="X82" s="5"/>
-      <c r="Y82" s="5"/>
-      <c r="Z82" s="5"/>
-    </row>
-    <row r="83" spans="1:26">
+    </row>
+    <row r="83" spans="1:19">
       <c r="A83">
         <v>909</v>
       </c>
@@ -4130,11 +3962,8 @@
       <c r="G83" t="s">
         <v>28</v>
       </c>
-      <c r="X83" s="5"/>
-      <c r="Y83" s="5"/>
-      <c r="Z83" s="5"/>
-    </row>
-    <row r="84" spans="1:26">
+    </row>
+    <row r="84" spans="1:19">
       <c r="A84">
         <v>910</v>
       </c>
@@ -4156,11 +3985,8 @@
       <c r="G84" t="s">
         <v>28</v>
       </c>
-      <c r="X84" s="5"/>
-      <c r="Y84" s="5"/>
-      <c r="Z84" s="5"/>
-    </row>
-    <row r="85" spans="1:26">
+    </row>
+    <row r="85" spans="1:19">
       <c r="A85">
         <v>911</v>
       </c>
@@ -4185,11 +4011,8 @@
       <c r="O85" t="s">
         <v>186</v>
       </c>
-      <c r="X85" s="5"/>
-      <c r="Y85" s="5"/>
-      <c r="Z85" s="5"/>
-    </row>
-    <row r="86" spans="1:26">
+    </row>
+    <row r="86" spans="1:19">
       <c r="A86">
         <v>912</v>
       </c>
@@ -4214,11 +4037,8 @@
       <c r="J86" t="s">
         <v>187</v>
       </c>
-      <c r="X86" s="5"/>
-      <c r="Y86" s="5"/>
-      <c r="Z86" s="5"/>
-    </row>
-    <row r="87" spans="1:26">
+    </row>
+    <row r="87" spans="1:19">
       <c r="A87">
         <v>913</v>
       </c>
@@ -4249,11 +4069,8 @@
       <c r="S87" t="s">
         <v>188</v>
       </c>
-      <c r="X87" s="5"/>
-      <c r="Y87" s="5"/>
-      <c r="Z87" s="5"/>
-    </row>
-    <row r="88" spans="1:26">
+    </row>
+    <row r="88" spans="1:19">
       <c r="A88">
         <v>914</v>
       </c>
@@ -4278,11 +4095,8 @@
       <c r="J88" t="s">
         <v>189</v>
       </c>
-      <c r="X88" s="5"/>
-      <c r="Y88" s="5"/>
-      <c r="Z88" s="5"/>
-    </row>
-    <row r="89" spans="1:26">
+    </row>
+    <row r="89" spans="1:19">
       <c r="A89">
         <v>915</v>
       </c>
@@ -4307,11 +4121,8 @@
       <c r="L89" t="s">
         <v>190</v>
       </c>
-      <c r="X89" s="5"/>
-      <c r="Y89" s="5"/>
-      <c r="Z89" s="5"/>
-    </row>
-    <row r="90" spans="1:26">
+    </row>
+    <row r="90" spans="1:19">
       <c r="A90">
         <v>916</v>
       </c>
@@ -4339,11 +4150,8 @@
       <c r="N90" t="s">
         <v>193</v>
       </c>
-      <c r="X90" s="5"/>
-      <c r="Y90" s="5"/>
-      <c r="Z90" s="5"/>
-    </row>
-    <row r="91" spans="1:26">
+    </row>
+    <row r="91" spans="1:19">
       <c r="A91">
         <v>917</v>
       </c>
@@ -4368,11 +4176,8 @@
       <c r="L91" t="s">
         <v>196</v>
       </c>
-      <c r="X91" s="5"/>
-      <c r="Y91" s="5"/>
-      <c r="Z91" s="5"/>
-    </row>
-    <row r="92" spans="1:26">
+    </row>
+    <row r="92" spans="1:19">
       <c r="A92">
         <v>918</v>
       </c>
@@ -4397,11 +4202,8 @@
       <c r="J92" t="s">
         <v>199</v>
       </c>
-      <c r="X92" s="5"/>
-      <c r="Y92" s="5"/>
-      <c r="Z92" s="5"/>
-    </row>
-    <row r="93" spans="1:26">
+    </row>
+    <row r="93" spans="1:19">
       <c r="A93">
         <v>919</v>
       </c>
@@ -4426,11 +4228,8 @@
       <c r="K93" t="s">
         <v>200</v>
       </c>
-      <c r="X93" s="5"/>
-      <c r="Y93" s="5"/>
-      <c r="Z93" s="5"/>
-    </row>
-    <row r="94" spans="1:26">
+    </row>
+    <row r="94" spans="1:19">
       <c r="A94">
         <v>920</v>
       </c>
@@ -4455,11 +4254,8 @@
       <c r="L94" t="s">
         <v>203</v>
       </c>
-      <c r="X94" s="5"/>
-      <c r="Y94" s="5"/>
-      <c r="Z94" s="5"/>
-    </row>
-    <row r="95" spans="1:26">
+    </row>
+    <row r="95" spans="1:19">
       <c r="A95">
         <v>921</v>
       </c>
@@ -4484,11 +4280,8 @@
       <c r="L95" t="s">
         <v>204</v>
       </c>
-      <c r="X95" s="5"/>
-      <c r="Y95" s="5"/>
-      <c r="Z95" s="5"/>
-    </row>
-    <row r="96" spans="1:26">
+    </row>
+    <row r="96" spans="1:19">
       <c r="A96">
         <v>922</v>
       </c>
@@ -4513,11 +4306,8 @@
       <c r="O96" t="s">
         <v>205</v>
       </c>
-      <c r="X96" s="5"/>
-      <c r="Y96" s="5"/>
-      <c r="Z96" s="5"/>
-    </row>
-    <row r="97" spans="1:26">
+    </row>
+    <row r="97" spans="1:23">
       <c r="A97">
         <v>923</v>
       </c>
@@ -4548,11 +4338,8 @@
       <c r="S97" t="s">
         <v>206</v>
       </c>
-      <c r="X97" s="5"/>
-      <c r="Y97" s="5"/>
-      <c r="Z97" s="5"/>
-    </row>
-    <row r="98" spans="1:26">
+    </row>
+    <row r="98" spans="1:23">
       <c r="A98">
         <v>924</v>
       </c>
@@ -4574,11 +4361,8 @@
       <c r="G98" t="s">
         <v>28</v>
       </c>
-      <c r="X98" s="5"/>
-      <c r="Y98" s="5"/>
-      <c r="Z98" s="5"/>
-    </row>
-    <row r="99" spans="1:26">
+    </row>
+    <row r="99" spans="1:23">
       <c r="A99">
         <v>925</v>
       </c>
@@ -4603,11 +4387,8 @@
       <c r="L99" t="s">
         <v>209</v>
       </c>
-      <c r="X99" s="5"/>
-      <c r="Y99" s="5"/>
-      <c r="Z99" s="5"/>
-    </row>
-    <row r="100" spans="1:26">
+    </row>
+    <row r="100" spans="1:23">
       <c r="A100">
         <v>926</v>
       </c>
@@ -4635,11 +4416,8 @@
       <c r="I100" t="s">
         <v>210</v>
       </c>
-      <c r="X100" s="5"/>
-      <c r="Y100" s="5"/>
-      <c r="Z100" s="5"/>
-    </row>
-    <row r="101" spans="1:26">
+    </row>
+    <row r="101" spans="1:23">
       <c r="A101">
         <v>927</v>
       </c>
@@ -4675,11 +4453,8 @@
       <c r="S101" s="2"/>
       <c r="V101" s="2"/>
       <c r="W101" s="2"/>
-      <c r="X101" s="5"/>
-      <c r="Y101" s="5"/>
-      <c r="Z101" s="5"/>
-    </row>
-    <row r="102" spans="1:26">
+    </row>
+    <row r="102" spans="1:23">
       <c r="A102">
         <v>928</v>
       </c>
@@ -4717,11 +4492,8 @@
       <c r="S102" s="2"/>
       <c r="V102" s="2"/>
       <c r="W102" s="2"/>
-      <c r="X102" s="5"/>
-      <c r="Y102" s="5"/>
-      <c r="Z102" s="5"/>
-    </row>
-    <row r="103" spans="1:26">
+    </row>
+    <row r="103" spans="1:23">
       <c r="A103">
         <v>929</v>
       </c>
@@ -4759,11 +4531,8 @@
       <c r="S103" s="2"/>
       <c r="V103" s="2"/>
       <c r="W103" s="2"/>
-      <c r="X103" s="5"/>
-      <c r="Y103" s="5"/>
-      <c r="Z103" s="5"/>
-    </row>
-    <row r="104" spans="1:26">
+    </row>
+    <row r="104" spans="1:23">
       <c r="A104">
         <v>930</v>
       </c>
@@ -4803,11 +4572,8 @@
       <c r="S104" s="2"/>
       <c r="V104" s="2"/>
       <c r="W104" s="2"/>
-      <c r="X104" s="5"/>
-      <c r="Y104" s="5"/>
-      <c r="Z104" s="5"/>
-    </row>
-    <row r="105" spans="1:26">
+    </row>
+    <row r="105" spans="1:23">
       <c r="A105">
         <v>931</v>
       </c>
@@ -4845,11 +4611,8 @@
       <c r="S105" s="2"/>
       <c r="V105" s="2"/>
       <c r="W105" s="2"/>
-      <c r="X105" s="5"/>
-      <c r="Y105" s="5"/>
-      <c r="Z105" s="5"/>
-    </row>
-    <row r="106" spans="1:26">
+    </row>
+    <row r="106" spans="1:23">
       <c r="A106">
         <v>932</v>
       </c>
@@ -4887,11 +4650,8 @@
       <c r="S106" s="2"/>
       <c r="V106" s="2"/>
       <c r="W106" s="2"/>
-      <c r="X106" s="5"/>
-      <c r="Y106" s="5"/>
-      <c r="Z106" s="5"/>
-    </row>
-    <row r="107" spans="1:26">
+    </row>
+    <row r="107" spans="1:23">
       <c r="A107">
         <v>933</v>
       </c>
@@ -4931,11 +4691,8 @@
       <c r="S107" s="2"/>
       <c r="V107" s="2"/>
       <c r="W107" s="2"/>
-      <c r="X107" s="5"/>
-      <c r="Y107" s="5"/>
-      <c r="Z107" s="5"/>
-    </row>
-    <row r="108" spans="1:26">
+    </row>
+    <row r="108" spans="1:23">
       <c r="A108">
         <v>934</v>
       </c>
@@ -4973,11 +4730,8 @@
       <c r="S108" s="2"/>
       <c r="V108" s="2"/>
       <c r="W108" s="2"/>
-      <c r="X108" s="5"/>
-      <c r="Y108" s="5"/>
-      <c r="Z108" s="5"/>
-    </row>
-    <row r="109" spans="1:26">
+    </row>
+    <row r="109" spans="1:23">
       <c r="A109">
         <v>935</v>
       </c>
@@ -5015,11 +4769,8 @@
       <c r="S109" s="2"/>
       <c r="V109" s="2"/>
       <c r="W109" s="2"/>
-      <c r="X109" s="5"/>
-      <c r="Y109" s="5"/>
-      <c r="Z109" s="5"/>
-    </row>
-    <row r="110" spans="1:26">
+    </row>
+    <row r="110" spans="1:23">
       <c r="A110">
         <v>936</v>
       </c>
@@ -5057,11 +4808,8 @@
       <c r="S110" s="2"/>
       <c r="V110" s="2"/>
       <c r="W110" s="2"/>
-      <c r="X110" s="5"/>
-      <c r="Y110" s="5"/>
-      <c r="Z110" s="5"/>
-    </row>
-    <row r="111" spans="1:26">
+    </row>
+    <row r="111" spans="1:23">
       <c r="A111">
         <v>937</v>
       </c>
@@ -5097,11 +4845,8 @@
       <c r="S111" s="2"/>
       <c r="V111" s="2"/>
       <c r="W111" s="2"/>
-      <c r="X111" s="5"/>
-      <c r="Y111" s="5"/>
-      <c r="Z111" s="5"/>
-    </row>
-    <row r="112" spans="1:26">
+    </row>
+    <row r="112" spans="1:23">
       <c r="A112">
         <v>938</v>
       </c>
@@ -5139,11 +4884,8 @@
       <c r="S112" s="2"/>
       <c r="V112" s="2"/>
       <c r="W112" s="2"/>
-      <c r="X112" s="5"/>
-      <c r="Y112" s="5"/>
-      <c r="Z112" s="5"/>
-    </row>
-    <row r="113" spans="1:26">
+    </row>
+    <row r="113" spans="1:23">
       <c r="A113">
         <v>939</v>
       </c>
@@ -5181,11 +4923,8 @@
       <c r="S113" s="2"/>
       <c r="V113" s="2"/>
       <c r="W113" s="2"/>
-      <c r="X113" s="5"/>
-      <c r="Y113" s="5"/>
-      <c r="Z113" s="5"/>
-    </row>
-    <row r="114" spans="1:26">
+    </row>
+    <row r="114" spans="1:23">
       <c r="A114">
         <v>940</v>
       </c>
@@ -5223,11 +4962,8 @@
       <c r="S114" s="2"/>
       <c r="V114" s="2"/>
       <c r="W114" s="2"/>
-      <c r="X114" s="5"/>
-      <c r="Y114" s="5"/>
-      <c r="Z114" s="5"/>
-    </row>
-    <row r="115" spans="1:26">
+    </row>
+    <row r="115" spans="1:23">
       <c r="A115">
         <v>941</v>
       </c>
@@ -5263,11 +4999,8 @@
       <c r="S115" s="2"/>
       <c r="V115" s="2"/>
       <c r="W115" s="2"/>
-      <c r="X115" s="5"/>
-      <c r="Y115" s="5"/>
-      <c r="Z115" s="5"/>
-    </row>
-    <row r="116" spans="1:26">
+    </row>
+    <row r="116" spans="1:23">
       <c r="A116">
         <v>942</v>
       </c>
@@ -5305,11 +5038,8 @@
       <c r="S116" s="2"/>
       <c r="V116" s="2"/>
       <c r="W116" s="2"/>
-      <c r="X116" s="5"/>
-      <c r="Y116" s="5"/>
-      <c r="Z116" s="5"/>
-    </row>
-    <row r="117" spans="1:26">
+    </row>
+    <row r="117" spans="1:23">
       <c r="A117">
         <v>943</v>
       </c>
@@ -5347,11 +5077,8 @@
       <c r="S117" s="2"/>
       <c r="V117" s="2"/>
       <c r="W117" s="2"/>
-      <c r="X117" s="5"/>
-      <c r="Y117" s="5"/>
-      <c r="Z117" s="5"/>
-    </row>
-    <row r="118" spans="1:26">
+    </row>
+    <row r="118" spans="1:23">
       <c r="A118">
         <v>944</v>
       </c>
@@ -5393,11 +5120,8 @@
       </c>
       <c r="V118" s="2"/>
       <c r="W118" s="2"/>
-      <c r="X118" s="5"/>
-      <c r="Y118" s="5"/>
-      <c r="Z118" s="5"/>
-    </row>
-    <row r="119" spans="1:26">
+    </row>
+    <row r="119" spans="1:23">
       <c r="A119">
         <v>945</v>
       </c>
@@ -5439,11 +5163,8 @@
       </c>
       <c r="V119" s="2"/>
       <c r="W119" s="2"/>
-      <c r="X119" s="5"/>
-      <c r="Y119" s="5"/>
-      <c r="Z119" s="5"/>
-    </row>
-    <row r="120" spans="1:26">
+    </row>
+    <row r="120" spans="1:23">
       <c r="A120">
         <v>946</v>
       </c>
@@ -5479,11 +5200,8 @@
       <c r="S120" s="2"/>
       <c r="V120" s="2"/>
       <c r="W120" s="2"/>
-      <c r="X120" s="5"/>
-      <c r="Y120" s="5"/>
-      <c r="Z120" s="5"/>
-    </row>
-    <row r="121" spans="1:26">
+    </row>
+    <row r="121" spans="1:23">
       <c r="A121">
         <v>947</v>
       </c>
@@ -5519,11 +5237,8 @@
       <c r="S121" s="2"/>
       <c r="V121" s="2"/>
       <c r="W121" s="2"/>
-      <c r="X121" s="5"/>
-      <c r="Y121" s="5"/>
-      <c r="Z121" s="5"/>
-    </row>
-    <row r="122" spans="1:26">
+    </row>
+    <row r="122" spans="1:23">
       <c r="A122">
         <v>948</v>
       </c>
@@ -5561,11 +5276,8 @@
       <c r="S122" s="2"/>
       <c r="V122" s="2"/>
       <c r="W122" s="2"/>
-      <c r="X122" s="5"/>
-      <c r="Y122" s="5"/>
-      <c r="Z122" s="5"/>
-    </row>
-    <row r="123" spans="1:26">
+    </row>
+    <row r="123" spans="1:23">
       <c r="A123">
         <v>949</v>
       </c>
@@ -5605,11 +5317,8 @@
       <c r="W123" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="X123" s="5"/>
-      <c r="Y123" s="5"/>
-      <c r="Z123" s="5"/>
-    </row>
-    <row r="124" spans="1:26">
+    </row>
+    <row r="124" spans="1:23">
       <c r="A124">
         <v>950</v>
       </c>
@@ -5647,11 +5356,8 @@
       <c r="S124" s="2"/>
       <c r="V124" s="2"/>
       <c r="W124" s="2"/>
-      <c r="X124" s="5"/>
-      <c r="Y124" s="5"/>
-      <c r="Z124" s="5"/>
-    </row>
-    <row r="125" spans="1:26">
+    </row>
+    <row r="125" spans="1:23">
       <c r="A125">
         <v>951</v>
       </c>
@@ -5689,11 +5395,8 @@
       <c r="S125" s="2"/>
       <c r="V125" s="2"/>
       <c r="W125" s="2"/>
-      <c r="X125" s="5"/>
-      <c r="Y125" s="5"/>
-      <c r="Z125" s="5"/>
-    </row>
-    <row r="126" spans="1:26">
+    </row>
+    <row r="126" spans="1:23">
       <c r="A126">
         <v>952</v>
       </c>
@@ -5731,11 +5434,8 @@
       <c r="S126" s="2"/>
       <c r="V126" s="2"/>
       <c r="W126" s="2"/>
-      <c r="X126" s="5"/>
-      <c r="Y126" s="5"/>
-      <c r="Z126" s="5"/>
-    </row>
-    <row r="127" spans="1:26">
+    </row>
+    <row r="127" spans="1:23">
       <c r="A127">
         <v>953</v>
       </c>
@@ -5775,11 +5475,8 @@
       <c r="S127" s="2"/>
       <c r="V127" s="2"/>
       <c r="W127" s="2"/>
-      <c r="X127" s="5"/>
-      <c r="Y127" s="5"/>
-      <c r="Z127" s="5"/>
-    </row>
-    <row r="128" spans="1:26">
+    </row>
+    <row r="128" spans="1:23">
       <c r="A128">
         <v>954</v>
       </c>
@@ -5817,11 +5514,8 @@
       <c r="S128" s="2"/>
       <c r="V128" s="2"/>
       <c r="W128" s="2"/>
-      <c r="X128" s="5"/>
-      <c r="Y128" s="5"/>
-      <c r="Z128" s="5"/>
-    </row>
-    <row r="129" spans="1:26">
+    </row>
+    <row r="129" spans="1:23">
       <c r="A129">
         <v>955</v>
       </c>
@@ -5857,11 +5551,8 @@
       <c r="S129" s="2"/>
       <c r="V129" s="2"/>
       <c r="W129" s="2"/>
-      <c r="X129" s="5"/>
-      <c r="Y129" s="5"/>
-      <c r="Z129" s="5"/>
-    </row>
-    <row r="130" spans="1:26">
+    </row>
+    <row r="130" spans="1:23">
       <c r="A130">
         <v>956</v>
       </c>
@@ -5899,11 +5590,8 @@
       <c r="S130" s="2"/>
       <c r="V130" s="2"/>
       <c r="W130" s="2"/>
-      <c r="X130" s="5"/>
-      <c r="Y130" s="5"/>
-      <c r="Z130" s="5"/>
-    </row>
-    <row r="131" spans="1:26">
+    </row>
+    <row r="131" spans="1:23">
       <c r="A131">
         <v>957</v>
       </c>
@@ -5939,11 +5627,8 @@
       <c r="S131" s="2"/>
       <c r="V131" s="2"/>
       <c r="W131" s="2"/>
-      <c r="X131" s="5"/>
-      <c r="Y131" s="5"/>
-      <c r="Z131" s="5"/>
-    </row>
-    <row r="132" spans="1:26">
+    </row>
+    <row r="132" spans="1:23">
       <c r="A132">
         <v>958</v>
       </c>
@@ -5979,11 +5664,8 @@
       <c r="S132" s="2"/>
       <c r="V132" s="2"/>
       <c r="W132" s="2"/>
-      <c r="X132" s="5"/>
-      <c r="Y132" s="5"/>
-      <c r="Z132" s="5"/>
-    </row>
-    <row r="133" spans="1:26">
+    </row>
+    <row r="133" spans="1:23">
       <c r="A133">
         <v>959</v>
       </c>
@@ -6021,11 +5703,8 @@
       <c r="S133" s="2"/>
       <c r="V133" s="2"/>
       <c r="W133" s="2"/>
-      <c r="X133" s="5"/>
-      <c r="Y133" s="5"/>
-      <c r="Z133" s="5"/>
-    </row>
-    <row r="134" spans="1:26">
+    </row>
+    <row r="134" spans="1:23">
       <c r="A134">
         <v>960</v>
       </c>
@@ -6061,11 +5740,8 @@
       <c r="S134" s="2"/>
       <c r="V134" s="2"/>
       <c r="W134" s="2"/>
-      <c r="X134" s="5"/>
-      <c r="Y134" s="5"/>
-      <c r="Z134" s="5"/>
-    </row>
-    <row r="135" spans="1:26">
+    </row>
+    <row r="135" spans="1:23">
       <c r="A135">
         <v>961</v>
       </c>
@@ -6101,11 +5777,8 @@
       <c r="S135" s="2"/>
       <c r="V135" s="2"/>
       <c r="W135" s="2"/>
-      <c r="X135" s="5"/>
-      <c r="Y135" s="5"/>
-      <c r="Z135" s="5"/>
-    </row>
-    <row r="136" spans="1:26">
+    </row>
+    <row r="136" spans="1:23">
       <c r="A136">
         <v>962</v>
       </c>
@@ -6145,11 +5818,8 @@
       <c r="S136" s="2"/>
       <c r="V136" s="2"/>
       <c r="W136" s="2"/>
-      <c r="X136" s="5"/>
-      <c r="Y136" s="5"/>
-      <c r="Z136" s="5"/>
-    </row>
-    <row r="137" spans="1:26">
+    </row>
+    <row r="137" spans="1:23">
       <c r="A137">
         <v>963</v>
       </c>
@@ -6185,11 +5855,8 @@
       <c r="S137" s="2"/>
       <c r="V137" s="2"/>
       <c r="W137" s="2"/>
-      <c r="X137" s="5"/>
-      <c r="Y137" s="5"/>
-      <c r="Z137" s="5"/>
-    </row>
-    <row r="138" spans="1:26">
+    </row>
+    <row r="138" spans="1:23">
       <c r="A138">
         <v>964</v>
       </c>
@@ -6225,11 +5892,8 @@
       <c r="S138" s="2"/>
       <c r="V138" s="2"/>
       <c r="W138" s="2"/>
-      <c r="X138" s="5"/>
-      <c r="Y138" s="5"/>
-      <c r="Z138" s="5"/>
-    </row>
-    <row r="139" spans="1:26">
+    </row>
+    <row r="139" spans="1:23">
       <c r="A139">
         <v>965</v>
       </c>
@@ -6265,11 +5929,8 @@
       <c r="S139" s="2"/>
       <c r="V139" s="2"/>
       <c r="W139" s="2"/>
-      <c r="X139" s="5"/>
-      <c r="Y139" s="5"/>
-      <c r="Z139" s="5"/>
-    </row>
-    <row r="140" spans="1:26">
+    </row>
+    <row r="140" spans="1:23">
       <c r="A140">
         <v>966</v>
       </c>
@@ -6307,11 +5968,8 @@
       <c r="S140" s="2"/>
       <c r="V140" s="2"/>
       <c r="W140" s="2"/>
-      <c r="X140" s="5"/>
-      <c r="Y140" s="5"/>
-      <c r="Z140" s="5"/>
-    </row>
-    <row r="141" spans="1:26">
+    </row>
+    <row r="141" spans="1:23">
       <c r="A141">
         <v>967</v>
       </c>
@@ -6349,11 +6007,8 @@
       <c r="S141" s="2"/>
       <c r="V141" s="2"/>
       <c r="W141" s="2"/>
-      <c r="X141" s="5"/>
-      <c r="Y141" s="5"/>
-      <c r="Z141" s="5"/>
-    </row>
-    <row r="142" spans="1:26">
+    </row>
+    <row r="142" spans="1:23">
       <c r="A142">
         <v>968</v>
       </c>
@@ -6389,11 +6044,8 @@
       <c r="S142" s="2"/>
       <c r="V142" s="2"/>
       <c r="W142" s="2"/>
-      <c r="X142" s="5"/>
-      <c r="Y142" s="5"/>
-      <c r="Z142" s="5"/>
-    </row>
-    <row r="143" spans="1:26">
+    </row>
+    <row r="143" spans="1:23">
       <c r="A143">
         <v>969</v>
       </c>
@@ -6429,11 +6081,8 @@
       <c r="S143" s="2"/>
       <c r="V143" s="2"/>
       <c r="W143" s="2"/>
-      <c r="X143" s="5"/>
-      <c r="Y143" s="5"/>
-      <c r="Z143" s="5"/>
-    </row>
-    <row r="144" spans="1:26">
+    </row>
+    <row r="144" spans="1:23">
       <c r="A144">
         <v>970</v>
       </c>
@@ -6469,11 +6118,8 @@
       <c r="S144" s="2"/>
       <c r="V144" s="2"/>
       <c r="W144" s="2"/>
-      <c r="X144" s="5"/>
-      <c r="Y144" s="5"/>
-      <c r="Z144" s="5"/>
-    </row>
-    <row r="145" spans="1:26">
+    </row>
+    <row r="145" spans="1:23">
       <c r="A145">
         <v>971</v>
       </c>
@@ -6511,11 +6157,8 @@
       <c r="S145" s="2"/>
       <c r="V145" s="2"/>
       <c r="W145" s="2"/>
-      <c r="X145" s="5"/>
-      <c r="Y145" s="5"/>
-      <c r="Z145" s="5"/>
-    </row>
-    <row r="146" spans="1:26">
+    </row>
+    <row r="146" spans="1:23">
       <c r="A146">
         <v>972</v>
       </c>
@@ -6553,11 +6196,8 @@
       <c r="S146" s="2"/>
       <c r="V146" s="2"/>
       <c r="W146" s="2"/>
-      <c r="X146" s="5"/>
-      <c r="Y146" s="5"/>
-      <c r="Z146" s="5"/>
-    </row>
-    <row r="147" spans="1:26">
+    </row>
+    <row r="147" spans="1:23">
       <c r="A147">
         <v>973</v>
       </c>
@@ -6595,11 +6235,8 @@
       <c r="S147" s="2"/>
       <c r="V147" s="2"/>
       <c r="W147" s="2"/>
-      <c r="X147" s="5"/>
-      <c r="Y147" s="5"/>
-      <c r="Z147" s="5"/>
-    </row>
-    <row r="148" spans="1:26">
+    </row>
+    <row r="148" spans="1:23">
       <c r="A148">
         <v>974</v>
       </c>
@@ -6637,11 +6274,8 @@
       <c r="S148" s="2"/>
       <c r="V148" s="2"/>
       <c r="W148" s="2"/>
-      <c r="X148" s="5"/>
-      <c r="Y148" s="5"/>
-      <c r="Z148" s="5"/>
-    </row>
-    <row r="149" spans="1:26">
+    </row>
+    <row r="149" spans="1:23">
       <c r="A149">
         <v>975</v>
       </c>
@@ -6679,11 +6313,8 @@
       <c r="S149" s="2"/>
       <c r="V149" s="2"/>
       <c r="W149" s="2"/>
-      <c r="X149" s="5"/>
-      <c r="Y149" s="5"/>
-      <c r="Z149" s="5"/>
-    </row>
-    <row r="150" spans="1:26">
+    </row>
+    <row r="150" spans="1:23">
       <c r="A150">
         <v>976</v>
       </c>
@@ -6721,11 +6352,8 @@
       <c r="S150" s="2"/>
       <c r="V150" s="2"/>
       <c r="W150" s="2"/>
-      <c r="X150" s="5"/>
-      <c r="Y150" s="5"/>
-      <c r="Z150" s="5"/>
-    </row>
-    <row r="151" spans="1:26">
+    </row>
+    <row r="151" spans="1:23">
       <c r="A151">
         <v>977</v>
       </c>
@@ -6763,11 +6391,8 @@
       <c r="S151" s="2"/>
       <c r="V151" s="2"/>
       <c r="W151" s="2"/>
-      <c r="X151" s="5"/>
-      <c r="Y151" s="5"/>
-      <c r="Z151" s="5"/>
-    </row>
-    <row r="152" spans="1:26">
+    </row>
+    <row r="152" spans="1:23">
       <c r="A152">
         <v>978</v>
       </c>
@@ -6805,11 +6430,8 @@
       <c r="S152" s="2"/>
       <c r="V152" s="2"/>
       <c r="W152" s="2"/>
-      <c r="X152" s="5"/>
-      <c r="Y152" s="5"/>
-      <c r="Z152" s="5"/>
-    </row>
-    <row r="153" spans="1:26">
+    </row>
+    <row r="153" spans="1:23">
       <c r="A153">
         <v>979</v>
       </c>
@@ -6847,11 +6469,8 @@
       <c r="S153" s="2"/>
       <c r="V153" s="2"/>
       <c r="W153" s="2"/>
-      <c r="X153" s="5"/>
-      <c r="Y153" s="5"/>
-      <c r="Z153" s="5"/>
-    </row>
-    <row r="154" spans="1:26">
+    </row>
+    <row r="154" spans="1:23">
       <c r="A154">
         <v>980</v>
       </c>
@@ -6889,11 +6508,8 @@
       <c r="S154" s="2"/>
       <c r="V154" s="2"/>
       <c r="W154" s="2"/>
-      <c r="X154" s="5"/>
-      <c r="Y154" s="5"/>
-      <c r="Z154" s="5"/>
-    </row>
-    <row r="155" spans="1:26">
+    </row>
+    <row r="155" spans="1:23">
       <c r="A155">
         <v>981</v>
       </c>
@@ -6931,11 +6547,8 @@
       <c r="S155" s="2"/>
       <c r="V155" s="2"/>
       <c r="W155" s="2"/>
-      <c r="X155" s="5"/>
-      <c r="Y155" s="5"/>
-      <c r="Z155" s="5"/>
-    </row>
-    <row r="156" spans="1:26">
+    </row>
+    <row r="156" spans="1:23">
       <c r="A156">
         <v>982</v>
       </c>
@@ -6973,11 +6586,8 @@
       <c r="S156" s="2"/>
       <c r="V156" s="2"/>
       <c r="W156" s="2"/>
-      <c r="X156" s="5"/>
-      <c r="Y156" s="5"/>
-      <c r="Z156" s="5"/>
-    </row>
-    <row r="157" spans="1:26">
+    </row>
+    <row r="157" spans="1:23">
       <c r="A157">
         <v>983</v>
       </c>
@@ -7015,11 +6625,8 @@
       <c r="S157" s="2"/>
       <c r="V157" s="2"/>
       <c r="W157" s="2"/>
-      <c r="X157" s="5"/>
-      <c r="Y157" s="5"/>
-      <c r="Z157" s="5"/>
-    </row>
-    <row r="158" spans="1:26">
+    </row>
+    <row r="158" spans="1:23">
       <c r="A158">
         <v>984</v>
       </c>
@@ -7057,11 +6664,8 @@
       <c r="S158" s="2"/>
       <c r="V158" s="2"/>
       <c r="W158" s="2"/>
-      <c r="X158" s="5"/>
-      <c r="Y158" s="5"/>
-      <c r="Z158" s="5"/>
-    </row>
-    <row r="159" spans="1:26">
+    </row>
+    <row r="159" spans="1:23">
       <c r="A159">
         <v>985</v>
       </c>
@@ -7103,11 +6707,8 @@
       </c>
       <c r="V159" s="2"/>
       <c r="W159" s="2"/>
-      <c r="X159" s="5"/>
-      <c r="Y159" s="5"/>
-      <c r="Z159" s="5"/>
-    </row>
-    <row r="160" spans="1:26">
+    </row>
+    <row r="160" spans="1:23">
       <c r="A160">
         <v>986</v>
       </c>
@@ -7143,11 +6744,8 @@
       <c r="S160" s="2"/>
       <c r="V160" s="2"/>
       <c r="W160" s="2"/>
-      <c r="X160" s="5"/>
-      <c r="Y160" s="5"/>
-      <c r="Z160" s="5"/>
-    </row>
-    <row r="161" spans="1:26">
+    </row>
+    <row r="161" spans="1:23">
       <c r="A161">
         <v>987</v>
       </c>
@@ -7185,11 +6783,8 @@
       <c r="S161" s="2"/>
       <c r="V161" s="2"/>
       <c r="W161" s="2"/>
-      <c r="X161" s="5"/>
-      <c r="Y161" s="5"/>
-      <c r="Z161" s="5"/>
-    </row>
-    <row r="162" spans="1:26">
+    </row>
+    <row r="162" spans="1:23">
       <c r="A162">
         <v>988</v>
       </c>
@@ -7225,11 +6820,8 @@
       <c r="S162" s="2"/>
       <c r="V162" s="2"/>
       <c r="W162" s="2"/>
-      <c r="X162" s="5"/>
-      <c r="Y162" s="5"/>
-      <c r="Z162" s="5"/>
-    </row>
-    <row r="163" spans="1:26">
+    </row>
+    <row r="163" spans="1:23">
       <c r="A163">
         <v>989</v>
       </c>
@@ -7267,11 +6859,8 @@
       <c r="S163" s="2"/>
       <c r="V163" s="2"/>
       <c r="W163" s="2"/>
-      <c r="X163" s="5"/>
-      <c r="Y163" s="5"/>
-      <c r="Z163" s="5"/>
-    </row>
-    <row r="164" spans="1:26">
+    </row>
+    <row r="164" spans="1:23">
       <c r="A164">
         <v>990</v>
       </c>
@@ -7309,11 +6898,8 @@
       <c r="S164" s="2"/>
       <c r="V164" s="2"/>
       <c r="W164" s="2"/>
-      <c r="X164" s="5"/>
-      <c r="Y164" s="5"/>
-      <c r="Z164" s="5"/>
-    </row>
-    <row r="165" spans="1:26">
+    </row>
+    <row r="165" spans="1:23">
       <c r="A165">
         <v>991</v>
       </c>
@@ -7351,11 +6937,8 @@
       <c r="S165" s="2"/>
       <c r="V165" s="2"/>
       <c r="W165" s="2"/>
-      <c r="X165" s="5"/>
-      <c r="Y165" s="5"/>
-      <c r="Z165" s="5"/>
-    </row>
-    <row r="166" spans="1:26">
+    </row>
+    <row r="166" spans="1:23">
       <c r="A166">
         <v>992</v>
       </c>
@@ -7393,11 +6976,8 @@
       <c r="S166" s="2"/>
       <c r="V166" s="2"/>
       <c r="W166" s="2"/>
-      <c r="X166" s="5"/>
-      <c r="Y166" s="5"/>
-      <c r="Z166" s="5"/>
-    </row>
-    <row r="167" spans="1:26">
+    </row>
+    <row r="167" spans="1:23">
       <c r="A167">
         <v>993</v>
       </c>
@@ -7435,11 +7015,8 @@
       <c r="S167" s="2"/>
       <c r="V167" s="2"/>
       <c r="W167" s="2"/>
-      <c r="X167" s="5"/>
-      <c r="Y167" s="5"/>
-      <c r="Z167" s="5"/>
-    </row>
-    <row r="168" spans="1:26">
+    </row>
+    <row r="168" spans="1:23">
       <c r="A168">
         <v>994</v>
       </c>
@@ -7477,11 +7054,8 @@
       <c r="S168" s="2"/>
       <c r="V168" s="2"/>
       <c r="W168" s="2"/>
-      <c r="X168" s="5"/>
-      <c r="Y168" s="5"/>
-      <c r="Z168" s="5"/>
-    </row>
-    <row r="169" spans="1:26">
+    </row>
+    <row r="169" spans="1:23">
       <c r="A169">
         <v>995</v>
       </c>
@@ -7519,11 +7093,8 @@
       <c r="S169" s="2"/>
       <c r="V169" s="2"/>
       <c r="W169" s="2"/>
-      <c r="X169" s="5"/>
-      <c r="Y169" s="5"/>
-      <c r="Z169" s="5"/>
-    </row>
-    <row r="170" spans="1:26">
+    </row>
+    <row r="170" spans="1:23">
       <c r="A170">
         <v>996</v>
       </c>
@@ -7561,11 +7132,8 @@
       <c r="S170" s="2"/>
       <c r="V170" s="2"/>
       <c r="W170" s="2"/>
-      <c r="X170" s="5"/>
-      <c r="Y170" s="5"/>
-      <c r="Z170" s="5"/>
-    </row>
-    <row r="171" spans="1:26">
+    </row>
+    <row r="171" spans="1:23">
       <c r="A171">
         <v>997</v>
       </c>
@@ -7605,11 +7173,8 @@
       <c r="W171" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="X171" s="5"/>
-      <c r="Y171" s="5"/>
-      <c r="Z171" s="5"/>
-    </row>
-    <row r="172" spans="1:26">
+    </row>
+    <row r="172" spans="1:23">
       <c r="A172">
         <v>998</v>
       </c>
@@ -7647,11 +7212,8 @@
       <c r="S172" s="2"/>
       <c r="V172" s="2"/>
       <c r="W172" s="2"/>
-      <c r="X172" s="5"/>
-      <c r="Y172" s="5"/>
-      <c r="Z172" s="5"/>
-    </row>
-    <row r="173" spans="1:26">
+    </row>
+    <row r="173" spans="1:23">
       <c r="A173">
         <v>999</v>
       </c>
@@ -7689,11 +7251,8 @@
       <c r="S173" s="2"/>
       <c r="V173" s="2"/>
       <c r="W173" s="2"/>
-      <c r="X173" s="5"/>
-      <c r="Y173" s="5"/>
-      <c r="Z173" s="5"/>
-    </row>
-    <row r="174" spans="1:26">
+    </row>
+    <row r="174" spans="1:23">
       <c r="A174">
         <v>1000</v>
       </c>
@@ -7731,11 +7290,8 @@
       <c r="S174" s="2"/>
       <c r="V174" s="2"/>
       <c r="W174" s="2"/>
-      <c r="X174" s="5"/>
-      <c r="Y174" s="5"/>
-      <c r="Z174" s="5"/>
-    </row>
-    <row r="175" spans="1:26">
+    </row>
+    <row r="175" spans="1:23">
       <c r="A175">
         <v>1001</v>
       </c>
@@ -7773,11 +7329,8 @@
       <c r="S175" s="2"/>
       <c r="V175" s="2"/>
       <c r="W175" s="2"/>
-      <c r="X175" s="5"/>
-      <c r="Y175" s="5"/>
-      <c r="Z175" s="5"/>
-    </row>
-    <row r="176" spans="1:26">
+    </row>
+    <row r="176" spans="1:23">
       <c r="A176">
         <v>1002</v>
       </c>
@@ -7817,11 +7370,8 @@
       <c r="W176" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="X176" s="5"/>
-      <c r="Y176" s="5"/>
-      <c r="Z176" s="5"/>
-    </row>
-    <row r="177" spans="1:26">
+    </row>
+    <row r="177" spans="1:23">
       <c r="A177">
         <v>1003</v>
       </c>
@@ -7861,11 +7411,8 @@
       <c r="S177" s="2"/>
       <c r="V177" s="2"/>
       <c r="W177" s="2"/>
-      <c r="X177" s="5"/>
-      <c r="Y177" s="5"/>
-      <c r="Z177" s="5"/>
-    </row>
-    <row r="178" spans="1:26">
+    </row>
+    <row r="178" spans="1:23">
       <c r="A178">
         <v>1004</v>
       </c>
@@ -7901,11 +7448,8 @@
       <c r="S178" s="2"/>
       <c r="V178" s="2"/>
       <c r="W178" s="2"/>
-      <c r="X178" s="5"/>
-      <c r="Y178" s="5"/>
-      <c r="Z178" s="5"/>
-    </row>
-    <row r="179" spans="1:26">
+    </row>
+    <row r="179" spans="1:23">
       <c r="A179">
         <v>1005</v>
       </c>
@@ -7941,11 +7485,8 @@
       <c r="S179" s="2"/>
       <c r="V179" s="2"/>
       <c r="W179" s="2"/>
-      <c r="X179" s="5"/>
-      <c r="Y179" s="5"/>
-      <c r="Z179" s="5"/>
-    </row>
-    <row r="180" spans="1:26">
+    </row>
+    <row r="180" spans="1:23">
       <c r="A180">
         <v>1006</v>
       </c>
@@ -7985,11 +7526,8 @@
       <c r="W180" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="X180" s="5"/>
-      <c r="Y180" s="5"/>
-      <c r="Z180" s="5"/>
-    </row>
-    <row r="181" spans="1:26">
+    </row>
+    <row r="181" spans="1:23">
       <c r="A181">
         <v>1007</v>
       </c>
@@ -8027,11 +7565,8 @@
       <c r="S181" s="2"/>
       <c r="V181" s="2"/>
       <c r="W181" s="2"/>
-      <c r="X181" s="5"/>
-      <c r="Y181" s="5"/>
-      <c r="Z181" s="5"/>
-    </row>
-    <row r="182" spans="1:26">
+    </row>
+    <row r="182" spans="1:23">
       <c r="A182">
         <v>1008</v>
       </c>
@@ -8069,11 +7604,8 @@
       <c r="S182" s="2"/>
       <c r="V182" s="2"/>
       <c r="W182" s="2"/>
-      <c r="X182" s="5"/>
-      <c r="Y182" s="5"/>
-      <c r="Z182" s="5"/>
-    </row>
-    <row r="183" spans="1:26">
+    </row>
+    <row r="183" spans="1:23">
       <c r="A183">
         <v>1009</v>
       </c>
@@ -8111,11 +7643,8 @@
       <c r="S183" s="2"/>
       <c r="V183" s="2"/>
       <c r="W183" s="2"/>
-      <c r="X183" s="5"/>
-      <c r="Y183" s="5"/>
-      <c r="Z183" s="5"/>
-    </row>
-    <row r="184" spans="1:26">
+    </row>
+    <row r="184" spans="1:23">
       <c r="A184">
         <v>1010</v>
       </c>
@@ -8155,12 +7684,9 @@
       <c r="S184" s="2"/>
       <c r="V184" s="2"/>
       <c r="W184" s="2"/>
-      <c r="X184" s="5"/>
-      <c r="Y184" s="5"/>
-      <c r="Z184" s="5"/>
-    </row>
-    <row r="185" spans="1:26">
-      <c r="A185" s="5">
+    </row>
+    <row r="185" spans="1:23">
+      <c r="A185">
         <v>1011</v>
       </c>
       <c r="B185" s="3">
@@ -8175,7 +7701,7 @@
       <c r="E185" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="F185" s="5">
+      <c r="F185">
         <v>38289</v>
       </c>
       <c r="G185" s="2" t="s">
@@ -8195,16 +7721,11 @@
       <c r="Q185" s="2"/>
       <c r="R185" s="2"/>
       <c r="S185" s="2"/>
-      <c r="T185" s="5"/>
-      <c r="U185" s="5"/>
       <c r="V185" s="2"/>
       <c r="W185" s="2"/>
-      <c r="X185" s="5"/>
-      <c r="Y185" s="5"/>
-      <c r="Z185" s="5"/>
-    </row>
-    <row r="186" spans="1:26">
-      <c r="A186" s="5">
+    </row>
+    <row r="186" spans="1:23">
+      <c r="A186">
         <v>1012</v>
       </c>
       <c r="B186" s="3">
@@ -8219,7 +7740,7 @@
       <c r="E186" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F186" s="5">
+      <c r="F186">
         <v>38226</v>
       </c>
       <c r="G186" s="2" t="s">
@@ -8239,16 +7760,11 @@
       <c r="Q186" s="2"/>
       <c r="R186" s="2"/>
       <c r="S186" s="2"/>
-      <c r="T186" s="5"/>
-      <c r="U186" s="5"/>
       <c r="V186" s="2"/>
       <c r="W186" s="2"/>
-      <c r="X186" s="5"/>
-      <c r="Y186" s="5"/>
-      <c r="Z186" s="5"/>
-    </row>
-    <row r="187" spans="1:26">
-      <c r="A187" s="5">
+    </row>
+    <row r="187" spans="1:23">
+      <c r="A187">
         <v>1013</v>
       </c>
       <c r="B187" s="3">
@@ -8263,7 +7779,7 @@
       <c r="E187" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F187" s="5">
+      <c r="F187">
         <v>38226</v>
       </c>
       <c r="G187" s="2" t="s">
@@ -8285,16 +7801,11 @@
       <c r="Q187" s="2"/>
       <c r="R187" s="2"/>
       <c r="S187" s="2"/>
-      <c r="T187" s="5"/>
-      <c r="U187" s="5"/>
       <c r="V187" s="2"/>
       <c r="W187" s="2"/>
-      <c r="X187" s="5"/>
-      <c r="Y187" s="5"/>
-      <c r="Z187" s="5"/>
-    </row>
-    <row r="188" spans="1:26">
-      <c r="A188" s="5">
+    </row>
+    <row r="188" spans="1:23">
+      <c r="A188">
         <v>1014</v>
       </c>
       <c r="B188" s="3">
@@ -8309,7 +7820,7 @@
       <c r="E188" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F188" s="5">
+      <c r="F188">
         <v>38226</v>
       </c>
       <c r="G188" s="2" t="s">
@@ -8333,16 +7844,11 @@
       <c r="S188" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="T188" s="5"/>
-      <c r="U188" s="5"/>
       <c r="V188" s="2"/>
       <c r="W188" s="2"/>
-      <c r="X188" s="5"/>
-      <c r="Y188" s="5"/>
-      <c r="Z188" s="5"/>
-    </row>
-    <row r="189" spans="1:26">
-      <c r="A189" s="5">
+    </row>
+    <row r="189" spans="1:23">
+      <c r="A189">
         <v>1015</v>
       </c>
       <c r="B189" s="3">
@@ -8357,7 +7863,7 @@
       <c r="E189" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F189" s="5">
+      <c r="F189">
         <v>38226</v>
       </c>
       <c r="G189" s="2" t="s">
@@ -8377,16 +7883,11 @@
       <c r="Q189" s="2"/>
       <c r="R189" s="2"/>
       <c r="S189" s="2"/>
-      <c r="T189" s="5"/>
-      <c r="U189" s="5"/>
       <c r="V189" s="2"/>
       <c r="W189" s="2"/>
-      <c r="X189" s="5"/>
-      <c r="Y189" s="5"/>
-      <c r="Z189" s="5"/>
-    </row>
-    <row r="190" spans="1:26">
-      <c r="A190" s="5">
+    </row>
+    <row r="190" spans="1:23">
+      <c r="A190">
         <v>1016</v>
       </c>
       <c r="B190" s="3">
@@ -8401,7 +7902,7 @@
       <c r="E190" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F190" s="5">
+      <c r="F190">
         <v>38226</v>
       </c>
       <c r="G190" s="2" t="s">
@@ -8421,16 +7922,11 @@
       <c r="Q190" s="2"/>
       <c r="R190" s="2"/>
       <c r="S190" s="2"/>
-      <c r="T190" s="5"/>
-      <c r="U190" s="5"/>
       <c r="V190" s="2"/>
       <c r="W190" s="2"/>
-      <c r="X190" s="5"/>
-      <c r="Y190" s="5"/>
-      <c r="Z190" s="5"/>
-    </row>
-    <row r="191" spans="1:26">
-      <c r="A191" s="5">
+    </row>
+    <row r="191" spans="1:23">
+      <c r="A191">
         <v>1017</v>
       </c>
       <c r="B191" s="3">
@@ -8445,7 +7941,7 @@
       <c r="E191" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F191" s="5">
+      <c r="F191">
         <v>38226</v>
       </c>
       <c r="G191" s="2" t="s">
@@ -8463,20 +7959,17 @@
       <c r="Q191" s="2"/>
       <c r="R191" s="2"/>
       <c r="S191" s="2"/>
-      <c r="T191" s="5">
+      <c r="T191">
         <v>5</v>
       </c>
-      <c r="U191" s="5">
+      <c r="U191">
         <v>2</v>
       </c>
       <c r="V191" s="2"/>
       <c r="W191" s="2"/>
-      <c r="X191" s="5"/>
-      <c r="Y191" s="5"/>
-      <c r="Z191" s="5"/>
-    </row>
-    <row r="192" spans="1:26">
-      <c r="A192" s="5">
+    </row>
+    <row r="192" spans="1:23">
+      <c r="A192">
         <v>1018</v>
       </c>
       <c r="B192" s="3">
@@ -8491,7 +7984,7 @@
       <c r="E192" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="F192" s="5">
+      <c r="F192">
         <v>38226</v>
       </c>
       <c r="G192" s="2" t="s">
@@ -8511,16 +8004,11 @@
       <c r="Q192" s="2"/>
       <c r="R192" s="2"/>
       <c r="S192" s="2"/>
-      <c r="T192" s="5"/>
-      <c r="U192" s="5"/>
       <c r="V192" s="2"/>
       <c r="W192" s="2"/>
-      <c r="X192" s="5"/>
-      <c r="Y192" s="5"/>
-      <c r="Z192" s="5"/>
     </row>
     <row r="193" spans="1:26">
-      <c r="A193" s="5">
+      <c r="A193">
         <v>1019</v>
       </c>
       <c r="B193" s="3">
@@ -8535,7 +8023,7 @@
       <c r="E193" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F193" s="5">
+      <c r="F193">
         <v>38611</v>
       </c>
       <c r="G193" s="2" t="s">
@@ -8555,16 +8043,11 @@
       <c r="Q193" s="2"/>
       <c r="R193" s="2"/>
       <c r="S193" s="2"/>
-      <c r="T193" s="5"/>
-      <c r="U193" s="5"/>
       <c r="V193" s="2"/>
       <c r="W193" s="2"/>
-      <c r="X193" s="5"/>
-      <c r="Y193" s="5"/>
-      <c r="Z193" s="5"/>
     </row>
     <row r="194" spans="1:26">
-      <c r="A194" s="5">
+      <c r="A194">
         <v>1020</v>
       </c>
       <c r="B194" s="3">
@@ -8579,7 +8062,7 @@
       <c r="E194" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="F194" s="5">
+      <c r="F194">
         <v>38611</v>
       </c>
       <c r="G194" s="2" t="s">
@@ -8599,16 +8082,11 @@
       <c r="Q194" s="2"/>
       <c r="R194" s="2"/>
       <c r="S194" s="2"/>
-      <c r="T194" s="5"/>
-      <c r="U194" s="5"/>
       <c r="V194" s="2"/>
       <c r="W194" s="2"/>
-      <c r="X194" s="5"/>
-      <c r="Y194" s="5"/>
-      <c r="Z194" s="5"/>
     </row>
     <row r="195" spans="1:26">
-      <c r="A195" s="5">
+      <c r="A195">
         <v>1021</v>
       </c>
       <c r="B195" s="3">
@@ -8623,7 +8101,7 @@
       <c r="E195" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F195" s="5">
+      <c r="F195">
         <v>38925</v>
       </c>
       <c r="G195" s="2" t="s">
@@ -8641,20 +8119,17 @@
       <c r="Q195" s="2"/>
       <c r="R195" s="2"/>
       <c r="S195" s="2"/>
-      <c r="T195" s="5">
+      <c r="T195">
         <v>8</v>
       </c>
-      <c r="U195" s="5">
+      <c r="U195">
         <v>0</v>
       </c>
       <c r="V195" s="2"/>
       <c r="W195" s="2"/>
-      <c r="X195" s="5"/>
-      <c r="Y195" s="5"/>
-      <c r="Z195" s="5"/>
     </row>
     <row r="196" spans="1:26">
-      <c r="A196" s="5">
+      <c r="A196">
         <v>1022</v>
       </c>
       <c r="B196" s="3">
@@ -8669,7 +8144,7 @@
       <c r="E196" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="F196" s="5">
+      <c r="F196">
         <v>38417</v>
       </c>
       <c r="G196" s="2" t="s">
@@ -8689,16 +8164,11 @@
       <c r="Q196" s="2"/>
       <c r="R196" s="2"/>
       <c r="S196" s="2"/>
-      <c r="T196" s="5"/>
-      <c r="U196" s="5"/>
       <c r="V196" s="2"/>
       <c r="W196" s="2"/>
-      <c r="X196" s="5"/>
-      <c r="Y196" s="5"/>
-      <c r="Z196" s="5"/>
     </row>
     <row r="197" spans="1:26">
-      <c r="A197" s="5">
+      <c r="A197">
         <v>1024</v>
       </c>
       <c r="B197" s="3">
@@ -8713,7 +8183,7 @@
       <c r="E197" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F197" s="5">
+      <c r="F197">
         <v>38333</v>
       </c>
       <c r="G197" s="2" t="s">
@@ -8731,20 +8201,17 @@
       <c r="Q197" s="2"/>
       <c r="R197" s="2"/>
       <c r="S197" s="2"/>
-      <c r="T197" s="5">
+      <c r="T197">
         <v>18</v>
       </c>
-      <c r="U197" s="5">
+      <c r="U197">
         <v>0</v>
       </c>
       <c r="V197" s="2"/>
       <c r="W197" s="2"/>
-      <c r="X197" s="5"/>
-      <c r="Y197" s="5"/>
-      <c r="Z197" s="5"/>
     </row>
     <row r="198" spans="1:26">
-      <c r="A198" s="5">
+      <c r="A198">
         <v>1025</v>
       </c>
       <c r="B198" s="3">
@@ -8759,7 +8226,7 @@
       <c r="E198" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F198" s="5">
+      <c r="F198">
         <v>38339</v>
       </c>
       <c r="G198" s="2" t="s">
@@ -8777,20 +8244,17 @@
       <c r="Q198" s="2"/>
       <c r="R198" s="2"/>
       <c r="S198" s="2"/>
-      <c r="T198" s="5">
+      <c r="T198">
         <v>15</v>
       </c>
-      <c r="U198" s="5">
+      <c r="U198">
         <v>0</v>
       </c>
       <c r="V198" s="2"/>
       <c r="W198" s="2"/>
-      <c r="X198" s="5"/>
-      <c r="Y198" s="5"/>
-      <c r="Z198" s="5"/>
     </row>
     <row r="199" spans="1:26">
-      <c r="A199" s="5">
+      <c r="A199">
         <v>1026</v>
       </c>
       <c r="B199" s="3">
@@ -8805,7 +8269,7 @@
       <c r="E199" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F199" s="5">
+      <c r="F199">
         <v>38368</v>
       </c>
       <c r="G199" s="2" t="s">
@@ -8823,20 +8287,17 @@
       <c r="Q199" s="2"/>
       <c r="R199" s="2"/>
       <c r="S199" s="2"/>
-      <c r="T199" s="5">
+      <c r="T199">
         <v>14</v>
       </c>
-      <c r="U199" s="5">
+      <c r="U199">
         <v>2</v>
       </c>
       <c r="V199" s="2"/>
       <c r="W199" s="2"/>
-      <c r="X199" s="5"/>
-      <c r="Y199" s="5"/>
-      <c r="Z199" s="5"/>
     </row>
     <row r="200" spans="1:26">
-      <c r="A200" s="5">
+      <c r="A200">
         <v>1027</v>
       </c>
       <c r="B200" s="3">
@@ -8851,7 +8312,7 @@
       <c r="E200" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F200" s="5">
+      <c r="F200">
         <v>38401</v>
       </c>
       <c r="G200" s="2" t="s">
@@ -8869,20 +8330,17 @@
       <c r="Q200" s="2"/>
       <c r="R200" s="2"/>
       <c r="S200" s="2"/>
-      <c r="T200" s="5">
+      <c r="T200">
         <v>8</v>
       </c>
-      <c r="U200" s="5">
+      <c r="U200">
         <v>0</v>
       </c>
       <c r="V200" s="2"/>
       <c r="W200" s="2"/>
-      <c r="X200" s="5"/>
-      <c r="Y200" s="5"/>
-      <c r="Z200" s="5"/>
     </row>
     <row r="201" spans="1:26">
-      <c r="A201" s="5">
+      <c r="A201">
         <v>1028</v>
       </c>
       <c r="B201" s="3">
@@ -8897,7 +8355,7 @@
       <c r="E201" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F201" s="5">
+      <c r="F201">
         <v>38456</v>
       </c>
       <c r="G201" s="2" t="s">
@@ -8915,20 +8373,17 @@
       <c r="Q201" s="2"/>
       <c r="R201" s="2"/>
       <c r="S201" s="2"/>
-      <c r="T201" s="5">
+      <c r="T201">
         <v>12</v>
       </c>
-      <c r="U201" s="5">
+      <c r="U201">
         <v>0</v>
       </c>
       <c r="V201" s="2"/>
       <c r="W201" s="2"/>
-      <c r="X201" s="5"/>
-      <c r="Y201" s="5"/>
-      <c r="Z201" s="5"/>
     </row>
     <row r="202" spans="1:26">
-      <c r="A202" s="5">
+      <c r="A202">
         <v>1029</v>
       </c>
       <c r="B202" s="3">
@@ -8943,7 +8398,7 @@
       <c r="E202" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F202" s="5">
+      <c r="F202">
         <v>38515</v>
       </c>
       <c r="G202" s="2" t="s">
@@ -8961,20 +8416,17 @@
       <c r="Q202" s="2"/>
       <c r="R202" s="2"/>
       <c r="S202" s="2"/>
-      <c r="T202" s="5">
+      <c r="T202">
         <v>15</v>
       </c>
-      <c r="U202" s="5">
+      <c r="U202">
         <v>0</v>
       </c>
       <c r="V202" s="2"/>
       <c r="W202" s="2"/>
-      <c r="X202" s="5"/>
-      <c r="Y202" s="5"/>
-      <c r="Z202" s="5"/>
     </row>
     <row r="203" spans="1:26">
-      <c r="A203" s="5">
+      <c r="A203">
         <v>1030</v>
       </c>
       <c r="B203" s="3">
@@ -8989,7 +8441,7 @@
       <c r="E203" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F203" s="5">
+      <c r="F203">
         <v>38604</v>
       </c>
       <c r="G203" s="2" t="s">
@@ -9007,20 +8459,17 @@
       <c r="Q203" s="2"/>
       <c r="R203" s="2"/>
       <c r="S203" s="2"/>
-      <c r="T203" s="5">
+      <c r="T203">
         <v>16</v>
       </c>
-      <c r="U203" s="5">
+      <c r="U203">
         <v>0</v>
       </c>
       <c r="V203" s="2"/>
       <c r="W203" s="2"/>
-      <c r="X203" s="5"/>
-      <c r="Y203" s="5"/>
-      <c r="Z203" s="5"/>
     </row>
     <row r="204" spans="1:26">
-      <c r="A204" s="5">
+      <c r="A204">
         <v>1031</v>
       </c>
       <c r="B204" s="3">
@@ -9035,7 +8484,7 @@
       <c r="E204" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F204" s="5">
+      <c r="F204">
         <v>38862</v>
       </c>
       <c r="G204" s="2" t="s">
@@ -9053,20 +8502,17 @@
       <c r="Q204" s="2"/>
       <c r="R204" s="2"/>
       <c r="S204" s="2"/>
-      <c r="T204" s="5">
+      <c r="T204">
         <v>17</v>
       </c>
-      <c r="U204" s="5">
+      <c r="U204">
         <v>0</v>
       </c>
       <c r="V204" s="2"/>
       <c r="W204" s="2"/>
-      <c r="X204" s="5"/>
-      <c r="Y204" s="5"/>
-      <c r="Z204" s="5"/>
     </row>
     <row r="205" spans="1:26">
-      <c r="A205" s="5">
+      <c r="A205">
         <v>1032</v>
       </c>
       <c r="B205" s="3">
@@ -9081,7 +8527,7 @@
       <c r="E205" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F205" s="5">
+      <c r="F205">
         <v>38894</v>
       </c>
       <c r="G205" s="2" t="s">
@@ -9099,20 +8545,17 @@
       <c r="Q205" s="2"/>
       <c r="R205" s="2"/>
       <c r="S205" s="2"/>
-      <c r="T205" s="5">
+      <c r="T205">
         <v>15</v>
       </c>
-      <c r="U205" s="5">
+      <c r="U205">
         <v>0</v>
       </c>
       <c r="V205" s="2"/>
       <c r="W205" s="2"/>
-      <c r="X205" s="5"/>
-      <c r="Y205" s="5"/>
-      <c r="Z205" s="5"/>
     </row>
     <row r="206" spans="1:26">
-      <c r="A206" s="5">
+      <c r="A206">
         <v>1033</v>
       </c>
       <c r="B206" s="3">
@@ -9127,7 +8570,7 @@
       <c r="E206" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="F206" s="5">
+      <c r="F206">
         <v>43193</v>
       </c>
       <c r="G206" s="2" t="s">
@@ -9145,17 +8588,1486 @@
       <c r="Q206" s="2"/>
       <c r="R206" s="2"/>
       <c r="S206" s="2"/>
-      <c r="T206" s="5">
+      <c r="T206">
         <v>9</v>
       </c>
-      <c r="U206" s="5">
+      <c r="U206">
         <v>0</v>
       </c>
       <c r="V206" s="2"/>
       <c r="W206" s="2"/>
-      <c r="X206" s="5"/>
-      <c r="Y206" s="5"/>
-      <c r="Z206" s="5"/>
+    </row>
+    <row r="207" spans="1:26">
+      <c r="A207" s="6">
+        <v>1034</v>
+      </c>
+      <c r="B207" s="3">
+        <v>46293.387280092596</v>
+      </c>
+      <c r="C207" s="3">
+        <v>46293.388124999998</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E207" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F207" s="6">
+        <v>38894</v>
+      </c>
+      <c r="G207" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H207" s="2"/>
+      <c r="I207" s="2"/>
+      <c r="J207" s="2"/>
+      <c r="K207" s="2"/>
+      <c r="L207" s="2"/>
+      <c r="M207" s="2"/>
+      <c r="N207" s="2"/>
+      <c r="O207" s="2"/>
+      <c r="P207" s="2"/>
+      <c r="Q207" s="2"/>
+      <c r="R207" s="2"/>
+      <c r="S207" s="2"/>
+      <c r="T207" s="6">
+        <v>15</v>
+      </c>
+      <c r="U207" s="6">
+        <v>0</v>
+      </c>
+      <c r="V207" s="2"/>
+      <c r="W207" s="2"/>
+      <c r="X207" s="6"/>
+      <c r="Y207" s="6"/>
+      <c r="Z207" s="6"/>
+    </row>
+    <row r="208" spans="1:26">
+      <c r="A208" s="6">
+        <v>1035</v>
+      </c>
+      <c r="B208" s="3">
+        <v>46293.387245370403</v>
+      </c>
+      <c r="C208" s="3">
+        <v>46293.389340277798</v>
+      </c>
+      <c r="D208" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="E208" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F208" s="6">
+        <v>43152</v>
+      </c>
+      <c r="G208" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H208" s="2"/>
+      <c r="I208" s="2"/>
+      <c r="J208" s="2"/>
+      <c r="K208" s="2"/>
+      <c r="L208" s="2"/>
+      <c r="M208" s="2"/>
+      <c r="N208" s="2"/>
+      <c r="O208" s="2"/>
+      <c r="P208" s="2"/>
+      <c r="Q208" s="2"/>
+      <c r="R208" s="2"/>
+      <c r="S208" s="2"/>
+      <c r="T208" s="6">
+        <v>8</v>
+      </c>
+      <c r="U208" s="6">
+        <v>1</v>
+      </c>
+      <c r="V208" s="2"/>
+      <c r="W208" s="2"/>
+      <c r="X208" s="6"/>
+      <c r="Y208" s="6"/>
+      <c r="Z208" s="6"/>
+    </row>
+    <row r="209" spans="1:26">
+      <c r="A209" s="6">
+        <v>1036</v>
+      </c>
+      <c r="B209" s="3">
+        <v>46293.389027777797</v>
+      </c>
+      <c r="C209" s="3">
+        <v>46293.389675925901</v>
+      </c>
+      <c r="D209" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E209" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F209" s="6">
+        <v>38205</v>
+      </c>
+      <c r="G209" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H209" s="2"/>
+      <c r="I209" s="2"/>
+      <c r="J209" s="2"/>
+      <c r="K209" s="2"/>
+      <c r="L209" s="2"/>
+      <c r="M209" s="2"/>
+      <c r="N209" s="2"/>
+      <c r="O209" s="2"/>
+      <c r="P209" s="2"/>
+      <c r="Q209" s="2"/>
+      <c r="R209" s="2"/>
+      <c r="S209" s="2"/>
+      <c r="T209" s="6">
+        <v>18</v>
+      </c>
+      <c r="U209" s="6">
+        <v>1</v>
+      </c>
+      <c r="V209" s="2"/>
+      <c r="W209" s="2"/>
+      <c r="X209" s="6"/>
+      <c r="Y209" s="6"/>
+      <c r="Z209" s="6"/>
+    </row>
+    <row r="210" spans="1:26">
+      <c r="A210" s="6">
+        <v>1037</v>
+      </c>
+      <c r="B210" s="3">
+        <v>46293.3902662037</v>
+      </c>
+      <c r="C210" s="3">
+        <v>46293.390798611101</v>
+      </c>
+      <c r="D210" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F210" s="6">
+        <v>38862</v>
+      </c>
+      <c r="G210" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H210" s="2"/>
+      <c r="I210" s="2"/>
+      <c r="J210" s="2"/>
+      <c r="K210" s="2"/>
+      <c r="L210" s="2"/>
+      <c r="M210" s="2"/>
+      <c r="N210" s="2"/>
+      <c r="O210" s="2"/>
+      <c r="P210" s="2"/>
+      <c r="Q210" s="2"/>
+      <c r="R210" s="2"/>
+      <c r="S210" s="2"/>
+      <c r="T210" s="6">
+        <v>17</v>
+      </c>
+      <c r="U210" s="6">
+        <v>0</v>
+      </c>
+      <c r="V210" s="2"/>
+      <c r="W210" s="2"/>
+      <c r="X210" s="6"/>
+      <c r="Y210" s="6"/>
+      <c r="Z210" s="6"/>
+    </row>
+    <row r="211" spans="1:26">
+      <c r="A211" s="6">
+        <v>1038</v>
+      </c>
+      <c r="B211" s="3">
+        <v>46293.390902777799</v>
+      </c>
+      <c r="C211" s="3">
+        <v>46293.391331018502</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="F211" s="6">
+        <v>38590</v>
+      </c>
+      <c r="G211" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H211" s="2"/>
+      <c r="I211" s="2"/>
+      <c r="J211" s="2"/>
+      <c r="K211" s="2"/>
+      <c r="L211" s="2"/>
+      <c r="M211" s="2"/>
+      <c r="N211" s="2"/>
+      <c r="O211" s="2"/>
+      <c r="P211" s="2"/>
+      <c r="Q211" s="2"/>
+      <c r="R211" s="2"/>
+      <c r="S211" s="2"/>
+      <c r="T211" s="6">
+        <v>13</v>
+      </c>
+      <c r="U211" s="6">
+        <v>1</v>
+      </c>
+      <c r="V211" s="2"/>
+      <c r="W211" s="2"/>
+      <c r="X211" s="6"/>
+      <c r="Y211" s="6"/>
+      <c r="Z211" s="6"/>
+    </row>
+    <row r="212" spans="1:26">
+      <c r="A212" s="6">
+        <v>1039</v>
+      </c>
+      <c r="B212" s="3">
+        <v>46293.391550925902</v>
+      </c>
+      <c r="C212" s="3">
+        <v>46293.392071759299</v>
+      </c>
+      <c r="D212" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F212" s="6">
+        <v>38695</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H212" s="2"/>
+      <c r="I212" s="2"/>
+      <c r="J212" s="2"/>
+      <c r="K212" s="2"/>
+      <c r="L212" s="2"/>
+      <c r="M212" s="2"/>
+      <c r="N212" s="2"/>
+      <c r="O212" s="2"/>
+      <c r="P212" s="2"/>
+      <c r="Q212" s="2"/>
+      <c r="R212" s="2"/>
+      <c r="S212" s="2"/>
+      <c r="T212" s="6">
+        <v>12</v>
+      </c>
+      <c r="U212" s="6">
+        <v>6</v>
+      </c>
+      <c r="V212" s="2"/>
+      <c r="W212" s="2"/>
+      <c r="X212" s="6"/>
+      <c r="Y212" s="6"/>
+      <c r="Z212" s="6"/>
+    </row>
+    <row r="213" spans="1:26">
+      <c r="A213" s="6">
+        <v>1040</v>
+      </c>
+      <c r="B213" s="3">
+        <v>46293.3917476852</v>
+      </c>
+      <c r="C213" s="3">
+        <v>46293.392210648097</v>
+      </c>
+      <c r="D213" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E213" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="F213" s="6">
+        <v>38604</v>
+      </c>
+      <c r="G213" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H213" s="2"/>
+      <c r="I213" s="2"/>
+      <c r="J213" s="2"/>
+      <c r="K213" s="2"/>
+      <c r="L213" s="2"/>
+      <c r="M213" s="2"/>
+      <c r="N213" s="2"/>
+      <c r="O213" s="2"/>
+      <c r="P213" s="2"/>
+      <c r="Q213" s="2"/>
+      <c r="R213" s="2"/>
+      <c r="S213" s="2"/>
+      <c r="T213" s="6">
+        <v>15</v>
+      </c>
+      <c r="U213" s="6">
+        <v>0</v>
+      </c>
+      <c r="V213" s="2"/>
+      <c r="W213" s="2"/>
+      <c r="X213" s="6"/>
+      <c r="Y213" s="6"/>
+      <c r="Z213" s="6"/>
+    </row>
+    <row r="214" spans="1:26">
+      <c r="A214" s="6">
+        <v>1041</v>
+      </c>
+      <c r="B214" s="3">
+        <v>46293.391817129603</v>
+      </c>
+      <c r="C214" s="3">
+        <v>46293.392685185201</v>
+      </c>
+      <c r="D214" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="F214" s="6">
+        <v>38442</v>
+      </c>
+      <c r="G214" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H214" s="2"/>
+      <c r="I214" s="2"/>
+      <c r="J214" s="2"/>
+      <c r="K214" s="2"/>
+      <c r="L214" s="2"/>
+      <c r="M214" s="2"/>
+      <c r="N214" s="2"/>
+      <c r="O214" s="2"/>
+      <c r="P214" s="2"/>
+      <c r="Q214" s="2"/>
+      <c r="R214" s="2"/>
+      <c r="S214" s="2"/>
+      <c r="T214" s="6">
+        <v>15</v>
+      </c>
+      <c r="U214" s="6">
+        <v>0</v>
+      </c>
+      <c r="V214" s="2"/>
+      <c r="W214" s="2"/>
+      <c r="X214" s="6"/>
+      <c r="Y214" s="6"/>
+      <c r="Z214" s="6"/>
+    </row>
+    <row r="215" spans="1:26">
+      <c r="A215" s="6">
+        <v>1042</v>
+      </c>
+      <c r="B215" s="3">
+        <v>46293.3933217593</v>
+      </c>
+      <c r="C215" s="3">
+        <v>46293.393865740698</v>
+      </c>
+      <c r="D215" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="F215" s="6">
+        <v>38475</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="2"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215" s="2"/>
+      <c r="P215" s="2"/>
+      <c r="Q215" s="2"/>
+      <c r="R215" s="2"/>
+      <c r="S215" s="2"/>
+      <c r="T215" s="6">
+        <v>13</v>
+      </c>
+      <c r="U215" s="6">
+        <v>3</v>
+      </c>
+      <c r="V215" s="2"/>
+      <c r="W215" s="2"/>
+      <c r="X215" s="6"/>
+      <c r="Y215" s="6"/>
+      <c r="Z215" s="6"/>
+    </row>
+    <row r="216" spans="1:26">
+      <c r="A216" s="6">
+        <v>1043</v>
+      </c>
+      <c r="B216" s="3">
+        <v>46293.393645833297</v>
+      </c>
+      <c r="C216" s="3">
+        <v>46293.394618055601</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F216" s="6">
+        <v>38197</v>
+      </c>
+      <c r="G216" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
+      <c r="J216" s="2"/>
+      <c r="K216" s="2"/>
+      <c r="L216" s="2"/>
+      <c r="M216" s="2"/>
+      <c r="N216" s="2"/>
+      <c r="O216" s="2"/>
+      <c r="P216" s="2"/>
+      <c r="Q216" s="2"/>
+      <c r="R216" s="2"/>
+      <c r="S216" s="2"/>
+      <c r="T216" s="6">
+        <v>16</v>
+      </c>
+      <c r="U216" s="6">
+        <v>0</v>
+      </c>
+      <c r="V216" s="2"/>
+      <c r="W216" s="2"/>
+      <c r="X216" s="6"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+    </row>
+    <row r="217" spans="1:26">
+      <c r="A217" s="6">
+        <v>1044</v>
+      </c>
+      <c r="B217" s="3">
+        <v>46293.394988425898</v>
+      </c>
+      <c r="C217" s="3">
+        <v>46293.395393518498</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="F217" s="6">
+        <v>38117</v>
+      </c>
+      <c r="G217" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
+      <c r="J217" s="2"/>
+      <c r="K217" s="2"/>
+      <c r="L217" s="2"/>
+      <c r="M217" s="2"/>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
+      <c r="P217" s="2"/>
+      <c r="Q217" s="2"/>
+      <c r="R217" s="2"/>
+      <c r="S217" s="2"/>
+      <c r="T217" s="6">
+        <v>9</v>
+      </c>
+      <c r="U217" s="6">
+        <v>0</v>
+      </c>
+      <c r="V217" s="2"/>
+      <c r="W217" s="2"/>
+      <c r="X217" s="6"/>
+      <c r="Y217" s="6"/>
+      <c r="Z217" s="6"/>
+    </row>
+    <row r="218" spans="1:26">
+      <c r="A218" s="6">
+        <v>1045</v>
+      </c>
+      <c r="B218" s="3">
+        <v>46293.397430555597</v>
+      </c>
+      <c r="C218" s="3">
+        <v>46293.398090277798</v>
+      </c>
+      <c r="D218" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="F218" s="6">
+        <v>38903</v>
+      </c>
+      <c r="G218" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
+      <c r="J218" s="2"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
+      <c r="M218" s="2"/>
+      <c r="N218" s="2"/>
+      <c r="O218" s="2"/>
+      <c r="P218" s="2"/>
+      <c r="Q218" s="2"/>
+      <c r="R218" s="2"/>
+      <c r="S218" s="2"/>
+      <c r="T218" s="6">
+        <v>15</v>
+      </c>
+      <c r="U218" s="6">
+        <v>0</v>
+      </c>
+      <c r="V218" s="2"/>
+      <c r="W218" s="2"/>
+      <c r="X218" s="6"/>
+      <c r="Y218" s="6"/>
+      <c r="Z218" s="6"/>
+    </row>
+    <row r="219" spans="1:26">
+      <c r="A219" s="6">
+        <v>1046</v>
+      </c>
+      <c r="B219" s="3">
+        <v>46293.388703703698</v>
+      </c>
+      <c r="C219" s="3">
+        <v>46293.398472222201</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F219" s="6">
+        <v>38186</v>
+      </c>
+      <c r="G219" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
+      <c r="J219" s="2"/>
+      <c r="K219" s="2"/>
+      <c r="L219" s="2"/>
+      <c r="M219" s="2"/>
+      <c r="N219" s="2"/>
+      <c r="O219" s="2"/>
+      <c r="P219" s="2"/>
+      <c r="Q219" s="2"/>
+      <c r="R219" s="2"/>
+      <c r="S219" s="2"/>
+      <c r="T219" s="6">
+        <v>10</v>
+      </c>
+      <c r="U219" s="6">
+        <v>0</v>
+      </c>
+      <c r="V219" s="2"/>
+      <c r="W219" s="2"/>
+      <c r="X219" s="6"/>
+      <c r="Y219" s="6"/>
+      <c r="Z219" s="6"/>
+    </row>
+    <row r="220" spans="1:26">
+      <c r="A220" s="6">
+        <v>1047</v>
+      </c>
+      <c r="B220" s="3">
+        <v>46293.396354166704</v>
+      </c>
+      <c r="C220" s="3">
+        <v>46293.398854166699</v>
+      </c>
+      <c r="D220" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="F220" s="6">
+        <v>38606</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2"/>
+      <c r="R220" s="2"/>
+      <c r="S220" s="2"/>
+      <c r="T220" s="6">
+        <v>16</v>
+      </c>
+      <c r="U220" s="6">
+        <v>1</v>
+      </c>
+      <c r="V220" s="2"/>
+      <c r="W220" s="2"/>
+      <c r="X220" s="6"/>
+      <c r="Y220" s="6"/>
+      <c r="Z220" s="6"/>
+    </row>
+    <row r="221" spans="1:26">
+      <c r="A221" s="6">
+        <v>1048</v>
+      </c>
+      <c r="B221" s="3">
+        <v>46293.395509259302</v>
+      </c>
+      <c r="C221" s="3">
+        <v>46293.3991087963</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F221" s="6">
+        <v>38456</v>
+      </c>
+      <c r="G221" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+      <c r="N221" s="2"/>
+      <c r="O221" s="2"/>
+      <c r="P221" s="2"/>
+      <c r="Q221" s="2"/>
+      <c r="R221" s="2"/>
+      <c r="S221" s="2"/>
+      <c r="T221" s="6">
+        <v>12</v>
+      </c>
+      <c r="U221" s="6">
+        <v>0</v>
+      </c>
+      <c r="V221" s="2"/>
+      <c r="W221" s="2"/>
+      <c r="X221" s="6"/>
+      <c r="Y221" s="6"/>
+      <c r="Z221" s="6"/>
+    </row>
+    <row r="222" spans="1:26">
+      <c r="A222" s="6">
+        <v>1049</v>
+      </c>
+      <c r="B222" s="3">
+        <v>46293.399768518502</v>
+      </c>
+      <c r="C222" s="3">
+        <v>46293.4003240741</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="F222" s="6">
+        <v>38266</v>
+      </c>
+      <c r="G222" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+      <c r="M222" s="2"/>
+      <c r="N222" s="2"/>
+      <c r="O222" s="2"/>
+      <c r="P222" s="2"/>
+      <c r="Q222" s="2"/>
+      <c r="R222" s="2"/>
+      <c r="S222" s="2"/>
+      <c r="T222" s="6">
+        <v>11</v>
+      </c>
+      <c r="U222" s="6">
+        <v>2</v>
+      </c>
+      <c r="V222" s="2"/>
+      <c r="W222" s="2"/>
+      <c r="X222" s="6"/>
+      <c r="Y222" s="6"/>
+      <c r="Z222" s="6"/>
+    </row>
+    <row r="223" spans="1:26">
+      <c r="A223" s="6">
+        <v>1050</v>
+      </c>
+      <c r="B223" s="3">
+        <v>46293.402986111098</v>
+      </c>
+      <c r="C223" s="3">
+        <v>46293.404432870397</v>
+      </c>
+      <c r="D223" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E223" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="F223" s="6">
+        <v>38770</v>
+      </c>
+      <c r="G223" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="2"/>
+      <c r="O223" s="2"/>
+      <c r="P223" s="2"/>
+      <c r="Q223" s="2"/>
+      <c r="R223" s="2"/>
+      <c r="S223" s="2"/>
+      <c r="T223" s="6">
+        <v>8</v>
+      </c>
+      <c r="U223" s="6">
+        <v>2</v>
+      </c>
+      <c r="V223" s="2"/>
+      <c r="W223" s="2"/>
+      <c r="X223" s="6"/>
+      <c r="Y223" s="6"/>
+      <c r="Z223" s="6"/>
+    </row>
+    <row r="224" spans="1:26">
+      <c r="A224" s="6">
+        <v>1051</v>
+      </c>
+      <c r="B224" s="3">
+        <v>46293.402824074103</v>
+      </c>
+      <c r="C224" s="3">
+        <v>46293.404594907399</v>
+      </c>
+      <c r="D224" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E224" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F224" s="6">
+        <v>38411</v>
+      </c>
+      <c r="G224" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H224" s="2"/>
+      <c r="I224" s="2"/>
+      <c r="J224" s="2"/>
+      <c r="K224" s="2"/>
+      <c r="L224" s="2"/>
+      <c r="M224" s="2"/>
+      <c r="N224" s="2"/>
+      <c r="O224" s="2"/>
+      <c r="P224" s="2"/>
+      <c r="Q224" s="2"/>
+      <c r="R224" s="2"/>
+      <c r="S224" s="2"/>
+      <c r="T224" s="6">
+        <v>12</v>
+      </c>
+      <c r="U224" s="6">
+        <v>5</v>
+      </c>
+      <c r="V224" s="2"/>
+      <c r="W224" s="2"/>
+      <c r="X224" s="6"/>
+      <c r="Y224" s="6"/>
+      <c r="Z224" s="6"/>
+    </row>
+    <row r="225" spans="1:26">
+      <c r="A225" s="6">
+        <v>1052</v>
+      </c>
+      <c r="B225" s="3">
+        <v>46293.4031944444</v>
+      </c>
+      <c r="C225" s="3">
+        <v>46293.404594907399</v>
+      </c>
+      <c r="D225" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F225" s="6">
+        <v>38661</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H225" s="2"/>
+      <c r="I225" s="2"/>
+      <c r="J225" s="2"/>
+      <c r="K225" s="2"/>
+      <c r="L225" s="2"/>
+      <c r="M225" s="2"/>
+      <c r="N225" s="2"/>
+      <c r="O225" s="2"/>
+      <c r="P225" s="2"/>
+      <c r="Q225" s="2"/>
+      <c r="R225" s="2"/>
+      <c r="S225" s="2"/>
+      <c r="T225" s="6">
+        <v>12</v>
+      </c>
+      <c r="U225" s="6">
+        <v>0</v>
+      </c>
+      <c r="V225" s="2"/>
+      <c r="W225" s="2"/>
+      <c r="X225" s="6"/>
+      <c r="Y225" s="6"/>
+      <c r="Z225" s="6"/>
+    </row>
+    <row r="226" spans="1:26">
+      <c r="A226" s="6">
+        <v>1053</v>
+      </c>
+      <c r="B226" s="3">
+        <v>46293.403726851902</v>
+      </c>
+      <c r="C226" s="3">
+        <v>46293.405196759297</v>
+      </c>
+      <c r="D226" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F226" s="6">
+        <v>38561</v>
+      </c>
+      <c r="G226" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H226" s="2"/>
+      <c r="I226" s="2"/>
+      <c r="J226" s="2"/>
+      <c r="K226" s="2"/>
+      <c r="L226" s="2"/>
+      <c r="M226" s="2"/>
+      <c r="N226" s="2"/>
+      <c r="O226" s="2"/>
+      <c r="P226" s="2"/>
+      <c r="Q226" s="2"/>
+      <c r="R226" s="2"/>
+      <c r="S226" s="2"/>
+      <c r="T226" s="6">
+        <v>16</v>
+      </c>
+      <c r="U226" s="6">
+        <v>0</v>
+      </c>
+      <c r="V226" s="2"/>
+      <c r="W226" s="2"/>
+      <c r="X226" s="6"/>
+      <c r="Y226" s="6"/>
+      <c r="Z226" s="6"/>
+    </row>
+    <row r="227" spans="1:26">
+      <c r="A227" s="6">
+        <v>1054</v>
+      </c>
+      <c r="B227" s="3">
+        <v>46293.405057870397</v>
+      </c>
+      <c r="C227" s="3">
+        <v>46293.405729166698</v>
+      </c>
+      <c r="D227" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="F227" s="6">
+        <v>38651</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H227" s="2"/>
+      <c r="I227" s="2"/>
+      <c r="J227" s="2"/>
+      <c r="K227" s="2"/>
+      <c r="L227" s="2"/>
+      <c r="M227" s="2"/>
+      <c r="N227" s="2"/>
+      <c r="O227" s="2"/>
+      <c r="P227" s="2"/>
+      <c r="Q227" s="2"/>
+      <c r="R227" s="2"/>
+      <c r="S227" s="2"/>
+      <c r="T227" s="6">
+        <v>13</v>
+      </c>
+      <c r="U227" s="6">
+        <v>6</v>
+      </c>
+      <c r="V227" s="2"/>
+      <c r="W227" s="2"/>
+      <c r="X227" s="6"/>
+      <c r="Y227" s="6"/>
+      <c r="Z227" s="6"/>
+    </row>
+    <row r="228" spans="1:26">
+      <c r="A228" s="6">
+        <v>1055</v>
+      </c>
+      <c r="B228" s="3">
+        <v>46293.408831018503</v>
+      </c>
+      <c r="C228" s="3">
+        <v>46293.409340277802</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F228" s="6">
+        <v>38561</v>
+      </c>
+      <c r="G228" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H228" s="2"/>
+      <c r="I228" s="2"/>
+      <c r="J228" s="2"/>
+      <c r="K228" s="2"/>
+      <c r="L228" s="2"/>
+      <c r="M228" s="2"/>
+      <c r="N228" s="2"/>
+      <c r="O228" s="2"/>
+      <c r="P228" s="2"/>
+      <c r="Q228" s="2"/>
+      <c r="R228" s="2"/>
+      <c r="S228" s="2"/>
+      <c r="T228" s="6"/>
+      <c r="U228" s="6"/>
+      <c r="V228" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="W228" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="X228" s="6"/>
+      <c r="Y228" s="6"/>
+      <c r="Z228" s="6"/>
+    </row>
+    <row r="229" spans="1:26">
+      <c r="A229" s="6">
+        <v>1056</v>
+      </c>
+      <c r="B229" s="3">
+        <v>46293.408078703702</v>
+      </c>
+      <c r="C229" s="3">
+        <v>46293.409675925897</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F229" s="6">
+        <v>38371</v>
+      </c>
+      <c r="G229" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H229" s="2"/>
+      <c r="I229" s="2"/>
+      <c r="J229" s="2"/>
+      <c r="K229" s="2"/>
+      <c r="L229" s="2"/>
+      <c r="M229" s="2"/>
+      <c r="N229" s="2"/>
+      <c r="O229" s="2"/>
+      <c r="P229" s="2"/>
+      <c r="Q229" s="2"/>
+      <c r="R229" s="2"/>
+      <c r="S229" s="2"/>
+      <c r="T229" s="6">
+        <v>25</v>
+      </c>
+      <c r="U229" s="6">
+        <v>7</v>
+      </c>
+      <c r="V229" s="2"/>
+      <c r="W229" s="2"/>
+      <c r="X229" s="6"/>
+      <c r="Y229" s="6"/>
+      <c r="Z229" s="6"/>
+    </row>
+    <row r="230" spans="1:26">
+      <c r="A230" s="6">
+        <v>1057</v>
+      </c>
+      <c r="B230" s="3">
+        <v>46293.408379629604</v>
+      </c>
+      <c r="C230" s="3">
+        <v>46293.410381944399</v>
+      </c>
+      <c r="D230" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F230" s="6">
+        <v>38992</v>
+      </c>
+      <c r="G230" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H230" s="2"/>
+      <c r="I230" s="2"/>
+      <c r="J230" s="2"/>
+      <c r="K230" s="2"/>
+      <c r="L230" s="2"/>
+      <c r="M230" s="2"/>
+      <c r="N230" s="2"/>
+      <c r="O230" s="2"/>
+      <c r="P230" s="2"/>
+      <c r="Q230" s="2"/>
+      <c r="R230" s="2"/>
+      <c r="S230" s="2"/>
+      <c r="T230" s="6">
+        <v>10</v>
+      </c>
+      <c r="U230" s="6">
+        <v>6</v>
+      </c>
+      <c r="V230" s="2"/>
+      <c r="W230" s="2"/>
+      <c r="X230" s="6"/>
+      <c r="Y230" s="6"/>
+      <c r="Z230" s="6"/>
+    </row>
+    <row r="231" spans="1:26">
+      <c r="A231" s="6">
+        <v>1058</v>
+      </c>
+      <c r="B231" s="3">
+        <v>46293.409398148098</v>
+      </c>
+      <c r="C231" s="3">
+        <v>46293.410509259302</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F231" s="6">
+        <v>38561</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H231" s="2"/>
+      <c r="I231" s="2"/>
+      <c r="J231" s="2"/>
+      <c r="K231" s="2"/>
+      <c r="L231" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="M231" s="2"/>
+      <c r="N231" s="2"/>
+      <c r="O231" s="2"/>
+      <c r="P231" s="2"/>
+      <c r="Q231" s="2"/>
+      <c r="R231" s="2"/>
+      <c r="S231" s="2"/>
+      <c r="T231" s="6"/>
+      <c r="U231" s="6"/>
+      <c r="V231" s="2"/>
+      <c r="W231" s="2"/>
+      <c r="X231" s="6"/>
+      <c r="Y231" s="6"/>
+      <c r="Z231" s="6"/>
+    </row>
+    <row r="232" spans="1:26">
+      <c r="A232" s="6">
+        <v>1059</v>
+      </c>
+      <c r="B232" s="3">
+        <v>46293.410509259302</v>
+      </c>
+      <c r="C232" s="3">
+        <v>46293.411805555603</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F232" s="6">
+        <v>43194</v>
+      </c>
+      <c r="G232" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H232" s="2"/>
+      <c r="I232" s="2"/>
+      <c r="J232" s="2"/>
+      <c r="K232" s="2"/>
+      <c r="L232" s="2"/>
+      <c r="M232" s="2"/>
+      <c r="N232" s="2"/>
+      <c r="O232" s="2"/>
+      <c r="P232" s="2"/>
+      <c r="Q232" s="2"/>
+      <c r="R232" s="2"/>
+      <c r="S232" s="2"/>
+      <c r="T232" s="6">
+        <v>5</v>
+      </c>
+      <c r="U232" s="6">
+        <v>4</v>
+      </c>
+      <c r="V232" s="2"/>
+      <c r="W232" s="2"/>
+      <c r="X232" s="6"/>
+      <c r="Y232" s="6"/>
+      <c r="Z232" s="6"/>
+    </row>
+    <row r="233" spans="1:26">
+      <c r="A233" s="6">
+        <v>1060</v>
+      </c>
+      <c r="B233" s="3">
+        <v>46293.408969907403</v>
+      </c>
+      <c r="C233" s="3">
+        <v>46293.4119907407</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F233" s="6">
+        <v>38837</v>
+      </c>
+      <c r="G233" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H233" s="2"/>
+      <c r="I233" s="2"/>
+      <c r="J233" s="2"/>
+      <c r="K233" s="2"/>
+      <c r="L233" s="2"/>
+      <c r="M233" s="2"/>
+      <c r="N233" s="2"/>
+      <c r="O233" s="2"/>
+      <c r="P233" s="2"/>
+      <c r="Q233" s="2"/>
+      <c r="R233" s="2"/>
+      <c r="S233" s="2"/>
+      <c r="T233" s="6">
+        <v>8</v>
+      </c>
+      <c r="U233" s="6">
+        <v>3</v>
+      </c>
+      <c r="V233" s="2"/>
+      <c r="W233" s="2"/>
+      <c r="X233" s="6"/>
+      <c r="Y233" s="6"/>
+      <c r="Z233" s="6"/>
+    </row>
+    <row r="234" spans="1:26">
+      <c r="A234" s="6">
+        <v>1061</v>
+      </c>
+      <c r="B234" s="3">
+        <v>46293.410636574103</v>
+      </c>
+      <c r="C234" s="3">
+        <v>46293.4121759259</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="F234" s="6">
+        <v>38561</v>
+      </c>
+      <c r="G234" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H234" s="2"/>
+      <c r="I234" s="2"/>
+      <c r="J234" s="2"/>
+      <c r="K234" s="2"/>
+      <c r="L234" s="2"/>
+      <c r="M234" s="2"/>
+      <c r="N234" s="2"/>
+      <c r="O234" s="2"/>
+      <c r="P234" s="2"/>
+      <c r="Q234" s="2"/>
+      <c r="R234" s="2"/>
+      <c r="S234" s="2"/>
+      <c r="T234" s="6"/>
+      <c r="U234" s="6"/>
+      <c r="V234" s="2"/>
+      <c r="W234" s="2"/>
+      <c r="X234" s="6">
+        <v>36</v>
+      </c>
+      <c r="Y234" s="6">
+        <v>5</v>
+      </c>
+      <c r="Z234" s="6" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="235" spans="1:26">
+      <c r="A235" s="6">
+        <v>1062</v>
+      </c>
+      <c r="B235" s="3">
+        <v>46293.407233796301</v>
+      </c>
+      <c r="C235" s="3">
+        <v>46293.412326388898</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E235" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="F235" s="6">
+        <v>43111</v>
+      </c>
+      <c r="G235" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H235" s="2"/>
+      <c r="I235" s="2"/>
+      <c r="J235" s="2"/>
+      <c r="K235" s="2"/>
+      <c r="L235" s="2"/>
+      <c r="M235" s="2"/>
+      <c r="N235" s="2"/>
+      <c r="O235" s="2"/>
+      <c r="P235" s="2"/>
+      <c r="Q235" s="2"/>
+      <c r="R235" s="2"/>
+      <c r="S235" s="2"/>
+      <c r="T235" s="6">
+        <v>11</v>
+      </c>
+      <c r="U235" s="6">
+        <v>0</v>
+      </c>
+      <c r="V235" s="2"/>
+      <c r="W235" s="2"/>
+      <c r="X235" s="6"/>
+      <c r="Y235" s="6"/>
+      <c r="Z235" s="6"/>
+    </row>
+    <row r="236" spans="1:26">
+      <c r="A236" s="6">
+        <v>1063</v>
+      </c>
+      <c r="B236" s="3">
+        <v>46293.412326388898</v>
+      </c>
+      <c r="C236" s="3">
+        <v>46293.413032407399</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E236" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F236" s="6">
+        <v>43132</v>
+      </c>
+      <c r="G236" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H236" s="2"/>
+      <c r="I236" s="2"/>
+      <c r="J236" s="2"/>
+      <c r="K236" s="2"/>
+      <c r="L236" s="2"/>
+      <c r="M236" s="2"/>
+      <c r="N236" s="2"/>
+      <c r="O236" s="2"/>
+      <c r="P236" s="2"/>
+      <c r="Q236" s="2"/>
+      <c r="R236" s="2"/>
+      <c r="S236" s="2"/>
+      <c r="T236" s="6">
+        <v>7</v>
+      </c>
+      <c r="U236" s="6">
+        <v>3</v>
+      </c>
+      <c r="V236" s="2"/>
+      <c r="W236" s="2"/>
+      <c r="X236" s="6"/>
+      <c r="Y236" s="6"/>
+      <c r="Z236" s="6"/>
+    </row>
+    <row r="237" spans="1:26">
+      <c r="A237" s="6">
+        <v>1064</v>
+      </c>
+      <c r="B237" s="3">
+        <v>46293.414502314801</v>
+      </c>
+      <c r="C237" s="3">
+        <v>46293.419016203698</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="F237" s="6">
+        <v>38527</v>
+      </c>
+      <c r="G237" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H237" s="2"/>
+      <c r="I237" s="2"/>
+      <c r="J237" s="2"/>
+      <c r="K237" s="2"/>
+      <c r="L237" s="2"/>
+      <c r="M237" s="2"/>
+      <c r="N237" s="2"/>
+      <c r="O237" s="2"/>
+      <c r="P237" s="2"/>
+      <c r="Q237" s="2"/>
+      <c r="R237" s="2"/>
+      <c r="S237" s="2"/>
+      <c r="T237" s="6">
+        <v>13</v>
+      </c>
+      <c r="U237" s="6">
+        <v>8</v>
+      </c>
+      <c r="V237" s="2"/>
+      <c r="W237" s="2"/>
+      <c r="X237" s="6"/>
+      <c r="Y237" s="6"/>
+      <c r="Z237" s="6"/>
+    </row>
+    <row r="238" spans="1:26">
+      <c r="A238" s="6">
+        <v>1065</v>
+      </c>
+      <c r="B238" s="3">
+        <v>46293.418263888903</v>
+      </c>
+      <c r="C238" s="3">
+        <v>46293.419247685197</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F238" s="6">
+        <v>38458</v>
+      </c>
+      <c r="G238" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H238" s="2"/>
+      <c r="I238" s="2"/>
+      <c r="J238" s="2"/>
+      <c r="K238" s="2"/>
+      <c r="L238" s="2"/>
+      <c r="M238" s="2"/>
+      <c r="N238" s="2"/>
+      <c r="O238" s="2"/>
+      <c r="P238" s="2"/>
+      <c r="Q238" s="2"/>
+      <c r="R238" s="2"/>
+      <c r="S238" s="2"/>
+      <c r="T238" s="6">
+        <v>13</v>
+      </c>
+      <c r="U238" s="6">
+        <v>0</v>
+      </c>
+      <c r="V238" s="2"/>
+      <c r="W238" s="2"/>
+      <c r="X238" s="6"/>
+      <c r="Y238" s="6"/>
+      <c r="Z238" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{48D7B1FB-56F5-4795-9781-3EF0608CA620}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4B293EC-7EB8-4F4E-911A-43FDB8D3FE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="892" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="399">
   <si>
     <t>Id</t>
   </si>
@@ -1224,6 +1224,18 @@
   </si>
   <si>
     <t>Starbucks El Rosario</t>
+  </si>
+  <si>
+    <t>sbmx43261@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Encuentro Tlalnepantla</t>
+  </si>
+  <si>
+    <t>SBMX38207@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Parque Lindavista Kiosko</t>
   </si>
 </sst>
 </file>
@@ -1360,8 +1372,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z238" totalsRowShown="0">
-  <autoFilter ref="A1:Z238" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z240" totalsRowShown="0">
+  <autoFilter ref="A1:Z240" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1549,7 +1561,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1065" latestEventMarker="1511">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1067" latestEventMarker="1513">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1879,7 +1891,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z238"/>
+  <dimension ref="A1:Z240"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -10069,6 +10081,98 @@
       <c r="Y238" s="6"/>
       <c r="Z238" s="6"/>
     </row>
+    <row r="239" spans="1:26">
+      <c r="A239" s="6">
+        <v>1066</v>
+      </c>
+      <c r="B239" s="3">
+        <v>46293.425289351901</v>
+      </c>
+      <c r="C239" s="3">
+        <v>46293.426087963002</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F239" s="6">
+        <v>43261</v>
+      </c>
+      <c r="G239" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H239" s="2"/>
+      <c r="I239" s="2"/>
+      <c r="J239" s="2"/>
+      <c r="K239" s="2"/>
+      <c r="L239" s="2"/>
+      <c r="M239" s="2"/>
+      <c r="N239" s="2"/>
+      <c r="O239" s="2"/>
+      <c r="P239" s="2"/>
+      <c r="Q239" s="2"/>
+      <c r="R239" s="2"/>
+      <c r="S239" s="2"/>
+      <c r="T239" s="6">
+        <v>5</v>
+      </c>
+      <c r="U239" s="6">
+        <v>6</v>
+      </c>
+      <c r="V239" s="2"/>
+      <c r="W239" s="2"/>
+      <c r="X239" s="6"/>
+      <c r="Y239" s="6"/>
+      <c r="Z239" s="6"/>
+    </row>
+    <row r="240" spans="1:26">
+      <c r="A240" s="6">
+        <v>1067</v>
+      </c>
+      <c r="B240" s="3">
+        <v>46293.426192129598</v>
+      </c>
+      <c r="C240" s="3">
+        <v>46293.426747685196</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="F240" s="6">
+        <v>38207</v>
+      </c>
+      <c r="G240" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H240" s="2"/>
+      <c r="I240" s="2"/>
+      <c r="J240" s="2"/>
+      <c r="K240" s="2"/>
+      <c r="L240" s="2"/>
+      <c r="M240" s="2"/>
+      <c r="N240" s="2"/>
+      <c r="O240" s="2"/>
+      <c r="P240" s="2"/>
+      <c r="Q240" s="2"/>
+      <c r="R240" s="2"/>
+      <c r="S240" s="2"/>
+      <c r="T240" s="6">
+        <v>8</v>
+      </c>
+      <c r="U240" s="6">
+        <v>1</v>
+      </c>
+      <c r="V240" s="2"/>
+      <c r="W240" s="2"/>
+      <c r="X240" s="6"/>
+      <c r="Y240" s="6"/>
+      <c r="Z240" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A4B293EC-7EB8-4F4E-911A-43FDB8D3FE2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFF0C411-AC91-4381-8215-3362D430CF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="898" uniqueCount="399">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="402">
   <si>
     <t>Id</t>
   </si>
@@ -1236,6 +1236,15 @@
   </si>
   <si>
     <t>Starbucks Parque Lindavista Kiosko</t>
+  </si>
+  <si>
+    <t>sbmx43195@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Parque Jardín Kiosko</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/LayOut_Distrital_Cesar_Alfonso_Castillo_Romer_Marlene%20Danaee%20Herna.jpg</t>
   </si>
 </sst>
 </file>
@@ -1372,8 +1381,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z240" totalsRowShown="0">
-  <autoFilter ref="A1:Z240" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z243" totalsRowShown="0">
+  <autoFilter ref="A1:Z243" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1561,7 +1570,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1067" latestEventMarker="1513">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1070" latestEventMarker="1516">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1891,7 +1900,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z240"/>
+  <dimension ref="A1:Z243"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -10173,6 +10182,142 @@
       <c r="Y240" s="6"/>
       <c r="Z240" s="6"/>
     </row>
+    <row r="241" spans="1:26">
+      <c r="A241" s="6">
+        <v>1068</v>
+      </c>
+      <c r="B241" s="3">
+        <v>46293.4286111111</v>
+      </c>
+      <c r="C241" s="3">
+        <v>46293.429918981499</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="F241" s="6">
+        <v>43195</v>
+      </c>
+      <c r="G241" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H241" s="2"/>
+      <c r="I241" s="2"/>
+      <c r="J241" s="2"/>
+      <c r="K241" s="2"/>
+      <c r="L241" s="2"/>
+      <c r="M241" s="2"/>
+      <c r="N241" s="2"/>
+      <c r="O241" s="2"/>
+      <c r="P241" s="2"/>
+      <c r="Q241" s="2"/>
+      <c r="R241" s="2"/>
+      <c r="S241" s="2"/>
+      <c r="T241" s="6">
+        <v>5</v>
+      </c>
+      <c r="U241" s="6">
+        <v>4</v>
+      </c>
+      <c r="V241" s="2"/>
+      <c r="W241" s="2"/>
+      <c r="X241" s="6"/>
+      <c r="Y241" s="6"/>
+      <c r="Z241" s="6"/>
+    </row>
+    <row r="242" spans="1:26">
+      <c r="A242" s="6">
+        <v>1069</v>
+      </c>
+      <c r="B242" s="3">
+        <v>46293.431342592601</v>
+      </c>
+      <c r="C242" s="3">
+        <v>46293.432002314803</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F242" s="6">
+        <v>38656</v>
+      </c>
+      <c r="G242" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H242" s="2"/>
+      <c r="I242" s="2"/>
+      <c r="J242" s="2"/>
+      <c r="K242" s="2"/>
+      <c r="L242" s="2"/>
+      <c r="M242" s="2"/>
+      <c r="N242" s="2"/>
+      <c r="O242" s="2"/>
+      <c r="P242" s="2"/>
+      <c r="Q242" s="2"/>
+      <c r="R242" s="2"/>
+      <c r="S242" s="2"/>
+      <c r="T242" s="6">
+        <v>19</v>
+      </c>
+      <c r="U242" s="6">
+        <v>4</v>
+      </c>
+      <c r="V242" s="2"/>
+      <c r="W242" s="2"/>
+      <c r="X242" s="6"/>
+      <c r="Y242" s="6"/>
+      <c r="Z242" s="6"/>
+    </row>
+    <row r="243" spans="1:26">
+      <c r="A243" s="6">
+        <v>1070</v>
+      </c>
+      <c r="B243" s="3">
+        <v>46293.431400463</v>
+      </c>
+      <c r="C243" s="3">
+        <v>46293.432129629597</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F243" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H243" s="2"/>
+      <c r="I243" s="2"/>
+      <c r="J243" s="2"/>
+      <c r="K243" s="2"/>
+      <c r="L243" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="M243" s="2"/>
+      <c r="N243" s="2"/>
+      <c r="O243" s="2"/>
+      <c r="P243" s="2"/>
+      <c r="Q243" s="2"/>
+      <c r="R243" s="2"/>
+      <c r="S243" s="2"/>
+      <c r="T243" s="6"/>
+      <c r="U243" s="6"/>
+      <c r="V243" s="2"/>
+      <c r="W243" s="2"/>
+      <c r="X243" s="6"/>
+      <c r="Y243" s="6"/>
+      <c r="Z243" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{AFF0C411-AC91-4381-8215-3362D430CF83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2457ACFD-E93B-4586-9C75-E7F16AC1F2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="908" uniqueCount="402">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="429">
   <si>
     <t>Id</t>
   </si>
@@ -1245,6 +1245,87 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/LayOut_Distrital_Cesar_Alfonso_Castillo_Romer_Marlene%20Danaee%20Herna.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38546@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Patio Claveria</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Jose%20Arturo%20Ocampo%20M.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Santa%20Tere.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Jose%20Arturo%20Ocampo%20M.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/image_Jose%20Arturo%20Ocampo%20M.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/IMG-20260917-WA0048_Laila%20America%20Mu%C3%B1oz.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/1790614206736132548087897768143_Laila%20America%20Mu%C3%B1oz.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/image_Jose%20Arturo%20Ocampo%20M.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/IMG-20260522-WA0025_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/17906143817678312607789152762485_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Jose%20Arturo%20Ocampo%20M.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/17906146642979035000396181614435_Laila%20America%20Mu%C3%B1oz.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Jose%20Arturo%20Ocampo%20M.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/LayOut_Distrital_Cesar_Alfonso_Castillo_Grand_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG_6301_Marlene%20Danaee%20Herna.jpeg</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Lay_Out%201/image_Marlene%20Danaee%20Herna.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17906154915515136307138135372529_Laila%20America%20Mu%C3%B1oz.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/IMG-20260928-WA0012_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/IMG-20260928-WA0019_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17906158855593850030471349090695_Laila%20America%20Mu%C3%B1oz.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG_6308_Marlene%20Danaee%20Herna.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17906165500448192698186520840931_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG-20260928-WA0020_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG-20260928-WA0020_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG-20260523-WA0021_Starbucks%20Hospital%20A.jpg</t>
   </si>
 </sst>
 </file>
@@ -1381,8 +1462,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z243" totalsRowShown="0">
-  <autoFilter ref="A1:Z243" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z271" totalsRowShown="0">
+  <autoFilter ref="A1:Z271" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1570,7 +1651,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1070" latestEventMarker="1516">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1098" latestEventMarker="1544">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1900,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z243"/>
+  <dimension ref="A1:Z271"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -8028,7 +8109,7 @@
       <c r="V192" s="2"/>
       <c r="W192" s="2"/>
     </row>
-    <row r="193" spans="1:26">
+    <row r="193" spans="1:23">
       <c r="A193">
         <v>1019</v>
       </c>
@@ -8067,7 +8148,7 @@
       <c r="V193" s="2"/>
       <c r="W193" s="2"/>
     </row>
-    <row r="194" spans="1:26">
+    <row r="194" spans="1:23">
       <c r="A194">
         <v>1020</v>
       </c>
@@ -8106,7 +8187,7 @@
       <c r="V194" s="2"/>
       <c r="W194" s="2"/>
     </row>
-    <row r="195" spans="1:26">
+    <row r="195" spans="1:23">
       <c r="A195">
         <v>1021</v>
       </c>
@@ -8149,7 +8230,7 @@
       <c r="V195" s="2"/>
       <c r="W195" s="2"/>
     </row>
-    <row r="196" spans="1:26">
+    <row r="196" spans="1:23">
       <c r="A196">
         <v>1022</v>
       </c>
@@ -8188,7 +8269,7 @@
       <c r="V196" s="2"/>
       <c r="W196" s="2"/>
     </row>
-    <row r="197" spans="1:26">
+    <row r="197" spans="1:23">
       <c r="A197">
         <v>1024</v>
       </c>
@@ -8231,7 +8312,7 @@
       <c r="V197" s="2"/>
       <c r="W197" s="2"/>
     </row>
-    <row r="198" spans="1:26">
+    <row r="198" spans="1:23">
       <c r="A198">
         <v>1025</v>
       </c>
@@ -8274,7 +8355,7 @@
       <c r="V198" s="2"/>
       <c r="W198" s="2"/>
     </row>
-    <row r="199" spans="1:26">
+    <row r="199" spans="1:23">
       <c r="A199">
         <v>1026</v>
       </c>
@@ -8317,7 +8398,7 @@
       <c r="V199" s="2"/>
       <c r="W199" s="2"/>
     </row>
-    <row r="200" spans="1:26">
+    <row r="200" spans="1:23">
       <c r="A200">
         <v>1027</v>
       </c>
@@ -8360,7 +8441,7 @@
       <c r="V200" s="2"/>
       <c r="W200" s="2"/>
     </row>
-    <row r="201" spans="1:26">
+    <row r="201" spans="1:23">
       <c r="A201">
         <v>1028</v>
       </c>
@@ -8403,7 +8484,7 @@
       <c r="V201" s="2"/>
       <c r="W201" s="2"/>
     </row>
-    <row r="202" spans="1:26">
+    <row r="202" spans="1:23">
       <c r="A202">
         <v>1029</v>
       </c>
@@ -8446,7 +8527,7 @@
       <c r="V202" s="2"/>
       <c r="W202" s="2"/>
     </row>
-    <row r="203" spans="1:26">
+    <row r="203" spans="1:23">
       <c r="A203">
         <v>1030</v>
       </c>
@@ -8489,7 +8570,7 @@
       <c r="V203" s="2"/>
       <c r="W203" s="2"/>
     </row>
-    <row r="204" spans="1:26">
+    <row r="204" spans="1:23">
       <c r="A204">
         <v>1031</v>
       </c>
@@ -8532,7 +8613,7 @@
       <c r="V204" s="2"/>
       <c r="W204" s="2"/>
     </row>
-    <row r="205" spans="1:26">
+    <row r="205" spans="1:23">
       <c r="A205">
         <v>1032</v>
       </c>
@@ -8575,7 +8656,7 @@
       <c r="V205" s="2"/>
       <c r="W205" s="2"/>
     </row>
-    <row r="206" spans="1:26">
+    <row r="206" spans="1:23">
       <c r="A206">
         <v>1033</v>
       </c>
@@ -8618,8 +8699,8 @@
       <c r="V206" s="2"/>
       <c r="W206" s="2"/>
     </row>
-    <row r="207" spans="1:26">
-      <c r="A207" s="6">
+    <row r="207" spans="1:23">
+      <c r="A207">
         <v>1034</v>
       </c>
       <c r="B207" s="3">
@@ -8634,7 +8715,7 @@
       <c r="E207" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F207" s="6">
+      <c r="F207">
         <v>38894</v>
       </c>
       <c r="G207" s="2" t="s">
@@ -8652,20 +8733,17 @@
       <c r="Q207" s="2"/>
       <c r="R207" s="2"/>
       <c r="S207" s="2"/>
-      <c r="T207" s="6">
+      <c r="T207">
         <v>15</v>
       </c>
-      <c r="U207" s="6">
+      <c r="U207">
         <v>0</v>
       </c>
       <c r="V207" s="2"/>
       <c r="W207" s="2"/>
-      <c r="X207" s="6"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-    </row>
-    <row r="208" spans="1:26">
-      <c r="A208" s="6">
+    </row>
+    <row r="208" spans="1:23">
+      <c r="A208">
         <v>1035</v>
       </c>
       <c r="B208" s="3">
@@ -8680,7 +8758,7 @@
       <c r="E208" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="F208" s="6">
+      <c r="F208">
         <v>43152</v>
       </c>
       <c r="G208" s="2" t="s">
@@ -8698,20 +8776,17 @@
       <c r="Q208" s="2"/>
       <c r="R208" s="2"/>
       <c r="S208" s="2"/>
-      <c r="T208" s="6">
+      <c r="T208">
         <v>8</v>
       </c>
-      <c r="U208" s="6">
+      <c r="U208">
         <v>1</v>
       </c>
       <c r="V208" s="2"/>
       <c r="W208" s="2"/>
-      <c r="X208" s="6"/>
-      <c r="Y208" s="6"/>
-      <c r="Z208" s="6"/>
-    </row>
-    <row r="209" spans="1:26">
-      <c r="A209" s="6">
+    </row>
+    <row r="209" spans="1:23">
+      <c r="A209">
         <v>1036</v>
       </c>
       <c r="B209" s="3">
@@ -8726,7 +8801,7 @@
       <c r="E209" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F209" s="6">
+      <c r="F209">
         <v>38205</v>
       </c>
       <c r="G209" s="2" t="s">
@@ -8744,20 +8819,17 @@
       <c r="Q209" s="2"/>
       <c r="R209" s="2"/>
       <c r="S209" s="2"/>
-      <c r="T209" s="6">
+      <c r="T209">
         <v>18</v>
       </c>
-      <c r="U209" s="6">
+      <c r="U209">
         <v>1</v>
       </c>
       <c r="V209" s="2"/>
       <c r="W209" s="2"/>
-      <c r="X209" s="6"/>
-      <c r="Y209" s="6"/>
-      <c r="Z209" s="6"/>
-    </row>
-    <row r="210" spans="1:26">
-      <c r="A210" s="6">
+    </row>
+    <row r="210" spans="1:23">
+      <c r="A210">
         <v>1037</v>
       </c>
       <c r="B210" s="3">
@@ -8772,7 +8844,7 @@
       <c r="E210" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F210" s="6">
+      <c r="F210">
         <v>38862</v>
       </c>
       <c r="G210" s="2" t="s">
@@ -8790,20 +8862,17 @@
       <c r="Q210" s="2"/>
       <c r="R210" s="2"/>
       <c r="S210" s="2"/>
-      <c r="T210" s="6">
+      <c r="T210">
         <v>17</v>
       </c>
-      <c r="U210" s="6">
+      <c r="U210">
         <v>0</v>
       </c>
       <c r="V210" s="2"/>
       <c r="W210" s="2"/>
-      <c r="X210" s="6"/>
-      <c r="Y210" s="6"/>
-      <c r="Z210" s="6"/>
-    </row>
-    <row r="211" spans="1:26">
-      <c r="A211" s="6">
+    </row>
+    <row r="211" spans="1:23">
+      <c r="A211">
         <v>1038</v>
       </c>
       <c r="B211" s="3">
@@ -8818,7 +8887,7 @@
       <c r="E211" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="F211" s="6">
+      <c r="F211">
         <v>38590</v>
       </c>
       <c r="G211" s="2" t="s">
@@ -8836,20 +8905,17 @@
       <c r="Q211" s="2"/>
       <c r="R211" s="2"/>
       <c r="S211" s="2"/>
-      <c r="T211" s="6">
+      <c r="T211">
         <v>13</v>
       </c>
-      <c r="U211" s="6">
+      <c r="U211">
         <v>1</v>
       </c>
       <c r="V211" s="2"/>
       <c r="W211" s="2"/>
-      <c r="X211" s="6"/>
-      <c r="Y211" s="6"/>
-      <c r="Z211" s="6"/>
-    </row>
-    <row r="212" spans="1:26">
-      <c r="A212" s="6">
+    </row>
+    <row r="212" spans="1:23">
+      <c r="A212">
         <v>1039</v>
       </c>
       <c r="B212" s="3">
@@ -8864,7 +8930,7 @@
       <c r="E212" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="F212" s="6">
+      <c r="F212">
         <v>38695</v>
       </c>
       <c r="G212" s="2" t="s">
@@ -8882,20 +8948,17 @@
       <c r="Q212" s="2"/>
       <c r="R212" s="2"/>
       <c r="S212" s="2"/>
-      <c r="T212" s="6">
+      <c r="T212">
         <v>12</v>
       </c>
-      <c r="U212" s="6">
+      <c r="U212">
         <v>6</v>
       </c>
       <c r="V212" s="2"/>
       <c r="W212" s="2"/>
-      <c r="X212" s="6"/>
-      <c r="Y212" s="6"/>
-      <c r="Z212" s="6"/>
-    </row>
-    <row r="213" spans="1:26">
-      <c r="A213" s="6">
+    </row>
+    <row r="213" spans="1:23">
+      <c r="A213">
         <v>1040</v>
       </c>
       <c r="B213" s="3">
@@ -8910,7 +8973,7 @@
       <c r="E213" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="F213" s="6">
+      <c r="F213">
         <v>38604</v>
       </c>
       <c r="G213" s="2" t="s">
@@ -8928,20 +8991,17 @@
       <c r="Q213" s="2"/>
       <c r="R213" s="2"/>
       <c r="S213" s="2"/>
-      <c r="T213" s="6">
+      <c r="T213">
         <v>15</v>
       </c>
-      <c r="U213" s="6">
+      <c r="U213">
         <v>0</v>
       </c>
       <c r="V213" s="2"/>
       <c r="W213" s="2"/>
-      <c r="X213" s="6"/>
-      <c r="Y213" s="6"/>
-      <c r="Z213" s="6"/>
-    </row>
-    <row r="214" spans="1:26">
-      <c r="A214" s="6">
+    </row>
+    <row r="214" spans="1:23">
+      <c r="A214">
         <v>1041</v>
       </c>
       <c r="B214" s="3">
@@ -8956,7 +9016,7 @@
       <c r="E214" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F214" s="6">
+      <c r="F214">
         <v>38442</v>
       </c>
       <c r="G214" s="2" t="s">
@@ -8974,20 +9034,17 @@
       <c r="Q214" s="2"/>
       <c r="R214" s="2"/>
       <c r="S214" s="2"/>
-      <c r="T214" s="6">
+      <c r="T214">
         <v>15</v>
       </c>
-      <c r="U214" s="6">
+      <c r="U214">
         <v>0</v>
       </c>
       <c r="V214" s="2"/>
       <c r="W214" s="2"/>
-      <c r="X214" s="6"/>
-      <c r="Y214" s="6"/>
-      <c r="Z214" s="6"/>
-    </row>
-    <row r="215" spans="1:26">
-      <c r="A215" s="6">
+    </row>
+    <row r="215" spans="1:23">
+      <c r="A215">
         <v>1042</v>
       </c>
       <c r="B215" s="3">
@@ -9002,7 +9059,7 @@
       <c r="E215" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F215" s="6">
+      <c r="F215">
         <v>38475</v>
       </c>
       <c r="G215" s="2" t="s">
@@ -9020,20 +9077,17 @@
       <c r="Q215" s="2"/>
       <c r="R215" s="2"/>
       <c r="S215" s="2"/>
-      <c r="T215" s="6">
+      <c r="T215">
         <v>13</v>
       </c>
-      <c r="U215" s="6">
+      <c r="U215">
         <v>3</v>
       </c>
       <c r="V215" s="2"/>
       <c r="W215" s="2"/>
-      <c r="X215" s="6"/>
-      <c r="Y215" s="6"/>
-      <c r="Z215" s="6"/>
-    </row>
-    <row r="216" spans="1:26">
-      <c r="A216" s="6">
+    </row>
+    <row r="216" spans="1:23">
+      <c r="A216">
         <v>1043</v>
       </c>
       <c r="B216" s="3">
@@ -9048,7 +9102,7 @@
       <c r="E216" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F216" s="6">
+      <c r="F216">
         <v>38197</v>
       </c>
       <c r="G216" s="2" t="s">
@@ -9066,20 +9120,17 @@
       <c r="Q216" s="2"/>
       <c r="R216" s="2"/>
       <c r="S216" s="2"/>
-      <c r="T216" s="6">
+      <c r="T216">
         <v>16</v>
       </c>
-      <c r="U216" s="6">
+      <c r="U216">
         <v>0</v>
       </c>
       <c r="V216" s="2"/>
       <c r="W216" s="2"/>
-      <c r="X216" s="6"/>
-      <c r="Y216" s="6"/>
-      <c r="Z216" s="6"/>
-    </row>
-    <row r="217" spans="1:26">
-      <c r="A217" s="6">
+    </row>
+    <row r="217" spans="1:23">
+      <c r="A217">
         <v>1044</v>
       </c>
       <c r="B217" s="3">
@@ -9094,7 +9145,7 @@
       <c r="E217" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F217" s="6">
+      <c r="F217">
         <v>38117</v>
       </c>
       <c r="G217" s="2" t="s">
@@ -9112,20 +9163,17 @@
       <c r="Q217" s="2"/>
       <c r="R217" s="2"/>
       <c r="S217" s="2"/>
-      <c r="T217" s="6">
+      <c r="T217">
         <v>9</v>
       </c>
-      <c r="U217" s="6">
+      <c r="U217">
         <v>0</v>
       </c>
       <c r="V217" s="2"/>
       <c r="W217" s="2"/>
-      <c r="X217" s="6"/>
-      <c r="Y217" s="6"/>
-      <c r="Z217" s="6"/>
-    </row>
-    <row r="218" spans="1:26">
-      <c r="A218" s="6">
+    </row>
+    <row r="218" spans="1:23">
+      <c r="A218">
         <v>1045</v>
       </c>
       <c r="B218" s="3">
@@ -9140,7 +9188,7 @@
       <c r="E218" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="F218" s="6">
+      <c r="F218">
         <v>38903</v>
       </c>
       <c r="G218" s="2" t="s">
@@ -9158,20 +9206,17 @@
       <c r="Q218" s="2"/>
       <c r="R218" s="2"/>
       <c r="S218" s="2"/>
-      <c r="T218" s="6">
+      <c r="T218">
         <v>15</v>
       </c>
-      <c r="U218" s="6">
+      <c r="U218">
         <v>0</v>
       </c>
       <c r="V218" s="2"/>
       <c r="W218" s="2"/>
-      <c r="X218" s="6"/>
-      <c r="Y218" s="6"/>
-      <c r="Z218" s="6"/>
-    </row>
-    <row r="219" spans="1:26">
-      <c r="A219" s="6">
+    </row>
+    <row r="219" spans="1:23">
+      <c r="A219">
         <v>1046</v>
       </c>
       <c r="B219" s="3">
@@ -9186,7 +9231,7 @@
       <c r="E219" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="F219" s="6">
+      <c r="F219">
         <v>38186</v>
       </c>
       <c r="G219" s="2" t="s">
@@ -9204,20 +9249,17 @@
       <c r="Q219" s="2"/>
       <c r="R219" s="2"/>
       <c r="S219" s="2"/>
-      <c r="T219" s="6">
+      <c r="T219">
         <v>10</v>
       </c>
-      <c r="U219" s="6">
+      <c r="U219">
         <v>0</v>
       </c>
       <c r="V219" s="2"/>
       <c r="W219" s="2"/>
-      <c r="X219" s="6"/>
-      <c r="Y219" s="6"/>
-      <c r="Z219" s="6"/>
-    </row>
-    <row r="220" spans="1:26">
-      <c r="A220" s="6">
+    </row>
+    <row r="220" spans="1:23">
+      <c r="A220">
         <v>1047</v>
       </c>
       <c r="B220" s="3">
@@ -9232,7 +9274,7 @@
       <c r="E220" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F220" s="6">
+      <c r="F220">
         <v>38606</v>
       </c>
       <c r="G220" s="2" t="s">
@@ -9250,20 +9292,17 @@
       <c r="Q220" s="2"/>
       <c r="R220" s="2"/>
       <c r="S220" s="2"/>
-      <c r="T220" s="6">
+      <c r="T220">
         <v>16</v>
       </c>
-      <c r="U220" s="6">
+      <c r="U220">
         <v>1</v>
       </c>
       <c r="V220" s="2"/>
       <c r="W220" s="2"/>
-      <c r="X220" s="6"/>
-      <c r="Y220" s="6"/>
-      <c r="Z220" s="6"/>
-    </row>
-    <row r="221" spans="1:26">
-      <c r="A221" s="6">
+    </row>
+    <row r="221" spans="1:23">
+      <c r="A221">
         <v>1048</v>
       </c>
       <c r="B221" s="3">
@@ -9278,7 +9317,7 @@
       <c r="E221" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F221" s="6">
+      <c r="F221">
         <v>38456</v>
       </c>
       <c r="G221" s="2" t="s">
@@ -9296,20 +9335,17 @@
       <c r="Q221" s="2"/>
       <c r="R221" s="2"/>
       <c r="S221" s="2"/>
-      <c r="T221" s="6">
+      <c r="T221">
         <v>12</v>
       </c>
-      <c r="U221" s="6">
+      <c r="U221">
         <v>0</v>
       </c>
       <c r="V221" s="2"/>
       <c r="W221" s="2"/>
-      <c r="X221" s="6"/>
-      <c r="Y221" s="6"/>
-      <c r="Z221" s="6"/>
-    </row>
-    <row r="222" spans="1:26">
-      <c r="A222" s="6">
+    </row>
+    <row r="222" spans="1:23">
+      <c r="A222">
         <v>1049</v>
       </c>
       <c r="B222" s="3">
@@ -9324,7 +9360,7 @@
       <c r="E222" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="F222" s="6">
+      <c r="F222">
         <v>38266</v>
       </c>
       <c r="G222" s="2" t="s">
@@ -9342,20 +9378,17 @@
       <c r="Q222" s="2"/>
       <c r="R222" s="2"/>
       <c r="S222" s="2"/>
-      <c r="T222" s="6">
+      <c r="T222">
         <v>11</v>
       </c>
-      <c r="U222" s="6">
+      <c r="U222">
         <v>2</v>
       </c>
       <c r="V222" s="2"/>
       <c r="W222" s="2"/>
-      <c r="X222" s="6"/>
-      <c r="Y222" s="6"/>
-      <c r="Z222" s="6"/>
-    </row>
-    <row r="223" spans="1:26">
-      <c r="A223" s="6">
+    </row>
+    <row r="223" spans="1:23">
+      <c r="A223">
         <v>1050</v>
       </c>
       <c r="B223" s="3">
@@ -9370,7 +9403,7 @@
       <c r="E223" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="F223" s="6">
+      <c r="F223">
         <v>38770</v>
       </c>
       <c r="G223" s="2" t="s">
@@ -9388,20 +9421,17 @@
       <c r="Q223" s="2"/>
       <c r="R223" s="2"/>
       <c r="S223" s="2"/>
-      <c r="T223" s="6">
+      <c r="T223">
         <v>8</v>
       </c>
-      <c r="U223" s="6">
+      <c r="U223">
         <v>2</v>
       </c>
       <c r="V223" s="2"/>
       <c r="W223" s="2"/>
-      <c r="X223" s="6"/>
-      <c r="Y223" s="6"/>
-      <c r="Z223" s="6"/>
-    </row>
-    <row r="224" spans="1:26">
-      <c r="A224" s="6">
+    </row>
+    <row r="224" spans="1:23">
+      <c r="A224">
         <v>1051</v>
       </c>
       <c r="B224" s="3">
@@ -9416,7 +9446,7 @@
       <c r="E224" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F224" s="6">
+      <c r="F224">
         <v>38411</v>
       </c>
       <c r="G224" s="2" t="s">
@@ -9434,20 +9464,17 @@
       <c r="Q224" s="2"/>
       <c r="R224" s="2"/>
       <c r="S224" s="2"/>
-      <c r="T224" s="6">
+      <c r="T224">
         <v>12</v>
       </c>
-      <c r="U224" s="6">
+      <c r="U224">
         <v>5</v>
       </c>
       <c r="V224" s="2"/>
       <c r="W224" s="2"/>
-      <c r="X224" s="6"/>
-      <c r="Y224" s="6"/>
-      <c r="Z224" s="6"/>
     </row>
     <row r="225" spans="1:26">
-      <c r="A225" s="6">
+      <c r="A225">
         <v>1052</v>
       </c>
       <c r="B225" s="3">
@@ -9462,7 +9489,7 @@
       <c r="E225" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F225" s="6">
+      <c r="F225">
         <v>38661</v>
       </c>
       <c r="G225" s="2" t="s">
@@ -9480,20 +9507,17 @@
       <c r="Q225" s="2"/>
       <c r="R225" s="2"/>
       <c r="S225" s="2"/>
-      <c r="T225" s="6">
+      <c r="T225">
         <v>12</v>
       </c>
-      <c r="U225" s="6">
+      <c r="U225">
         <v>0</v>
       </c>
       <c r="V225" s="2"/>
       <c r="W225" s="2"/>
-      <c r="X225" s="6"/>
-      <c r="Y225" s="6"/>
-      <c r="Z225" s="6"/>
     </row>
     <row r="226" spans="1:26">
-      <c r="A226" s="6">
+      <c r="A226">
         <v>1053</v>
       </c>
       <c r="B226" s="3">
@@ -9508,7 +9532,7 @@
       <c r="E226" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F226" s="6">
+      <c r="F226">
         <v>38561</v>
       </c>
       <c r="G226" s="2" t="s">
@@ -9526,20 +9550,17 @@
       <c r="Q226" s="2"/>
       <c r="R226" s="2"/>
       <c r="S226" s="2"/>
-      <c r="T226" s="6">
+      <c r="T226">
         <v>16</v>
       </c>
-      <c r="U226" s="6">
+      <c r="U226">
         <v>0</v>
       </c>
       <c r="V226" s="2"/>
       <c r="W226" s="2"/>
-      <c r="X226" s="6"/>
-      <c r="Y226" s="6"/>
-      <c r="Z226" s="6"/>
     </row>
     <row r="227" spans="1:26">
-      <c r="A227" s="6">
+      <c r="A227">
         <v>1054</v>
       </c>
       <c r="B227" s="3">
@@ -9554,7 +9575,7 @@
       <c r="E227" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="F227" s="6">
+      <c r="F227">
         <v>38651</v>
       </c>
       <c r="G227" s="2" t="s">
@@ -9572,20 +9593,17 @@
       <c r="Q227" s="2"/>
       <c r="R227" s="2"/>
       <c r="S227" s="2"/>
-      <c r="T227" s="6">
+      <c r="T227">
         <v>13</v>
       </c>
-      <c r="U227" s="6">
+      <c r="U227">
         <v>6</v>
       </c>
       <c r="V227" s="2"/>
       <c r="W227" s="2"/>
-      <c r="X227" s="6"/>
-      <c r="Y227" s="6"/>
-      <c r="Z227" s="6"/>
     </row>
     <row r="228" spans="1:26">
-      <c r="A228" s="6">
+      <c r="A228">
         <v>1055</v>
       </c>
       <c r="B228" s="3">
@@ -9600,7 +9618,7 @@
       <c r="E228" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F228" s="6">
+      <c r="F228">
         <v>38561</v>
       </c>
       <c r="G228" s="2" t="s">
@@ -9618,20 +9636,15 @@
       <c r="Q228" s="2"/>
       <c r="R228" s="2"/>
       <c r="S228" s="2"/>
-      <c r="T228" s="6"/>
-      <c r="U228" s="6"/>
       <c r="V228" s="2" t="s">
         <v>376</v>
       </c>
       <c r="W228" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="X228" s="6"/>
-      <c r="Y228" s="6"/>
-      <c r="Z228" s="6"/>
     </row>
     <row r="229" spans="1:26">
-      <c r="A229" s="6">
+      <c r="A229">
         <v>1056</v>
       </c>
       <c r="B229" s="3">
@@ -9646,7 +9659,7 @@
       <c r="E229" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="F229" s="6">
+      <c r="F229">
         <v>38371</v>
       </c>
       <c r="G229" s="2" t="s">
@@ -9664,20 +9677,17 @@
       <c r="Q229" s="2"/>
       <c r="R229" s="2"/>
       <c r="S229" s="2"/>
-      <c r="T229" s="6">
+      <c r="T229">
         <v>25</v>
       </c>
-      <c r="U229" s="6">
+      <c r="U229">
         <v>7</v>
       </c>
       <c r="V229" s="2"/>
       <c r="W229" s="2"/>
-      <c r="X229" s="6"/>
-      <c r="Y229" s="6"/>
-      <c r="Z229" s="6"/>
     </row>
     <row r="230" spans="1:26">
-      <c r="A230" s="6">
+      <c r="A230">
         <v>1057</v>
       </c>
       <c r="B230" s="3">
@@ -9692,7 +9702,7 @@
       <c r="E230" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="F230" s="6">
+      <c r="F230">
         <v>38992</v>
       </c>
       <c r="G230" s="2" t="s">
@@ -9710,20 +9720,17 @@
       <c r="Q230" s="2"/>
       <c r="R230" s="2"/>
       <c r="S230" s="2"/>
-      <c r="T230" s="6">
+      <c r="T230">
         <v>10</v>
       </c>
-      <c r="U230" s="6">
+      <c r="U230">
         <v>6</v>
       </c>
       <c r="V230" s="2"/>
       <c r="W230" s="2"/>
-      <c r="X230" s="6"/>
-      <c r="Y230" s="6"/>
-      <c r="Z230" s="6"/>
     </row>
     <row r="231" spans="1:26">
-      <c r="A231" s="6">
+      <c r="A231">
         <v>1058</v>
       </c>
       <c r="B231" s="3">
@@ -9738,7 +9745,7 @@
       <c r="E231" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F231" s="6">
+      <c r="F231">
         <v>38561</v>
       </c>
       <c r="G231" s="2" t="s">
@@ -9758,16 +9765,11 @@
       <c r="Q231" s="2"/>
       <c r="R231" s="2"/>
       <c r="S231" s="2"/>
-      <c r="T231" s="6"/>
-      <c r="U231" s="6"/>
       <c r="V231" s="2"/>
       <c r="W231" s="2"/>
-      <c r="X231" s="6"/>
-      <c r="Y231" s="6"/>
-      <c r="Z231" s="6"/>
     </row>
     <row r="232" spans="1:26">
-      <c r="A232" s="6">
+      <c r="A232">
         <v>1059</v>
       </c>
       <c r="B232" s="3">
@@ -9782,7 +9784,7 @@
       <c r="E232" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="F232" s="6">
+      <c r="F232">
         <v>43194</v>
       </c>
       <c r="G232" s="2" t="s">
@@ -9800,20 +9802,17 @@
       <c r="Q232" s="2"/>
       <c r="R232" s="2"/>
       <c r="S232" s="2"/>
-      <c r="T232" s="6">
+      <c r="T232">
         <v>5</v>
       </c>
-      <c r="U232" s="6">
+      <c r="U232">
         <v>4</v>
       </c>
       <c r="V232" s="2"/>
       <c r="W232" s="2"/>
-      <c r="X232" s="6"/>
-      <c r="Y232" s="6"/>
-      <c r="Z232" s="6"/>
     </row>
     <row r="233" spans="1:26">
-      <c r="A233" s="6">
+      <c r="A233">
         <v>1060</v>
       </c>
       <c r="B233" s="3">
@@ -9828,7 +9827,7 @@
       <c r="E233" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="F233" s="6">
+      <c r="F233">
         <v>38837</v>
       </c>
       <c r="G233" s="2" t="s">
@@ -9846,20 +9845,17 @@
       <c r="Q233" s="2"/>
       <c r="R233" s="2"/>
       <c r="S233" s="2"/>
-      <c r="T233" s="6">
+      <c r="T233">
         <v>8</v>
       </c>
-      <c r="U233" s="6">
+      <c r="U233">
         <v>3</v>
       </c>
       <c r="V233" s="2"/>
       <c r="W233" s="2"/>
-      <c r="X233" s="6"/>
-      <c r="Y233" s="6"/>
-      <c r="Z233" s="6"/>
     </row>
     <row r="234" spans="1:26">
-      <c r="A234" s="6">
+      <c r="A234">
         <v>1061</v>
       </c>
       <c r="B234" s="3">
@@ -9874,7 +9870,7 @@
       <c r="E234" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="F234" s="6">
+      <c r="F234">
         <v>38561</v>
       </c>
       <c r="G234" s="2" t="s">
@@ -9892,22 +9888,20 @@
       <c r="Q234" s="2"/>
       <c r="R234" s="2"/>
       <c r="S234" s="2"/>
-      <c r="T234" s="6"/>
-      <c r="U234" s="6"/>
       <c r="V234" s="2"/>
       <c r="W234" s="2"/>
-      <c r="X234" s="6">
+      <c r="X234">
         <v>36</v>
       </c>
-      <c r="Y234" s="6">
+      <c r="Y234">
         <v>5</v>
       </c>
-      <c r="Z234" s="6" t="s">
+      <c r="Z234" t="s">
         <v>388</v>
       </c>
     </row>
     <row r="235" spans="1:26">
-      <c r="A235" s="6">
+      <c r="A235">
         <v>1062</v>
       </c>
       <c r="B235" s="3">
@@ -9922,7 +9916,7 @@
       <c r="E235" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="F235" s="6">
+      <c r="F235">
         <v>43111</v>
       </c>
       <c r="G235" s="2" t="s">
@@ -9940,20 +9934,17 @@
       <c r="Q235" s="2"/>
       <c r="R235" s="2"/>
       <c r="S235" s="2"/>
-      <c r="T235" s="6">
+      <c r="T235">
         <v>11</v>
       </c>
-      <c r="U235" s="6">
+      <c r="U235">
         <v>0</v>
       </c>
       <c r="V235" s="2"/>
       <c r="W235" s="2"/>
-      <c r="X235" s="6"/>
-      <c r="Y235" s="6"/>
-      <c r="Z235" s="6"/>
     </row>
     <row r="236" spans="1:26">
-      <c r="A236" s="6">
+      <c r="A236">
         <v>1063</v>
       </c>
       <c r="B236" s="3">
@@ -9968,7 +9959,7 @@
       <c r="E236" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="F236" s="6">
+      <c r="F236">
         <v>43132</v>
       </c>
       <c r="G236" s="2" t="s">
@@ -9986,20 +9977,17 @@
       <c r="Q236" s="2"/>
       <c r="R236" s="2"/>
       <c r="S236" s="2"/>
-      <c r="T236" s="6">
+      <c r="T236">
         <v>7</v>
       </c>
-      <c r="U236" s="6">
+      <c r="U236">
         <v>3</v>
       </c>
       <c r="V236" s="2"/>
       <c r="W236" s="2"/>
-      <c r="X236" s="6"/>
-      <c r="Y236" s="6"/>
-      <c r="Z236" s="6"/>
     </row>
     <row r="237" spans="1:26">
-      <c r="A237" s="6">
+      <c r="A237">
         <v>1064</v>
       </c>
       <c r="B237" s="3">
@@ -10014,7 +10002,7 @@
       <c r="E237" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="F237" s="6">
+      <c r="F237">
         <v>38527</v>
       </c>
       <c r="G237" s="2" t="s">
@@ -10032,20 +10020,17 @@
       <c r="Q237" s="2"/>
       <c r="R237" s="2"/>
       <c r="S237" s="2"/>
-      <c r="T237" s="6">
+      <c r="T237">
         <v>13</v>
       </c>
-      <c r="U237" s="6">
+      <c r="U237">
         <v>8</v>
       </c>
       <c r="V237" s="2"/>
       <c r="W237" s="2"/>
-      <c r="X237" s="6"/>
-      <c r="Y237" s="6"/>
-      <c r="Z237" s="6"/>
     </row>
     <row r="238" spans="1:26">
-      <c r="A238" s="6">
+      <c r="A238">
         <v>1065</v>
       </c>
       <c r="B238" s="3">
@@ -10060,7 +10045,7 @@
       <c r="E238" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="F238" s="6">
+      <c r="F238">
         <v>38458</v>
       </c>
       <c r="G238" s="2" t="s">
@@ -10078,20 +10063,17 @@
       <c r="Q238" s="2"/>
       <c r="R238" s="2"/>
       <c r="S238" s="2"/>
-      <c r="T238" s="6">
+      <c r="T238">
         <v>13</v>
       </c>
-      <c r="U238" s="6">
+      <c r="U238">
         <v>0</v>
       </c>
       <c r="V238" s="2"/>
       <c r="W238" s="2"/>
-      <c r="X238" s="6"/>
-      <c r="Y238" s="6"/>
-      <c r="Z238" s="6"/>
     </row>
     <row r="239" spans="1:26">
-      <c r="A239" s="6">
+      <c r="A239">
         <v>1066</v>
       </c>
       <c r="B239" s="3">
@@ -10106,7 +10088,7 @@
       <c r="E239" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="F239" s="6">
+      <c r="F239">
         <v>43261</v>
       </c>
       <c r="G239" s="2" t="s">
@@ -10124,20 +10106,17 @@
       <c r="Q239" s="2"/>
       <c r="R239" s="2"/>
       <c r="S239" s="2"/>
-      <c r="T239" s="6">
+      <c r="T239">
         <v>5</v>
       </c>
-      <c r="U239" s="6">
+      <c r="U239">
         <v>6</v>
       </c>
       <c r="V239" s="2"/>
       <c r="W239" s="2"/>
-      <c r="X239" s="6"/>
-      <c r="Y239" s="6"/>
-      <c r="Z239" s="6"/>
     </row>
     <row r="240" spans="1:26">
-      <c r="A240" s="6">
+      <c r="A240">
         <v>1067</v>
       </c>
       <c r="B240" s="3">
@@ -10152,7 +10131,7 @@
       <c r="E240" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="F240" s="6">
+      <c r="F240">
         <v>38207</v>
       </c>
       <c r="G240" s="2" t="s">
@@ -10170,20 +10149,17 @@
       <c r="Q240" s="2"/>
       <c r="R240" s="2"/>
       <c r="S240" s="2"/>
-      <c r="T240" s="6">
+      <c r="T240">
         <v>8</v>
       </c>
-      <c r="U240" s="6">
+      <c r="U240">
         <v>1</v>
       </c>
       <c r="V240" s="2"/>
       <c r="W240" s="2"/>
-      <c r="X240" s="6"/>
-      <c r="Y240" s="6"/>
-      <c r="Z240" s="6"/>
     </row>
     <row r="241" spans="1:26">
-      <c r="A241" s="6">
+      <c r="A241">
         <v>1068</v>
       </c>
       <c r="B241" s="3">
@@ -10198,7 +10174,7 @@
       <c r="E241" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="F241" s="6">
+      <c r="F241">
         <v>43195</v>
       </c>
       <c r="G241" s="2" t="s">
@@ -10216,20 +10192,17 @@
       <c r="Q241" s="2"/>
       <c r="R241" s="2"/>
       <c r="S241" s="2"/>
-      <c r="T241" s="6">
+      <c r="T241">
         <v>5</v>
       </c>
-      <c r="U241" s="6">
+      <c r="U241">
         <v>4</v>
       </c>
       <c r="V241" s="2"/>
       <c r="W241" s="2"/>
-      <c r="X241" s="6"/>
-      <c r="Y241" s="6"/>
-      <c r="Z241" s="6"/>
     </row>
     <row r="242" spans="1:26">
-      <c r="A242" s="6">
+      <c r="A242">
         <v>1069</v>
       </c>
       <c r="B242" s="3">
@@ -10244,7 +10217,7 @@
       <c r="E242" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="F242" s="6">
+      <c r="F242">
         <v>38656</v>
       </c>
       <c r="G242" s="2" t="s">
@@ -10262,20 +10235,17 @@
       <c r="Q242" s="2"/>
       <c r="R242" s="2"/>
       <c r="S242" s="2"/>
-      <c r="T242" s="6">
+      <c r="T242">
         <v>19</v>
       </c>
-      <c r="U242" s="6">
+      <c r="U242">
         <v>4</v>
       </c>
       <c r="V242" s="2"/>
       <c r="W242" s="2"/>
-      <c r="X242" s="6"/>
-      <c r="Y242" s="6"/>
-      <c r="Z242" s="6"/>
     </row>
     <row r="243" spans="1:26">
-      <c r="A243" s="6">
+      <c r="A243">
         <v>1070</v>
       </c>
       <c r="B243" s="3">
@@ -10290,7 +10260,7 @@
       <c r="E243" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F243" s="6">
+      <c r="F243">
         <v>38129</v>
       </c>
       <c r="G243" s="2" t="s">
@@ -10310,13 +10280,1216 @@
       <c r="Q243" s="2"/>
       <c r="R243" s="2"/>
       <c r="S243" s="2"/>
-      <c r="T243" s="6"/>
-      <c r="U243" s="6"/>
       <c r="V243" s="2"/>
       <c r="W243" s="2"/>
-      <c r="X243" s="6"/>
-      <c r="Y243" s="6"/>
-      <c r="Z243" s="6"/>
+    </row>
+    <row r="244" spans="1:26">
+      <c r="A244">
+        <v>1071</v>
+      </c>
+      <c r="B244" s="3">
+        <v>46293.437268518501</v>
+      </c>
+      <c r="C244" s="3">
+        <v>46293.437835648103</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F244">
+        <v>38427</v>
+      </c>
+      <c r="G244" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H244" s="2"/>
+      <c r="I244" s="2"/>
+      <c r="J244" s="2"/>
+      <c r="K244" s="2"/>
+      <c r="L244" s="2"/>
+      <c r="M244" s="2"/>
+      <c r="N244" s="2"/>
+      <c r="O244" s="2"/>
+      <c r="P244" s="2"/>
+      <c r="Q244" s="2"/>
+      <c r="R244" s="2"/>
+      <c r="S244" s="2"/>
+      <c r="T244">
+        <v>15</v>
+      </c>
+      <c r="U244">
+        <v>4</v>
+      </c>
+      <c r="V244" s="2"/>
+      <c r="W244" s="2"/>
+    </row>
+    <row r="245" spans="1:26">
+      <c r="A245">
+        <v>1072</v>
+      </c>
+      <c r="B245" s="3">
+        <v>46293.4211111111</v>
+      </c>
+      <c r="C245" s="3">
+        <v>46293.437881944403</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F245">
+        <v>38546</v>
+      </c>
+      <c r="G245" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H245" s="2"/>
+      <c r="I245" s="2"/>
+      <c r="J245" s="2"/>
+      <c r="K245" s="2"/>
+      <c r="L245" s="2"/>
+      <c r="M245" s="2"/>
+      <c r="N245" s="2"/>
+      <c r="O245" s="2"/>
+      <c r="P245" s="2"/>
+      <c r="Q245" s="2"/>
+      <c r="R245" s="2"/>
+      <c r="S245" s="2"/>
+      <c r="T245">
+        <v>8</v>
+      </c>
+      <c r="U245">
+        <v>9</v>
+      </c>
+      <c r="V245" s="2"/>
+      <c r="W245" s="2"/>
+    </row>
+    <row r="246" spans="1:26">
+      <c r="A246">
+        <v>1073</v>
+      </c>
+      <c r="B246" s="3">
+        <v>46293.446701388901</v>
+      </c>
+      <c r="C246" s="3">
+        <v>46293.448807870402</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F246">
+        <v>38428</v>
+      </c>
+      <c r="G246" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H246" s="2"/>
+      <c r="I246" s="2"/>
+      <c r="J246" s="2"/>
+      <c r="K246" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="L246" s="2"/>
+      <c r="M246" s="2"/>
+      <c r="N246" s="2"/>
+      <c r="O246" s="2"/>
+      <c r="P246" s="2"/>
+      <c r="Q246" s="2"/>
+      <c r="R246" s="2"/>
+      <c r="S246" s="2"/>
+      <c r="V246" s="2"/>
+      <c r="W246" s="2"/>
+    </row>
+    <row r="247" spans="1:26">
+      <c r="A247">
+        <v>1074</v>
+      </c>
+      <c r="B247" s="3">
+        <v>46293.449097222197</v>
+      </c>
+      <c r="C247" s="3">
+        <v>46293.449340277803</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F247">
+        <v>38428</v>
+      </c>
+      <c r="G247" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H247" s="2"/>
+      <c r="I247" s="2"/>
+      <c r="J247" s="2"/>
+      <c r="K247" s="2"/>
+      <c r="L247" s="2"/>
+      <c r="M247" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N247" s="2"/>
+      <c r="O247" s="2"/>
+      <c r="P247" s="2"/>
+      <c r="Q247" s="2"/>
+      <c r="R247" s="2"/>
+      <c r="S247" s="2"/>
+      <c r="V247" s="2"/>
+      <c r="W247" s="2"/>
+    </row>
+    <row r="248" spans="1:26">
+      <c r="A248">
+        <v>1075</v>
+      </c>
+      <c r="B248" s="3">
+        <v>46293.448148148098</v>
+      </c>
+      <c r="C248" s="3">
+        <v>46293.449340277803</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F248">
+        <v>38116</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H248" s="2"/>
+      <c r="I248" s="2"/>
+      <c r="J248" s="2"/>
+      <c r="K248" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="L248" s="2"/>
+      <c r="M248" s="2"/>
+      <c r="N248" s="2"/>
+      <c r="O248" s="2"/>
+      <c r="P248" s="2"/>
+      <c r="Q248" s="2"/>
+      <c r="R248" s="2"/>
+      <c r="S248" s="2"/>
+      <c r="V248" s="2"/>
+      <c r="W248" s="2"/>
+    </row>
+    <row r="249" spans="1:26">
+      <c r="A249">
+        <v>1076</v>
+      </c>
+      <c r="B249" s="3">
+        <v>46293.450127314798</v>
+      </c>
+      <c r="C249" s="3">
+        <v>46293.4511458333</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F249">
+        <v>38428</v>
+      </c>
+      <c r="G249" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H249" s="2"/>
+      <c r="I249" s="2"/>
+      <c r="J249" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="K249" s="2"/>
+      <c r="L249" s="2"/>
+      <c r="M249" s="2"/>
+      <c r="N249" s="2"/>
+      <c r="O249" s="2"/>
+      <c r="P249" s="2"/>
+      <c r="Q249" s="2"/>
+      <c r="R249" s="2"/>
+      <c r="S249" s="2"/>
+      <c r="V249" s="2"/>
+      <c r="W249" s="2"/>
+    </row>
+    <row r="250" spans="1:26">
+      <c r="A250">
+        <v>1077</v>
+      </c>
+      <c r="B250" s="3">
+        <v>46293.451527777797</v>
+      </c>
+      <c r="C250" s="3">
+        <v>46293.452291666697</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F250">
+        <v>38428</v>
+      </c>
+      <c r="G250" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H250" s="2"/>
+      <c r="I250" s="2"/>
+      <c r="J250" s="2"/>
+      <c r="K250" s="2"/>
+      <c r="L250" s="2"/>
+      <c r="M250" s="2"/>
+      <c r="N250" s="2"/>
+      <c r="O250" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="P250" s="2"/>
+      <c r="Q250" s="2"/>
+      <c r="R250" s="2"/>
+      <c r="S250" s="2"/>
+      <c r="V250" s="2"/>
+      <c r="W250" s="2"/>
+    </row>
+    <row r="251" spans="1:26">
+      <c r="A251">
+        <v>1078</v>
+      </c>
+      <c r="B251" s="3">
+        <v>46293.450324074103</v>
+      </c>
+      <c r="C251" s="3">
+        <v>46293.452696759297</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E251" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F251">
+        <v>38571</v>
+      </c>
+      <c r="G251" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H251" s="2"/>
+      <c r="I251" s="2"/>
+      <c r="J251" s="2"/>
+      <c r="K251" s="2"/>
+      <c r="L251" s="2"/>
+      <c r="M251" s="2"/>
+      <c r="N251" s="2"/>
+      <c r="O251" s="2"/>
+      <c r="P251" s="2"/>
+      <c r="Q251" s="2"/>
+      <c r="R251" s="2"/>
+      <c r="S251" s="2"/>
+      <c r="V251" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="W251" s="2" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="252" spans="1:26">
+      <c r="A252">
+        <v>1079</v>
+      </c>
+      <c r="B252" s="3">
+        <v>46293.452569444402</v>
+      </c>
+      <c r="C252" s="3">
+        <v>46293.454004629602</v>
+      </c>
+      <c r="D252" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E252" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F252">
+        <v>38428</v>
+      </c>
+      <c r="G252" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H252" s="2"/>
+      <c r="I252" s="2"/>
+      <c r="J252" s="2"/>
+      <c r="K252" s="2"/>
+      <c r="L252" s="2"/>
+      <c r="M252" s="2"/>
+      <c r="N252" s="2"/>
+      <c r="O252" s="2"/>
+      <c r="P252" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="Q252" s="2"/>
+      <c r="R252" s="2"/>
+      <c r="S252" s="2"/>
+      <c r="V252" s="2"/>
+      <c r="W252" s="2"/>
+    </row>
+    <row r="253" spans="1:26">
+      <c r="A253">
+        <v>1080</v>
+      </c>
+      <c r="B253" s="3">
+        <v>46293.444884259297</v>
+      </c>
+      <c r="C253" s="3">
+        <v>46293.4550115741</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F253">
+        <v>43159</v>
+      </c>
+      <c r="G253" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H253" s="2"/>
+      <c r="I253" s="2"/>
+      <c r="J253" s="2"/>
+      <c r="K253" s="2"/>
+      <c r="L253" s="2"/>
+      <c r="M253" s="2"/>
+      <c r="N253" s="2"/>
+      <c r="O253" s="2"/>
+      <c r="P253" s="2"/>
+      <c r="Q253" s="2"/>
+      <c r="R253" s="2"/>
+      <c r="S253" s="2"/>
+      <c r="V253" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="W253" s="2" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="254" spans="1:26">
+      <c r="A254">
+        <v>1081</v>
+      </c>
+      <c r="B254" s="3">
+        <v>46293.454444444404</v>
+      </c>
+      <c r="C254" s="3">
+        <v>46293.455231481501</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E254" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F254">
+        <v>38428</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H254" s="2"/>
+      <c r="I254" s="2"/>
+      <c r="J254" s="2"/>
+      <c r="K254" s="2"/>
+      <c r="L254" s="2"/>
+      <c r="M254" s="2"/>
+      <c r="N254" s="2"/>
+      <c r="O254" s="2"/>
+      <c r="P254" s="2"/>
+      <c r="Q254" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R254" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S254" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="V254" s="2"/>
+      <c r="W254" s="2"/>
+    </row>
+    <row r="255" spans="1:26">
+      <c r="A255">
+        <v>1082</v>
+      </c>
+      <c r="B255" s="3">
+        <v>46293.456608796303</v>
+      </c>
+      <c r="C255" s="3">
+        <v>46293.457025463002</v>
+      </c>
+      <c r="D255" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F255">
+        <v>38571</v>
+      </c>
+      <c r="G255" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H255" s="2"/>
+      <c r="I255" s="2"/>
+      <c r="J255" s="2"/>
+      <c r="K255" s="2"/>
+      <c r="L255" s="2"/>
+      <c r="M255" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="N255" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="O255" s="2"/>
+      <c r="P255" s="2"/>
+      <c r="Q255" s="4"/>
+      <c r="R255" s="4"/>
+      <c r="S255" s="2"/>
+      <c r="V255" s="2"/>
+      <c r="W255" s="2"/>
+    </row>
+    <row r="256" spans="1:26">
+      <c r="A256">
+        <v>1083</v>
+      </c>
+      <c r="B256" s="3">
+        <v>46293.455497685201</v>
+      </c>
+      <c r="C256" s="3">
+        <v>46293.458379629599</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F256">
+        <v>38428</v>
+      </c>
+      <c r="G256" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H256" s="2"/>
+      <c r="I256" s="2"/>
+      <c r="J256" s="2"/>
+      <c r="K256" s="2"/>
+      <c r="L256" s="2"/>
+      <c r="M256" s="2"/>
+      <c r="N256" s="2"/>
+      <c r="O256" s="2"/>
+      <c r="P256" s="2"/>
+      <c r="Q256" s="4"/>
+      <c r="R256" s="4"/>
+      <c r="S256" s="2"/>
+      <c r="V256" s="2"/>
+      <c r="W256" s="2"/>
+      <c r="X256">
+        <v>29</v>
+      </c>
+      <c r="Y256">
+        <v>4</v>
+      </c>
+      <c r="Z256" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="257" spans="1:26">
+      <c r="A257" s="6">
+        <v>1084</v>
+      </c>
+      <c r="B257" s="3">
+        <v>46293.458923611099</v>
+      </c>
+      <c r="C257" s="3">
+        <v>46293.459548611099</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="F257" s="6">
+        <v>38428</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H257" s="2"/>
+      <c r="I257" s="2"/>
+      <c r="J257" s="2"/>
+      <c r="K257" s="2"/>
+      <c r="L257" s="2"/>
+      <c r="M257" s="2"/>
+      <c r="N257" s="2"/>
+      <c r="O257" s="2"/>
+      <c r="P257" s="2"/>
+      <c r="Q257" s="4"/>
+      <c r="R257" s="4"/>
+      <c r="S257" s="2"/>
+      <c r="T257" s="6">
+        <v>11</v>
+      </c>
+      <c r="U257" s="6">
+        <v>0</v>
+      </c>
+      <c r="V257" s="2"/>
+      <c r="W257" s="2"/>
+      <c r="X257" s="6"/>
+      <c r="Y257" s="6"/>
+      <c r="Z257" s="6"/>
+    </row>
+    <row r="258" spans="1:26">
+      <c r="A258" s="6">
+        <v>1085</v>
+      </c>
+      <c r="B258" s="3">
+        <v>46293.460358796299</v>
+      </c>
+      <c r="C258" s="3">
+        <v>46293.460567129601</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F258" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G258" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H258" s="2"/>
+      <c r="I258" s="2"/>
+      <c r="J258" s="2"/>
+      <c r="K258" s="2"/>
+      <c r="L258" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="M258" s="2"/>
+      <c r="N258" s="2"/>
+      <c r="O258" s="2"/>
+      <c r="P258" s="2"/>
+      <c r="Q258" s="4"/>
+      <c r="R258" s="4"/>
+      <c r="S258" s="2"/>
+      <c r="T258" s="6"/>
+      <c r="U258" s="6"/>
+      <c r="V258" s="2"/>
+      <c r="W258" s="2"/>
+      <c r="X258" s="6"/>
+      <c r="Y258" s="6"/>
+      <c r="Z258" s="6"/>
+    </row>
+    <row r="259" spans="1:26">
+      <c r="A259" s="6">
+        <v>1086</v>
+      </c>
+      <c r="B259" s="3">
+        <v>46293.463715277801</v>
+      </c>
+      <c r="C259" s="3">
+        <v>46293.464178240698</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F259" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G259" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H259" s="2"/>
+      <c r="I259" s="2"/>
+      <c r="J259" s="2"/>
+      <c r="K259" s="2"/>
+      <c r="L259" s="2"/>
+      <c r="M259" s="2"/>
+      <c r="N259" s="2"/>
+      <c r="O259" s="2"/>
+      <c r="P259" s="2"/>
+      <c r="Q259" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="R259" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="S259" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="T259" s="6"/>
+      <c r="U259" s="6"/>
+      <c r="V259" s="2"/>
+      <c r="W259" s="2"/>
+      <c r="X259" s="6"/>
+      <c r="Y259" s="6"/>
+      <c r="Z259" s="6"/>
+    </row>
+    <row r="260" spans="1:26">
+      <c r="A260" s="6">
+        <v>1087</v>
+      </c>
+      <c r="B260" s="3">
+        <v>46293.464282407404</v>
+      </c>
+      <c r="C260" s="3">
+        <v>46293.464456018497</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F260" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G260" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H260" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I260" s="2"/>
+      <c r="J260" s="2"/>
+      <c r="K260" s="2"/>
+      <c r="L260" s="2"/>
+      <c r="M260" s="2"/>
+      <c r="N260" s="2"/>
+      <c r="O260" s="2"/>
+      <c r="P260" s="2"/>
+      <c r="Q260" s="4"/>
+      <c r="R260" s="4"/>
+      <c r="S260" s="2"/>
+      <c r="T260" s="6"/>
+      <c r="U260" s="6"/>
+      <c r="V260" s="2"/>
+      <c r="W260" s="2"/>
+      <c r="X260" s="6"/>
+      <c r="Y260" s="6"/>
+      <c r="Z260" s="6"/>
+    </row>
+    <row r="261" spans="1:26">
+      <c r="A261" s="6">
+        <v>1088</v>
+      </c>
+      <c r="B261" s="3">
+        <v>46293.464548611097</v>
+      </c>
+      <c r="C261" s="3">
+        <v>46293.465428240699</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F261" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H261" s="2"/>
+      <c r="I261" s="2"/>
+      <c r="J261" s="2"/>
+      <c r="K261" s="2"/>
+      <c r="L261" s="2"/>
+      <c r="M261" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="N261" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="O261" s="2"/>
+      <c r="P261" s="2"/>
+      <c r="Q261" s="4"/>
+      <c r="R261" s="4"/>
+      <c r="S261" s="2"/>
+      <c r="T261" s="6"/>
+      <c r="U261" s="6"/>
+      <c r="V261" s="2"/>
+      <c r="W261" s="2"/>
+      <c r="X261" s="6"/>
+      <c r="Y261" s="6"/>
+      <c r="Z261" s="6"/>
+    </row>
+    <row r="262" spans="1:26">
+      <c r="A262" s="6">
+        <v>1089</v>
+      </c>
+      <c r="B262" s="3">
+        <v>46293.457523148099</v>
+      </c>
+      <c r="C262" s="3">
+        <v>46293.466608796298</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F262" s="6">
+        <v>38571</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H262" s="2"/>
+      <c r="I262" s="2"/>
+      <c r="J262" s="2"/>
+      <c r="K262" s="2"/>
+      <c r="L262" s="2"/>
+      <c r="M262" s="2"/>
+      <c r="N262" s="2"/>
+      <c r="O262" s="2"/>
+      <c r="P262" s="2"/>
+      <c r="Q262" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R262" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S262" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="T262" s="6"/>
+      <c r="U262" s="6"/>
+      <c r="V262" s="2"/>
+      <c r="W262" s="2"/>
+      <c r="X262" s="6"/>
+      <c r="Y262" s="6"/>
+      <c r="Z262" s="6"/>
+    </row>
+    <row r="263" spans="1:26">
+      <c r="A263" s="6">
+        <v>1090</v>
+      </c>
+      <c r="B263" s="3">
+        <v>46293.460763888899</v>
+      </c>
+      <c r="C263" s="3">
+        <v>46293.467465277798</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F263" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G263" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H263" s="2"/>
+      <c r="I263" s="2"/>
+      <c r="J263" s="2"/>
+      <c r="K263" s="2"/>
+      <c r="L263" s="2"/>
+      <c r="M263" s="2"/>
+      <c r="N263" s="2"/>
+      <c r="O263" s="2"/>
+      <c r="P263" s="2"/>
+      <c r="Q263" s="4"/>
+      <c r="R263" s="4"/>
+      <c r="S263" s="2"/>
+      <c r="T263" s="6"/>
+      <c r="U263" s="6"/>
+      <c r="V263" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="W263" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="X263" s="6"/>
+      <c r="Y263" s="6"/>
+      <c r="Z263" s="6"/>
+    </row>
+    <row r="264" spans="1:26">
+      <c r="A264" s="6">
+        <v>1091</v>
+      </c>
+      <c r="B264" s="3">
+        <v>46293.466712963003</v>
+      </c>
+      <c r="C264" s="3">
+        <v>46293.4676273148</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F264" s="6">
+        <v>38571</v>
+      </c>
+      <c r="G264" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H264" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I264" s="2"/>
+      <c r="J264" s="2"/>
+      <c r="K264" s="2"/>
+      <c r="L264" s="2"/>
+      <c r="M264" s="2"/>
+      <c r="N264" s="2"/>
+      <c r="O264" s="2"/>
+      <c r="P264" s="2"/>
+      <c r="Q264" s="4"/>
+      <c r="R264" s="4"/>
+      <c r="S264" s="2"/>
+      <c r="T264" s="6"/>
+      <c r="U264" s="6"/>
+      <c r="V264" s="2"/>
+      <c r="W264" s="2"/>
+      <c r="X264" s="6"/>
+      <c r="Y264" s="6"/>
+      <c r="Z264" s="6"/>
+    </row>
+    <row r="265" spans="1:26">
+      <c r="A265" s="6">
+        <v>1092</v>
+      </c>
+      <c r="B265" s="3">
+        <v>46293.470740740697</v>
+      </c>
+      <c r="C265" s="3">
+        <v>46293.4711342593</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F265" s="6">
+        <v>38571</v>
+      </c>
+      <c r="G265" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H265" s="2"/>
+      <c r="I265" s="2"/>
+      <c r="J265" s="2"/>
+      <c r="K265" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="L265" s="2"/>
+      <c r="M265" s="2"/>
+      <c r="N265" s="2"/>
+      <c r="O265" s="2"/>
+      <c r="P265" s="2"/>
+      <c r="Q265" s="4"/>
+      <c r="R265" s="4"/>
+      <c r="S265" s="2"/>
+      <c r="T265" s="6"/>
+      <c r="U265" s="6"/>
+      <c r="V265" s="2"/>
+      <c r="W265" s="2"/>
+      <c r="X265" s="6"/>
+      <c r="Y265" s="6"/>
+      <c r="Z265" s="6"/>
+    </row>
+    <row r="266" spans="1:26">
+      <c r="A266" s="6">
+        <v>1093</v>
+      </c>
+      <c r="B266" s="3">
+        <v>46293.465578703697</v>
+      </c>
+      <c r="C266" s="3">
+        <v>46293.478622685201</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F266" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G266" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H266" s="2"/>
+      <c r="I266" s="2"/>
+      <c r="J266" s="2"/>
+      <c r="K266" s="2"/>
+      <c r="L266" s="2"/>
+      <c r="M266" s="2"/>
+      <c r="N266" s="2"/>
+      <c r="O266" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="P266" s="2"/>
+      <c r="Q266" s="4"/>
+      <c r="R266" s="4"/>
+      <c r="S266" s="2"/>
+      <c r="T266" s="6"/>
+      <c r="U266" s="6"/>
+      <c r="V266" s="2"/>
+      <c r="W266" s="2"/>
+      <c r="X266" s="6"/>
+      <c r="Y266" s="6"/>
+      <c r="Z266" s="6"/>
+    </row>
+    <row r="267" spans="1:26">
+      <c r="A267" s="6">
+        <v>1094</v>
+      </c>
+      <c r="B267" s="3">
+        <v>46293.469178240703</v>
+      </c>
+      <c r="C267" s="3">
+        <v>46293.479432870401</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F267" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G267" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H267" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I267" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="J267" s="2"/>
+      <c r="K267" s="2"/>
+      <c r="L267" s="2"/>
+      <c r="M267" s="2"/>
+      <c r="N267" s="2"/>
+      <c r="O267" s="2"/>
+      <c r="P267" s="2"/>
+      <c r="Q267" s="4"/>
+      <c r="R267" s="4"/>
+      <c r="S267" s="2"/>
+      <c r="T267" s="6"/>
+      <c r="U267" s="6"/>
+      <c r="V267" s="2"/>
+      <c r="W267" s="2"/>
+      <c r="X267" s="6"/>
+      <c r="Y267" s="6"/>
+      <c r="Z267" s="6"/>
+    </row>
+    <row r="268" spans="1:26">
+      <c r="A268" s="6">
+        <v>1095</v>
+      </c>
+      <c r="B268" s="3">
+        <v>46293.458611111098</v>
+      </c>
+      <c r="C268" s="3">
+        <v>46293.480243055601</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E268" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F268" s="6">
+        <v>43159</v>
+      </c>
+      <c r="G268" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H268" s="2"/>
+      <c r="I268" s="2"/>
+      <c r="J268" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="K268" s="2"/>
+      <c r="L268" s="2"/>
+      <c r="M268" s="2"/>
+      <c r="N268" s="2"/>
+      <c r="O268" s="2"/>
+      <c r="P268" s="2"/>
+      <c r="Q268" s="4"/>
+      <c r="R268" s="4"/>
+      <c r="S268" s="2"/>
+      <c r="T268" s="6"/>
+      <c r="U268" s="6"/>
+      <c r="V268" s="2"/>
+      <c r="W268" s="2"/>
+      <c r="X268" s="6"/>
+      <c r="Y268" s="6"/>
+      <c r="Z268" s="6"/>
+    </row>
+    <row r="269" spans="1:26">
+      <c r="A269" s="6">
+        <v>1096</v>
+      </c>
+      <c r="B269" s="3">
+        <v>46293.479803240698</v>
+      </c>
+      <c r="C269" s="3">
+        <v>46293.4816782407</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F269" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G269" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H269" s="2"/>
+      <c r="I269" s="2"/>
+      <c r="J269" s="2"/>
+      <c r="K269" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="L269" s="2"/>
+      <c r="M269" s="2"/>
+      <c r="N269" s="2"/>
+      <c r="O269" s="2"/>
+      <c r="P269" s="2"/>
+      <c r="Q269" s="4"/>
+      <c r="R269" s="4"/>
+      <c r="S269" s="2"/>
+      <c r="T269" s="6"/>
+      <c r="U269" s="6"/>
+      <c r="V269" s="2"/>
+      <c r="W269" s="2"/>
+      <c r="X269" s="6"/>
+      <c r="Y269" s="6"/>
+      <c r="Z269" s="6"/>
+    </row>
+    <row r="270" spans="1:26">
+      <c r="A270" s="6">
+        <v>1097</v>
+      </c>
+      <c r="B270" s="3">
+        <v>46293.480474536998</v>
+      </c>
+      <c r="C270" s="3">
+        <v>46293.482141203698</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E270" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F270" s="6">
+        <v>43159</v>
+      </c>
+      <c r="G270" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H270" s="2"/>
+      <c r="I270" s="2"/>
+      <c r="J270" s="2"/>
+      <c r="K270" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="L270" s="2"/>
+      <c r="M270" s="2"/>
+      <c r="N270" s="2"/>
+      <c r="O270" s="2"/>
+      <c r="P270" s="2"/>
+      <c r="Q270" s="4"/>
+      <c r="R270" s="4"/>
+      <c r="S270" s="2"/>
+      <c r="T270" s="6"/>
+      <c r="U270" s="6"/>
+      <c r="V270" s="2"/>
+      <c r="W270" s="2"/>
+      <c r="X270" s="6"/>
+      <c r="Y270" s="6"/>
+      <c r="Z270" s="6"/>
+    </row>
+    <row r="271" spans="1:26">
+      <c r="A271" s="6">
+        <v>1098</v>
+      </c>
+      <c r="B271" s="3">
+        <v>46293.482280092598</v>
+      </c>
+      <c r="C271" s="3">
+        <v>46293.483587962997</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E271" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F271" s="6">
+        <v>43159</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H271" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I271" s="2"/>
+      <c r="J271" s="2"/>
+      <c r="K271" s="2"/>
+      <c r="L271" s="2"/>
+      <c r="M271" s="2"/>
+      <c r="N271" s="2"/>
+      <c r="O271" s="2"/>
+      <c r="P271" s="2"/>
+      <c r="Q271" s="4"/>
+      <c r="R271" s="4"/>
+      <c r="S271" s="2"/>
+      <c r="T271" s="6"/>
+      <c r="U271" s="6"/>
+      <c r="V271" s="2"/>
+      <c r="W271" s="2"/>
+      <c r="X271" s="6"/>
+      <c r="Y271" s="6"/>
+      <c r="Z271" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2457ACFD-E93B-4586-9C75-E7F16AC1F2DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5959BEE-2477-4BF3-90A4-AE284329453E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1029" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="429">
   <si>
     <t>Id</t>
   </si>
@@ -1462,8 +1462,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z271" totalsRowShown="0">
-  <autoFilter ref="A1:Z271" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z272" totalsRowShown="0">
+  <autoFilter ref="A1:Z272" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1651,7 +1651,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1098" latestEventMarker="1544">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1099" latestEventMarker="1545">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1981,7 +1981,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z271"/>
+  <dimension ref="A1:Z272"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -11491,6 +11491,50 @@
       <c r="Y271" s="6"/>
       <c r="Z271" s="6"/>
     </row>
+    <row r="272" spans="1:26">
+      <c r="A272" s="6">
+        <v>1099</v>
+      </c>
+      <c r="B272" s="3">
+        <v>46293.4837037037</v>
+      </c>
+      <c r="C272" s="3">
+        <v>46293.488877314798</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F272" s="6">
+        <v>43159</v>
+      </c>
+      <c r="G272" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H272" s="2"/>
+      <c r="I272" s="2"/>
+      <c r="J272" s="2"/>
+      <c r="K272" s="2"/>
+      <c r="L272" s="2"/>
+      <c r="M272" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N272" s="2"/>
+      <c r="O272" s="2"/>
+      <c r="P272" s="2"/>
+      <c r="Q272" s="4"/>
+      <c r="R272" s="4"/>
+      <c r="S272" s="2"/>
+      <c r="T272" s="6"/>
+      <c r="U272" s="6"/>
+      <c r="V272" s="2"/>
+      <c r="W272" s="2"/>
+      <c r="X272" s="6"/>
+      <c r="Y272" s="6"/>
+      <c r="Z272" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5959BEE-2477-4BF3-90A4-AE284329453E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EE8F044-D726-416C-B508-59DA46A48A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1033" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="430">
   <si>
     <t>Id</t>
   </si>
@@ -1326,6 +1326,9 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG-20260523-WA0021_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG-20260928-WA0021_Starbucks%20Grand%20San.jpg</t>
   </si>
 </sst>
 </file>
@@ -1462,8 +1465,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z272" totalsRowShown="0">
-  <autoFilter ref="A1:Z272" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z274" totalsRowShown="0">
+  <autoFilter ref="A1:Z274" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1651,7 +1654,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1099" latestEventMarker="1545">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1101" latestEventMarker="1547">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1981,7 +1984,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z272"/>
+  <dimension ref="A1:Z274"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
@@ -11535,6 +11538,96 @@
       <c r="Y272" s="6"/>
       <c r="Z272" s="6"/>
     </row>
+    <row r="273" spans="1:26">
+      <c r="A273" s="6">
+        <v>1100</v>
+      </c>
+      <c r="B273" s="3">
+        <v>46293.481932870403</v>
+      </c>
+      <c r="C273" s="3">
+        <v>46293.494745370401</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F273" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G273" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H273" s="2"/>
+      <c r="I273" s="2"/>
+      <c r="J273" s="2"/>
+      <c r="K273" s="2"/>
+      <c r="L273" s="2"/>
+      <c r="M273" s="2"/>
+      <c r="N273" s="2"/>
+      <c r="O273" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="P273" s="2"/>
+      <c r="Q273" s="4"/>
+      <c r="R273" s="4"/>
+      <c r="S273" s="2"/>
+      <c r="T273" s="6"/>
+      <c r="U273" s="6"/>
+      <c r="V273" s="2"/>
+      <c r="W273" s="2"/>
+      <c r="X273" s="6"/>
+      <c r="Y273" s="6"/>
+      <c r="Z273" s="6"/>
+    </row>
+    <row r="274" spans="1:26">
+      <c r="A274" s="6">
+        <v>1101</v>
+      </c>
+      <c r="B274" s="3">
+        <v>46293.495567129597</v>
+      </c>
+      <c r="C274" s="3">
+        <v>46293.496122685203</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="F274" s="6">
+        <v>38230</v>
+      </c>
+      <c r="G274" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H274" s="2"/>
+      <c r="I274" s="2"/>
+      <c r="J274" s="2"/>
+      <c r="K274" s="2"/>
+      <c r="L274" s="2"/>
+      <c r="M274" s="2"/>
+      <c r="N274" s="2"/>
+      <c r="O274" s="2"/>
+      <c r="P274" s="2"/>
+      <c r="Q274" s="4"/>
+      <c r="R274" s="4"/>
+      <c r="S274" s="2"/>
+      <c r="T274" s="6">
+        <v>12</v>
+      </c>
+      <c r="U274" s="6">
+        <v>0</v>
+      </c>
+      <c r="V274" s="2"/>
+      <c r="W274" s="2"/>
+      <c r="X274" s="6"/>
+      <c r="Y274" s="6"/>
+      <c r="Z274" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3EE8F044-D726-416C-B508-59DA46A48A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B1855BD-B3C0-490D-92D6-679BDA8C3892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="430">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="433">
   <si>
     <t>Id</t>
   </si>
@@ -1329,6 +1329,15 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG-20260928-WA0021_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG-20260928-WA0034_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Rosa%20Patricia%20Aguila.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_20260928_121213721_HDR_Starbucks%20Hospital%20A.jpg</t>
   </si>
 </sst>
 </file>
@@ -1465,8 +1474,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z274" totalsRowShown="0">
-  <autoFilter ref="A1:Z274" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z281" totalsRowShown="0">
+  <autoFilter ref="A1:Z281" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1654,7 +1663,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1101" latestEventMarker="1547">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1108" latestEventMarker="1554">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1984,10 +1993,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z274"/>
+  <dimension ref="A1:Z281"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="23" width="20" bestFit="1" customWidth="1"/>
+    <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="25.140625" customWidth="1"/>
+    <col min="6" max="23" width="20" bestFit="1" customWidth="1"/>
     <col min="24" max="26" width="19" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11628,6 +11639,322 @@
       <c r="Y274" s="6"/>
       <c r="Z274" s="6"/>
     </row>
+    <row r="275" spans="1:26">
+      <c r="A275" s="6">
+        <v>1102</v>
+      </c>
+      <c r="B275" s="3">
+        <v>46293.488993055602</v>
+      </c>
+      <c r="C275" s="3">
+        <v>46293.5069097222</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E275" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F275" s="6">
+        <v>43159</v>
+      </c>
+      <c r="G275" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H275" s="2"/>
+      <c r="I275" s="2"/>
+      <c r="J275" s="2"/>
+      <c r="K275" s="2"/>
+      <c r="L275" s="2"/>
+      <c r="M275" s="2"/>
+      <c r="N275" s="2"/>
+      <c r="O275" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="P275" s="2"/>
+      <c r="Q275" s="4"/>
+      <c r="R275" s="4"/>
+      <c r="S275" s="2"/>
+      <c r="T275" s="6"/>
+      <c r="U275" s="6"/>
+      <c r="V275" s="2"/>
+      <c r="W275" s="2"/>
+      <c r="X275" s="6"/>
+      <c r="Y275" s="6"/>
+      <c r="Z275" s="6"/>
+    </row>
+    <row r="276" spans="1:26">
+      <c r="A276" s="6">
+        <v>1103</v>
+      </c>
+      <c r="B276" s="3">
+        <v>46293.506793981498</v>
+      </c>
+      <c r="C276" s="3">
+        <v>46293.510995370401</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F276" s="6">
+        <v>38691</v>
+      </c>
+      <c r="G276" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H276" s="2"/>
+      <c r="I276" s="2"/>
+      <c r="J276" s="2"/>
+      <c r="K276" s="2"/>
+      <c r="L276" s="2"/>
+      <c r="M276" s="2"/>
+      <c r="N276" s="2"/>
+      <c r="O276" s="2"/>
+      <c r="P276" s="2"/>
+      <c r="Q276" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="R276" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S276" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="T276" s="6"/>
+      <c r="U276" s="6"/>
+      <c r="V276" s="2"/>
+      <c r="W276" s="2"/>
+      <c r="X276" s="6"/>
+      <c r="Y276" s="6"/>
+      <c r="Z276" s="6"/>
+    </row>
+    <row r="277" spans="1:26">
+      <c r="A277" s="6">
+        <v>1104</v>
+      </c>
+      <c r="B277" s="3">
+        <v>46293.511701388903</v>
+      </c>
+      <c r="C277" s="3">
+        <v>46293.511863425898</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F277" s="6">
+        <v>3869</v>
+      </c>
+      <c r="G277" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H277" s="2"/>
+      <c r="I277" s="2"/>
+      <c r="J277" s="2"/>
+      <c r="K277" s="2"/>
+      <c r="L277" s="2"/>
+      <c r="M277" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N277" s="2"/>
+      <c r="O277" s="2"/>
+      <c r="P277" s="2"/>
+      <c r="Q277" s="4"/>
+      <c r="R277" s="4"/>
+      <c r="S277" s="2"/>
+      <c r="T277" s="6"/>
+      <c r="U277" s="6"/>
+      <c r="V277" s="2"/>
+      <c r="W277" s="2"/>
+      <c r="X277" s="6"/>
+      <c r="Y277" s="6"/>
+      <c r="Z277" s="6"/>
+    </row>
+    <row r="278" spans="1:26">
+      <c r="A278" s="6">
+        <v>1105</v>
+      </c>
+      <c r="B278" s="3">
+        <v>46293.512870370403</v>
+      </c>
+      <c r="C278" s="3">
+        <v>46293.513368055603</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="F278" s="6">
+        <v>38691</v>
+      </c>
+      <c r="G278" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H278" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I278" s="2"/>
+      <c r="J278" s="2"/>
+      <c r="K278" s="2"/>
+      <c r="L278" s="2"/>
+      <c r="M278" s="2"/>
+      <c r="N278" s="2"/>
+      <c r="O278" s="2"/>
+      <c r="P278" s="2"/>
+      <c r="Q278" s="4"/>
+      <c r="R278" s="4"/>
+      <c r="S278" s="2"/>
+      <c r="T278" s="6"/>
+      <c r="U278" s="6"/>
+      <c r="V278" s="2"/>
+      <c r="W278" s="2"/>
+      <c r="X278" s="6"/>
+      <c r="Y278" s="6"/>
+      <c r="Z278" s="6"/>
+    </row>
+    <row r="279" spans="1:26">
+      <c r="A279" s="6">
+        <v>1106</v>
+      </c>
+      <c r="B279" s="3">
+        <v>46293.5131944444</v>
+      </c>
+      <c r="C279" s="3">
+        <v>46293.513622685197</v>
+      </c>
+      <c r="D279" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E279" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F279" s="6">
+        <v>38142</v>
+      </c>
+      <c r="G279" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H279" s="2"/>
+      <c r="I279" s="2"/>
+      <c r="J279" s="2"/>
+      <c r="K279" s="2"/>
+      <c r="L279" s="2"/>
+      <c r="M279" s="2"/>
+      <c r="N279" s="2"/>
+      <c r="O279" s="2"/>
+      <c r="P279" s="2"/>
+      <c r="Q279" s="4"/>
+      <c r="R279" s="4"/>
+      <c r="S279" s="2"/>
+      <c r="T279" s="6">
+        <v>12</v>
+      </c>
+      <c r="U279" s="6">
+        <v>0</v>
+      </c>
+      <c r="V279" s="2"/>
+      <c r="W279" s="2"/>
+      <c r="X279" s="6"/>
+      <c r="Y279" s="6"/>
+      <c r="Z279" s="6"/>
+    </row>
+    <row r="280" spans="1:26">
+      <c r="A280" s="6">
+        <v>1107</v>
+      </c>
+      <c r="B280" s="3">
+        <v>46293.507037037001</v>
+      </c>
+      <c r="C280" s="3">
+        <v>46293.516620370399</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F280" s="6">
+        <v>43159</v>
+      </c>
+      <c r="G280" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H280" s="2"/>
+      <c r="I280" s="2"/>
+      <c r="J280" s="2"/>
+      <c r="K280" s="2"/>
+      <c r="L280" s="2"/>
+      <c r="M280" s="2"/>
+      <c r="N280" s="2"/>
+      <c r="O280" s="2"/>
+      <c r="P280" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="Q280" s="4"/>
+      <c r="R280" s="4"/>
+      <c r="S280" s="2"/>
+      <c r="T280" s="6"/>
+      <c r="U280" s="6"/>
+      <c r="V280" s="2"/>
+      <c r="W280" s="2"/>
+      <c r="X280" s="6"/>
+      <c r="Y280" s="6"/>
+      <c r="Z280" s="6"/>
+    </row>
+    <row r="281" spans="1:26">
+      <c r="A281" s="6">
+        <v>1108</v>
+      </c>
+      <c r="B281" s="3">
+        <v>46293.5178703704</v>
+      </c>
+      <c r="C281" s="3">
+        <v>46293.518333333297</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="F281" s="6">
+        <v>43043</v>
+      </c>
+      <c r="G281" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H281" s="2"/>
+      <c r="I281" s="2"/>
+      <c r="J281" s="2"/>
+      <c r="K281" s="2"/>
+      <c r="L281" s="2"/>
+      <c r="M281" s="2"/>
+      <c r="N281" s="2"/>
+      <c r="O281" s="2"/>
+      <c r="P281" s="2"/>
+      <c r="Q281" s="4"/>
+      <c r="R281" s="4"/>
+      <c r="S281" s="2"/>
+      <c r="T281" s="6">
+        <v>9</v>
+      </c>
+      <c r="U281" s="6">
+        <v>2</v>
+      </c>
+      <c r="V281" s="2"/>
+      <c r="W281" s="2"/>
+      <c r="X281" s="6"/>
+      <c r="Y281" s="6"/>
+      <c r="Z281" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2B1855BD-B3C0-490D-92D6-679BDA8C3892}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BD8C53D-6C48-428B-92A4-70A0A697D154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1068" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="438">
   <si>
     <t>Id</t>
   </si>
@@ -1338,6 +1338,21 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_20260928_121213721_HDR_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>ana.gonzalez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Ana Laura Gonzalez Martínez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/IMG_20260909_071544_Ana%20Laura%20Gonzalez%20M.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/IMG_20260928_122845_Ana%20Laura%20Gonzalez%20M.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17906202978228533674482905004280_Starbucks%20Hospital%20A.jpg</t>
   </si>
 </sst>
 </file>
@@ -1474,8 +1489,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z281" totalsRowShown="0">
-  <autoFilter ref="A1:Z281" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z285" totalsRowShown="0">
+  <autoFilter ref="A1:Z285" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1663,7 +1678,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1108" latestEventMarker="1554">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1112" latestEventMarker="1558">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1993,7 +2008,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z281"/>
+  <dimension ref="A1:Z285"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -11955,6 +11970,192 @@
       <c r="Y281" s="6"/>
       <c r="Z281" s="6"/>
     </row>
+    <row r="282" spans="1:26">
+      <c r="A282" s="6">
+        <v>1109</v>
+      </c>
+      <c r="B282" s="3">
+        <v>46293.506064814799</v>
+      </c>
+      <c r="C282" s="3">
+        <v>46293.520868055602</v>
+      </c>
+      <c r="D282" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E282" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F282" s="6">
+        <v>38107</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H282" s="2"/>
+      <c r="I282" s="2"/>
+      <c r="J282" s="2"/>
+      <c r="K282" s="2"/>
+      <c r="L282" s="2"/>
+      <c r="M282" s="2"/>
+      <c r="N282" s="2"/>
+      <c r="O282" s="2"/>
+      <c r="P282" s="2"/>
+      <c r="Q282" s="4"/>
+      <c r="R282" s="4"/>
+      <c r="S282" s="2"/>
+      <c r="T282" s="6"/>
+      <c r="U282" s="6"/>
+      <c r="V282" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="W282" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="X282" s="6"/>
+      <c r="Y282" s="6"/>
+      <c r="Z282" s="6"/>
+    </row>
+    <row r="283" spans="1:26">
+      <c r="A283" s="6">
+        <v>1110</v>
+      </c>
+      <c r="B283" s="3">
+        <v>46293.519571759301</v>
+      </c>
+      <c r="C283" s="3">
+        <v>46293.522141203699</v>
+      </c>
+      <c r="D283" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E283" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="F283" s="6">
+        <v>43130</v>
+      </c>
+      <c r="G283" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H283" s="2"/>
+      <c r="I283" s="2"/>
+      <c r="J283" s="2"/>
+      <c r="K283" s="2"/>
+      <c r="L283" s="2"/>
+      <c r="M283" s="2"/>
+      <c r="N283" s="2"/>
+      <c r="O283" s="2"/>
+      <c r="P283" s="2"/>
+      <c r="Q283" s="4"/>
+      <c r="R283" s="4"/>
+      <c r="S283" s="2"/>
+      <c r="T283" s="6">
+        <v>9</v>
+      </c>
+      <c r="U283" s="6">
+        <v>3</v>
+      </c>
+      <c r="V283" s="2"/>
+      <c r="W283" s="2"/>
+      <c r="X283" s="6"/>
+      <c r="Y283" s="6"/>
+      <c r="Z283" s="6"/>
+    </row>
+    <row r="284" spans="1:26">
+      <c r="A284" s="6">
+        <v>1111</v>
+      </c>
+      <c r="B284" s="3">
+        <v>46293.5203819444</v>
+      </c>
+      <c r="C284" s="3">
+        <v>46293.522141203699</v>
+      </c>
+      <c r="D284" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E284" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F284" s="6">
+        <v>43159</v>
+      </c>
+      <c r="G284" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H284" s="2"/>
+      <c r="I284" s="2"/>
+      <c r="J284" s="2"/>
+      <c r="K284" s="2"/>
+      <c r="L284" s="2"/>
+      <c r="M284" s="2"/>
+      <c r="N284" s="2"/>
+      <c r="O284" s="2"/>
+      <c r="P284" s="2"/>
+      <c r="Q284" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R284" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S284" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="T284" s="6"/>
+      <c r="U284" s="6"/>
+      <c r="V284" s="2"/>
+      <c r="W284" s="2"/>
+      <c r="X284" s="6"/>
+      <c r="Y284" s="6"/>
+      <c r="Z284" s="6"/>
+    </row>
+    <row r="285" spans="1:26">
+      <c r="A285" s="6">
+        <v>1112</v>
+      </c>
+      <c r="B285" s="3">
+        <v>46293.522789351897</v>
+      </c>
+      <c r="C285" s="3">
+        <v>46293.523460648197</v>
+      </c>
+      <c r="D285" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E285" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="F285" s="6">
+        <v>38507</v>
+      </c>
+      <c r="G285" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H285" s="2"/>
+      <c r="I285" s="2"/>
+      <c r="J285" s="2"/>
+      <c r="K285" s="2"/>
+      <c r="L285" s="2"/>
+      <c r="M285" s="2"/>
+      <c r="N285" s="2"/>
+      <c r="O285" s="2"/>
+      <c r="P285" s="2"/>
+      <c r="Q285" s="4"/>
+      <c r="R285" s="4"/>
+      <c r="S285" s="2"/>
+      <c r="T285" s="6">
+        <v>9</v>
+      </c>
+      <c r="U285" s="6">
+        <v>0</v>
+      </c>
+      <c r="V285" s="2"/>
+      <c r="W285" s="2"/>
+      <c r="X285" s="6"/>
+      <c r="Y285" s="6"/>
+      <c r="Z285" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BD8C53D-6C48-428B-92A4-70A0A697D154}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE959A44-51FC-4285-ABE9-F1AC839458E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1085" uniqueCount="438">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="442">
   <si>
     <t>Id</t>
   </si>
@@ -1353,6 +1353,18 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17906202978228533674482905004280_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/Collage_20260928_123453194_Ana%20Laura%20Gonzalez%20M.jpg</t>
+  </si>
+  <si>
+    <t>carlos.cortes@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Carlos Cortes Aguilar</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG-20260928-WA0022_Starbucks%20Grand%20San.jpg</t>
   </si>
 </sst>
 </file>
@@ -1489,8 +1501,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z285" totalsRowShown="0">
-  <autoFilter ref="A1:Z285" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z293" totalsRowShown="0">
+  <autoFilter ref="A1:Z293" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1678,7 +1690,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1112" latestEventMarker="1558">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1120" latestEventMarker="1566">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2008,7 +2020,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z285"/>
+  <dimension ref="A1:Z293"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -12156,6 +12168,370 @@
       <c r="Y285" s="6"/>
       <c r="Z285" s="6"/>
     </row>
+    <row r="286" spans="1:26">
+      <c r="A286" s="6">
+        <v>1113</v>
+      </c>
+      <c r="B286" s="3">
+        <v>46293.521828703699</v>
+      </c>
+      <c r="C286" s="3">
+        <v>46293.524571759299</v>
+      </c>
+      <c r="D286" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E286" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F286" s="6">
+        <v>38107</v>
+      </c>
+      <c r="G286" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H286" s="2"/>
+      <c r="I286" s="2"/>
+      <c r="J286" s="2"/>
+      <c r="K286" s="2"/>
+      <c r="L286" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="M286" s="2"/>
+      <c r="N286" s="2"/>
+      <c r="O286" s="2"/>
+      <c r="P286" s="2"/>
+      <c r="Q286" s="4"/>
+      <c r="R286" s="4"/>
+      <c r="S286" s="2"/>
+      <c r="T286" s="6"/>
+      <c r="U286" s="6"/>
+      <c r="V286" s="2"/>
+      <c r="W286" s="2"/>
+      <c r="X286" s="6"/>
+      <c r="Y286" s="6"/>
+      <c r="Z286" s="6"/>
+    </row>
+    <row r="287" spans="1:26">
+      <c r="A287" s="6">
+        <v>1114</v>
+      </c>
+      <c r="B287" s="3">
+        <v>46293.524143518502</v>
+      </c>
+      <c r="C287" s="3">
+        <v>46293.524710648097</v>
+      </c>
+      <c r="D287" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E287" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="F287" s="6">
+        <v>38119</v>
+      </c>
+      <c r="G287" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H287" s="2"/>
+      <c r="I287" s="2"/>
+      <c r="J287" s="2"/>
+      <c r="K287" s="2"/>
+      <c r="L287" s="2"/>
+      <c r="M287" s="2"/>
+      <c r="N287" s="2"/>
+      <c r="O287" s="2"/>
+      <c r="P287" s="2"/>
+      <c r="Q287" s="4"/>
+      <c r="R287" s="4"/>
+      <c r="S287" s="2"/>
+      <c r="T287" s="6">
+        <v>9</v>
+      </c>
+      <c r="U287" s="6">
+        <v>4</v>
+      </c>
+      <c r="V287" s="2"/>
+      <c r="W287" s="2"/>
+      <c r="X287" s="6"/>
+      <c r="Y287" s="6"/>
+      <c r="Z287" s="6"/>
+    </row>
+    <row r="288" spans="1:26">
+      <c r="A288" s="6">
+        <v>1115</v>
+      </c>
+      <c r="B288" s="3">
+        <v>46293.524826388901</v>
+      </c>
+      <c r="C288" s="3">
+        <v>46293.525405092601</v>
+      </c>
+      <c r="D288" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E288" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F288" s="6">
+        <v>38115</v>
+      </c>
+      <c r="G288" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H288" s="2"/>
+      <c r="I288" s="2"/>
+      <c r="J288" s="2"/>
+      <c r="K288" s="2"/>
+      <c r="L288" s="2"/>
+      <c r="M288" s="2"/>
+      <c r="N288" s="2"/>
+      <c r="O288" s="2"/>
+      <c r="P288" s="2"/>
+      <c r="Q288" s="4"/>
+      <c r="R288" s="4"/>
+      <c r="S288" s="2"/>
+      <c r="T288" s="6">
+        <v>7</v>
+      </c>
+      <c r="U288" s="6">
+        <v>2</v>
+      </c>
+      <c r="V288" s="2"/>
+      <c r="W288" s="2"/>
+      <c r="X288" s="6"/>
+      <c r="Y288" s="6"/>
+      <c r="Z288" s="6"/>
+    </row>
+    <row r="289" spans="1:26">
+      <c r="A289" s="6">
+        <v>1116</v>
+      </c>
+      <c r="B289" s="3">
+        <v>46293.525231481501</v>
+      </c>
+      <c r="C289" s="3">
+        <v>46293.525613425903</v>
+      </c>
+      <c r="D289" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E289" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F289" s="6">
+        <v>38363</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H289" s="2"/>
+      <c r="I289" s="2"/>
+      <c r="J289" s="2"/>
+      <c r="K289" s="2"/>
+      <c r="L289" s="2"/>
+      <c r="M289" s="2"/>
+      <c r="N289" s="2"/>
+      <c r="O289" s="2"/>
+      <c r="P289" s="2"/>
+      <c r="Q289" s="4"/>
+      <c r="R289" s="4"/>
+      <c r="S289" s="2"/>
+      <c r="T289" s="6">
+        <v>11</v>
+      </c>
+      <c r="U289" s="6">
+        <v>5</v>
+      </c>
+      <c r="V289" s="2"/>
+      <c r="W289" s="2"/>
+      <c r="X289" s="6"/>
+      <c r="Y289" s="6"/>
+      <c r="Z289" s="6"/>
+    </row>
+    <row r="290" spans="1:26">
+      <c r="A290" s="6">
+        <v>1117</v>
+      </c>
+      <c r="B290" s="3">
+        <v>46293.524930555599</v>
+      </c>
+      <c r="C290" s="3">
+        <v>46293.525810185201</v>
+      </c>
+      <c r="D290" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E290" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="F290" s="6">
+        <v>38394</v>
+      </c>
+      <c r="G290" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H290" s="2"/>
+      <c r="I290" s="2"/>
+      <c r="J290" s="2"/>
+      <c r="K290" s="2"/>
+      <c r="L290" s="2"/>
+      <c r="M290" s="2"/>
+      <c r="N290" s="2"/>
+      <c r="O290" s="2"/>
+      <c r="P290" s="2"/>
+      <c r="Q290" s="4"/>
+      <c r="R290" s="4"/>
+      <c r="S290" s="2"/>
+      <c r="T290" s="6">
+        <v>10</v>
+      </c>
+      <c r="U290" s="6">
+        <v>1</v>
+      </c>
+      <c r="V290" s="2"/>
+      <c r="W290" s="2"/>
+      <c r="X290" s="6"/>
+      <c r="Y290" s="6"/>
+      <c r="Z290" s="6"/>
+    </row>
+    <row r="291" spans="1:26">
+      <c r="A291" s="6">
+        <v>1118</v>
+      </c>
+      <c r="B291" s="3">
+        <v>46293.524768518502</v>
+      </c>
+      <c r="C291" s="3">
+        <v>46293.528310185196</v>
+      </c>
+      <c r="D291" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E291" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F291" s="6">
+        <v>38176</v>
+      </c>
+      <c r="G291" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H291" s="2"/>
+      <c r="I291" s="2"/>
+      <c r="J291" s="2"/>
+      <c r="K291" s="2"/>
+      <c r="L291" s="2"/>
+      <c r="M291" s="2"/>
+      <c r="N291" s="2"/>
+      <c r="O291" s="2"/>
+      <c r="P291" s="2"/>
+      <c r="Q291" s="4"/>
+      <c r="R291" s="4"/>
+      <c r="S291" s="2"/>
+      <c r="T291" s="6">
+        <v>23</v>
+      </c>
+      <c r="U291" s="6">
+        <v>0</v>
+      </c>
+      <c r="V291" s="2"/>
+      <c r="W291" s="2"/>
+      <c r="X291" s="6"/>
+      <c r="Y291" s="6"/>
+      <c r="Z291" s="6"/>
+    </row>
+    <row r="292" spans="1:26">
+      <c r="A292" s="6">
+        <v>1119</v>
+      </c>
+      <c r="B292" s="3">
+        <v>46293.527708333299</v>
+      </c>
+      <c r="C292" s="3">
+        <v>46293.5285532407</v>
+      </c>
+      <c r="D292" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E292" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="F292" s="6">
+        <v>38149</v>
+      </c>
+      <c r="G292" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H292" s="2"/>
+      <c r="I292" s="2"/>
+      <c r="J292" s="2"/>
+      <c r="K292" s="2"/>
+      <c r="L292" s="2"/>
+      <c r="M292" s="2"/>
+      <c r="N292" s="2"/>
+      <c r="O292" s="2"/>
+      <c r="P292" s="2"/>
+      <c r="Q292" s="4"/>
+      <c r="R292" s="4"/>
+      <c r="S292" s="2"/>
+      <c r="T292" s="6">
+        <v>12</v>
+      </c>
+      <c r="U292" s="6">
+        <v>0</v>
+      </c>
+      <c r="V292" s="2"/>
+      <c r="W292" s="2"/>
+      <c r="X292" s="6"/>
+      <c r="Y292" s="6"/>
+      <c r="Z292" s="6"/>
+    </row>
+    <row r="293" spans="1:26">
+      <c r="A293" s="6">
+        <v>1120</v>
+      </c>
+      <c r="B293" s="3">
+        <v>46293.495185185202</v>
+      </c>
+      <c r="C293" s="3">
+        <v>46293.528993055603</v>
+      </c>
+      <c r="D293" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E293" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F293" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G293" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H293" s="2"/>
+      <c r="I293" s="2"/>
+      <c r="J293" s="2"/>
+      <c r="K293" s="2"/>
+      <c r="L293" s="2"/>
+      <c r="M293" s="2"/>
+      <c r="N293" s="2"/>
+      <c r="O293" s="2"/>
+      <c r="P293" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="Q293" s="4"/>
+      <c r="R293" s="4"/>
+      <c r="S293" s="2"/>
+      <c r="T293" s="6"/>
+      <c r="U293" s="6"/>
+      <c r="V293" s="2"/>
+      <c r="W293" s="2"/>
+      <c r="X293" s="6"/>
+      <c r="Y293" s="6"/>
+      <c r="Z293" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CE959A44-51FC-4285-ABE9-F1AC839458E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6D0A6CE-D412-4157-B2E4-FC2BB0020FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1111" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="446">
   <si>
     <t>Id</t>
   </si>
@@ -1365,6 +1365,18 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG-20260928-WA0022_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38535@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks City Center Esmeralda</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Starbucks%20Galerias%20P.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17906215172309032253877619866021_Starbucks%20Grand%20San.jpg</t>
   </si>
 </sst>
 </file>
@@ -1501,8 +1513,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z293" totalsRowShown="0">
-  <autoFilter ref="A1:Z293" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z296" totalsRowShown="0">
+  <autoFilter ref="A1:Z296" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1690,7 +1702,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1120" latestEventMarker="1566">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1123" latestEventMarker="1569">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2020,7 +2032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z293"/>
+  <dimension ref="A1:Z296"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -12532,6 +12544,148 @@
       <c r="Y293" s="6"/>
       <c r="Z293" s="6"/>
     </row>
+    <row r="294" spans="1:26">
+      <c r="A294" s="6">
+        <v>1121</v>
+      </c>
+      <c r="B294" s="3">
+        <v>46293.531458333302</v>
+      </c>
+      <c r="C294" s="3">
+        <v>46293.5319212963</v>
+      </c>
+      <c r="D294" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E294" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F294" s="6">
+        <v>38535</v>
+      </c>
+      <c r="G294" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H294" s="2"/>
+      <c r="I294" s="2"/>
+      <c r="J294" s="2"/>
+      <c r="K294" s="2"/>
+      <c r="L294" s="2"/>
+      <c r="M294" s="2"/>
+      <c r="N294" s="2"/>
+      <c r="O294" s="2"/>
+      <c r="P294" s="2"/>
+      <c r="Q294" s="4"/>
+      <c r="R294" s="4"/>
+      <c r="S294" s="2"/>
+      <c r="T294" s="6">
+        <v>20</v>
+      </c>
+      <c r="U294" s="6">
+        <v>8</v>
+      </c>
+      <c r="V294" s="2"/>
+      <c r="W294" s="2"/>
+      <c r="X294" s="6"/>
+      <c r="Y294" s="6"/>
+      <c r="Z294" s="6"/>
+    </row>
+    <row r="295" spans="1:26">
+      <c r="A295" s="6">
+        <v>1122</v>
+      </c>
+      <c r="B295" s="3">
+        <v>46293.534537036998</v>
+      </c>
+      <c r="C295" s="3">
+        <v>46293.535775463002</v>
+      </c>
+      <c r="D295" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E295" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="F295" s="6">
+        <v>38894</v>
+      </c>
+      <c r="G295" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H295" s="2"/>
+      <c r="I295" s="2"/>
+      <c r="J295" s="2"/>
+      <c r="K295" s="2"/>
+      <c r="L295" s="2"/>
+      <c r="M295" s="2"/>
+      <c r="N295" s="2"/>
+      <c r="O295" s="2"/>
+      <c r="P295" s="2"/>
+      <c r="Q295" s="4"/>
+      <c r="R295" s="4"/>
+      <c r="S295" s="2"/>
+      <c r="T295" s="6"/>
+      <c r="U295" s="6"/>
+      <c r="V295" s="2"/>
+      <c r="W295" s="2"/>
+      <c r="X295" s="6">
+        <v>3</v>
+      </c>
+      <c r="Y295" s="6">
+        <v>6</v>
+      </c>
+      <c r="Z295" s="6" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="296" spans="1:26">
+      <c r="A296" s="6">
+        <v>1123</v>
+      </c>
+      <c r="B296" s="3">
+        <v>46293.529224537</v>
+      </c>
+      <c r="C296" s="3">
+        <v>46293.537337962996</v>
+      </c>
+      <c r="D296" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E296" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F296" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G296" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H296" s="2"/>
+      <c r="I296" s="2"/>
+      <c r="J296" s="2"/>
+      <c r="K296" s="2"/>
+      <c r="L296" s="2"/>
+      <c r="M296" s="2"/>
+      <c r="N296" s="2"/>
+      <c r="O296" s="2"/>
+      <c r="P296" s="2"/>
+      <c r="Q296" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R296" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S296" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="T296" s="6"/>
+      <c r="U296" s="6"/>
+      <c r="V296" s="2"/>
+      <c r="W296" s="2"/>
+      <c r="X296" s="6"/>
+      <c r="Y296" s="6"/>
+      <c r="Z296" s="6"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A6D0A6CE-D412-4157-B2E4-FC2BB0020FA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA6C781-83F6-45A7-A3D5-6D61DE8F68EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1124" uniqueCount="446">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="476">
   <si>
     <t>Id</t>
   </si>
@@ -1377,6 +1377,96 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17906215172309032253877619866021_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/17906220493061822202990744192708_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20Santa%20Tere.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG_20260928_130336_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17906224487814490315058580141368_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Starbucks%20Hospital%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG_20260928_131507_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG_20260928_132249_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/b2977134-a039-4eba-a0ec-8e2c08899eac_Starbucks%20Hospital%20A.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_20260928_132957_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38694@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Villas de la Hacienda</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/17906239264083416231501546352865_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>dulce.guzman@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Dulce Maria Guzman Silva</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/e049d5a8-5df8-439a-94bd-fbebbdcb426f_Starbucks%20Hospital%20A.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/IMG_20260928_133856_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38431@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Eduardo Molina</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/3d72dffb-61fa-4c53-a420-27f819a535bc_Starbucks%20Hospital%20A.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/D510E489-431E-4D9A-9DCC-D0BEF33C84F5_Starbucks%20Mega%20Izcal.jpeg</t>
+  </si>
+  <si>
+    <t>jessica.mendoza@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Jessica Mendoza Garcia</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/IMG_20260928_135208_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/IMG_20260928_135208_Amparo%20Delgado%20Res%C3%A9n.jpg</t>
+  </si>
+  <si>
+    <t>vanessa.carreno@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Vanessa Carreño Rios</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17906248660798027879660485910940_Ramon%20Espinosa%20Macia.jpg</t>
+  </si>
+  <si>
+    <t>cristian.posadas@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Cristian Alexis Posadas Lorenzo</t>
   </si>
 </sst>
 </file>
@@ -1513,8 +1603,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z296" totalsRowShown="0">
-  <autoFilter ref="A1:Z296" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z330" totalsRowShown="0">
+  <autoFilter ref="A1:Z330" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1702,7 +1792,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1123" latestEventMarker="1569">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1157" latestEventMarker="1603">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2032,7 +2122,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z296"/>
+  <dimension ref="A1:Z330"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -10868,8 +10958,8 @@
         <v>415</v>
       </c>
     </row>
-    <row r="257" spans="1:26">
-      <c r="A257" s="6">
+    <row r="257" spans="1:23">
+      <c r="A257">
         <v>1084</v>
       </c>
       <c r="B257" s="3">
@@ -10884,7 +10974,7 @@
       <c r="E257" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="F257" s="6">
+      <c r="F257">
         <v>38428</v>
       </c>
       <c r="G257" s="2" t="s">
@@ -10902,20 +10992,17 @@
       <c r="Q257" s="4"/>
       <c r="R257" s="4"/>
       <c r="S257" s="2"/>
-      <c r="T257" s="6">
+      <c r="T257">
         <v>11</v>
       </c>
-      <c r="U257" s="6">
+      <c r="U257">
         <v>0</v>
       </c>
       <c r="V257" s="2"/>
       <c r="W257" s="2"/>
-      <c r="X257" s="6"/>
-      <c r="Y257" s="6"/>
-      <c r="Z257" s="6"/>
-    </row>
-    <row r="258" spans="1:26">
-      <c r="A258" s="6">
+    </row>
+    <row r="258" spans="1:23">
+      <c r="A258">
         <v>1085</v>
       </c>
       <c r="B258" s="3">
@@ -10930,7 +11017,7 @@
       <c r="E258" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F258" s="6">
+      <c r="F258">
         <v>38615</v>
       </c>
       <c r="G258" s="2" t="s">
@@ -10950,16 +11037,11 @@
       <c r="Q258" s="4"/>
       <c r="R258" s="4"/>
       <c r="S258" s="2"/>
-      <c r="T258" s="6"/>
-      <c r="U258" s="6"/>
       <c r="V258" s="2"/>
       <c r="W258" s="2"/>
-      <c r="X258" s="6"/>
-      <c r="Y258" s="6"/>
-      <c r="Z258" s="6"/>
-    </row>
-    <row r="259" spans="1:26">
-      <c r="A259" s="6">
+    </row>
+    <row r="259" spans="1:23">
+      <c r="A259">
         <v>1086</v>
       </c>
       <c r="B259" s="3">
@@ -10974,7 +11056,7 @@
       <c r="E259" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F259" s="6">
+      <c r="F259">
         <v>38129</v>
       </c>
       <c r="G259" s="2" t="s">
@@ -10998,16 +11080,11 @@
       <c r="S259" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="T259" s="6"/>
-      <c r="U259" s="6"/>
       <c r="V259" s="2"/>
       <c r="W259" s="2"/>
-      <c r="X259" s="6"/>
-      <c r="Y259" s="6"/>
-      <c r="Z259" s="6"/>
-    </row>
-    <row r="260" spans="1:26">
-      <c r="A260" s="6">
+    </row>
+    <row r="260" spans="1:23">
+      <c r="A260">
         <v>1087</v>
       </c>
       <c r="B260" s="3">
@@ -11022,7 +11099,7 @@
       <c r="E260" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F260" s="6">
+      <c r="F260">
         <v>38129</v>
       </c>
       <c r="G260" s="2" t="s">
@@ -11042,16 +11119,11 @@
       <c r="Q260" s="4"/>
       <c r="R260" s="4"/>
       <c r="S260" s="2"/>
-      <c r="T260" s="6"/>
-      <c r="U260" s="6"/>
       <c r="V260" s="2"/>
       <c r="W260" s="2"/>
-      <c r="X260" s="6"/>
-      <c r="Y260" s="6"/>
-      <c r="Z260" s="6"/>
-    </row>
-    <row r="261" spans="1:26">
-      <c r="A261" s="6">
+    </row>
+    <row r="261" spans="1:23">
+      <c r="A261">
         <v>1088</v>
       </c>
       <c r="B261" s="3">
@@ -11066,7 +11138,7 @@
       <c r="E261" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F261" s="6">
+      <c r="F261">
         <v>38129</v>
       </c>
       <c r="G261" s="2" t="s">
@@ -11088,16 +11160,11 @@
       <c r="Q261" s="4"/>
       <c r="R261" s="4"/>
       <c r="S261" s="2"/>
-      <c r="T261" s="6"/>
-      <c r="U261" s="6"/>
       <c r="V261" s="2"/>
       <c r="W261" s="2"/>
-      <c r="X261" s="6"/>
-      <c r="Y261" s="6"/>
-      <c r="Z261" s="6"/>
-    </row>
-    <row r="262" spans="1:26">
-      <c r="A262" s="6">
+    </row>
+    <row r="262" spans="1:23">
+      <c r="A262">
         <v>1089</v>
       </c>
       <c r="B262" s="3">
@@ -11112,7 +11179,7 @@
       <c r="E262" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F262" s="6">
+      <c r="F262">
         <v>38571</v>
       </c>
       <c r="G262" s="2" t="s">
@@ -11136,16 +11203,11 @@
       <c r="S262" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="T262" s="6"/>
-      <c r="U262" s="6"/>
       <c r="V262" s="2"/>
       <c r="W262" s="2"/>
-      <c r="X262" s="6"/>
-      <c r="Y262" s="6"/>
-      <c r="Z262" s="6"/>
-    </row>
-    <row r="263" spans="1:26">
-      <c r="A263" s="6">
+    </row>
+    <row r="263" spans="1:23">
+      <c r="A263">
         <v>1090</v>
       </c>
       <c r="B263" s="3">
@@ -11160,7 +11222,7 @@
       <c r="E263" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F263" s="6">
+      <c r="F263">
         <v>38615</v>
       </c>
       <c r="G263" s="2" t="s">
@@ -11178,20 +11240,15 @@
       <c r="Q263" s="4"/>
       <c r="R263" s="4"/>
       <c r="S263" s="2"/>
-      <c r="T263" s="6"/>
-      <c r="U263" s="6"/>
       <c r="V263" s="2" t="s">
         <v>421</v>
       </c>
       <c r="W263" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="X263" s="6"/>
-      <c r="Y263" s="6"/>
-      <c r="Z263" s="6"/>
-    </row>
-    <row r="264" spans="1:26">
-      <c r="A264" s="6">
+    </row>
+    <row r="264" spans="1:23">
+      <c r="A264">
         <v>1091</v>
       </c>
       <c r="B264" s="3">
@@ -11206,7 +11263,7 @@
       <c r="E264" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F264" s="6">
+      <c r="F264">
         <v>38571</v>
       </c>
       <c r="G264" s="2" t="s">
@@ -11226,16 +11283,11 @@
       <c r="Q264" s="4"/>
       <c r="R264" s="4"/>
       <c r="S264" s="2"/>
-      <c r="T264" s="6"/>
-      <c r="U264" s="6"/>
       <c r="V264" s="2"/>
       <c r="W264" s="2"/>
-      <c r="X264" s="6"/>
-      <c r="Y264" s="6"/>
-      <c r="Z264" s="6"/>
-    </row>
-    <row r="265" spans="1:26">
-      <c r="A265" s="6">
+    </row>
+    <row r="265" spans="1:23">
+      <c r="A265">
         <v>1092</v>
       </c>
       <c r="B265" s="3">
@@ -11250,7 +11302,7 @@
       <c r="E265" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F265" s="6">
+      <c r="F265">
         <v>38571</v>
       </c>
       <c r="G265" s="2" t="s">
@@ -11270,16 +11322,11 @@
       <c r="Q265" s="4"/>
       <c r="R265" s="4"/>
       <c r="S265" s="2"/>
-      <c r="T265" s="6"/>
-      <c r="U265" s="6"/>
       <c r="V265" s="2"/>
       <c r="W265" s="2"/>
-      <c r="X265" s="6"/>
-      <c r="Y265" s="6"/>
-      <c r="Z265" s="6"/>
-    </row>
-    <row r="266" spans="1:26">
-      <c r="A266" s="6">
+    </row>
+    <row r="266" spans="1:23">
+      <c r="A266">
         <v>1093</v>
       </c>
       <c r="B266" s="3">
@@ -11294,7 +11341,7 @@
       <c r="E266" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F266" s="6">
+      <c r="F266">
         <v>38129</v>
       </c>
       <c r="G266" s="2" t="s">
@@ -11314,16 +11361,11 @@
       <c r="Q266" s="4"/>
       <c r="R266" s="4"/>
       <c r="S266" s="2"/>
-      <c r="T266" s="6"/>
-      <c r="U266" s="6"/>
       <c r="V266" s="2"/>
       <c r="W266" s="2"/>
-      <c r="X266" s="6"/>
-      <c r="Y266" s="6"/>
-      <c r="Z266" s="6"/>
-    </row>
-    <row r="267" spans="1:26">
-      <c r="A267" s="6">
+    </row>
+    <row r="267" spans="1:23">
+      <c r="A267">
         <v>1094</v>
       </c>
       <c r="B267" s="3">
@@ -11338,7 +11380,7 @@
       <c r="E267" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F267" s="6">
+      <c r="F267">
         <v>38615</v>
       </c>
       <c r="G267" s="2" t="s">
@@ -11360,16 +11402,11 @@
       <c r="Q267" s="4"/>
       <c r="R267" s="4"/>
       <c r="S267" s="2"/>
-      <c r="T267" s="6"/>
-      <c r="U267" s="6"/>
       <c r="V267" s="2"/>
       <c r="W267" s="2"/>
-      <c r="X267" s="6"/>
-      <c r="Y267" s="6"/>
-      <c r="Z267" s="6"/>
-    </row>
-    <row r="268" spans="1:26">
-      <c r="A268" s="6">
+    </row>
+    <row r="268" spans="1:23">
+      <c r="A268">
         <v>1095</v>
       </c>
       <c r="B268" s="3">
@@ -11384,7 +11421,7 @@
       <c r="E268" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F268" s="6">
+      <c r="F268">
         <v>43159</v>
       </c>
       <c r="G268" s="2" t="s">
@@ -11404,16 +11441,11 @@
       <c r="Q268" s="4"/>
       <c r="R268" s="4"/>
       <c r="S268" s="2"/>
-      <c r="T268" s="6"/>
-      <c r="U268" s="6"/>
       <c r="V268" s="2"/>
       <c r="W268" s="2"/>
-      <c r="X268" s="6"/>
-      <c r="Y268" s="6"/>
-      <c r="Z268" s="6"/>
-    </row>
-    <row r="269" spans="1:26">
-      <c r="A269" s="6">
+    </row>
+    <row r="269" spans="1:23">
+      <c r="A269">
         <v>1096</v>
       </c>
       <c r="B269" s="3">
@@ -11428,7 +11460,7 @@
       <c r="E269" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F269" s="6">
+      <c r="F269">
         <v>38615</v>
       </c>
       <c r="G269" s="2" t="s">
@@ -11448,16 +11480,11 @@
       <c r="Q269" s="4"/>
       <c r="R269" s="4"/>
       <c r="S269" s="2"/>
-      <c r="T269" s="6"/>
-      <c r="U269" s="6"/>
       <c r="V269" s="2"/>
       <c r="W269" s="2"/>
-      <c r="X269" s="6"/>
-      <c r="Y269" s="6"/>
-      <c r="Z269" s="6"/>
-    </row>
-    <row r="270" spans="1:26">
-      <c r="A270" s="6">
+    </row>
+    <row r="270" spans="1:23">
+      <c r="A270">
         <v>1097</v>
       </c>
       <c r="B270" s="3">
@@ -11472,7 +11499,7 @@
       <c r="E270" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F270" s="6">
+      <c r="F270">
         <v>43159</v>
       </c>
       <c r="G270" s="2" t="s">
@@ -11492,16 +11519,11 @@
       <c r="Q270" s="4"/>
       <c r="R270" s="4"/>
       <c r="S270" s="2"/>
-      <c r="T270" s="6"/>
-      <c r="U270" s="6"/>
       <c r="V270" s="2"/>
       <c r="W270" s="2"/>
-      <c r="X270" s="6"/>
-      <c r="Y270" s="6"/>
-      <c r="Z270" s="6"/>
-    </row>
-    <row r="271" spans="1:26">
-      <c r="A271" s="6">
+    </row>
+    <row r="271" spans="1:23">
+      <c r="A271">
         <v>1098</v>
       </c>
       <c r="B271" s="3">
@@ -11516,7 +11538,7 @@
       <c r="E271" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F271" s="6">
+      <c r="F271">
         <v>43159</v>
       </c>
       <c r="G271" s="2" t="s">
@@ -11536,16 +11558,11 @@
       <c r="Q271" s="4"/>
       <c r="R271" s="4"/>
       <c r="S271" s="2"/>
-      <c r="T271" s="6"/>
-      <c r="U271" s="6"/>
       <c r="V271" s="2"/>
       <c r="W271" s="2"/>
-      <c r="X271" s="6"/>
-      <c r="Y271" s="6"/>
-      <c r="Z271" s="6"/>
-    </row>
-    <row r="272" spans="1:26">
-      <c r="A272" s="6">
+    </row>
+    <row r="272" spans="1:23">
+      <c r="A272">
         <v>1099</v>
       </c>
       <c r="B272" s="3">
@@ -11560,7 +11577,7 @@
       <c r="E272" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F272" s="6">
+      <c r="F272">
         <v>43159</v>
       </c>
       <c r="G272" s="2" t="s">
@@ -11580,16 +11597,11 @@
       <c r="Q272" s="4"/>
       <c r="R272" s="4"/>
       <c r="S272" s="2"/>
-      <c r="T272" s="6"/>
-      <c r="U272" s="6"/>
       <c r="V272" s="2"/>
       <c r="W272" s="2"/>
-      <c r="X272" s="6"/>
-      <c r="Y272" s="6"/>
-      <c r="Z272" s="6"/>
-    </row>
-    <row r="273" spans="1:26">
-      <c r="A273" s="6">
+    </row>
+    <row r="273" spans="1:23">
+      <c r="A273">
         <v>1100</v>
       </c>
       <c r="B273" s="3">
@@ -11604,7 +11616,7 @@
       <c r="E273" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F273" s="6">
+      <c r="F273">
         <v>38615</v>
       </c>
       <c r="G273" s="2" t="s">
@@ -11624,16 +11636,11 @@
       <c r="Q273" s="4"/>
       <c r="R273" s="4"/>
       <c r="S273" s="2"/>
-      <c r="T273" s="6"/>
-      <c r="U273" s="6"/>
       <c r="V273" s="2"/>
       <c r="W273" s="2"/>
-      <c r="X273" s="6"/>
-      <c r="Y273" s="6"/>
-      <c r="Z273" s="6"/>
-    </row>
-    <row r="274" spans="1:26">
-      <c r="A274" s="6">
+    </row>
+    <row r="274" spans="1:23">
+      <c r="A274">
         <v>1101</v>
       </c>
       <c r="B274" s="3">
@@ -11648,7 +11655,7 @@
       <c r="E274" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="F274" s="6">
+      <c r="F274">
         <v>38230</v>
       </c>
       <c r="G274" s="2" t="s">
@@ -11666,20 +11673,17 @@
       <c r="Q274" s="4"/>
       <c r="R274" s="4"/>
       <c r="S274" s="2"/>
-      <c r="T274" s="6">
+      <c r="T274">
         <v>12</v>
       </c>
-      <c r="U274" s="6">
+      <c r="U274">
         <v>0</v>
       </c>
       <c r="V274" s="2"/>
       <c r="W274" s="2"/>
-      <c r="X274" s="6"/>
-      <c r="Y274" s="6"/>
-      <c r="Z274" s="6"/>
-    </row>
-    <row r="275" spans="1:26">
-      <c r="A275" s="6">
+    </row>
+    <row r="275" spans="1:23">
+      <c r="A275">
         <v>1102</v>
       </c>
       <c r="B275" s="3">
@@ -11694,7 +11698,7 @@
       <c r="E275" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F275" s="6">
+      <c r="F275">
         <v>43159</v>
       </c>
       <c r="G275" s="2" t="s">
@@ -11714,16 +11718,11 @@
       <c r="Q275" s="4"/>
       <c r="R275" s="4"/>
       <c r="S275" s="2"/>
-      <c r="T275" s="6"/>
-      <c r="U275" s="6"/>
       <c r="V275" s="2"/>
       <c r="W275" s="2"/>
-      <c r="X275" s="6"/>
-      <c r="Y275" s="6"/>
-      <c r="Z275" s="6"/>
-    </row>
-    <row r="276" spans="1:26">
-      <c r="A276" s="6">
+    </row>
+    <row r="276" spans="1:23">
+      <c r="A276">
         <v>1103</v>
       </c>
       <c r="B276" s="3">
@@ -11738,7 +11737,7 @@
       <c r="E276" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F276" s="6">
+      <c r="F276">
         <v>38691</v>
       </c>
       <c r="G276" s="2" t="s">
@@ -11762,16 +11761,11 @@
       <c r="S276" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="T276" s="6"/>
-      <c r="U276" s="6"/>
       <c r="V276" s="2"/>
       <c r="W276" s="2"/>
-      <c r="X276" s="6"/>
-      <c r="Y276" s="6"/>
-      <c r="Z276" s="6"/>
-    </row>
-    <row r="277" spans="1:26">
-      <c r="A277" s="6">
+    </row>
+    <row r="277" spans="1:23">
+      <c r="A277">
         <v>1104</v>
       </c>
       <c r="B277" s="3">
@@ -11786,7 +11780,7 @@
       <c r="E277" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F277" s="6">
+      <c r="F277">
         <v>3869</v>
       </c>
       <c r="G277" s="2" t="s">
@@ -11806,16 +11800,11 @@
       <c r="Q277" s="4"/>
       <c r="R277" s="4"/>
       <c r="S277" s="2"/>
-      <c r="T277" s="6"/>
-      <c r="U277" s="6"/>
       <c r="V277" s="2"/>
       <c r="W277" s="2"/>
-      <c r="X277" s="6"/>
-      <c r="Y277" s="6"/>
-      <c r="Z277" s="6"/>
-    </row>
-    <row r="278" spans="1:26">
-      <c r="A278" s="6">
+    </row>
+    <row r="278" spans="1:23">
+      <c r="A278">
         <v>1105</v>
       </c>
       <c r="B278" s="3">
@@ -11830,7 +11819,7 @@
       <c r="E278" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="F278" s="6">
+      <c r="F278">
         <v>38691</v>
       </c>
       <c r="G278" s="2" t="s">
@@ -11850,16 +11839,11 @@
       <c r="Q278" s="4"/>
       <c r="R278" s="4"/>
       <c r="S278" s="2"/>
-      <c r="T278" s="6"/>
-      <c r="U278" s="6"/>
       <c r="V278" s="2"/>
       <c r="W278" s="2"/>
-      <c r="X278" s="6"/>
-      <c r="Y278" s="6"/>
-      <c r="Z278" s="6"/>
-    </row>
-    <row r="279" spans="1:26">
-      <c r="A279" s="6">
+    </row>
+    <row r="279" spans="1:23">
+      <c r="A279">
         <v>1106</v>
       </c>
       <c r="B279" s="3">
@@ -11874,7 +11858,7 @@
       <c r="E279" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="F279" s="6">
+      <c r="F279">
         <v>38142</v>
       </c>
       <c r="G279" s="2" t="s">
@@ -11892,20 +11876,17 @@
       <c r="Q279" s="4"/>
       <c r="R279" s="4"/>
       <c r="S279" s="2"/>
-      <c r="T279" s="6">
+      <c r="T279">
         <v>12</v>
       </c>
-      <c r="U279" s="6">
+      <c r="U279">
         <v>0</v>
       </c>
       <c r="V279" s="2"/>
       <c r="W279" s="2"/>
-      <c r="X279" s="6"/>
-      <c r="Y279" s="6"/>
-      <c r="Z279" s="6"/>
-    </row>
-    <row r="280" spans="1:26">
-      <c r="A280" s="6">
+    </row>
+    <row r="280" spans="1:23">
+      <c r="A280">
         <v>1107</v>
       </c>
       <c r="B280" s="3">
@@ -11920,7 +11901,7 @@
       <c r="E280" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F280" s="6">
+      <c r="F280">
         <v>43159</v>
       </c>
       <c r="G280" s="2" t="s">
@@ -11940,16 +11921,11 @@
       <c r="Q280" s="4"/>
       <c r="R280" s="4"/>
       <c r="S280" s="2"/>
-      <c r="T280" s="6"/>
-      <c r="U280" s="6"/>
       <c r="V280" s="2"/>
       <c r="W280" s="2"/>
-      <c r="X280" s="6"/>
-      <c r="Y280" s="6"/>
-      <c r="Z280" s="6"/>
-    </row>
-    <row r="281" spans="1:26">
-      <c r="A281" s="6">
+    </row>
+    <row r="281" spans="1:23">
+      <c r="A281">
         <v>1108</v>
       </c>
       <c r="B281" s="3">
@@ -11964,7 +11940,7 @@
       <c r="E281" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F281" s="6">
+      <c r="F281">
         <v>43043</v>
       </c>
       <c r="G281" s="2" t="s">
@@ -11982,20 +11958,17 @@
       <c r="Q281" s="4"/>
       <c r="R281" s="4"/>
       <c r="S281" s="2"/>
-      <c r="T281" s="6">
+      <c r="T281">
         <v>9</v>
       </c>
-      <c r="U281" s="6">
+      <c r="U281">
         <v>2</v>
       </c>
       <c r="V281" s="2"/>
       <c r="W281" s="2"/>
-      <c r="X281" s="6"/>
-      <c r="Y281" s="6"/>
-      <c r="Z281" s="6"/>
-    </row>
-    <row r="282" spans="1:26">
-      <c r="A282" s="6">
+    </row>
+    <row r="282" spans="1:23">
+      <c r="A282">
         <v>1109</v>
       </c>
       <c r="B282" s="3">
@@ -12010,7 +11983,7 @@
       <c r="E282" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="F282" s="6">
+      <c r="F282">
         <v>38107</v>
       </c>
       <c r="G282" s="2" t="s">
@@ -12028,20 +12001,15 @@
       <c r="Q282" s="4"/>
       <c r="R282" s="4"/>
       <c r="S282" s="2"/>
-      <c r="T282" s="6"/>
-      <c r="U282" s="6"/>
       <c r="V282" s="2" t="s">
         <v>435</v>
       </c>
       <c r="W282" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="X282" s="6"/>
-      <c r="Y282" s="6"/>
-      <c r="Z282" s="6"/>
-    </row>
-    <row r="283" spans="1:26">
-      <c r="A283" s="6">
+    </row>
+    <row r="283" spans="1:23">
+      <c r="A283">
         <v>1110</v>
       </c>
       <c r="B283" s="3">
@@ -12056,7 +12024,7 @@
       <c r="E283" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="F283" s="6">
+      <c r="F283">
         <v>43130</v>
       </c>
       <c r="G283" s="2" t="s">
@@ -12074,20 +12042,17 @@
       <c r="Q283" s="4"/>
       <c r="R283" s="4"/>
       <c r="S283" s="2"/>
-      <c r="T283" s="6">
+      <c r="T283">
         <v>9</v>
       </c>
-      <c r="U283" s="6">
+      <c r="U283">
         <v>3</v>
       </c>
       <c r="V283" s="2"/>
       <c r="W283" s="2"/>
-      <c r="X283" s="6"/>
-      <c r="Y283" s="6"/>
-      <c r="Z283" s="6"/>
-    </row>
-    <row r="284" spans="1:26">
-      <c r="A284" s="6">
+    </row>
+    <row r="284" spans="1:23">
+      <c r="A284">
         <v>1111</v>
       </c>
       <c r="B284" s="3">
@@ -12102,7 +12067,7 @@
       <c r="E284" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="F284" s="6">
+      <c r="F284">
         <v>43159</v>
       </c>
       <c r="G284" s="2" t="s">
@@ -12126,16 +12091,11 @@
       <c r="S284" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="T284" s="6"/>
-      <c r="U284" s="6"/>
       <c r="V284" s="2"/>
       <c r="W284" s="2"/>
-      <c r="X284" s="6"/>
-      <c r="Y284" s="6"/>
-      <c r="Z284" s="6"/>
-    </row>
-    <row r="285" spans="1:26">
-      <c r="A285" s="6">
+    </row>
+    <row r="285" spans="1:23">
+      <c r="A285">
         <v>1112</v>
       </c>
       <c r="B285" s="3">
@@ -12150,7 +12110,7 @@
       <c r="E285" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F285" s="6">
+      <c r="F285">
         <v>38507</v>
       </c>
       <c r="G285" s="2" t="s">
@@ -12168,20 +12128,17 @@
       <c r="Q285" s="4"/>
       <c r="R285" s="4"/>
       <c r="S285" s="2"/>
-      <c r="T285" s="6">
+      <c r="T285">
         <v>9</v>
       </c>
-      <c r="U285" s="6">
+      <c r="U285">
         <v>0</v>
       </c>
       <c r="V285" s="2"/>
       <c r="W285" s="2"/>
-      <c r="X285" s="6"/>
-      <c r="Y285" s="6"/>
-      <c r="Z285" s="6"/>
-    </row>
-    <row r="286" spans="1:26">
-      <c r="A286" s="6">
+    </row>
+    <row r="286" spans="1:23">
+      <c r="A286">
         <v>1113</v>
       </c>
       <c r="B286" s="3">
@@ -12196,7 +12153,7 @@
       <c r="E286" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="F286" s="6">
+      <c r="F286">
         <v>38107</v>
       </c>
       <c r="G286" s="2" t="s">
@@ -12216,16 +12173,11 @@
       <c r="Q286" s="4"/>
       <c r="R286" s="4"/>
       <c r="S286" s="2"/>
-      <c r="T286" s="6"/>
-      <c r="U286" s="6"/>
       <c r="V286" s="2"/>
       <c r="W286" s="2"/>
-      <c r="X286" s="6"/>
-      <c r="Y286" s="6"/>
-      <c r="Z286" s="6"/>
-    </row>
-    <row r="287" spans="1:26">
-      <c r="A287" s="6">
+    </row>
+    <row r="287" spans="1:23">
+      <c r="A287">
         <v>1114</v>
       </c>
       <c r="B287" s="3">
@@ -12240,7 +12192,7 @@
       <c r="E287" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F287" s="6">
+      <c r="F287">
         <v>38119</v>
       </c>
       <c r="G287" s="2" t="s">
@@ -12258,20 +12210,17 @@
       <c r="Q287" s="4"/>
       <c r="R287" s="4"/>
       <c r="S287" s="2"/>
-      <c r="T287" s="6">
+      <c r="T287">
         <v>9</v>
       </c>
-      <c r="U287" s="6">
+      <c r="U287">
         <v>4</v>
       </c>
       <c r="V287" s="2"/>
       <c r="W287" s="2"/>
-      <c r="X287" s="6"/>
-      <c r="Y287" s="6"/>
-      <c r="Z287" s="6"/>
-    </row>
-    <row r="288" spans="1:26">
-      <c r="A288" s="6">
+    </row>
+    <row r="288" spans="1:23">
+      <c r="A288">
         <v>1115</v>
       </c>
       <c r="B288" s="3">
@@ -12286,7 +12235,7 @@
       <c r="E288" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F288" s="6">
+      <c r="F288">
         <v>38115</v>
       </c>
       <c r="G288" s="2" t="s">
@@ -12304,20 +12253,17 @@
       <c r="Q288" s="4"/>
       <c r="R288" s="4"/>
       <c r="S288" s="2"/>
-      <c r="T288" s="6">
+      <c r="T288">
         <v>7</v>
       </c>
-      <c r="U288" s="6">
+      <c r="U288">
         <v>2</v>
       </c>
       <c r="V288" s="2"/>
       <c r="W288" s="2"/>
-      <c r="X288" s="6"/>
-      <c r="Y288" s="6"/>
-      <c r="Z288" s="6"/>
     </row>
     <row r="289" spans="1:26">
-      <c r="A289" s="6">
+      <c r="A289">
         <v>1116</v>
       </c>
       <c r="B289" s="3">
@@ -12332,7 +12278,7 @@
       <c r="E289" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="F289" s="6">
+      <c r="F289">
         <v>38363</v>
       </c>
       <c r="G289" s="2" t="s">
@@ -12350,20 +12296,17 @@
       <c r="Q289" s="4"/>
       <c r="R289" s="4"/>
       <c r="S289" s="2"/>
-      <c r="T289" s="6">
+      <c r="T289">
         <v>11</v>
       </c>
-      <c r="U289" s="6">
+      <c r="U289">
         <v>5</v>
       </c>
       <c r="V289" s="2"/>
       <c r="W289" s="2"/>
-      <c r="X289" s="6"/>
-      <c r="Y289" s="6"/>
-      <c r="Z289" s="6"/>
     </row>
     <row r="290" spans="1:26">
-      <c r="A290" s="6">
+      <c r="A290">
         <v>1117</v>
       </c>
       <c r="B290" s="3">
@@ -12378,7 +12321,7 @@
       <c r="E290" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F290" s="6">
+      <c r="F290">
         <v>38394</v>
       </c>
       <c r="G290" s="2" t="s">
@@ -12396,20 +12339,17 @@
       <c r="Q290" s="4"/>
       <c r="R290" s="4"/>
       <c r="S290" s="2"/>
-      <c r="T290" s="6">
+      <c r="T290">
         <v>10</v>
       </c>
-      <c r="U290" s="6">
+      <c r="U290">
         <v>1</v>
       </c>
       <c r="V290" s="2"/>
       <c r="W290" s="2"/>
-      <c r="X290" s="6"/>
-      <c r="Y290" s="6"/>
-      <c r="Z290" s="6"/>
     </row>
     <row r="291" spans="1:26">
-      <c r="A291" s="6">
+      <c r="A291">
         <v>1118</v>
       </c>
       <c r="B291" s="3">
@@ -12424,7 +12364,7 @@
       <c r="E291" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F291" s="6">
+      <c r="F291">
         <v>38176</v>
       </c>
       <c r="G291" s="2" t="s">
@@ -12442,20 +12382,17 @@
       <c r="Q291" s="4"/>
       <c r="R291" s="4"/>
       <c r="S291" s="2"/>
-      <c r="T291" s="6">
+      <c r="T291">
         <v>23</v>
       </c>
-      <c r="U291" s="6">
+      <c r="U291">
         <v>0</v>
       </c>
       <c r="V291" s="2"/>
       <c r="W291" s="2"/>
-      <c r="X291" s="6"/>
-      <c r="Y291" s="6"/>
-      <c r="Z291" s="6"/>
     </row>
     <row r="292" spans="1:26">
-      <c r="A292" s="6">
+      <c r="A292">
         <v>1119</v>
       </c>
       <c r="B292" s="3">
@@ -12470,7 +12407,7 @@
       <c r="E292" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="F292" s="6">
+      <c r="F292">
         <v>38149</v>
       </c>
       <c r="G292" s="2" t="s">
@@ -12488,20 +12425,17 @@
       <c r="Q292" s="4"/>
       <c r="R292" s="4"/>
       <c r="S292" s="2"/>
-      <c r="T292" s="6">
+      <c r="T292">
         <v>12</v>
       </c>
-      <c r="U292" s="6">
+      <c r="U292">
         <v>0</v>
       </c>
       <c r="V292" s="2"/>
       <c r="W292" s="2"/>
-      <c r="X292" s="6"/>
-      <c r="Y292" s="6"/>
-      <c r="Z292" s="6"/>
     </row>
     <row r="293" spans="1:26">
-      <c r="A293" s="6">
+      <c r="A293">
         <v>1120</v>
       </c>
       <c r="B293" s="3">
@@ -12516,7 +12450,7 @@
       <c r="E293" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F293" s="6">
+      <c r="F293">
         <v>38615</v>
       </c>
       <c r="G293" s="2" t="s">
@@ -12536,16 +12470,11 @@
       <c r="Q293" s="4"/>
       <c r="R293" s="4"/>
       <c r="S293" s="2"/>
-      <c r="T293" s="6"/>
-      <c r="U293" s="6"/>
       <c r="V293" s="2"/>
       <c r="W293" s="2"/>
-      <c r="X293" s="6"/>
-      <c r="Y293" s="6"/>
-      <c r="Z293" s="6"/>
     </row>
     <row r="294" spans="1:26">
-      <c r="A294" s="6">
+      <c r="A294">
         <v>1121</v>
       </c>
       <c r="B294" s="3">
@@ -12560,7 +12489,7 @@
       <c r="E294" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="F294" s="6">
+      <c r="F294">
         <v>38535</v>
       </c>
       <c r="G294" s="2" t="s">
@@ -12578,20 +12507,17 @@
       <c r="Q294" s="4"/>
       <c r="R294" s="4"/>
       <c r="S294" s="2"/>
-      <c r="T294" s="6">
+      <c r="T294">
         <v>20</v>
       </c>
-      <c r="U294" s="6">
+      <c r="U294">
         <v>8</v>
       </c>
       <c r="V294" s="2"/>
       <c r="W294" s="2"/>
-      <c r="X294" s="6"/>
-      <c r="Y294" s="6"/>
-      <c r="Z294" s="6"/>
     </row>
     <row r="295" spans="1:26">
-      <c r="A295" s="6">
+      <c r="A295">
         <v>1122</v>
       </c>
       <c r="B295" s="3">
@@ -12606,7 +12532,7 @@
       <c r="E295" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="F295" s="6">
+      <c r="F295">
         <v>38894</v>
       </c>
       <c r="G295" s="2" t="s">
@@ -12624,22 +12550,20 @@
       <c r="Q295" s="4"/>
       <c r="R295" s="4"/>
       <c r="S295" s="2"/>
-      <c r="T295" s="6"/>
-      <c r="U295" s="6"/>
       <c r="V295" s="2"/>
       <c r="W295" s="2"/>
-      <c r="X295" s="6">
+      <c r="X295">
         <v>3</v>
       </c>
-      <c r="Y295" s="6">
+      <c r="Y295">
         <v>6</v>
       </c>
-      <c r="Z295" s="6" t="s">
+      <c r="Z295" t="s">
         <v>444</v>
       </c>
     </row>
     <row r="296" spans="1:26">
-      <c r="A296" s="6">
+      <c r="A296">
         <v>1123</v>
       </c>
       <c r="B296" s="3">
@@ -12654,7 +12578,7 @@
       <c r="E296" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F296" s="6">
+      <c r="F296">
         <v>38615</v>
       </c>
       <c r="G296" s="2" t="s">
@@ -12678,13 +12602,1553 @@
       <c r="S296" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="T296" s="6"/>
-      <c r="U296" s="6"/>
       <c r="V296" s="2"/>
       <c r="W296" s="2"/>
-      <c r="X296" s="6"/>
-      <c r="Y296" s="6"/>
-      <c r="Z296" s="6"/>
+    </row>
+    <row r="297" spans="1:26">
+      <c r="A297">
+        <v>1124</v>
+      </c>
+      <c r="B297" s="3">
+        <v>46293.542141203703</v>
+      </c>
+      <c r="C297" s="3">
+        <v>46293.542523148099</v>
+      </c>
+      <c r="D297" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E297" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F297">
+        <v>38580</v>
+      </c>
+      <c r="G297" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H297" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I297" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="J297" s="2"/>
+      <c r="K297" s="2"/>
+      <c r="L297" s="2"/>
+      <c r="M297" s="2"/>
+      <c r="N297" s="2"/>
+      <c r="O297" s="2"/>
+      <c r="P297" s="2"/>
+      <c r="Q297" s="4"/>
+      <c r="R297" s="4"/>
+      <c r="S297" s="2"/>
+      <c r="V297" s="2"/>
+      <c r="W297" s="2"/>
+    </row>
+    <row r="298" spans="1:26">
+      <c r="A298" s="6">
+        <v>1125</v>
+      </c>
+      <c r="B298" s="3">
+        <v>46293.544097222199</v>
+      </c>
+      <c r="C298" s="3">
+        <v>46293.544814814799</v>
+      </c>
+      <c r="D298" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E298" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F298" s="6">
+        <v>38116</v>
+      </c>
+      <c r="G298" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H298" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="I298" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="J298" s="2"/>
+      <c r="K298" s="2"/>
+      <c r="L298" s="2"/>
+      <c r="M298" s="2"/>
+      <c r="N298" s="2"/>
+      <c r="O298" s="2"/>
+      <c r="P298" s="2"/>
+      <c r="Q298" s="4"/>
+      <c r="R298" s="4"/>
+      <c r="S298" s="2"/>
+      <c r="T298" s="6"/>
+      <c r="U298" s="6"/>
+      <c r="V298" s="2"/>
+      <c r="W298" s="2"/>
+      <c r="X298" s="6"/>
+      <c r="Y298" s="6"/>
+      <c r="Z298" s="6"/>
+    </row>
+    <row r="299" spans="1:26">
+      <c r="A299" s="6">
+        <v>1126</v>
+      </c>
+      <c r="B299" s="3">
+        <v>46293.542719907397</v>
+      </c>
+      <c r="C299" s="3">
+        <v>46293.545474537001</v>
+      </c>
+      <c r="D299" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E299" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F299" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G299" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H299" s="2"/>
+      <c r="I299" s="2"/>
+      <c r="J299" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="K299" s="2"/>
+      <c r="L299" s="2"/>
+      <c r="M299" s="2"/>
+      <c r="N299" s="2"/>
+      <c r="O299" s="2"/>
+      <c r="P299" s="2"/>
+      <c r="Q299" s="4"/>
+      <c r="R299" s="4"/>
+      <c r="S299" s="2"/>
+      <c r="T299" s="6"/>
+      <c r="U299" s="6"/>
+      <c r="V299" s="2"/>
+      <c r="W299" s="2"/>
+      <c r="X299" s="6"/>
+      <c r="Y299" s="6"/>
+      <c r="Z299" s="6"/>
+    </row>
+    <row r="300" spans="1:26">
+      <c r="A300" s="6">
+        <v>1127</v>
+      </c>
+      <c r="B300" s="3">
+        <v>46293.546053240701</v>
+      </c>
+      <c r="C300" s="3">
+        <v>46293.547106481499</v>
+      </c>
+      <c r="D300" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E300" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F300" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G300" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H300" s="2"/>
+      <c r="I300" s="2"/>
+      <c r="J300" s="2"/>
+      <c r="K300" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="L300" s="2"/>
+      <c r="M300" s="2"/>
+      <c r="N300" s="2"/>
+      <c r="O300" s="2"/>
+      <c r="P300" s="2"/>
+      <c r="Q300" s="4"/>
+      <c r="R300" s="4"/>
+      <c r="S300" s="2"/>
+      <c r="T300" s="6"/>
+      <c r="U300" s="6"/>
+      <c r="V300" s="2"/>
+      <c r="W300" s="2"/>
+      <c r="X300" s="6"/>
+      <c r="Y300" s="6"/>
+      <c r="Z300" s="6"/>
+    </row>
+    <row r="301" spans="1:26">
+      <c r="A301" s="6">
+        <v>1128</v>
+      </c>
+      <c r="B301" s="3">
+        <v>46293.545879629601</v>
+      </c>
+      <c r="C301" s="3">
+        <v>46293.547245370399</v>
+      </c>
+      <c r="D301" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E301" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F301" s="6">
+        <v>38447</v>
+      </c>
+      <c r="G301" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H301" s="2"/>
+      <c r="I301" s="2"/>
+      <c r="J301" s="2"/>
+      <c r="K301" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="L301" s="2"/>
+      <c r="M301" s="2"/>
+      <c r="N301" s="2"/>
+      <c r="O301" s="2"/>
+      <c r="P301" s="2"/>
+      <c r="Q301" s="4"/>
+      <c r="R301" s="4"/>
+      <c r="S301" s="2"/>
+      <c r="T301" s="6"/>
+      <c r="U301" s="6"/>
+      <c r="V301" s="2"/>
+      <c r="W301" s="2"/>
+      <c r="X301" s="6"/>
+      <c r="Y301" s="6"/>
+      <c r="Z301" s="6"/>
+    </row>
+    <row r="302" spans="1:26">
+      <c r="A302" s="6">
+        <v>1129</v>
+      </c>
+      <c r="B302" s="3">
+        <v>46293.547337962998</v>
+      </c>
+      <c r="C302" s="3">
+        <v>46293.547939814802</v>
+      </c>
+      <c r="D302" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E302" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F302" s="6">
+        <v>38447</v>
+      </c>
+      <c r="G302" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H302" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I302" s="2"/>
+      <c r="J302" s="2"/>
+      <c r="K302" s="2"/>
+      <c r="L302" s="2"/>
+      <c r="M302" s="2"/>
+      <c r="N302" s="2"/>
+      <c r="O302" s="2"/>
+      <c r="P302" s="2"/>
+      <c r="Q302" s="4"/>
+      <c r="R302" s="4"/>
+      <c r="S302" s="2"/>
+      <c r="T302" s="6"/>
+      <c r="U302" s="6"/>
+      <c r="V302" s="2"/>
+      <c r="W302" s="2"/>
+      <c r="X302" s="6"/>
+      <c r="Y302" s="6"/>
+      <c r="Z302" s="6"/>
+    </row>
+    <row r="303" spans="1:26">
+      <c r="A303" s="6">
+        <v>1130</v>
+      </c>
+      <c r="B303" s="3">
+        <v>46293.548842592601</v>
+      </c>
+      <c r="C303" s="3">
+        <v>46293.551168981503</v>
+      </c>
+      <c r="D303" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E303" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F303" s="6">
+        <v>38447</v>
+      </c>
+      <c r="G303" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H303" s="2"/>
+      <c r="I303" s="2"/>
+      <c r="J303" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="K303" s="2"/>
+      <c r="L303" s="2"/>
+      <c r="M303" s="2"/>
+      <c r="N303" s="2"/>
+      <c r="O303" s="2"/>
+      <c r="P303" s="2"/>
+      <c r="Q303" s="4"/>
+      <c r="R303" s="4"/>
+      <c r="S303" s="2"/>
+      <c r="T303" s="6"/>
+      <c r="U303" s="6"/>
+      <c r="V303" s="2"/>
+      <c r="W303" s="2"/>
+      <c r="X303" s="6"/>
+      <c r="Y303" s="6"/>
+      <c r="Z303" s="6"/>
+    </row>
+    <row r="304" spans="1:26">
+      <c r="A304" s="6">
+        <v>1131</v>
+      </c>
+      <c r="B304" s="3">
+        <v>46293.547557870399</v>
+      </c>
+      <c r="C304" s="3">
+        <v>46293.552384259303</v>
+      </c>
+      <c r="D304" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E304" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F304" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G304" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H304" s="2"/>
+      <c r="I304" s="2"/>
+      <c r="J304" s="2"/>
+      <c r="K304" s="2"/>
+      <c r="L304" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="M304" s="2"/>
+      <c r="N304" s="2"/>
+      <c r="O304" s="2"/>
+      <c r="P304" s="2"/>
+      <c r="Q304" s="4"/>
+      <c r="R304" s="4"/>
+      <c r="S304" s="2"/>
+      <c r="T304" s="6"/>
+      <c r="U304" s="6"/>
+      <c r="V304" s="2"/>
+      <c r="W304" s="2"/>
+      <c r="X304" s="6"/>
+      <c r="Y304" s="6"/>
+      <c r="Z304" s="6"/>
+    </row>
+    <row r="305" spans="1:26">
+      <c r="A305" s="6">
+        <v>1132</v>
+      </c>
+      <c r="B305" s="3">
+        <v>46293.552592592598</v>
+      </c>
+      <c r="C305" s="3">
+        <v>46293.552743055603</v>
+      </c>
+      <c r="D305" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E305" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F305" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G305" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H305" s="2"/>
+      <c r="I305" s="2"/>
+      <c r="J305" s="2"/>
+      <c r="K305" s="2"/>
+      <c r="L305" s="2"/>
+      <c r="M305" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N305" s="2"/>
+      <c r="O305" s="2"/>
+      <c r="P305" s="2"/>
+      <c r="Q305" s="4"/>
+      <c r="R305" s="4"/>
+      <c r="S305" s="2"/>
+      <c r="T305" s="6"/>
+      <c r="U305" s="6"/>
+      <c r="V305" s="2"/>
+      <c r="W305" s="2"/>
+      <c r="X305" s="6"/>
+      <c r="Y305" s="6"/>
+      <c r="Z305" s="6"/>
+    </row>
+    <row r="306" spans="1:26">
+      <c r="A306" s="6">
+        <v>1133</v>
+      </c>
+      <c r="B306" s="3">
+        <v>46293.551215277803</v>
+      </c>
+      <c r="C306" s="3">
+        <v>46293.5528009259</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F306" s="6">
+        <v>38447</v>
+      </c>
+      <c r="G306" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H306" s="2"/>
+      <c r="I306" s="2"/>
+      <c r="J306" s="2"/>
+      <c r="K306" s="2"/>
+      <c r="L306" s="2"/>
+      <c r="M306" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N306" s="2"/>
+      <c r="O306" s="2"/>
+      <c r="P306" s="2"/>
+      <c r="Q306" s="4"/>
+      <c r="R306" s="4"/>
+      <c r="S306" s="2"/>
+      <c r="T306" s="6"/>
+      <c r="U306" s="6"/>
+      <c r="V306" s="2"/>
+      <c r="W306" s="2"/>
+      <c r="X306" s="6"/>
+      <c r="Y306" s="6"/>
+      <c r="Z306" s="6"/>
+    </row>
+    <row r="307" spans="1:26">
+      <c r="A307" s="6">
+        <v>1134</v>
+      </c>
+      <c r="B307" s="3">
+        <v>46293.550717592603</v>
+      </c>
+      <c r="C307" s="3">
+        <v>46293.554965277799</v>
+      </c>
+      <c r="D307" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E307" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F307" s="6">
+        <v>38270</v>
+      </c>
+      <c r="G307" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H307" s="2"/>
+      <c r="I307" s="2"/>
+      <c r="J307" s="2"/>
+      <c r="K307" s="2"/>
+      <c r="L307" s="2"/>
+      <c r="M307" s="2"/>
+      <c r="N307" s="2"/>
+      <c r="O307" s="2"/>
+      <c r="P307" s="2"/>
+      <c r="Q307" s="4"/>
+      <c r="R307" s="4"/>
+      <c r="S307" s="2"/>
+      <c r="T307" s="6">
+        <v>8</v>
+      </c>
+      <c r="U307" s="6">
+        <v>3</v>
+      </c>
+      <c r="V307" s="2"/>
+      <c r="W307" s="2"/>
+      <c r="X307" s="6"/>
+      <c r="Y307" s="6"/>
+      <c r="Z307" s="6"/>
+    </row>
+    <row r="308" spans="1:26">
+      <c r="A308" s="6">
+        <v>1135</v>
+      </c>
+      <c r="B308" s="3">
+        <v>46293.552881944401</v>
+      </c>
+      <c r="C308" s="3">
+        <v>46293.557731481502</v>
+      </c>
+      <c r="D308" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E308" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F308" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G308" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H308" s="2"/>
+      <c r="I308" s="2"/>
+      <c r="J308" s="2"/>
+      <c r="K308" s="2"/>
+      <c r="L308" s="2"/>
+      <c r="M308" s="2"/>
+      <c r="N308" s="2"/>
+      <c r="O308" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="P308" s="2"/>
+      <c r="Q308" s="4"/>
+      <c r="R308" s="4"/>
+      <c r="S308" s="2"/>
+      <c r="T308" s="6"/>
+      <c r="U308" s="6"/>
+      <c r="V308" s="2"/>
+      <c r="W308" s="2"/>
+      <c r="X308" s="6"/>
+      <c r="Y308" s="6"/>
+      <c r="Z308" s="6"/>
+    </row>
+    <row r="309" spans="1:26">
+      <c r="A309" s="6">
+        <v>1136</v>
+      </c>
+      <c r="B309" s="3">
+        <v>46293.555532407401</v>
+      </c>
+      <c r="C309" s="3">
+        <v>46293.560046296298</v>
+      </c>
+      <c r="D309" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E309" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F309" s="6">
+        <v>38447</v>
+      </c>
+      <c r="G309" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H309" s="2"/>
+      <c r="I309" s="2"/>
+      <c r="J309" s="2"/>
+      <c r="K309" s="2"/>
+      <c r="L309" s="2"/>
+      <c r="M309" s="2"/>
+      <c r="N309" s="2"/>
+      <c r="O309" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="P309" s="2"/>
+      <c r="Q309" s="4"/>
+      <c r="R309" s="4"/>
+      <c r="S309" s="2"/>
+      <c r="T309" s="6"/>
+      <c r="U309" s="6"/>
+      <c r="V309" s="2"/>
+      <c r="W309" s="2"/>
+      <c r="X309" s="6"/>
+      <c r="Y309" s="6"/>
+      <c r="Z309" s="6"/>
+    </row>
+    <row r="310" spans="1:26">
+      <c r="A310" s="6">
+        <v>1137</v>
+      </c>
+      <c r="B310" s="3">
+        <v>46293.560138888897</v>
+      </c>
+      <c r="C310" s="3">
+        <v>46293.560636574097</v>
+      </c>
+      <c r="D310" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E310" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F310" s="6">
+        <v>38374</v>
+      </c>
+      <c r="G310" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H310" s="2"/>
+      <c r="I310" s="2"/>
+      <c r="J310" s="2"/>
+      <c r="K310" s="2"/>
+      <c r="L310" s="2"/>
+      <c r="M310" s="2"/>
+      <c r="N310" s="2"/>
+      <c r="O310" s="2"/>
+      <c r="P310" s="2"/>
+      <c r="Q310" s="4"/>
+      <c r="R310" s="4"/>
+      <c r="S310" s="2"/>
+      <c r="T310" s="6">
+        <v>9</v>
+      </c>
+      <c r="U310" s="6">
+        <v>2</v>
+      </c>
+      <c r="V310" s="2"/>
+      <c r="W310" s="2"/>
+      <c r="X310" s="6"/>
+      <c r="Y310" s="6"/>
+      <c r="Z310" s="6"/>
+    </row>
+    <row r="311" spans="1:26">
+      <c r="A311" s="6">
+        <v>1138</v>
+      </c>
+      <c r="B311" s="3">
+        <v>46293.559143518498</v>
+      </c>
+      <c r="C311" s="3">
+        <v>46293.562615740702</v>
+      </c>
+      <c r="D311" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E311" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F311" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G311" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H311" s="2"/>
+      <c r="I311" s="2"/>
+      <c r="J311" s="2"/>
+      <c r="K311" s="2"/>
+      <c r="L311" s="2"/>
+      <c r="M311" s="2"/>
+      <c r="N311" s="2"/>
+      <c r="O311" s="2"/>
+      <c r="P311" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="Q311" s="4"/>
+      <c r="R311" s="4"/>
+      <c r="S311" s="2"/>
+      <c r="T311" s="6"/>
+      <c r="U311" s="6"/>
+      <c r="V311" s="2"/>
+      <c r="W311" s="2"/>
+      <c r="X311" s="6"/>
+      <c r="Y311" s="6"/>
+      <c r="Z311" s="6"/>
+    </row>
+    <row r="312" spans="1:26">
+      <c r="A312" s="6">
+        <v>1139</v>
+      </c>
+      <c r="B312" s="3">
+        <v>46293.561851851897</v>
+      </c>
+      <c r="C312" s="3">
+        <v>46293.5631712963</v>
+      </c>
+      <c r="D312" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E312" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="F312" s="6">
+        <v>38845</v>
+      </c>
+      <c r="G312" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H312" s="2"/>
+      <c r="I312" s="2"/>
+      <c r="J312" s="2"/>
+      <c r="K312" s="2"/>
+      <c r="L312" s="2"/>
+      <c r="M312" s="2"/>
+      <c r="N312" s="2"/>
+      <c r="O312" s="2"/>
+      <c r="P312" s="2"/>
+      <c r="Q312" s="4"/>
+      <c r="R312" s="4"/>
+      <c r="S312" s="2"/>
+      <c r="T312" s="6">
+        <v>8</v>
+      </c>
+      <c r="U312" s="6">
+        <v>2</v>
+      </c>
+      <c r="V312" s="2"/>
+      <c r="W312" s="2"/>
+      <c r="X312" s="6"/>
+      <c r="Y312" s="6"/>
+      <c r="Z312" s="6"/>
+    </row>
+    <row r="313" spans="1:26">
+      <c r="A313" s="6">
+        <v>1140</v>
+      </c>
+      <c r="B313" s="3">
+        <v>46293.562962962998</v>
+      </c>
+      <c r="C313" s="3">
+        <v>46293.563483796301</v>
+      </c>
+      <c r="D313" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E313" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="F313" s="6">
+        <v>38694</v>
+      </c>
+      <c r="G313" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H313" s="2"/>
+      <c r="I313" s="2"/>
+      <c r="J313" s="2"/>
+      <c r="K313" s="2"/>
+      <c r="L313" s="2"/>
+      <c r="M313" s="2"/>
+      <c r="N313" s="2"/>
+      <c r="O313" s="2"/>
+      <c r="P313" s="2"/>
+      <c r="Q313" s="4"/>
+      <c r="R313" s="4"/>
+      <c r="S313" s="2"/>
+      <c r="T313" s="6">
+        <v>5</v>
+      </c>
+      <c r="U313" s="6">
+        <v>8</v>
+      </c>
+      <c r="V313" s="2"/>
+      <c r="W313" s="2"/>
+      <c r="X313" s="6"/>
+      <c r="Y313" s="6"/>
+      <c r="Z313" s="6"/>
+    </row>
+    <row r="314" spans="1:26">
+      <c r="A314" s="6">
+        <v>1141</v>
+      </c>
+      <c r="B314" s="3">
+        <v>46293.5624074074</v>
+      </c>
+      <c r="C314" s="3">
+        <v>46293.5637615741</v>
+      </c>
+      <c r="D314" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E314" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="F314" s="6">
+        <v>38460</v>
+      </c>
+      <c r="G314" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H314" s="2"/>
+      <c r="I314" s="2"/>
+      <c r="J314" s="2"/>
+      <c r="K314" s="2"/>
+      <c r="L314" s="2"/>
+      <c r="M314" s="2"/>
+      <c r="N314" s="2"/>
+      <c r="O314" s="2"/>
+      <c r="P314" s="2"/>
+      <c r="Q314" s="4"/>
+      <c r="R314" s="4"/>
+      <c r="S314" s="2"/>
+      <c r="T314" s="6">
+        <v>11</v>
+      </c>
+      <c r="U314" s="6">
+        <v>0</v>
+      </c>
+      <c r="V314" s="2"/>
+      <c r="W314" s="2"/>
+      <c r="X314" s="6"/>
+      <c r="Y314" s="6"/>
+      <c r="Z314" s="6"/>
+    </row>
+    <row r="315" spans="1:26">
+      <c r="A315" s="6">
+        <v>1142</v>
+      </c>
+      <c r="B315" s="3">
+        <v>46293.562986111101</v>
+      </c>
+      <c r="C315" s="3">
+        <v>46293.564583333296</v>
+      </c>
+      <c r="D315" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E315" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F315" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G315" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H315" s="2"/>
+      <c r="I315" s="2"/>
+      <c r="J315" s="2"/>
+      <c r="K315" s="2"/>
+      <c r="L315" s="2"/>
+      <c r="M315" s="2"/>
+      <c r="N315" s="2"/>
+      <c r="O315" s="2"/>
+      <c r="P315" s="2"/>
+      <c r="Q315" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R315" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="S315" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="T315" s="6"/>
+      <c r="U315" s="6"/>
+      <c r="V315" s="2"/>
+      <c r="W315" s="2"/>
+      <c r="X315" s="6"/>
+      <c r="Y315" s="6"/>
+      <c r="Z315" s="6"/>
+    </row>
+    <row r="316" spans="1:26">
+      <c r="A316" s="6">
+        <v>1143</v>
+      </c>
+      <c r="B316" s="3">
+        <v>46293.564699074101</v>
+      </c>
+      <c r="C316" s="3">
+        <v>46293.566168981502</v>
+      </c>
+      <c r="D316" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E316" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="F316" s="6">
+        <v>38924</v>
+      </c>
+      <c r="G316" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H316" s="2"/>
+      <c r="I316" s="2"/>
+      <c r="J316" s="2"/>
+      <c r="K316" s="2"/>
+      <c r="L316" s="2"/>
+      <c r="M316" s="2"/>
+      <c r="N316" s="2"/>
+      <c r="O316" s="2"/>
+      <c r="P316" s="2"/>
+      <c r="Q316" s="4"/>
+      <c r="R316" s="4"/>
+      <c r="S316" s="2"/>
+      <c r="T316" s="6">
+        <v>12</v>
+      </c>
+      <c r="U316" s="6">
+        <v>0</v>
+      </c>
+      <c r="V316" s="2"/>
+      <c r="W316" s="2"/>
+      <c r="X316" s="6"/>
+      <c r="Y316" s="6"/>
+      <c r="Z316" s="6"/>
+    </row>
+    <row r="317" spans="1:26">
+      <c r="A317" s="6">
+        <v>1144</v>
+      </c>
+      <c r="B317" s="3">
+        <v>46293.566782407397</v>
+      </c>
+      <c r="C317" s="3">
+        <v>46293.566909722198</v>
+      </c>
+      <c r="D317" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E317" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F317" s="6">
+        <v>38674</v>
+      </c>
+      <c r="G317" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H317" s="2"/>
+      <c r="I317" s="2"/>
+      <c r="J317" s="2"/>
+      <c r="K317" s="2"/>
+      <c r="L317" s="2"/>
+      <c r="M317" s="2"/>
+      <c r="N317" s="2"/>
+      <c r="O317" s="2"/>
+      <c r="P317" s="2"/>
+      <c r="Q317" s="4"/>
+      <c r="R317" s="4"/>
+      <c r="S317" s="2"/>
+      <c r="T317" s="6">
+        <v>6</v>
+      </c>
+      <c r="U317" s="6">
+        <v>4</v>
+      </c>
+      <c r="V317" s="2"/>
+      <c r="W317" s="2"/>
+      <c r="X317" s="6"/>
+      <c r="Y317" s="6"/>
+      <c r="Z317" s="6"/>
+    </row>
+    <row r="318" spans="1:26">
+      <c r="A318" s="6">
+        <v>1145</v>
+      </c>
+      <c r="B318" s="3">
+        <v>46293.560104166703</v>
+      </c>
+      <c r="C318" s="3">
+        <v>46293.567662037</v>
+      </c>
+      <c r="D318" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E318" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F318" s="6">
+        <v>38448</v>
+      </c>
+      <c r="G318" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H318" s="2"/>
+      <c r="I318" s="2"/>
+      <c r="J318" s="2"/>
+      <c r="K318" s="2"/>
+      <c r="L318" s="2"/>
+      <c r="M318" s="2"/>
+      <c r="N318" s="2"/>
+      <c r="O318" s="2"/>
+      <c r="P318" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="Q318" s="4"/>
+      <c r="R318" s="4"/>
+      <c r="S318" s="2"/>
+      <c r="T318" s="6"/>
+      <c r="U318" s="6"/>
+      <c r="V318" s="2"/>
+      <c r="W318" s="2"/>
+      <c r="X318" s="6"/>
+      <c r="Y318" s="6"/>
+      <c r="Z318" s="6"/>
+    </row>
+    <row r="319" spans="1:26">
+      <c r="A319" s="6">
+        <v>1146</v>
+      </c>
+      <c r="B319" s="3">
+        <v>46293.566192129598</v>
+      </c>
+      <c r="C319" s="3">
+        <v>46293.567997685197</v>
+      </c>
+      <c r="D319" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E319" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F319" s="6">
+        <v>38136</v>
+      </c>
+      <c r="G319" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H319" s="2"/>
+      <c r="I319" s="2"/>
+      <c r="J319" s="2"/>
+      <c r="K319" s="2"/>
+      <c r="L319" s="2"/>
+      <c r="M319" s="2"/>
+      <c r="N319" s="2"/>
+      <c r="O319" s="2"/>
+      <c r="P319" s="2"/>
+      <c r="Q319" s="4"/>
+      <c r="R319" s="4"/>
+      <c r="S319" s="2"/>
+      <c r="T319" s="6">
+        <v>9</v>
+      </c>
+      <c r="U319" s="6">
+        <v>2</v>
+      </c>
+      <c r="V319" s="2"/>
+      <c r="W319" s="2"/>
+      <c r="X319" s="6"/>
+      <c r="Y319" s="6"/>
+      <c r="Z319" s="6"/>
+    </row>
+    <row r="320" spans="1:26">
+      <c r="A320" s="6">
+        <v>1147</v>
+      </c>
+      <c r="B320" s="3">
+        <v>46293.564675925903</v>
+      </c>
+      <c r="C320" s="3">
+        <v>46293.569039351903</v>
+      </c>
+      <c r="D320" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E320" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F320" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G320" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H320" s="2"/>
+      <c r="I320" s="2"/>
+      <c r="J320" s="2"/>
+      <c r="K320" s="2"/>
+      <c r="L320" s="2"/>
+      <c r="M320" s="2"/>
+      <c r="N320" s="2"/>
+      <c r="O320" s="2"/>
+      <c r="P320" s="2"/>
+      <c r="Q320" s="4"/>
+      <c r="R320" s="4"/>
+      <c r="S320" s="2"/>
+      <c r="T320" s="6"/>
+      <c r="U320" s="6"/>
+      <c r="V320" s="2"/>
+      <c r="W320" s="2"/>
+      <c r="X320" s="6">
+        <v>30</v>
+      </c>
+      <c r="Y320" s="6">
+        <v>2</v>
+      </c>
+      <c r="Z320" s="6" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="321" spans="1:26">
+      <c r="A321" s="6">
+        <v>1148</v>
+      </c>
+      <c r="B321" s="3">
+        <v>46293.565231481502</v>
+      </c>
+      <c r="C321" s="3">
+        <v>46293.569421296299</v>
+      </c>
+      <c r="D321" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E321" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="F321" s="6">
+        <v>38431</v>
+      </c>
+      <c r="G321" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H321" s="2"/>
+      <c r="I321" s="2"/>
+      <c r="J321" s="2"/>
+      <c r="K321" s="2"/>
+      <c r="L321" s="2"/>
+      <c r="M321" s="2"/>
+      <c r="N321" s="2"/>
+      <c r="O321" s="2"/>
+      <c r="P321" s="2"/>
+      <c r="Q321" s="4"/>
+      <c r="R321" s="4"/>
+      <c r="S321" s="2"/>
+      <c r="T321" s="6">
+        <v>11</v>
+      </c>
+      <c r="U321" s="6">
+        <v>3</v>
+      </c>
+      <c r="V321" s="2"/>
+      <c r="W321" s="2"/>
+      <c r="X321" s="6"/>
+      <c r="Y321" s="6"/>
+      <c r="Z321" s="6"/>
+    </row>
+    <row r="322" spans="1:26">
+      <c r="A322" s="6">
+        <v>1149</v>
+      </c>
+      <c r="B322" s="3">
+        <v>46293.567696759303</v>
+      </c>
+      <c r="C322" s="3">
+        <v>46293.5722453704</v>
+      </c>
+      <c r="D322" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E322" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F322" s="6">
+        <v>38447</v>
+      </c>
+      <c r="G322" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H322" s="2"/>
+      <c r="I322" s="2"/>
+      <c r="J322" s="2"/>
+      <c r="K322" s="2"/>
+      <c r="L322" s="2"/>
+      <c r="M322" s="2"/>
+      <c r="N322" s="2"/>
+      <c r="O322" s="2"/>
+      <c r="P322" s="2"/>
+      <c r="Q322" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R322" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="S322" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="T322" s="6"/>
+      <c r="U322" s="6"/>
+      <c r="V322" s="2"/>
+      <c r="W322" s="2"/>
+      <c r="X322" s="6"/>
+      <c r="Y322" s="6"/>
+      <c r="Z322" s="6"/>
+    </row>
+    <row r="323" spans="1:26">
+      <c r="A323" s="6">
+        <v>1150</v>
+      </c>
+      <c r="B323" s="3">
+        <v>46293.578113425901</v>
+      </c>
+      <c r="C323" s="3">
+        <v>46293.5784837963</v>
+      </c>
+      <c r="D323" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E323" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="F323" s="6">
+        <v>38333</v>
+      </c>
+      <c r="G323" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H323" s="2"/>
+      <c r="I323" s="2"/>
+      <c r="J323" s="2"/>
+      <c r="K323" s="2"/>
+      <c r="L323" s="2"/>
+      <c r="M323" s="2"/>
+      <c r="N323" s="2"/>
+      <c r="O323" s="2"/>
+      <c r="P323" s="2"/>
+      <c r="Q323" s="4"/>
+      <c r="R323" s="4"/>
+      <c r="S323" s="2"/>
+      <c r="T323" s="6"/>
+      <c r="U323" s="6"/>
+      <c r="V323" s="2"/>
+      <c r="W323" s="2"/>
+      <c r="X323" s="6">
+        <v>40</v>
+      </c>
+      <c r="Y323" s="6">
+        <v>4</v>
+      </c>
+      <c r="Z323" s="6" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="324" spans="1:26">
+      <c r="A324" s="6">
+        <v>1151</v>
+      </c>
+      <c r="B324" s="3">
+        <v>46293.5785763889</v>
+      </c>
+      <c r="C324" s="3">
+        <v>46293.5790277778</v>
+      </c>
+      <c r="D324" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E324" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F324" s="6">
+        <v>38937</v>
+      </c>
+      <c r="G324" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H324" s="2"/>
+      <c r="I324" s="2"/>
+      <c r="J324" s="2"/>
+      <c r="K324" s="2"/>
+      <c r="L324" s="2"/>
+      <c r="M324" s="2"/>
+      <c r="N324" s="2"/>
+      <c r="O324" s="2"/>
+      <c r="P324" s="2"/>
+      <c r="Q324" s="4"/>
+      <c r="R324" s="4"/>
+      <c r="S324" s="2"/>
+      <c r="T324" s="6">
+        <v>13</v>
+      </c>
+      <c r="U324" s="6">
+        <v>2</v>
+      </c>
+      <c r="V324" s="2"/>
+      <c r="W324" s="2"/>
+      <c r="X324" s="6"/>
+      <c r="Y324" s="6"/>
+      <c r="Z324" s="6"/>
+    </row>
+    <row r="325" spans="1:26">
+      <c r="A325" s="6">
+        <v>1152</v>
+      </c>
+      <c r="B325" s="3">
+        <v>46293.577233796299</v>
+      </c>
+      <c r="C325" s="3">
+        <v>46293.579178240703</v>
+      </c>
+      <c r="D325" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E325" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F325" s="6">
+        <v>38580</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H325" s="2"/>
+      <c r="I325" s="2"/>
+      <c r="J325" s="2"/>
+      <c r="K325" s="2"/>
+      <c r="L325" s="2"/>
+      <c r="M325" s="2"/>
+      <c r="N325" s="2"/>
+      <c r="O325" s="2"/>
+      <c r="P325" s="2"/>
+      <c r="Q325" s="4"/>
+      <c r="R325" s="4"/>
+      <c r="S325" s="2"/>
+      <c r="T325" s="6"/>
+      <c r="U325" s="6"/>
+      <c r="V325" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="W325" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="X325" s="6"/>
+      <c r="Y325" s="6"/>
+      <c r="Z325" s="6"/>
+    </row>
+    <row r="326" spans="1:26">
+      <c r="A326" s="6">
+        <v>1153</v>
+      </c>
+      <c r="B326" s="3">
+        <v>46293.578969907401</v>
+      </c>
+      <c r="C326" s="3">
+        <v>46293.5796064815</v>
+      </c>
+      <c r="D326" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E326" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="F326" s="6">
+        <v>38677</v>
+      </c>
+      <c r="G326" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H326" s="2"/>
+      <c r="I326" s="2"/>
+      <c r="J326" s="2"/>
+      <c r="K326" s="2"/>
+      <c r="L326" s="2"/>
+      <c r="M326" s="2"/>
+      <c r="N326" s="2"/>
+      <c r="O326" s="2"/>
+      <c r="P326" s="2"/>
+      <c r="Q326" s="4"/>
+      <c r="R326" s="4"/>
+      <c r="S326" s="2"/>
+      <c r="T326" s="6">
+        <v>13</v>
+      </c>
+      <c r="U326" s="6">
+        <v>3</v>
+      </c>
+      <c r="V326" s="2"/>
+      <c r="W326" s="2"/>
+      <c r="X326" s="6"/>
+      <c r="Y326" s="6"/>
+      <c r="Z326" s="6"/>
+    </row>
+    <row r="327" spans="1:26">
+      <c r="A327" s="6">
+        <v>1154</v>
+      </c>
+      <c r="B327" s="3">
+        <v>46293.567511574103</v>
+      </c>
+      <c r="C327" s="3">
+        <v>46293.579861111102</v>
+      </c>
+      <c r="D327" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E327" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="F327" s="6">
+        <v>38456</v>
+      </c>
+      <c r="G327" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H327" s="2"/>
+      <c r="I327" s="2"/>
+      <c r="J327" s="2"/>
+      <c r="K327" s="2"/>
+      <c r="L327" s="2"/>
+      <c r="M327" s="2"/>
+      <c r="N327" s="2"/>
+      <c r="O327" s="2"/>
+      <c r="P327" s="2"/>
+      <c r="Q327" s="4"/>
+      <c r="R327" s="4"/>
+      <c r="S327" s="2"/>
+      <c r="T327" s="6"/>
+      <c r="U327" s="6"/>
+      <c r="V327" s="2"/>
+      <c r="W327" s="2"/>
+      <c r="X327" s="6">
+        <v>36</v>
+      </c>
+      <c r="Y327" s="6">
+        <v>6</v>
+      </c>
+      <c r="Z327" s="6" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="328" spans="1:26">
+      <c r="A328" s="6">
+        <v>1155</v>
+      </c>
+      <c r="B328" s="3">
+        <v>46293.582233796304</v>
+      </c>
+      <c r="C328" s="3">
+        <v>46293.582743055602</v>
+      </c>
+      <c r="D328" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E328" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="F328" s="6">
+        <v>38995</v>
+      </c>
+      <c r="G328" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H328" s="2"/>
+      <c r="I328" s="2"/>
+      <c r="J328" s="2"/>
+      <c r="K328" s="2"/>
+      <c r="L328" s="2"/>
+      <c r="M328" s="2"/>
+      <c r="N328" s="2"/>
+      <c r="O328" s="2"/>
+      <c r="P328" s="2"/>
+      <c r="Q328" s="4"/>
+      <c r="R328" s="4"/>
+      <c r="S328" s="2"/>
+      <c r="T328" s="6">
+        <v>10</v>
+      </c>
+      <c r="U328" s="6">
+        <v>1</v>
+      </c>
+      <c r="V328" s="2"/>
+      <c r="W328" s="2"/>
+      <c r="X328" s="6"/>
+      <c r="Y328" s="6"/>
+      <c r="Z328" s="6"/>
+    </row>
+    <row r="329" spans="1:26">
+      <c r="A329" s="6">
+        <v>1156</v>
+      </c>
+      <c r="B329" s="3">
+        <v>46293.5871064815</v>
+      </c>
+      <c r="C329" s="3">
+        <v>46293.587488425903</v>
+      </c>
+      <c r="D329" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="E329" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F329" s="6">
+        <v>38930</v>
+      </c>
+      <c r="G329" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H329" s="2"/>
+      <c r="I329" s="2"/>
+      <c r="J329" s="2"/>
+      <c r="K329" s="2"/>
+      <c r="L329" s="2"/>
+      <c r="M329" s="2"/>
+      <c r="N329" s="2"/>
+      <c r="O329" s="2"/>
+      <c r="P329" s="2"/>
+      <c r="Q329" s="4"/>
+      <c r="R329" s="4"/>
+      <c r="S329" s="2"/>
+      <c r="T329" s="6">
+        <v>20</v>
+      </c>
+      <c r="U329" s="6">
+        <v>6</v>
+      </c>
+      <c r="V329" s="2"/>
+      <c r="W329" s="2"/>
+      <c r="X329" s="6"/>
+      <c r="Y329" s="6"/>
+      <c r="Z329" s="6"/>
+    </row>
+    <row r="330" spans="1:26">
+      <c r="A330" s="6">
+        <v>1157</v>
+      </c>
+      <c r="B330" s="3">
+        <v>46293.5878240741</v>
+      </c>
+      <c r="C330" s="3">
+        <v>46293.588969907403</v>
+      </c>
+      <c r="D330" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E330" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F330" s="6">
+        <v>38792</v>
+      </c>
+      <c r="G330" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H330" s="2"/>
+      <c r="I330" s="2"/>
+      <c r="J330" s="2"/>
+      <c r="K330" s="2"/>
+      <c r="L330" s="2"/>
+      <c r="M330" s="2"/>
+      <c r="N330" s="2"/>
+      <c r="O330" s="2"/>
+      <c r="P330" s="2"/>
+      <c r="Q330" s="4"/>
+      <c r="R330" s="4"/>
+      <c r="S330" s="2"/>
+      <c r="T330" s="6">
+        <v>5</v>
+      </c>
+      <c r="U330" s="6">
+        <v>8</v>
+      </c>
+      <c r="V330" s="2"/>
+      <c r="W330" s="2"/>
+      <c r="X330" s="6"/>
+      <c r="Y330" s="6"/>
+      <c r="Z330" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2CA6C781-83F6-45A7-A3D5-6D61DE8F68EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{81B4777D-CE65-4245-ABE1-7A9632BB76AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1253" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="482">
   <si>
     <t>Id</t>
   </si>
@@ -1467,6 +1467,24 @@
   </si>
   <si>
     <t>Cristian Alexis Posadas Lorenzo</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Peanuts_Linus%26Snoopy/c4ce60af-9ddb-47fc-b4c9-ea81f7bd273b_Starbucks%20Hospital%20A.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Despues/07CC6D17-055D-459A-9720-388498BCDE60_Starbucks%20Hospital%20A.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/Screenshot_20260928-145935.Drive_Laila%20America%20Mu%C3%B1oz.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/Screenshot_20260928-151127.Drive_Laila%20America%20Mu%C3%B1oz.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/Screenshot_20260928-151439.Drive_Laila%20America%20Mu%C3%B1oz.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17906307672903396997221993622528_Starbucks%20San%20Miguel.jpg</t>
   </si>
 </sst>
 </file>
@@ -1603,8 +1621,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z330" totalsRowShown="0">
-  <autoFilter ref="A1:Z330" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z336" totalsRowShown="0">
+  <autoFilter ref="A1:Z336" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1792,7 +1810,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1157" latestEventMarker="1603">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1163" latestEventMarker="1609">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2122,7 +2140,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z330"/>
+  <dimension ref="A1:Z336"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -14150,6 +14168,278 @@
       <c r="Y330" s="6"/>
       <c r="Z330" s="6"/>
     </row>
+    <row r="331" spans="1:26">
+      <c r="A331" s="6">
+        <v>1158</v>
+      </c>
+      <c r="B331" s="3">
+        <v>46293.596747685202</v>
+      </c>
+      <c r="C331" s="3">
+        <v>46293.597245370402</v>
+      </c>
+      <c r="D331" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E331" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F331" s="6">
+        <v>38529</v>
+      </c>
+      <c r="G331" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H331" s="2"/>
+      <c r="I331" s="2"/>
+      <c r="J331" s="2"/>
+      <c r="K331" s="2"/>
+      <c r="L331" s="2"/>
+      <c r="M331" s="2"/>
+      <c r="N331" s="2"/>
+      <c r="O331" s="2"/>
+      <c r="P331" s="2"/>
+      <c r="Q331" s="4"/>
+      <c r="R331" s="4"/>
+      <c r="S331" s="2"/>
+      <c r="T331" s="6">
+        <v>9</v>
+      </c>
+      <c r="U331" s="6">
+        <v>5</v>
+      </c>
+      <c r="V331" s="2"/>
+      <c r="W331" s="2"/>
+      <c r="X331" s="6"/>
+      <c r="Y331" s="6"/>
+      <c r="Z331" s="6"/>
+    </row>
+    <row r="332" spans="1:26">
+      <c r="A332" s="6">
+        <v>1159</v>
+      </c>
+      <c r="B332" s="3">
+        <v>46293.623263888898</v>
+      </c>
+      <c r="C332" s="3">
+        <v>46293.6248611111</v>
+      </c>
+      <c r="D332" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E332" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="F332" s="6">
+        <v>38447</v>
+      </c>
+      <c r="G332" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H332" s="2"/>
+      <c r="I332" s="2"/>
+      <c r="J332" s="2"/>
+      <c r="K332" s="2"/>
+      <c r="L332" s="2"/>
+      <c r="M332" s="2"/>
+      <c r="N332" s="2"/>
+      <c r="O332" s="2"/>
+      <c r="P332" s="2"/>
+      <c r="Q332" s="4"/>
+      <c r="R332" s="4"/>
+      <c r="S332" s="2"/>
+      <c r="T332" s="6"/>
+      <c r="U332" s="6"/>
+      <c r="V332" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="W332" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="X332" s="6"/>
+      <c r="Y332" s="6"/>
+      <c r="Z332" s="6"/>
+    </row>
+    <row r="333" spans="1:26">
+      <c r="A333" s="6">
+        <v>1160</v>
+      </c>
+      <c r="B333" s="3">
+        <v>46293.618946759299</v>
+      </c>
+      <c r="C333" s="3">
+        <v>46293.625381944403</v>
+      </c>
+      <c r="D333" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E333" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F333" s="6">
+        <v>38571</v>
+      </c>
+      <c r="G333" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H333" s="2"/>
+      <c r="I333" s="2"/>
+      <c r="J333" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="K333" s="2"/>
+      <c r="L333" s="2"/>
+      <c r="M333" s="2"/>
+      <c r="N333" s="2"/>
+      <c r="O333" s="2"/>
+      <c r="P333" s="2"/>
+      <c r="Q333" s="4"/>
+      <c r="R333" s="4"/>
+      <c r="S333" s="2"/>
+      <c r="T333" s="6"/>
+      <c r="U333" s="6"/>
+      <c r="V333" s="2"/>
+      <c r="W333" s="2"/>
+      <c r="X333" s="6"/>
+      <c r="Y333" s="6"/>
+      <c r="Z333" s="6"/>
+    </row>
+    <row r="334" spans="1:26">
+      <c r="A334" s="6">
+        <v>1161</v>
+      </c>
+      <c r="B334" s="3">
+        <v>46293.627662036997</v>
+      </c>
+      <c r="C334" s="3">
+        <v>46293.633252314801</v>
+      </c>
+      <c r="D334" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E334" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F334" s="6">
+        <v>38571</v>
+      </c>
+      <c r="G334" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H334" s="2"/>
+      <c r="I334" s="2"/>
+      <c r="J334" s="2"/>
+      <c r="K334" s="2"/>
+      <c r="L334" s="2"/>
+      <c r="M334" s="2"/>
+      <c r="N334" s="2"/>
+      <c r="O334" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="P334" s="2"/>
+      <c r="Q334" s="4"/>
+      <c r="R334" s="4"/>
+      <c r="S334" s="2"/>
+      <c r="T334" s="6"/>
+      <c r="U334" s="6"/>
+      <c r="V334" s="2"/>
+      <c r="W334" s="2"/>
+      <c r="X334" s="6"/>
+      <c r="Y334" s="6"/>
+      <c r="Z334" s="6"/>
+    </row>
+    <row r="335" spans="1:26">
+      <c r="A335" s="6">
+        <v>1162</v>
+      </c>
+      <c r="B335" s="3">
+        <v>46293.633368055598</v>
+      </c>
+      <c r="C335" s="3">
+        <v>46293.635798611103</v>
+      </c>
+      <c r="D335" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E335" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F335" s="6">
+        <v>38571</v>
+      </c>
+      <c r="G335" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H335" s="2"/>
+      <c r="I335" s="2"/>
+      <c r="J335" s="2"/>
+      <c r="K335" s="2"/>
+      <c r="L335" s="2"/>
+      <c r="M335" s="2"/>
+      <c r="N335" s="2"/>
+      <c r="O335" s="2"/>
+      <c r="P335" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="Q335" s="4"/>
+      <c r="R335" s="4"/>
+      <c r="S335" s="2"/>
+      <c r="T335" s="6"/>
+      <c r="U335" s="6"/>
+      <c r="V335" s="2"/>
+      <c r="W335" s="2"/>
+      <c r="X335" s="6"/>
+      <c r="Y335" s="6"/>
+      <c r="Z335" s="6"/>
+    </row>
+    <row r="336" spans="1:26">
+      <c r="A336" s="6">
+        <v>1163</v>
+      </c>
+      <c r="B336" s="3">
+        <v>46293.6414351852</v>
+      </c>
+      <c r="C336" s="3">
+        <v>46293.643344907403</v>
+      </c>
+      <c r="D336" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E336" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F336" s="6">
+        <v>38862</v>
+      </c>
+      <c r="G336" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H336" s="2"/>
+      <c r="I336" s="2"/>
+      <c r="J336" s="2"/>
+      <c r="K336" s="2"/>
+      <c r="L336" s="2"/>
+      <c r="M336" s="2"/>
+      <c r="N336" s="2"/>
+      <c r="O336" s="2"/>
+      <c r="P336" s="2"/>
+      <c r="Q336" s="4"/>
+      <c r="R336" s="4"/>
+      <c r="S336" s="2"/>
+      <c r="T336" s="6"/>
+      <c r="U336" s="6"/>
+      <c r="V336" s="2"/>
+      <c r="W336" s="2"/>
+      <c r="X336" s="6">
+        <v>22</v>
+      </c>
+      <c r="Y336" s="6">
+        <v>3</v>
+      </c>
+      <c r="Z336" s="6" t="s">
+        <v>481</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81B4777D-CE65-4245-ABE1-7A9632BB76AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{54028C68-8103-4A53-86E2-B397ECDC5ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -14400,7 +14400,7 @@
         <v>46293.6414351852</v>
       </c>
       <c r="C336" s="3">
-        <v>46293.643344907403</v>
+        <v>46293.64334490741</v>
       </c>
       <c r="D336" s="2" t="s">
         <v>54</v>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{54028C68-8103-4A53-86E2-B397ECDC5ED4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="336" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{987A32E6-FB14-40E8-8E0D-C1214491DCF9}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="496">
   <si>
     <t>Id</t>
   </si>
@@ -1485,6 +1485,48 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17906307672903396997221993622528_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38169@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Altavista</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/17906313916336472544954228358760_Starbucks%20Altavista.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38398@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Mexfund Pedregal</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/image_Starbucks%20Mexfund%20Pe.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17906326268534085397137724795773_Starbucks%20Grand%20San.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/Screenshot_20260928-155844.Drive_Laila%20America%20Mu%C3%B1oz.png</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/1790633020135949333741733695445_Starbucks%20Altavista.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG-20260928-WA0003_Starbucks%20San%20Jeroni.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/IMG-20260928-WA0004_Starbucks%20San%20Jeroni.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/BAD14A48-CD9F-45AA-9D6C-22C9BF4FD81E_Starbucks%20Mexfund%20Pe.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%207/IMG-20260928-WA0005_Starbucks%20San%20Jeroni.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG-20260928-WA0006_Starbucks%20San%20Jeroni.jpg</t>
   </si>
 </sst>
 </file>
@@ -1621,8 +1663,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z336" totalsRowShown="0">
-  <autoFilter ref="A1:Z336" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z349" totalsRowShown="0">
+  <autoFilter ref="A1:Z349" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1810,7 +1852,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1163" latestEventMarker="1609">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1176" latestEventMarker="1622">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2140,7 +2182,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z336"/>
+  <dimension ref="A1:Z349"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -12665,7 +12707,7 @@
       <c r="W297" s="2"/>
     </row>
     <row r="298" spans="1:26">
-      <c r="A298" s="6">
+      <c r="A298">
         <v>1125</v>
       </c>
       <c r="B298" s="3">
@@ -12680,7 +12722,7 @@
       <c r="E298" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F298" s="6">
+      <c r="F298">
         <v>38116</v>
       </c>
       <c r="G298" s="2" t="s">
@@ -12702,16 +12744,11 @@
       <c r="Q298" s="4"/>
       <c r="R298" s="4"/>
       <c r="S298" s="2"/>
-      <c r="T298" s="6"/>
-      <c r="U298" s="6"/>
       <c r="V298" s="2"/>
       <c r="W298" s="2"/>
-      <c r="X298" s="6"/>
-      <c r="Y298" s="6"/>
-      <c r="Z298" s="6"/>
     </row>
     <row r="299" spans="1:26">
-      <c r="A299" s="6">
+      <c r="A299">
         <v>1126</v>
       </c>
       <c r="B299" s="3">
@@ -12726,7 +12763,7 @@
       <c r="E299" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F299" s="6">
+      <c r="F299">
         <v>38580</v>
       </c>
       <c r="G299" s="2" t="s">
@@ -12746,16 +12783,11 @@
       <c r="Q299" s="4"/>
       <c r="R299" s="4"/>
       <c r="S299" s="2"/>
-      <c r="T299" s="6"/>
-      <c r="U299" s="6"/>
       <c r="V299" s="2"/>
       <c r="W299" s="2"/>
-      <c r="X299" s="6"/>
-      <c r="Y299" s="6"/>
-      <c r="Z299" s="6"/>
     </row>
     <row r="300" spans="1:26">
-      <c r="A300" s="6">
+      <c r="A300">
         <v>1127</v>
       </c>
       <c r="B300" s="3">
@@ -12770,7 +12802,7 @@
       <c r="E300" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F300" s="6">
+      <c r="F300">
         <v>38580</v>
       </c>
       <c r="G300" s="2" t="s">
@@ -12790,16 +12822,11 @@
       <c r="Q300" s="4"/>
       <c r="R300" s="4"/>
       <c r="S300" s="2"/>
-      <c r="T300" s="6"/>
-      <c r="U300" s="6"/>
       <c r="V300" s="2"/>
       <c r="W300" s="2"/>
-      <c r="X300" s="6"/>
-      <c r="Y300" s="6"/>
-      <c r="Z300" s="6"/>
     </row>
     <row r="301" spans="1:26">
-      <c r="A301" s="6">
+      <c r="A301">
         <v>1128</v>
       </c>
       <c r="B301" s="3">
@@ -12814,7 +12841,7 @@
       <c r="E301" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F301" s="6">
+      <c r="F301">
         <v>38447</v>
       </c>
       <c r="G301" s="2" t="s">
@@ -12834,16 +12861,11 @@
       <c r="Q301" s="4"/>
       <c r="R301" s="4"/>
       <c r="S301" s="2"/>
-      <c r="T301" s="6"/>
-      <c r="U301" s="6"/>
       <c r="V301" s="2"/>
       <c r="W301" s="2"/>
-      <c r="X301" s="6"/>
-      <c r="Y301" s="6"/>
-      <c r="Z301" s="6"/>
     </row>
     <row r="302" spans="1:26">
-      <c r="A302" s="6">
+      <c r="A302">
         <v>1129</v>
       </c>
       <c r="B302" s="3">
@@ -12858,7 +12880,7 @@
       <c r="E302" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F302" s="6">
+      <c r="F302">
         <v>38447</v>
       </c>
       <c r="G302" s="2" t="s">
@@ -12878,16 +12900,11 @@
       <c r="Q302" s="4"/>
       <c r="R302" s="4"/>
       <c r="S302" s="2"/>
-      <c r="T302" s="6"/>
-      <c r="U302" s="6"/>
       <c r="V302" s="2"/>
       <c r="W302" s="2"/>
-      <c r="X302" s="6"/>
-      <c r="Y302" s="6"/>
-      <c r="Z302" s="6"/>
     </row>
     <row r="303" spans="1:26">
-      <c r="A303" s="6">
+      <c r="A303">
         <v>1130</v>
       </c>
       <c r="B303" s="3">
@@ -12902,7 +12919,7 @@
       <c r="E303" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F303" s="6">
+      <c r="F303">
         <v>38447</v>
       </c>
       <c r="G303" s="2" t="s">
@@ -12922,16 +12939,11 @@
       <c r="Q303" s="4"/>
       <c r="R303" s="4"/>
       <c r="S303" s="2"/>
-      <c r="T303" s="6"/>
-      <c r="U303" s="6"/>
       <c r="V303" s="2"/>
       <c r="W303" s="2"/>
-      <c r="X303" s="6"/>
-      <c r="Y303" s="6"/>
-      <c r="Z303" s="6"/>
     </row>
     <row r="304" spans="1:26">
-      <c r="A304" s="6">
+      <c r="A304">
         <v>1131</v>
       </c>
       <c r="B304" s="3">
@@ -12946,7 +12958,7 @@
       <c r="E304" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F304" s="6">
+      <c r="F304">
         <v>38580</v>
       </c>
       <c r="G304" s="2" t="s">
@@ -12966,16 +12978,11 @@
       <c r="Q304" s="4"/>
       <c r="R304" s="4"/>
       <c r="S304" s="2"/>
-      <c r="T304" s="6"/>
-      <c r="U304" s="6"/>
       <c r="V304" s="2"/>
       <c r="W304" s="2"/>
-      <c r="X304" s="6"/>
-      <c r="Y304" s="6"/>
-      <c r="Z304" s="6"/>
     </row>
     <row r="305" spans="1:26">
-      <c r="A305" s="6">
+      <c r="A305">
         <v>1132</v>
       </c>
       <c r="B305" s="3">
@@ -12990,7 +12997,7 @@
       <c r="E305" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F305" s="6">
+      <c r="F305">
         <v>38580</v>
       </c>
       <c r="G305" s="2" t="s">
@@ -13010,16 +13017,11 @@
       <c r="Q305" s="4"/>
       <c r="R305" s="4"/>
       <c r="S305" s="2"/>
-      <c r="T305" s="6"/>
-      <c r="U305" s="6"/>
       <c r="V305" s="2"/>
       <c r="W305" s="2"/>
-      <c r="X305" s="6"/>
-      <c r="Y305" s="6"/>
-      <c r="Z305" s="6"/>
     </row>
     <row r="306" spans="1:26">
-      <c r="A306" s="6">
+      <c r="A306">
         <v>1133</v>
       </c>
       <c r="B306" s="3">
@@ -13034,7 +13036,7 @@
       <c r="E306" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F306" s="6">
+      <c r="F306">
         <v>38447</v>
       </c>
       <c r="G306" s="2" t="s">
@@ -13054,16 +13056,11 @@
       <c r="Q306" s="4"/>
       <c r="R306" s="4"/>
       <c r="S306" s="2"/>
-      <c r="T306" s="6"/>
-      <c r="U306" s="6"/>
       <c r="V306" s="2"/>
       <c r="W306" s="2"/>
-      <c r="X306" s="6"/>
-      <c r="Y306" s="6"/>
-      <c r="Z306" s="6"/>
     </row>
     <row r="307" spans="1:26">
-      <c r="A307" s="6">
+      <c r="A307">
         <v>1134</v>
       </c>
       <c r="B307" s="3">
@@ -13078,7 +13075,7 @@
       <c r="E307" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F307" s="6">
+      <c r="F307">
         <v>38270</v>
       </c>
       <c r="G307" s="2" t="s">
@@ -13096,20 +13093,17 @@
       <c r="Q307" s="4"/>
       <c r="R307" s="4"/>
       <c r="S307" s="2"/>
-      <c r="T307" s="6">
+      <c r="T307">
         <v>8</v>
       </c>
-      <c r="U307" s="6">
+      <c r="U307">
         <v>3</v>
       </c>
       <c r="V307" s="2"/>
       <c r="W307" s="2"/>
-      <c r="X307" s="6"/>
-      <c r="Y307" s="6"/>
-      <c r="Z307" s="6"/>
     </row>
     <row r="308" spans="1:26">
-      <c r="A308" s="6">
+      <c r="A308">
         <v>1135</v>
       </c>
       <c r="B308" s="3">
@@ -13124,7 +13118,7 @@
       <c r="E308" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F308" s="6">
+      <c r="F308">
         <v>38580</v>
       </c>
       <c r="G308" s="2" t="s">
@@ -13144,16 +13138,11 @@
       <c r="Q308" s="4"/>
       <c r="R308" s="4"/>
       <c r="S308" s="2"/>
-      <c r="T308" s="6"/>
-      <c r="U308" s="6"/>
       <c r="V308" s="2"/>
       <c r="W308" s="2"/>
-      <c r="X308" s="6"/>
-      <c r="Y308" s="6"/>
-      <c r="Z308" s="6"/>
     </row>
     <row r="309" spans="1:26">
-      <c r="A309" s="6">
+      <c r="A309">
         <v>1136</v>
       </c>
       <c r="B309" s="3">
@@ -13168,7 +13157,7 @@
       <c r="E309" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F309" s="6">
+      <c r="F309">
         <v>38447</v>
       </c>
       <c r="G309" s="2" t="s">
@@ -13188,16 +13177,11 @@
       <c r="Q309" s="4"/>
       <c r="R309" s="4"/>
       <c r="S309" s="2"/>
-      <c r="T309" s="6"/>
-      <c r="U309" s="6"/>
       <c r="V309" s="2"/>
       <c r="W309" s="2"/>
-      <c r="X309" s="6"/>
-      <c r="Y309" s="6"/>
-      <c r="Z309" s="6"/>
     </row>
     <row r="310" spans="1:26">
-      <c r="A310" s="6">
+      <c r="A310">
         <v>1137</v>
       </c>
       <c r="B310" s="3">
@@ -13212,7 +13196,7 @@
       <c r="E310" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F310" s="6">
+      <c r="F310">
         <v>38374</v>
       </c>
       <c r="G310" s="2" t="s">
@@ -13230,20 +13214,17 @@
       <c r="Q310" s="4"/>
       <c r="R310" s="4"/>
       <c r="S310" s="2"/>
-      <c r="T310" s="6">
+      <c r="T310">
         <v>9</v>
       </c>
-      <c r="U310" s="6">
+      <c r="U310">
         <v>2</v>
       </c>
       <c r="V310" s="2"/>
       <c r="W310" s="2"/>
-      <c r="X310" s="6"/>
-      <c r="Y310" s="6"/>
-      <c r="Z310" s="6"/>
     </row>
     <row r="311" spans="1:26">
-      <c r="A311" s="6">
+      <c r="A311">
         <v>1138</v>
       </c>
       <c r="B311" s="3">
@@ -13258,7 +13239,7 @@
       <c r="E311" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F311" s="6">
+      <c r="F311">
         <v>38580</v>
       </c>
       <c r="G311" s="2" t="s">
@@ -13278,16 +13259,11 @@
       <c r="Q311" s="4"/>
       <c r="R311" s="4"/>
       <c r="S311" s="2"/>
-      <c r="T311" s="6"/>
-      <c r="U311" s="6"/>
       <c r="V311" s="2"/>
       <c r="W311" s="2"/>
-      <c r="X311" s="6"/>
-      <c r="Y311" s="6"/>
-      <c r="Z311" s="6"/>
     </row>
     <row r="312" spans="1:26">
-      <c r="A312" s="6">
+      <c r="A312">
         <v>1139</v>
       </c>
       <c r="B312" s="3">
@@ -13302,7 +13278,7 @@
       <c r="E312" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="F312" s="6">
+      <c r="F312">
         <v>38845</v>
       </c>
       <c r="G312" s="2" t="s">
@@ -13320,20 +13296,17 @@
       <c r="Q312" s="4"/>
       <c r="R312" s="4"/>
       <c r="S312" s="2"/>
-      <c r="T312" s="6">
+      <c r="T312">
         <v>8</v>
       </c>
-      <c r="U312" s="6">
+      <c r="U312">
         <v>2</v>
       </c>
       <c r="V312" s="2"/>
       <c r="W312" s="2"/>
-      <c r="X312" s="6"/>
-      <c r="Y312" s="6"/>
-      <c r="Z312" s="6"/>
     </row>
     <row r="313" spans="1:26">
-      <c r="A313" s="6">
+      <c r="A313">
         <v>1140</v>
       </c>
       <c r="B313" s="3">
@@ -13348,7 +13321,7 @@
       <c r="E313" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="F313" s="6">
+      <c r="F313">
         <v>38694</v>
       </c>
       <c r="G313" s="2" t="s">
@@ -13366,20 +13339,17 @@
       <c r="Q313" s="4"/>
       <c r="R313" s="4"/>
       <c r="S313" s="2"/>
-      <c r="T313" s="6">
+      <c r="T313">
         <v>5</v>
       </c>
-      <c r="U313" s="6">
+      <c r="U313">
         <v>8</v>
       </c>
       <c r="V313" s="2"/>
       <c r="W313" s="2"/>
-      <c r="X313" s="6"/>
-      <c r="Y313" s="6"/>
-      <c r="Z313" s="6"/>
     </row>
     <row r="314" spans="1:26">
-      <c r="A314" s="6">
+      <c r="A314">
         <v>1141</v>
       </c>
       <c r="B314" s="3">
@@ -13394,7 +13364,7 @@
       <c r="E314" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="F314" s="6">
+      <c r="F314">
         <v>38460</v>
       </c>
       <c r="G314" s="2" t="s">
@@ -13412,20 +13382,17 @@
       <c r="Q314" s="4"/>
       <c r="R314" s="4"/>
       <c r="S314" s="2"/>
-      <c r="T314" s="6">
+      <c r="T314">
         <v>11</v>
       </c>
-      <c r="U314" s="6">
+      <c r="U314">
         <v>0</v>
       </c>
       <c r="V314" s="2"/>
       <c r="W314" s="2"/>
-      <c r="X314" s="6"/>
-      <c r="Y314" s="6"/>
-      <c r="Z314" s="6"/>
     </row>
     <row r="315" spans="1:26">
-      <c r="A315" s="6">
+      <c r="A315">
         <v>1142</v>
       </c>
       <c r="B315" s="3">
@@ -13440,7 +13407,7 @@
       <c r="E315" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F315" s="6">
+      <c r="F315">
         <v>38580</v>
       </c>
       <c r="G315" s="2" t="s">
@@ -13464,16 +13431,11 @@
       <c r="S315" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="T315" s="6"/>
-      <c r="U315" s="6"/>
       <c r="V315" s="2"/>
       <c r="W315" s="2"/>
-      <c r="X315" s="6"/>
-      <c r="Y315" s="6"/>
-      <c r="Z315" s="6"/>
     </row>
     <row r="316" spans="1:26">
-      <c r="A316" s="6">
+      <c r="A316">
         <v>1143</v>
       </c>
       <c r="B316" s="3">
@@ -13488,7 +13450,7 @@
       <c r="E316" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="F316" s="6">
+      <c r="F316">
         <v>38924</v>
       </c>
       <c r="G316" s="2" t="s">
@@ -13506,20 +13468,17 @@
       <c r="Q316" s="4"/>
       <c r="R316" s="4"/>
       <c r="S316" s="2"/>
-      <c r="T316" s="6">
+      <c r="T316">
         <v>12</v>
       </c>
-      <c r="U316" s="6">
+      <c r="U316">
         <v>0</v>
       </c>
       <c r="V316" s="2"/>
       <c r="W316" s="2"/>
-      <c r="X316" s="6"/>
-      <c r="Y316" s="6"/>
-      <c r="Z316" s="6"/>
     </row>
     <row r="317" spans="1:26">
-      <c r="A317" s="6">
+      <c r="A317">
         <v>1144</v>
       </c>
       <c r="B317" s="3">
@@ -13534,7 +13493,7 @@
       <c r="E317" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="F317" s="6">
+      <c r="F317">
         <v>38674</v>
       </c>
       <c r="G317" s="2" t="s">
@@ -13552,20 +13511,17 @@
       <c r="Q317" s="4"/>
       <c r="R317" s="4"/>
       <c r="S317" s="2"/>
-      <c r="T317" s="6">
+      <c r="T317">
         <v>6</v>
       </c>
-      <c r="U317" s="6">
+      <c r="U317">
         <v>4</v>
       </c>
       <c r="V317" s="2"/>
       <c r="W317" s="2"/>
-      <c r="X317" s="6"/>
-      <c r="Y317" s="6"/>
-      <c r="Z317" s="6"/>
     </row>
     <row r="318" spans="1:26">
-      <c r="A318" s="6">
+      <c r="A318">
         <v>1145</v>
       </c>
       <c r="B318" s="3">
@@ -13580,7 +13536,7 @@
       <c r="E318" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F318" s="6">
+      <c r="F318">
         <v>38448</v>
       </c>
       <c r="G318" s="2" t="s">
@@ -13600,16 +13556,11 @@
       <c r="Q318" s="4"/>
       <c r="R318" s="4"/>
       <c r="S318" s="2"/>
-      <c r="T318" s="6"/>
-      <c r="U318" s="6"/>
       <c r="V318" s="2"/>
       <c r="W318" s="2"/>
-      <c r="X318" s="6"/>
-      <c r="Y318" s="6"/>
-      <c r="Z318" s="6"/>
     </row>
     <row r="319" spans="1:26">
-      <c r="A319" s="6">
+      <c r="A319">
         <v>1146</v>
       </c>
       <c r="B319" s="3">
@@ -13624,7 +13575,7 @@
       <c r="E319" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="F319" s="6">
+      <c r="F319">
         <v>38136</v>
       </c>
       <c r="G319" s="2" t="s">
@@ -13642,20 +13593,17 @@
       <c r="Q319" s="4"/>
       <c r="R319" s="4"/>
       <c r="S319" s="2"/>
-      <c r="T319" s="6">
+      <c r="T319">
         <v>9</v>
       </c>
-      <c r="U319" s="6">
+      <c r="U319">
         <v>2</v>
       </c>
       <c r="V319" s="2"/>
       <c r="W319" s="2"/>
-      <c r="X319" s="6"/>
-      <c r="Y319" s="6"/>
-      <c r="Z319" s="6"/>
     </row>
     <row r="320" spans="1:26">
-      <c r="A320" s="6">
+      <c r="A320">
         <v>1147</v>
       </c>
       <c r="B320" s="3">
@@ -13670,7 +13618,7 @@
       <c r="E320" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F320" s="6">
+      <c r="F320">
         <v>38580</v>
       </c>
       <c r="G320" s="2" t="s">
@@ -13688,22 +13636,20 @@
       <c r="Q320" s="4"/>
       <c r="R320" s="4"/>
       <c r="S320" s="2"/>
-      <c r="T320" s="6"/>
-      <c r="U320" s="6"/>
       <c r="V320" s="2"/>
       <c r="W320" s="2"/>
-      <c r="X320" s="6">
+      <c r="X320">
         <v>30</v>
       </c>
-      <c r="Y320" s="6">
+      <c r="Y320">
         <v>2</v>
       </c>
-      <c r="Z320" s="6" t="s">
+      <c r="Z320" t="s">
         <v>462</v>
       </c>
     </row>
     <row r="321" spans="1:26">
-      <c r="A321" s="6">
+      <c r="A321">
         <v>1148</v>
       </c>
       <c r="B321" s="3">
@@ -13718,7 +13664,7 @@
       <c r="E321" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="F321" s="6">
+      <c r="F321">
         <v>38431</v>
       </c>
       <c r="G321" s="2" t="s">
@@ -13736,20 +13682,17 @@
       <c r="Q321" s="4"/>
       <c r="R321" s="4"/>
       <c r="S321" s="2"/>
-      <c r="T321" s="6">
+      <c r="T321">
         <v>11</v>
       </c>
-      <c r="U321" s="6">
+      <c r="U321">
         <v>3</v>
       </c>
       <c r="V321" s="2"/>
       <c r="W321" s="2"/>
-      <c r="X321" s="6"/>
-      <c r="Y321" s="6"/>
-      <c r="Z321" s="6"/>
     </row>
     <row r="322" spans="1:26">
-      <c r="A322" s="6">
+      <c r="A322">
         <v>1149</v>
       </c>
       <c r="B322" s="3">
@@ -13764,7 +13707,7 @@
       <c r="E322" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F322" s="6">
+      <c r="F322">
         <v>38447</v>
       </c>
       <c r="G322" s="2" t="s">
@@ -13788,16 +13731,11 @@
       <c r="S322" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="T322" s="6"/>
-      <c r="U322" s="6"/>
       <c r="V322" s="2"/>
       <c r="W322" s="2"/>
-      <c r="X322" s="6"/>
-      <c r="Y322" s="6"/>
-      <c r="Z322" s="6"/>
     </row>
     <row r="323" spans="1:26">
-      <c r="A323" s="6">
+      <c r="A323">
         <v>1150</v>
       </c>
       <c r="B323" s="3">
@@ -13812,7 +13750,7 @@
       <c r="E323" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F323" s="6">
+      <c r="F323">
         <v>38333</v>
       </c>
       <c r="G323" s="2" t="s">
@@ -13830,22 +13768,20 @@
       <c r="Q323" s="4"/>
       <c r="R323" s="4"/>
       <c r="S323" s="2"/>
-      <c r="T323" s="6"/>
-      <c r="U323" s="6"/>
       <c r="V323" s="2"/>
       <c r="W323" s="2"/>
-      <c r="X323" s="6">
+      <c r="X323">
         <v>40</v>
       </c>
-      <c r="Y323" s="6">
+      <c r="Y323">
         <v>4</v>
       </c>
-      <c r="Z323" s="6" t="s">
+      <c r="Z323" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="324" spans="1:26">
-      <c r="A324" s="6">
+      <c r="A324">
         <v>1151</v>
       </c>
       <c r="B324" s="3">
@@ -13860,7 +13796,7 @@
       <c r="E324" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="F324" s="6">
+      <c r="F324">
         <v>38937</v>
       </c>
       <c r="G324" s="2" t="s">
@@ -13878,20 +13814,17 @@
       <c r="Q324" s="4"/>
       <c r="R324" s="4"/>
       <c r="S324" s="2"/>
-      <c r="T324" s="6">
+      <c r="T324">
         <v>13</v>
       </c>
-      <c r="U324" s="6">
+      <c r="U324">
         <v>2</v>
       </c>
       <c r="V324" s="2"/>
       <c r="W324" s="2"/>
-      <c r="X324" s="6"/>
-      <c r="Y324" s="6"/>
-      <c r="Z324" s="6"/>
     </row>
     <row r="325" spans="1:26">
-      <c r="A325" s="6">
+      <c r="A325">
         <v>1152</v>
       </c>
       <c r="B325" s="3">
@@ -13906,7 +13839,7 @@
       <c r="E325" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F325" s="6">
+      <c r="F325">
         <v>38580</v>
       </c>
       <c r="G325" s="2" t="s">
@@ -13924,20 +13857,15 @@
       <c r="Q325" s="4"/>
       <c r="R325" s="4"/>
       <c r="S325" s="2"/>
-      <c r="T325" s="6"/>
-      <c r="U325" s="6"/>
       <c r="V325" s="2" t="s">
         <v>469</v>
       </c>
       <c r="W325" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="X325" s="6"/>
-      <c r="Y325" s="6"/>
-      <c r="Z325" s="6"/>
     </row>
     <row r="326" spans="1:26">
-      <c r="A326" s="6">
+      <c r="A326">
         <v>1153</v>
       </c>
       <c r="B326" s="3">
@@ -13952,7 +13880,7 @@
       <c r="E326" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="F326" s="6">
+      <c r="F326">
         <v>38677</v>
       </c>
       <c r="G326" s="2" t="s">
@@ -13970,20 +13898,17 @@
       <c r="Q326" s="4"/>
       <c r="R326" s="4"/>
       <c r="S326" s="2"/>
-      <c r="T326" s="6">
+      <c r="T326">
         <v>13</v>
       </c>
-      <c r="U326" s="6">
+      <c r="U326">
         <v>3</v>
       </c>
       <c r="V326" s="2"/>
       <c r="W326" s="2"/>
-      <c r="X326" s="6"/>
-      <c r="Y326" s="6"/>
-      <c r="Z326" s="6"/>
     </row>
     <row r="327" spans="1:26">
-      <c r="A327" s="6">
+      <c r="A327">
         <v>1154</v>
       </c>
       <c r="B327" s="3">
@@ -13998,7 +13923,7 @@
       <c r="E327" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F327" s="6">
+      <c r="F327">
         <v>38456</v>
       </c>
       <c r="G327" s="2" t="s">
@@ -14016,22 +13941,20 @@
       <c r="Q327" s="4"/>
       <c r="R327" s="4"/>
       <c r="S327" s="2"/>
-      <c r="T327" s="6"/>
-      <c r="U327" s="6"/>
       <c r="V327" s="2"/>
       <c r="W327" s="2"/>
-      <c r="X327" s="6">
+      <c r="X327">
         <v>36</v>
       </c>
-      <c r="Y327" s="6">
+      <c r="Y327">
         <v>6</v>
       </c>
-      <c r="Z327" s="6" t="s">
+      <c r="Z327" t="s">
         <v>473</v>
       </c>
     </row>
     <row r="328" spans="1:26">
-      <c r="A328" s="6">
+      <c r="A328">
         <v>1155</v>
       </c>
       <c r="B328" s="3">
@@ -14046,7 +13969,7 @@
       <c r="E328" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F328" s="6">
+      <c r="F328">
         <v>38995</v>
       </c>
       <c r="G328" s="2" t="s">
@@ -14064,20 +13987,17 @@
       <c r="Q328" s="4"/>
       <c r="R328" s="4"/>
       <c r="S328" s="2"/>
-      <c r="T328" s="6">
+      <c r="T328">
         <v>10</v>
       </c>
-      <c r="U328" s="6">
+      <c r="U328">
         <v>1</v>
       </c>
       <c r="V328" s="2"/>
       <c r="W328" s="2"/>
-      <c r="X328" s="6"/>
-      <c r="Y328" s="6"/>
-      <c r="Z328" s="6"/>
     </row>
     <row r="329" spans="1:26">
-      <c r="A329" s="6">
+      <c r="A329">
         <v>1156</v>
       </c>
       <c r="B329" s="3">
@@ -14092,7 +14012,7 @@
       <c r="E329" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="F329" s="6">
+      <c r="F329">
         <v>38930</v>
       </c>
       <c r="G329" s="2" t="s">
@@ -14110,20 +14030,17 @@
       <c r="Q329" s="4"/>
       <c r="R329" s="4"/>
       <c r="S329" s="2"/>
-      <c r="T329" s="6">
+      <c r="T329">
         <v>20</v>
       </c>
-      <c r="U329" s="6">
+      <c r="U329">
         <v>6</v>
       </c>
       <c r="V329" s="2"/>
       <c r="W329" s="2"/>
-      <c r="X329" s="6"/>
-      <c r="Y329" s="6"/>
-      <c r="Z329" s="6"/>
     </row>
     <row r="330" spans="1:26">
-      <c r="A330" s="6">
+      <c r="A330">
         <v>1157</v>
       </c>
       <c r="B330" s="3">
@@ -14138,7 +14055,7 @@
       <c r="E330" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="F330" s="6">
+      <c r="F330">
         <v>38792</v>
       </c>
       <c r="G330" s="2" t="s">
@@ -14156,20 +14073,17 @@
       <c r="Q330" s="4"/>
       <c r="R330" s="4"/>
       <c r="S330" s="2"/>
-      <c r="T330" s="6">
+      <c r="T330">
         <v>5</v>
       </c>
-      <c r="U330" s="6">
+      <c r="U330">
         <v>8</v>
       </c>
       <c r="V330" s="2"/>
       <c r="W330" s="2"/>
-      <c r="X330" s="6"/>
-      <c r="Y330" s="6"/>
-      <c r="Z330" s="6"/>
     </row>
     <row r="331" spans="1:26">
-      <c r="A331" s="6">
+      <c r="A331">
         <v>1158</v>
       </c>
       <c r="B331" s="3">
@@ -14184,7 +14098,7 @@
       <c r="E331" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="F331" s="6">
+      <c r="F331">
         <v>38529</v>
       </c>
       <c r="G331" s="2" t="s">
@@ -14202,20 +14116,17 @@
       <c r="Q331" s="4"/>
       <c r="R331" s="4"/>
       <c r="S331" s="2"/>
-      <c r="T331" s="6">
+      <c r="T331">
         <v>9</v>
       </c>
-      <c r="U331" s="6">
+      <c r="U331">
         <v>5</v>
       </c>
       <c r="V331" s="2"/>
       <c r="W331" s="2"/>
-      <c r="X331" s="6"/>
-      <c r="Y331" s="6"/>
-      <c r="Z331" s="6"/>
     </row>
     <row r="332" spans="1:26">
-      <c r="A332" s="6">
+      <c r="A332">
         <v>1159</v>
       </c>
       <c r="B332" s="3">
@@ -14230,7 +14141,7 @@
       <c r="E332" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="F332" s="6">
+      <c r="F332">
         <v>38447</v>
       </c>
       <c r="G332" s="2" t="s">
@@ -14248,20 +14159,15 @@
       <c r="Q332" s="4"/>
       <c r="R332" s="4"/>
       <c r="S332" s="2"/>
-      <c r="T332" s="6"/>
-      <c r="U332" s="6"/>
       <c r="V332" s="2" t="s">
         <v>476</v>
       </c>
       <c r="W332" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="X332" s="6"/>
-      <c r="Y332" s="6"/>
-      <c r="Z332" s="6"/>
     </row>
     <row r="333" spans="1:26">
-      <c r="A333" s="6">
+      <c r="A333">
         <v>1160</v>
       </c>
       <c r="B333" s="3">
@@ -14276,7 +14182,7 @@
       <c r="E333" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F333" s="6">
+      <c r="F333">
         <v>38571</v>
       </c>
       <c r="G333" s="2" t="s">
@@ -14296,16 +14202,11 @@
       <c r="Q333" s="4"/>
       <c r="R333" s="4"/>
       <c r="S333" s="2"/>
-      <c r="T333" s="6"/>
-      <c r="U333" s="6"/>
       <c r="V333" s="2"/>
       <c r="W333" s="2"/>
-      <c r="X333" s="6"/>
-      <c r="Y333" s="6"/>
-      <c r="Z333" s="6"/>
     </row>
     <row r="334" spans="1:26">
-      <c r="A334" s="6">
+      <c r="A334">
         <v>1161</v>
       </c>
       <c r="B334" s="3">
@@ -14320,7 +14221,7 @@
       <c r="E334" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F334" s="6">
+      <c r="F334">
         <v>38571</v>
       </c>
       <c r="G334" s="2" t="s">
@@ -14340,16 +14241,11 @@
       <c r="Q334" s="4"/>
       <c r="R334" s="4"/>
       <c r="S334" s="2"/>
-      <c r="T334" s="6"/>
-      <c r="U334" s="6"/>
       <c r="V334" s="2"/>
       <c r="W334" s="2"/>
-      <c r="X334" s="6"/>
-      <c r="Y334" s="6"/>
-      <c r="Z334" s="6"/>
     </row>
     <row r="335" spans="1:26">
-      <c r="A335" s="6">
+      <c r="A335">
         <v>1162</v>
       </c>
       <c r="B335" s="3">
@@ -14364,7 +14260,7 @@
       <c r="E335" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F335" s="6">
+      <c r="F335">
         <v>38571</v>
       </c>
       <c r="G335" s="2" t="s">
@@ -14384,16 +14280,11 @@
       <c r="Q335" s="4"/>
       <c r="R335" s="4"/>
       <c r="S335" s="2"/>
-      <c r="T335" s="6"/>
-      <c r="U335" s="6"/>
       <c r="V335" s="2"/>
       <c r="W335" s="2"/>
-      <c r="X335" s="6"/>
-      <c r="Y335" s="6"/>
-      <c r="Z335" s="6"/>
     </row>
     <row r="336" spans="1:26">
-      <c r="A336" s="6">
+      <c r="A336">
         <v>1163</v>
       </c>
       <c r="B336" s="3">
@@ -14408,7 +14299,7 @@
       <c r="E336" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F336" s="6">
+      <c r="F336">
         <v>38862</v>
       </c>
       <c r="G336" s="2" t="s">
@@ -14426,19 +14317,583 @@
       <c r="Q336" s="4"/>
       <c r="R336" s="4"/>
       <c r="S336" s="2"/>
-      <c r="T336" s="6"/>
-      <c r="U336" s="6"/>
       <c r="V336" s="2"/>
       <c r="W336" s="2"/>
-      <c r="X336" s="6">
+      <c r="X336">
         <v>22</v>
       </c>
-      <c r="Y336" s="6">
+      <c r="Y336">
         <v>3</v>
       </c>
-      <c r="Z336" s="6" t="s">
+      <c r="Z336" t="s">
         <v>481</v>
       </c>
+    </row>
+    <row r="337" spans="1:26">
+      <c r="A337">
+        <v>1164</v>
+      </c>
+      <c r="B337" s="3">
+        <v>46293.645925925899</v>
+      </c>
+      <c r="C337" s="3">
+        <v>46293.650706018503</v>
+      </c>
+      <c r="D337" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E337" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F337">
+        <v>38169</v>
+      </c>
+      <c r="G337" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H337" s="2"/>
+      <c r="I337" s="2"/>
+      <c r="J337" s="2"/>
+      <c r="K337" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="L337" s="2"/>
+      <c r="M337" s="2"/>
+      <c r="N337" s="2"/>
+      <c r="O337" s="2"/>
+      <c r="P337" s="2"/>
+      <c r="Q337" s="4"/>
+      <c r="R337" s="4"/>
+      <c r="S337" s="2"/>
+      <c r="V337" s="2"/>
+      <c r="W337" s="2"/>
+    </row>
+    <row r="338" spans="1:26">
+      <c r="A338">
+        <v>1165</v>
+      </c>
+      <c r="B338" s="3">
+        <v>46293.651099536997</v>
+      </c>
+      <c r="C338" s="3">
+        <v>46293.651967592603</v>
+      </c>
+      <c r="D338" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E338" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F338">
+        <v>38169</v>
+      </c>
+      <c r="G338" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H338" s="2"/>
+      <c r="I338" s="2"/>
+      <c r="J338" s="2"/>
+      <c r="K338" s="2"/>
+      <c r="L338" s="2"/>
+      <c r="M338" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N338" s="2"/>
+      <c r="O338" s="2"/>
+      <c r="P338" s="2"/>
+      <c r="Q338" s="4"/>
+      <c r="R338" s="4"/>
+      <c r="S338" s="2"/>
+      <c r="V338" s="2"/>
+      <c r="W338" s="2"/>
+    </row>
+    <row r="339" spans="1:26">
+      <c r="A339">
+        <v>1166</v>
+      </c>
+      <c r="B339" s="3">
+        <v>46293.652546296304</v>
+      </c>
+      <c r="C339" s="3">
+        <v>46293.657719907402</v>
+      </c>
+      <c r="D339" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E339" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F339">
+        <v>38398</v>
+      </c>
+      <c r="G339" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H339" s="2"/>
+      <c r="I339" s="2"/>
+      <c r="J339" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="K339" s="2"/>
+      <c r="L339" s="2"/>
+      <c r="M339" s="2"/>
+      <c r="N339" s="2"/>
+      <c r="O339" s="2"/>
+      <c r="P339" s="2"/>
+      <c r="Q339" s="4"/>
+      <c r="R339" s="4"/>
+      <c r="S339" s="2"/>
+      <c r="V339" s="2"/>
+      <c r="W339" s="2"/>
+    </row>
+    <row r="340" spans="1:26">
+      <c r="A340">
+        <v>1167</v>
+      </c>
+      <c r="B340" s="3">
+        <v>46293.658090277801</v>
+      </c>
+      <c r="C340" s="3">
+        <v>46293.658275463</v>
+      </c>
+      <c r="D340" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E340" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F340">
+        <v>38398</v>
+      </c>
+      <c r="G340" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="H340" s="2"/>
+      <c r="I340" s="2"/>
+      <c r="J340" s="2"/>
+      <c r="K340" s="2"/>
+      <c r="L340" s="2"/>
+      <c r="M340" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="N340" s="2"/>
+      <c r="O340" s="2"/>
+      <c r="P340" s="2"/>
+      <c r="Q340" s="4"/>
+      <c r="R340" s="4"/>
+      <c r="S340" s="2"/>
+      <c r="V340" s="2"/>
+      <c r="W340" s="2"/>
+    </row>
+    <row r="341" spans="1:26">
+      <c r="A341" s="6">
+        <v>1168</v>
+      </c>
+      <c r="B341" s="3">
+        <v>46293.651331018496</v>
+      </c>
+      <c r="C341" s="3">
+        <v>46293.6652777778</v>
+      </c>
+      <c r="D341" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E341" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F341" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G341" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H341" s="2"/>
+      <c r="I341" s="2"/>
+      <c r="J341" s="2"/>
+      <c r="K341" s="2"/>
+      <c r="L341" s="2"/>
+      <c r="M341" s="2"/>
+      <c r="N341" s="2"/>
+      <c r="O341" s="2"/>
+      <c r="P341" s="2"/>
+      <c r="Q341" s="4"/>
+      <c r="R341" s="4"/>
+      <c r="S341" s="2"/>
+      <c r="T341" s="6"/>
+      <c r="U341" s="6"/>
+      <c r="V341" s="2"/>
+      <c r="W341" s="2"/>
+      <c r="X341" s="6">
+        <v>0</v>
+      </c>
+      <c r="Y341" s="6">
+        <v>3</v>
+      </c>
+      <c r="Z341" s="6" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="342" spans="1:26">
+      <c r="A342" s="6">
+        <v>1169</v>
+      </c>
+      <c r="B342" s="3">
+        <v>46293.666458333297</v>
+      </c>
+      <c r="C342" s="3">
+        <v>46293.666585648098</v>
+      </c>
+      <c r="D342" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="E342" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F342" s="6">
+        <v>38571</v>
+      </c>
+      <c r="G342" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H342" s="2"/>
+      <c r="I342" s="2"/>
+      <c r="J342" s="2"/>
+      <c r="K342" s="2"/>
+      <c r="L342" s="2"/>
+      <c r="M342" s="2"/>
+      <c r="N342" s="2"/>
+      <c r="O342" s="2"/>
+      <c r="P342" s="2"/>
+      <c r="Q342" s="4"/>
+      <c r="R342" s="4"/>
+      <c r="S342" s="2"/>
+      <c r="T342" s="6"/>
+      <c r="U342" s="6"/>
+      <c r="V342" s="2"/>
+      <c r="W342" s="2"/>
+      <c r="X342" s="6">
+        <v>30</v>
+      </c>
+      <c r="Y342" s="6">
+        <v>8</v>
+      </c>
+      <c r="Z342" s="6" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="343" spans="1:26">
+      <c r="A343" s="6">
+        <v>1170</v>
+      </c>
+      <c r="B343" s="3">
+        <v>46293.667511574102</v>
+      </c>
+      <c r="C343" s="3">
+        <v>46293.670636574097</v>
+      </c>
+      <c r="D343" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E343" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="F343" s="6">
+        <v>38169</v>
+      </c>
+      <c r="G343" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H343" s="2"/>
+      <c r="I343" s="2"/>
+      <c r="J343" s="2"/>
+      <c r="K343" s="2"/>
+      <c r="L343" s="2"/>
+      <c r="M343" s="2"/>
+      <c r="N343" s="2"/>
+      <c r="O343" s="2"/>
+      <c r="P343" s="2"/>
+      <c r="Q343" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R343" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="S343" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="T343" s="6"/>
+      <c r="U343" s="6"/>
+      <c r="V343" s="2"/>
+      <c r="W343" s="2"/>
+      <c r="X343" s="6"/>
+      <c r="Y343" s="6"/>
+      <c r="Z343" s="6"/>
+    </row>
+    <row r="344" spans="1:26">
+      <c r="A344" s="6">
+        <v>1171</v>
+      </c>
+      <c r="B344" s="3">
+        <v>46293.665763888901</v>
+      </c>
+      <c r="C344" s="3">
+        <v>46293.6733564815</v>
+      </c>
+      <c r="D344" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E344" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F344" s="6">
+        <v>38124</v>
+      </c>
+      <c r="G344" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H344" s="2"/>
+      <c r="I344" s="2"/>
+      <c r="J344" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="K344" s="2"/>
+      <c r="L344" s="2"/>
+      <c r="M344" s="2"/>
+      <c r="N344" s="2"/>
+      <c r="O344" s="2"/>
+      <c r="P344" s="2"/>
+      <c r="Q344" s="4"/>
+      <c r="R344" s="4"/>
+      <c r="S344" s="2"/>
+      <c r="T344" s="6"/>
+      <c r="U344" s="6"/>
+      <c r="V344" s="2"/>
+      <c r="W344" s="2"/>
+      <c r="X344" s="6"/>
+      <c r="Y344" s="6"/>
+      <c r="Z344" s="6"/>
+    </row>
+    <row r="345" spans="1:26">
+      <c r="A345" s="6">
+        <v>1172</v>
+      </c>
+      <c r="B345" s="3">
+        <v>46293.673587963</v>
+      </c>
+      <c r="C345" s="3">
+        <v>46293.674942129597</v>
+      </c>
+      <c r="D345" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E345" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F345" s="6">
+        <v>38124</v>
+      </c>
+      <c r="G345" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H345" s="2"/>
+      <c r="I345" s="2"/>
+      <c r="J345" s="2"/>
+      <c r="K345" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="L345" s="2"/>
+      <c r="M345" s="2"/>
+      <c r="N345" s="2"/>
+      <c r="O345" s="2"/>
+      <c r="P345" s="2"/>
+      <c r="Q345" s="4"/>
+      <c r="R345" s="4"/>
+      <c r="S345" s="2"/>
+      <c r="T345" s="6"/>
+      <c r="U345" s="6"/>
+      <c r="V345" s="2"/>
+      <c r="W345" s="2"/>
+      <c r="X345" s="6"/>
+      <c r="Y345" s="6"/>
+      <c r="Z345" s="6"/>
+    </row>
+    <row r="346" spans="1:26">
+      <c r="A346" s="6">
+        <v>1173</v>
+      </c>
+      <c r="B346" s="3">
+        <v>46293.658622685201</v>
+      </c>
+      <c r="C346" s="3">
+        <v>46293.679652777799</v>
+      </c>
+      <c r="D346" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E346" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F346" s="6">
+        <v>38398</v>
+      </c>
+      <c r="G346" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H346" s="2"/>
+      <c r="I346" s="2"/>
+      <c r="J346" s="2"/>
+      <c r="K346" s="2"/>
+      <c r="L346" s="2"/>
+      <c r="M346" s="2"/>
+      <c r="N346" s="2"/>
+      <c r="O346" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="P346" s="2"/>
+      <c r="Q346" s="4"/>
+      <c r="R346" s="4"/>
+      <c r="S346" s="2"/>
+      <c r="T346" s="6"/>
+      <c r="U346" s="6"/>
+      <c r="V346" s="2"/>
+      <c r="W346" s="2"/>
+      <c r="X346" s="6"/>
+      <c r="Y346" s="6"/>
+      <c r="Z346" s="6"/>
+    </row>
+    <row r="347" spans="1:26">
+      <c r="A347" s="6">
+        <v>1174</v>
+      </c>
+      <c r="B347" s="3">
+        <v>46293.683240740698</v>
+      </c>
+      <c r="C347" s="3">
+        <v>46293.685324074097</v>
+      </c>
+      <c r="D347" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E347" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F347" s="6">
+        <v>38398</v>
+      </c>
+      <c r="G347" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H347" s="2"/>
+      <c r="I347" s="2"/>
+      <c r="J347" s="2"/>
+      <c r="K347" s="2"/>
+      <c r="L347" s="2"/>
+      <c r="M347" s="2"/>
+      <c r="N347" s="2"/>
+      <c r="O347" s="2"/>
+      <c r="P347" s="2"/>
+      <c r="Q347" s="4"/>
+      <c r="R347" s="4"/>
+      <c r="S347" s="2"/>
+      <c r="T347" s="6">
+        <v>8</v>
+      </c>
+      <c r="U347" s="6">
+        <v>1</v>
+      </c>
+      <c r="V347" s="2"/>
+      <c r="W347" s="2"/>
+      <c r="X347" s="6"/>
+      <c r="Y347" s="6"/>
+      <c r="Z347" s="6"/>
+    </row>
+    <row r="348" spans="1:26">
+      <c r="A348" s="6">
+        <v>1175</v>
+      </c>
+      <c r="B348" s="3">
+        <v>46293.675856481503</v>
+      </c>
+      <c r="C348" s="3">
+        <v>46293.705335648097</v>
+      </c>
+      <c r="D348" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E348" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F348" s="6">
+        <v>38124</v>
+      </c>
+      <c r="G348" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="H348" s="2"/>
+      <c r="I348" s="2"/>
+      <c r="J348" s="2"/>
+      <c r="K348" s="2"/>
+      <c r="L348" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="M348" s="2"/>
+      <c r="N348" s="2"/>
+      <c r="O348" s="2"/>
+      <c r="P348" s="2"/>
+      <c r="Q348" s="4"/>
+      <c r="R348" s="4"/>
+      <c r="S348" s="2"/>
+      <c r="T348" s="6"/>
+      <c r="U348" s="6"/>
+      <c r="V348" s="2"/>
+      <c r="W348" s="2"/>
+      <c r="X348" s="6"/>
+      <c r="Y348" s="6"/>
+      <c r="Z348" s="6"/>
+    </row>
+    <row r="349" spans="1:26">
+      <c r="A349" s="6">
+        <v>1176</v>
+      </c>
+      <c r="B349" s="3">
+        <v>46293.7120138889</v>
+      </c>
+      <c r="C349" s="3">
+        <v>46293.712453703702</v>
+      </c>
+      <c r="D349" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E349" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F349" s="6">
+        <v>38124</v>
+      </c>
+      <c r="G349" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H349" s="2"/>
+      <c r="I349" s="2"/>
+      <c r="J349" s="2"/>
+      <c r="K349" s="2"/>
+      <c r="L349" s="2"/>
+      <c r="M349" s="2"/>
+      <c r="N349" s="2"/>
+      <c r="O349" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="P349" s="2"/>
+      <c r="Q349" s="4"/>
+      <c r="R349" s="4"/>
+      <c r="S349" s="2"/>
+      <c r="T349" s="6"/>
+      <c r="U349" s="6"/>
+      <c r="V349" s="2"/>
+      <c r="W349" s="2"/>
+      <c r="X349" s="6"/>
+      <c r="Y349" s="6"/>
+      <c r="Z349" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="336" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{987A32E6-FB14-40E8-8E0D-C1214491DCF9}"/>
+  <xr:revisionPtr revIDLastSave="340" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE853CEC-2FBC-4EE6-B208-EBFEF8797A53}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1330" uniqueCount="496">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="502">
   <si>
     <t>Id</t>
   </si>
@@ -1527,6 +1527,24 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Activacion_PSL_Sharpie/IMG-20260928-WA0006_Starbucks%20San%20Jeroni.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/image_Starbucks%20Santa%20Tere.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Lobby%201/IMG-20260928-WA0007_Starbucks%20San%20Jeroni.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/IMG-20260928-WA0010_Starbucks%20San%20Jeroni.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG-20260928-WA0011_Starbucks%20San%20Jeroni.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38811@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Plaza Tepeyac</t>
   </si>
 </sst>
 </file>
@@ -1663,8 +1681,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z349" totalsRowShown="0">
-  <autoFilter ref="A1:Z349" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z358" totalsRowShown="0">
+  <autoFilter ref="A1:Z358" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1852,7 +1870,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1176" latestEventMarker="1622">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1185" latestEventMarker="1631">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2182,7 +2200,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z349"/>
+  <dimension ref="A1:Z358"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -14486,7 +14504,7 @@
       <c r="W340" s="2"/>
     </row>
     <row r="341" spans="1:26">
-      <c r="A341" s="6">
+      <c r="A341">
         <v>1168</v>
       </c>
       <c r="B341" s="3">
@@ -14501,7 +14519,7 @@
       <c r="E341" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F341" s="6">
+      <c r="F341">
         <v>38615</v>
       </c>
       <c r="G341" s="2" t="s">
@@ -14519,22 +14537,20 @@
       <c r="Q341" s="4"/>
       <c r="R341" s="4"/>
       <c r="S341" s="2"/>
-      <c r="T341" s="6"/>
-      <c r="U341" s="6"/>
       <c r="V341" s="2"/>
       <c r="W341" s="2"/>
-      <c r="X341" s="6">
+      <c r="X341">
         <v>0</v>
       </c>
-      <c r="Y341" s="6">
+      <c r="Y341">
         <v>3</v>
       </c>
-      <c r="Z341" s="6" t="s">
+      <c r="Z341" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="342" spans="1:26">
-      <c r="A342" s="6">
+      <c r="A342">
         <v>1169</v>
       </c>
       <c r="B342" s="3">
@@ -14549,7 +14565,7 @@
       <c r="E342" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="F342" s="6">
+      <c r="F342">
         <v>38571</v>
       </c>
       <c r="G342" s="2" t="s">
@@ -14567,22 +14583,20 @@
       <c r="Q342" s="4"/>
       <c r="R342" s="4"/>
       <c r="S342" s="2"/>
-      <c r="T342" s="6"/>
-      <c r="U342" s="6"/>
       <c r="V342" s="2"/>
       <c r="W342" s="2"/>
-      <c r="X342" s="6">
+      <c r="X342">
         <v>30</v>
       </c>
-      <c r="Y342" s="6">
+      <c r="Y342">
         <v>8</v>
       </c>
-      <c r="Z342" s="6" t="s">
+      <c r="Z342" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="343" spans="1:26">
-      <c r="A343" s="6">
+      <c r="A343">
         <v>1170</v>
       </c>
       <c r="B343" s="3">
@@ -14597,7 +14611,7 @@
       <c r="E343" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="F343" s="6">
+      <c r="F343">
         <v>38169</v>
       </c>
       <c r="G343" s="2" t="s">
@@ -14621,16 +14635,11 @@
       <c r="S343" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="T343" s="6"/>
-      <c r="U343" s="6"/>
       <c r="V343" s="2"/>
       <c r="W343" s="2"/>
-      <c r="X343" s="6"/>
-      <c r="Y343" s="6"/>
-      <c r="Z343" s="6"/>
     </row>
     <row r="344" spans="1:26">
-      <c r="A344" s="6">
+      <c r="A344">
         <v>1171</v>
       </c>
       <c r="B344" s="3">
@@ -14645,7 +14654,7 @@
       <c r="E344" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F344" s="6">
+      <c r="F344">
         <v>38124</v>
       </c>
       <c r="G344" s="2" t="s">
@@ -14665,16 +14674,11 @@
       <c r="Q344" s="4"/>
       <c r="R344" s="4"/>
       <c r="S344" s="2"/>
-      <c r="T344" s="6"/>
-      <c r="U344" s="6"/>
       <c r="V344" s="2"/>
       <c r="W344" s="2"/>
-      <c r="X344" s="6"/>
-      <c r="Y344" s="6"/>
-      <c r="Z344" s="6"/>
     </row>
     <row r="345" spans="1:26">
-      <c r="A345" s="6">
+      <c r="A345">
         <v>1172</v>
       </c>
       <c r="B345" s="3">
@@ -14689,7 +14693,7 @@
       <c r="E345" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F345" s="6">
+      <c r="F345">
         <v>38124</v>
       </c>
       <c r="G345" s="2" t="s">
@@ -14709,16 +14713,11 @@
       <c r="Q345" s="4"/>
       <c r="R345" s="4"/>
       <c r="S345" s="2"/>
-      <c r="T345" s="6"/>
-      <c r="U345" s="6"/>
       <c r="V345" s="2"/>
       <c r="W345" s="2"/>
-      <c r="X345" s="6"/>
-      <c r="Y345" s="6"/>
-      <c r="Z345" s="6"/>
     </row>
     <row r="346" spans="1:26">
-      <c r="A346" s="6">
+      <c r="A346">
         <v>1173</v>
       </c>
       <c r="B346" s="3">
@@ -14733,7 +14732,7 @@
       <c r="E346" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="F346" s="6">
+      <c r="F346">
         <v>38398</v>
       </c>
       <c r="G346" s="2" t="s">
@@ -14753,16 +14752,11 @@
       <c r="Q346" s="4"/>
       <c r="R346" s="4"/>
       <c r="S346" s="2"/>
-      <c r="T346" s="6"/>
-      <c r="U346" s="6"/>
       <c r="V346" s="2"/>
       <c r="W346" s="2"/>
-      <c r="X346" s="6"/>
-      <c r="Y346" s="6"/>
-      <c r="Z346" s="6"/>
     </row>
     <row r="347" spans="1:26">
-      <c r="A347" s="6">
+      <c r="A347">
         <v>1174</v>
       </c>
       <c r="B347" s="3">
@@ -14777,7 +14771,7 @@
       <c r="E347" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="F347" s="6">
+      <c r="F347">
         <v>38398</v>
       </c>
       <c r="G347" s="2" t="s">
@@ -14795,20 +14789,17 @@
       <c r="Q347" s="4"/>
       <c r="R347" s="4"/>
       <c r="S347" s="2"/>
-      <c r="T347" s="6">
+      <c r="T347">
         <v>8</v>
       </c>
-      <c r="U347" s="6">
+      <c r="U347">
         <v>1</v>
       </c>
       <c r="V347" s="2"/>
       <c r="W347" s="2"/>
-      <c r="X347" s="6"/>
-      <c r="Y347" s="6"/>
-      <c r="Z347" s="6"/>
     </row>
     <row r="348" spans="1:26">
-      <c r="A348" s="6">
+      <c r="A348">
         <v>1175</v>
       </c>
       <c r="B348" s="3">
@@ -14823,7 +14814,7 @@
       <c r="E348" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F348" s="6">
+      <c r="F348">
         <v>38124</v>
       </c>
       <c r="G348" s="2" t="s">
@@ -14843,16 +14834,11 @@
       <c r="Q348" s="4"/>
       <c r="R348" s="4"/>
       <c r="S348" s="2"/>
-      <c r="T348" s="6"/>
-      <c r="U348" s="6"/>
       <c r="V348" s="2"/>
       <c r="W348" s="2"/>
-      <c r="X348" s="6"/>
-      <c r="Y348" s="6"/>
-      <c r="Z348" s="6"/>
     </row>
     <row r="349" spans="1:26">
-      <c r="A349" s="6">
+      <c r="A349">
         <v>1176</v>
       </c>
       <c r="B349" s="3">
@@ -14867,7 +14853,7 @@
       <c r="E349" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F349" s="6">
+      <c r="F349">
         <v>38124</v>
       </c>
       <c r="G349" s="2" t="s">
@@ -14887,13 +14873,426 @@
       <c r="Q349" s="4"/>
       <c r="R349" s="4"/>
       <c r="S349" s="2"/>
-      <c r="T349" s="6"/>
-      <c r="U349" s="6"/>
       <c r="V349" s="2"/>
       <c r="W349" s="2"/>
-      <c r="X349" s="6"/>
-      <c r="Y349" s="6"/>
-      <c r="Z349" s="6"/>
+    </row>
+    <row r="350" spans="1:26">
+      <c r="A350" s="6">
+        <v>1177</v>
+      </c>
+      <c r="B350" s="3">
+        <v>46293.718946759298</v>
+      </c>
+      <c r="C350" s="3">
+        <v>46293.7211342593</v>
+      </c>
+      <c r="D350" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="E350" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="F350" s="6">
+        <v>38116</v>
+      </c>
+      <c r="G350" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H350" s="2"/>
+      <c r="I350" s="2"/>
+      <c r="J350" s="2"/>
+      <c r="K350" s="2"/>
+      <c r="L350" s="2"/>
+      <c r="M350" s="2"/>
+      <c r="N350" s="2"/>
+      <c r="O350" s="2"/>
+      <c r="P350" s="2"/>
+      <c r="Q350" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R350" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S350" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="T350" s="6"/>
+      <c r="U350" s="6"/>
+      <c r="V350" s="2"/>
+      <c r="W350" s="2"/>
+      <c r="X350" s="6"/>
+      <c r="Y350" s="6"/>
+      <c r="Z350" s="6"/>
+    </row>
+    <row r="351" spans="1:26">
+      <c r="A351" s="6">
+        <v>1178</v>
+      </c>
+      <c r="B351" s="3">
+        <v>46293.718634259298</v>
+      </c>
+      <c r="C351" s="3">
+        <v>46293.723715277803</v>
+      </c>
+      <c r="D351" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E351" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F351" s="6">
+        <v>38124</v>
+      </c>
+      <c r="G351" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H351" s="2"/>
+      <c r="I351" s="2"/>
+      <c r="J351" s="2"/>
+      <c r="K351" s="2"/>
+      <c r="L351" s="2"/>
+      <c r="M351" s="2"/>
+      <c r="N351" s="2"/>
+      <c r="O351" s="2"/>
+      <c r="P351" s="2"/>
+      <c r="Q351" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="R351" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="S351" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="T351" s="6"/>
+      <c r="U351" s="6"/>
+      <c r="V351" s="2"/>
+      <c r="W351" s="2"/>
+      <c r="X351" s="6"/>
+      <c r="Y351" s="6"/>
+      <c r="Z351" s="6"/>
+    </row>
+    <row r="352" spans="1:26">
+      <c r="A352" s="6">
+        <v>1179</v>
+      </c>
+      <c r="B352" s="3">
+        <v>46293.726747685199</v>
+      </c>
+      <c r="C352" s="3">
+        <v>46293.7270601852</v>
+      </c>
+      <c r="D352" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E352" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="F352" s="6">
+        <v>38859</v>
+      </c>
+      <c r="G352" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H352" s="2"/>
+      <c r="I352" s="2"/>
+      <c r="J352" s="2"/>
+      <c r="K352" s="2"/>
+      <c r="L352" s="2"/>
+      <c r="M352" s="2"/>
+      <c r="N352" s="2"/>
+      <c r="O352" s="2"/>
+      <c r="P352" s="2"/>
+      <c r="Q352" s="4"/>
+      <c r="R352" s="4"/>
+      <c r="S352" s="2"/>
+      <c r="T352" s="6">
+        <v>15</v>
+      </c>
+      <c r="U352" s="6">
+        <v>0</v>
+      </c>
+      <c r="V352" s="2"/>
+      <c r="W352" s="2"/>
+      <c r="X352" s="6"/>
+      <c r="Y352" s="6"/>
+      <c r="Z352" s="6"/>
+    </row>
+    <row r="353" spans="1:26">
+      <c r="A353" s="6">
+        <v>1180</v>
+      </c>
+      <c r="B353" s="3">
+        <v>46293.723900463003</v>
+      </c>
+      <c r="C353" s="3">
+        <v>46293.729895833298</v>
+      </c>
+      <c r="D353" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E353" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F353" s="6">
+        <v>38124</v>
+      </c>
+      <c r="G353" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H353" s="2"/>
+      <c r="I353" s="2"/>
+      <c r="J353" s="2"/>
+      <c r="K353" s="2"/>
+      <c r="L353" s="2"/>
+      <c r="M353" s="2"/>
+      <c r="N353" s="2"/>
+      <c r="O353" s="2"/>
+      <c r="P353" s="2"/>
+      <c r="Q353" s="4"/>
+      <c r="R353" s="4"/>
+      <c r="S353" s="2"/>
+      <c r="T353" s="6"/>
+      <c r="U353" s="6"/>
+      <c r="V353" s="2"/>
+      <c r="W353" s="2"/>
+      <c r="X353" s="6">
+        <v>38</v>
+      </c>
+      <c r="Y353" s="6">
+        <v>2</v>
+      </c>
+      <c r="Z353" s="6" t="s">
+        <v>498</v>
+      </c>
+    </row>
+    <row r="354" spans="1:26">
+      <c r="A354" s="6">
+        <v>1181</v>
+      </c>
+      <c r="B354" s="3">
+        <v>46293.730486111097</v>
+      </c>
+      <c r="C354" s="3">
+        <v>46293.734803240703</v>
+      </c>
+      <c r="D354" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E354" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F354" s="6">
+        <v>38124</v>
+      </c>
+      <c r="G354" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H354" s="2"/>
+      <c r="I354" s="2"/>
+      <c r="J354" s="2"/>
+      <c r="K354" s="2"/>
+      <c r="L354" s="2"/>
+      <c r="M354" s="2"/>
+      <c r="N354" s="2"/>
+      <c r="O354" s="2"/>
+      <c r="P354" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q354" s="4"/>
+      <c r="R354" s="4"/>
+      <c r="S354" s="2"/>
+      <c r="T354" s="6"/>
+      <c r="U354" s="6"/>
+      <c r="V354" s="2"/>
+      <c r="W354" s="2"/>
+      <c r="X354" s="6"/>
+      <c r="Y354" s="6"/>
+      <c r="Z354" s="6"/>
+    </row>
+    <row r="355" spans="1:26">
+      <c r="A355" s="6">
+        <v>1182</v>
+      </c>
+      <c r="B355" s="3">
+        <v>46293.767175925903</v>
+      </c>
+      <c r="C355" s="3">
+        <v>46293.7675115741</v>
+      </c>
+      <c r="D355" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E355" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F355" s="6">
+        <v>38719</v>
+      </c>
+      <c r="G355" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H355" s="2"/>
+      <c r="I355" s="2"/>
+      <c r="J355" s="2"/>
+      <c r="K355" s="2"/>
+      <c r="L355" s="2"/>
+      <c r="M355" s="2"/>
+      <c r="N355" s="2"/>
+      <c r="O355" s="2"/>
+      <c r="P355" s="2"/>
+      <c r="Q355" s="4"/>
+      <c r="R355" s="4"/>
+      <c r="S355" s="2"/>
+      <c r="T355" s="6">
+        <v>10</v>
+      </c>
+      <c r="U355" s="6">
+        <v>3</v>
+      </c>
+      <c r="V355" s="2"/>
+      <c r="W355" s="2"/>
+      <c r="X355" s="6"/>
+      <c r="Y355" s="6"/>
+      <c r="Z355" s="6"/>
+    </row>
+    <row r="356" spans="1:26">
+      <c r="A356" s="6">
+        <v>1183</v>
+      </c>
+      <c r="B356" s="3">
+        <v>46293.781631944403</v>
+      </c>
+      <c r="C356" s="3">
+        <v>46293.782453703701</v>
+      </c>
+      <c r="D356" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="E356" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F356" s="6">
+        <v>38811</v>
+      </c>
+      <c r="G356" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H356" s="2"/>
+      <c r="I356" s="2"/>
+      <c r="J356" s="2"/>
+      <c r="K356" s="2"/>
+      <c r="L356" s="2"/>
+      <c r="M356" s="2"/>
+      <c r="N356" s="2"/>
+      <c r="O356" s="2"/>
+      <c r="P356" s="2"/>
+      <c r="Q356" s="4"/>
+      <c r="R356" s="4"/>
+      <c r="S356" s="2"/>
+      <c r="T356" s="6">
+        <v>6</v>
+      </c>
+      <c r="U356" s="6">
+        <v>5</v>
+      </c>
+      <c r="V356" s="2"/>
+      <c r="W356" s="2"/>
+      <c r="X356" s="6"/>
+      <c r="Y356" s="6"/>
+      <c r="Z356" s="6"/>
+    </row>
+    <row r="357" spans="1:26">
+      <c r="A357" s="6">
+        <v>1184</v>
+      </c>
+      <c r="B357" s="3">
+        <v>46293.788935185199</v>
+      </c>
+      <c r="C357" s="3">
+        <v>46293.789525462998</v>
+      </c>
+      <c r="D357" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E357" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="F357" s="6">
+        <v>38965</v>
+      </c>
+      <c r="G357" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H357" s="2"/>
+      <c r="I357" s="2"/>
+      <c r="J357" s="2"/>
+      <c r="K357" s="2"/>
+      <c r="L357" s="2"/>
+      <c r="M357" s="2"/>
+      <c r="N357" s="2"/>
+      <c r="O357" s="2"/>
+      <c r="P357" s="2"/>
+      <c r="Q357" s="4"/>
+      <c r="R357" s="4"/>
+      <c r="S357" s="2"/>
+      <c r="T357" s="6">
+        <v>11</v>
+      </c>
+      <c r="U357" s="6">
+        <v>1</v>
+      </c>
+      <c r="V357" s="2"/>
+      <c r="W357" s="2"/>
+      <c r="X357" s="6"/>
+      <c r="Y357" s="6"/>
+      <c r="Z357" s="6"/>
+    </row>
+    <row r="358" spans="1:26" hidden="1">
+      <c r="A358" s="6">
+        <v>1185</v>
+      </c>
+      <c r="B358" s="3">
+        <v>46293.878692129598</v>
+      </c>
+      <c r="C358" s="3">
+        <v>46293.879467592596</v>
+      </c>
+      <c r="D358" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E358" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="F358" s="6">
+        <v>38368</v>
+      </c>
+      <c r="G358" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H358" s="2"/>
+      <c r="I358" s="2"/>
+      <c r="J358" s="2"/>
+      <c r="K358" s="2"/>
+      <c r="L358" s="2"/>
+      <c r="M358" s="2"/>
+      <c r="N358" s="2"/>
+      <c r="O358" s="2"/>
+      <c r="P358" s="2"/>
+      <c r="Q358" s="4"/>
+      <c r="R358" s="4"/>
+      <c r="S358" s="2"/>
+      <c r="T358" s="6">
+        <v>14</v>
+      </c>
+      <c r="U358" s="6">
+        <v>2</v>
+      </c>
+      <c r="V358" s="2"/>
+      <c r="W358" s="2"/>
+      <c r="X358" s="6"/>
+      <c r="Y358" s="6"/>
+      <c r="Z358" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="340" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE853CEC-2FBC-4EE6-B208-EBFEF8797A53}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{479C5659-3547-4782-864A-D843FED0B37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1580,7 +1580,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1589,7 +1589,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -14877,7 +14876,7 @@
       <c r="W349" s="2"/>
     </row>
     <row r="350" spans="1:26">
-      <c r="A350" s="6">
+      <c r="A350">
         <v>1177</v>
       </c>
       <c r="B350" s="3">
@@ -14892,7 +14891,7 @@
       <c r="E350" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="F350" s="6">
+      <c r="F350">
         <v>38116</v>
       </c>
       <c r="G350" s="2" t="s">
@@ -14916,16 +14915,11 @@
       <c r="S350" s="2" t="s">
         <v>496</v>
       </c>
-      <c r="T350" s="6"/>
-      <c r="U350" s="6"/>
       <c r="V350" s="2"/>
       <c r="W350" s="2"/>
-      <c r="X350" s="6"/>
-      <c r="Y350" s="6"/>
-      <c r="Z350" s="6"/>
     </row>
     <row r="351" spans="1:26">
-      <c r="A351" s="6">
+      <c r="A351">
         <v>1178</v>
       </c>
       <c r="B351" s="3">
@@ -14940,7 +14934,7 @@
       <c r="E351" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F351" s="6">
+      <c r="F351">
         <v>38124</v>
       </c>
       <c r="G351" s="2" t="s">
@@ -14964,16 +14958,11 @@
       <c r="S351" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="T351" s="6"/>
-      <c r="U351" s="6"/>
       <c r="V351" s="2"/>
       <c r="W351" s="2"/>
-      <c r="X351" s="6"/>
-      <c r="Y351" s="6"/>
-      <c r="Z351" s="6"/>
     </row>
     <row r="352" spans="1:26">
-      <c r="A352" s="6">
+      <c r="A352">
         <v>1179</v>
       </c>
       <c r="B352" s="3">
@@ -14988,7 +14977,7 @@
       <c r="E352" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="F352" s="6">
+      <c r="F352">
         <v>38859</v>
       </c>
       <c r="G352" s="2" t="s">
@@ -15006,20 +14995,17 @@
       <c r="Q352" s="4"/>
       <c r="R352" s="4"/>
       <c r="S352" s="2"/>
-      <c r="T352" s="6">
+      <c r="T352">
         <v>15</v>
       </c>
-      <c r="U352" s="6">
+      <c r="U352">
         <v>0</v>
       </c>
       <c r="V352" s="2"/>
       <c r="W352" s="2"/>
-      <c r="X352" s="6"/>
-      <c r="Y352" s="6"/>
-      <c r="Z352" s="6"/>
     </row>
     <row r="353" spans="1:26">
-      <c r="A353" s="6">
+      <c r="A353">
         <v>1180</v>
       </c>
       <c r="B353" s="3">
@@ -15034,7 +15020,7 @@
       <c r="E353" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F353" s="6">
+      <c r="F353">
         <v>38124</v>
       </c>
       <c r="G353" s="2" t="s">
@@ -15052,22 +15038,20 @@
       <c r="Q353" s="4"/>
       <c r="R353" s="4"/>
       <c r="S353" s="2"/>
-      <c r="T353" s="6"/>
-      <c r="U353" s="6"/>
       <c r="V353" s="2"/>
       <c r="W353" s="2"/>
-      <c r="X353" s="6">
+      <c r="X353">
         <v>38</v>
       </c>
-      <c r="Y353" s="6">
+      <c r="Y353">
         <v>2</v>
       </c>
-      <c r="Z353" s="6" t="s">
+      <c r="Z353" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="354" spans="1:26">
-      <c r="A354" s="6">
+      <c r="A354">
         <v>1181</v>
       </c>
       <c r="B354" s="3">
@@ -15082,7 +15066,7 @@
       <c r="E354" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F354" s="6">
+      <c r="F354">
         <v>38124</v>
       </c>
       <c r="G354" s="2" t="s">
@@ -15102,16 +15086,11 @@
       <c r="Q354" s="4"/>
       <c r="R354" s="4"/>
       <c r="S354" s="2"/>
-      <c r="T354" s="6"/>
-      <c r="U354" s="6"/>
       <c r="V354" s="2"/>
       <c r="W354" s="2"/>
-      <c r="X354" s="6"/>
-      <c r="Y354" s="6"/>
-      <c r="Z354" s="6"/>
     </row>
     <row r="355" spans="1:26">
-      <c r="A355" s="6">
+      <c r="A355">
         <v>1182</v>
       </c>
       <c r="B355" s="3">
@@ -15126,7 +15105,7 @@
       <c r="E355" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F355" s="6">
+      <c r="F355">
         <v>38719</v>
       </c>
       <c r="G355" s="2" t="s">
@@ -15144,20 +15123,17 @@
       <c r="Q355" s="4"/>
       <c r="R355" s="4"/>
       <c r="S355" s="2"/>
-      <c r="T355" s="6">
+      <c r="T355">
         <v>10</v>
       </c>
-      <c r="U355" s="6">
+      <c r="U355">
         <v>3</v>
       </c>
       <c r="V355" s="2"/>
       <c r="W355" s="2"/>
-      <c r="X355" s="6"/>
-      <c r="Y355" s="6"/>
-      <c r="Z355" s="6"/>
     </row>
     <row r="356" spans="1:26">
-      <c r="A356" s="6">
+      <c r="A356">
         <v>1183</v>
       </c>
       <c r="B356" s="3">
@@ -15172,7 +15148,7 @@
       <c r="E356" s="2" t="s">
         <v>501</v>
       </c>
-      <c r="F356" s="6">
+      <c r="F356">
         <v>38811</v>
       </c>
       <c r="G356" s="2" t="s">
@@ -15190,20 +15166,17 @@
       <c r="Q356" s="4"/>
       <c r="R356" s="4"/>
       <c r="S356" s="2"/>
-      <c r="T356" s="6">
+      <c r="T356">
         <v>6</v>
       </c>
-      <c r="U356" s="6">
+      <c r="U356">
         <v>5</v>
       </c>
       <c r="V356" s="2"/>
       <c r="W356" s="2"/>
-      <c r="X356" s="6"/>
-      <c r="Y356" s="6"/>
-      <c r="Z356" s="6"/>
     </row>
     <row r="357" spans="1:26">
-      <c r="A357" s="6">
+      <c r="A357">
         <v>1184</v>
       </c>
       <c r="B357" s="3">
@@ -15218,7 +15191,7 @@
       <c r="E357" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="F357" s="6">
+      <c r="F357">
         <v>38965</v>
       </c>
       <c r="G357" s="2" t="s">
@@ -15236,20 +15209,17 @@
       <c r="Q357" s="4"/>
       <c r="R357" s="4"/>
       <c r="S357" s="2"/>
-      <c r="T357" s="6">
+      <c r="T357">
         <v>11</v>
       </c>
-      <c r="U357" s="6">
+      <c r="U357">
         <v>1</v>
       </c>
       <c r="V357" s="2"/>
       <c r="W357" s="2"/>
-      <c r="X357" s="6"/>
-      <c r="Y357" s="6"/>
-      <c r="Z357" s="6"/>
     </row>
     <row r="358" spans="1:26" hidden="1">
-      <c r="A358" s="6">
+      <c r="A358">
         <v>1185</v>
       </c>
       <c r="B358" s="3">
@@ -15264,7 +15234,7 @@
       <c r="E358" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="F358" s="6">
+      <c r="F358">
         <v>38368</v>
       </c>
       <c r="G358" s="2" t="s">
@@ -15282,17 +15252,14 @@
       <c r="Q358" s="4"/>
       <c r="R358" s="4"/>
       <c r="S358" s="2"/>
-      <c r="T358" s="6">
+      <c r="T358">
         <v>14</v>
       </c>
-      <c r="U358" s="6">
+      <c r="U358">
         <v>2</v>
       </c>
       <c r="V358" s="2"/>
       <c r="W358" s="2"/>
-      <c r="X358" s="6"/>
-      <c r="Y358" s="6"/>
-      <c r="Z358" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{479C5659-3547-4782-864A-D843FED0B37F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="343" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ECF39E7-BD7C-4098-814F-0AEFC9E12A88}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="502">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="511">
   <si>
     <t>Id</t>
   </si>
@@ -1545,6 +1545,33 @@
   </si>
   <si>
     <t>Starbucks Plaza Tepeyac</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Starbucks%20Jinetes.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/20260929_101259-COLLAGE_Starbucks%20San%20Miguel.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/Collage_20260929_101306_Starbucks%20DT%20Perifer.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%206/image_Marlene%20Danaee%20Herna.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Se%C3%B1aletica_Back/IMG_6331_Marlene%20Danaee%20Herna.jpeg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/IMG_6321_Marlene%20Danaee%20Herna.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx43193@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Cosmopol N1</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/1790699935497746412465194118686_Starbucks%20Cosmopol%20N.jpg</t>
   </si>
 </sst>
 </file>
@@ -1580,7 +1607,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1589,6 +1616,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1680,8 +1708,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z358" totalsRowShown="0">
-  <autoFilter ref="A1:Z358" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z367" totalsRowShown="0">
+  <autoFilter ref="A1:Z367" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1869,7 +1897,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1185" latestEventMarker="1631">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1194" latestEventMarker="1640">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2199,7 +2227,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z358"/>
+  <dimension ref="A1:Z367"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -15261,6 +15289,424 @@
       <c r="V358" s="2"/>
       <c r="W358" s="2"/>
     </row>
+    <row r="359" spans="1:26">
+      <c r="A359" s="6">
+        <v>1186</v>
+      </c>
+      <c r="B359" s="3">
+        <v>46294.395891203698</v>
+      </c>
+      <c r="C359" s="3">
+        <v>46294.396759259304</v>
+      </c>
+      <c r="D359" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E359" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="F359" s="6">
+        <v>38615</v>
+      </c>
+      <c r="G359" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="H359" s="2"/>
+      <c r="I359" s="2"/>
+      <c r="J359" s="2"/>
+      <c r="K359" s="2"/>
+      <c r="L359" s="2"/>
+      <c r="M359" s="2"/>
+      <c r="N359" s="2"/>
+      <c r="O359" s="2"/>
+      <c r="P359" s="2"/>
+      <c r="Q359" s="4"/>
+      <c r="R359" s="4"/>
+      <c r="S359" s="2"/>
+      <c r="T359" s="6">
+        <v>15</v>
+      </c>
+      <c r="U359" s="6">
+        <v>0</v>
+      </c>
+      <c r="V359" s="2"/>
+      <c r="W359" s="2"/>
+      <c r="X359" s="6"/>
+      <c r="Y359" s="6"/>
+      <c r="Z359" s="6"/>
+    </row>
+    <row r="360" spans="1:26">
+      <c r="A360" s="6">
+        <v>1187</v>
+      </c>
+      <c r="B360" s="3">
+        <v>46294.421342592599</v>
+      </c>
+      <c r="C360" s="3">
+        <v>46294.425532407397</v>
+      </c>
+      <c r="D360" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E360" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F360" s="6">
+        <v>38661</v>
+      </c>
+      <c r="G360" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H360" s="2"/>
+      <c r="I360" s="2"/>
+      <c r="J360" s="2"/>
+      <c r="K360" s="2"/>
+      <c r="L360" s="2"/>
+      <c r="M360" s="2"/>
+      <c r="N360" s="2"/>
+      <c r="O360" s="2"/>
+      <c r="P360" s="2"/>
+      <c r="Q360" s="4"/>
+      <c r="R360" s="4"/>
+      <c r="S360" s="2"/>
+      <c r="T360" s="6"/>
+      <c r="U360" s="6"/>
+      <c r="V360" s="2"/>
+      <c r="W360" s="2"/>
+      <c r="X360" s="6">
+        <v>36</v>
+      </c>
+      <c r="Y360" s="6">
+        <v>4</v>
+      </c>
+      <c r="Z360" s="6" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="361" spans="1:26">
+      <c r="A361" s="6">
+        <v>1188</v>
+      </c>
+      <c r="B361" s="3">
+        <v>46294.407789351899</v>
+      </c>
+      <c r="C361" s="3">
+        <v>46294.426145833299</v>
+      </c>
+      <c r="D361" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E361" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F361" s="6">
+        <v>38862</v>
+      </c>
+      <c r="G361" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H361" s="2"/>
+      <c r="I361" s="2"/>
+      <c r="J361" s="2"/>
+      <c r="K361" s="2"/>
+      <c r="L361" s="2"/>
+      <c r="M361" s="2"/>
+      <c r="N361" s="2"/>
+      <c r="O361" s="2"/>
+      <c r="P361" s="2"/>
+      <c r="Q361" s="4"/>
+      <c r="R361" s="4"/>
+      <c r="S361" s="2"/>
+      <c r="T361" s="6"/>
+      <c r="U361" s="6"/>
+      <c r="V361" s="2"/>
+      <c r="W361" s="2"/>
+      <c r="X361" s="6">
+        <v>22</v>
+      </c>
+      <c r="Y361" s="6">
+        <v>3</v>
+      </c>
+      <c r="Z361" s="6" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="362" spans="1:26">
+      <c r="A362" s="6">
+        <v>1189</v>
+      </c>
+      <c r="B362" s="3">
+        <v>46294.422060185199</v>
+      </c>
+      <c r="C362" s="3">
+        <v>46294.426284722198</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E362" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F362" s="6">
+        <v>38117</v>
+      </c>
+      <c r="G362" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H362" s="2"/>
+      <c r="I362" s="2"/>
+      <c r="J362" s="2"/>
+      <c r="K362" s="2"/>
+      <c r="L362" s="2"/>
+      <c r="M362" s="2"/>
+      <c r="N362" s="2"/>
+      <c r="O362" s="2"/>
+      <c r="P362" s="2"/>
+      <c r="Q362" s="4"/>
+      <c r="R362" s="4"/>
+      <c r="S362" s="2"/>
+      <c r="T362" s="6"/>
+      <c r="U362" s="6"/>
+      <c r="V362" s="2"/>
+      <c r="W362" s="2"/>
+      <c r="X362" s="6">
+        <v>12</v>
+      </c>
+      <c r="Y362" s="6">
+        <v>0</v>
+      </c>
+      <c r="Z362" s="6" t="s">
+        <v>504</v>
+      </c>
+    </row>
+    <row r="363" spans="1:26">
+      <c r="A363" s="6">
+        <v>1190</v>
+      </c>
+      <c r="B363" s="3">
+        <v>46294.432245370401</v>
+      </c>
+      <c r="C363" s="3">
+        <v>46294.432615740698</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F363" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G363" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H363" s="2"/>
+      <c r="I363" s="2"/>
+      <c r="J363" s="2"/>
+      <c r="K363" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="L363" s="2"/>
+      <c r="M363" s="2"/>
+      <c r="N363" s="2"/>
+      <c r="O363" s="2"/>
+      <c r="P363" s="2"/>
+      <c r="Q363" s="4"/>
+      <c r="R363" s="4"/>
+      <c r="S363" s="2"/>
+      <c r="T363" s="6"/>
+      <c r="U363" s="6"/>
+      <c r="V363" s="2"/>
+      <c r="W363" s="2"/>
+      <c r="X363" s="6"/>
+      <c r="Y363" s="6"/>
+      <c r="Z363" s="6"/>
+    </row>
+    <row r="364" spans="1:26">
+      <c r="A364" s="6">
+        <v>1191</v>
+      </c>
+      <c r="B364" s="3">
+        <v>46294.432858796303</v>
+      </c>
+      <c r="C364" s="3">
+        <v>46294.433020833298</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F364" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G364" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="H364" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="I364" s="2"/>
+      <c r="J364" s="2"/>
+      <c r="K364" s="2"/>
+      <c r="L364" s="2"/>
+      <c r="M364" s="2"/>
+      <c r="N364" s="2"/>
+      <c r="O364" s="2"/>
+      <c r="P364" s="2"/>
+      <c r="Q364" s="4"/>
+      <c r="R364" s="4"/>
+      <c r="S364" s="2"/>
+      <c r="T364" s="6"/>
+      <c r="U364" s="6"/>
+      <c r="V364" s="2"/>
+      <c r="W364" s="2"/>
+      <c r="X364" s="6"/>
+      <c r="Y364" s="6"/>
+      <c r="Z364" s="6"/>
+    </row>
+    <row r="365" spans="1:26">
+      <c r="A365" s="6">
+        <v>1192</v>
+      </c>
+      <c r="B365" s="3">
+        <v>46294.433113425897</v>
+      </c>
+      <c r="C365" s="3">
+        <v>46294.436874999999</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E365" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F365" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G365" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="H365" s="2"/>
+      <c r="I365" s="2"/>
+      <c r="J365" s="2"/>
+      <c r="K365" s="2"/>
+      <c r="L365" s="2"/>
+      <c r="M365" s="2"/>
+      <c r="N365" s="2"/>
+      <c r="O365" s="2"/>
+      <c r="P365" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="Q365" s="4"/>
+      <c r="R365" s="4"/>
+      <c r="S365" s="2"/>
+      <c r="T365" s="6"/>
+      <c r="U365" s="6"/>
+      <c r="V365" s="2"/>
+      <c r="W365" s="2"/>
+      <c r="X365" s="6"/>
+      <c r="Y365" s="6"/>
+      <c r="Z365" s="6"/>
+    </row>
+    <row r="366" spans="1:26">
+      <c r="A366" s="6">
+        <v>1193</v>
+      </c>
+      <c r="B366" s="3">
+        <v>46294.437199074098</v>
+      </c>
+      <c r="C366" s="3">
+        <v>46294.437974537002</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E366" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F366" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G366" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H366" s="2"/>
+      <c r="I366" s="2"/>
+      <c r="J366" s="2"/>
+      <c r="K366" s="2"/>
+      <c r="L366" s="2"/>
+      <c r="M366" s="2"/>
+      <c r="N366" s="2"/>
+      <c r="O366" s="2"/>
+      <c r="P366" s="2"/>
+      <c r="Q366" s="4"/>
+      <c r="R366" s="4"/>
+      <c r="S366" s="2"/>
+      <c r="T366" s="6"/>
+      <c r="U366" s="6"/>
+      <c r="V366" s="2"/>
+      <c r="W366" s="2"/>
+      <c r="X366" s="6">
+        <v>25</v>
+      </c>
+      <c r="Y366" s="6">
+        <v>8</v>
+      </c>
+      <c r="Z366" s="6" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="367" spans="1:26">
+      <c r="A367" s="6">
+        <v>1194</v>
+      </c>
+      <c r="B367" s="3">
+        <v>46294.437581018501</v>
+      </c>
+      <c r="C367" s="3">
+        <v>46294.443946759297</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="F367" s="6">
+        <v>43193</v>
+      </c>
+      <c r="G367" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H367" s="2"/>
+      <c r="I367" s="2"/>
+      <c r="J367" s="2"/>
+      <c r="K367" s="2"/>
+      <c r="L367" s="2"/>
+      <c r="M367" s="2"/>
+      <c r="N367" s="2"/>
+      <c r="O367" s="2"/>
+      <c r="P367" s="2"/>
+      <c r="Q367" s="4"/>
+      <c r="R367" s="4"/>
+      <c r="S367" s="2"/>
+      <c r="T367" s="6"/>
+      <c r="U367" s="6"/>
+      <c r="V367" s="2"/>
+      <c r="W367" s="2"/>
+      <c r="X367" s="6">
+        <v>39</v>
+      </c>
+      <c r="Y367" s="6">
+        <v>10</v>
+      </c>
+      <c r="Z367" s="6" t="s">
+        <v>510</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="343" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1ECF39E7-BD7C-4098-814F-0AEFC9E12A88}"/>
+  <xr:revisionPtr revIDLastSave="346" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79D5F1E1-4C85-4F87-A057-265ED9F3CAF2}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1400" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="524">
   <si>
     <t>Id</t>
   </si>
@@ -1572,6 +1572,45 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/1790699935497746412465194118686_Starbucks%20Cosmopol%20N.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%204/IMG_6341_Marlene%20Danaee%20Herna.jpeg</t>
+  </si>
+  <si>
+    <t>fernando.velasco@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Fernando Axel Velasco Guzman</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17907016434976330151614007036568_Fernando%20Axel%20Velasc.jpg</t>
+  </si>
+  <si>
+    <t>jesus.vazquez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Jesus Francisco Vazquez Huerta</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17907019515118257165487028246287_Jesus%20Francisco%20Vazq.jpg</t>
+  </si>
+  <si>
+    <t>perla.franco@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Perla Franco Brito</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/IMG_20260929_111431_Perla%20Franco%20Brito.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38755@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Corporativo Santander</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Starbucks%20Corporativ.jpg</t>
   </si>
 </sst>
 </file>
@@ -1708,8 +1747,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z367" totalsRowShown="0">
-  <autoFilter ref="A1:Z367" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:Z372" totalsRowShown="0">
+  <autoFilter ref="A1:Z372" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="23">
       <extLst>
@@ -1897,7 +1936,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1194" latestEventMarker="1640">
+      <xlmsforms:msForm id="zETMD2hYl0iYHnsE951h2GyhcEMyHFZHoew1o1ZEZ_JUM0ZDSFVZOFBERkxYS0Y2NFFKUkY3R1dWOS4u" isFormConnected="1" maxResponseId="1199" latestEventMarker="1645">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2227,7 +2266,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z367"/>
+  <dimension ref="A1:Z372"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="20" bestFit="1" customWidth="1"/>
@@ -15290,7 +15329,7 @@
       <c r="W358" s="2"/>
     </row>
     <row r="359" spans="1:26">
-      <c r="A359" s="6">
+      <c r="A359">
         <v>1186</v>
       </c>
       <c r="B359" s="3">
@@ -15305,7 +15344,7 @@
       <c r="E359" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="F359" s="6">
+      <c r="F359">
         <v>38615</v>
       </c>
       <c r="G359" s="2" t="s">
@@ -15323,20 +15362,17 @@
       <c r="Q359" s="4"/>
       <c r="R359" s="4"/>
       <c r="S359" s="2"/>
-      <c r="T359" s="6">
+      <c r="T359">
         <v>15</v>
       </c>
-      <c r="U359" s="6">
+      <c r="U359">
         <v>0</v>
       </c>
       <c r="V359" s="2"/>
       <c r="W359" s="2"/>
-      <c r="X359" s="6"/>
-      <c r="Y359" s="6"/>
-      <c r="Z359" s="6"/>
     </row>
     <row r="360" spans="1:26">
-      <c r="A360" s="6">
+      <c r="A360">
         <v>1187</v>
       </c>
       <c r="B360" s="3">
@@ -15351,7 +15387,7 @@
       <c r="E360" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F360" s="6">
+      <c r="F360">
         <v>38661</v>
       </c>
       <c r="G360" s="2" t="s">
@@ -15369,22 +15405,20 @@
       <c r="Q360" s="4"/>
       <c r="R360" s="4"/>
       <c r="S360" s="2"/>
-      <c r="T360" s="6"/>
-      <c r="U360" s="6"/>
       <c r="V360" s="2"/>
       <c r="W360" s="2"/>
-      <c r="X360" s="6">
+      <c r="X360">
         <v>36</v>
       </c>
-      <c r="Y360" s="6">
+      <c r="Y360">
         <v>4</v>
       </c>
-      <c r="Z360" s="6" t="s">
+      <c r="Z360" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="361" spans="1:26">
-      <c r="A361" s="6">
+      <c r="A361">
         <v>1188</v>
       </c>
       <c r="B361" s="3">
@@ -15399,7 +15433,7 @@
       <c r="E361" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F361" s="6">
+      <c r="F361">
         <v>38862</v>
       </c>
       <c r="G361" s="2" t="s">
@@ -15417,22 +15451,20 @@
       <c r="Q361" s="4"/>
       <c r="R361" s="4"/>
       <c r="S361" s="2"/>
-      <c r="T361" s="6"/>
-      <c r="U361" s="6"/>
       <c r="V361" s="2"/>
       <c r="W361" s="2"/>
-      <c r="X361" s="6">
+      <c r="X361">
         <v>22</v>
       </c>
-      <c r="Y361" s="6">
+      <c r="Y361">
         <v>3</v>
       </c>
-      <c r="Z361" s="6" t="s">
+      <c r="Z361" t="s">
         <v>503</v>
       </c>
     </row>
     <row r="362" spans="1:26">
-      <c r="A362" s="6">
+      <c r="A362">
         <v>1189</v>
       </c>
       <c r="B362" s="3">
@@ -15447,7 +15479,7 @@
       <c r="E362" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="F362" s="6">
+      <c r="F362">
         <v>38117</v>
       </c>
       <c r="G362" s="2" t="s">
@@ -15465,22 +15497,20 @@
       <c r="Q362" s="4"/>
       <c r="R362" s="4"/>
       <c r="S362" s="2"/>
-      <c r="T362" s="6"/>
-      <c r="U362" s="6"/>
       <c r="V362" s="2"/>
       <c r="W362" s="2"/>
-      <c r="X362" s="6">
+      <c r="X362">
         <v>12</v>
       </c>
-      <c r="Y362" s="6">
+      <c r="Y362">
         <v>0</v>
       </c>
-      <c r="Z362" s="6" t="s">
+      <c r="Z362" t="s">
         <v>504</v>
       </c>
     </row>
     <row r="363" spans="1:26">
-      <c r="A363" s="6">
+      <c r="A363">
         <v>1190</v>
       </c>
       <c r="B363" s="3">
@@ -15495,7 +15525,7 @@
       <c r="E363" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F363" s="6">
+      <c r="F363">
         <v>38129</v>
       </c>
       <c r="G363" s="2" t="s">
@@ -15515,16 +15545,11 @@
       <c r="Q363" s="4"/>
       <c r="R363" s="4"/>
       <c r="S363" s="2"/>
-      <c r="T363" s="6"/>
-      <c r="U363" s="6"/>
       <c r="V363" s="2"/>
       <c r="W363" s="2"/>
-      <c r="X363" s="6"/>
-      <c r="Y363" s="6"/>
-      <c r="Z363" s="6"/>
     </row>
     <row r="364" spans="1:26">
-      <c r="A364" s="6">
+      <c r="A364">
         <v>1191</v>
       </c>
       <c r="B364" s="3">
@@ -15539,7 +15564,7 @@
       <c r="E364" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F364" s="6">
+      <c r="F364">
         <v>38129</v>
       </c>
       <c r="G364" s="2" t="s">
@@ -15559,16 +15584,11 @@
       <c r="Q364" s="4"/>
       <c r="R364" s="4"/>
       <c r="S364" s="2"/>
-      <c r="T364" s="6"/>
-      <c r="U364" s="6"/>
       <c r="V364" s="2"/>
       <c r="W364" s="2"/>
-      <c r="X364" s="6"/>
-      <c r="Y364" s="6"/>
-      <c r="Z364" s="6"/>
     </row>
     <row r="365" spans="1:26">
-      <c r="A365" s="6">
+      <c r="A365">
         <v>1192</v>
       </c>
       <c r="B365" s="3">
@@ -15583,7 +15603,7 @@
       <c r="E365" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F365" s="6">
+      <c r="F365">
         <v>38129</v>
       </c>
       <c r="G365" s="2" t="s">
@@ -15603,16 +15623,11 @@
       <c r="Q365" s="4"/>
       <c r="R365" s="4"/>
       <c r="S365" s="2"/>
-      <c r="T365" s="6"/>
-      <c r="U365" s="6"/>
       <c r="V365" s="2"/>
       <c r="W365" s="2"/>
-      <c r="X365" s="6"/>
-      <c r="Y365" s="6"/>
-      <c r="Z365" s="6"/>
     </row>
     <row r="366" spans="1:26">
-      <c r="A366" s="6">
+      <c r="A366">
         <v>1193</v>
       </c>
       <c r="B366" s="3">
@@ -15627,7 +15642,7 @@
       <c r="E366" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="F366" s="6">
+      <c r="F366">
         <v>38129</v>
       </c>
       <c r="G366" s="2" t="s">
@@ -15645,22 +15660,20 @@
       <c r="Q366" s="4"/>
       <c r="R366" s="4"/>
       <c r="S366" s="2"/>
-      <c r="T366" s="6"/>
-      <c r="U366" s="6"/>
       <c r="V366" s="2"/>
       <c r="W366" s="2"/>
-      <c r="X366" s="6">
+      <c r="X366">
         <v>25</v>
       </c>
-      <c r="Y366" s="6">
+      <c r="Y366">
         <v>8</v>
       </c>
-      <c r="Z366" s="6" t="s">
+      <c r="Z366" t="s">
         <v>507</v>
       </c>
     </row>
     <row r="367" spans="1:26">
-      <c r="A367" s="6">
+      <c r="A367">
         <v>1194</v>
       </c>
       <c r="B367" s="3">
@@ -15675,7 +15688,7 @@
       <c r="E367" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="F367" s="6">
+      <c r="F367">
         <v>43193</v>
       </c>
       <c r="G367" s="2" t="s">
@@ -15693,18 +15706,252 @@
       <c r="Q367" s="4"/>
       <c r="R367" s="4"/>
       <c r="S367" s="2"/>
-      <c r="T367" s="6"/>
-      <c r="U367" s="6"/>
       <c r="V367" s="2"/>
       <c r="W367" s="2"/>
-      <c r="X367" s="6">
+      <c r="X367">
         <v>39</v>
       </c>
-      <c r="Y367" s="6">
+      <c r="Y367">
         <v>10</v>
       </c>
-      <c r="Z367" s="6" t="s">
+      <c r="Z367" t="s">
         <v>510</v>
+      </c>
+    </row>
+    <row r="368" spans="1:26">
+      <c r="A368" s="6">
+        <v>1195</v>
+      </c>
+      <c r="B368" s="3">
+        <v>46294.4553703704</v>
+      </c>
+      <c r="C368" s="3">
+        <v>46294.460474537002</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F368" s="6">
+        <v>38129</v>
+      </c>
+      <c r="G368" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="H368" s="2"/>
+      <c r="I368" s="2"/>
+      <c r="J368" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="K368" s="2"/>
+      <c r="L368" s="2"/>
+      <c r="M368" s="2"/>
+      <c r="N368" s="2"/>
+      <c r="O368" s="2"/>
+      <c r="P368" s="2"/>
+      <c r="Q368" s="4"/>
+      <c r="R368" s="4"/>
+      <c r="S368" s="2"/>
+      <c r="T368" s="6"/>
+      <c r="U368" s="6"/>
+      <c r="V368" s="2"/>
+      <c r="W368" s="2"/>
+      <c r="X368" s="6"/>
+      <c r="Y368" s="6"/>
+      <c r="Z368" s="6"/>
+    </row>
+    <row r="369" spans="1:26">
+      <c r="A369" s="6">
+        <v>1196</v>
+      </c>
+      <c r="B369" s="3">
+        <v>46294.460601851897</v>
+      </c>
+      <c r="C369" s="3">
+        <v>46294.463854166701</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="E369" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="F369" s="6">
+        <v>38121</v>
+      </c>
+      <c r="G369" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H369" s="2"/>
+      <c r="I369" s="2"/>
+      <c r="J369" s="2"/>
+      <c r="K369" s="2"/>
+      <c r="L369" s="2"/>
+      <c r="M369" s="2"/>
+      <c r="N369" s="2"/>
+      <c r="O369" s="2"/>
+      <c r="P369" s="2"/>
+      <c r="Q369" s="4"/>
+      <c r="R369" s="4"/>
+      <c r="S369" s="2"/>
+      <c r="T369" s="6"/>
+      <c r="U369" s="6"/>
+      <c r="V369" s="2"/>
+      <c r="W369" s="2"/>
+      <c r="X369" s="6">
+        <v>36</v>
+      </c>
+      <c r="Y369" s="6">
+        <v>10</v>
+      </c>
+      <c r="Z369" s="6" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="370" spans="1:26">
+      <c r="A370" s="6">
+        <v>1197</v>
+      </c>
+      <c r="B370" s="3">
+        <v>46294.466180555602</v>
+      </c>
+      <c r="C370" s="3">
+        <v>46294.467453703699</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="F370" s="6">
+        <v>38780</v>
+      </c>
+      <c r="G370" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H370" s="2"/>
+      <c r="I370" s="2"/>
+      <c r="J370" s="2"/>
+      <c r="K370" s="2"/>
+      <c r="L370" s="2"/>
+      <c r="M370" s="2"/>
+      <c r="N370" s="2"/>
+      <c r="O370" s="2"/>
+      <c r="P370" s="2"/>
+      <c r="Q370" s="4"/>
+      <c r="R370" s="4"/>
+      <c r="S370" s="2"/>
+      <c r="T370" s="6"/>
+      <c r="U370" s="6"/>
+      <c r="V370" s="2"/>
+      <c r="W370" s="2"/>
+      <c r="X370" s="6">
+        <v>20</v>
+      </c>
+      <c r="Y370" s="6">
+        <v>6</v>
+      </c>
+      <c r="Z370" s="6" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="371" spans="1:26">
+      <c r="A371" s="6">
+        <v>1198</v>
+      </c>
+      <c r="B371" s="3">
+        <v>46294.463136574101</v>
+      </c>
+      <c r="C371" s="3">
+        <v>46294.468645833302</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="E371" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="F371" s="6">
+        <v>38512</v>
+      </c>
+      <c r="G371" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H371" s="2"/>
+      <c r="I371" s="2"/>
+      <c r="J371" s="2"/>
+      <c r="K371" s="2"/>
+      <c r="L371" s="2"/>
+      <c r="M371" s="2"/>
+      <c r="N371" s="2"/>
+      <c r="O371" s="2"/>
+      <c r="P371" s="2"/>
+      <c r="Q371" s="4"/>
+      <c r="R371" s="4"/>
+      <c r="S371" s="2"/>
+      <c r="T371" s="6"/>
+      <c r="U371" s="6"/>
+      <c r="V371" s="2"/>
+      <c r="W371" s="2"/>
+      <c r="X371" s="6">
+        <v>32</v>
+      </c>
+      <c r="Y371" s="6">
+        <v>10</v>
+      </c>
+      <c r="Z371" s="6" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="372" spans="1:26">
+      <c r="A372" s="6">
+        <v>1199</v>
+      </c>
+      <c r="B372" s="3">
+        <v>46294.467349537001</v>
+      </c>
+      <c r="C372" s="3">
+        <v>46294.4687037037</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E372" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="F372" s="6">
+        <v>38755</v>
+      </c>
+      <c r="G372" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="H372" s="2"/>
+      <c r="I372" s="2"/>
+      <c r="J372" s="2"/>
+      <c r="K372" s="2"/>
+      <c r="L372" s="2"/>
+      <c r="M372" s="2"/>
+      <c r="N372" s="2"/>
+      <c r="O372" s="2"/>
+      <c r="P372" s="2"/>
+      <c r="Q372" s="4"/>
+      <c r="R372" s="4"/>
+      <c r="S372" s="2"/>
+      <c r="T372" s="6"/>
+      <c r="U372" s="6"/>
+      <c r="V372" s="2"/>
+      <c r="W372" s="2"/>
+      <c r="X372" s="6">
+        <v>27</v>
+      </c>
+      <c r="Y372" s="6">
+        <v>7</v>
+      </c>
+      <c r="Z372" s="6" t="s">
+        <v>523</v>
       </c>
     </row>
   </sheetData>

--- a/cms/Sistema de Evidencias OPS.xlsx
+++ b/cms/Sistema de Evidencias OPS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="346" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{79D5F1E1-4C85-4F87-A057-265ED9F3CAF2}"/>
+  <xr:revisionPtr revIDLastSave="349" documentId="13_ncr:1_{AD74628D-BE06-4FC1-BE04-2187DD70E9AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C08DE3FB-ECAB-43E2-9683-7CCAED594ACA}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1420" uniqueCount="524">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="577">
   <si>
     <t>Id</t>
   </si>
@@ -1611,6 +1611,165 @@
   </si>
   <si>
     <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Starbucks%20Corporativ.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38929@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Apto Toluca AMB</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Starbucks%20Apto%20Toluc.jpg</t>
+  </si>
+  <si>
+    <t>sbmx43147@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Juarez 70 Core</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Starbucks%20Juarez%2070.jpg</t>
+  </si>
+  <si>
+    <t>monica.baltazar@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Monica Luisa Baltazar Alvarez</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17907023732558498002547326873597_Monica%20Luisa%20Baltaza.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38954@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Universidad Anahuac Campus Sur</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17907025416638153292302154181555_Starbucks%20Universida.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38122@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Santa Fe</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Starbucks%20Santa%20Fe.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38773@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks HOSPITAL ABC II</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/image_Starbucks%20HOSPITAL%20A.jpg</t>
+  </si>
+  <si>
+    <t>SBMX38166@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Superama Santa Fe</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/fotos_juntas_izquierda_derecha_Starbucks%20Superama%20S.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/64A3A273-7E9E-4483-98B1-DA9FFAA5E2A0_Starbucks%20Galerias%20A.jpeg</t>
+  </si>
+  <si>
+    <t>sbmx38549@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Galerias Insurgentes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Starbucks%20Galerias%20I.jpg</t>
+  </si>
+  <si>
+    <t>maria.miguel@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Maria Fernanda Miguel Fuentes</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/39ccf74d-49cc-47c1-8a03-f85a99c5dddf_Maria%20Fernanda%20Migue.jpeg</t>
+  </si>
+  <si>
+    <t>carlos.rodriguez@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Carlos Rodriguez Moreno</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Carlos%20Rodriguez%20Mor.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38798@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Corporativo Televisa Santa Fe</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/IMG_20260929_115037_Starbucks%20Corporativ.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/image_Starbucks%20HOSPITAL%20A.jpg</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia%202/1790704506846~2_Starbucks%20Corporativ.jpg</t>
+  </si>
+  <si>
+    <t>sbmx38400@starbucks.com.mx</t>
+  </si>
+  <si>
+    <t>Starbucks Centro Médico ABC Santa Fe</t>
+  </si>
+  <si>
+    <t>https://grupovips-my.sharepoint.com/personal/enrique_cesar_starbucks_com_mx/Documents/Nube_EnriqueCesar/Aplicaciones/Microsoft%20Forms/Sistema%20de%20Evidencias%20OPS/Evidencia_Organizacion_Refrigeradores_Back_Antes/17907048649904553299126803878225_Starbucks%20Ce